--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/EN/EN_MAJAH.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/EN/EN_MAJAH.xlsx
@@ -60,8 +60,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -488,7 +492,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr and Umar’s Rank","description":"$book_name$ $hadith_number$ - $chapter_name$. Praises Abu Bakr and Umar as leaders of the mature people of Paradise, except Prophets and Messengers."},"heading":{"title":"Hadith About Abu Bakr and Umar as Leaders of Paradise","description":"This hadith about Abu Bakr and Umar’s rank repeats a clear praise. The Prophet صلى الله عليه وسلم said Abu Bakr and Umar are the leaders of the mature people of Paradise, from the first and the last, except the Prophets and the Messengers. The narration gives them a high position while also keeping the Prophets and Messengers above that comparison. Its message is simple: these two companions hold a special honor in the words of the Prophet صلى الله عليه وسلم. The hadith is useful for anyone searching for virtues of Abu Bakr and Umar because it names both men directly and connects their rank to the people of Paradise."},"teachings":["Abu Bakr and Umar are praised together in this narration.","Their rank is connected to the people of Paradise.","The Prophets and Messengers are clearly excluded from the comparison.","The hadith teaches respect for those whom the Prophet صلى الله عليه وسلم honored."],"related_hadiths":[{"id":"95","book_id":"6","label":"Sunan Ibn Majah"},{"id":"96","book_id":"6","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr and Umar’s Rank","description":"$book_name$ $hadith_number$ - $chapter_name$. Praises Abu Bakr and Umar as leaders of the mature people of Paradise, except Prophets and Messengers."},"heading":{"title":"Hadith About Abu Bakr and Umar as Leaders of Paradise","description":"This hadith about Abu Bakr and Umar’s rank repeats a clear praise. The Prophet صلى الله عليه وسلم said Abu Bakr and Umar are the leaders of the mature people of Paradise, from the first and the last, except the Prophets and the Messengers. The narration gives them a high position while also keeping the Prophets and Messengers above that comparison. Its message is simple: these two companions hold a special honor in the words of the Prophet صلى الله عليه وسلم. The hadith is useful for anyone searching for virtues of Abu Bakr and Umar because it names both men directly and connects their rank to the people of Paradise."},"teachings":["Abu Bakr and Umar are praised together in this narration.","Their rank is connected to the people of Paradise.","The Prophets and Messengers are clearly excluded from the comparison.","The hadith teaches respect for those whom the Prophet صلى الله عليه وسلم honored."],"related_hadiths":[{"id":"95","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"96","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E2" s="4" t="n"/>
@@ -511,7 +515,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Men and Women Prayer Rows","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم described the best rows for men and women in congregational prayer, showing row order has meaning."},"heading":{"title":"Men and Women Prayer Rows Hadith: Best Rows in Salah","description":"This men and women prayer rows hadith gives a direct statement about row placement in congregational prayer. The Prophet صلى الله عليه وسلم said that the best rows for women are the back rows and the worst are the front rows, while the best rows for men are the front rows and the worst are the back rows. The safest way to explain this is to stay with the text and not add details it does not mention. The hadith about best rows in salah shows that row order matters and that men and women are addressed differently in this narration. It also connects with the wider group of hadiths about straight rows, first rows, and completing the lines."},"teachings":["The hadith describes different row virtues for men and women.","Men are encouraged toward the front rows in this narration.","Women’s back rows are described as better in this narration.","Prayer row order is treated as meaningful, not random."],"related_hadiths":[{"id":"997","book_id":"6","label":"Sunan Ibn Majah"},{"id":"998","book_id":"6","label":"Sunan Ibn Majah"},{"id":"999","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Men and Women Prayer Rows","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم described the best rows for men and women in congregational prayer, showing row order has meaning."},"heading":{"title":"Men and Women Prayer Rows Hadith: Best Rows in Salah","description":"This men and women prayer rows hadith gives a direct statement about row placement in congregational prayer. The Prophet صلى الله عليه وسلم said that the best rows for women are the back rows and the worst are the front rows, while the best rows for men are the front rows and the worst are the back rows. The safest way to explain this is to stay with the text and not add details it does not mention. The hadith about best rows in salah shows that row order matters and that men and women are addressed differently in this narration. It also connects with the wider group of hadiths about straight rows, first rows, and completing the lines."},"teachings":["The hadith describes different row virtues for men and women.","Men are encouraged toward the front rows in this narration.","Women’s back rows are described as better in this narration.","Prayer row order is treated as meaningful, not random."],"related_hadiths":[{"id":"997","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"998","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"999","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E3" s="4" t="n"/>
@@ -534,7 +538,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Rows in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches proper prayer rows for men and women in congregation."},"heading":{"title":"Best Rows in Prayer: A Clear Hadith on Congregation","description":"This hadith about prayer rows gives clear guidance for men and women in congregational prayer. The Prophet صلى الله عليه وسلم said that the best rows for men are the front rows, while the back rows are described as the worst for them. For women, the best rows are the back rows, while the front rows are described as the worst. The message is simple: worship has order, and the prayer row is not random. Each person should take the place that best fits the guidance given in the hadith. This best rows in prayer hadith also shows that small details in salah matter because they help keep the congregation organized, calm, and respectful."},"teachings":["Men are encouraged in this text to stand in the front rows of congregational prayer.","Women are guided in this text toward the back rows in congregation.","Prayer rows should be formed with care, not treated casually.","The hadith shows that order in congregational prayer has value."],"related_hadiths":[{"id":"1000","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1005","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1006","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Rows in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches proper prayer rows for men and women in congregation."},"heading":{"title":"Best Rows in Prayer: A Clear Hadith on Congregation","description":"This hadith about prayer rows gives clear guidance for men and women in congregational prayer. The Prophet صلى الله عليه وسلم said that the best rows for men are the front rows, while the back rows are described as the worst for them. For women, the best rows are the back rows, while the front rows are described as the worst. The message is simple: worship has order, and the prayer row is not random. Each person should take the place that best fits the guidance given in the hadith. This best rows in prayer hadith also shows that small details in salah matter because they help keep the congregation organized, calm, and respectful."},"teachings":["Men are encouraged in this text to stand in the front rows of congregational prayer.","Women are guided in this text toward the back rows in congregation.","Prayer rows should be formed with care, not treated casually.","The hadith shows that order in congregational prayer has value."],"related_hadiths":[{"id":"1000","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1005","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1006","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E4" s="4" t="n"/>
@@ -557,7 +561,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Between Pillars","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against forming prayer rows between pillars in congregation."},"heading":{"title":"Prayer Between Pillars: A Hadith on Proper Rows","description":"This hadith about prayer between pillars speaks about the way rows were managed at the time of the Messenger of Allah صلى الله عليه وسلم. The narrator says they were forbidden to form a row between two pillars, and they were moved away from that place strongly. The wording shows that this was not a light matter in that setting. The focus is on keeping the prayer row proper and suitable for congregational salah. A row broken by pillars can disturb the shape of the line, so this narration points to careful row arrangement. The hadith does not give a long explanation, but it clearly teaches that worshippers should not ignore the physical layout of the mosque when forming rows."},"teachings":["Rows in prayer should be formed in a suitable place.","The Companions were stopped from forming rows between two pillars.","Mosque layout matters when arranging congregational prayer.","Prayer rows should not be treated as an afterthought."],"related_hadiths":[{"id":"1001","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1003","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1004","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Between Pillars","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against forming prayer rows between pillars in congregation."},"heading":{"title":"Prayer Between Pillars: A Hadith on Proper Rows","description":"This hadith about prayer between pillars speaks about the way rows were managed at the time of the Messenger of Allah صلى الله عليه وسلم. The narrator says they were forbidden to form a row between two pillars, and they were moved away from that place strongly. The wording shows that this was not a light matter in that setting. The focus is on keeping the prayer row proper and suitable for congregational salah. A row broken by pillars can disturb the shape of the line, so this narration points to careful row arrangement. The hadith does not give a long explanation, but it clearly teaches that worshippers should not ignore the physical layout of the mosque when forming rows."},"teachings":["Rows in prayer should be formed in a suitable place.","The Companions were stopped from forming rows between two pillars.","Mosque layout matters when arranging congregational prayer.","Prayer rows should not be treated as an afterthought."],"related_hadiths":[{"id":"1001","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1003","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1004","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E5" s="4" t="n"/>
@@ -580,7 +584,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying Alone Behind the Row","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that a person should not pray alone behind the row."},"heading":{"title":"Praying Alone Behind the Row: A Serious Prayer Lesson","description":"This hadith about praying alone behind the row describes a clear event after congregational prayer. The Prophet صلى الله عليه وسلم finished the prayer and saw a man praying by himself behind the row. When the man finished, the Prophet صلى الله عليه وسلم told him to repeat his prayer and said that there is no prayer for the one who is behind the row. The wording is direct and strong. The main lesson is that a person should join the prayer row rather than stand alone behind it when praying in congregation. This hadith on prayer rows shows that congregational salah is not only about praying at the same time. It is also about standing with the group in the proper way."},"teachings":["A person should not stand alone behind the row in congregational prayer.","The Prophet صلى الله عليه وسلم instructed the man to repeat his prayer.","Joining the row is part of proper congregational prayer in this narration.","The prayer row has a clear place in the structure of salah."],"related_hadiths":[{"id":"1004","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1001","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1002","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying Alone Behind the Row","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that a person should not pray alone behind the row."},"heading":{"title":"Praying Alone Behind the Row: A Serious Prayer Lesson","description":"This hadith about praying alone behind the row describes a clear event after congregational prayer. The Prophet صلى الله عليه وسلم finished the prayer and saw a man praying by himself behind the row. When the man finished, the Prophet صلى الله عليه وسلم told him to repeat his prayer and said that there is no prayer for the one who is behind the row. The wording is direct and strong. The main lesson is that a person should join the prayer row rather than stand alone behind it when praying in congregation. This hadith on prayer rows shows that congregational salah is not only about praying at the same time. It is also about standing with the group in the proper way."},"teachings":["A person should not stand alone behind the row in congregational prayer.","The Prophet صلى الله عليه وسلم instructed the man to repeat his prayer.","Joining the row is part of proper congregational prayer in this narration.","The prayer row has a clear place in the structure of salah."],"related_hadiths":[{"id":"1004","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1001","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1002","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E6" s="4" t="n"/>
@@ -603,7 +607,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Repeat Prayer Behind the Row","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith states that a man who prayed alone behind the row was told to repeat."},"heading":{"title":"Repeat Prayer Behind the Row: Hadith on Congregation","description":"This hadith about repeating prayer behind the row is short but very clear. Wabisah bin Ma'bad reported that a man prayed behind the row by himself, and the Prophet صلى الله عليه وسلم commanded him to repeat the prayer. The narration does not add extra details, so the main focus stays on one point: standing alone behind the row was not accepted in this case. This hadith supports the importance of joining the prayer row in congregational salah. It also teaches that the shape and order of the congregation matter. A worshipper should not separate himself from the row when praying with others unless there is a valid reason mentioned elsewhere by scholars."},"teachings":["The man who prayed alone behind the row was commanded to repeat.","Congregational prayer should be performed with the row, not apart from it.","The hadith shows the importance of visible order in salah.","The text keeps attention on the act of standing alone behind the row."],"related_hadiths":[{"id":"1003","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1001","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1002","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Repeat Prayer Behind the Row","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith states that a man who prayed alone behind the row was told to repeat."},"heading":{"title":"Repeat Prayer Behind the Row: Hadith on Congregation","description":"This hadith about repeating prayer behind the row is short but very clear. Wabisah bin Ma'bad reported that a man prayed behind the row by himself, and the Prophet صلى الله عليه وسلم commanded him to repeat the prayer. The narration does not add extra details, so the main focus stays on one point: standing alone behind the row was not accepted in this case. This hadith supports the importance of joining the prayer row in congregational salah. It also teaches that the shape and order of the congregation matter. A worshipper should not separate himself from the row when praying with others unless there is a valid reason mentioned elsewhere by scholars."},"teachings":["The man who prayed alone behind the row was commanded to repeat.","Congregational prayer should be performed with the row, not apart from it.","The hadith shows the importance of visible order in salah.","The text keeps attention on the act of standing alone behind the row."],"related_hadiths":[{"id":"1003","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1001","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1002","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
@@ -626,7 +630,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Filling the Left Side of the Mosque","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith encourages people to fill the left side of the mosque."},"heading":{"title":"Filling the Left Side of the Mosque: A Hadith on Balance","description":"This hadith about the left side of the mosque mentions that the left side had been abandoned. The Prophet صلى الله عليه وسلم said that whoever frequents the left side of the mosque will have two Kifl of reward recorded for him. The narration points to a practical issue: one part of the mosque was being left empty. The answer encouraged people to use that side too. This hadith about filling the mosque teaches that congregational prayer is not only about personal preference. It also includes helping the space of the mosque serve the whole congregation. The text does not cancel the virtue mentioned in other narrations about the right side, but it shows that neglected areas should also be filled."},"teachings":["The left side of the mosque should not be left abandoned.","The hadith mentions reward for frequenting the left side when it was empty.","A worshipper should think about the needs of the congregation.","Prayer spaces should be used in a balanced and orderly way."],"related_hadiths":[{"id":"1005","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1006","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1001","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Filling the Left Side of the Mosque","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith encourages people to fill the left side of the mosque."},"heading":{"title":"Filling the Left Side of the Mosque: A Hadith on Balance","description":"This hadith about the left side of the mosque mentions that the left side had been abandoned. The Prophet صلى الله عليه وسلم said that whoever frequents the left side of the mosque will have two Kifl of reward recorded for him. The narration points to a practical issue: one part of the mosque was being left empty. The answer encouraged people to use that side too. This hadith about filling the mosque teaches that congregational prayer is not only about personal preference. It also includes helping the space of the mosque serve the whole congregation. The text does not cancel the virtue mentioned in other narrations about the right side, but it shows that neglected areas should also be filled."},"teachings":["The left side of the mosque should not be left abandoned.","The hadith mentions reward for frequenting the left side when it was empty.","A worshipper should think about the needs of the congregation.","Prayer spaces should be used in a balanced and orderly way."],"related_hadiths":[{"id":"1005","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1006","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1001","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Maqam Ibrahim as a Place of Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith connects Maqam Ibrahim with the Qur’anic command to pray there."},"heading":{"title":"Maqam Ibrahim as a Place of Prayer: Hadith and Verse","description":"This hadith about Maqam Ibrahim describes what happened after the Messenger of Allah صلى الله عليه وسلم finished Tawaf around the Ka'bah. He came to the Station of Ibrahim, and Umar mentioned the verse in which Allah says to take Maqam Ibrahim as a place of prayer. The narration directly links Tawaf, Maqam Ibrahim, and the Qur'anic wording from Surah Al-Baqarah 2:125. The focus is not on a long legal discussion, but on the clear connection between this sacred place and prayer. For someone searching for Maqam Ibrahim prayer hadith, this text shows the Prophet صلى الله عليه وسلم reaching that station after Tawaf and Umar pointing to the verse about praying there."},"teachings":["Maqam Ibrahim is mentioned in connection with prayer after Tawaf.","The hadith cites the Qur’anic command about taking Maqam Ibrahim as a place of prayer.","Umar identified the Station of Ibrahim in the narration.","The text links worship at the Ka'bah with Qur’anic guidance."],"related_hadiths":[{"id":"1009","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1010","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1020","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Maqam Ibrahim as a Place of Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith connects Maqam Ibrahim with the Qur’anic command to pray there."},"heading":{"title":"Maqam Ibrahim as a Place of Prayer: Hadith and Verse","description":"This hadith about Maqam Ibrahim describes what happened after the Messenger of Allah صلى الله عليه وسلم finished Tawaf around the Ka'bah. He came to the Station of Ibrahim, and Umar mentioned the verse in which Allah says to take Maqam Ibrahim as a place of prayer. The narration directly links Tawaf, Maqam Ibrahim, and the Qur'anic wording from Surah Al-Baqarah 2:125. The focus is not on a long legal discussion, but on the clear connection between this sacred place and prayer. For someone searching for Maqam Ibrahim prayer hadith, this text shows the Prophet صلى الله عليه وسلم reaching that station after Tawaf and Umar pointing to the verse about praying there."},"teachings":["Maqam Ibrahim is mentioned in connection with prayer after Tawaf.","The hadith cites the Qur’anic command about taking Maqam Ibrahim as a place of prayer.","Umar identified the Station of Ibrahim in the narration.","The text links worship at the Ka'bah with Qur’anic guidance."],"related_hadiths":[{"id":"1009","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1010","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1020","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
@@ -672,7 +676,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Beloved People of the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet's stated love for Aishah and her father, Abu Bakr."},"heading":{"title":"Hadith About the Prophet's Beloved People","description":"This hadith about the Prophet's beloved people gives a clear answer to a direct question. Anas narrates that the Messenger of Allah was asked who was most beloved to him among the people. He answered, \"Aishah.\" When he was asked about men, he answered, \"her father,\" meaning Abu Bakr. The main lesson is simple: the Prophet openly honored people of faith and closeness when asked. The narration also shows the high rank of Aishah and Abu Bakr in the Prophet's love. It does not list every virtue of either person. It only records this specific question and answer, so the explanation should stay focused on that point: love, honor, and the special place of Aishah and Abu Bakr in this report."},"teachings":["The Prophet answered questions about love and rank with clear words.","Aishah is named in this narration as the person most beloved to him.","Abu Bakr is indicated as the most beloved among men in this report.","The hadith teaches respect for those whom the Prophet honored."],"related_hadiths":[{"id":"94","book_id":"6","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Beloved People of the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet's stated love for Aishah and her father, Abu Bakr."},"heading":{"title":"Hadith About the Prophet's Beloved People","description":"This hadith about the Prophet's beloved people gives a clear answer to a direct question. Anas narrates that the Messenger of Allah was asked who was most beloved to him among the people. He answered, \"Aishah.\" When he was asked about men, he answered, \"her father,\" meaning Abu Bakr. The main lesson is simple: the Prophet openly honored people of faith and closeness when asked. The narration also shows the high rank of Aishah and Abu Bakr in the Prophet's love. It does not list every virtue of either person. It only records this specific question and answer, so the explanation should stay focused on that point: love, honor, and the special place of Aishah and Abu Bakr in this report."},"teachings":["The Prophet answered questions about love and rank with clear words.","Aishah is named in this narration as the person most beloved to him.","Abu Bakr is indicated as the most beloved among men in this report.","The hadith teaches respect for those whom the Prophet honored."],"related_hadiths":[{"id":"94","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E10" s="4" t="n"/>
@@ -695,7 +699,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Garlic Onion and Mosque Etiquette","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches mosque etiquette about strong smells from garlic and onion."},"heading":{"title":"Garlic Onion and Mosque Etiquette: A Hadith on Smell","description":"This hadith about garlic, onion, and mosque etiquette comes from a Friday sermon of Umar bin Khattab. He spoke about two plants, garlic and onion, and described their smell as offensive. He said that during the time of the Messenger of Allah صلى الله عليه وسلم, when the smell was found on a man, he would be taken out to Al-Baqi'. Then Umar said that whoever must eat them should cook them thoroughly. The teaching is about not harming people in the mosque with bad smells. This hadith does not ban food in general. It focuses on the smell that disturbs worshippers, especially when people gather for prayer."},"teachings":["Strong food smells should not disturb people in the mosque.","Garlic and onion are named in the narration because of their odor.","Umar advised cooking them thoroughly if someone needed to eat them.","Mosque etiquette includes care for others during worship."],"related_hadiths":[{"id":"1015","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1016","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1012","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Garlic Onion and Mosque Etiquette","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches mosque etiquette about strong smells from garlic and onion."},"heading":{"title":"Garlic Onion and Mosque Etiquette: A Hadith on Smell","description":"This hadith about garlic, onion, and mosque etiquette comes from a Friday sermon of Umar bin Khattab. He spoke about two plants, garlic and onion, and described their smell as offensive. He said that during the time of the Messenger of Allah صلى الله عليه وسلم, when the smell was found on a man, he would be taken out to Al-Baqi'. Then Umar said that whoever must eat them should cook them thoroughly. The teaching is about not harming people in the mosque with bad smells. This hadith does not ban food in general. It focuses on the smell that disturbs worshippers, especially when people gather for prayer."},"teachings":["Strong food smells should not disturb people in the mosque.","Garlic and onion are named in the narration because of their odor.","Umar advised cooking them thoroughly if someone needed to eat them.","Mosque etiquette includes care for others during worship."],"related_hadiths":[{"id":"1015","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1016","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1012","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E11" s="4" t="n"/>
@@ -718,7 +722,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding the Mosque After Eating Strong Smells","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns those who eat from the plant not to come to the mosque."},"heading":{"title":"Avoiding the Mosque After Strong Smells: A Hadith Lesson","description":"This hadith about avoiding the mosque after eating from this plant gives a short and serious instruction. Ibn Umar narrated that the Messenger of Allah صلى الله عليه وسلم said whoever eats anything from this plant should not come to the mosque. The narration does not name the plant in this line, but it comes in the same theme as nearby reports about strong-smelling foods. So the safe explanation is that the text warns against coming to the mosque while carrying a smell that may disturb others. This hadith about mosque etiquette teaches that personal choices can affect the congregation. A worshipper should not bring avoidable annoyance into a place where people gather for prayer."},"teachings":["The hadith tells the eater of this plant not to come to the mosque.","The warning is tied to avoiding annoyance in the mosque.","A worshipper should think about how personal smell affects others.","Mosque etiquette includes care before arriving for prayer."],"related_hadiths":[{"id":"1015","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1014","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1012","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding the Mosque After Eating Strong Smells","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns those who eat from the plant not to come to the mosque."},"heading":{"title":"Avoiding the Mosque After Strong Smells: A Hadith Lesson","description":"This hadith about avoiding the mosque after eating from this plant gives a short and serious instruction. Ibn Umar narrated that the Messenger of Allah صلى الله عليه وسلم said whoever eats anything from this plant should not come to the mosque. The narration does not name the plant in this line, but it comes in the same theme as nearby reports about strong-smelling foods. So the safe explanation is that the text warns against coming to the mosque while carrying a smell that may disturb others. This hadith about mosque etiquette teaches that personal choices can affect the congregation. A worshipper should not bring avoidable annoyance into a place where people gather for prayer."},"teachings":["The hadith tells the eater of this plant not to come to the mosque.","The warning is tied to avoiding annoyance in the mosque.","A worshipper should think about how personal smell affects others.","Mosque etiquette includes care before arriving for prayer."],"related_hadiths":[{"id":"1015","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1014","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1012","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -741,7 +745,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Greeting During Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet responding to greetings in prayer by gesture."},"heading":{"title":"Greeting During Prayer: Responding by Gesture","description":"This hadith about greeting during prayer describes the Prophet صلى الله عليه وسلم praying in the mosque at Quba'. Some men from the Ansar came and greeted him. Abdullah bin Umar asked Suhaib how the Messenger of Allah صلى الله عليه وسلم responded to them while he was praying. Suhaib said that he gestured with his hand. The main lesson is that the Prophet صلى الله عليه وسلم did not answer with normal speech during prayer in this report. He responded by a hand gesture. This hadith is useful for people searching for how to respond to salam during salah. The wording stays focused on one event: greeting came while he was praying, and the response was a gesture."},"teachings":["The Prophet صلى الله عليه وسلم responded to greetings during prayer with a hand gesture.","The hadith shows that normal speech was not used in this event.","The narration connects prayer focus with respectful response.","Gestures may be used in prayer as shown in this report."],"related_hadiths":[{"id":"1018","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1019","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1037","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Greeting During Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet responding to greetings in prayer by gesture."},"heading":{"title":"Greeting During Prayer: Responding by Gesture","description":"This hadith about greeting during prayer describes the Prophet صلى الله عليه وسلم praying in the mosque at Quba'. Some men from the Ansar came and greeted him. Abdullah bin Umar asked Suhaib how the Messenger of Allah صلى الله عليه وسلم responded to them while he was praying. Suhaib said that he gestured with his hand. The main lesson is that the Prophet صلى الله عليه وسلم did not answer with normal speech during prayer in this report. He responded by a hand gesture. This hadith is useful for people searching for how to respond to salam during salah. The wording stays focused on one event: greeting came while he was praying, and the response was a gesture."},"teachings":["The Prophet صلى الله عليه وسلم responded to greetings during prayer with a hand gesture.","The hadith shows that normal speech was not used in this event.","The narration connects prayer focus with respectful response.","Gestures may be used in prayer as shown in this report."],"related_hadiths":[{"id":"1018","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1019","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1037","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
@@ -764,7 +768,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Salam While Praying","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet gesturing when greeted during prayer."},"heading":{"title":"Salam While Praying: A Hadith on Prayer Focus","description":"This hadith about salam while praying reports that Jabir greeted the Prophet صلى الله عليه وسلم while the Prophet صلى الله عليه وسلم was performing prayer. The Prophet صلى الله عليه وسلم gestured to him. After finishing the prayer, he called Jabir and explained that Jabir had greeted him while he was praying. The narration teaches two things directly from the text: the Prophet صلى الله عليه وسلم did not give a spoken reply during the prayer, and he later clarified the matter when the prayer was complete. This responding to salam in salah hadith shows the special focus of prayer. It also shows kindness in correction, because the Prophet صلى الله عليه وسلم addressed Jabir after finishing rather than interrupting the prayer with speech."},"teachings":["The Prophet صلى الله عليه وسلم gestured when greeted during prayer.","He explained the matter after the prayer was finished.","The hadith shows that prayer has a focused state.","Correction can be given calmly after worship is complete."],"related_hadiths":[{"id":"1017","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1019","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1037","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Salam While Praying","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet gesturing when greeted during prayer."},"heading":{"title":"Salam While Praying: A Hadith on Prayer Focus","description":"This hadith about salam while praying reports that Jabir greeted the Prophet صلى الله عليه وسلم while the Prophet صلى الله عليه وسلم was performing prayer. The Prophet صلى الله عليه وسلم gestured to him. After finishing the prayer, he called Jabir and explained that Jabir had greeted him while he was praying. The narration teaches two things directly from the text: the Prophet صلى الله عليه وسلم did not give a spoken reply during the prayer, and he later clarified the matter when the prayer was complete. This responding to salam in salah hadith shows the special focus of prayer. It also shows kindness in correction, because the Prophet صلى الله عليه وسلم addressed Jabir after finishing rather than interrupting the prayer with speech."},"teachings":["The Prophet صلى الله عليه وسلم gestured when greeted during prayer.","He explained the matter after the prayer was finished.","The hadith shows that prayer has a focused state.","Correction can be given calmly after worship is complete."],"related_hadiths":[{"id":"1017","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1019","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1037","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E14" s="4" t="n"/>
@@ -787,7 +791,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Beloved Companions","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah names Abu Bakr, Umar, and Abu Ubaidah among the Companions beloved to the Prophet."},"heading":{"title":"Hadith About the Prophet's Beloved Companions","description":"This hadith about the Prophet's beloved Companions records a careful question asked to Aishah. Abdullah bin Shaqiq asked which Companion was most beloved to the Prophet. Aishah answered, \"Abu Bakr.\" When asked who came next, she said, \"Umar.\" When asked again, she said, \"Abu Ubaidah.\" The narration is short, but it carries a clear message about the honor of these Companions. It does not give a long list or discuss every Companion. It only reports Aishah's answer to the order asked in that moment. For readers searching for a hadith about Abu Bakr, Umar, and Abu Ubaidah, this report highlights their closeness to the Messenger of Allah as stated by Aishah."},"teachings":["Aishah was asked directly about the Companions beloved to the Prophet.","Abu Bakr is named first in her answer.","Umar and Abu Ubaidah are also named in this report.","The narration teaches careful respect when speaking about the Companions."],"related_hadiths":[{"id":"95","book_id":"6","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","label":"Sunan Ibn Majah"},{"id":"135","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Beloved Companions","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah names Abu Bakr, Umar, and Abu Ubaidah among the Companions beloved to the Prophet."},"heading":{"title":"Hadith About the Prophet's Beloved Companions","description":"This hadith about the Prophet's beloved Companions records a careful question asked to Aishah. Abdullah bin Shaqiq asked which Companion was most beloved to the Prophet. Aishah answered, \"Abu Bakr.\" When asked who came next, she said, \"Umar.\" When asked again, she said, \"Abu Ubaidah.\" The narration is short, but it carries a clear message about the honor of these Companions. It does not give a long list or discuss every Companion. It only reports Aishah's answer to the order asked in that moment. For readers searching for a hadith about Abu Bakr, Umar, and Abu Ubaidah, this report highlights their closeness to the Messenger of Allah as stated by Aishah."},"teachings":["Aishah was asked directly about the Companions beloved to the Prophet.","Abu Bakr is named first in her answer.","Umar and Abu Ubaidah are also named in this report.","The narration teaches careful respect when speaking about the Companions."],"related_hadiths":[{"id":"95","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"135","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E15" s="4" t="n"/>
@@ -810,7 +814,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umar's Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration says the people of heaven rejoiced when Umar became Muslim."},"heading":{"title":"Hadith About Umar's Islam and Joy in Heaven","description":"This hadith about Umar's Islam reports a striking statement from the narration of Ibn Abbas. It says that when Umar became Muslim, Jibril came down and told the Prophet that the people of heaven were rejoicing because of Umar's Islam. The core topic is the honor given to Umar's acceptance of Islam in this report. The hadith does not describe the full story of his conversion, nor does it explain the details of what happened before or after it. It simply connects Umar becoming Muslim with joy among the people of heaven. For someone searching for a hadith about Umar becoming Muslim, this narration points to the value and impact of his Islam as mentioned in the text."},"teachings":["Umar's acceptance of Islam is presented as a cause of joy in this narration.","The report links Jibril with delivering this message to the Prophet.","The hadith highlights Umar's special place in this specific wording.","The narration should be read for what it says, without adding extra story details."],"related_hadiths":[{"id":"95","book_id":"6","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umar's Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration says the people of heaven rejoiced when Umar became Muslim."},"heading":{"title":"Hadith About Umar's Islam and Joy in Heaven","description":"This hadith about Umar's Islam reports a striking statement from the narration of Ibn Abbas. It says that when Umar became Muslim, Jibril came down and told the Prophet that the people of heaven were rejoicing because of Umar's Islam. The core topic is the honor given to Umar's acceptance of Islam in this report. The hadith does not describe the full story of his conversion, nor does it explain the details of what happened before or after it. It simply connects Umar becoming Muslim with joy among the people of heaven. For someone searching for a hadith about Umar becoming Muslim, this narration points to the value and impact of his Islam as mentioned in the text."},"teachings":["Umar's acceptance of Islam is presented as a cause of joy in this narration.","The report links Jibril with delivering this message to the Prophet.","The hadith highlights Umar's special place in this specific wording.","The narration should be read for what it says, without adding extra story details."],"related_hadiths":[{"id":"95","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E16" s="4" t="n"/>
@@ -833,7 +837,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umar and Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions special greetings and entry into Paradise for Umar."},"heading":{"title":"Hadith About Umar and Paradise","description":"This hadith about Umar and Paradise reports words attributed to the Messenger of Allah about Umar's honor. Ubayy bin Ka'b narrates that Umar will be the first person with whom Allah will shake hands, the first to be greeted with Salam, and the first to be taken by the hand and admitted into Paradise. The wording is very specific, so the explanation should stay close to it. It is a narration about rank, greeting, and entry into Paradise as described in the text. It does not give a general rule for all people, nor does it discuss the full details of the Hereafter. Its message is centered on the virtue of Umar in this report."},"teachings":["The narration presents Umar with a special honor in relation to Paradise.","It mentions Salam as a mark of honor in the wording.","The text connects Umar with being taken by the hand and admitted into Paradise.","The hadith should be explained according to its exact wording."],"related_hadiths":[{"id":"95","book_id":"6","label":"Sunan Ibn Majah"},{"id":"96","book_id":"6","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umar and Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions special greetings and entry into Paradise for Umar."},"heading":{"title":"Hadith About Umar and Paradise","description":"This hadith about Umar and Paradise reports words attributed to the Messenger of Allah about Umar's honor. Ubayy bin Ka'b narrates that Umar will be the first person with whom Allah will shake hands, the first to be greeted with Salam, and the first to be taken by the hand and admitted into Paradise. The wording is very specific, so the explanation should stay close to it. It is a narration about rank, greeting, and entry into Paradise as described in the text. It does not give a general rule for all people, nor does it discuss the full details of the Hereafter. Its message is centered on the virtue of Umar in this report."},"teachings":["The narration presents Umar with a special honor in relation to Paradise.","It mentions Salam as a mark of honor in the wording.","The text connects Umar with being taken by the hand and admitted into Paradise.","The hadith should be explained according to its exact wording."],"related_hadiths":[{"id":"95","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"96","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E17" s="4" t="n"/>
@@ -856,7 +860,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Etiquette: Praying With Braided Hair","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet forbade a man from praying with braided hair, showing care for outward prayer manners and humble posture."},"heading":{"title":"Hadith About Praying With Braided Hair","description":"This Hadith focuses on hadith about praying with braided hair. Abu Rafi saw Hasan bin Ali praying while his hair was braided, so he undid it or told him not to do that. He then said that the Messenger of Allah forbade a man from performing prayer while his hair was braided. The narration is direct and should not be stretched beyond its wording. It speaks about a man praying with hair braided or tied in that way. The teaching is about salah manners and the way a worshipper presents himself in prayer. It also shows that companions corrected prayer practice when they knew a clear instruction from the Prophet."},"teachings":["A man should not pray with his hair braided as stated in this narration.","Correcting prayer manners can be done when based on clear prophetic instruction.","Outward prayer conduct matters alongside recitation and movement.","The report limits the ruling to the described act: praying with braided hair."],"related_hadiths":[{"id":"810","book_id":"1","label":"Sahih Bukhari"},{"id":"815","book_id":"1","label":"Sahih Bukhari"},{"id":"816","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Etiquette: Praying With Braided Hair","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet forbade a man from praying with braided hair, showing care for outward prayer manners and humble posture."},"heading":{"title":"Hadith About Praying With Braided Hair","description":"This Hadith focuses on hadith about praying with braided hair. Abu Rafi saw Hasan bin Ali praying while his hair was braided, so he undid it or told him not to do that. He then said that the Messenger of Allah forbade a man from performing prayer while his hair was braided. The narration is direct and should not be stretched beyond its wording. It speaks about a man praying with hair braided or tied in that way. The teaching is about salah manners and the way a worshipper presents himself in prayer. It also shows that companions corrected prayer practice when they knew a clear instruction from the Prophet."},"teachings":["A man should not pray with his hair braided as stated in this narration.","Correcting prayer manners can be done when based on clear prophetic instruction.","Outward prayer conduct matters alongside recitation and movement.","The report limits the ruling to the described act: praying with braided hair."],"related_hadiths":[{"id":"810","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"815","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"816","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E18" s="4" t="n"/>
@@ -879,7 +883,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Strengthen Islam with Umar","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asks Allah to strengthen Islam through Umar bin Khattab in particular."},"heading":{"title":"Hadith About Strengthening Islam with Umar","description":"This hadith about strengthening Islam with Umar is short and direct. Aishah narrates that the Messenger of Allah said, \"O Allah! Strengthen Islam with Umar bin Khattab in particular.\" The core message is a supplication for Islam to be strengthened through Umar. The narration does not explain the setting, the time, or a wider story. It only gives the Prophet's prayer as reported here. For readers searching for the dua for Umar bin Khattab or a hadith about Umar's virtue, this report shows a clear link between Umar and strength for Islam. The wording also teaches that honor belongs to Allah, since the Prophet asks Allah to give strength through whomever He wills."},"teachings":["The Prophet made a supplication connected to Umar in this report.","The hadith links Umar with strength for Islam.","The wording shows that strength comes from Allah.","The narration is focused on one specific dua, not a long biography."],"related_hadiths":[{"id":"97","book_id":"6","label":"Sunan Ibn Majah"},{"id":"95","book_id":"6","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Strengthen Islam with Umar","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asks Allah to strengthen Islam through Umar bin Khattab in particular."},"heading":{"title":"Hadith About Strengthening Islam with Umar","description":"This hadith about strengthening Islam with Umar is short and direct. Aishah narrates that the Messenger of Allah said, \"O Allah! Strengthen Islam with Umar bin Khattab in particular.\" The core message is a supplication for Islam to be strengthened through Umar. The narration does not explain the setting, the time, or a wider story. It only gives the Prophet's prayer as reported here. For readers searching for the dua for Umar bin Khattab or a hadith about Umar's virtue, this report shows a clear link between Umar and strength for Islam. The wording also teaches that honor belongs to Allah, since the Prophet asks Allah to give strength through whomever He wills."},"teachings":["The Prophet made a supplication connected to Umar in this report.","The hadith links Umar with strength for Islam.","The wording shows that strength comes from Allah.","The narration is focused on one specific dua, not a long biography."],"related_hadiths":[{"id":"97","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"95","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E19" s="4" t="n"/>
@@ -902,7 +906,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr and Umar's Rank","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali states that the best people after the Prophet are Abu Bakr, then Umar."},"heading":{"title":"Hadith About Abu Bakr and Umar's Rank","description":"This hadith about Abu Bakr and Umar's rank is narrated from Abdullah bin Salimah, who heard Ali say that the best of people after the Messenger of Allah is Abu Bakr, and the best after Abu Bakr is Umar. The narration is important because it reports Ali's own statement about their rank. It does not discuss a debate, a later event, or a full list of Companions. It simply presents a clear order: the Messenger of Allah, then Abu Bakr, then Umar. For users searching for a hadith about the best people after the Prophet, this narration gives a short and focused answer from Ali's words."},"teachings":["Ali named Abu Bakr as the best after the Messenger of Allah.","Ali then named Umar as the best after Abu Bakr.","The report teaches respect for the rank of the early Companions.","The wording is simple and should not be stretched beyond its statement."],"related_hadiths":[{"id":"95","book_id":"6","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr and Umar's Rank","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali states that the best people after the Prophet are Abu Bakr, then Umar."},"heading":{"title":"Hadith About Abu Bakr and Umar's Rank","description":"This hadith about Abu Bakr and Umar's rank is narrated from Abdullah bin Salimah, who heard Ali say that the best of people after the Messenger of Allah is Abu Bakr, and the best after Abu Bakr is Umar. The narration is important because it reports Ali's own statement about their rank. It does not discuss a debate, a later event, or a full list of Companions. It simply presents a clear order: the Messenger of Allah, then Abu Bakr, then Umar. For users searching for a hadith about the best people after the Prophet, this narration gives a short and focused answer from Ali's words."},"teachings":["Ali named Abu Bakr as the best after the Messenger of Allah.","Ali then named Umar as the best after Abu Bakr.","The report teaches respect for the rank of the early Companions.","The wording is simple and should not be stretched beyond its statement."],"related_hadiths":[{"id":"95","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E20" s="4" t="n"/>
@@ -925,7 +929,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Posture and Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes proper ablution, facing the Qiblah, bowing, prostration, and sitting in prayer."},"heading":{"title":"Prayer Posture Hadith: Wudu, Qiblah, Ruku and Sujud","description":"This Hadith answers the question: how did the Messenger of Allah (صلى الله عليه وسلم) perform prayer? ‘Aishah described several clear actions. He would say Bismillah when beginning ablution, perform wudu properly, stand facing the Qiblah, say the Takbir, and raise his hands to shoulder level. In ruku, he placed his hands on his knees and kept his arms away from his sides. After rising, he straightened his back and stood a little longer than the standing of those being addressed. In sujud, his hands faced the Qiblah, and he kept his arms away from his sides as much as possible. The Hadith also describes sitting on the left foot while keeping the right foot upright."},"teachings":["Proper wudu comes before prayer in this description.","Facing the Qiblah is part of the prayer action mentioned here.","The Prophet’s ruku and sujud were done with clear body posture.","Sitting in prayer is described with the left foot under and the right foot upright."],"related_hadiths":[{"id":"1061","book_id":"6","label":"Sunan Ibn Majah"},{"id":"631","book_id":"1","label":"Sahih Bukhari"},{"id":"828","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Posture and Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes proper ablution, facing the Qiblah, bowing, prostration, and sitting in prayer."},"heading":{"title":"Prayer Posture Hadith: Wudu, Qiblah, Ruku and Sujud","description":"This Hadith answers the question: how did the Messenger of Allah (صلى الله عليه وسلم) perform prayer? ‘Aishah described several clear actions. He would say Bismillah when beginning ablution, perform wudu properly, stand facing the Qiblah, say the Takbir, and raise his hands to shoulder level. In ruku, he placed his hands on his knees and kept his arms away from his sides. After rising, he straightened his back and stood a little longer than the standing of those being addressed. In sujud, his hands faced the Qiblah, and he kept his arms away from his sides as much as possible. The Hadith also describes sitting on the left foot while keeping the right foot upright."},"teachings":["Proper wudu comes before prayer in this description.","Facing the Qiblah is part of the prayer action mentioned here.","The Prophet’s ruku and sujud were done with clear body posture.","Sitting in prayer is described with the left foot under and the right foot upright."],"related_hadiths":[{"id":"1061","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"631","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"828","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E21" s="4" t="n"/>
@@ -948,7 +952,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umar's Palace in Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet describes seeing a palace in Paradise linked to Umar in a dream."},"heading":{"title":"Hadith About Umar's Palace in Paradise","description":"This hadith about Umar's palace in Paradise is narrated by Abu Hurairah. The Prophet said that while sleeping, he saw himself in Paradise and saw a woman performing ablution beside a palace. When he asked whose palace it was, he was told it belonged to Umar. The Prophet then remembered Umar's protective jealousy and turned away. Abu Hurairah adds that Umar wept and spoke with deep respect to the Messenger of Allah. The narration focuses on a dream, a palace in Paradise, and Umar's respectful reaction. It does not describe the palace in detail, nor does it explain the identity of the woman. The safe explanation is to keep the focus on the honor shown to Umar in this report."},"teachings":["The Prophet described a dream in which Umar had a palace in Paradise.","Umar's protective jealousy is mentioned in the text.","Umar responded with humility and deep respect.","The narration teaches careful speech when explaining reports about Paradise."],"related_hadiths":[{"id":"96","book_id":"6","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umar's Palace in Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet describes seeing a palace in Paradise linked to Umar in a dream."},"heading":{"title":"Hadith About Umar's Palace in Paradise","description":"This hadith about Umar's palace in Paradise is narrated by Abu Hurairah. The Prophet said that while sleeping, he saw himself in Paradise and saw a woman performing ablution beside a palace. When he asked whose palace it was, he was told it belonged to Umar. The Prophet then remembered Umar's protective jealousy and turned away. Abu Hurairah adds that Umar wept and spoke with deep respect to the Messenger of Allah. The narration focuses on a dream, a palace in Paradise, and Umar's respectful reaction. It does not describe the palace in detail, nor does it explain the identity of the woman. The safe explanation is to keep the focus on the honor shown to Umar in this report."},"teachings":["The Prophet described a dream in which Umar had a palace in Paradise.","Umar's protective jealousy is mentioned in the text.","Umar responded with humility and deep respect.","The narration teaches careful speech when explaining reports about Paradise."],"related_hadiths":[{"id":"96","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"97","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E22" s="4" t="n"/>
@@ -971,7 +975,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Truth on Umar's Tongue","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet says Allah placed truth on Umar's tongue and he speaks with it."},"heading":{"title":"Hadith About Truth on Umar's Tongue","description":"This hadith about truth on Umar's tongue is narrated by Abu Dharr. He heard the Messenger of Allah say that Allah placed the truth on Umar's tongue and that Umar speaks with that truth. The core topic is Umar's truthfulness and right speech as mentioned in this narration. The hadith does not say that Umar was a prophet, nor does it make every personal action a separate rule. It simply praises the truth placed on his tongue in the wording of the report. For readers searching for \"Allah placed truth on Umar's tongue,\" this narration is the direct source in this batch and should be explained with balance and respect."},"teachings":["The Prophet praised Umar's speech in connection with truth.","The narration attributes this honor to Allah.","The hadith teaches the value of truthful speech.","The wording should not be used to add meanings that are not stated."],"related_hadiths":[{"id":"97","book_id":"6","label":"Sunan Ibn Majah"},{"id":"95","book_id":"6","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Truth on Umar's Tongue","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet says Allah placed truth on Umar's tongue and he speaks with it."},"heading":{"title":"Hadith About Truth on Umar's Tongue","description":"This hadith about truth on Umar's tongue is narrated by Abu Dharr. He heard the Messenger of Allah say that Allah placed the truth on Umar's tongue and that Umar speaks with that truth. The core topic is Umar's truthfulness and right speech as mentioned in this narration. The hadith does not say that Umar was a prophet, nor does it make every personal action a separate rule. It simply praises the truth placed on his tongue in the wording of the report. For readers searching for \"Allah placed truth on Umar's tongue,\" this narration is the direct source in this batch and should be explained with balance and respect."},"teachings":["The Prophet praised Umar's speech in connection with truth.","The narration attributes this honor to Allah.","The hadith teaches the value of truthful speech.","The wording should not be used to add meanings that are not stated."],"related_hadiths":[{"id":"97","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"95","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"100","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E23" s="4" t="n"/>
@@ -994,7 +998,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Friday Adhan Timing","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith shows the Friday Adhan was called when the shadow was like a sandal strap."},"heading":{"title":"Friday Adhan Timing in the Prophet’s Time","description":"This Hadith gives a clear picture of Friday Adhan timing during the time of the Messenger of Allah (صلى الله عليه وسلم). The report says that the Mu’adh-dhin would call the Adhan on Fridays when the shadow was like a sandal strap. The main lesson is about the timing connected to Jumu’ah prayer, not a long discussion about later practice. The wording is simple: the call was made when a small shadow had appeared. For someone searching for a hadith about Friday Adhan, this narration points to how carefully the Companions observed prayer times. It also shows that the Adhan was tied to a real, visible sign of time, not guesswork."},"teachings":["The Friday Adhan was connected to a visible sign of time.","The Companions preserved details of the Prophet’s Friday practice.","Jumu’ah prayer had an organized call to gather people.","The Hadith teaches care and order in acts of worship."],"related_hadiths":[{"id":"1102","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1103","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Friday Adhan Timing","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith shows the Friday Adhan was called when the shadow was like a sandal strap."},"heading":{"title":"Friday Adhan Timing in the Prophet’s Time","description":"This Hadith gives a clear picture of Friday Adhan timing during the time of the Messenger of Allah (صلى الله عليه وسلم). The report says that the Mu’adh-dhin would call the Adhan on Fridays when the shadow was like a sandal strap. The main lesson is about the timing connected to Jumu’ah prayer, not a long discussion about later practice. The wording is simple: the call was made when a small shadow had appeared. For someone searching for a hadith about Friday Adhan, this narration points to how carefully the Companions observed prayer times. It also shows that the Adhan was tied to a real, visible sign of time, not guesswork."},"teachings":["The Friday Adhan was connected to a visible sign of time.","The Companions preserved details of the Prophet’s Friday practice.","Jumu’ah prayer had an organized call to gather people.","The Hadith teaches care and order in acts of worship."],"related_hadiths":[{"id":"1102","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1103","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E24" s="4" t="n"/>
@@ -1017,7 +1021,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Friday Prayer and Qailulah","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas describes praying Jumu’ah, returning home, and then taking the midday rest."},"heading":{"title":"Friday Prayer and Qailulah After Jumu’ah","description":"This Hadith is short, but it gives a simple view of Friday prayer in the time of the Companions. Anas said they used to perform the Friday prayer, then return and take a Qailulah, meaning a midday nap or rest. The focus is not on making a new rule from the text, but on showing the order of their Friday routine. They prayed first, then went back for rest. For people searching for a hadith about Jumu’ah prayer and Qailulah, this narration shows that Friday worship was part of daily life in a natural and balanced way. Prayer came first, and rest came after it."},"teachings":["The Companions placed Friday prayer before their midday rest.","Jumu’ah was treated as a central part of the day.","Rest after worship is mentioned as part of their routine.","The Hadith shows a simple pattern: pray, return, and rest."],"related_hadiths":[{"id":"1101","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1118","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Friday Prayer and Qailulah","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas describes praying Jumu’ah, returning home, and then taking the midday rest."},"heading":{"title":"Friday Prayer and Qailulah After Jumu’ah","description":"This Hadith is short, but it gives a simple view of Friday prayer in the time of the Companions. Anas said they used to perform the Friday prayer, then return and take a Qailulah, meaning a midday nap or rest. The focus is not on making a new rule from the text, but on showing the order of their Friday routine. They prayed first, then went back for rest. For people searching for a hadith about Jumu’ah prayer and Qailulah, this narration shows that Friday worship was part of daily life in a natural and balanced way. Prayer came first, and rest came after it."},"teachings":["The Companions placed Friday prayer before their midday rest.","Jumu’ah was treated as a central part of the day.","Rest after worship is mentioned as part of their routine.","The Hadith shows a simple pattern: pray, return, and rest."],"related_hadiths":[{"id":"1101","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1118","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E25" s="4" t="n"/>
@@ -1040,7 +1044,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Friday Sermons","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم delivered two Friday sermons and sat briefly between them."},"heading":{"title":"Two Friday Sermons in the Jumu’ah Khutbah","description":"This Hadith describes the form of the Friday sermon of the Prophet (صلى الله عليه وسلم). Ibn ‘Umar narrated that the Prophet (صلى الله عليه وسلم) used to deliver two sermons and sit briefly between them. One narrator added that the sermons were delivered while standing. The core topic is the Jumu’ah khutbah structure: two parts with a short sitting between them. The Hadith does not add extra details about length, topic, or wording in this report. It simply shows the repeated practice that was remembered and passed on. For anyone searching for a hadith about two khutbahs on Friday, this narration gives a direct and clear basis from the Prophet’s own practice."},"teachings":["The Friday khutbah had two sermons.","The Prophet صلى الله عليه وسلم sat briefly between the two sermons.","The sermon was delivered while standing according to the added wording.","The Companions carefully reported the form of Jumu’ah worship."],"related_hadiths":[{"id":"1105","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1106","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Friday Sermons","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم delivered two Friday sermons and sat briefly between them."},"heading":{"title":"Two Friday Sermons in the Jumu’ah Khutbah","description":"This Hadith describes the form of the Friday sermon of the Prophet (صلى الله عليه وسلم). Ibn ‘Umar narrated that the Prophet (صلى الله عليه وسلم) used to deliver two sermons and sit briefly between them. One narrator added that the sermons were delivered while standing. The core topic is the Jumu’ah khutbah structure: two parts with a short sitting between them. The Hadith does not add extra details about length, topic, or wording in this report. It simply shows the repeated practice that was remembered and passed on. For anyone searching for a hadith about two khutbahs on Friday, this narration gives a direct and clear basis from the Prophet’s own practice."},"teachings":["The Friday khutbah had two sermons.","The Prophet صلى الله عليه وسلم sat briefly between the two sermons.","The sermon was delivered while standing according to the added wording.","The Companions carefully reported the form of Jumu’ah worship."],"related_hadiths":[{"id":"1105","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1106","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E26" s="4" t="n"/>
@@ -1063,7 +1067,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Moderate Khutbah and Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم gave a moderate sermon, recited verses, remembered Allah, and prayed moderately."},"heading":{"title":"Moderate Khutbah and Prayer in Jumu’ah","description":"This Hadith gives more detail about the Prophet’s Friday sermon. Jabir bin Samurah said that the Prophet (صلى الله عليه وسلم) would deliver the sermon standing, sit down, then stand again. He would recite verses and remember Allah. The report then says his sermon was moderate and his prayer was moderate, meaning neither too long nor too short as explained in the translation. This is a clear hadith about moderate khutbah and prayer. It shows balance in public worship: enough teaching, recitation, and remembrance, without making the sermon or prayer overly heavy. The text is a helpful reminder that the Prophet’s way combined meaning, worship, and ease."},"teachings":["The Prophet صلى الله عليه وسلم recited verses during the sermon.","He remembered Allah during the khutbah.","His sermon was moderate in length.","His prayer was also moderate, neither too long nor too short."],"related_hadiths":[{"id":"1103","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1105","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Moderate Khutbah and Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم gave a moderate sermon, recited verses, remembered Allah, and prayed moderately."},"heading":{"title":"Moderate Khutbah and Prayer in Jumu’ah","description":"This Hadith gives more detail about the Prophet’s Friday sermon. Jabir bin Samurah said that the Prophet (صلى الله عليه وسلم) would deliver the sermon standing, sit down, then stand again. He would recite verses and remember Allah. The report then says his sermon was moderate and his prayer was moderate, meaning neither too long nor too short as explained in the translation. This is a clear hadith about moderate khutbah and prayer. It shows balance in public worship: enough teaching, recitation, and remembrance, without making the sermon or prayer overly heavy. The text is a helpful reminder that the Prophet’s way combined meaning, worship, and ease."},"teachings":["The Prophet صلى الله عليه وسلم recited verses during the sermon.","He remembered Allah during the khutbah.","His sermon was moderate in length.","His prayer was also moderate, neither too long nor too short."],"related_hadiths":[{"id":"1103","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1105","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E27" s="4" t="n"/>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Staff in Friday Khutbah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم leaned on a bow during battlefield speech and on a staff for the Friday sermon."},"heading":{"title":"Staff in Friday Khutbah and Bow in Battle Speech","description":"This Hadith mentions two different settings and keeps them separate. When the Messenger of Allah (صلى الله عليه وسلم) delivered a speech on the battlefield, he leaned on a bow. When he delivered the Friday sermon, he leaned on his staff. The core topic is the Prophet’s manner during public speech, especially the staff in Friday khutbah. The narration does not say these two situations were the same. It clearly names one practice for battle and another for Jumu’ah. This helps the reader avoid mixing details. The Hadith also shows that the Companions noticed how the Prophet (صلى الله عليه وسلم) stood and what he used while addressing people in different places."},"teachings":["The Prophet صلى الله عليه وسلم leaned on a bow when speaking on the battlefield.","He leaned on a staff during the Friday sermon.","The Hadith separates battlefield speech from Jumu’ah khutbah.","The Companions preserved practical details of the Prophet’s public address."],"related_hadiths":[{"id":"1103","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1105","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Staff in Friday Khutbah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم leaned on a bow during battlefield speech and on a staff for the Friday sermon."},"heading":{"title":"Staff in Friday Khutbah and Bow in Battle Speech","description":"This Hadith mentions two different settings and keeps them separate. When the Messenger of Allah (صلى الله عليه وسلم) delivered a speech on the battlefield, he leaned on a bow. When he delivered the Friday sermon, he leaned on his staff. The core topic is the Prophet’s manner during public speech, especially the staff in Friday khutbah. The narration does not say these two situations were the same. It clearly names one practice for battle and another for Jumu’ah. This helps the reader avoid mixing details. The Hadith also shows that the Companions noticed how the Prophet (صلى الله عليه وسلم) stood and what he used while addressing people in different places."},"teachings":["The Prophet صلى الله عليه وسلم leaned on a bow when speaking on the battlefield.","He leaned on a staff during the Friday sermon.","The Hadith separates battlefield speech from Jumu’ah khutbah.","The Companions preserved practical details of the Prophet’s public address."],"related_hadiths":[{"id":"1103","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1105","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E28" s="4" t="n"/>
@@ -1109,7 +1113,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Salam on the Pulpit","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم would greet the people with Salam when he ascended the pulpit."},"heading":{"title":"Salam on the Pulpit Before the Khutbah","description":"This Hadith describes a simple and beautiful action before the sermon. Jabir narrated that whenever the Prophet (صلى الله عليه وسلم) ascended the pulpit, he would greet the people with Salam. The core topic is Salam on the pulpit. The narration does not add a long speech or extra steps; it focuses on the greeting when he went up. This makes the Hadith easy to understand: public worship and teaching began with peace. For people searching for a hadith about Salam before khutbah, this report gives a direct wording. It also shows the Prophet’s respectful manner with the people before addressing them from the pulpit."},"teachings":["The Prophet صلى الله عليه وسلم greeted the people when he ascended the pulpit.","The greeting mentioned was Salam.","The Hadith shows a respectful start to the Friday sermon.","The report focuses on one clear action before the khutbah."],"related_hadiths":[{"id":"1104","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1110","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Salam on the Pulpit","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم would greet the people with Salam when he ascended the pulpit."},"heading":{"title":"Salam on the Pulpit Before the Khutbah","description":"This Hadith describes a simple and beautiful action before the sermon. Jabir narrated that whenever the Prophet (صلى الله عليه وسلم) ascended the pulpit, he would greet the people with Salam. The core topic is Salam on the pulpit. The narration does not add a long speech or extra steps; it focuses on the greeting when he went up. This makes the Hadith easy to understand: public worship and teaching began with peace. For people searching for a hadith about Salam before khutbah, this report gives a direct wording. It also shows the Prophet’s respectful manner with the people before addressing them from the pulpit."},"teachings":["The Prophet صلى الله عليه وسلم greeted the people when he ascended the pulpit.","The greeting mentioned was Salam.","The Hadith shows a respectful start to the Friday sermon.","The report focuses on one clear action before the khutbah."],"related_hadiths":[{"id":"1104","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1110","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E29" s="4" t="n"/>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Uthman Upon Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. During mention of a coming trial, the Prophet points to Uthman as being upon guidance."},"heading":{"title":"Hadith About Uthman Upon Right Guidance","description":"This hadith about Uthman upon right guidance is narrated by Ka'b bin Ujrah. The Messenger of Allah mentioned a fitnah that had drawn near. Then a man passed with his head covered, and the Prophet said that on that day this man would be following right guidance. Ka'b then held Uthman's arms and asked if this was the man. The Prophet confirmed, \"This man.\" The narration is focused on Uthman during a time of trial. It does not explain every detail of that fitnah, so the safest wording is to say that the Prophet identified Uthman as being on guidance in that context. This makes it a key hadith about Uthman's virtue and patience during tribulation."},"teachings":["The Prophet mentioned a coming fitnah in this narration.","Uthman is identified as being upon right guidance in that setting.","Ka'b sought clear confirmation, and the Prophet confirmed it.","The report teaches caution and fairness during times of trial."],"related_hadiths":[{"id":"133","book_id":"6","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Uthman Upon Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. During mention of a coming trial, the Prophet points to Uthman as being upon guidance."},"heading":{"title":"Hadith About Uthman Upon Right Guidance","description":"This hadith about Uthman upon right guidance is narrated by Ka'b bin Ujrah. The Messenger of Allah mentioned a fitnah that had drawn near. Then a man passed with his head covered, and the Prophet said that on that day this man would be following right guidance. Ka'b then held Uthman's arms and asked if this was the man. The Prophet confirmed, \"This man.\" The narration is focused on Uthman during a time of trial. It does not explain every detail of that fitnah, so the safest wording is to say that the Prophet identified Uthman as being on guidance in that context. This makes it a key hadith about Uthman's virtue and patience during tribulation."},"teachings":["The Prophet mentioned a coming fitnah in this narration.","Uthman is identified as being upon right guidance in that setting.","Ka'b sought clear confirmation, and the Prophet confirmed it.","The report teaches caution and fairness during times of trial."],"related_hadiths":[{"id":"133","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E30" s="4" t="n"/>
@@ -1155,7 +1159,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Silence During Friday Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. A question during the Friday sermon was treated as idle talk, and the Prophet صلى الله عليه وسلم confirmed Ubayy’s response."},"heading":{"title":"Silence During Friday Sermon and Avoiding Laghw","description":"This Hadith gives a real example of why silence during the Friday sermon matters. The Prophet (صلى الله عليه وسلم) recited Tabarak, Surah Al-Mulk, while standing and reminding the people of the Days of Allah. Abu Darda’ or Abu Dharr asked Ubayy when the Surah had been revealed, but Ubayy only gestured for him to be silent. Afterward, Ubayy said that he had gained nothing from his prayer that day except the idle talk he engaged in. When the matter was brought to the Prophet (صلى الله عليه وسلم), he said, “Ubayy spoke the truth.” The lesson is directly tied to the khutbah: avoid questions and side talk while the sermon is happening."},"teachings":["Questions during the sermon can fall under idle talk.","Ubayy responded with a gesture instead of speaking.","The Prophet صلى الله عليه وسلم confirmed Ubayy’s warning.","The Hadith stresses listening during the Friday sermon."],"related_hadiths":[{"id":"1110","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1117","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Silence During Friday Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. A question during the Friday sermon was treated as idle talk, and the Prophet صلى الله عليه وسلم confirmed Ubayy’s response."},"heading":{"title":"Silence During Friday Sermon and Avoiding Laghw","description":"This Hadith gives a real example of why silence during the Friday sermon matters. The Prophet (صلى الله عليه وسلم) recited Tabarak, Surah Al-Mulk, while standing and reminding the people of the Days of Allah. Abu Darda’ or Abu Dharr asked Ubayy when the Surah had been revealed, but Ubayy only gestured for him to be silent. Afterward, Ubayy said that he had gained nothing from his prayer that day except the idle talk he engaged in. When the matter was brought to the Prophet (صلى الله عليه وسلم), he said, “Ubayy spoke the truth.” The lesson is directly tied to the khutbah: avoid questions and side talk while the sermon is happening."},"teachings":["Questions during the sermon can fall under idle talk.","Ubayy responded with a gesture instead of speaking.","The Prophet صلى الله عليه وسلم confirmed Ubayy’s warning.","The Hadith stresses listening during the Friday sermon."],"related_hadiths":[{"id":"1110","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1117","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E31" s="4" t="n"/>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak’ah During Khutbah","description":"$book_name$ $hadith_number$ - $chapter_name$. A man entered during the sermon, had not prayed, and the Prophet صلى الله عليه وسلم told him to pray two Rak’ah."},"heading":{"title":"Two Rak’ah When Entering During the Khutbah","description":"This Hadith tells us about Sulaik Ghatafani entering the mosque while the Prophet (صلى الله عليه وسلم) was delivering the sermon. The Prophet (صلى الله عليه وسلم) asked him, “Have you prayed?” When he said no, the Prophet (صلى الله عليه وسلم) told him to perform two Rak’ah. The focus is the two Rak’ah when entering during the khutbah. The narration is not a general story about many actions in the mosque; it is about a person who entered while the sermon was already being delivered and had not prayed. The Prophet’s response was clear and direct. This Hadith is often searched by people asking what to do if they enter the mosque during the Friday khutbah."},"teachings":["The Prophet صلى الله عليه وسلم noticed a man who entered during the sermon.","He asked whether the man had prayed.","When the man said no, he told him to pray two Rak’ah.","The Hadith keeps the action brief and focused."],"related_hadiths":[{"id":"1113","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1114","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak’ah During Khutbah","description":"$book_name$ $hadith_number$ - $chapter_name$. A man entered during the sermon, had not prayed, and the Prophet صلى الله عليه وسلم told him to pray two Rak’ah."},"heading":{"title":"Two Rak’ah When Entering During the Khutbah","description":"This Hadith tells us about Sulaik Ghatafani entering the mosque while the Prophet (صلى الله عليه وسلم) was delivering the sermon. The Prophet (صلى الله عليه وسلم) asked him, “Have you prayed?” When he said no, the Prophet (صلى الله عليه وسلم) told him to perform two Rak’ah. The focus is the two Rak’ah when entering during the khutbah. The narration is not a general story about many actions in the mosque; it is about a person who entered while the sermon was already being delivered and had not prayed. The Prophet’s response was clear and direct. This Hadith is often searched by people asking what to do if they enter the mosque during the Friday khutbah."},"teachings":["The Prophet صلى الله عليه وسلم noticed a man who entered during the sermon.","He asked whether the man had prayed.","When the man said no, he told him to pray two Rak’ah.","The Hadith keeps the action brief and focused."],"related_hadiths":[{"id":"1113","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1114","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E32" s="4" t="n"/>
@@ -1201,7 +1205,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray Two Rak’ah","description":"$book_name$ $hadith_number$ - $chapter_name$. A man entered while the Prophet صلى الله عليه وسلم was preaching and was told to pray two Rak’ah."},"heading":{"title":"Pray Two Rak’ah When Entering During Khutbah","description":"This Hadith is another report about a man entering the mosque while the Prophet (صلى الله عليه وسلم) was delivering the sermon. The Prophet (صلى الله عليه وسلم) asked, “Have you prayed?” The man replied, “No.” The Prophet (صلى الله عليه وسلم) then said, “Then pray two Rak’ah.” The message is short and practical. It links entering the mosque during the Friday khutbah with praying two Rak’ah when the person has not already prayed. The report does not name the man in this wording, and it does not add extra details about a long prayer. It simply preserves the question, the answer, and the Prophet’s instruction. This makes it easy for readers to understand the core teaching."},"teachings":["The Prophet صلى الله عليه وسلم spoke to a man who entered during the sermon.","He checked whether the man had prayed.","The instruction was to pray two Rak’ah.","The Hadith gives a short and direct answer to a practical situation."],"related_hadiths":[{"id":"1112","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1114","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray Two Rak’ah","description":"$book_name$ $hadith_number$ - $chapter_name$. A man entered while the Prophet صلى الله عليه وسلم was preaching and was told to pray two Rak’ah."},"heading":{"title":"Pray Two Rak’ah When Entering During Khutbah","description":"This Hadith is another report about a man entering the mosque while the Prophet (صلى الله عليه وسلم) was delivering the sermon. The Prophet (صلى الله عليه وسلم) asked, “Have you prayed?” The man replied, “No.” The Prophet (صلى الله عليه وسلم) then said, “Then pray two Rak’ah.” The message is short and practical. It links entering the mosque during the Friday khutbah with praying two Rak’ah when the person has not already prayed. The report does not name the man in this wording, and it does not add extra details about a long prayer. It simply preserves the question, the answer, and the Prophet’s instruction. This makes it easy for readers to understand the core teaching."},"teachings":["The Prophet صلى الله عليه وسلم spoke to a man who entered during the sermon.","He checked whether the man had prayed.","The instruction was to pray two Rak’ah.","The Hadith gives a short and direct answer to a practical situation."],"related_hadiths":[{"id":"1112","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1114","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E33" s="4" t="n"/>
@@ -1224,7 +1228,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Step Over People","description":"$book_name$ $hadith_number$ - $chapter_name$. A late man stepped over people during the sermon, and the Prophet صلى الله عليه وسلم told him he had annoyed them."},"heading":{"title":"Do Not Step Over People on Friday","description":"This Hadith teaches manners in the mosque on Friday. A man entered the mosque while the Messenger of Allah (صلى الله عليه وسلم) was delivering the sermon, and he began stepping over people’s shoulders. The Prophet (صلى الله عليه وسلم) told him, “Sit down, for you have annoyed people and you are late.” The core message is clear: do not step over people on Friday, especially when the sermon is already being delivered. The Hadith does not only mention lateness; it also mentions causing annoyance. This makes the lesson practical and easy to apply. A worshipper should avoid disturbing people in order to reach a place, especially after arriving late."},"teachings":["Stepping over people during the sermon annoyed them.","The Prophet صلى الله عليه وسلم told the man to sit down.","The man’s lateness was mentioned along with the harm caused.","The Hadith teaches mosque manners on Friday."],"related_hadiths":[{"id":"1116","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1110","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Step Over People","description":"$book_name$ $hadith_number$ - $chapter_name$. A late man stepped over people during the sermon, and the Prophet صلى الله عليه وسلم told him he had annoyed them."},"heading":{"title":"Do Not Step Over People on Friday","description":"This Hadith teaches manners in the mosque on Friday. A man entered the mosque while the Messenger of Allah (صلى الله عليه وسلم) was delivering the sermon, and he began stepping over people’s shoulders. The Prophet (صلى الله عليه وسلم) told him, “Sit down, for you have annoyed people and you are late.” The core message is clear: do not step over people on Friday, especially when the sermon is already being delivered. The Hadith does not only mention lateness; it also mentions causing annoyance. This makes the lesson practical and easy to apply. A worshipper should avoid disturbing people in order to reach a place, especially after arriving late."},"teachings":["Stepping over people during the sermon annoyed them.","The Prophet صلى الله عليه وسلم told the man to sit down.","The man’s lateness was mentioned along with the harm caused.","The Hadith teaches mosque manners on Friday."],"related_hadiths":[{"id":"1116","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1110","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E34" s="4" t="n"/>
@@ -1247,7 +1251,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surahs in Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah recited Al-Jumu’ah and Al-Munafiqun and said he heard the Prophet صلى الله عليه وسلم recite them."},"heading":{"title":"Surahs Recited in Friday Prayer: Al-Jumu’ah and Al-Munafiqun","description":"This Hadith tells us what Abu Hurairah recited when he led the Friday prayer. In the first Rak’ah, he recited Surah Al-Jumu’ah. In the second Rak’ah, he recited Surah Al-Munafiqun. When ‘Ubaidullah mentioned that ‘Ali used to recite the same two Surahs in Kufah, Abu Hurairah explained that he heard the Messenger of Allah (صلى الله عليه وسلم) reciting them. The core topic is Surahs in Friday prayer. The report does not discuss the sermon; it focuses on recitation in the prayer itself. It shows that Abu Hurairah connected his recitation choice to what he had heard from the Prophet (صلى الله عليه وسلم). The wording keeps the focus on what was actually recited."},"teachings":["Surah Al-Jumu’ah was recited in the first Rak’ah.","Surah Al-Munafiqun was recited in the second Rak’ah.","Abu Hurairah linked this recitation to what he heard from the Prophet صلى الله عليه وسلم.","The Hadith records a specific recitation pattern in Friday prayer."],"related_hadiths":[{"id":"1119","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1120","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surahs in Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah recited Al-Jumu’ah and Al-Munafiqun and said he heard the Prophet صلى الله عليه وسلم recite them."},"heading":{"title":"Surahs Recited in Friday Prayer: Al-Jumu’ah and Al-Munafiqun","description":"This Hadith tells us what Abu Hurairah recited when he led the Friday prayer. In the first Rak’ah, he recited Surah Al-Jumu’ah. In the second Rak’ah, he recited Surah Al-Munafiqun. When ‘Ubaidullah mentioned that ‘Ali used to recite the same two Surahs in Kufah, Abu Hurairah explained that he heard the Messenger of Allah (صلى الله عليه وسلم) reciting them. The core topic is Surahs in Friday prayer. The report does not discuss the sermon; it focuses on recitation in the prayer itself. It shows that Abu Hurairah connected his recitation choice to what he had heard from the Prophet (صلى الله عليه وسلم). The wording keeps the focus on what was actually recited."},"teachings":["Surah Al-Jumu’ah was recited in the first Rak’ah.","Surah Al-Munafiqun was recited in the second Rak’ah.","Abu Hurairah linked this recitation to what he heard from the Prophet صلى الله عليه وسلم.","The Hadith records a specific recitation pattern in Friday prayer."],"related_hadiths":[{"id":"1119","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1120","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E35" s="4" t="n"/>
@@ -1270,7 +1274,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Uthman and Authority","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet tells Uthman not to give up the position Allah clothed him with."},"heading":{"title":"Hadith About Uthman and Authority","description":"This hadith about Uthman and authority is narrated by Aishah. The Messenger of Allah told Uthman that if Allah placed him in authority over this matter one day, and hypocrites wanted him to remove the garment Allah had clothed him with, he should not remove it. The Prophet said this three times. The narration itself explains the garment as the position of caliph. It also includes Nu'man asking Aishah why she had not told people, and she answered that she was made to forget it. The explanation should stay close to these details. The core topic is Uthman's authority, pressure from hypocrites, and the Prophet's instruction to remain firm."},"teachings":["The Prophet gave Uthman a repeated instruction in this narration.","The garment is explained in the text as the position of caliph.","The hadith mentions pressure from hypocrites.","Aishah's answer shows that forgetting is mentioned as part of the report."],"related_hadiths":[{"id":"133","book_id":"6","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Uthman and Authority","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet tells Uthman not to give up the position Allah clothed him with."},"heading":{"title":"Hadith About Uthman and Authority","description":"This hadith about Uthman and authority is narrated by Aishah. The Messenger of Allah told Uthman that if Allah placed him in authority over this matter one day, and hypocrites wanted him to remove the garment Allah had clothed him with, he should not remove it. The Prophet said this three times. The narration itself explains the garment as the position of caliph. It also includes Nu'man asking Aishah why she had not told people, and she answered that she was made to forget it. The explanation should stay close to these details. The core topic is Uthman's authority, pressure from hypocrites, and the Prophet's instruction to remain firm."},"teachings":["The Prophet gave Uthman a repeated instruction in this narration.","The garment is explained in the text as the position of caliph.","The hadith mentions pressure from hypocrites.","Aishah's answer shows that forgetting is mentioned as part of the report."],"related_hadiths":[{"id":"133","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E36" s="4" t="n"/>
@@ -1293,7 +1297,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Uthman's Patience","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet privately speaks to Uthman, who later recalls the matter with patience."},"heading":{"title":"Hadith About Uthman's Patience","description":"This hadith about Uthman's patience is narrated by Aishah. During the Prophet's illness, he said that he wanted some of his Companions with him. When Abu Bakr and Umar were suggested, he remained silent. When Uthman was suggested, he said yes. Uthman came, and the Prophet spoke to him in private, while Uthman's expression changed. Later, on the Day of the House, Uthman said that the Messenger of Allah had told him what would come to pass, and in one wording he said he would bear it with patience. The narration does not spell out every detail of the private talk. It focuses on the Prophet's private words to Uthman and Uthman's later patience."},"teachings":["The Prophet asked for some Companions during his illness.","He agreed when Uthman was suggested.","The private conversation affected Uthman's expression.","Uthman later connected that private matter with patience."],"related_hadiths":[{"id":"133","book_id":"6","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Uthman's Patience","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet privately speaks to Uthman, who later recalls the matter with patience."},"heading":{"title":"Hadith About Uthman's Patience","description":"This hadith about Uthman's patience is narrated by Aishah. During the Prophet's illness, he said that he wanted some of his Companions with him. When Abu Bakr and Umar were suggested, he remained silent. When Uthman was suggested, he said yes. Uthman came, and the Prophet spoke to him in private, while Uthman's expression changed. Later, on the Day of the House, Uthman said that the Messenger of Allah had told him what would come to pass, and in one wording he said he would bear it with patience. The narration does not spell out every detail of the private talk. It focuses on the Prophet's private words to Uthman and Uthman's later patience."},"teachings":["The Prophet asked for some Companions during his illness.","He agreed when Uthman was suggested.","The private conversation affected Uthman's expression.","Uthman later connected that private matter with patience."],"related_hadiths":[{"id":"133","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E37" s="4" t="n"/>
@@ -1316,7 +1320,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Love for Ali","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali narrates that love for him is linked with faith and hatred of him with hypocrisy."},"heading":{"title":"Hadith About Love for Ali and Faith","description":"This hadith about love for Ali is narrated in Ali's own words. He says that the Unlettered Prophet informed him that none but a believer would love him, and none but a hypocrite would hate him. The core topic is love for Ali as a sign connected to faith in this narration. The report does not give a list of actions, nor does it discuss every form of disagreement or personal issue. It states a clear spiritual marker: loving Ali is tied to belief, and hating him is tied to hypocrisy. For readers searching for \"none loves Ali but a believer,\" this narration should be explained with its exact wording and with respect for Ali's rank."},"teachings":["The narration links love for Ali with belief.","It links hatred of Ali with hypocrisy.","Ali reports this as something the Prophet informed him.","The hadith teaches respect for Ali without adding details beyond the text."],"related_hadiths":[{"id":"121","book_id":"6","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Love for Ali","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali narrates that love for him is linked with faith and hatred of him with hypocrisy."},"heading":{"title":"Hadith About Love for Ali and Faith","description":"This hadith about love for Ali is narrated in Ali's own words. He says that the Unlettered Prophet informed him that none but a believer would love him, and none but a hypocrite would hate him. The core topic is love for Ali as a sign connected to faith in this narration. The report does not give a list of actions, nor does it discuss every form of disagreement or personal issue. It states a clear spiritual marker: loving Ali is tied to belief, and hating him is tied to hypocrisy. For readers searching for \"none loves Ali but a believer,\" this narration should be explained with its exact wording and with respect for Ali's rank."},"teachings":["The narration links love for Ali with belief.","It links hatred of Ali with hypocrisy.","Ali reports this as something the Prophet informed him.","The hadith teaches respect for Ali without adding details beyond the text."],"related_hadiths":[{"id":"121","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E38" s="4" t="n"/>
@@ -1339,7 +1343,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali Like Harun to Musa","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet tells Ali that his position to him is like Harun's position to Musa."},"heading":{"title":"Hadith About Ali Like Harun to Musa","description":"This hadith about Ali like Harun to Musa is narrated from Sa'd bin Abu Waqqas through his father. The Prophet said to Ali, \"Would it not please you to be to me as Harun was to Musa?\" The wording shows a special closeness and honored position for Ali. The narration in this input does not add the longer wording found in some other reports, so the explanation should not add extra phrases here. It is enough to say that the Prophet compared Ali's place with him to the place of Harun with Musa. For users searching for the Harun and Musa hadith about Ali, this narration gives a short and powerful form of that statement."},"teachings":["The Prophet addressed Ali with an honored comparison.","The hadith connects Ali's position to Harun's position with Musa.","The wording shows closeness between the Prophet and Ali.","The explanation should stay with the short wording provided here."],"related_hadiths":[{"id":"121","book_id":"6","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali Like Harun to Musa","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet tells Ali that his position to him is like Harun's position to Musa."},"heading":{"title":"Hadith About Ali Like Harun to Musa","description":"This hadith about Ali like Harun to Musa is narrated from Sa'd bin Abu Waqqas through his father. The Prophet said to Ali, \"Would it not please you to be to me as Harun was to Musa?\" The wording shows a special closeness and honored position for Ali. The narration in this input does not add the longer wording found in some other reports, so the explanation should not add extra phrases here. It is enough to say that the Prophet compared Ali's place with him to the place of Harun with Musa. For users searching for the Harun and Musa hadith about Ali, this narration gives a short and powerful form of that statement."},"teachings":["The Prophet addressed Ali with an honored comparison.","The hadith connects Ali's position to Harun's position with Musa.","The wording shows closeness between the Prophet and Ali.","The explanation should stay with the short wording provided here."],"related_hadiths":[{"id":"121","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E39" s="4" t="n"/>
@@ -1362,7 +1366,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali as Mawla","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet takes Ali's hand and prays for those who befriend him."},"heading":{"title":"Hadith About Ali as Mawla and Friend","description":"This hadith about Ali as mawla is narrated by Bara' bin Azib. On the return from Hajj, the Prophet stopped on the road, commanded congregational prayer, then took Ali's hand. He asked whether he was dearer to the believers than their own selves, and they said yes. He then said that Ali is the friend of those whose master he is, and he prayed that Allah take as friends those who take Ali as a friend and take as enemies those who take him as an enemy. The text is about love, loyalty, and support for Ali. It does not require adding later debates into the explanation. A simple reading should stay with the Prophet's words and prayer in the narration."},"teachings":["The Prophet took Ali's hand before making this statement.","The companions affirmed the Prophet's closeness to the believers.","The narration calls for friendship and support toward Ali.","The Prophet made a prayer connected to those who befriend or oppose him."],"related_hadiths":[{"id":"121","book_id":"6","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali as Mawla","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet takes Ali's hand and prays for those who befriend him."},"heading":{"title":"Hadith About Ali as Mawla and Friend","description":"This hadith about Ali as mawla is narrated by Bara' bin Azib. On the return from Hajj, the Prophet stopped on the road, commanded congregational prayer, then took Ali's hand. He asked whether he was dearer to the believers than their own selves, and they said yes. He then said that Ali is the friend of those whose master he is, and he prayed that Allah take as friends those who take Ali as a friend and take as enemies those who take him as an enemy. The text is about love, loyalty, and support for Ali. It does not require adding later debates into the explanation. A simple reading should stay with the Prophet's words and prayer in the narration."},"teachings":["The Prophet took Ali's hand before making this statement.","The companions affirmed the Prophet's closeness to the believers.","The narration calls for friendship and support toward Ali.","The Prophet made a prayer connected to those who befriend or oppose him."],"related_hadiths":[{"id":"121","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E40" s="4" t="n"/>
@@ -1385,7 +1389,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali at Khaibar","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet heals Ali's eyes and gives him the banner at Khaibar."},"heading":{"title":"Hadith About Ali at Khaibar","description":"This hadith about Ali at Khaibar includes two clear parts. First, Ali says that his eyes were sore, and the Messenger of Allah put some spittle into his eyes and prayed that heat and cold be removed from him. Ali says he did not feel heat or cold after that day. Second, the Prophet said he would send a man who loves Allah and His Messenger, whom Allah and His Messenger love, and who does not flee from the battlefield. The people looked forward to that honor, and the Prophet sent for Ali and gave him the banner. The narration highlights Ali's love for Allah and His Messenger, the Prophet's love for him, and Ali's role with the banner at Khaibar."},"teachings":["The Prophet prayed for Ali when his eyes were sore.","Ali is described as loving Allah and His Messenger.","The narration says Allah and His Messenger love Ali.","Ali was given the banner after people looked forward to that honor."],"related_hadiths":[{"id":"121","book_id":"6","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali at Khaibar","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet heals Ali's eyes and gives him the banner at Khaibar."},"heading":{"title":"Hadith About Ali at Khaibar","description":"This hadith about Ali at Khaibar includes two clear parts. First, Ali says that his eyes were sore, and the Messenger of Allah put some spittle into his eyes and prayed that heat and cold be removed from him. Ali says he did not feel heat or cold after that day. Second, the Prophet said he would send a man who loves Allah and His Messenger, whom Allah and His Messenger love, and who does not flee from the battlefield. The people looked forward to that honor, and the Prophet sent for Ali and gave him the banner. The narration highlights Ali's love for Allah and His Messenger, the Prophet's love for him, and Ali's role with the banner at Khaibar."},"teachings":["The Prophet prayed for Ali when his eyes were sore.","Ali is described as loving Allah and His Messenger.","The narration says Allah and His Messenger love Ali.","Ali was given the banner after people looked forward to that honor."],"related_hadiths":[{"id":"121","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E41" s="4" t="n"/>
@@ -1408,7 +1412,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hasan and Husain","description":"$book_name$ $hadith_number$ - $chapter_name$. Hasan and Husain are named leaders of the youth of Paradise, with their father praised."},"heading":{"title":"Hadith About Hasan and Husain in Paradise","description":"This hadith about Hasan and Husain in Paradise is narrated by Ibn Umar. The Messenger of Allah said that Hasan and Husain will be the leaders of the youth of Paradise, and that their father is better than them. The narration gives honor to both grandsons of the Prophet and also praises their father, Ali. It does not describe the youth of Paradise in detail, nor does it list all their virtues. It gives one clear statement of rank. For readers searching for \"Hasan and Husain leaders of youth of Paradise,\" this hadith is focused on their honor in Paradise and the added praise given to their father."},"teachings":["Hasan and Husain are named as leaders of the youth of Paradise.","The narration also praises their father.","The hadith shows honor for the family of the Prophet.","The explanation should not add details about Paradise beyond the text."],"related_hadiths":[{"id":"121","book_id":"6","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3768","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hasan and Husain","description":"$book_name$ $hadith_number$ - $chapter_name$. Hasan and Husain are named leaders of the youth of Paradise, with their father praised."},"heading":{"title":"Hadith About Hasan and Husain in Paradise","description":"This hadith about Hasan and Husain in Paradise is narrated by Ibn Umar. The Messenger of Allah said that Hasan and Husain will be the leaders of the youth of Paradise, and that their father is better than them. The narration gives honor to both grandsons of the Prophet and also praises their father, Ali. It does not describe the youth of Paradise in detail, nor does it list all their virtues. It gives one clear statement of rank. For readers searching for \"Hasan and Husain leaders of youth of Paradise,\" this hadith is focused on their honor in Paradise and the added praise given to their father."},"teachings":["Hasan and Husain are named as leaders of the youth of Paradise.","The narration also praises their father.","The hadith shows honor for the family of the Prophet.","The explanation should not add details about Paradise beyond the text."],"related_hadiths":[{"id":"121","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3768","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E42" s="4" t="n"/>
@@ -1431,7 +1435,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Etiquette with Raised Palms","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the Prophetic manner of making dua with palms upward and wiping the face after finishing."},"heading":{"title":"Hadith About Dua Etiquette with Raised Palms","description":"This Hadith teaches a clear and simple point about how to make dua. The Messenger of Allah صلى الله عليه وسلم said that when a person calls upon Allah, he should do so with the palms of his hands facing upward, not with the backs of the hands facing upward. The Hadith also mentions wiping the face with the hands after finishing. The main lesson is about adab of dua, or respectful manners when asking Allah. It does not mention a special wording, time, or place for the dua. It focuses only on the hand position and the action after completing the supplication. For anyone searching for hadith about raising hands in dua, this narration gives direct guidance from the text itself."},"teachings":["When making dua, the palms should face upward as stated in the Hadith.","The backs of the hands should not be raised upward for this form of supplication.","The Hadith mentions wiping the face with the hands after finishing the dua.","Dua should be made with care, respect, and attention to Prophetic manners."],"related_hadiths":[{"id":"1182","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1191","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Etiquette with Raised Palms","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the Prophetic manner of making dua with palms upward and wiping the face after finishing."},"heading":{"title":"Hadith About Dua Etiquette with Raised Palms","description":"This Hadith teaches a clear and simple point about how to make dua. The Messenger of Allah صلى الله عليه وسلم said that when a person calls upon Allah, he should do so with the palms of his hands facing upward, not with the backs of the hands facing upward. The Hadith also mentions wiping the face with the hands after finishing. The main lesson is about adab of dua, or respectful manners when asking Allah. It does not mention a special wording, time, or place for the dua. It focuses only on the hand position and the action after completing the supplication. For anyone searching for hadith about raising hands in dua, this narration gives direct guidance from the text itself."},"teachings":["When making dua, the palms should face upward as stated in the Hadith.","The backs of the hands should not be raised upward for this form of supplication.","The Hadith mentions wiping the face with the hands after finishing the dua.","Dua should be made with care, respect, and attention to Prophetic manners."],"related_hadiths":[{"id":"1182","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1191","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E43" s="4" t="n"/>
@@ -1454,7 +1458,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Qunut Before Ruku","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows that the Prophet صلى الله عليه وسلم prayed Witr and recited Qunut before going into Ruku."},"heading":{"title":"Witr Qunut Before Ruku in Hadith","description":"This Hadith focuses on Witr prayer and the place of Qunut in it. Ubayy bin Ka‘b narrated that the Messenger of Allah صلى الله عليه وسلم used to pray Witr and recite Qunut before Ruku. The wording is short, but it gives a direct practice: Witr was prayed, and Qunut came before bowing. The Hadith does not give the exact words of the Qunut, nor does it mention the number of Rak‘ah in this report. So the explanation should stay with what is stated: Qunut before Ruku in Witr. For people searching for witr qunut before ruku hadith or when to read dua qunut in Witr, this narration is directly connected to that question."},"teachings":["The Prophet صلى الله عليه وسلم prayed Witr as part of his night prayer practice.","This narration places Qunut before Ruku in Witr.","The Hadith does not mention the wording of Qunut, only its position.","Witr prayer has a clear place in the Prophetic practice described here."],"related_hadiths":[{"id":"1183","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1184","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Qunut Before Ruku","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows that the Prophet صلى الله عليه وسلم prayed Witr and recited Qunut before going into Ruku."},"heading":{"title":"Witr Qunut Before Ruku in Hadith","description":"This Hadith focuses on Witr prayer and the place of Qunut in it. Ubayy bin Ka‘b narrated that the Messenger of Allah صلى الله عليه وسلم used to pray Witr and recite Qunut before Ruku. The wording is short, but it gives a direct practice: Witr was prayed, and Qunut came before bowing. The Hadith does not give the exact words of the Qunut, nor does it mention the number of Rak‘ah in this report. So the explanation should stay with what is stated: Qunut before Ruku in Witr. For people searching for witr qunut before ruku hadith or when to read dua qunut in Witr, this narration is directly connected to that question."},"teachings":["The Prophet صلى الله عليه وسلم prayed Witr as part of his night prayer practice.","This narration places Qunut before Ruku in Witr.","The Hadith does not mention the wording of Qunut, only its position.","Witr prayer has a clear place in the Prophetic practice described here."],"related_hadiths":[{"id":"1183","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1184","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E44" s="4" t="n"/>
@@ -1477,7 +1481,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut After Ruku","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas reported that the Prophet صلى الله عليه وسلم recited Qunut after Ruku."},"heading":{"title":"Hadith About Qunut After Ruku","description":"This Hadith gives a brief answer about Qunut after Ruku. Muhammad said that he asked Anas bin Malik about Qunut, and Anas replied that the Messenger of Allah صلى الله عليه وسلم recited Qunut after Ruku. The report is focused and does not mention the prayer name in the translation, nor does it give the words of the Qunut. It only tells us where Qunut happened in this narration: after Ruku. This matters for people searching for qunut after ruku hadith, because some narrations mention Qunut before Ruku while this one mentions after it. The safe explanation is that this Hadith records one reported position of Qunut from Anas, without adding details not found in the text."},"teachings":["Anas was asked about Qunut and answered from what he knew.","This narration places Qunut after Ruku.","The Hadith does not provide the wording of the Qunut.","Prayer details should be learned carefully from narrated reports."],"related_hadiths":[{"id":"1182","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1183","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut After Ruku","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas reported that the Prophet صلى الله عليه وسلم recited Qunut after Ruku."},"heading":{"title":"Hadith About Qunut After Ruku","description":"This Hadith gives a brief answer about Qunut after Ruku. Muhammad said that he asked Anas bin Malik about Qunut, and Anas replied that the Messenger of Allah صلى الله عليه وسلم recited Qunut after Ruku. The report is focused and does not mention the prayer name in the translation, nor does it give the words of the Qunut. It only tells us where Qunut happened in this narration: after Ruku. This matters for people searching for qunut after ruku hadith, because some narrations mention Qunut before Ruku while this one mentions after it. The safe explanation is that this Hadith records one reported position of Qunut from Anas, without adding details not found in the text."},"teachings":["Anas was asked about Qunut and answered from what he knew.","This narration places Qunut after Ruku.","The Hadith does not provide the wording of the Qunut.","Prayer details should be learned carefully from narrated reports."],"related_hadiths":[{"id":"1182","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1183","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E45" s="4" t="n"/>
@@ -1500,7 +1504,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet’s Witr Before Dawn","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali reported that the Prophet صلى الله عليه وسلم prayed Witr at different times, ending with Witr before dawn."},"heading":{"title":"Hadith on the Prophet’s Witr Before Dawn","description":"This Hadith is about the timing of Witr prayer in the life of the Messenger of Allah صلى الله عليه وسلم. Ali said that the Prophet صلى الله عليه وسلم prayed Witr at every part of the night: at the beginning and in the middle. Then his Witr finally came to be just before dawn. The narration is close in meaning to reports from Aishah about Witr timing. It does not discuss the number of Rak‘ah, Qunut, or the words recited. It only focuses on when Witr was prayed. For searchers asking about Prophet Witr before dawn or best time for Witr in Hadith, this narration gives a clear timing point: his final practice mentioned here was Witr in the last part before dawn."},"teachings":["The Prophet صلى الله عليه وسلم prayed Witr at more than one time of the night.","Ali mentioned the beginning and middle of the night.","The Prophet’s Witr finally reached the time before dawn.","The Hadith focuses on timing, not the wording or number of Rak‘ah."],"related_hadiths":[{"id":"1185","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1187","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet’s Witr Before Dawn","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali reported that the Prophet صلى الله عليه وسلم prayed Witr at different times, ending with Witr before dawn."},"heading":{"title":"Hadith on the Prophet’s Witr Before Dawn","description":"This Hadith is about the timing of Witr prayer in the life of the Messenger of Allah صلى الله عليه وسلم. Ali said that the Prophet صلى الله عليه وسلم prayed Witr at every part of the night: at the beginning and in the middle. Then his Witr finally came to be just before dawn. The narration is close in meaning to reports from Aishah about Witr timing. It does not discuss the number of Rak‘ah, Qunut, or the words recited. It only focuses on when Witr was prayed. For searchers asking about Prophet Witr before dawn or best time for Witr in Hadith, this narration gives a clear timing point: his final practice mentioned here was Witr in the last part before dawn."},"teachings":["The Prophet صلى الله عليه وسلم prayed Witr at more than one time of the night.","Ali mentioned the beginning and middle of the night.","The Prophet’s Witr finally reached the time before dawn.","The Hadith focuses on timing, not the wording or number of Rak‘ah."],"related_hadiths":[{"id":"1185","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1187","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E46" s="4" t="n"/>
@@ -1523,7 +1527,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali Is Part of Me","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet says Ali is part of him and will represent him."},"heading":{"title":"Hadith About Ali Is Part of Me","description":"This hadith about Ali is part of me is narrated by Hubshi bin Junadah. He heard the Messenger of Allah say, \"Ali is part of me and I am part of him, and no one will represent me except Ali.\" The wording shows a close bond between the Prophet and Ali. It also mentions representation by Ali in the wording of this report. The narration does not explain the wider setting, so the explanation should not add one. It is best understood as a statement of closeness and special trust as stated in the text. For search terms, this is a key hadith about Ali's virtue, closeness to the Prophet, and the phrase \"Ali is from me and I am from him.\""},"teachings":["The Prophet described a close bond between himself and Ali.","The narration says Ali is part of the Prophet and the Prophet is part of him.","It mentions Ali representing the Prophet in this report.","The explanation should not add a setting that is not included in the text."],"related_hadiths":[{"id":"121","book_id":"6","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali Is Part of Me","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet says Ali is part of him and will represent him."},"heading":{"title":"Hadith About Ali Is Part of Me","description":"This hadith about Ali is part of me is narrated by Hubshi bin Junadah. He heard the Messenger of Allah say, \"Ali is part of me and I am part of him, and no one will represent me except Ali.\" The wording shows a close bond between the Prophet and Ali. It also mentions representation by Ali in the wording of this report. The narration does not explain the wider setting, so the explanation should not add one. It is best understood as a statement of closeness and special trust as stated in the text. For search terms, this is a key hadith about Ali's virtue, closeness to the Prophet, and the phrase \"Ali is from me and I am from him.\""},"teachings":["The Prophet described a close bond between himself and Ali.","The narration says Ali is part of the Prophet and the Prophet is part of him.","It mentions Ali representing the Prophet in this report.","The explanation should not add a setting that is not included in the text."],"related_hadiths":[{"id":"121","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E47" s="4" t="n"/>
@@ -1546,7 +1550,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali's Early Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali describes himself as Allah's slave, the Prophet's brother, and an early worshipper."},"heading":{"title":"Hadith About Ali's Early Prayer","description":"This hadith about Ali's early prayer is narrated from Abbad bin Abdullah, who reports Ali's own statement. Ali says, \"I am the slave of Allah and the brother of His Messenger.\" He also calls himself the greatest teller of truth and says that no one after him would say this except a liar. He adds that he prayed seven years before the people. The narration is centered on Ali's self-description, his closeness to the Messenger of Allah, and his early prayer. It does not give a full timeline or explain who is meant by \"the people\" in detail. A careful explanation should present only what the text says and avoid adding claims that are not inside the report."},"teachings":["Ali describes himself first as the slave of Allah.","He mentions his brotherhood with the Messenger of Allah.","The narration reports Ali's statement about early prayer.","The wording should be handled carefully without adding a timeline not stated in the text."],"related_hadiths":[{"id":"121","book_id":"6","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali's Early Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali describes himself as Allah's slave, the Prophet's brother, and an early worshipper."},"heading":{"title":"Hadith About Ali's Early Prayer","description":"This hadith about Ali's early prayer is narrated from Abbad bin Abdullah, who reports Ali's own statement. Ali says, \"I am the slave of Allah and the brother of His Messenger.\" He also calls himself the greatest teller of truth and says that no one after him would say this except a liar. He adds that he prayed seven years before the people. The narration is centered on Ali's self-description, his closeness to the Messenger of Allah, and his early prayer. It does not give a full timeline or explain who is meant by \"the people\" in detail. A careful explanation should present only what the text says and avoid adding claims that are not inside the report."},"teachings":["Ali describes himself first as the slave of Allah.","He mentions his brotherhood with the Messenger of Allah.","The narration reports Ali's statement about early prayer.","The wording should be handled carefully without adding a timeline not stated in the text."],"related_hadiths":[{"id":"121","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"133","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"134","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E48" s="4" t="n"/>
@@ -1569,7 +1573,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Prayer While Riding","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed Witr on his mount, showing ease in voluntary night prayer."},"heading":{"title":"Witr Prayer While Riding a Mount","description":"This Hadith about Witr prayer shows a simple action of the Prophet صلى الله عليه وسلم: he used to pray Witr while riding his mount. The text does not add extra details about the journey, direction, or exact situation, so the meaning should stay focused on what is stated. It highlights that Witr was a regular prayer in the Prophet’s practice, even while riding. For people searching for Witr prayer while traveling or praying Witr on a ride, this narration gives a clear example from the Sunnah. The main point is not to make prayer feel hard, but to notice how the Prophet صلى الله عليه وسلم kept connected to worship even when he was on his mount."},"teachings":["The Prophet صلى الله عليه وسلم practiced Witr even while riding his mount.","Witr prayer has a strong place in the Prophet’s regular worship.","The Hadith shows ease in voluntary prayer based on what is directly mentioned."],"related_hadiths":[{"id":"1202","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Prayer While Riding","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed Witr on his mount, showing ease in voluntary night prayer."},"heading":{"title":"Witr Prayer While Riding a Mount","description":"This Hadith about Witr prayer shows a simple action of the Prophet صلى الله عليه وسلم: he used to pray Witr while riding his mount. The text does not add extra details about the journey, direction, or exact situation, so the meaning should stay focused on what is stated. It highlights that Witr was a regular prayer in the Prophet’s practice, even while riding. For people searching for Witr prayer while traveling or praying Witr on a ride, this narration gives a clear example from the Sunnah. The main point is not to make prayer feel hard, but to notice how the Prophet صلى الله عليه وسلم kept connected to worship even when he was on his mount."},"teachings":["The Prophet صلى الله عليه وسلم practiced Witr even while riding his mount.","Witr prayer has a strong place in the Prophet’s regular worship.","The Hadith shows ease in voluntary prayer based on what is directly mentioned."],"related_hadiths":[{"id":"1202","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E49" s="4" t="n"/>
@@ -1592,7 +1596,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Doubt About Rak‘ah Count","description":"$book_name$ $hadith_number$ - $chapter_name$. If someone does not know how many Rak‘ah were prayed, the Hadith teaches two prostrations."},"heading":{"title":"What to Do When You Forget How Many Rak‘ah","description":"This Hadith focuses on doubt in prayer, especially when a person does not know how many Rak‘ah they have prayed. Iyad asked Abu Saeed Al-Khudri about this exact problem. Abu Saeed answered with the words of the Messenger of Allah صلى الله عليه وسلم: when one of you prays and does not know how many he has prayed, he should perform two prostrations while sitting. The Hadith is short, but it gives direct help for a common prayer mistake. People often search for sujood sahw for doubt in salah, and this narration speaks to that issue in plain words. It keeps the response simple: two prostrations while sitting."},"teachings":["A worshipper may become unsure about the number of Rak‘ah.","The Prophet صلى الله عليه وسلم gave a direct action for this type of doubt.","Two prostrations while sitting are mentioned as the response.","The Hadith teaches calm correction instead of confusion."],"related_hadiths":[{"id":"1203","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1209","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1210","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Doubt About Rak‘ah Count","description":"$book_name$ $hadith_number$ - $chapter_name$. If someone does not know how many Rak‘ah were prayed, the Hadith teaches two prostrations."},"heading":{"title":"What to Do When You Forget How Many Rak‘ah","description":"This Hadith focuses on doubt in prayer, especially when a person does not know how many Rak‘ah they have prayed. Iyad asked Abu Saeed Al-Khudri about this exact problem. Abu Saeed answered with the words of the Messenger of Allah صلى الله عليه وسلم: when one of you prays and does not know how many he has prayed, he should perform two prostrations while sitting. The Hadith is short, but it gives direct help for a common prayer mistake. People often search for sujood sahw for doubt in salah, and this narration speaks to that issue in plain words. It keeps the response simple: two prostrations while sitting."},"teachings":["A worshipper may become unsure about the number of Rak‘ah.","The Prophet صلى الله عليه وسلم gave a direct action for this type of doubt.","Two prostrations while sitting are mentioned as the response.","The Hadith teaches calm correction instead of confusion."],"related_hadiths":[{"id":"1203","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1209","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1210","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E50" s="4" t="n"/>
@@ -1615,7 +1619,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Extra Rak‘ah in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed Zuhr as five Rak‘ah, then corrected it with two prostrations."},"heading":{"title":"Sujood Sahw After an Extra Rak‘ah","description":"This Hadith describes a prayer mistake where the Prophet صلى الله عليه وسلم prayed Zuhr as five Rak‘ah. The people asked whether something had been added to the prayer. He asked what they meant, and they told him what had happened. Then he turned back toward the Qiblah and performed two prostrations. The Hadith is often searched as a Hadith about extra Rak‘ah in salah or sujood sahw after adding in prayer. Its message is focused and practical. When an extra action happens in prayer, the correction mentioned here is two prostrations. The text also shows that the Companions told the Prophet صلى الله عليه وسلم what they noticed."},"teachings":["An extra Rak‘ah in prayer is addressed through correction.","The Prophet صلى الله عليه وسلم performed two prostrations after being informed.","The Companions asked respectfully when they noticed a prayer issue.","The Hadith gives a clear example related to Zuhr prayer."],"related_hadiths":[{"id":"1203","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1211","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1218","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Extra Rak‘ah in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed Zuhr as five Rak‘ah, then corrected it with two prostrations."},"heading":{"title":"Sujood Sahw After an Extra Rak‘ah","description":"This Hadith describes a prayer mistake where the Prophet صلى الله عليه وسلم prayed Zuhr as five Rak‘ah. The people asked whether something had been added to the prayer. He asked what they meant, and they told him what had happened. Then he turned back toward the Qiblah and performed two prostrations. The Hadith is often searched as a Hadith about extra Rak‘ah in salah or sujood sahw after adding in prayer. Its message is focused and practical. When an extra action happens in prayer, the correction mentioned here is two prostrations. The text also shows that the Companions told the Prophet صلى الله عليه وسلم what they noticed."},"teachings":["An extra Rak‘ah in prayer is addressed through correction.","The Prophet صلى الله عليه وسلم performed two prostrations after being informed.","The Companions asked respectfully when they noticed a prayer issue.","The Hadith gives a clear example related to Zuhr prayer."],"related_hadiths":[{"id":"1203","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1211","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1218","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E51" s="4" t="n"/>
@@ -1638,7 +1642,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forgetting the Sitting","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم stood before sitting in the second Rak‘ah and made two prostrations before Salam."},"heading":{"title":"Sujood Sahw for Forgetting the Sitting","description":"This Hadith describes the Prophet صلى الله عليه وسلم standing up in the second Rak‘ah before sitting. The narrator says he thinks the prayer was Asr. Before the Prophet صلى الله عليه وسلم said the Salam, he performed two prostrations. This is a key narration for people searching sujood sahw before Salam or what to do if you forget the sitting in prayer. The text does not add long details, but the action is clear. A sitting was missed, the prayer continued, and before ending the prayer with Salam, two prostrations were made. The Hadith gives a simple example of how a missed sitting was corrected in prayer."},"teachings":["Forgetting to sit in the second Rak‘ah is mentioned in this narration.","The Prophet صلى الله عليه وسلم corrected the mistake with two prostrations.","The two prostrations happened before the Salam in this report.","The Hadith gives a practical example of sujood sahw."],"related_hadiths":[{"id":"1207","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1208","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1216","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forgetting the Sitting","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم stood before sitting in the second Rak‘ah and made two prostrations before Salam."},"heading":{"title":"Sujood Sahw for Forgetting the Sitting","description":"This Hadith describes the Prophet صلى الله عليه وسلم standing up in the second Rak‘ah before sitting. The narrator says he thinks the prayer was Asr. Before the Prophet صلى الله عليه وسلم said the Salam, he performed two prostrations. This is a key narration for people searching sujood sahw before Salam or what to do if you forget the sitting in prayer. The text does not add long details, but the action is clear. A sitting was missed, the prayer continued, and before ending the prayer with Salam, two prostrations were made. The Hadith gives a simple example of how a missed sitting was corrected in prayer."},"teachings":["Forgetting to sit in the second Rak‘ah is mentioned in this narration.","The Prophet صلى الله عليه وسلم corrected the mistake with two prostrations.","The two prostrations happened before the Salam in this report.","The Hadith gives a practical example of sujood sahw."],"related_hadiths":[{"id":"1207","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1208","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1216","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E52" s="4" t="n"/>
@@ -1661,7 +1665,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Missing the Sitting in Zuhr","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم forgot the sitting in Zuhr, then made two prostrations before Salam."},"heading":{"title":"Forgetting the Sitting in Zuhr Prayer","description":"This Hadith gives another report about forgetting the sitting in prayer. Ibn Buhainah said that the Prophet صلى الله عليه وسلم stood up in the second Rak‘ah of Zuhr and forgot to sit. When he had finished the prayer, and before saying the Salam, he performed the two prostrations of forgetfulness and then said the Salam. This narration is useful for searches like sujood sahw for missing tashahhud or forgetting the sitting in Zuhr prayer. The wording is very direct. It names the prayer as Zuhr, mentions the missed sitting, and places the two prostrations before the Salam. The lesson is focused on correcting a mistake without breaking the flow of prayer."},"teachings":["The Prophet صلى الله عليه وسلم forgot the sitting in the second Rak‘ah of Zuhr.","He completed the prayer before making the two prostrations.","The prostrations of forgetfulness were done before the Salam in this report.","The Hadith shows a clear response to missing a sitting."],"related_hadiths":[{"id":"1206","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1208","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1216","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Missing the Sitting in Zuhr","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم forgot the sitting in Zuhr, then made two prostrations before Salam."},"heading":{"title":"Forgetting the Sitting in Zuhr Prayer","description":"This Hadith gives another report about forgetting the sitting in prayer. Ibn Buhainah said that the Prophet صلى الله عليه وسلم stood up in the second Rak‘ah of Zuhr and forgot to sit. When he had finished the prayer, and before saying the Salam, he performed the two prostrations of forgetfulness and then said the Salam. This narration is useful for searches like sujood sahw for missing tashahhud or forgetting the sitting in Zuhr prayer. The wording is very direct. It names the prayer as Zuhr, mentions the missed sitting, and places the two prostrations before the Salam. The lesson is focused on correcting a mistake without breaking the flow of prayer."},"teachings":["The Prophet صلى الله عليه وسلم forgot the sitting in the second Rak‘ah of Zuhr.","He completed the prayer before making the two prostrations.","The prostrations of forgetfulness were done before the Salam in this report.","The Hadith shows a clear response to missing a sitting."],"related_hadiths":[{"id":"1206","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1208","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1216","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E53" s="4" t="n"/>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing After Two Rak‘ah","description":"$book_name$ $hadith_number$ - $chapter_name$. If one stands after two Rak‘ah, the Hadith explains when to sit and when to continue."},"heading":{"title":"What to Do If You Stand After Two Rak‘ah","description":"This Hadith gives a clear rule for a specific prayer mistake. The Messenger of Allah صلى الله عليه وسلم said that if someone stands after two Rak‘ah and has not yet fully stood up, he should sit back down. But if he has already stood fully, he should not sit back down. Instead, he should perform two prostrations for forgetfulness. This is one of the clearest Hadiths for people searching what to do if you stand up before tashahhud or sujood sahw after standing fully. The text carefully separates two cases: not fully standing and fully standing. That makes the instruction easy to follow without adding anything beyond the narration."},"teachings":["If a person has not fully stood, the Hadith says to sit down again.","If a person has fully stood, the Hadith says not to sit back down.","Two prostrations for forgetfulness are mentioned after fully standing.","The Hadith separates the response based on the person’s position."],"related_hadiths":[{"id":"1206","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1207","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1212","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing After Two Rak‘ah","description":"$book_name$ $hadith_number$ - $chapter_name$. If one stands after two Rak‘ah, the Hadith explains when to sit and when to continue."},"heading":{"title":"What to Do If You Stand After Two Rak‘ah","description":"This Hadith gives a clear rule for a specific prayer mistake. The Messenger of Allah صلى الله عليه وسلم said that if someone stands after two Rak‘ah and has not yet fully stood up, he should sit back down. But if he has already stood fully, he should not sit back down. Instead, he should perform two prostrations for forgetfulness. This is one of the clearest Hadiths for people searching what to do if you stand up before tashahhud or sujood sahw after standing fully. The text carefully separates two cases: not fully standing and fully standing. That makes the instruction easy to follow without adding anything beyond the narration."},"teachings":["If a person has not fully stood, the Hadith says to sit down again.","If a person has fully stood, the Hadith says not to sit back down.","Two prostrations for forgetfulness are mentioned after fully standing.","The Hadith separates the response based on the person’s position."],"related_hadiths":[{"id":"1206","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1207","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1212","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E54" s="4" t="n"/>
@@ -1707,7 +1711,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seek What Is Closest to Correct","description":"$book_name$ $hadith_number$ - $chapter_name$. If unsure in prayer, the Hadith teaches seeking what is closest to correct, then prostrating twice."},"heading":{"title":"When Unsure in Prayer, Choose What Seems Correct","description":"This Hadith gives a full scene about uncertainty in prayer. The Messenger of Allah صلى الله عليه وسلم prayed, and the narrator was not sure whether something was added or omitted. After being told, the Prophet صلى الله عليه وسلم faced the Qiblah, prostrated twice, and said the Salam. He then explained that if any new command about prayer had come, he would have told them. He also said that he was human and could forget, and if he forgot, they should remind him. For anyone uncertain about the prayer, he said to seek what is closest to correct, complete the prayer, say the Salam, and prostrate twice. This is a core Hadith for sujood sahw and prayer doubt."},"teachings":["The Prophet صلى الله عليه وسلم told the Companions to remind him if he forgot.","If unsure in prayer, the Hadith says to seek what is closest to correct.","The person should complete the prayer, say Salam, and prostrate twice.","The Hadith shows correction through calm reminder and action."],"related_hadiths":[{"id":"1203","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1212","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1218","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seek What Is Closest to Correct","description":"$book_name$ $hadith_number$ - $chapter_name$. If unsure in prayer, the Hadith teaches seeking what is closest to correct, then prostrating twice."},"heading":{"title":"When Unsure in Prayer, Choose What Seems Correct","description":"This Hadith gives a full scene about uncertainty in prayer. The Messenger of Allah صلى الله عليه وسلم prayed, and the narrator was not sure whether something was added or omitted. After being told, the Prophet صلى الله عليه وسلم faced the Qiblah, prostrated twice, and said the Salam. He then explained that if any new command about prayer had come, he would have told them. He also said that he was human and could forget, and if he forgot, they should remind him. For anyone uncertain about the prayer, he said to seek what is closest to correct, complete the prayer, say the Salam, and prostrate twice. This is a core Hadith for sujood sahw and prayer doubt."},"teachings":["The Prophet صلى الله عليه وسلم told the Companions to remind him if he forgot.","If unsure in prayer, the Hadith says to seek what is closest to correct.","The person should complete the prayer, say Salam, and prostrate twice.","The Hadith shows correction through calm reminder and action."],"related_hadiths":[{"id":"1203","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1212","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1218","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E55" s="4" t="n"/>
@@ -1730,7 +1734,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhul-Yadain and Shortened Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. After Salam at two Rak‘ah, the Prophet صلى الله عليه وسلم confirmed the matter, completed prayer, and prostrated twice."},"heading":{"title":"Dhul-Yadain Hadith About Completing Prayer","description":"This Hadith tells the well-known prayer incident involving Dhul-Yadain. The Messenger of Allah صلى الله عليه وسلم forgot and said the Taslim after two Rak‘ah. Dhul-Yadain asked whether the prayer had been shortened or whether the Prophet صلى الله عليه وسلم had forgotten. The Prophet صلى الله عليه وسلم replied that it had not been shortened and he had not forgotten. When Dhul-Yadain said that only two Rak‘ah had been prayed, the Prophet صلى الله عليه وسلم asked the people if his statement was true. They said yes. So the Prophet صلى الله عليه وسلم went forward, prayed two more Rak‘ah, said Salam, and then made two prostrations of forgetfulness. The Hadith teaches checking the matter and completing the prayer."},"teachings":["Dhul-Yadain respectfully asked about a possible prayer mistake.","The Prophet صلى الله عليه وسلم confirmed the matter with the people present.","The omitted Rak‘ah were completed before the prostrations of forgetfulness.","The Hadith shows sujood sahw after completing a shortened prayer by mistake."],"related_hadiths":[{"id":"1214","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1215","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1219","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhul-Yadain and Shortened Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. After Salam at two Rak‘ah, the Prophet صلى الله عليه وسلم confirmed the matter, completed prayer, and prostrated twice."},"heading":{"title":"Dhul-Yadain Hadith About Completing Prayer","description":"This Hadith tells the well-known prayer incident involving Dhul-Yadain. The Messenger of Allah صلى الله عليه وسلم forgot and said the Taslim after two Rak‘ah. Dhul-Yadain asked whether the prayer had been shortened or whether the Prophet صلى الله عليه وسلم had forgotten. The Prophet صلى الله عليه وسلم replied that it had not been shortened and he had not forgotten. When Dhul-Yadain said that only two Rak‘ah had been prayed, the Prophet صلى الله عليه وسلم asked the people if his statement was true. They said yes. So the Prophet صلى الله عليه وسلم went forward, prayed two more Rak‘ah, said Salam, and then made two prostrations of forgetfulness. The Hadith teaches checking the matter and completing the prayer."},"teachings":["Dhul-Yadain respectfully asked about a possible prayer mistake.","The Prophet صلى الله عليه وسلم confirmed the matter with the people present.","The omitted Rak‘ah were completed before the prostrations of forgetfulness.","The Hadith shows sujood sahw after completing a shortened prayer by mistake."],"related_hadiths":[{"id":"1214","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1215","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1219","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E56" s="4" t="n"/>
@@ -1753,7 +1757,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Satan’s Distraction in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Satan may cause doubt in prayer; the Hadith teaches two prostrations before Salam."},"heading":{"title":"Satan’s Distraction and Doubt in Salah","description":"This Hadith speaks about a cause of confusion during prayer. The Prophet صلى الله عليه وسلم said that Satan comes to a person while he is praying and comes between him and himself until he does not know whether he added something or omitted something. If that happens, the person should prostrate twice before saying Salam, then say Salam. This is an important Hadith for searches like waswasah in salah, Satan causing doubt in prayer, and sujood sahw before Salam. The text does not tell the person to stop praying or panic. It gives a direct response: make two prostrations before the Salam when this kind of doubt happens."},"teachings":["Satan may cause a person to become unsure during prayer.","The doubt may be about adding or omitting something.","The Hadith teaches two prostrations before the Salam in this case.","The person then says the Salam after the two prostrations."],"related_hadiths":[{"id":"1217","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1210","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1212","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Satan’s Distraction in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Satan may cause doubt in prayer; the Hadith teaches two prostrations before Salam."},"heading":{"title":"Satan’s Distraction and Doubt in Salah","description":"This Hadith speaks about a cause of confusion during prayer. The Prophet صلى الله عليه وسلم said that Satan comes to a person while he is praying and comes between him and himself until he does not know whether he added something or omitted something. If that happens, the person should prostrate twice before saying Salam, then say Salam. This is an important Hadith for searches like waswasah in salah, Satan causing doubt in prayer, and sujood sahw before Salam. The text does not tell the person to stop praying or panic. It gives a direct response: make two prostrations before the Salam when this kind of doubt happens."},"teachings":["Satan may cause a person to become unsure during prayer.","The doubt may be about adding or omitting something.","The Hadith teaches two prostrations before the Salam in this case.","The person then says the Salam after the two prostrations."],"related_hadiths":[{"id":"1217","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1210","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1212","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E57" s="4" t="n"/>
@@ -1776,7 +1780,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Doubt Caused During Salah","description":"$book_name$ $hadith_number$ - $chapter_name$. When Satan causes uncertainty about Rak‘ah count, the Hadith teaches two prostrations before Salam."},"heading":{"title":"When You Do Not Know How Many Rak‘ah You Prayed","description":"This Hadith is closely tied to doubt in Rak‘ah count during salah. The Prophet صلى الله عليه وسلم said that Satan comes between the son of Adam and his soul, so the person does not know how many Rak‘ah he has prayed. If a person notices that, he should perform two prostrations before saying the Salam. The Hadith is simple and very practical. It does not list many cases; it focuses on one common problem: losing track of the number of Rak‘ah. For people searching what to do when you forget how many Rak‘ah in prayer, this narration gives a direct answer connected to sujood sahw before Salam."},"teachings":["A person may lose track of the number of Rak‘ah in prayer.","The Hadith links this confusion to Satan’s interference.","The response mentioned is two prostrations before Salam.","The Hadith gives a clear action when the person notices this doubt."],"related_hadiths":[{"id":"1216","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1204","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1209","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Doubt Caused During Salah","description":"$book_name$ $hadith_number$ - $chapter_name$. When Satan causes uncertainty about Rak‘ah count, the Hadith teaches two prostrations before Salam."},"heading":{"title":"When You Do Not Know How Many Rak‘ah You Prayed","description":"This Hadith is closely tied to doubt in Rak‘ah count during salah. The Prophet صلى الله عليه وسلم said that Satan comes between the son of Adam and his soul, so the person does not know how many Rak‘ah he has prayed. If a person notices that, he should perform two prostrations before saying the Salam. The Hadith is simple and very practical. It does not list many cases; it focuses on one common problem: losing track of the number of Rak‘ah. For people searching what to do when you forget how many Rak‘ah in prayer, this narration gives a direct answer connected to sujood sahw before Salam."},"teachings":["A person may lose track of the number of Rak‘ah in prayer.","The Hadith links this confusion to Satan’s interference.","The response mentioned is two prostrations before Salam.","The Hadith gives a clear action when the person notices this doubt."],"related_hadiths":[{"id":"1216","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1204","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1209","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E58" s="4" t="n"/>
@@ -1799,7 +1803,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sujood Sahw After Salam","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Mas‘ud made two prostrations after Salam and said the Prophet صلى الله عليه وسلم did that."},"heading":{"title":"Sujood Sahw After the Salam","description":"This Hadith is short but important for the topic of sujood sahw after Salam. Alqamah narrated that Ibn Mas‘ud performed the two prostrations of forgetfulness after the Salam. He also mentioned that the Prophet صلى الله عليه وسلم did that. The Hadith does not give a long story or name a specific mistake in this text. Its focus is the timing of the prostrations: after the Salam. This is useful for people searching whether sujood sahw can be after Salam. Since other narrations in the same batch mention before Salam in certain cases, this report shows that after Salam is also stated in the provided text."},"teachings":["Ibn Mas‘ud performed the prostrations of forgetfulness after Salam.","He mentioned that the Prophet صلى الله عليه وسلم did that.","The Hadith focuses on the timing of sujood sahw.","The narration supports the wording: two prostrations after Salam."],"related_hadiths":[{"id":"1219","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1211","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1205","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sujood Sahw After Salam","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Mas‘ud made two prostrations after Salam and said the Prophet صلى الله عليه وسلم did that."},"heading":{"title":"Sujood Sahw After the Salam","description":"This Hadith is short but important for the topic of sujood sahw after Salam. Alqamah narrated that Ibn Mas‘ud performed the two prostrations of forgetfulness after the Salam. He also mentioned that the Prophet صلى الله عليه وسلم did that. The Hadith does not give a long story or name a specific mistake in this text. Its focus is the timing of the prostrations: after the Salam. This is useful for people searching whether sujood sahw can be after Salam. Since other narrations in the same batch mention before Salam in certain cases, this report shows that after Salam is also stated in the provided text."},"teachings":["Ibn Mas‘ud performed the prostrations of forgetfulness after Salam.","He mentioned that the Prophet صلى الله عليه وسلم did that.","The Hadith focuses on the timing of sujood sahw.","The narration supports the wording: two prostrations after Salam."],"related_hadiths":[{"id":"1219","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1211","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1205","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E59" s="4" t="n"/>
@@ -1822,7 +1826,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Prostrations for Every Mistake","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith states that every mistake has two prostrations after saying the Salam."},"heading":{"title":"Two Prostrations for Every Mistake in Prayer","description":"This Hadith gives a broad statement about sujood sahw. Thawban said he heard the Messenger of Allah صلى الله عليه وسلم say, “For every mistake there are two prostrations, after saying the Salam.” The text is brief, so the explanation should stay close to it. It tells us that mistakes in prayer are met with two prostrations, and this narration places them after the Salam. This Hadith is highly relevant for searches like two prostrations for every mistake, sujood sahw after Salam, and prostration of forgetfulness Hadith. It is not a long case study like some other narrations, but it gives a clear general wording about mistakes and correction."},"teachings":["The Hadith states that every mistake has two prostrations.","This narration places the two prostrations after the Salam.","The text connects mistakes in prayer with a clear corrective action.","The wording is general and easy to remember."],"related_hadiths":[{"id":"1218","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1213","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1215","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Prostrations for Every Mistake","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith states that every mistake has two prostrations after saying the Salam."},"heading":{"title":"Two Prostrations for Every Mistake in Prayer","description":"This Hadith gives a broad statement about sujood sahw. Thawban said he heard the Messenger of Allah صلى الله عليه وسلم say, “For every mistake there are two prostrations, after saying the Salam.” The text is brief, so the explanation should stay close to it. It tells us that mistakes in prayer are met with two prostrations, and this narration places them after the Salam. This Hadith is highly relevant for searches like two prostrations for every mistake, sujood sahw after Salam, and prostration of forgetfulness Hadith. It is not a long case study like some other narrations, but it gives a clear general wording about mistakes and correction."},"teachings":["The Hadith states that every mistake has two prostrations.","This narration places the two prostrations after the Salam.","The text connects mistakes in prayer with a clear corrective action.","The wording is general and easy to remember."],"related_hadiths":[{"id":"1218","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1213","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1215","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E60" s="4" t="n"/>
@@ -1845,7 +1849,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Follow Imam Movements","description":"$book_name$ $hadith_number$ - $chapter_name$. $book_name$ teaches full coordination behind the imam: takbir, bowing, praise, prostration, and sitting if the imam sits."},"heading":{"title":"Follow the Imam: Takbir, Bowing, and Prostration","description":"This Hadith gives a fuller list of how followers act behind the imam. Anas bin Malik reports that the Prophet صلى الله عليه وسلم fell from his horse and injured his right side. When the time for prayer came, he led them while sitting, and they prayed behind him sitting. After the prayer, he explained that the imam is appointed to be followed. When the imam says Allahu Akbar, the followers say Allahu Akbar. When he bows, they bow. When he says Sami’ Allahu liman hamidah, they say Rabbana wa lakal-hamd. When he prostrates, they prostrate. If he prays sitting, they pray sitting."},"teachings":["Followers say takbir after the imam says takbir.","Followers bow and prostrate with the imam’s actions.","The Hadith teaches the response to Sami’ Allahu liman hamidah.","When the imam prayed sitting in this report, the followers prayed sitting."],"related_hadiths":[{"id":"688","book_id":"1","label":"Sahih Bukhari"},{"id":"689","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Follow Imam Movements","description":"$book_name$ $hadith_number$ - $chapter_name$. $book_name$ teaches full coordination behind the imam: takbir, bowing, praise, prostration, and sitting if the imam sits."},"heading":{"title":"Follow the Imam: Takbir, Bowing, and Prostration","description":"This Hadith gives a fuller list of how followers act behind the imam. Anas bin Malik reports that the Prophet صلى الله عليه وسلم fell from his horse and injured his right side. When the time for prayer came, he led them while sitting, and they prayed behind him sitting. After the prayer, he explained that the imam is appointed to be followed. When the imam says Allahu Akbar, the followers say Allahu Akbar. When he bows, they bow. When he says Sami’ Allahu liman hamidah, they say Rabbana wa lakal-hamd. When he prostrates, they prostrate. If he prays sitting, they pray sitting."},"teachings":["Followers say takbir after the imam says takbir.","Followers bow and prostrate with the imam’s actions.","The Hadith teaches the response to Sami’ Allahu liman hamidah.","When the imam prayed sitting in this report, the followers prayed sitting."],"related_hadiths":[{"id":"688","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"689","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E61" s="4" t="n"/>
@@ -1868,7 +1872,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Temporary Qunut in Subh Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas reports that the Prophet recited Qunut in Subh for one month while supplicating against a tribe, then stopped."},"heading":{"title":"Qunut in Subh Prayer: A One-Month Practice Mentioned by Anas","description":"This Hadith explains a specific case of Qunut in the Subh prayer. Anas bin Malik narrated that the Messenger of Allah (صلى الله عليه وسلم) used to recite Qunut in Subh and supplicate against one of the Arab tribes for one month. Then he stopped doing so. The important detail is the time limit mentioned in the report: one month. The narration does not present it as an endless daily routine in this wording. It shows a prayer moment connected with supplication, then an end to that action. People searching for Qunut in Fajr hadith or Subh prayer Qunut should notice the exact wording: he did it, made supplication, and then stopped."},"teachings":["The report mentions Qunut in Subh connected with supplication against a tribe.","The action is described as lasting for one month.","The ending, “then he stopped,” is part of the teaching and should not be ignored."],"related_hadiths":[{"id":"1241","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1242","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1244","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Temporary Qunut in Subh Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas reports that the Prophet recited Qunut in Subh for one month while supplicating against a tribe, then stopped."},"heading":{"title":"Qunut in Subh Prayer: A One-Month Practice Mentioned by Anas","description":"This Hadith explains a specific case of Qunut in the Subh prayer. Anas bin Malik narrated that the Messenger of Allah (صلى الله عليه وسلم) used to recite Qunut in Subh and supplicate against one of the Arab tribes for one month. Then he stopped doing so. The important detail is the time limit mentioned in the report: one month. The narration does not present it as an endless daily routine in this wording. It shows a prayer moment connected with supplication, then an end to that action. People searching for Qunut in Fajr hadith or Subh prayer Qunut should notice the exact wording: he did it, made supplication, and then stopped."},"teachings":["The report mentions Qunut in Subh connected with supplication against a tribe.","The action is described as lasting for one month.","The ending, “then he stopped,” is part of the teaching and should not be ignored."],"related_hadiths":[{"id":"1241","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1242","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1244","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E62" s="4" t="n"/>
@@ -1891,7 +1895,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Supplication After Ruku in Subh","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah reports a Subh prayer supplication for oppressed people in Makkah and against Mudar."},"heading":{"title":"Subh Prayer Dua: The Prophet’s Supplication for the Oppressed","description":"This Hadith gives the wording of a supplication said after rising from Ruku’ in the Subh prayer. Abu Hurairah narrated that the Messenger of Allah (صلى الله عليه وسلم) asked Allah to save Al-Walid bin Walid, Salamah bin Hisham, Ayyash bin Abu Rabi’ah, and the oppressed in Makkah. He also asked Allah to tighten His grip on Mudar and send them years like the famine of Yusuf. The core topic is prayer dua in Subh and concern for oppressed believers. The report is specific: it names people, mentions the oppressed in Makkah, and places the supplication after raising the head from Ruku’. This keeps the lesson close to the narrated wording."},"teachings":["The Prophet’s supplication included named people and the oppressed in Makkah.","The dua was said after rising from Ruku’ in the Subh prayer.","The Hadith shows that prayer can include heartfelt supplication for people in hardship."],"related_hadiths":[{"id":"1243","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1241","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1242","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Supplication After Ruku in Subh","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah reports a Subh prayer supplication for oppressed people in Makkah and against Mudar."},"heading":{"title":"Subh Prayer Dua: The Prophet’s Supplication for the Oppressed","description":"This Hadith gives the wording of a supplication said after rising from Ruku’ in the Subh prayer. Abu Hurairah narrated that the Messenger of Allah (صلى الله عليه وسلم) asked Allah to save Al-Walid bin Walid, Salamah bin Hisham, Ayyash bin Abu Rabi’ah, and the oppressed in Makkah. He also asked Allah to tighten His grip on Mudar and send them years like the famine of Yusuf. The core topic is prayer dua in Subh and concern for oppressed believers. The report is specific: it names people, mentions the oppressed in Makkah, and places the supplication after raising the head from Ruku’. This keeps the lesson close to the narrated wording."},"teachings":["The Prophet’s supplication included named people and the oppressed in Makkah.","The dua was said after rising from Ruku’ in the Subh prayer.","The Hadith shows that prayer can include heartfelt supplication for people in hardship."],"related_hadiths":[{"id":"1243","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1241","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1242","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E63" s="4" t="n"/>
@@ -1914,7 +1918,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Scorpion Harm During Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports the Prophet was stung during prayer and ordered scorpions killed in Hill and Haram."},"heading":{"title":"Scorpion During Prayer Hadith: Harm Is Not Ignored","description":"This Hadith gives a clear example of harm during prayer. Aishah narrated that the Prophet (صلى الله عليه وسلم) was stung by a scorpion while praying. He then said that the scorpion does not spare the one who is praying or the one who is not praying, and he ordered that it be killed whether in Ihram or not, in Al-Hill or Al-Haram. The wording keeps the focus on scorpions and the danger they pose. People looking for scorpion in prayer hadith or killing scorpion in Ihram should notice that the text links the command to the scorpion’s harm and its lack of distinction between people."},"teachings":["The Prophet (صلى الله عليه وسلم) was stung by a scorpion while praying, according to the report.","The Hadith states that a scorpion does not spare the praying or non-praying person.","The command is mentioned for both Ihram and non-Ihram, and for Hill and Haram."],"related_hadiths":[{"id":"1245","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1247","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1254","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Scorpion Harm During Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports the Prophet was stung during prayer and ordered scorpions killed in Hill and Haram."},"heading":{"title":"Scorpion During Prayer Hadith: Harm Is Not Ignored","description":"This Hadith gives a clear example of harm during prayer. Aishah narrated that the Prophet (صلى الله عليه وسلم) was stung by a scorpion while praying. He then said that the scorpion does not spare the one who is praying or the one who is not praying, and he ordered that it be killed whether in Ihram or not, in Al-Hill or Al-Haram. The wording keeps the focus on scorpions and the danger they pose. People looking for scorpion in prayer hadith or killing scorpion in Ihram should notice that the text links the command to the scorpion’s harm and its lack of distinction between people."},"teachings":["The Prophet (صلى الله عليه وسلم) was stung by a scorpion while praying, according to the report.","The Hadith states that a scorpion does not spare the praying or non-praying person.","The command is mentioned for both Ihram and non-Ihram, and for Hill and Haram."],"related_hadiths":[{"id":"1245","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1247","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1254","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E64" s="4" t="n"/>
@@ -1937,7 +1941,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witnesses on Restricted Prayer Times","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports testimony from trusted men, including Umar, about no prayer after Fajr or Asr until sunrise or sunset."},"heading":{"title":"Restricted Prayer Times Hadith: Testimony from Trusted Men","description":"This Hadith reports the same timing rule through Ibn Abbas, who said that good men testified before him, including Umar bin Khattab, whom he held in high regard. They testified that the Messenger of Allah (صلى الله عليه وسلم) said there is no prayer after Fajr until the sun has risen, and no prayer after Asr until the sun has set. The wording adds the idea of testimony from trusted people while keeping the ruling tied to two times. Searches like hadith no prayer after Fajr and no salah after Asr connect strongly to this report. It teaches both timing and care in transmitting prayer knowledge."},"teachings":["The report gives the rule through testimony from trusted men.","It confirms no prayer after Fajr until sunrise.","It confirms no prayer after Asr until sunset."],"related_hadiths":[{"id":"1248","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1249","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1251","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witnesses on Restricted Prayer Times","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports testimony from trusted men, including Umar, about no prayer after Fajr or Asr until sunrise or sunset."},"heading":{"title":"Restricted Prayer Times Hadith: Testimony from Trusted Men","description":"This Hadith reports the same timing rule through Ibn Abbas, who said that good men testified before him, including Umar bin Khattab, whom he held in high regard. They testified that the Messenger of Allah (صلى الله عليه وسلم) said there is no prayer after Fajr until the sun has risen, and no prayer after Asr until the sun has set. The wording adds the idea of testimony from trusted people while keeping the ruling tied to two times. Searches like hadith no prayer after Fajr and no salah after Asr connect strongly to this report. It teaches both timing and care in transmitting prayer knowledge."},"teachings":["The report gives the rule through testimony from trusted men.","It confirms no prayer after Fajr until sunrise.","It confirms no prayer after Asr until sunset."],"related_hadiths":[{"id":"1248","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1249","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1251","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E65" s="4" t="n"/>
@@ -1960,7 +1964,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Time and Times to Stop Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Amr bin Abasah reports the middle of the night as beloved and lists times to pray or refrain from prayer."},"heading":{"title":"Best Time for Prayer and Times to Refrain: Amr bin Abasah Hadith","description":"This Hadith gives a fuller map of prayer times. Amr bin Abasah asked whether one time is more beloved to Allah than another. The Prophet (صلى الله عليه وسلم) answered that the middle of the night is beloved, then explained when to pray and when to stop. The report says to pray until dawn, stop until the sun rises and becomes clear, pray until noon, stop until the sun crosses the zenith, then pray until Asr, and stop until sunset. It also mentions the sun rising and setting between the two horns of Satan. People searching for best time for night prayer or forbidden prayer times will find both themes here."},"teachings":["The middle of the night is named as a beloved time for prayer.","The Hadith gives several times to pray and several times to refrain.","The report connects the prayer schedule with dawn, sunrise, noon, Asr, and sunset."],"related_hadiths":[{"id":"1248","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1252","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1253","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Time and Times to Stop Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Amr bin Abasah reports the middle of the night as beloved and lists times to pray or refrain from prayer."},"heading":{"title":"Best Time for Prayer and Times to Refrain: Amr bin Abasah Hadith","description":"This Hadith gives a fuller map of prayer times. Amr bin Abasah asked whether one time is more beloved to Allah than another. The Prophet (صلى الله عليه وسلم) answered that the middle of the night is beloved, then explained when to pray and when to stop. The report says to pray until dawn, stop until the sun rises and becomes clear, pray until noon, stop until the sun crosses the zenith, then pray until Asr, and stop until sunset. It also mentions the sun rising and setting between the two horns of Satan. People searching for best time for night prayer or forbidden prayer times will find both themes here."},"teachings":["The middle of the night is named as a beloved time for prayer.","The Hadith gives several times to pray and several times to refrain.","The report connects the prayer schedule with dawn, sunrise, noon, Asr, and sunset."],"related_hadiths":[{"id":"1248","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1252","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1253","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E66" s="4" t="n"/>
@@ -1983,7 +1987,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Disliked Times for Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Safwan asks about disliked prayer times, and the Prophet explains periods after Subh, at midday, and after Asr."},"heading":{"title":"Disliked Times for Prayer: A Direct Question and Answer","description":"This Hadith is built around a clear question. Safwan bin Muattal asked the Messenger of Allah (صلى الله عليه وسلم) whether there is any time of the night or day when prayer is disliked. The answer names key times: after Subh until sunrise, when the sun is overhead like a spear until it passes the zenith, and after Asr until sunset. The narration also says that prayer is attended and acceptable after the sun has risen and after it has passed the zenith until Asr. People searching for disliked prayer times in Islam or prayer after Fajr hadith should notice the careful movement from stop, to pray, to stop again."},"teachings":["The Companion asked directly about times when prayer is disliked.","The Hadith names stopping after Subh, at midday, and after Asr.","The report also mentions times when prayer is attended and acceptable."],"related_hadiths":[{"id":"1251","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1253","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1248","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Disliked Times for Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Safwan asks about disliked prayer times, and the Prophet explains periods after Subh, at midday, and after Asr."},"heading":{"title":"Disliked Times for Prayer: A Direct Question and Answer","description":"This Hadith is built around a clear question. Safwan bin Muattal asked the Messenger of Allah (صلى الله عليه وسلم) whether there is any time of the night or day when prayer is disliked. The answer names key times: after Subh until sunrise, when the sun is overhead like a spear until it passes the zenith, and after Asr until sunset. The narration also says that prayer is attended and acceptable after the sun has risen and after it has passed the zenith until Asr. People searching for disliked prayer times in Islam or prayer after Fajr hadith should notice the careful movement from stop, to pray, to stop again."},"teachings":["The Companion asked directly about times when prayer is disliked.","The Hadith names stopping after Subh, at midday, and after Asr.","The report also mentions times when prayer is attended and acceptable."],"related_hadiths":[{"id":"1251","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1253","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1248","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E67" s="4" t="n"/>
@@ -2006,7 +2010,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Times Not to Pray","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet mentions three times linked with sunrise, midday, and sunset when prayer should not be offered."},"heading":{"title":"Three Forbidden Prayer Times: Sunrise, Midday and Sunset","description":"This Hadith gives a focused summary of three times not to pray. Abu Abdullah As-Sunabihi narrated that the Messenger of Allah (صلى الله عليه وسلم) spoke about the sun and the two horns of Satan. The report mentions sunrise, the middle of the sky, and the time near sunset. It says Satan parts from the sun after it has risen, after it has crossed the zenith, and after it has set. The final instruction is clear: do not pray at these three times. For searches like three forbidden prayer times or sunrise sunset prayer hadith, this narration gives the main time markers in one report."},"teachings":["The Hadith identifies three times connected with the sun’s position.","It names sunrise, the middle of the sky, and near sunset.","The final command is to avoid prayer during those three times."],"related_hadiths":[{"id":"1251","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1252","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1249","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Times Not to Pray","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet mentions three times linked with sunrise, midday, and sunset when prayer should not be offered."},"heading":{"title":"Three Forbidden Prayer Times: Sunrise, Midday and Sunset","description":"This Hadith gives a focused summary of three times not to pray. Abu Abdullah As-Sunabihi narrated that the Messenger of Allah (صلى الله عليه وسلم) spoke about the sun and the two horns of Satan. The report mentions sunrise, the middle of the sky, and the time near sunset. It says Satan parts from the sun after it has risen, after it has crossed the zenith, and after it has set. The final instruction is clear: do not pray at these three times. For searches like three forbidden prayer times or sunrise sunset prayer hadith, this narration gives the main time markers in one report."},"teachings":["The Hadith identifies three times connected with the sun’s position.","It names sunrise, the middle of the sky, and near sunset.","The final command is to avoid prayer during those three times."],"related_hadiths":[{"id":"1251","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1252","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1249","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E68" s="4" t="n"/>
@@ -2029,7 +2033,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying On Time With Delayed Leaders","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Masud reports guidance when people offer prayer at the wrong time: pray on time, then join them as voluntary."},"heading":{"title":"Pray on Time: What to Do When Others Delay the Prayer","description":"This Hadith gives practical guidance for a difficult situation. Abdullah bin Masud narrated that the Messenger of Allah (صلى الله عليه وسلم) said people may come across groups who pray at the wrong time. If that happens, they should pray in their houses at the time they know, then pray with those people and make it voluntary. The text keeps two duties clear: protect the known prayer time, and still join the later prayer as a voluntary act. People searching for pray on time hadith or leaders delaying prayer hadith will see a balanced instruction without making the delayed prayer replace the timely one."},"teachings":["The first instruction is to pray at the time that is known.","The later prayer with others is described as voluntary.","The Hadith prepares Muslims for a situation where prayer is offered at the wrong time."],"related_hadiths":[{"id":"1256","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1257","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1248","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying On Time With Delayed Leaders","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Masud reports guidance when people offer prayer at the wrong time: pray on time, then join them as voluntary."},"heading":{"title":"Pray on Time: What to Do When Others Delay the Prayer","description":"This Hadith gives practical guidance for a difficult situation. Abdullah bin Masud narrated that the Messenger of Allah (صلى الله عليه وسلم) said people may come across groups who pray at the wrong time. If that happens, they should pray in their houses at the time they know, then pray with those people and make it voluntary. The text keeps two duties clear: protect the known prayer time, and still join the later prayer as a voluntary act. People searching for pray on time hadith or leaders delaying prayer hadith will see a balanced instruction without making the delayed prayer replace the timely one."},"teachings":["The first instruction is to pray at the time that is known.","The later prayer with others is described as voluntary.","The Hadith prepares Muslims for a situation where prayer is offered at the wrong time."],"related_hadiths":[{"id":"1256","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1257","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1248","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E69" s="4" t="n"/>
@@ -2052,7 +2056,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Delayed Prayer by Leaders","description":"$book_name$ $hadith_number$ - $chapter_name$. Ubadah reports that some leaders will delay prayer past its time, so praying with them should be made voluntary."},"heading":{"title":"Delayed Prayer by Leaders: Keep Your Prayer Safe","description":"This Hadith speaks about leaders who become distracted by matters and delay prayer beyond its proper time. Ubadah bin Samit narrated that the Prophet (صلى الله عليه وسلم) said to make the prayer with them voluntary. The wording does not praise delaying prayer. It points to a situation that may happen and tells the believer how to respond. The key is that the person should not let the delayed group prayer become his only prayer if the proper time has passed. For searches like leaders delay prayer hadith or pray with delayed imam, this narration is closely linked to the duty of guarding prayer time."},"teachings":["The Hadith warns of leaders who delay prayer beyond its proper time.","The prayer with those leaders is to be made voluntary.","The report teaches care for the proper time of prayer."],"related_hadiths":[{"id":"1255","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1256","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1248","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Delayed Prayer by Leaders","description":"$book_name$ $hadith_number$ - $chapter_name$. Ubadah reports that some leaders will delay prayer past its time, so praying with them should be made voluntary."},"heading":{"title":"Delayed Prayer by Leaders: Keep Your Prayer Safe","description":"This Hadith speaks about leaders who become distracted by matters and delay prayer beyond its proper time. Ubadah bin Samit narrated that the Prophet (صلى الله عليه وسلم) said to make the prayer with them voluntary. The wording does not praise delaying prayer. It points to a situation that may happen and tells the believer how to respond. The key is that the person should not let the delayed group prayer become his only prayer if the proper time has passed. For searches like leaders delay prayer hadith or pray with delayed imam, this narration is closely linked to the duty of guarding prayer time."},"teachings":["The Hadith warns of leaders who delay prayer beyond its proper time.","The prayer with those leaders is to be made voluntary.","The report teaches care for the proper time of prayer."],"related_hadiths":[{"id":"1255","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1256","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1248","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E70" s="4" t="n"/>
@@ -2075,7 +2079,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | How to Pray in Fear","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports a form of fear prayer with two groups, an Imam, guarding, and prayer on foot or riding if fear is greater."},"heading":{"title":"Fear Prayer Hadith: Two Groups, One Imam, and Guarding","description":"This Hadith explains a form of Salat al-Khawf, the fear prayer. Ibn Umar narrated that the Imam leads one group while another group stands between them and the enemy. The first group prays one Rak’ah with the leader, then changes places with the group that has not prayed. The second group then prays one Rak’ah with the leader. After the leader finishes, each group completes one Rak’ah by itself. The report also says that if fear is greater, they may pray on foot or riding. People searching for fear prayer hadith or how to pray Salat al-Khawf will find the steps clearly laid out here."},"teachings":["The Hadith describes two groups taking turns in prayer and guarding.","The Imam’s prayer is completed while each group completes what remains.","If fear is greater, the report allows praying on foot or riding."],"related_hadiths":[{"id":"1259","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1260","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | How to Pray in Fear","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports a form of fear prayer with two groups, an Imam, guarding, and prayer on foot or riding if fear is greater."},"heading":{"title":"Fear Prayer Hadith: Two Groups, One Imam, and Guarding","description":"This Hadith explains a form of Salat al-Khawf, the fear prayer. Ibn Umar narrated that the Imam leads one group while another group stands between them and the enemy. The first group prays one Rak’ah with the leader, then changes places with the group that has not prayed. The second group then prays one Rak’ah with the leader. After the leader finishes, each group completes one Rak’ah by itself. The report also says that if fear is greater, they may pray on foot or riding. People searching for fear prayer hadith or how to pray Salat al-Khawf will find the steps clearly laid out here."},"teachings":["The Hadith describes two groups taking turns in prayer and guarding.","The Imam’s prayer is completed while each group completes what remains.","If fear is greater, the report allows praying on foot or riding."],"related_hadiths":[{"id":"1259","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1260","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E71" s="4" t="n"/>
@@ -2098,7 +2102,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fear Prayer Facing the Qiblah","description":"$book_name$ $hadith_number$ - $chapter_name$. Sahl reports a fear prayer method where one group prays with the Imam while another faces the enemy, then they switch."},"heading":{"title":"Fear Prayer Method: Groups Switching While Guarding","description":"This Hadith gives another detailed description of the fear prayer. Sahl bin Abu Hathmah said that the Imam stands facing the Qiblah. One group stands with him, while another group faces the enemy. The Imam leads the first group in one Rak’ah. They then complete bowing and two prostrations by themselves and move to the place of the other group. The second group comes and prays one Rak’ah with the leader, then completes another Rak’ah. The wording is organized around prayer, guarding, and switching places. Searches like Salat al-Khawf method and fear prayer two groups fit this report closely. This keeps the lesson close to the narrated wording."},"teachings":["The Imam stands facing the Qiblah in this description.","One group prays while another group watches toward the enemy.","The groups switch so both take part in prayer and guarding."],"related_hadiths":[{"id":"1258","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1260","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fear Prayer Facing the Qiblah","description":"$book_name$ $hadith_number$ - $chapter_name$. Sahl reports a fear prayer method where one group prays with the Imam while another faces the enemy, then they switch."},"heading":{"title":"Fear Prayer Method: Groups Switching While Guarding","description":"This Hadith gives another detailed description of the fear prayer. Sahl bin Abu Hathmah said that the Imam stands facing the Qiblah. One group stands with him, while another group faces the enemy. The Imam leads the first group in one Rak’ah. They then complete bowing and two prostrations by themselves and move to the place of the other group. The second group comes and prays one Rak’ah with the leader, then completes another Rak’ah. The wording is organized around prayer, guarding, and switching places. Searches like Salat al-Khawf method and fear prayer two groups fit this report closely. This keeps the lesson close to the narrated wording."},"teachings":["The Imam stands facing the Qiblah in this description.","One group prays while another group watches toward the enemy.","The groups switch so both take part in prayer and guarding."],"related_hadiths":[{"id":"1258","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1260","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E72" s="4" t="n"/>
@@ -2121,7 +2125,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eclipse Prayer and Allah's Signs","description":"$book_name$ $hadith_number$ - $chapter_name$. The eclipse is not tied to anyone's death; believers are taught to stand in prayer."},"heading":{"title":"Eclipse Prayer: A Clear Sunnah Response","description":"This Hadith teaches a clear message about the eclipse prayer. The sun and moon do not become eclipsed because of the death of any person. The Prophet صلى الله عليه وسلم corrected that belief in simple words and directed people to prayer when they see an eclipse. The main lesson is not fear of people or events, but turning to Allah through Salah. For anyone searching for a hadith about eclipse, solar eclipse prayer, or lunar eclipse in Islam, this narration gives the direct response: stand and pray. The Hadith keeps the focus on worship and removes superstition from the heart."},"teachings":["An eclipse is not caused by the death of any human being.","When an eclipse is seen, prayer is the taught response.","Islam guides people away from superstition and toward worship.","Natural signs should remind believers to turn to Allah."],"related_hadiths":[{"id":"1262","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1263","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1264","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eclipse Prayer and Allah's Signs","description":"$book_name$ $hadith_number$ - $chapter_name$. The eclipse is not tied to anyone's death; believers are taught to stand in prayer."},"heading":{"title":"Eclipse Prayer: A Clear Sunnah Response","description":"This Hadith teaches a clear message about the eclipse prayer. The sun and moon do not become eclipsed because of the death of any person. The Prophet صلى الله عليه وسلم corrected that belief in simple words and directed people to prayer when they see an eclipse. The main lesson is not fear of people or events, but turning to Allah through Salah. For anyone searching for a hadith about eclipse, solar eclipse prayer, or lunar eclipse in Islam, this narration gives the direct response: stand and pray. The Hadith keeps the focus on worship and removes superstition from the heart."},"teachings":["An eclipse is not caused by the death of any human being.","When an eclipse is seen, prayer is the taught response.","Islam guides people away from superstition and toward worship.","Natural signs should remind believers to turn to Allah."],"related_hadiths":[{"id":"1262","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1263","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1264","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E73" s="4" t="n"/>
@@ -2144,7 +2148,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eclipse and Humility Before Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. The eclipse is not for a leader's death or birth; creation humbles itself before Allah."},"heading":{"title":"Eclipse Hadith: Humility Before Allah","description":"This Hadith shows how the Prophet صلى الله عليه وسلم reacted when the sun was eclipsed. He went out alarmed to the mosque and kept praying until the eclipse ended. Then he corrected a common claim: the sun and moon do not become eclipsed because of the death of a great person, nor because of anyone's life. The Hadith points the heart back to Allah. It says that when Allah manifests Himself to anything in His creation, it becomes humble before Him. So the core lesson of this eclipse hadith is humility, prayer, and leaving false beliefs about natural signs."},"teachings":["The eclipse is not linked to the death or birth of any person.","The Prophet صلى الله عليه وسلم responded to the eclipse with prayer.","Creation humbles itself before Allah.","False claims about natural signs should be corrected with clear teaching."],"related_hadiths":[{"id":"1261","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1263","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1265","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eclipse and Humility Before Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. The eclipse is not for a leader's death or birth; creation humbles itself before Allah."},"heading":{"title":"Eclipse Hadith: Humility Before Allah","description":"This Hadith shows how the Prophet صلى الله عليه وسلم reacted when the sun was eclipsed. He went out alarmed to the mosque and kept praying until the eclipse ended. Then he corrected a common claim: the sun and moon do not become eclipsed because of the death of a great person, nor because of anyone's life. The Hadith points the heart back to Allah. It says that when Allah manifests Himself to anything in His creation, it becomes humble before Him. So the core lesson of this eclipse hadith is humility, prayer, and leaving false beliefs about natural signs."},"teachings":["The eclipse is not linked to the death or birth of any person.","The Prophet صلى الله عليه وسلم responded to the eclipse with prayer.","Creation humbles itself before Allah.","False claims about natural signs should be corrected with clear teaching."],"related_hadiths":[{"id":"1261","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1263","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1265","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E74" s="4" t="n"/>
@@ -2167,7 +2171,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | How the Eclipse Prayer Was Prayed","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed long recitations and bows during the eclipse, then called people to prayer."},"heading":{"title":"How to Pray Eclipse Prayer from Hadith","description":"This detailed Hadith explains the eclipse prayer in action. When the sun was eclipsed, the Prophet صلى الله عليه وسلم went to the mosque, said Takbir, and the people lined up behind him. He recited for a long time, bowed for a long time, stood again, recited again, and bowed again. The same pattern was repeated in the next Rak'ah, making four bows and four prostrations in total. Afterward, he addressed the people and said that the sun and moon are signs of Allah. They do not eclipse for anyone's death or birth. If people see them, they should seek help in prayer."},"teachings":["The eclipse prayer is connected with long standing, recitation, bowing, and prostration.","The Prophet صلى الله عليه وسلم led the people in prayer during the eclipse.","The sun and moon are signs of Allah, not signs of human death or birth.","Prayer is a means of seeking help when such signs are seen."],"related_hadiths":[{"id":"1261","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1262","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1265","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | How the Eclipse Prayer Was Prayed","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed long recitations and bows during the eclipse, then called people to prayer."},"heading":{"title":"How to Pray Eclipse Prayer from Hadith","description":"This detailed Hadith explains the eclipse prayer in action. When the sun was eclipsed, the Prophet صلى الله عليه وسلم went to the mosque, said Takbir, and the people lined up behind him. He recited for a long time, bowed for a long time, stood again, recited again, and bowed again. The same pattern was repeated in the next Rak'ah, making four bows and four prostrations in total. Afterward, he addressed the people and said that the sun and moon are signs of Allah. They do not eclipse for anyone's death or birth. If people see them, they should seek help in prayer."},"teachings":["The eclipse prayer is connected with long standing, recitation, bowing, and prostration.","The Prophet صلى الله عليه وسلم led the people in prayer during the eclipse.","The sun and moon are signs of Allah, not signs of human death or birth.","Prayer is a means of seeking help when such signs are seen."],"related_hadiths":[{"id":"1261","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1262","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1265","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E75" s="4" t="n"/>
@@ -2190,7 +2194,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Silent Recitation in Eclipse Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Samurah reports that the Prophet صلى الله عليه وسلم led the eclipse prayer and his voice was not heard."},"heading":{"title":"Silent Eclipse Prayer in the Sunnah","description":"This short Hadith focuses on one clear detail from the eclipse prayer. Samurah bin Jundab said that the Messenger of Allah صلى الله عليه وسلم led them in the eclipse prayer, and they did not hear his voice. The narration does not add extra explanation or describe the full prayer method. Its main value is the reported practice during that prayer: the people were led in Salah, but the recitation was not heard by them. For searches like silent eclipse prayer, eclipse prayer recitation, and Salatul Kusuf hadith, this narration should be explained carefully without adding details that are not in the text."},"teachings":["The Prophet صلى الله عليه وسلم led the companions in the eclipse prayer.","Samurah reports that they did not hear his voice during that prayer.","A short Hadith can preserve one specific practice clearly.","Explanations should stay within the detail given in the narration."],"related_hadiths":[{"id":"1261","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1263","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1265","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Silent Recitation in Eclipse Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Samurah reports that the Prophet صلى الله عليه وسلم led the eclipse prayer and his voice was not heard."},"heading":{"title":"Silent Eclipse Prayer in the Sunnah","description":"This short Hadith focuses on one clear detail from the eclipse prayer. Samurah bin Jundab said that the Messenger of Allah صلى الله عليه وسلم led them in the eclipse prayer, and they did not hear his voice. The narration does not add extra explanation or describe the full prayer method. Its main value is the reported practice during that prayer: the people were led in Salah, but the recitation was not heard by them. For searches like silent eclipse prayer, eclipse prayer recitation, and Salatul Kusuf hadith, this narration should be explained carefully without adding details that are not in the text."},"teachings":["The Prophet صلى الله عليه وسلم led the companions in the eclipse prayer.","Samurah reports that they did not hear his voice during that prayer.","A short Hadith can preserve one specific practice clearly.","Explanations should stay within the detail given in the narration."],"related_hadiths":[{"id":"1261","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1263","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1265","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E76" s="4" t="n"/>
@@ -2213,7 +2217,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer for Rain with Humility","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم went out humbly for rain prayer and prayed two Rak'ah like Eid."},"heading":{"title":"Prayer for Rain: Humility and Two Rak'ah","description":"This Hadith explains the prayer for rain through the report of Ibn 'Abbas. The Prophet صلى الله عليه وسلم went out in a humble state, with a humble and moderate walk, showing need before Allah. He performed two Rak'ah as he used to pray for Eid. The narration also says that he did not give a sermon like the sermon being referred to in the question. The core teaching is that Salat al-Istisqa is not only an outward prayer for rain; it is done with humility, calmness, and pleading to Allah. For anyone searching for prayer for rain hadith, this narration gives a simple picture of the Prophet's manner."},"teachings":["The prayer for rain is connected with humility before Allah.","The Prophet صلى الله عليه وسلم prayed two Rak'ah for rain.","The prayer was compared to the Eid prayer in this narration.","Asking Allah for rain should be done with need and humbleness."],"related_hadiths":[{"id":"1267","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1268","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1271","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer for Rain with Humility","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم went out humbly for rain prayer and prayed two Rak'ah like Eid."},"heading":{"title":"Prayer for Rain: Humility and Two Rak'ah","description":"This Hadith explains the prayer for rain through the report of Ibn 'Abbas. The Prophet صلى الله عليه وسلم went out in a humble state, with a humble and moderate walk, showing need before Allah. He performed two Rak'ah as he used to pray for Eid. The narration also says that he did not give a sermon like the sermon being referred to in the question. The core teaching is that Salat al-Istisqa is not only an outward prayer for rain; it is done with humility, calmness, and pleading to Allah. For anyone searching for prayer for rain hadith, this narration gives a simple picture of the Prophet's manner."},"teachings":["The prayer for rain is connected with humility before Allah.","The Prophet صلى الله عليه وسلم prayed two Rak'ah for rain.","The prayer was compared to the Eid prayer in this narration.","Asking Allah for rain should be done with need and humbleness."],"related_hadiths":[{"id":"1267","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1268","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1271","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E77" s="4" t="n"/>
@@ -2236,7 +2240,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rain Prayer Without Adhan","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed two Rak'ah for rain without Adhan or Iqamah, then made dua."},"heading":{"title":"Rain Prayer Without Adhan or Iqamah","description":"This Hadith explains several details about the prayer for rain. Abu Hurairah reports that the Prophet صلى الله عليه وسلم went out one day to pray for rain. He led the people in two Rak'ah without any Adhan or Iqamah. Then he addressed them and supplicated to Allah. He turned his face toward the Qiblah, raised his hands, and turned his cloak, putting the right side on the left and the left side on the right. For searches like prayer for rain without Adhan, Salat al-Istisqa method, and rain dua hadith, this narration is direct and practical. It shows prayer, supplication, Qiblah, raised hands, and cloak turning together."},"teachings":["The rain prayer was performed as two Rak'ah in this report.","There was no Adhan or Iqamah for this prayer.","The Prophet صلى الله عليه وسلم made dua facing the Qiblah and raising his hands.","He turned his cloak by placing the right side on the left and the left on the right."],"related_hadiths":[{"id":"1266","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1267","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1271","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rain Prayer Without Adhan","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed two Rak'ah for rain without Adhan or Iqamah, then made dua."},"heading":{"title":"Rain Prayer Without Adhan or Iqamah","description":"This Hadith explains several details about the prayer for rain. Abu Hurairah reports that the Prophet صلى الله عليه وسلم went out one day to pray for rain. He led the people in two Rak'ah without any Adhan or Iqamah. Then he addressed them and supplicated to Allah. He turned his face toward the Qiblah, raised his hands, and turned his cloak, putting the right side on the left and the left side on the right. For searches like prayer for rain without Adhan, Salat al-Istisqa method, and rain dua hadith, this narration is direct and practical. It shows prayer, supplication, Qiblah, raised hands, and cloak turning together."},"teachings":["The rain prayer was performed as two Rak'ah in this report.","There was no Adhan or Iqamah for this prayer.","The Prophet صلى الله عليه وسلم made dua facing the Qiblah and raising his hands.","He turned his cloak by placing the right side on the left and the left on the right."],"related_hadiths":[{"id":"1266","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1267","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1271","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E78" s="4" t="n"/>
@@ -2259,7 +2263,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rain Dua in Time of Need","description":"$book_name$ $hadith_number$ - $chapter_name$. A Bedouin described drought, and the Prophet صلى الله عليه وسلم asked Allah for abundant, wholesome rain."},"heading":{"title":"Rain Dua When People Are in Need","description":"This Hadith shows a moment of real need. A Bedouin came to the Prophet صلى الله عليه وسلم and described people whose flocks had no place to graze and whose camels had become weak. The Prophet صلى الله عليه وسلم mounted the pulpit, praised Allah, and asked for abundant, wholesome, productive, plentiful rain, sooner rather than later. After the rain came down, people came from different directions saying they had been revived. The narration teaches that the Prophet صلى الله عليه وسلم responded to hardship by praising Allah and making dua. For searches like dua for rain in drought, prayer for rain hadith, and rain dua Arabic, this Hadith is direct and moving."},"teachings":["The Prophet صلى الله عليه وسلم listened to people who described drought and hardship.","He praised Allah before making the rain dua.","He asked for rain that was abundant, wholesome, productive, and quick.","The report shows relief after the rain came down."],"related_hadiths":[{"id":"1269","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1271","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1268","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rain Dua in Time of Need","description":"$book_name$ $hadith_number$ - $chapter_name$. A Bedouin described drought, and the Prophet صلى الله عليه وسلم asked Allah for abundant, wholesome rain."},"heading":{"title":"Rain Dua When People Are in Need","description":"This Hadith shows a moment of real need. A Bedouin came to the Prophet صلى الله عليه وسلم and described people whose flocks had no place to graze and whose camels had become weak. The Prophet صلى الله عليه وسلم mounted the pulpit, praised Allah, and asked for abundant, wholesome, productive, plentiful rain, sooner rather than later. After the rain came down, people came from different directions saying they had been revived. The narration teaches that the Prophet صلى الله عليه وسلم responded to hardship by praising Allah and making dua. For searches like dua for rain in drought, prayer for rain hadith, and rain dua Arabic, this Hadith is direct and moving."},"teachings":["The Prophet صلى الله عليه وسلم listened to people who described drought and hardship.","He praised Allah before making the rain dua.","He asked for rain that was abundant, wholesome, productive, and quick.","The report shows relief after the rain came down."],"related_hadiths":[{"id":"1269","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1271","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1268","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E79" s="4" t="n"/>
@@ -2282,7 +2286,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Raising Hands in Rain Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah reports the Prophet صلى الله عليه وسلم raised his hands high while supplicating for rain."},"heading":{"title":"Raising Hands High in Dua for Rain","description":"This Hadith focuses on the Prophet's صلى الله عليه وسلم posture while making dua for rain. Abu Hurairah reports that the Prophet صلى الله عليه وسلم supplicated for rain until the whiteness of his armpits could be seen. The narration is brief, but it gives a strong visual detail: the hands were raised high in supplication. The text does not give the wording of the dua here, nor the full prayer method. Its main topic is raising hands in rain dua. For people searching for Salat al-Istisqa hadith, raising hands for rain, or how the Prophet made dua for rain, this narration gives one clear practice from the Sunnah."},"teachings":["The Prophet صلى الله عليه وسلم supplicated for rain.","He raised his hands high during this supplication.","The narration gives a specific detail without adding the full wording of the dua.","Asking Allah for rain is shown as an earnest act of need."],"related_hadiths":[{"id":"1268","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1269","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1270","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Raising Hands in Rain Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah reports the Prophet صلى الله عليه وسلم raised his hands high while supplicating for rain."},"heading":{"title":"Raising Hands High in Dua for Rain","description":"This Hadith focuses on the Prophet's صلى الله عليه وسلم posture while making dua for rain. Abu Hurairah reports that the Prophet صلى الله عليه وسلم supplicated for rain until the whiteness of his armpits could be seen. The narration is brief, but it gives a strong visual detail: the hands were raised high in supplication. The text does not give the wording of the dua here, nor the full prayer method. Its main topic is raising hands in rain dua. For people searching for Salat al-Istisqa hadith, raising hands for rain, or how the Prophet made dua for rain, this narration gives one clear practice from the Sunnah."},"teachings":["The Prophet صلى الله عليه وسلم supplicated for rain.","He raised his hands high during this supplication.","The narration gives a specific detail without adding the full wording of the dua.","Asking Allah for rain is shown as an earnest act of need."],"related_hadiths":[{"id":"1268","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1269","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1270","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E80" s="4" t="n"/>
@@ -2305,7 +2309,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the Prophet’s practice of reciting Al-A’la and Al-Ghashiyah in the Eid prayer."},"heading":{"title":"Eid Prayer Recitation: Surahs the Prophet Used","description":"This hadith explains a clear part of the Prophet’s Eid prayer recitation. Nu’man bin Bashir narrated that the Messenger of Allah صلى الله عليه وسلم used to recite Surah Al-A’la and Surah Al-Ghashiyah in the two Eid prayers. The main lesson is simple: Eid prayer was not only a public gathering, but also a prayer filled with Qur’an. For people searching for what to recite in Eid prayer, this narration gives a direct answer from the practice of the Prophet صلى الله عليه وسلم. The wording says he used to recite these chapters, so we should present it as a reported practice, not as an invented rule beyond the text."},"teachings":["The Prophet صلى الله عليه وسلم recited Qur’an in the Eid prayer.","Surah Al-A’la and Surah Al-Ghashiyah are mentioned as Eid prayer recitations.","A repeated Prophetic practice can guide Muslims in worship.","The narration keeps the focus on prayer and Qur’an during Eid."],"related_hadiths":[{"id":"1283","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1282","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the Prophet’s practice of reciting Al-A’la and Al-Ghashiyah in the Eid prayer."},"heading":{"title":"Eid Prayer Recitation: Surahs the Prophet Used","description":"This hadith explains a clear part of the Prophet’s Eid prayer recitation. Nu’man bin Bashir narrated that the Messenger of Allah صلى الله عليه وسلم used to recite Surah Al-A’la and Surah Al-Ghashiyah in the two Eid prayers. The main lesson is simple: Eid prayer was not only a public gathering, but also a prayer filled with Qur’an. For people searching for what to recite in Eid prayer, this narration gives a direct answer from the practice of the Prophet صلى الله عليه وسلم. The wording says he used to recite these chapters, so we should present it as a reported practice, not as an invented rule beyond the text."},"teachings":["The Prophet صلى الله عليه وسلم recited Qur’an in the Eid prayer.","Surah Al-A’la and Surah Al-Ghashiyah are mentioned as Eid prayer recitations.","A repeated Prophetic practice can guide Muslims in worship.","The narration keeps the focus on prayer and Qur’an during Eid."],"related_hadiths":[{"id":"1283","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1282","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E81" s="4" t="n"/>
@@ -2328,7 +2332,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qaf and Al-Qamar in Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith reports that the Prophet صلى الله عليه وسلم recited Surah Qaf and Surah Al-Qamar on Eid."},"heading":{"title":"Eid Prayer Recitation with Surah Qaf and Al-Qamar","description":"This hadith gives another reported example of Eid prayer recitation. Umar went out on Eid and asked Abu Waqid Al-Laithi what the Prophet صلى الله عليه وسلم used to recite on a day like this. Abu Waqid answered that he recited Surah Qaf and Surah Al-Qamar. This is useful for anyone searching for Eid salah surahs or the Sunnah recitation in Eid prayer. The narration also shows that the Companions asked about the Prophet’s practice so they could follow it carefully. The text does not say this was the only recitation used on Eid, but it clearly reports these two chapters as part of his practice."},"teachings":["The Companions cared about preserving the Prophet’s Eid prayer practice.","Surah Qaf and Surah Al-Qamar are reported as Eid prayer recitations.","Asking knowledgeable people can help preserve Sunnah practice.","Eid prayer includes Qur’an recitation with meaningful reminders."],"related_hadiths":[{"id":"1281","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1283","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qaf and Al-Qamar in Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith reports that the Prophet صلى الله عليه وسلم recited Surah Qaf and Surah Al-Qamar on Eid."},"heading":{"title":"Eid Prayer Recitation with Surah Qaf and Al-Qamar","description":"This hadith gives another reported example of Eid prayer recitation. Umar went out on Eid and asked Abu Waqid Al-Laithi what the Prophet صلى الله عليه وسلم used to recite on a day like this. Abu Waqid answered that he recited Surah Qaf and Surah Al-Qamar. This is useful for anyone searching for Eid salah surahs or the Sunnah recitation in Eid prayer. The narration also shows that the Companions asked about the Prophet’s practice so they could follow it carefully. The text does not say this was the only recitation used on Eid, but it clearly reports these two chapters as part of his practice."},"teachings":["The Companions cared about preserving the Prophet’s Eid prayer practice.","Surah Qaf and Surah Al-Qamar are reported as Eid prayer recitations.","Asking knowledgeable people can help preserve Sunnah practice.","Eid prayer includes Qur’an recitation with meaningful reminders."],"related_hadiths":[{"id":"1281","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1283","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E82" s="4" t="n"/>
@@ -2351,7 +2355,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Al-A’la and Al-Ghashiyah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet’s recitation of Al-A’la and Al-Ghashiyah in Eid prayer."},"heading":{"title":"Eid Prayer Recitation of Al-A’la and Al-Ghashiyah","description":"This narration from Ibn Abbas confirms a known Eid prayer recitation: the Prophet صلى الله عليه وسلم used to recite Surah Al-A’la and Surah Al-Ghashiyah in the Eid prayer. The hadith is short, but its meaning is clear. Eid prayer has a special place, and the Qur’an remains at the heart of it. For people searching for the hadith about Eid prayer surahs, this report gives a direct answer. It also matches the wording of another narration in this same set, which strengthens the practical value of the report. The text does not add extra details about the number of takbirs or the sermon, so the explanation should stay focused on the recited chapters."},"teachings":["Eid prayer includes recitation from the Qur’an.","Surah Al-A’la and Surah Al-Ghashiyah are named in the narration.","The Companion Ibn Abbas transmitted this practice from the Prophet صلى الله عليه وسلم.","The hadith helps Muslims learn a reported Sunnah of Eid prayer."],"related_hadiths":[{"id":"1281","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1282","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Al-A’la and Al-Ghashiyah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet’s recitation of Al-A’la and Al-Ghashiyah in Eid prayer."},"heading":{"title":"Eid Prayer Recitation of Al-A’la and Al-Ghashiyah","description":"This narration from Ibn Abbas confirms a known Eid prayer recitation: the Prophet صلى الله عليه وسلم used to recite Surah Al-A’la and Surah Al-Ghashiyah in the Eid prayer. The hadith is short, but its meaning is clear. Eid prayer has a special place, and the Qur’an remains at the heart of it. For people searching for the hadith about Eid prayer surahs, this report gives a direct answer. It also matches the wording of another narration in this same set, which strengthens the practical value of the report. The text does not add extra details about the number of takbirs or the sermon, so the explanation should stay focused on the recited chapters."},"teachings":["Eid prayer includes recitation from the Qur’an.","Surah Al-A’la and Surah Al-Ghashiyah are named in the narration.","The Companion Ibn Abbas transmitted this practice from the Prophet صلى الله عليه وسلم.","The hadith helps Muslims learn a reported Sunnah of Eid prayer."],"related_hadiths":[{"id":"1281","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1282","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E83" s="4" t="n"/>
@@ -2374,7 +2378,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet’s Sermon on a Camel","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the Prophet صلى الله عليه وسلم delivering a sermon while seated on his she-camel."},"heading":{"title":"Prophet’s Sermon on a She-Camel","description":"This hadith gives a simple scene from the Prophet’s public sermon. Abu Kahil reported that he saw the Prophet صلى الله عليه وسلم delivering a sermon while on a she-camel, and an Ethiopian man was holding its reins. The main focus is the way the sermon was delivered in that moment. It shows that the Prophet صلى الله عليه وسلم addressed people in a practical public setting, where people could see and hear him. For searchers looking for a hadith about the Prophet giving a sermon on a camel, this narration is directly relevant. The text does not state the full sermon topic, so we should not add a message that is not mentioned. The safe lesson is about the form and setting of the sermon."},"teachings":["The Prophet صلى الله عليه وسلم delivered sermons in public settings.","He was seen giving a sermon while on a she-camel.","The narration records a real observed moment from a Companion.","Details in hadith should be explained without adding unknown speech."],"related_hadiths":[{"id":"1285","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1286","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet’s Sermon on a Camel","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the Prophet صلى الله عليه وسلم delivering a sermon while seated on his she-camel."},"heading":{"title":"Prophet’s Sermon on a She-Camel","description":"This hadith gives a simple scene from the Prophet’s public sermon. Abu Kahil reported that he saw the Prophet صلى الله عليه وسلم delivering a sermon while on a she-camel, and an Ethiopian man was holding its reins. The main focus is the way the sermon was delivered in that moment. It shows that the Prophet صلى الله عليه وسلم addressed people in a practical public setting, where people could see and hear him. For searchers looking for a hadith about the Prophet giving a sermon on a camel, this narration is directly relevant. The text does not state the full sermon topic, so we should not add a message that is not mentioned. The safe lesson is about the form and setting of the sermon."},"teachings":["The Prophet صلى الله عليه وسلم delivered sermons in public settings.","He was seen giving a sermon while on a she-camel.","The narration records a real observed moment from a Companion.","Details in hadith should be explained without adding unknown speech."],"related_hadiths":[{"id":"1285","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1286","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E84" s="4" t="n"/>
@@ -2397,7 +2401,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sermon Atop a She-Camel","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Kahil reports seeing the Prophet صلى الله عليه وسلم deliver a sermon from a beautiful she-camel."},"heading":{"title":"Sermon Atop a She-Camel in the Prophet’s Practice","description":"This hadith reports that Abu Kahil, also named Qais bin A’idh, saw the Prophet صلى الله عليه وسلم delivering a sermon from a beautiful she-camel while an Ethiopian man held its reins. The narration is brief, but it gives a clear visual detail about a public khutbah. It is useful for people searching for Prophet khutbah on camel or hadith about sermon on she-camel. The text does not mention the words of the sermon, the place, or a legal ruling. Because of that, the explanation should stay close to what is narrated. The hadith mainly records how the Prophet صلى الله عليه وسلم was seen addressing people in a public gathering."},"teachings":["The Prophet صلى الله عليه وسلم was seen delivering a sermon from a she-camel.","The report preserves details about the setting of the sermon.","A Companion’s eyewitness account is part of hadith transmission.","We should avoid adding sermon content that is not in the narration."],"related_hadiths":[{"id":"1284","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1286","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sermon Atop a She-Camel","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Kahil reports seeing the Prophet صلى الله عليه وسلم deliver a sermon from a beautiful she-camel."},"heading":{"title":"Sermon Atop a She-Camel in the Prophet’s Practice","description":"This hadith reports that Abu Kahil, also named Qais bin A’idh, saw the Prophet صلى الله عليه وسلم delivering a sermon from a beautiful she-camel while an Ethiopian man held its reins. The narration is brief, but it gives a clear visual detail about a public khutbah. It is useful for people searching for Prophet khutbah on camel or hadith about sermon on she-camel. The text does not mention the words of the sermon, the place, or a legal ruling. Because of that, the explanation should stay close to what is narrated. The hadith mainly records how the Prophet صلى الله عليه وسلم was seen addressing people in a public gathering."},"teachings":["The Prophet صلى الله عليه وسلم was seen delivering a sermon from a she-camel.","The report preserves details about the setting of the sermon.","A Companion’s eyewitness account is part of hadith transmission.","We should avoid adding sermon content that is not in the narration."],"related_hadiths":[{"id":"1284","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1286","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E85" s="4" t="n"/>
@@ -2420,7 +2424,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sermon During Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions the Prophet صلى الله عليه وسلم delivering a sermon from atop his camel."},"heading":{"title":"Prophet’s Sermon Atop His Camel","description":"This hadith states that the father of Salamah bin Nubait performed Hajj and saw the Prophet صلى الله عليه وسلم delivering a sermon from atop his camel. The wording is short and direct. It tells us what was seen, not the full content of what was said. For readers searching for a hadith about the Prophet’s sermon on a camel, this narration gives a clear report. The mention of Hajj belongs to this specific narration, so it should not be mixed with other Eid reports unless clearly labeled separately. The main teaching here is that the Prophet صلى الله عليه وسلم addressed people in a way that suited the public gathering and allowed them to receive his sermon."},"teachings":["The Prophet صلى الله عليه وسلم delivered a sermon while on his camel.","The narrator connects this sighting with Hajj.","Hadith reports may preserve both actions and settings.","The narration should be explained without adding the unmentioned sermon text."],"related_hadiths":[{"id":"1284","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1285","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sermon During Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions the Prophet صلى الله عليه وسلم delivering a sermon from atop his camel."},"heading":{"title":"Prophet’s Sermon Atop His Camel","description":"This hadith states that the father of Salamah bin Nubait performed Hajj and saw the Prophet صلى الله عليه وسلم delivering a sermon from atop his camel. The wording is short and direct. It tells us what was seen, not the full content of what was said. For readers searching for a hadith about the Prophet’s sermon on a camel, this narration gives a clear report. The mention of Hajj belongs to this specific narration, so it should not be mixed with other Eid reports unless clearly labeled separately. The main teaching here is that the Prophet صلى الله عليه وسلم addressed people in a way that suited the public gathering and allowed them to receive his sermon."},"teachings":["The Prophet صلى الله عليه وسلم delivered a sermon while on his camel.","The narrator connects this sighting with Hajj.","Hadith reports may preserve both actions and settings.","The narration should be explained without adding the unmentioned sermon text."],"related_hadiths":[{"id":"1284","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1285","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E86" s="4" t="n"/>
@@ -2443,7 +2447,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Takbir in Eid Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith reports that the Prophet صلى الله عليه وسلم said Takbir often during the Eid sermon."},"heading":{"title":"Takbir in the Eid Sermon","description":"This hadith focuses on Takbir during the Eid sermon. It reports that the Prophet صلى الله عليه وسلم used to say Takbir between the two sermons and that he said Takbir a great deal in the sermon of the two Eids. For people searching for Eid khutbah Takbir hadith or Takbir in Eid sermon, this narration gives a direct text. The wording connects Takbir with the sermon itself, not only with the prayer. It also shows that Eid has a strong tone of praising Allah through Allahu Akbar. The narration does not give the full wording of the sermon or the exact number of Takbirs, so the explanation should not claim more than the text states."},"teachings":["Takbir was part of the Prophet’s Eid sermon practice.","The narration mentions Takbir between the two sermons.","Eid sermons carried repeated praise of Allah.","The text does not give an exact number, so that should not be invented."],"related_hadiths":[{"id":"1288","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1290","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Takbir in Eid Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith reports that the Prophet صلى الله عليه وسلم said Takbir often during the Eid sermon."},"heading":{"title":"Takbir in the Eid Sermon","description":"This hadith focuses on Takbir during the Eid sermon. It reports that the Prophet صلى الله عليه وسلم used to say Takbir between the two sermons and that he said Takbir a great deal in the sermon of the two Eids. For people searching for Eid khutbah Takbir hadith or Takbir in Eid sermon, this narration gives a direct text. The wording connects Takbir with the sermon itself, not only with the prayer. It also shows that Eid has a strong tone of praising Allah through Allahu Akbar. The narration does not give the full wording of the sermon or the exact number of Takbirs, so the explanation should not claim more than the text states."},"teachings":["Takbir was part of the Prophet’s Eid sermon practice.","The narration mentions Takbir between the two sermons.","Eid sermons carried repeated praise of Allah.","The text does not give an exact number, so that should not be invented."],"related_hadiths":[{"id":"1288","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1290","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E87" s="4" t="n"/>
@@ -2466,7 +2470,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Charity After Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed two Rak’ah on Eid, then urged people to give charity."},"heading":{"title":"Charity After Eid Prayer: Give in Charity","description":"This hadith gives several clear details about the Eid gathering. Abu Sa’eed Al-Khudri narrated that the Prophet صلى الله عليه وسلم would go out on Eid, lead the people in two Rak’ah, say the Salam, then stand facing the people while they sat. He would say, ‘Give in charity. Give in charity.’ The narration also says women gave most in charity, including earrings, rings, and other things. If there was a need to send an expedition, he mentioned it; otherwise, he left. For searchers looking for a hadith about charity after Eid prayer, this narration is very direct. The message should stay close to the text: prayer, sermon-like address, charity, and public needs."},"teachings":["The Prophet صلى الله عليه وسلم led two Rak’ah on Eid.","He encouraged people to give charity after the prayer.","Women are mentioned as giving many items in charity.","Community needs were mentioned when there was a reason."],"related_hadiths":[{"id":"1290","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1287","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Charity After Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed two Rak’ah on Eid, then urged people to give charity."},"heading":{"title":"Charity After Eid Prayer: Give in Charity","description":"This hadith gives several clear details about the Eid gathering. Abu Sa’eed Al-Khudri narrated that the Prophet صلى الله عليه وسلم would go out on Eid, lead the people in two Rak’ah, say the Salam, then stand facing the people while they sat. He would say, ‘Give in charity. Give in charity.’ The narration also says women gave most in charity, including earrings, rings, and other things. If there was a need to send an expedition, he mentioned it; otherwise, he left. For searchers looking for a hadith about charity after Eid prayer, this narration is very direct. The message should stay close to the text: prayer, sermon-like address, charity, and public needs."},"teachings":["The Prophet صلى الله عليه وسلم led two Rak’ah on Eid.","He encouraged people to give charity after the prayer.","Women are mentioned as giving many items in charity.","Community needs were mentioned when there was a reason."],"related_hadiths":[{"id":"1290","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1287","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E88" s="4" t="n"/>
@@ -2489,7 +2493,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing Eid Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir reports that the Prophet صلى الله عليه وسلم delivered the Eid sermon standing, sat briefly, then stood again."},"heading":{"title":"Eid Sermon Standing, Sitting, Then Standing Again","description":"This hadith reports a specific detail about the Prophet’s Eid sermon. Jabir narrated that the Messenger of Allah صلى الله عليه وسلم went out on the day of Fitr or Adha and delivered a sermon while standing. Then he sat briefly, then stood again. This is useful for people searching for Eid khutbah standing hadith or how the Eid sermon was delivered. The narration focuses only on the posture and order of the sermon: standing, sitting briefly, then standing again. It does not mention the exact words of the sermon, the length, or a wider ruling. A careful explanation should keep the reader’s attention on the described practice without adding details from outside this text."},"teachings":["The Prophet صلى الله عليه وسلم delivered an Eid sermon while standing.","The narration mentions a brief sitting between standing parts.","Both Fitr and Adha are mentioned in the report.","The hadith records the form of the sermon, not its full wording."],"related_hadiths":[{"id":"1288","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1290","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1287","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing Eid Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir reports that the Prophet صلى الله عليه وسلم delivered the Eid sermon standing, sat briefly, then stood again."},"heading":{"title":"Eid Sermon Standing, Sitting, Then Standing Again","description":"This hadith reports a specific detail about the Prophet’s Eid sermon. Jabir narrated that the Messenger of Allah صلى الله عليه وسلم went out on the day of Fitr or Adha and delivered a sermon while standing. Then he sat briefly, then stood again. This is useful for people searching for Eid khutbah standing hadith or how the Eid sermon was delivered. The narration focuses only on the posture and order of the sermon: standing, sitting briefly, then standing again. It does not mention the exact words of the sermon, the length, or a wider ruling. A careful explanation should keep the reader’s attention on the described practice without adding details from outside this text."},"teachings":["The Prophet صلى الله عليه وسلم delivered an Eid sermon while standing.","The narration mentions a brief sitting between standing parts.","Both Fitr and Adha are mentioned in the report.","The hadith records the form of the sermon, not its full wording."],"related_hadiths":[{"id":"1288","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1290","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1287","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E89" s="4" t="n"/>
@@ -2512,7 +2516,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sitting for Eid Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم allowed people to sit for the Eid sermon or leave after the prayer."},"heading":{"title":"Eid Sermon After Prayer: Sit or Leave","description":"This hadith describes what happened after the Eid prayer. Abdullah bin Sa’ib said he attended Eid prayer with the Messenger of Allah صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم led the prayer, then said that the prayer had been completed. Whoever wanted to sit and listen to the sermon could sit, and whoever wanted to leave could leave. For people searching for whether the Eid khutbah is after the prayer or about staying for the Eid sermon, this narration is directly relevant. The wording shows permission in that specific setting. The explanation should not go beyond the text by making broad claims that are not stated. The key point is the Prophet’s clear statement after completing the Eid prayer."},"teachings":["The Eid prayer was completed before the sermon mentioned here.","The Prophet صلى الله عليه وسلم allowed people to sit and listen to the sermon.","He also allowed those who wanted to leave to leave.","The narration shows clear communication after worship."],"related_hadiths":[{"id":"1288","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1291","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sitting for Eid Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم allowed people to sit for the Eid sermon or leave after the prayer."},"heading":{"title":"Eid Sermon After Prayer: Sit or Leave","description":"This hadith describes what happened after the Eid prayer. Abdullah bin Sa’ib said he attended Eid prayer with the Messenger of Allah صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم led the prayer, then said that the prayer had been completed. Whoever wanted to sit and listen to the sermon could sit, and whoever wanted to leave could leave. For people searching for whether the Eid khutbah is after the prayer or about staying for the Eid sermon, this narration is directly relevant. The wording shows permission in that specific setting. The explanation should not go beyond the text by making broad claims that are not stated. The key point is the Prophet’s clear statement after completing the Eid prayer."},"teachings":["The Eid prayer was completed before the sermon mentioned here.","The Prophet صلى الله عليه وسلم allowed people to sit and listen to the sermon.","He also allowed those who wanted to leave to leave.","The narration shows clear communication after worship."],"related_hadiths":[{"id":"1288","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1289","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1291","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E90" s="4" t="n"/>
@@ -2535,7 +2539,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Prayer Before or After Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم did not pray before or after the Eid prayer."},"heading":{"title":"No Prayer Before or After Eid Prayer","description":"This hadith reports a clear practice about the Eid prayer. Ibn Abbas narrated that the Messenger of Allah صلى الله عليه وسلم went out and led the people in the Eid prayer, and he did not pray before it or after it. For people searching for Sunnah before Eid prayer or nafl after Eid salah, this narration gives a direct report from the Prophet’s action. The text is focused on what he did in that setting. It does not discuss prayer at home, other times, or every possible situation, so the explanation should remain careful. The main point is that in this narration, the Prophet صلى الله عليه وسلم performed the Eid prayer without praying before it or after it."},"teachings":["The Prophet صلى الله عليه وسلم led the Eid prayer publicly.","He did not pray before the Eid prayer in this narration.","He did not pray after the Eid prayer in this narration.","The hadith helps describe the observed form of Eid prayer."],"related_hadiths":[{"id":"1292","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1293","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1290","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Prayer Before or After Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم did not pray before or after the Eid prayer."},"heading":{"title":"No Prayer Before or After Eid Prayer","description":"This hadith reports a clear practice about the Eid prayer. Ibn Abbas narrated that the Messenger of Allah صلى الله عليه وسلم went out and led the people in the Eid prayer, and he did not pray before it or after it. For people searching for Sunnah before Eid prayer or nafl after Eid salah, this narration gives a direct report from the Prophet’s action. The text is focused on what he did in that setting. It does not discuss prayer at home, other times, or every possible situation, so the explanation should remain careful. The main point is that in this narration, the Prophet صلى الله عليه وسلم performed the Eid prayer without praying before it or after it."},"teachings":["The Prophet صلى الله عليه وسلم led the Eid prayer publicly.","He did not pray before the Eid prayer in this narration.","He did not pray after the Eid prayer in this narration.","The hadith helps describe the observed form of Eid prayer."],"related_hadiths":[{"id":"1292","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1293","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1290","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E91" s="4" t="n"/>
@@ -2558,7 +2562,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak’ah After Returning Home","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم did not pray before Eid, but prayed two Rak’ah after returning home."},"heading":{"title":"Two Rak’ah at Home After Eid Prayer","description":"This hadith gives a more specific detail about prayer around Eid. Abu Sa’eed Al-Khudri narrated that the Messenger of Allah صلى الله عليه وسلم did not pray anything before the Eid prayer. But when he returned to his house, he would pray two Rak’ah. For people searching for two Rak’ah after Eid prayer at home, this narration is directly connected. It should not be confused with reports that only mention no prayer before or after Eid in the prayer place. This text includes the added detail of returning home and praying two Rak’ah there. A careful explanation should keep those parts together: no prayer before Eid, then two Rak’ah after returning home."},"teachings":["The Prophet صلى الله عليه وسلم did not pray before the Eid prayer in this narration.","He prayed two Rak’ah after returning to his house.","The place mentioned is his house after returning.","Similar topics should be explained without mixing details carelessly."],"related_hadiths":[{"id":"1291","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1292","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1288","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak’ah After Returning Home","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم did not pray before Eid, but prayed two Rak’ah after returning home."},"heading":{"title":"Two Rak’ah at Home After Eid Prayer","description":"This hadith gives a more specific detail about prayer around Eid. Abu Sa’eed Al-Khudri narrated that the Messenger of Allah صلى الله عليه وسلم did not pray anything before the Eid prayer. But when he returned to his house, he would pray two Rak’ah. For people searching for two Rak’ah after Eid prayer at home, this narration is directly connected. It should not be confused with reports that only mention no prayer before or after Eid in the prayer place. This text includes the added detail of returning home and praying two Rak’ah there. A careful explanation should keep those parts together: no prayer before Eid, then two Rak’ah after returning home."},"teachings":["The Prophet صلى الله عليه وسلم did not pray before the Eid prayer in this narration.","He prayed two Rak’ah after returning to his house.","The place mentioned is his house after returning.","Similar topics should be explained without mixing details carelessly."],"related_hadiths":[{"id":"1291","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1292","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1288","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E92" s="4" t="n"/>
@@ -2581,7 +2585,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sunnah to Walk to Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali said that walking to the Eid prayer is part of the Sunnah."},"heading":{"title":"Sunnah to Walk to Eid Prayer","description":"This hadith contains a short statement from Ali: ‘It is part of the Sunnah to walk to Eid prayers.’ The core topic is walking to Eid prayer. Unlike some narrations that describe what the Prophet صلى الله عليه وسلم did, this report phrases the matter as part of the Sunnah. For readers searching for is it Sunnah to walk to Eid prayer, this narration gives a direct answer from the text. The hadith does not mention walking back, changing routes, or the sermon. Those are found in other reports, but this specific narration only states the walking to Eid. A careful explanation keeps that focus and does not add extra conditions not mentioned here."},"teachings":["Ali described walking to Eid prayer as part of the Sunnah.","The hadith focuses on going to Eid on foot.","The narration is short but clear in its main message.","Extra details should not be added unless another narration is clearly cited."],"related_hadiths":[{"id":"1294","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1295","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1297","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sunnah to Walk to Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali said that walking to the Eid prayer is part of the Sunnah."},"heading":{"title":"Sunnah to Walk to Eid Prayer","description":"This hadith contains a short statement from Ali: ‘It is part of the Sunnah to walk to Eid prayers.’ The core topic is walking to Eid prayer. Unlike some narrations that describe what the Prophet صلى الله عليه وسلم did, this report phrases the matter as part of the Sunnah. For readers searching for is it Sunnah to walk to Eid prayer, this narration gives a direct answer from the text. The hadith does not mention walking back, changing routes, or the sermon. Those are found in other reports, but this specific narration only states the walking to Eid. A careful explanation keeps that focus and does not add extra conditions not mentioned here."},"teachings":["Ali described walking to Eid prayer as part of the Sunnah.","The hadith focuses on going to Eid on foot.","The narration is short but clear in its main message.","Extra details should not be added unless another narration is clearly cited."],"related_hadiths":[{"id":"1294","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1295","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1297","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E93" s="4" t="n"/>
@@ -2604,7 +2608,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Different Route on Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the Prophet صلى الله عليه وسلم taking one route to Eid and returning by another."},"heading":{"title":"Different Route on Eid Prayer Day","description":"This hadith gives detailed route information for the Prophet’s movement on the two Eids. It says that when he went out, he passed by certain houses and people, then returned by another route through Banu Zuraiq and toward Balat. For readers searching for the hadith about taking a different route on Eid, this narration is directly related. The core point is that the Prophet صلى الله عليه وسلم went one way and returned another way. The named places are part of the report, and they should be kept as route details without turning them into extra claims. The narration focuses on the path taken on Eid, not on the prayer recitation or sermon."},"teachings":["The Prophet صلى الله عليه وسلم is reported to have used a route when going out for Eid.","The narration describes a different route for return.","Specific places are preserved in the report.","The hadith focuses on movement to and from Eid, not sermon content."],"related_hadiths":[{"id":"1299","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1300","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1294","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Different Route on Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the Prophet صلى الله عليه وسلم taking one route to Eid and returning by another."},"heading":{"title":"Different Route on Eid Prayer Day","description":"This hadith gives detailed route information for the Prophet’s movement on the two Eids. It says that when he went out, he passed by certain houses and people, then returned by another route through Banu Zuraiq and toward Balat. For readers searching for the hadith about taking a different route on Eid, this narration is directly related. The core point is that the Prophet صلى الله عليه وسلم went one way and returned another way. The named places are part of the report, and they should be kept as route details without turning them into extra claims. The narration focuses on the path taken on Eid, not on the prayer recitation or sermon."},"teachings":["The Prophet صلى الله عليه وسلم is reported to have used a route when going out for Eid.","The narration describes a different route for return.","Specific places are preserved in the report.","The hadith focuses on movement to and from Eid, not sermon content."],"related_hadiths":[{"id":"1299","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1300","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1294","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E94" s="4" t="n"/>
@@ -2627,7 +2631,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Return by Another Route","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar went to Eid by one route and returned by another, saying the Prophet صلى الله عليه وسلم did so."},"heading":{"title":"Go to Eid by One Route and Return by Another","description":"This hadith reports that Ibn Umar used to go out to the Eid prayer by one route and return by another. He said that the Messenger of Allah صلى الله عليه وسلم used to do that. This is a clear report for people searching for taking a different route on Eid or Eid prayer route hadith. The narration shows both the Companion’s practice and his reason for doing it: he linked it to the Prophet صلى الله عليه وسلم. The text does not explain the reason behind changing routes, so a careful explanation should not invent one. The key teaching is the reported practice itself: going by one way and returning by another on Eid."},"teachings":["Ibn Umar went to Eid by one route and returned by another.","He connected this practice to the Messenger of Allah صلى الله عليه وسلم.","The hadith reports the action without giving its reason.","The narration helps describe a Sunnah-related Eid practice."],"related_hadiths":[{"id":"1298","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1300","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1295","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Return by Another Route","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar went to Eid by one route and returned by another, saying the Prophet صلى الله عليه وسلم did so."},"heading":{"title":"Go to Eid by One Route and Return by Another","description":"This hadith reports that Ibn Umar used to go out to the Eid prayer by one route and return by another. He said that the Messenger of Allah صلى الله عليه وسلم used to do that. This is a clear report for people searching for taking a different route on Eid or Eid prayer route hadith. The narration shows both the Companion’s practice and his reason for doing it: he linked it to the Prophet صلى الله عليه وسلم. The text does not explain the reason behind changing routes, so a careful explanation should not invent one. The key teaching is the reported practice itself: going by one way and returning by another on Eid."},"teachings":["Ibn Umar went to Eid by one route and returned by another.","He connected this practice to the Messenger of Allah صلى الله عليه وسلم.","The hadith reports the action without giving its reason.","The narration helps describe a Sunnah-related Eid practice."],"related_hadiths":[{"id":"1298","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1300","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1295","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E95" s="4" t="n"/>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Route Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم returned from Eid by a different route, showing a simple Sunnah of Eid prayer."},"heading":{"title":"Eid Route Sunnah: Returning by Another Way","description":"This hadith about Eid route shows a simple action of the Prophet صلى الله عليه وسلم. When he went out for the Eid prayer, he did not return by the same road. He returned by a different route from the one he had taken first. The text does not give a reason, so the safest explanation is to say exactly what the narration states: this was his practice when going out to Eid. For readers searching for the Sunnah of Eid prayer, this hadith highlights that Eid was not only about the prayer itself, but also about the manner in which the Prophet صلى الله عليه وسلم went to and returned from it. It teaches careful following of Prophetic practice without adding reasons that are not mentioned here."},"teachings":["The Prophet صلى الله عليه وسلم used a different route when returning from Eid prayer.","Small actions linked to worship can carry religious meaning when reported from the Sunnah.","A Muslim should avoid inventing reasons when the hadith itself does not mention them."],"related_hadiths":[{"id":"986","book_id":"1","label":"Sahih Bukhari"},{"id":"541","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Route Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم returned from Eid by a different route, showing a simple Sunnah of Eid prayer."},"heading":{"title":"Eid Route Sunnah: Returning by Another Way","description":"This hadith about Eid route shows a simple action of the Prophet صلى الله عليه وسلم. When he went out for the Eid prayer, he did not return by the same road. He returned by a different route from the one he had taken first. The text does not give a reason, so the safest explanation is to say exactly what the narration states: this was his practice when going out to Eid. For readers searching for the Sunnah of Eid prayer, this hadith highlights that Eid was not only about the prayer itself, but also about the manner in which the Prophet صلى الله عليه وسلم went to and returned from it. It teaches careful following of Prophetic practice without adding reasons that are not mentioned here."},"teachings":["The Prophet صلى الله عليه وسلم used a different route when returning from Eid prayer.","Small actions linked to worship can carry religious meaning when reported from the Sunnah.","A Muslim should avoid inventing reasons when the hadith itself does not mention them."],"related_hadiths":[{"id":"986","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"541","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Celebration and Taqlis","description":"$book_name$ $hadith_number$ - $chapter_name$. Iyad Al-Ash’ari noticed the absence of Taqlis at Eid, recalling festive celebration near the Prophet صلى الله عليه وسلم."},"heading":{"title":"Eid Celebration Hadith: Taqlis on a Festive Day","description":"This Eid celebration hadith mentions Taqlis, which the provided note explains as celebration on a festive occasion. ‘Amir reports that Iyad Al-Ash’ari was present in Anbar at the time of Eid. He asked why the people were not engaged in Taqlis as it had been done in the presence of the Messenger of Allah صلى الله عليه وسلم. The wording is brief, so we should not add details about the form of that celebration beyond the given meaning of Taqlis. The main point is that Eid was treated as a day of visible joy and public festivity. For those searching for hadith about Eid celebration, this report shows that celebration connected to Eid had a place among Muslims, as remembered by a Companion or early narrator."},"teachings":["Eid is linked with lawful festive expression in the narration.","Iyad Al-Ash’ari compared the people’s Eid practice with what was done near the Prophet صلى الله عليه وسلم.","The hadith should be explained without adding details about Taqlis that are not in the text."],"related_hadiths":[{"id":"949","book_id":"1","label":"Sahih Bukhari"},{"id":"892a","book_id":"2","label":"Sahih Muslim"},{"id":"1134","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Celebration and Taqlis","description":"$book_name$ $hadith_number$ - $chapter_name$. Iyad Al-Ash’ari noticed the absence of Taqlis at Eid, recalling festive celebration near the Prophet صلى الله عليه وسلم."},"heading":{"title":"Eid Celebration Hadith: Taqlis on a Festive Day","description":"This Eid celebration hadith mentions Taqlis, which the provided note explains as celebration on a festive occasion. ‘Amir reports that Iyad Al-Ash’ari was present in Anbar at the time of Eid. He asked why the people were not engaged in Taqlis as it had been done in the presence of the Messenger of Allah صلى الله عليه وسلم. The wording is brief, so we should not add details about the form of that celebration beyond the given meaning of Taqlis. The main point is that Eid was treated as a day of visible joy and public festivity. For those searching for hadith about Eid celebration, this report shows that celebration connected to Eid had a place among Muslims, as remembered by a Companion or early narrator."},"teachings":["Eid is linked with lawful festive expression in the narration.","Iyad Al-Ash’ari compared the people’s Eid practice with what was done near the Prophet صلى الله عليه وسلم.","The hadith should be explained without adding details about Taqlis that are not in the text."],"related_hadiths":[{"id":"949","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"892a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1134","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E97" s="4" t="n"/>
@@ -2700,7 +2704,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying Behind a Sutrah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed facing a small spear on Eid and other occasions, while people prayed behind him."},"heading":{"title":"Praying Behind a Sutrah: Eid and Other Occasions","description":"This hadith about praying behind a Sutrah adds another detail to the Eid prayer setting. Ibn ‘Umar says that when the Prophet صلى الله عليه وسلم prayed on Eid or on another occasion, a small spear was set up in front of him. He prayed facing it, and the people prayed behind him. Nafi‘ then said that leaders took this practice from there. The focus of the hadith is not only Eid, but the broader act of placing a small spear before the imam as a Sutrah. For users searching for Sutrah in prayer hadith, this narration shows a practical example: the imam faced the barrier, and the people prayed in rows behind him. The wording keeps the lesson simple and direct."},"teachings":["A small spear was placed in front of the Prophet صلى الله عليه وسلم when he prayed.","The people prayed behind him while he faced the Sutrah.","Nafi‘ connected this practice with what later leaders adopted."],"related_hadiths":[{"id":"973","book_id":"1","label":"Sahih Bukhari"},{"id":"494","book_id":"1","label":"Sahih Bukhari"},{"id":"501a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying Behind a Sutrah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed facing a small spear on Eid and other occasions, while people prayed behind him."},"heading":{"title":"Praying Behind a Sutrah: Eid and Other Occasions","description":"This hadith about praying behind a Sutrah adds another detail to the Eid prayer setting. Ibn ‘Umar says that when the Prophet صلى الله عليه وسلم prayed on Eid or on another occasion, a small spear was set up in front of him. He prayed facing it, and the people prayed behind him. Nafi‘ then said that leaders took this practice from there. The focus of the hadith is not only Eid, but the broader act of placing a small spear before the imam as a Sutrah. For users searching for Sutrah in prayer hadith, this narration shows a practical example: the imam faced the barrier, and the people prayed in rows behind him. The wording keeps the lesson simple and direct."},"teachings":["A small spear was placed in front of the Prophet صلى الله عليه وسلم when he prayed.","The people prayed behind him while he faced the Sutrah.","Nafi‘ connected this practice with what later leaders adopted."],"related_hadiths":[{"id":"973","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"494","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"501a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E98" s="4" t="n"/>
@@ -2723,7 +2727,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid and Friday on One Day","description":"$book_name$ $hadith_number$ - $chapter_name$. When Eid and Friday came on one day, the Prophet صلى الله عليه وسلم prayed Eid and gave a concession for Friday."},"heading":{"title":"Eid and Friday on One Day: A Concession Hadith","description":"This hadith about Eid and Friday on one day reports a question asked to Zaid bin Arqam. He was asked whether he had been present with the Messenger of Allah صلى الله عليه وسلم when two Eid occurred on one day. He answered yes. When asked what the Prophet صلى الله عليه وسلم did, he said that the Prophet صلى الله عليه وسلم prayed the Eid prayer, then granted a concession regarding Friday prayer, saying: “Whoever wants to pray, let him pray.” The hadith is about a specific case where Eid and Jumu‘ah met on the same day. The safe explanation is to keep the focus on the stated concession and not stretch the ruling beyond the wording. It shows ease in a special situation."},"teachings":["The Prophet صلى الله عليه وسلم prayed Eid when Eid and Friday came on one day.","He granted a concession regarding Friday prayer in that situation.","Those who wished to pray Friday were still allowed to do so."],"related_hadiths":[{"id":"1070","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1592","book_id":"3","label":"Sunan an-Nasai"},{"id":"5571","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid and Friday on One Day","description":"$book_name$ $hadith_number$ - $chapter_name$. When Eid and Friday came on one day, the Prophet صلى الله عليه وسلم prayed Eid and gave a concession for Friday."},"heading":{"title":"Eid and Friday on One Day: A Concession Hadith","description":"This hadith about Eid and Friday on one day reports a question asked to Zaid bin Arqam. He was asked whether he had been present with the Messenger of Allah صلى الله عليه وسلم when two Eid occurred on one day. He answered yes. When asked what the Prophet صلى الله عليه وسلم did, he said that the Prophet صلى الله عليه وسلم prayed the Eid prayer, then granted a concession regarding Friday prayer, saying: “Whoever wants to pray, let him pray.” The hadith is about a specific case where Eid and Jumu‘ah met on the same day. The safe explanation is to keep the focus on the stated concession and not stretch the ruling beyond the wording. It shows ease in a special situation."},"teachings":["The Prophet صلى الله عليه وسلم prayed Eid when Eid and Friday came on one day.","He granted a concession regarding Friday prayer in that situation.","Those who wished to pray Friday were still allowed to do so."],"related_hadiths":[{"id":"1070","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1592","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"5571","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E99" s="4" t="n"/>
@@ -2746,7 +2750,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Sufficing for Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said Eid could suffice for Friday for whoever wished, while he would pray Friday."},"heading":{"title":"Eid Sufficing for Friday: The Prophet’s Stated Ease","description":"This hadith about Eid sufficing for Friday is narrated from Ibn ‘Abbas, with another chain giving similar wording. The Messenger of Allah صلى الله عليه وسلم said that two Eid had come together on that day. He then said that whoever wanted, the Eid prayer would suffice him, and he would not have to pray Friday. At the same time, the Prophet صلى الله عليه وسلم said, “But we will pray Friday if Allah wills.” The wording shows both permission and the Prophet’s own stated action. For searchers looking for Eid and Jumu‘ah same day hadith, this report is direct. The explanation should stay with the text: a concession was given, while Friday prayer was still held by the Prophet صلى الله عليه وسلم."},"teachings":["Two Eid coming together refers here to Eid and Friday on the same day.","The Prophet صلى الله عليه وسلم allowed Eid prayer to suffice for whoever wished.","The Prophet صلى الله عليه وسلم also stated that he would pray Friday if Allah willed."],"related_hadiths":[{"id":"1070","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1592","book_id":"3","label":"Sunan an-Nasai"},{"id":"5571","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Sufficing for Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said Eid could suffice for Friday for whoever wished, while he would pray Friday."},"heading":{"title":"Eid Sufficing for Friday: The Prophet’s Stated Ease","description":"This hadith about Eid sufficing for Friday is narrated from Ibn ‘Abbas, with another chain giving similar wording. The Messenger of Allah صلى الله عليه وسلم said that two Eid had come together on that day. He then said that whoever wanted, the Eid prayer would suffice him, and he would not have to pray Friday. At the same time, the Prophet صلى الله عليه وسلم said, “But we will pray Friday if Allah wills.” The wording shows both permission and the Prophet’s own stated action. For searchers looking for Eid and Jumu‘ah same day hadith, this report is direct. The explanation should stay with the text: a concession was given, while Friday prayer was still held by the Prophet صلى الله عليه وسلم."},"teachings":["Two Eid coming together refers here to Eid and Friday on the same day.","The Prophet صلى الله عليه وسلم allowed Eid prayer to suffice for whoever wished.","The Prophet صلى الله عليه وسلم also stated that he would pray Friday if Allah willed."],"related_hadiths":[{"id":"1070","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1592","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"5571","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E100" s="4" t="n"/>
@@ -2769,7 +2773,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Weapons on Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم forbade wearing weapons on the two Eid in Muslim lands except when the enemy was present."},"heading":{"title":"Weapons on Eid: Safety in Muslim Lands","description":"This hadith about weapons on Eid is narrated from Ibn ‘Abbas. It states that the Prophet صلى الله عليه وسلم forbade wearing weapons in Muslim lands on the two Eid, except if the enemy was present. The wording gives both the rule and the exception. The core topic is Eid safety, because Eid is a public religious gathering and the narration limits the open carrying of weapons in Muslim lands. At the same time, it does not ignore real danger, since it makes an exception when the enemy is present. For search terms like weapons on Eid hadith and Eid safety in Islam, this report should be explained with balance: avoid weapons on Eid in Muslim lands, except in the stated case."},"teachings":["The Prophet صلى الله عليه وسلم forbade wearing weapons on the two Eid in Muslim lands.","The hadith gives an exception when the enemy is present.","The narration connects Eid gatherings with public safety and restraint."],"related_hadiths":[{"id":"1134","book_id":"4","label":"Sunan Abu Dawud"},{"id":"988","book_id":"1","label":"Sahih Bukhari"},{"id":"2064a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Weapons on Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم forbade wearing weapons on the two Eid in Muslim lands except when the enemy was present."},"heading":{"title":"Weapons on Eid: Safety in Muslim Lands","description":"This hadith about weapons on Eid is narrated from Ibn ‘Abbas. It states that the Prophet صلى الله عليه وسلم forbade wearing weapons in Muslim lands on the two Eid, except if the enemy was present. The wording gives both the rule and the exception. The core topic is Eid safety, because Eid is a public religious gathering and the narration limits the open carrying of weapons in Muslim lands. At the same time, it does not ignore real danger, since it makes an exception when the enemy is present. For search terms like weapons on Eid hadith and Eid safety in Islam, this report should be explained with balance: avoid weapons on Eid in Muslim lands, except in the stated case."},"teachings":["The Prophet صلى الله عليه وسلم forbade wearing weapons on the two Eid in Muslim lands.","The hadith gives an exception when the enemy is present.","The narration connects Eid gatherings with public safety and restraint."],"related_hadiths":[{"id":"1134","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"988","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2064a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E101" s="4" t="n"/>
@@ -2792,7 +2796,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bath on Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used to take a bath on the day of Fitr and the day of Adha."},"heading":{"title":"Bath on Eid: Ghusl for Fitr and Adha","description":"This hadith about bath on Eid is narrated from Ibn ‘Abbas. He says that the Messenger of Allah صلى الله عليه وسلم used to have a bath on the day of Fitr and the day of Adha. The narration is direct and does not add more details about timing, clothing, or other acts. The core message is the Prophet’s practice of bathing on the two Eid days. For readers searching for Eid ghusl hadith or bath before Eid prayer, this report gives a simple basis for understanding cleanliness connected to Eid. The safest explanation is that the Prophet صلى الله عليه وسلم took a bath on both days, and Muslims who study his practice can note this as part of Eid preparation."},"teachings":["The Prophet صلى الله عليه وسلم used to bathe on the day of Fitr.","He also used to bathe on the day of Adha.","The narration links Eid with cleanliness and preparation."],"related_hadiths":[{"id":"542","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1134","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bath on Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used to take a bath on the day of Fitr and the day of Adha."},"heading":{"title":"Bath on Eid: Ghusl for Fitr and Adha","description":"This hadith about bath on Eid is narrated from Ibn ‘Abbas. He says that the Messenger of Allah صلى الله عليه وسلم used to have a bath on the day of Fitr and the day of Adha. The narration is direct and does not add more details about timing, clothing, or other acts. The core message is the Prophet’s practice of bathing on the two Eid days. For readers searching for Eid ghusl hadith or bath before Eid prayer, this report gives a simple basis for understanding cleanliness connected to Eid. The safest explanation is that the Prophet صلى الله عليه وسلم took a bath on both days, and Muslims who study his practice can note this as part of Eid preparation."},"teachings":["The Prophet صلى الله عليه وسلم used to bathe on the day of Fitr.","He also used to bathe on the day of Adha.","The narration links Eid with cleanliness and preparation."],"related_hadiths":[{"id":"542","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1134","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -2819,7 +2823,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Timing","description":"$book_name$ $hadith_number$ - $chapter_name$. Abdullah bin Busr objected to the imam’s delay on Eid, saying they used to have finished by that time."},"heading":{"title":"Eid Prayer Timing: Avoiding Delay","description":"This hadith about Eid prayer timing is narrated by Yazid bin Khumair. He says that ‘Abdullah bin Busr went out with the people on the Day of Fitr or Adha and objected to the imam’s delay. He said, “We would have finished by this time,” and the narration adds that it was the time of Tasbih. The hadith does not give a clock time, so it should not be turned into a fixed modern schedule. Its clear message is that ‘Abdullah bin Busr saw the imam’s delay as unlike what they had known. For searchers looking for Eid prayer time hadith, this report points to the care early Muslims gave to not delaying Eid prayer."},"teachings":["‘Abdullah bin Busr objected when the imam delayed on Eid.","He remembered that they would have already finished by that time.","The narration shows concern for timely Eid prayer without giving a modern clock time."],"related_hadiths":[{"id":"1131","book_id":"4","label":"Sunan Abu Dawud"},{"id":"956","book_id":"1","label":"Sahih Bukhari"},{"id":"884a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Timing","description":"$book_name$ $hadith_number$ - $chapter_name$. Abdullah bin Busr objected to the imam’s delay on Eid, saying they used to have finished by that time."},"heading":{"title":"Eid Prayer Timing: Avoiding Delay","description":"This hadith about Eid prayer timing is narrated by Yazid bin Khumair. He says that ‘Abdullah bin Busr went out with the people on the Day of Fitr or Adha and objected to the imam’s delay. He said, “We would have finished by this time,” and the narration adds that it was the time of Tasbih. The hadith does not give a clock time, so it should not be turned into a fixed modern schedule. Its clear message is that ‘Abdullah bin Busr saw the imam’s delay as unlike what they had known. For searchers looking for Eid prayer time hadith, this report points to the care early Muslims gave to not delaying Eid prayer."},"teachings":["‘Abdullah bin Busr objected when the imam delayed on Eid.","He remembered that they would have already finished by that time.","The narration shows concern for timely Eid prayer without giving a modern clock time."],"related_hadiths":[{"id":"1131","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"956","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"884a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E103" s="4" t="n"/>
@@ -2842,7 +2846,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Night Prayer Two by Two","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used to offer night prayers two Rak’ah by two Rak’ah."},"heading":{"title":"Night Prayer Two by Two: A Clear Prophetic Practice","description":"This hadith about night prayer two by two is narrated from Ibn ‘Umar. He says that the Messenger of Allah صلى الله عليه وسلم used to offer the night prayers two by two. The text is simple and focuses on the form of the night prayer. It does not mention the total number of Rak‘ah, the length of recitation, or the exact time within the night. So the explanation should stay with the stated form: two Rak‘ah at a time. For readers searching for tahajjud two by two hadith or night prayer Rak‘ah hadith, this narration gives a clear phrase from the practice of the Prophet صلى الله عليه وسلم. It helps explain how voluntary night prayer was arranged in pairs."},"teachings":["The Prophet صلى الله عليه وسلم used to pray night prayer two Rak‘ah at a time.","The hadith focuses on the form of the prayer, not the total number.","A clear wording from Ibn ‘Umar helps explain the structure of night prayer."],"related_hadiths":[{"id":"991","book_id":"1","label":"Sahih Bukhari"},{"id":"749","book_id":"2","label":"Sahih Muslim"},{"id":"1322","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Night Prayer Two by Two","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used to offer night prayers two Rak’ah by two Rak’ah."},"heading":{"title":"Night Prayer Two by Two: A Clear Prophetic Practice","description":"This hadith about night prayer two by two is narrated from Ibn ‘Umar. He says that the Messenger of Allah صلى الله عليه وسلم used to offer the night prayers two by two. The text is simple and focuses on the form of the night prayer. It does not mention the total number of Rak‘ah, the length of recitation, or the exact time within the night. So the explanation should stay with the stated form: two Rak‘ah at a time. For readers searching for tahajjud two by two hadith or night prayer Rak‘ah hadith, this narration gives a clear phrase from the practice of the Prophet صلى الله عليه وسلم. It helps explain how voluntary night prayer was arranged in pairs."},"teachings":["The Prophet صلى الله عليه وسلم used to pray night prayer two Rak‘ah at a time.","The hadith focuses on the form of the prayer, not the total number.","A clear wording from Ibn ‘Umar helps explain the structure of night prayer."],"related_hadiths":[{"id":"991","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"749","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1322","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E104" s="4" t="n"/>
@@ -2865,7 +2869,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Night Prayer Format","description":"$book_name$ $hadith_number$ - $chapter_name$. The Messenger of Allah صلى الله عليه وسلم said that the night prayer is to be offered two by two."},"heading":{"title":"Night Prayer Format: Two Rak’ah by Two","description":"This hadith about night prayer format is narrated from Ibn ‘Umar. The Messenger of Allah صلى الله عليه وسلم said, “The night prayer is two by two.” Unlike a report that only describes what the Prophet صلى الله عليه وسلم did, this narration gives the wording as a statement from him. The meaning remains direct: night prayer is offered in pairs of two Rak‘ah. The hadith does not discuss how long each prayer should be or how many pairs a person should pray. For people searching for Salat al-Layl two by two hadith, this narration is a short and clear proof text. The best explanation is to keep it simple: the structure mentioned here is two Rak‘ah followed by two Rak‘ah."},"teachings":["The Prophet صلى الله عليه وسلم stated that night prayer is offered two by two.","The hadith gives the prayer format without mentioning a total number.","The wording helps a person understand night prayer in paired Rak‘ah."],"related_hadiths":[{"id":"991","book_id":"1","label":"Sahih Bukhari"},{"id":"749","book_id":"2","label":"Sahih Muslim"},{"id":"1322","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Night Prayer Format","description":"$book_name$ $hadith_number$ - $chapter_name$. The Messenger of Allah صلى الله عليه وسلم said that the night prayer is to be offered two by two."},"heading":{"title":"Night Prayer Format: Two Rak’ah by Two","description":"This hadith about night prayer format is narrated from Ibn ‘Umar. The Messenger of Allah صلى الله عليه وسلم said, “The night prayer is two by two.” Unlike a report that only describes what the Prophet صلى الله عليه وسلم did, this narration gives the wording as a statement from him. The meaning remains direct: night prayer is offered in pairs of two Rak‘ah. The hadith does not discuss how long each prayer should be or how many pairs a person should pray. For people searching for Salat al-Layl two by two hadith, this narration is a short and clear proof text. The best explanation is to keep it simple: the structure mentioned here is two Rak‘ah followed by two Rak‘ah."},"teachings":["The Prophet صلى الله عليه وسلم stated that night prayer is offered two by two.","The hadith gives the prayer format without mentioning a total number.","The wording helps a person understand night prayer in paired Rak‘ah."],"related_hadiths":[{"id":"991","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"749","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1322","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E105" s="4" t="n"/>
@@ -2888,7 +2892,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Beautiful Quran Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet praised a Companion’s sweet Qur’an voice, showing the beauty of sincere recitation."},"heading":{"title":"Beautiful Quran Recitation with a Sweet Voice","description":"This Hadith highlights the beauty of Qur’an recitation when it is read with a pleasing voice. The Messenger of Allah (صلى الله عليه وسلم) entered the mosque and heard someone reciting the Qur’an. He asked who it was, and he was told that it was Abdullah bin Qais. The Prophet (صلى الله عليه وسلم) then praised him by saying that he had been given a sweet voice from the Mazamir of the family of Dawud. The main message is simple: a beautiful Qur’an recitation can move the heart and deserves appreciation. The Hadith does not speak about showing off or performance. It focuses on the natural beauty of the voice used in reciting Allah’s words."},"teachings":["The Qur’an should be recited with care and beauty.","A pleasant voice in Qur’an recitation is a gift from Allah.","The Prophet (صلى الله عليه وسلم) noticed and praised good recitation.","Reciting Qur’an in the mosque can benefit those who hear it."],"related_hadiths":[{"id":"1342","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1353","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1354","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Beautiful Quran Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet praised a Companion’s sweet Qur’an voice, showing the beauty of sincere recitation."},"heading":{"title":"Beautiful Quran Recitation with a Sweet Voice","description":"This Hadith highlights the beauty of Qur’an recitation when it is read with a pleasing voice. The Messenger of Allah (صلى الله عليه وسلم) entered the mosque and heard someone reciting the Qur’an. He asked who it was, and he was told that it was Abdullah bin Qais. The Prophet (صلى الله عليه وسلم) then praised him by saying that he had been given a sweet voice from the Mazamir of the family of Dawud. The main message is simple: a beautiful Qur’an recitation can move the heart and deserves appreciation. The Hadith does not speak about showing off or performance. It focuses on the natural beauty of the voice used in reciting Allah’s words."},"teachings":["The Qur’an should be recited with care and beauty.","A pleasant voice in Qur’an recitation is a gift from Allah.","The Prophet (صلى الله عليه وسلم) noticed and praised good recitation.","Reciting Qur’an in the mosque can benefit those who hear it."],"related_hadiths":[{"id":"1342","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1353","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1354","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E106" s="4" t="n"/>
@@ -2911,7 +2915,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tasbih Prayer Gift","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Abbas a four-Rak'ah prayer with repeated tasbih as a special gift."},"heading":{"title":"Tasbih Prayer Hadith: Four Rak'ah and Dhikr","description":"This Tasbih prayer hadith presents the prayer as a gift and benefit that the Prophet offered to Abbas. The instruction is to pray four Rak'ah, reciting Al-Fatihah and a Surah in each Rak'ah. After the recitation, the worshipper says Subhan-Allah, Al-hamdu Lillah, La ilaha illallah, and Allahu Akbar fifteen times, then repeats the same words ten times in each main position of the prayer. The total becomes seventy-five in each Rak'ah and three hundred in four Rak'ah. The hadith also gives a flexible schedule: once a day, weekly, monthly, and finally yearly if unable. The main theme is prayer filled with remembrance of Allah."},"teachings":["The prayer described contains four Rak'ah.","Each Rak'ah includes repeated words of glorification, praise, Tawhid, and takbir.","The hadith gives a counted structure for the dhikr inside prayer.","The narration allows a person to do it according to ability."],"related_hadiths":[{"id":"1387","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1395","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tasbih Prayer Gift","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Abbas a four-Rak'ah prayer with repeated tasbih as a special gift."},"heading":{"title":"Tasbih Prayer Hadith: Four Rak'ah and Dhikr","description":"This Tasbih prayer hadith presents the prayer as a gift and benefit that the Prophet offered to Abbas. The instruction is to pray four Rak'ah, reciting Al-Fatihah and a Surah in each Rak'ah. After the recitation, the worshipper says Subhan-Allah, Al-hamdu Lillah, La ilaha illallah, and Allahu Akbar fifteen times, then repeats the same words ten times in each main position of the prayer. The total becomes seventy-five in each Rak'ah and three hundred in four Rak'ah. The hadith also gives a flexible schedule: once a day, weekly, monthly, and finally yearly if unable. The main theme is prayer filled with remembrance of Allah."},"teachings":["The prayer described contains four Rak'ah.","Each Rak'ah includes repeated words of glorification, praise, Tawhid, and takbir.","The hadith gives a counted structure for the dhikr inside prayer.","The narration allows a person to do it according to ability."],"related_hadiths":[{"id":"1387","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1395","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E107" s="4" t="n"/>
@@ -2934,7 +2938,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forgiveness on Mid-Sha'ban","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah found the Prophet at Al-Baqi, and he mentioned Allah's forgiveness on mid-Sha'ban night."},"heading":{"title":"Mid-Sha'ban Forgiveness Hadith from Aishah","description":"This mid-Sha'ban forgiveness hadith is narrated by Aishah. She said she missed the Prophet one night and went out looking for him. She found him at Al-Baqi, raising his head toward the sky. The Prophet asked whether she feared that Allah and His Messenger would wrong her. She explained that she thought he had gone to one of his other wives. The Prophet then mentioned the night of the middle of Sha'ban and said Allah descends to the lowest heaven and forgives more than the number of hairs on the sheep of Banu Kalb. The core message is Allah's vast forgiveness on that night, as stated in the narration."},"teachings":["Aishah searched for the Prophet when she missed him at night.","The Prophet was found at Al-Baqi, raising his head toward the sky.","The hadith mentions Allah's forgiveness on the middle night of Sha'ban.","The narration uses a large number to describe the breadth of forgiveness."],"related_hadiths":[{"id":"1388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1390","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forgiveness on Mid-Sha'ban","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah found the Prophet at Al-Baqi, and he mentioned Allah's forgiveness on mid-Sha'ban night."},"heading":{"title":"Mid-Sha'ban Forgiveness Hadith from Aishah","description":"This mid-Sha'ban forgiveness hadith is narrated by Aishah. She said she missed the Prophet one night and went out looking for him. She found him at Al-Baqi, raising his head toward the sky. The Prophet asked whether she feared that Allah and His Messenger would wrong her. She explained that she thought he had gone to one of his other wives. The Prophet then mentioned the night of the middle of Sha'ban and said Allah descends to the lowest heaven and forgives more than the number of hairs on the sheep of Banu Kalb. The core message is Allah's vast forgiveness on that night, as stated in the narration."},"teachings":["Aishah searched for the Prophet when she missed him at night.","The Prophet was found at Al-Baqi, raising his head toward the sky.","The hadith mentions Allah's forgiveness on the middle night of Sha'ban.","The narration uses a large number to describe the breadth of forgiveness."],"related_hadiths":[{"id":"1388","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1390","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E108" s="4" t="n"/>
@@ -2957,7 +2961,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sujood Shukr for Happy News","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet would fall in prostration to Allah when happy news came to him."},"heading":{"title":"Sujood Shukr Hadith for Happy News","description":"This sujood shukr hadith gives a clear general practice. Abu Bakrah narrated that when news came to the Prophet that made him happy, or news for which one should be happy, he would fall down prostrate in gratitude to Allah. The wording makes the reason plain: gratitude belongs to Allah, the Blessed and Exalted. The narration does not give a set dua or a number of prostrations in this text. It focuses on the act itself and the feeling behind it. When good news arrives, the Prophet's response was not only happiness, but humble thanks. This makes the hadith highly relevant for searches about prostration of gratitude in Islam."},"teachings":["The Prophet prostrated when happy news came to him.","The prostration was done in gratitude to Allah.","The hadith connects joy with humility before Allah.","The narration does not mention a fixed verbal formula."],"related_hadiths":[{"id":"1392","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1393","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sujood Shukr for Happy News","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet would fall in prostration to Allah when happy news came to him."},"heading":{"title":"Sujood Shukr Hadith for Happy News","description":"This sujood shukr hadith gives a clear general practice. Abu Bakrah narrated that when news came to the Prophet that made him happy, or news for which one should be happy, he would fall down prostrate in gratitude to Allah. The wording makes the reason plain: gratitude belongs to Allah, the Blessed and Exalted. The narration does not give a set dua or a number of prostrations in this text. It focuses on the act itself and the feeling behind it. When good news arrives, the Prophet's response was not only happiness, but humble thanks. This makes the hadith highly relevant for searches about prostration of gratitude in Islam."},"teachings":["The Prophet prostrated when happy news came to him.","The prostration was done in gratitude to Allah.","The hadith connects joy with humility before Allah.","The narration does not mention a fixed verbal formula."],"related_hadiths":[{"id":"1392","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1393","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E109" s="4" t="n"/>
@@ -2980,7 +2984,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Maintaining Prayer on Time","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith connects guarding the five prayers with Allah’s covenant and hope for Paradise."},"heading":{"title":"Maintaining the Five Prayers on Time","description":"This Hadith about maintaining prayer on time presents the five prayers as an obligation from Allah. In the wording of the Hadith, Allah says that He has enjoined five prayers upon the nation of the Prophet صلى الله عليه وسلم and made a covenant with Himself. Whoever maintains them will be admitted to Paradise. Whoever does not maintain them has no such covenant with Allah. The message is short but weighty. It is not only about praying sometimes, but about maintaining the prayers properly. The phrase five daily prayers appears clearly in the meaning of this narration, and the Hadith teaches Muslims to treat salah as a protected duty, not as something casual."},"teachings":["Allah enjoined five prayers upon the nation of the Prophet صلى الله عليه وسلم.","Maintaining the prayers is linked to Allah’s covenant.","Carelessness with prayer removes the special covenant mentioned in the Hadith.","Prayer should be treated as a regular and guarded duty."],"related_hadiths":[{"id":"8","book_id":"1","label":"Sahih Bukhari"},{"id":"16c","book_id":"2","label":"Sahih Muslim"},{"id":"1079","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Maintaining Prayer on Time","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith connects guarding the five prayers with Allah’s covenant and hope for Paradise."},"heading":{"title":"Maintaining the Five Prayers on Time","description":"This Hadith about maintaining prayer on time presents the five prayers as an obligation from Allah. In the wording of the Hadith, Allah says that He has enjoined five prayers upon the nation of the Prophet صلى الله عليه وسلم and made a covenant with Himself. Whoever maintains them will be admitted to Paradise. Whoever does not maintain them has no such covenant with Allah. The message is short but weighty. It is not only about praying sometimes, but about maintaining the prayers properly. The phrase five daily prayers appears clearly in the meaning of this narration, and the Hadith teaches Muslims to treat salah as a protected duty, not as something casual."},"teachings":["Allah enjoined five prayers upon the nation of the Prophet صلى الله عليه وسلم.","Maintaining the prayers is linked to Allah’s covenant.","Carelessness with prayer removes the special covenant mentioned in the Hadith.","Prayer should be treated as a regular and guarded duty."],"related_hadiths":[{"id":"8","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"16c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1079","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E110" s="4" t="n"/>
@@ -3003,7 +3007,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer in the Prophet’s Mosque","description":"$book_name$ $hadith_number$ - $chapter_name$. One prayer in the Prophet’s Mosque is better than a thousand elsewhere, except Al-Masjid Al-Haram."},"heading":{"title":"Prayer in the Prophet’s Mosque and Its Reward","description":"This Hadith about prayer in the Prophet’s Mosque highlights the special merit of praying in Masjid an-Nabawi. The Prophet صلى الله عليه وسلم said that one prayer in his mosque is better than a thousand prayers anywhere else, except the Sacred Mosque. The wording stays focused on the reward of prayer in that blessed mosque and also makes a clear exception for Al-Masjid Al-Haram. A reader searching for Masjid Nabawi prayer reward will find the main lesson easy to understand: some places of worship have a special rank given in the Sunnah. The Hadith does not discuss every mosque or every act, but it clearly points to the high virtue of prayer in the Prophet’s Mosque."},"teachings":["Prayer in the Prophet’s Mosque has a special reward mentioned in the Hadith.","The Sacred Mosque is clearly excluded from the comparison.","The Hadith teaches respect for places Allah gave special merit.","The focus of the narration is prayer, not general actions."],"related_hadiths":[{"id":"1190","book_id":"1","label":"Sahih Bukhari"},{"id":"1395a","book_id":"2","label":"Sahih Muslim"},{"id":"1189","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer in the Prophet’s Mosque","description":"$book_name$ $hadith_number$ - $chapter_name$. One prayer in the Prophet’s Mosque is better than a thousand elsewhere, except Al-Masjid Al-Haram."},"heading":{"title":"Prayer in the Prophet’s Mosque and Its Reward","description":"This Hadith about prayer in the Prophet’s Mosque highlights the special merit of praying in Masjid an-Nabawi. The Prophet صلى الله عليه وسلم said that one prayer in his mosque is better than a thousand prayers anywhere else, except the Sacred Mosque. The wording stays focused on the reward of prayer in that blessed mosque and also makes a clear exception for Al-Masjid Al-Haram. A reader searching for Masjid Nabawi prayer reward will find the main lesson easy to understand: some places of worship have a special rank given in the Sunnah. The Hadith does not discuss every mosque or every act, but it clearly points to the high virtue of prayer in the Prophet’s Mosque."},"teachings":["Prayer in the Prophet’s Mosque has a special reward mentioned in the Hadith.","The Sacred Mosque is clearly excluded from the comparison.","The Hadith teaches respect for places Allah gave special merit.","The focus of the narration is prayer, not general actions."],"related_hadiths":[{"id":"1190","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1395a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1189","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E111" s="4" t="n"/>
@@ -3026,7 +3030,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Masjid Nabawi Prayer Virtue","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم teaches the high reward of one prayer in his mosque, excepting the Sacred Mosque."},"heading":{"title":"Masjid Nabawi Prayer Reward in Hadith","description":"This Hadith about Masjid Nabawi prayer reward gives a clear statement from the Prophet صلى الله عليه وسلم. One prayer in his mosque is better than one thousand prayers in any other mosque, except the Sacred Mosque. The narration is short, direct, and easy to remember. It points to the special status of the Prophet’s Mosque and keeps the exception of Al-Masjid Al-Haram in place. The Hadith does not add other details, so the explanation should stay close to its words. For anyone searching one prayer in Masjid Nabawi hadith, the message is that prayer in this mosque has a special virtue that Muslims should honor when they are able to be there."},"teachings":["The Prophet’s Mosque has a special virtue for prayer.","One prayer there is described as better than one thousand prayers elsewhere.","Al-Masjid Al-Haram remains the exception in this comparison.","The Hadith encourages respect for the rank of blessed mosques."],"related_hadiths":[{"id":"1190","book_id":"1","label":"Sahih Bukhari"},{"id":"1395a","book_id":"2","label":"Sahih Muslim"},{"id":"1189","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Masjid Nabawi Prayer Virtue","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم teaches the high reward of one prayer in his mosque, excepting the Sacred Mosque."},"heading":{"title":"Masjid Nabawi Prayer Reward in Hadith","description":"This Hadith about Masjid Nabawi prayer reward gives a clear statement from the Prophet صلى الله عليه وسلم. One prayer in his mosque is better than one thousand prayers in any other mosque, except the Sacred Mosque. The narration is short, direct, and easy to remember. It points to the special status of the Prophet’s Mosque and keeps the exception of Al-Masjid Al-Haram in place. The Hadith does not add other details, so the explanation should stay close to its words. For anyone searching one prayer in Masjid Nabawi hadith, the message is that prayer in this mosque has a special virtue that Muslims should honor when they are able to be there."},"teachings":["The Prophet’s Mosque has a special virtue for prayer.","One prayer there is described as better than one thousand prayers elsewhere.","Al-Masjid Al-Haram remains the exception in this comparison.","The Hadith encourages respect for the rank of blessed mosques."],"related_hadiths":[{"id":"1190","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1395a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1189","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E112" s="4" t="n"/>
@@ -3049,7 +3053,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Khalil of Allah and Prophetic Honor","description":"$book_name$ $hadith_number$ - $chapter_name$. This report speaks about the Prophet as Allah's close friend and mentions the honor of Ibrahim and Abbas on the Day of Resurrection."},"heading":{"title":"Khalil of Allah Hadith and the Honor of the Prophets","description":"This Hadith about Khalil of Allah centers on a very high form of honor. The report says that Allah took the Messenger of Allah as a close friend, just as He took Ibrahim as a close friend. It also describes the houses of the Prophet and Ibrahim facing one another in Paradise on the Day of Resurrection, with Abbas between them as a believer between two close friends. Since the input itself marks this narration as Maudu', the content should be presented carefully as a reported wording, not as a basis for adding extra claims. The main message in the wording is about love, rank, and closeness to Allah, while also naming Ibrahim and Abbas with honor."},"teachings":["The wording links the Prophet and Ibrahim through the title Khalil, close friend of Allah.","The report mentions Paradise and the Day of Resurrection as a place of honor.","The text identifies Abbas as a believer placed between two close friends.","Because the input labels it Maudu', it should be handled with care."],"related_hadiths":[{"id":"3654","book_id":"1","label":"Sahih Bukhari"},{"id":"149","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Khalil of Allah and Prophetic Honor","description":"$book_name$ $hadith_number$ - $chapter_name$. This report speaks about the Prophet as Allah's close friend and mentions the honor of Ibrahim and Abbas on the Day of Resurrection."},"heading":{"title":"Khalil of Allah Hadith and the Honor of the Prophets","description":"This Hadith about Khalil of Allah centers on a very high form of honor. The report says that Allah took the Messenger of Allah as a close friend, just as He took Ibrahim as a close friend. It also describes the houses of the Prophet and Ibrahim facing one another in Paradise on the Day of Resurrection, with Abbas between them as a believer between two close friends. Since the input itself marks this narration as Maudu', the content should be presented carefully as a reported wording, not as a basis for adding extra claims. The main message in the wording is about love, rank, and closeness to Allah, while also naming Ibrahim and Abbas with honor."},"teachings":["The wording links the Prophet and Ibrahim through the title Khalil, close friend of Allah.","The report mentions Paradise and the Day of Resurrection as a place of honor.","The text identifies Abbas as a believer placed between two close friends.","Because the input labels it Maudu', it should be handled with care."],"related_hadiths":[{"id":"3654","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"149","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E113" s="4" t="n"/>
@@ -3072,7 +3076,7 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Prayer with Longer Qunut","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught that the best prayer is marked by longer Qunut, showing calm devotion."},"heading":{"title":"Best Prayer in Islam: Longer Qunut and Devotion","description":"This Hadith answers a simple but deep question: which prayer is best? The Prophet صلى الله عليه وسلم replied that it is the prayer with the longer Qunut. Based on the wording here, the focus is on prayer that carries more time, stillness, and devotion before Allah. The main lesson is not about rushing through prayer, but giving prayer its proper place. Many people search for best prayer in Islam or hadith about long prayer because they want to know what makes prayer better. This narration points to a prayer filled with patience, focus, and a longer standing or devotion to Allah."},"teachings":["A better prayer is connected to calm and longer devotion.","The Prophet صلى الله عليه وسلم answered religious questions with clear and simple guidance.","Prayer should not be treated as something to rush through."],"related_hadiths":[{"id":"1422","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1424","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Prayer with Longer Qunut","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught that the best prayer is marked by longer Qunut, showing calm devotion."},"heading":{"title":"Best Prayer in Islam: Longer Qunut and Devotion","description":"This Hadith answers a simple but deep question: which prayer is best? The Prophet صلى الله عليه وسلم replied that it is the prayer with the longer Qunut. Based on the wording here, the focus is on prayer that carries more time, stillness, and devotion before Allah. The main lesson is not about rushing through prayer, but giving prayer its proper place. Many people search for best prayer in Islam or hadith about long prayer because they want to know what makes prayer better. This narration points to a prayer filled with patience, focus, and a longer standing or devotion to Allah."},"teachings":["A better prayer is connected to calm and longer devotion.","The Prophet صلى الله عليه وسلم answered religious questions with clear and simple guidance.","Prayer should not be treated as something to rush through."],"related_hadiths":[{"id":"1422","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1424","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E114" s="4" t="n"/>
@@ -3095,7 +3099,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Reward of Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught that every prostration raises a believer’s rank and erases a sin."},"heading":{"title":"Hadith About Prostration: Raised in Rank and Forgiven","description":"This Hadith shows the value of sujud, or prostration, in a very direct way. Abu Fatimah asked the Prophet صلى الله عليه وسلم for a deed he could hold on to and keep doing. The Prophet صلى الله عليه وسلم guided him to prostration. He explained that whenever a person prostrates to Allah, Allah raises him one degree and removes one sin. This makes the hadith about prostration very meaningful for anyone trying to build steady worship. The text teaches that sujud is not just a movement in prayer. It is a deed loved by Allah and linked with spiritual growth, reward, and forgiveness."},"teachings":["Prostration is a deed a believer can keep doing with care.","Each sincere prostration is linked with being raised in status.","Each sincere prostration is also linked with the removal of a sin."],"related_hadiths":[{"id":"1423","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1424","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Reward of Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught that every prostration raises a believer’s rank and erases a sin."},"heading":{"title":"Hadith About Prostration: Raised in Rank and Forgiven","description":"This Hadith shows the value of sujud, or prostration, in a very direct way. Abu Fatimah asked the Prophet صلى الله عليه وسلم for a deed he could hold on to and keep doing. The Prophet صلى الله عليه وسلم guided him to prostration. He explained that whenever a person prostrates to Allah, Allah raises him one degree and removes one sin. This makes the hadith about prostration very meaningful for anyone trying to build steady worship. The text teaches that sujud is not just a movement in prayer. It is a deed loved by Allah and linked with spiritual growth, reward, and forgiveness."},"teachings":["Prostration is a deed a believer can keep doing with care.","Each sincere prostration is linked with being raised in status.","Each sincere prostration is also linked with the removal of a sin."],"related_hadiths":[{"id":"1423","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1424","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E115" s="4" t="n"/>
@@ -3118,7 +3122,7 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sujud Raises Status","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that one prostration for Allah raises a degree and removes a sin."},"heading":{"title":"Sujud Raises Status: A Hadith About Prostration","description":"This Hadith shares a moment of sincere seeking. Ma’dan asked Thawban for a Hadith that might benefit him. After being asked three times, Thawban advised him to prostrate to Allah and then quoted the Prophet صلى الله عليه وسلم. The message is clear: no servant prostrates to Allah except that Allah raises him one degree and removes one sin. Ma’dan later asked Abu Darda’ and received a similar answer. People searching for hadith about sujud or prostration removes sins can learn from this narration that sujud is a repeated path of worship, humility, and hope in Allah’s reward."},"teachings":["Seeking beneficial knowledge is praised in the wording of this report.","Prostration to Allah is tied to being raised one degree.","Prostration is also tied to the removal of one sin."],"related_hadiths":[{"id":"1422","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1424","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sujud Raises Status","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that one prostration for Allah raises a degree and removes a sin."},"heading":{"title":"Sujud Raises Status: A Hadith About Prostration","description":"This Hadith shares a moment of sincere seeking. Ma’dan asked Thawban for a Hadith that might benefit him. After being asked three times, Thawban advised him to prostrate to Allah and then quoted the Prophet صلى الله عليه وسلم. The message is clear: no servant prostrates to Allah except that Allah raises him one degree and removes one sin. Ma’dan later asked Abu Darda’ and received a similar answer. People searching for hadith about sujud or prostration removes sins can learn from this narration that sujud is a repeated path of worship, humility, and hope in Allah’s reward."},"teachings":["Seeking beneficial knowledge is praised in the wording of this report.","Prostration to Allah is tied to being raised one degree.","Prostration is also tied to the removal of one sin."],"related_hadiths":[{"id":"1422","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1424","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E116" s="4" t="n"/>
@@ -3141,7 +3145,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostrate a Great Deal","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم encouraged many prostrations, linking each one with reward, forgiveness, and rank."},"heading":{"title":"Prostrate a Great Deal: Reward of Sujud in Islam","description":"This Hadith gives a clear reason to increase sujud. The Prophet صلى الله عليه وسلم said that no servant prostrates to Allah except that Allah records one good deed for him, removes one bad deed, and raises him one degree. Then he said to prostrate a great deal. The wording makes the value of prostration easy to understand. It is a repeated act of worship with repeated reward. Many search for reward of sujud in Islam because they want practical deeds they can do often. This narration gives that answer in a direct way: increase prostration for Allah."},"teachings":["Every prostration to Allah is linked with one recorded good deed.","Every prostration is linked with one bad deed being erased.","The Prophet صلى الله عليه وسلم encouraged believers to prostrate a great deal."],"related_hadiths":[{"id":"1422","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1423","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostrate a Great Deal","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم encouraged many prostrations, linking each one with reward, forgiveness, and rank."},"heading":{"title":"Prostrate a Great Deal: Reward of Sujud in Islam","description":"This Hadith gives a clear reason to increase sujud. The Prophet صلى الله عليه وسلم said that no servant prostrates to Allah except that Allah records one good deed for him, removes one bad deed, and raises him one degree. Then he said to prostrate a great deal. The wording makes the value of prostration easy to understand. It is a repeated act of worship with repeated reward. Many search for reward of sujud in Islam because they want practical deeds they can do often. This narration gives that answer in a direct way: increase prostration for Allah."},"teachings":["Every prostration to Allah is linked with one recorded good deed.","Every prostration is linked with one bad deed being erased.","The Prophet صلى الله عليه وسلم encouraged believers to prostrate a great deal."],"related_hadiths":[{"id":"1422","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1423","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E117" s="4" t="n"/>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | First Deed Accounted","description":"$book_name$ $hadith_number$ - $chapter_name$. Prayer is the first deed brought to account, and voluntary prayer may complete what is lacking."},"heading":{"title":"First Deed on the Day of Resurrection: Prayer","description":"This Hadith teaches that the first matter a Muslim will be brought to account for on the Day of Resurrection is the prescribed prayer. If the obligatory prayers are complete, that is good. If they are lacking, it will be said to look for voluntary prayers. If voluntary prayers are found, they will be used to complete what is missing from the obligatory prayers. Then the same kind of reckoning will be done with other obligatory deeds. This hadith about prayer being the first deed reminds believers to care for the five daily prayers and also value voluntary prayers."},"teachings":["The prescribed prayer has a major place in accountability.","Voluntary prayers can help complete what is lacking in obligatory prayers.","Other obligatory deeds will also be reckoned in a similar way."],"related_hadiths":[{"id":"1426","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1427","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | First Deed Accounted","description":"$book_name$ $hadith_number$ - $chapter_name$. Prayer is the first deed brought to account, and voluntary prayer may complete what is lacking."},"heading":{"title":"First Deed on the Day of Resurrection: Prayer","description":"This Hadith teaches that the first matter a Muslim will be brought to account for on the Day of Resurrection is the prescribed prayer. If the obligatory prayers are complete, that is good. If they are lacking, it will be said to look for voluntary prayers. If voluntary prayers are found, they will be used to complete what is missing from the obligatory prayers. Then the same kind of reckoning will be done with other obligatory deeds. This hadith about prayer being the first deed reminds believers to care for the five daily prayers and also value voluntary prayers."},"teachings":["The prescribed prayer has a major place in accountability.","Voluntary prayers can help complete what is lacking in obligatory prayers.","Other obligatory deeds will also be reckoned in a similar way."],"related_hadiths":[{"id":"1426","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1427","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E118" s="4" t="n"/>
@@ -3187,7 +3191,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Moving for Voluntary Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم guided worshippers to move from their prayer spot for voluntary prayer."},"heading":{"title":"Voluntary Prayer in Islam: Moving from the Prayer Spot","description":"This Hadith speaks about a simple prayer practice. The Prophet صلى الله عليه وسلم asked whether one of you is unable, after praying, to step forward or backward, or to the right or left. The narrator explains that this refers to offering a voluntary prayer. The wording points to separating the place of one prayer from another by moving a little. Many people search for hadith about voluntary prayer after fard because they want to know what to do after the obligatory prayer. This narration gives a clear action: when praying extra prayer, one may change position instead of staying fixed in the same place."},"teachings":["A worshipper may move slightly before offering voluntary prayer.","The movement can be forward, backward, right, or left.","Voluntary prayer after obligatory prayer is treated with its own prayer manner."],"related_hadiths":[{"id":"1428","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1429","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Moving for Voluntary Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم guided worshippers to move from their prayer spot for voluntary prayer."},"heading":{"title":"Voluntary Prayer in Islam: Moving from the Prayer Spot","description":"This Hadith speaks about a simple prayer practice. The Prophet صلى الله عليه وسلم asked whether one of you is unable, after praying, to step forward or backward, or to the right or left. The narrator explains that this refers to offering a voluntary prayer. The wording points to separating the place of one prayer from another by moving a little. Many people search for hadith about voluntary prayer after fard because they want to know what to do after the obligatory prayer. This narration gives a clear action: when praying extra prayer, one may change position instead of staying fixed in the same place."},"teachings":["A worshipper may move slightly before offering voluntary prayer.","The movement can be forward, backward, right, or left.","Voluntary prayer after obligatory prayer is treated with its own prayer manner."],"related_hadiths":[{"id":"1428","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1429","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E119" s="4" t="n"/>
@@ -3210,7 +3214,7 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Imam Moving After Fard","description":"$book_name$ $hadith_number$ - $chapter_name$. The Imam should move aside before praying in the place of the obligatory prayer."},"heading":{"title":"Imam Moving After Obligatory Prayer: A Prayer Manner","description":"This Hadith gives guidance for the Imam after the obligatory prayer. The Prophet صلى الله عليه وسلم said that the Imam should not pray in the same place where he offered the obligatory prayer until he moves aside. The text is short, but the meaning is practical. It deals with prayer place and order after the fard prayer. People often search for imam moving after fard prayer or sunnah prayer after obligatory prayer because they want to know the correct manner. This narration focuses only on the Imam and the act of moving aside before praying again in the same place."},"teachings":["The Imam should not remain in the same prayer spot for the next prayer.","Moving aside separates the obligatory prayer from another prayer.","The Hadith teaches a clear prayer manner for the Imam."],"related_hadiths":[{"id":"1427","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1429","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Imam Moving After Fard","description":"$book_name$ $hadith_number$ - $chapter_name$. The Imam should move aside before praying in the place of the obligatory prayer."},"heading":{"title":"Imam Moving After Obligatory Prayer: A Prayer Manner","description":"This Hadith gives guidance for the Imam after the obligatory prayer. The Prophet صلى الله عليه وسلم said that the Imam should not pray in the same place where he offered the obligatory prayer until he moves aside. The text is short, but the meaning is practical. It deals with prayer place and order after the fard prayer. People often search for imam moving after fard prayer or sunnah prayer after obligatory prayer because they want to know the correct manner. This narration focuses only on the Imam and the act of moving aside before praying again in the same place."},"teachings":["The Imam should not remain in the same prayer spot for the next prayer.","Moving aside separates the obligatory prayer from another prayer.","The Hadith teaches a clear prayer manner for the Imam."],"related_hadiths":[{"id":"1427","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1429","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E120" s="4" t="n"/>
@@ -3233,7 +3237,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Bad Prayer Habits","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم forbade pecking, spreading forearms, and fixing one mosque spot."},"heading":{"title":"Prayer Manners in Islam: Three Things Forbidden","description":"This Hadith mentions three prayer habits the Messenger of Allah صلى الله عليه وسلم forbade. The first is pecking like a crow, which points to a rushed movement. The second is spreading the forearms like a beast of prey. The third is a man taking one place in the mosque as his fixed prayer spot, like a camel has a place it keeps returning to. Many search for prayer manners in Islam or hadith about rushing in prayer. This narration teaches that prayer should have dignity, proper posture, and should not become tied to a personal spot in the mosque in that way."},"teachings":["Prayer should not be rushed like pecking.","Forearms should not be spread in the manner described in the Hadith.","A person should not claim a fixed mosque spot like the example given."],"related_hadiths":[{"id":"1427","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1428","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Bad Prayer Habits","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم forbade pecking, spreading forearms, and fixing one mosque spot."},"heading":{"title":"Prayer Manners in Islam: Three Things Forbidden","description":"This Hadith mentions three prayer habits the Messenger of Allah صلى الله عليه وسلم forbade. The first is pecking like a crow, which points to a rushed movement. The second is spreading the forearms like a beast of prey. The third is a man taking one place in the mosque as his fixed prayer spot, like a camel has a place it keeps returning to. Many search for prayer manners in Islam or hadith about rushing in prayer. This narration teaches that prayer should have dignity, proper posture, and should not become tied to a personal spot in the mosque in that way."},"teachings":["Prayer should not be rushed like pecking.","Forearms should not be spread in the manner described in the Hadith.","A person should not claim a fixed mosque spot like the example given."],"related_hadiths":[{"id":"1427","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1428","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E121" s="4" t="n"/>
@@ -3256,7 +3260,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Love for Husain","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet kissed Husain and said Husain is part of him, while praying for Allah's love for those who love Husain."},"heading":{"title":"Hadith About Husain Is From Me and I Am From Husain","description":"This Hadith about Husain is from me shows the Prophet's loving treatment of Husain as a child. The narration says Husain was playing in the street, and the Prophet stretched out his hands, made him laugh, caught him, kissed him, and then spoke about him. The main wording is, \"Husain is part of me and I am part of him. May Allah love those who love Husain.\" The report also says, \"Husain is a tribe among tribes.\" The explanation should stay with the text: affection, closeness, and love for Husain. It also shows that the Prophet's love was not cold or hidden; it was shown through kindness, playfulness, a kiss, and dua."},"teachings":["The Prophet treated Husain with visible affection and kindness.","The Hadith links love for Husain with a dua for Allah's love.","The phrase \"Husain is part of me\" shows closeness in the wording of the report.","The narration shows care for a child through play, a smile, and a kiss."],"related_hadiths":[{"id":"3775","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"143","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Love for Husain","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet kissed Husain and said Husain is part of him, while praying for Allah's love for those who love Husain."},"heading":{"title":"Hadith About Husain Is From Me and I Am From Husain","description":"This Hadith about Husain is from me shows the Prophet's loving treatment of Husain as a child. The narration says Husain was playing in the street, and the Prophet stretched out his hands, made him laugh, caught him, kissed him, and then spoke about him. The main wording is, \"Husain is part of me and I am part of him. May Allah love those who love Husain.\" The report also says, \"Husain is a tribe among tribes.\" The explanation should stay with the text: affection, closeness, and love for Husain. It also shows that the Prophet's love was not cold or hidden; it was shown through kindness, playfulness, a kiss, and dua."},"teachings":["The Prophet treated Husain with visible affection and kindness.","The Hadith links love for Husain with a dua for Allah's love.","The phrase \"Husain is part of me\" shows closeness in the wording of the report.","The narration shows care for a child through play, a smile, and a kiss."],"related_hadiths":[{"id":"3775","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"143","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -3283,7 +3287,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ask the Sick for Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn why visiting the sick includes asking them for sincere dua, as their prayer is highly honored."},"heading":{"title":"Hadith About Visiting the Sick and Asking for Dua","description":"This Hadith about visiting the sick teaches a gentle and meaningful adab. The Prophet صلى الله عليه وسلم told Umar ibn Al-Khattab that when he entered upon a sick person, he should ask that person to pray for him. The reason given in the text is clear: the supplication of the sick person is like the supplication of the angels. The focus is not only on helping the sick, but also on seeing their spiritual worth. A sick person may look weak in body, yet their dua has a special value in this narration. The main lesson is simple: when visiting someone ill, speak kindly, ask for dua, and remember that sickness does not remove a believer’s honor."},"teachings":["Visiting a sick person should include kind words and sincere spiritual care.","The dua of a sick person is described as highly honored in this Hadith.","A person who is weak in body may still have a strong place before Allah."],"related_hadiths":[{"id":"1442","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1443","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ask the Sick for Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn why visiting the sick includes asking them for sincere dua, as their prayer is highly honored."},"heading":{"title":"Hadith About Visiting the Sick and Asking for Dua","description":"This Hadith about visiting the sick teaches a gentle and meaningful adab. The Prophet صلى الله عليه وسلم told Umar ibn Al-Khattab that when he entered upon a sick person, he should ask that person to pray for him. The reason given in the text is clear: the supplication of the sick person is like the supplication of the angels. The focus is not only on helping the sick, but also on seeing their spiritual worth. A sick person may look weak in body, yet their dua has a special value in this narration. The main lesson is simple: when visiting someone ill, speak kindly, ask for dua, and remember that sickness does not remove a believer’s honor."},"teachings":["Visiting a sick person should include kind words and sincere spiritual care.","The dua of a sick person is described as highly honored in this Hadith.","A person who is weak in body may still have a strong place before Allah."],"related_hadiths":[{"id":"1442","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1443","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E123" s="4" t="n"/>
@@ -3306,7 +3310,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward of Visiting the Sick","description":"$book_name$ $hadith_number$ - $chapter_name$. A powerful Hadith on visiting a sick Muslim, mercy, Paradise, and angels sending blessings."},"heading":{"title":"Reward of Visiting the Sick in Islam","description":"This Hadith about visiting the sick describes the great reward for someone who goes to visit his Muslim brother during illness. The Prophet صلى الله عليه وسلم said that such a person is walking among the harvest of Paradise until he sits. When he sits, he is covered with mercy. The Hadith also mentions that if the visit happens in the morning, seventy thousand angels send blessings upon him until evening. If it happens in the evening, they send blessings until morning. The message is warm and direct: visiting the sick is not a small social act. It is an act of mercy, brotherhood, and faith, connected in the Hadith to Paradise and the prayers of angels."},"teachings":["Visiting a sick Muslim is presented as a deeply rewarded act.","Mercy is linked to sitting with the sick person after visiting them.","The Hadith encourages Muslims to care for one another in times of illness."],"related_hadiths":[{"id":"1441","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1443","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward of Visiting the Sick","description":"$book_name$ $hadith_number$ - $chapter_name$. A powerful Hadith on visiting a sick Muslim, mercy, Paradise, and angels sending blessings."},"heading":{"title":"Reward of Visiting the Sick in Islam","description":"This Hadith about visiting the sick describes the great reward for someone who goes to visit his Muslim brother during illness. The Prophet صلى الله عليه وسلم said that such a person is walking among the harvest of Paradise until he sits. When he sits, he is covered with mercy. The Hadith also mentions that if the visit happens in the morning, seventy thousand angels send blessings upon him until evening. If it happens in the evening, they send blessings until morning. The message is warm and direct: visiting the sick is not a small social act. It is an act of mercy, brotherhood, and faith, connected in the Hadith to Paradise and the prayers of angels."},"teachings":["Visiting a sick Muslim is presented as a deeply rewarded act.","Mercy is linked to sitting with the sick person after visiting them.","The Hadith encourages Muslims to care for one another in times of illness."],"related_hadiths":[{"id":"1441","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1443","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E124" s="4" t="n"/>
@@ -3329,7 +3333,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Urging La Ilaha Illallah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Muslims to gently urge the dying to say La ilaha illallah."},"heading":{"title":"Hadith About Saying La Ilaha Illallah at Death","description":"This Hadith about saying La ilaha illallah at death is short, clear, and focused. Abu Hurairah narrated that the Messenger of Allah صلى الله عليه وسلم said to urge the dying ones to say La ilaha illallah. The Hadith points to the importance of tawhid at the final moments of life. The instruction is about prompting, not forcing. The words are simple: there is no deity worthy of worship except Allah. The text teaches Muslims to help a dying person remember Allah with the best words of faith. It also reminds the family and those present to stay mindful, calm, and focused on what benefits the dying person spiritually."},"teachings":["The dying person should be reminded of La ilaha illallah.","The final moments should be filled with remembrance of Allah.","Those present should help gently and keep the focus on faith."],"related_hadiths":[{"id":"1445","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1446","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Urging La Ilaha Illallah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Muslims to gently urge the dying to say La ilaha illallah."},"heading":{"title":"Hadith About Saying La Ilaha Illallah at Death","description":"This Hadith about saying La ilaha illallah at death is short, clear, and focused. Abu Hurairah narrated that the Messenger of Allah صلى الله عليه وسلم said to urge the dying ones to say La ilaha illallah. The Hadith points to the importance of tawhid at the final moments of life. The instruction is about prompting, not forcing. The words are simple: there is no deity worthy of worship except Allah. The text teaches Muslims to help a dying person remember Allah with the best words of faith. It also reminds the family and those present to stay mindful, calm, and focused on what benefits the dying person spiritually."},"teachings":["The dying person should be reminded of La ilaha illallah.","The final moments should be filled with remembrance of Allah.","Those present should help gently and keep the focus on faith."],"related_hadiths":[{"id":"1445","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1446","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E125" s="4" t="n"/>
@@ -3352,7 +3356,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Ilaha Illallah for the Dying","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear reminder to prompt the dying with La ilaha illallah during their final moments."},"heading":{"title":"La Ilaha Illallah for the Dying Person","description":"This Hadith about La ilaha illallah for the dying person carries the same direct teaching narrated from Abu Saeed Al-Khudri. The Messenger of Allah صلى الله عليه وسلم instructed Muslims to urge their dying ones to say La ilaha illallah. The words point to pure belief in Allah and are the best words to remember at the end of life. The Hadith keeps the instruction simple and easy to act upon. When a person is near death, those around them should not fill the moment with panic or careless speech. They should guide the person toward remembrance of Allah in a soft and respectful way, based on the wording of the Hadith."},"teachings":["La ilaha illallah should be gently prompted near death.","The people around the dying person should choose words of faith.","The Hadith highlights tawhid as the central reminder at life’s end."],"related_hadiths":[{"id":"1444","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1446","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Ilaha Illallah for the Dying","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear reminder to prompt the dying with La ilaha illallah during their final moments."},"heading":{"title":"La Ilaha Illallah for the Dying Person","description":"This Hadith about La ilaha illallah for the dying person carries the same direct teaching narrated from Abu Saeed Al-Khudri. The Messenger of Allah صلى الله عليه وسلم instructed Muslims to urge their dying ones to say La ilaha illallah. The words point to pure belief in Allah and are the best words to remember at the end of life. The Hadith keeps the instruction simple and easy to act upon. When a person is near death, those around them should not fill the moment with panic or careless speech. They should guide the person toward remembrance of Allah in a soft and respectful way, based on the wording of the Hadith."},"teachings":["La ilaha illallah should be gently prompted near death.","The people around the dying person should choose words of faith.","The Hadith highlights tawhid as the central reminder at life’s end."],"related_hadiths":[{"id":"1444","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1446","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E126" s="4" t="n"/>
@@ -3375,7 +3379,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr for the Dying and Living","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith teaching words of tawhid, glorification, and praise for the dying and the living."},"heading":{"title":"Dhikr for the Dying: La Ilaha Illallahul Halimul Karim","description":"This Hadith about dhikr for the dying gives a longer wording to be prompted near death. The Prophet صلى الله عليه وسلم said to urge the dying ones to say La ilaha illallahul-Halimul-Karim, Subhan-Allahi Rabbil-Arshil-Azim, Al-Hamdu Lillahi Rabbil-alamin. The translation in the text includes belief in Allah, praise of Allah, and glorifying Him as Lord of the magnificent Throne and Lord of the worlds. When the Companions asked about those who are alive, the Prophet صلى الله عليه وسلم said it is even better. So the Hadith is not only about the dying. It also encourages the living to say these words of remembrance with love and faith."},"teachings":["The dying may be prompted with words of tawhid, praise, and glorification.","The same dhikr is described as even better for living people.","The Hadith connects final moments with remembrance of Allah."],"related_hadiths":[{"id":"1444","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1445","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr for the Dying and Living","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith teaching words of tawhid, glorification, and praise for the dying and the living."},"heading":{"title":"Dhikr for the Dying: La Ilaha Illallahul Halimul Karim","description":"This Hadith about dhikr for the dying gives a longer wording to be prompted near death. The Prophet صلى الله عليه وسلم said to urge the dying ones to say La ilaha illallahul-Halimul-Karim, Subhan-Allahi Rabbil-Arshil-Azim, Al-Hamdu Lillahi Rabbil-alamin. The translation in the text includes belief in Allah, praise of Allah, and glorifying Him as Lord of the magnificent Throne and Lord of the worlds. When the Companions asked about those who are alive, the Prophet صلى الله عليه وسلم said it is even better. So the Hadith is not only about the dying. It also encourages the living to say these words of remembrance with love and faith."},"teachings":["The dying may be prompted with words of tawhid, praise, and glorification.","The same dhikr is described as even better for living people.","The Hadith connects final moments with remembrance of Allah."],"related_hadiths":[{"id":"1444","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1445","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E127" s="4" t="n"/>
@@ -3398,7 +3402,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Say Good Things Near the Sick","description":"$book_name$ $hadith_number$ - $chapter_name$. When visiting the sick or dying, speak good words because angels say Amin to what is said."},"heading":{"title":"Say Good Things Near the Sick and Dying","description":"This Hadith about saying good things near the sick and dying teaches careful speech at a sensitive time. The Messenger of Allah صلى الله عليه وسلم said that when people visit someone sick or dying, they should say good things because the angels say Amin to what they say. The report then shows Umm Salamah after Abu Salamah died. The Prophet صلى الله عليه وسلم taught her to ask Allah for forgiveness for herself and him, and to ask for a good replacement. She said the dua, and Allah compensated her with someone better: Muhammad the Messenger of Allah صلى الله عليه وسلم. The lesson is clear: at illness and death, words matter. Choose dua, mercy, and hope."},"teachings":["People should speak good words around the sick or dying.","The Hadith says angels say Amin to what is said in that moment.","Dua after loss should include forgiveness and asking Allah for good."],"related_hadiths":[{"id":"1455","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1454","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1441","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Say Good Things Near the Sick","description":"$book_name$ $hadith_number$ - $chapter_name$. When visiting the sick or dying, speak good words because angels say Amin to what is said."},"heading":{"title":"Say Good Things Near the Sick and Dying","description":"This Hadith about saying good things near the sick and dying teaches careful speech at a sensitive time. The Messenger of Allah صلى الله عليه وسلم said that when people visit someone sick or dying, they should say good things because the angels say Amin to what they say. The report then shows Umm Salamah after Abu Salamah died. The Prophet صلى الله عليه وسلم taught her to ask Allah for forgiveness for herself and him, and to ask for a good replacement. She said the dua, and Allah compensated her with someone better: Muhammad the Messenger of Allah صلى الله عليه وسلم. The lesson is clear: at illness and death, words matter. Choose dua, mercy, and hope."},"teachings":["People should speak good words around the sick or dying.","The Hadith says angels say Amin to what is said in that moment.","Dua after loss should include forgiveness and asking Allah for good."],"related_hadiths":[{"id":"1455","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1454","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1441","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E128" s="4" t="n"/>
@@ -3421,7 +3425,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Souls of Believers in Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. A narration about believers’ souls in green birds eating from the trees of Paradise."},"heading":{"title":"Souls of Believers in Green Birds Hadith","description":"This Hadith about the souls of believers mentions a conversation near the time of Kaab’s death. Umm Bishr asked him to convey Salam if he met someone. Kaab replied that they would be too busy for that. She then reminded him of the statement of the Messenger of Allah صلى الله عليه وسلم: the souls of the believers are in green birds, eating from the trees of Paradise. Kaab confirmed that he had heard it. The narration gives hope about the honor of believers after death, using the image mentioned in the text. It also shows how believers spoke about death with faith, hope, and a link to the words of the Prophet صلى الله عليه وسلم."},"teachings":["The Hadith mentions the souls of believers in green birds.","Paradise is described through the image of trees from which they eat.","The narration connects talk of death with hope based on Prophetic words."],"related_hadiths":[{"id":"1450","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1451","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1452","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Souls of Believers in Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. A narration about believers’ souls in green birds eating from the trees of Paradise."},"heading":{"title":"Souls of Believers in Green Birds Hadith","description":"This Hadith about the souls of believers mentions a conversation near the time of Kaab’s death. Umm Bishr asked him to convey Salam if he met someone. Kaab replied that they would be too busy for that. She then reminded him of the statement of the Messenger of Allah صلى الله عليه وسلم: the souls of the believers are in green birds, eating from the trees of Paradise. Kaab confirmed that he had heard it. The narration gives hope about the honor of believers after death, using the image mentioned in the text. It also shows how believers spoke about death with faith, hope, and a link to the words of the Prophet صلى الله عليه وسلم."},"teachings":["The Hadith mentions the souls of believers in green birds.","Paradise is described through the image of trees from which they eat.","The narration connects talk of death with hope based on Prophetic words."],"related_hadiths":[{"id":"1450","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1451","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1452","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E129" s="4" t="n"/>
@@ -3444,7 +3448,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Comfort During the Throes of Death","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet comforted Aishah by saying her relative’s death struggle was part of his merits."},"heading":{"title":"Hadith About Comfort During the Throes of Death","description":"This Hadith about comfort during the throes of death shows the Prophet صلى الله عليه وسلم responding to grief with gentle words. Aishah had a close relative who was in the throes of death, and she was upset. When the Prophet صلى الله عليه وسلم saw her state, he told her not to grieve for her relative, because that was part of his Hasanat, meaning merits. The Hadith does not remove the pain of seeing a loved one suffer, but it gives a faith-based way to look at the moment. The suffering mentioned in the text is not described as empty or meaningless. It is connected to the person’s merits, which can bring comfort to those present."},"teachings":["The Prophet صلى الله عليه وسلم comforted Aishah when she was upset over her relative.","The throes of death were described as part of the relative’s merits.","Kind words can help people face painful moments with faith."],"related_hadiths":[{"id":"1452","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1453","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Comfort During the Throes of Death","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet comforted Aishah by saying her relative’s death struggle was part of his merits."},"heading":{"title":"Hadith About Comfort During the Throes of Death","description":"This Hadith about comfort during the throes of death shows the Prophet صلى الله عليه وسلم responding to grief with gentle words. Aishah had a close relative who was in the throes of death, and she was upset. When the Prophet صلى الله عليه وسلم saw her state, he told her not to grieve for her relative, because that was part of his Hasanat, meaning merits. The Hadith does not remove the pain of seeing a loved one suffer, but it gives a faith-based way to look at the moment. The suffering mentioned in the text is not described as empty or meaningless. It is connected to the person’s merits, which can bring comfort to those present."},"teachings":["The Prophet صلى الله عليه وسلم comforted Aishah when she was upset over her relative.","The throes of death were described as part of the relative’s merits.","Kind words can help people face painful moments with faith."],"related_hadiths":[{"id":"1452","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1453","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E130" s="4" t="n"/>
@@ -3467,7 +3471,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sweat on the Believer’s Brow","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said the believer dies with sweat on his brow."},"heading":{"title":"The Believer Dies With Sweat on His Brow Hadith","description":"This Hadith about the believer dying with sweat on his brow is very short. Abu Buraidah narrated from his father that the Prophet صلى الله عليه وسلم said: the believer dies with sweat on his brow. The text gives a sign connected to the believer at death, but it does not add a long explanation in this narration. For that reason, it is best to avoid making claims beyond the wording. The Hadith reminds the reader that the moment of death has signs known through revelation. It also teaches us to speak about death carefully. Not every detail is explained here, but the statement itself is clear and memorable."},"teachings":["The Hadith mentions sweat on the brow as connected to the believer’s death.","The narration is brief, so extra claims should not be added to it.","Death is a serious moment that should be discussed with care."],"related_hadiths":[{"id":"1451","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1453","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1454","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sweat on the Believer’s Brow","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said the believer dies with sweat on his brow."},"heading":{"title":"The Believer Dies With Sweat on His Brow Hadith","description":"This Hadith about the believer dying with sweat on his brow is very short. Abu Buraidah narrated from his father that the Prophet صلى الله عليه وسلم said: the believer dies with sweat on his brow. The text gives a sign connected to the believer at death, but it does not add a long explanation in this narration. For that reason, it is best to avoid making claims beyond the wording. The Hadith reminds the reader that the moment of death has signs known through revelation. It also teaches us to speak about death carefully. Not every detail is explained here, but the statement itself is clear and memorable."},"teachings":["The Hadith mentions sweat on the brow as connected to the believer’s death.","The narration is brief, so extra claims should not be added to it.","Death is a serious moment that should be discussed with care."],"related_hadiths":[{"id":"1451","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1453","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1454","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E131" s="4" t="n"/>
@@ -3490,7 +3494,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recognition Near Death","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Musa asked when a person stops recognizing people, and the Prophet answered: when he sees."},"heading":{"title":"When a Person Stops Recognizing People Hadith","description":"This Hadith about when a person stops recognizing people records a question from Abu Musa. He asked the Messenger of Allah صلى الله عليه وسلم when a servant stops recognizing people. The Prophet صلى الله عليه وسلم answered: when he sees. The translation provided does not explain further what is seen, so the safe reading is to stay with the exact wording. The Hadith points to a moment near death when a person’s awareness of people changes. It also shows that the Companions asked the Prophet صلى الله عليه وسلم about serious matters linked to death. The narration is short, but it reminds us that the final stage of life has realities that people cannot fully explain by ordinary experience."},"teachings":["The Hadith links loss of recognition with a moment described as when he sees.","The text does not spell out more detail, so the explanation should stay limited.","Questions about death were asked directly to the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"1452","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1454","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recognition Near Death","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Musa asked when a person stops recognizing people, and the Prophet answered: when he sees."},"heading":{"title":"When a Person Stops Recognizing People Hadith","description":"This Hadith about when a person stops recognizing people records a question from Abu Musa. He asked the Messenger of Allah صلى الله عليه وسلم when a servant stops recognizing people. The Prophet صلى الله عليه وسلم answered: when he sees. The translation provided does not explain further what is seen, so the safe reading is to stay with the exact wording. The Hadith points to a moment near death when a person’s awareness of people changes. It also shows that the Companions asked the Prophet صلى الله عليه وسلم about serious matters linked to death. The narration is short, but it reminds us that the final stage of life has realities that people cannot fully explain by ordinary experience."},"teachings":["The Hadith links loss of recognition with a moment described as when he sees.","The text does not spell out more detail, so the explanation should stay limited.","Questions about death were asked directly to the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"1452","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1454","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E132" s="4" t="n"/>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Close the Eyes and Say Good","description":"$book_name$ $hadith_number$ - $chapter_name$. When coming to the deceased, close their eyes and say good words because angels say Amin."},"heading":{"title":"Close the Eyes of the Deceased and Say Good Things","description":"This Hadith about closing the eyes of the deceased brings together two important actions. The Messenger of Allah صلى الله عليه وسلم said that when people come to their dead ones, they should close the eyes, because the sight follows the soul. He also said to say good things, because the angels say Amin to what the members of the household say. The Hadith teaches both care for the body and care for the words spoken in the home. After death, people may feel shock and sadness, but the Prophet صلى الله عليه وسلم guides them to dignity, calm action, and good speech. The tongue should turn to dua and words that are pleasing."},"teachings":["The eyes of the deceased should be closed, as stated in the Hadith.","Good words should be said around the deceased.","The Hadith says angels say Amin to what the household says."],"related_hadiths":[{"id":"1454","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1456","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Close the Eyes and Say Good","description":"$book_name$ $hadith_number$ - $chapter_name$. When coming to the deceased, close their eyes and say good words because angels say Amin."},"heading":{"title":"Close the Eyes of the Deceased and Say Good Things","description":"This Hadith about closing the eyes of the deceased brings together two important actions. The Messenger of Allah صلى الله عليه وسلم said that when people come to their dead ones, they should close the eyes, because the sight follows the soul. He also said to say good things, because the angels say Amin to what the members of the household say. The Hadith teaches both care for the body and care for the words spoken in the home. After death, people may feel shock and sadness, but the Prophet صلى الله عليه وسلم guides them to dignity, calm action, and good speech. The tongue should turn to dua and words that are pleasing."},"teachings":["The eyes of the deceased should be closed, as stated in the Hadith.","Good words should be said around the deceased.","The Hadith says angels say Amin to what the household says."],"related_hadiths":[{"id":"1454","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1447","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1456","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E133" s="4" t="n"/>
@@ -3536,7 +3540,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Tears for the Deceased","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet kissed Uthman bin Mazun after death, with tears flowing down his cheeks."},"heading":{"title":"The Prophet Kissed the Deceased and Wept","description":"This Hadith about the Prophet صلى الله عليه وسلم kissing the deceased shows a tender human moment. Aishah said that the Messenger of Allah صلى الله عليه وسلم kissed Uthman bin Mazun when he had died. She remembered the scene so clearly that it was as if she could still see his tears flowing down his cheeks. The narration shows love, sadness, and mercy without adding long speech. It also reminds us that tears at death are not the same as rejecting Allah’s decree. The Hadith simply records the Prophet’s صلى الله عليه وسلم action and tears. For readers, it gives a balanced picture: grief can exist with faith, respect, and love for the deceased."},"teachings":["The Prophet صلى الله عليه وسلم kissed Uthman bin Mazun after he died.","The narration records the Prophet’s tears at that moment.","Grief can be shown with love and respect."],"related_hadiths":[{"id":"1457","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1454","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Tears for the Deceased","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet kissed Uthman bin Mazun after death, with tears flowing down his cheeks."},"heading":{"title":"The Prophet Kissed the Deceased and Wept","description":"This Hadith about the Prophet صلى الله عليه وسلم kissing the deceased shows a tender human moment. Aishah said that the Messenger of Allah صلى الله عليه وسلم kissed Uthman bin Mazun when he had died. She remembered the scene so clearly that it was as if she could still see his tears flowing down his cheeks. The narration shows love, sadness, and mercy without adding long speech. It also reminds us that tears at death are not the same as rejecting Allah’s decree. The Hadith simply records the Prophet’s صلى الله عليه وسلم action and tears. For readers, it gives a balanced picture: grief can exist with faith, respect, and love for the deceased."},"teachings":["The Prophet صلى الله عليه وسلم kissed Uthman bin Mazun after he died.","The narration records the Prophet’s tears at that moment.","Grief can be shown with love and respect."],"related_hadiths":[{"id":"1457","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1454","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E134" s="4" t="n"/>
@@ -3559,7 +3563,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr Kissed the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr kissed the Prophet after he died, as narrated from Ibn Abbas and Aishah."},"heading":{"title":"Abu Bakr Kissed the Prophet After His Death","description":"This Hadith about Abu Bakr kissing the Prophet صلى الله عليه وسلم after his death is short and deeply moving. Ibn Abbas and Aishah narrated that Abu Bakr kissed the Prophet صلى الله عليه وسلم when he had died. The report does not include extra details in the provided text, so the meaning should stay close to what is narrated. It shows love, respect, and closeness at a time of great loss. The Hadith also connects to other reports in this group where the deceased is treated with dignity and tenderness. Here, the focus is Abu Bakr’s action toward the Messenger of Allah صلى الله عليه وسلم after his passing, expressed through a simple act of love."},"teachings":["Abu Bakr kissed the Prophet صلى الله عليه وسلم after his death.","The report shows love and respect at the time of loss.","The narration should be understood without adding details not present in the text."],"related_hadiths":[{"id":"1456","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1450","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr Kissed the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr kissed the Prophet after he died, as narrated from Ibn Abbas and Aishah."},"heading":{"title":"Abu Bakr Kissed the Prophet After His Death","description":"This Hadith about Abu Bakr kissing the Prophet صلى الله عليه وسلم after his death is short and deeply moving. Ibn Abbas and Aishah narrated that Abu Bakr kissed the Prophet صلى الله عليه وسلم when he had died. The report does not include extra details in the provided text, so the meaning should stay close to what is narrated. It shows love, respect, and closeness at a time of great loss. The Hadith also connects to other reports in this group where the deceased is treated with dignity and tenderness. Here, the focus is Abu Bakr’s action toward the Messenger of Allah صلى الله عليه وسلم after his passing, expressed through a simple act of love."},"teachings":["Abu Bakr kissed the Prophet صلى الله عليه وسلم after his death.","The report shows love and respect at the time of loss.","The narration should be understood without adding details not present in the text."],"related_hadiths":[{"id":"1456","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1450","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E135" s="4" t="n"/>
@@ -3582,7 +3586,7 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Washing the Deceased with Care","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet instructed washing his daughter with water, lote leaves, and camphor, then shrouding her."},"heading":{"title":"Hadith About Washing the Deceased in Islam","description":"This Hadith about washing the deceased gives clear instructions from the Prophet صلى الله عليه وسلم when his daughter Umm Kulthum was being washed. He told the women to wash her three or five times, or more if they thought it was needed, using water and lote leaves. He also told them to put camphor, or a little camphor, in the final washing. When they finished, they called him, and he gave them his waist-wrapper, telling them to shroud her with it. The Hadith shows care, order, and respect in preparing the deceased. It also shows that those washing the body should act with attention and inform the family when finished."},"teachings":["The deceased should be washed with care and order, as described in the Hadith.","The Prophet صلى الله عليه وسلم mentioned three or five washings, or more if needed.","Camphor was placed in the final washing, according to the narration."],"related_hadiths":[{"id":"1459","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1460","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Washing the Deceased with Care","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet instructed washing his daughter with water, lote leaves, and camphor, then shrouding her."},"heading":{"title":"Hadith About Washing the Deceased in Islam","description":"This Hadith about washing the deceased gives clear instructions from the Prophet صلى الله عليه وسلم when his daughter Umm Kulthum was being washed. He told the women to wash her three or five times, or more if they thought it was needed, using water and lote leaves. He also told them to put camphor, or a little camphor, in the final washing. When they finished, they called him, and he gave them his waist-wrapper, telling them to shroud her with it. The Hadith shows care, order, and respect in preparing the deceased. It also shows that those washing the body should act with attention and inform the family when finished."},"teachings":["The deceased should be washed with care and order, as described in the Hadith.","The Prophet صلى الله عليه وسلم mentioned three or five washings, or more if needed.","Camphor was placed in the final washing, according to the narration."],"related_hadiths":[{"id":"1459","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1460","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E136" s="4" t="n"/>
@@ -3605,7 +3609,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Odd Washes and Right Side","description":"$book_name$ $hadith_number$ - $chapter_name$. The deceased was washed an odd number of times, starting with the right side and wudu places."},"heading":{"title":"Washing the Deceased an Odd Number of Times","description":"This Hadith about washing the deceased adds details to the report of Umm Atiyyah. It mentions washing the deceased an odd number of times, and also mentions three or five washings. The narration says to start with her right side and with the places washed in ablution. It also says that her hair was combed into three braids. These details show that washing the deceased was done with order, care, and respect. The Hadith does not present the process as careless or rushed. It teaches that even after death, the body is treated with dignity, and the people carrying out the washing should follow clear guidance."},"teachings":["The Hadith mentions washing the deceased an odd number of times.","It teaches starting with the right side and the places of wudu.","The deceased’s hair was combed into three braids in this narration."],"related_hadiths":[{"id":"1458","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1460","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Odd Washes and Right Side","description":"$book_name$ $hadith_number$ - $chapter_name$. The deceased was washed an odd number of times, starting with the right side and wudu places."},"heading":{"title":"Washing the Deceased an Odd Number of Times","description":"This Hadith about washing the deceased adds details to the report of Umm Atiyyah. It mentions washing the deceased an odd number of times, and also mentions three or five washings. The narration says to start with her right side and with the places washed in ablution. It also says that her hair was combed into three braids. These details show that washing the deceased was done with order, care, and respect. The Hadith does not present the process as careless or rushed. It teaches that even after death, the body is treated with dignity, and the people carrying out the washing should follow clear guidance."},"teachings":["The Hadith mentions washing the deceased an odd number of times.","It teaches starting with the right side and the places of wudu.","The deceased’s hair was combed into three braids in this narration."],"related_hadiths":[{"id":"1458","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1460","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E137" s="4" t="n"/>
@@ -3628,7 +3632,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Modesty Toward the Living and Dead","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet told Ali not to show his thigh or look at the thigh of the living or the dead."},"heading":{"title":"Hadith About Modesty Toward the Living and the Dead","description":"This Hadith about modesty records advice given by the Prophet صلى الله عليه وسلم to Ali. He said: do not show your thigh, and do not look at the thigh of anyone, living or dead. The wording is direct and includes both living people and deceased people. This teaches respect for the body and careful behavior in situations where a person may be exposed, including after death. The Hadith does not need extra stories to make its point. Its message is simple: a Muslim should guard modesty for himself and respect the modesty of others. The same sense of care applies when dealing with people who have passed away."},"teachings":["The Prophet صلى الله عليه وسلم told Ali not to show his thigh.","The Hadith also forbids looking at the thigh of the living or dead.","Modesty and respect apply even when dealing with the deceased."],"related_hadiths":[{"id":"1458","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1459","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Modesty Toward the Living and Dead","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet told Ali not to show his thigh or look at the thigh of the living or the dead."},"heading":{"title":"Hadith About Modesty Toward the Living and the Dead","description":"This Hadith about modesty records advice given by the Prophet صلى الله عليه وسلم to Ali. He said: do not show your thigh, and do not look at the thigh of anyone, living or dead. The wording is direct and includes both living people and deceased people. This teaches respect for the body and careful behavior in situations where a person may be exposed, including after death. The Hadith does not need extra stories to make its point. Its message is simple: a Muslim should guard modesty for himself and respect the modesty of others. The same sense of care applies when dealing with people who have passed away."},"teachings":["The Prophet صلى الله عليه وسلم told Ali not to show his thigh.","The Hadith also forbids looking at the thigh of the living or dead.","Modesty and respect apply even when dealing with the deceased."],"related_hadiths":[{"id":"1458","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1459","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1455","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E138" s="4" t="n"/>
@@ -3651,7 +3655,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bath After Washing","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever washes a dead person is told to take a bath, linking funeral washing with personal purification."},"heading":{"title":"Hadith About Taking a Bath After Washing the Dead","description":"This Hadith about taking a bath after washing the dead is short but very clear. Abu Hurairah narrated that the Messenger of Allah (صلى الله عليه وسلم) said, “Whoever washes a dead person, let him take a bath.” The core topic is purification after handling the deceased. The Hadith does not give extra details in this text, and it does not mention the full method of the bath. Its message is focused on what should happen after washing a dead person. The person who performs this funeral duty should then wash himself. In simple words, Islamic funeral washing is followed by attention to one’s own cleanliness and purification."},"teachings":["The washer of a dead person is told to take a bath afterward.","Funeral care is connected with cleanliness and purification.","The Hadith gives a direct instruction without extra details."],"related_hadiths":[{"id":"1458","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1459","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1460","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bath After Washing","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever washes a dead person is told to take a bath, linking funeral washing with personal purification."},"heading":{"title":"Hadith About Taking a Bath After Washing the Dead","description":"This Hadith about taking a bath after washing the dead is short but very clear. Abu Hurairah narrated that the Messenger of Allah (صلى الله عليه وسلم) said, “Whoever washes a dead person, let him take a bath.” The core topic is purification after handling the deceased. The Hadith does not give extra details in this text, and it does not mention the full method of the bath. Its message is focused on what should happen after washing a dead person. The person who performs this funeral duty should then wash himself. In simple words, Islamic funeral washing is followed by attention to one’s own cleanliness and purification."},"teachings":["The washer of a dead person is told to take a bath afterward.","Funeral care is connected with cleanliness and purification.","The Hadith gives a direct instruction without extra details."],"related_hadiths":[{"id":"1458","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1459","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1460","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E139" s="4" t="n"/>
@@ -3674,7 +3678,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ammar's Faith","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet described Ammar as overflowing with faith, showing his high spiritual quality."},"heading":{"title":"Hadith About Ammar's Heart Overflowing With Faith","description":"This Hadith about Ammar's faith says that Ammar entered upon Ali, and Ali welcomed him as \"the good and the purified.\" Ali then said that he heard the Messenger of Allah say, \"Ammar's heart overflows with faith,\" literally up to the top of his bones. The main topic is faith, but it is tied to the named Companion Ammar bin Yasir. The wording praises the depth of Ammar's iman in a vivid way. It does not mention a ruling or a separate event, so the explanation should stay with the praise itself. The best search phrase is \"Ammar filled with faith hadith,\" along with \"Ammar bin Yasir virtues.\""},"teachings":["The narration praises Ammar's strong faith.","Ali welcomed Ammar with honorable words.","The phrase about faith overflowing shows deep inner goodness in the report.","The lesson is to value iman, not just outward status."],"related_hadiths":[{"id":"146","book_id":"6","label":"Sunan Ibn Majah"},{"id":"148","book_id":"6","label":"Sunan Ibn Majah"},{"id":"150","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ammar's Faith","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet described Ammar as overflowing with faith, showing his high spiritual quality."},"heading":{"title":"Hadith About Ammar's Heart Overflowing With Faith","description":"This Hadith about Ammar's faith says that Ammar entered upon Ali, and Ali welcomed him as \"the good and the purified.\" Ali then said that he heard the Messenger of Allah say, \"Ammar's heart overflows with faith,\" literally up to the top of his bones. The main topic is faith, but it is tied to the named Companion Ammar bin Yasir. The wording praises the depth of Ammar's iman in a vivid way. It does not mention a ruling or a separate event, so the explanation should stay with the praise itself. The best search phrase is \"Ammar filled with faith hadith,\" along with \"Ammar bin Yasir virtues.\""},"teachings":["The narration praises Ammar's strong faith.","Ali welcomed Ammar with honorable words.","The phrase about faith overflowing shows deep inner goodness in the report.","The lesson is to value iman, not just outward status."],"related_hadiths":[{"id":"146","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"148","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"150","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E140" s="4" t="n"/>
@@ -3697,7 +3701,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Funeral Procession Etiquette","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn where riders and walkers may position themselves during a funeral procession."},"heading":{"title":"Funeral Procession Etiquette for Riders and Walkers","description":"This Hadith gives a clear teaching about funeral procession etiquette. The Prophet صلى الله عليه وسلم said that a rider should travel behind the funeral, while a person walking may walk wherever he wants. The main point is simple: attending a funeral has its own manners, and people should follow them with care. The Hadith about walking with the funeral shows that not everyone in the procession has the same position. A rider is guided to remain behind, while the walker is given more space in where to walk. The text does not add further details, so the lesson should stay focused on this simple instruction. It teaches order, respect, and calm behavior when accompanying the deceased."},"teachings":["A rider should remain behind the funeral procession.","A person walking with the funeral may walk wherever he wants.","Funeral attendance should be done with order and respect."],"related_hadiths":[{"id":"1482","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1483","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1484","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Funeral Procession Etiquette","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn where riders and walkers may position themselves during a funeral procession."},"heading":{"title":"Funeral Procession Etiquette for Riders and Walkers","description":"This Hadith gives a clear teaching about funeral procession etiquette. The Prophet صلى الله عليه وسلم said that a rider should travel behind the funeral, while a person walking may walk wherever he wants. The main point is simple: attending a funeral has its own manners, and people should follow them with care. The Hadith about walking with the funeral shows that not everyone in the procession has the same position. A rider is guided to remain behind, while the walker is given more space in where to walk. The text does not add further details, so the lesson should stay focused on this simple instruction. It teaches order, respect, and calm behavior when accompanying the deceased."},"teachings":["A rider should remain behind the funeral procession.","A person walking with the funeral may walk wherever he wants.","Funeral attendance should be done with order and respect."],"related_hadiths":[{"id":"1482","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1483","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1484","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E141" s="4" t="n"/>
@@ -3720,7 +3724,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Delay the Funeral","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught not to delay the funeral once it is ready."},"heading":{"title":"Do Not Delay the Funeral Once It Is Ready","description":"This Hadith gives a short and clear instruction: do not delay the funeral once it is ready. The core topic is prompt burial and funeral timing. The Prophet صلى الله عليه وسلم did not add many conditions in this narration, so the explanation should stay simple. When the funeral is prepared, it should not be held back without a reason mentioned in the text. The hadith about not delaying the funeral reminds Muslims that the janazah should be handled with seriousness and care. It also shows that honoring the deceased includes moving forward with the funeral when everything is ready. The wording is brief, but its message is practical. It teaches timely action, respect, and avoiding needless delay."},"teachings":["A funeral should not be delayed once it is ready.","The Hadith encourages timely action in funeral matters.","Respect for the deceased includes handling the funeral without needless delay."],"related_hadiths":[{"id":"1485","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1487","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1497","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Delay the Funeral","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught not to delay the funeral once it is ready."},"heading":{"title":"Do Not Delay the Funeral Once It Is Ready","description":"This Hadith gives a short and clear instruction: do not delay the funeral once it is ready. The core topic is prompt burial and funeral timing. The Prophet صلى الله عليه وسلم did not add many conditions in this narration, so the explanation should stay simple. When the funeral is prepared, it should not be held back without a reason mentioned in the text. The hadith about not delaying the funeral reminds Muslims that the janazah should be handled with seriousness and care. It also shows that honoring the deceased includes moving forward with the funeral when everything is ready. The wording is brief, but its message is practical. It teaches timely action, respect, and avoiding needless delay."},"teachings":["A funeral should not be delayed once it is ready.","The Hadith encourages timely action in funeral matters.","Respect for the deceased includes handling the funeral without needless delay."],"related_hadiths":[{"id":"1485","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1487","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1497","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E142" s="4" t="n"/>
@@ -3743,7 +3747,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wailing and Repentance","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against wailing over the dead and calls people back to repentance."},"heading":{"title":"Hadith About Wailing Over the Dead","description":"This hadith about wailing over the dead gives a serious warning about niyahah, or loud ritual wailing in grief. The Prophet صلى الله عليه وسلم described wailing as one of the affairs of the Days of Ignorance. That means it is not the way a believer should respond to death. The hadith also mentions the wailing woman who dies without repentance, showing that the door of return to Allah is still open before death. The main message is not that sadness is wrong. Rather, the hadith warns against turning grief into a forbidden display that includes wailing. A Muslim should meet loss with patience, repentance, and a heart that remembers Allah."},"teachings":["Wailing over the dead is strongly warned against in this hadith.","Repentance remains important before death comes.","Grief should not lead a person into practices linked to the Days of Ignorance.","A believer should respond to death with patience and fear of Allah."],"related_hadiths":[{"id":"1294","book_id":"1","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","label":"Sahih Muslim"},{"id":"1860","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wailing and Repentance","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against wailing over the dead and calls people back to repentance."},"heading":{"title":"Hadith About Wailing Over the Dead","description":"This hadith about wailing over the dead gives a serious warning about niyahah, or loud ritual wailing in grief. The Prophet صلى الله عليه وسلم described wailing as one of the affairs of the Days of Ignorance. That means it is not the way a believer should respond to death. The hadith also mentions the wailing woman who dies without repentance, showing that the door of return to Allah is still open before death. The main message is not that sadness is wrong. Rather, the hadith warns against turning grief into a forbidden display that includes wailing. A Muslim should meet loss with patience, repentance, and a heart that remembers Allah."},"teachings":["Wailing over the dead is strongly warned against in this hadith.","Repentance remains important before death comes.","Grief should not lead a person into practices linked to the Days of Ignorance.","A believer should respond to death with patience and fear of Allah."],"related_hadiths":[{"id":"1294","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1860","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E143" s="4" t="n"/>
@@ -3766,7 +3770,7 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Funeral Without Wailing","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that a funeral should not be followed by loud wailing."},"heading":{"title":"Funeral Etiquette Without Wailing","description":"This hadith about funeral etiquette teaches a clear rule: the Messenger of Allah صلى الله عليه وسلم forbade following a funeral that was accompanied by a wailing woman. The focus is on the behavior that goes with the funeral procession. A funeral is already a moment of reminder, humility, and sadness. The hadith shows that it should not be mixed with niyahah, or loud ritual wailing. The text does not discuss every kind of crying. It speaks about a funeral being accompanied by a wailing woman. So the lesson should stay exactly there: the funeral should be kept free from that forbidden mourning practice. This protects the dignity of the deceased and the seriousness of death."},"teachings":["A funeral procession should not be accompanied by wailing.","The hadith points to calm and respectful funeral conduct.","Public mourning should remain within Islamic limits.","Death should remind people of Allah, not of Jahiliyyah-style grief."],"related_hadiths":[{"id":"1294","book_id":"1","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","label":"Sahih Muslim"},{"id":"1860","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Funeral Without Wailing","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that a funeral should not be followed by loud wailing."},"heading":{"title":"Funeral Etiquette Without Wailing","description":"This hadith about funeral etiquette teaches a clear rule: the Messenger of Allah صلى الله عليه وسلم forbade following a funeral that was accompanied by a wailing woman. The focus is on the behavior that goes with the funeral procession. A funeral is already a moment of reminder, humility, and sadness. The hadith shows that it should not be mixed with niyahah, or loud ritual wailing. The text does not discuss every kind of crying. It speaks about a funeral being accompanied by a wailing woman. So the lesson should stay exactly there: the funeral should be kept free from that forbidden mourning practice. This protects the dignity of the deceased and the seriousness of death."},"teachings":["A funeral procession should not be accompanied by wailing.","The hadith points to calm and respectful funeral conduct.","Public mourning should remain within Islamic limits.","Death should remind people of Allah, not of Jahiliyyah-style grief."],"related_hadiths":[{"id":"1294","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1860","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E144" s="4" t="n"/>
@@ -3789,7 +3793,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mourning Without Jahiliyyah","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against tearing clothes, striking cheeks, and crying with Jahiliyyah cries."},"heading":{"title":"Hadith About Mourning Without Jahiliyyah","description":"This hadith about mourning without Jahiliyyah gives three examples of wrong behavior at the time of grief: tearing garments, striking cheeks, and crying with the cry of the Days of Ignorance. The Prophet صلى الله عليه وسلم said that the person who does this is not one of us. The wording is strong because these actions show uncontrolled grief and a return to ignorant customs. The hadith does not reject sadness itself. It rejects actions and words that go beyond proper Islamic mourning. The main lesson is that a Muslim can feel pain, but should not express it through forbidden acts. Faith should guide the tongue, hands, and behavior during calamity."},"teachings":["Tearing garments in grief is condemned in this hadith.","Striking the cheeks is not the way of Islamic mourning.","Crying with the cries of Jahiliyyah is strongly warned against.","A Muslim’s grief should be controlled by faith and obedience."],"related_hadiths":[{"id":"1294","book_id":"1","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","label":"Sahih Muslim"},{"id":"1860","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mourning Without Jahiliyyah","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against tearing clothes, striking cheeks, and crying with Jahiliyyah cries."},"heading":{"title":"Hadith About Mourning Without Jahiliyyah","description":"This hadith about mourning without Jahiliyyah gives three examples of wrong behavior at the time of grief: tearing garments, striking cheeks, and crying with the cry of the Days of Ignorance. The Prophet صلى الله عليه وسلم said that the person who does this is not one of us. The wording is strong because these actions show uncontrolled grief and a return to ignorant customs. The hadith does not reject sadness itself. It rejects actions and words that go beyond proper Islamic mourning. The main lesson is that a Muslim can feel pain, but should not express it through forbidden acts. Faith should guide the tongue, hands, and behavior during calamity."},"teachings":["Tearing garments in grief is condemned in this hadith.","Striking the cheeks is not the way of Islamic mourning.","Crying with the cries of Jahiliyyah is strongly warned against.","A Muslim’s grief should be controlled by faith and obedience."],"related_hadiths":[{"id":"1294","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1860","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E145" s="4" t="n"/>
@@ -3812,7 +3816,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Restraint During Calamity","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against shaving heads, raising voices, and tearing garments in calamity."},"heading":{"title":"Restraint During Calamity in Islam","description":"This hadith about restraint during calamity shows Abu Musa correcting his wife when she began to wail loudly during his serious illness. He reminded her of the Prophet’s صلى الله عليه وسلم statement: “I am innocent of those who shave their heads, raise their voices and tear their garments.” The narration focuses on actions done at times of calamity. It warns against loud wailing, tearing clothes, and other grief practices that show a lack of control. The hadith does not deny pain, fear, or sadness. It teaches that even in a painful moment, a believer should avoid actions that the Messenger of Allah صلى الله عليه وسلم disowned. Grief should stay within the path of Islam."},"teachings":["Raising the voice in wailing during calamity is warned against.","Tearing garments at times of loss is not acceptable.","A believer should remind family members of prophetic guidance.","Calamity should not lead to actions disowned by the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"1294","book_id":"1","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","label":"Sahih Muslim"},{"id":"1860","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Restraint During Calamity","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against shaving heads, raising voices, and tearing garments in calamity."},"heading":{"title":"Restraint During Calamity in Islam","description":"This hadith about restraint during calamity shows Abu Musa correcting his wife when she began to wail loudly during his serious illness. He reminded her of the Prophet’s صلى الله عليه وسلم statement: “I am innocent of those who shave their heads, raise their voices and tear their garments.” The narration focuses on actions done at times of calamity. It warns against loud wailing, tearing clothes, and other grief practices that show a lack of control. The hadith does not deny pain, fear, or sadness. It teaches that even in a painful moment, a believer should avoid actions that the Messenger of Allah صلى الله عليه وسلم disowned. Grief should stay within the path of Islam."},"teachings":["Raising the voice in wailing during calamity is warned against.","Tearing garments at times of loss is not acceptable.","A believer should remind family members of prophetic guidance.","Calamity should not lead to actions disowned by the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"1294","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1860","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E146" s="4" t="n"/>
@@ -3835,7 +3839,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Natural Tears in Grief","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows that tears and fresh grief can be treated with gentleness."},"heading":{"title":"Natural Tears in Grief Are Not Wailing","description":"This hadith about natural tears in grief shows a gentle side of the Prophet’s صلى الله عليه وسلم guidance. At a funeral, Umar saw a woman and shouted at her. The Prophet صلى الله عليه وسلم told him to leave her alone, saying that the eye weeps, the heart is afflicted, and the bereavement is recent. The text makes an important difference between forbidden wailing and natural sadness. A person who has just faced loss may cry because the pain is fresh. The hadith teaches care, not harshness, in such a moment. It does not open the door to forbidden mourning practices. It simply shows that tears and a wounded heart are part of human grief."},"teachings":["Fresh grief may bring tears and emotional pain.","People in recent bereavement should be treated gently.","Natural crying is different from forbidden wailing.","The Prophet صلى الله عليه وسلم showed mercy during a funeral."],"related_hadiths":[{"id":"1303","book_id":"1","label":"Sahih Bukhari"},{"id":"1283","book_id":"1","label":"Sahih Bukhari"},{"id":"5655","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Natural Tears in Grief","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows that tears and fresh grief can be treated with gentleness."},"heading":{"title":"Natural Tears in Grief Are Not Wailing","description":"This hadith about natural tears in grief shows a gentle side of the Prophet’s صلى الله عليه وسلم guidance. At a funeral, Umar saw a woman and shouted at her. The Prophet صلى الله عليه وسلم told him to leave her alone, saying that the eye weeps, the heart is afflicted, and the bereavement is recent. The text makes an important difference between forbidden wailing and natural sadness. A person who has just faced loss may cry because the pain is fresh. The hadith teaches care, not harshness, in such a moment. It does not open the door to forbidden mourning practices. It simply shows that tears and a wounded heart are part of human grief."},"teachings":["Fresh grief may bring tears and emotional pain.","People in recent bereavement should be treated gently.","Natural crying is different from forbidden wailing.","The Prophet صلى الله عليه وسلم showed mercy during a funeral."],"related_hadiths":[{"id":"1303","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1283","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5655","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E147" s="4" t="n"/>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Grief Without Angering Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows tears and sadness while keeping speech pleasing to Allah."},"heading":{"title":"Grief Without Saying What Angers Allah","description":"This hadith about grief without saying what angers Allah speaks about the death of Ibrahim, the son of the Messenger of Allah صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم wept and explained the proper balance: the eye weeps and the heart grieves, but we do not say anything that angers the Lord. This is a clear lesson in Islamic mourning. Tears are not denied. Sadness is not denied. But the tongue must stay safe. The hadith also mentions that death comes to all and that the latter will join the former. So the believer grieves, but does not speak in a way that displeases Allah. This is grief guided by faith."},"teachings":["The eye may weep and the heart may grieve.","A believer should avoid words that anger Allah during loss.","Death is described as something that comes to all.","The Prophet صلى الله عليه وسلم expressed sadness while staying within obedience."],"related_hadiths":[{"id":"1303","book_id":"1","label":"Sahih Bukhari"},{"id":"5655","book_id":"1","label":"Sahih Bukhari"},{"id":"1283","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Grief Without Angering Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows tears and sadness while keeping speech pleasing to Allah."},"heading":{"title":"Grief Without Saying What Angers Allah","description":"This hadith about grief without saying what angers Allah speaks about the death of Ibrahim, the son of the Messenger of Allah صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم wept and explained the proper balance: the eye weeps and the heart grieves, but we do not say anything that angers the Lord. This is a clear lesson in Islamic mourning. Tears are not denied. Sadness is not denied. But the tongue must stay safe. The hadith also mentions that death comes to all and that the latter will join the former. So the believer grieves, but does not speak in a way that displeases Allah. This is grief guided by faith."},"teachings":["The eye may weep and the heart may grieve.","A believer should avoid words that anger Allah during loss.","Death is described as something that comes to all.","The Prophet صلى الله عليه وسلم expressed sadness while staying within obedience."],"related_hadiths":[{"id":"1303","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5655","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1283","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E148" s="4" t="n"/>
@@ -3881,7 +3885,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet smiled at Jarir and made dua for him to be firm, guided, and a guide for others."},"heading":{"title":"Hadith About the Prophet's Dua for Jarir bin Abdullah","description":"This Hadith about the Prophet's dua for Jarir bin Abdullah shows personal kindness and prayer. Jarir says that after he became Muslim, the Messenger of Allah never refused to see him, and whenever he saw him, he smiled at him. Jarir then complained that he could not sit firmly on a horse. The Prophet placed his hand on his chest and prayed, \"O Allah, make him firm and cause him to guide others and be rightly-guided.\" The core topic is dua and kindness. The report does not turn this into a general rule for every problem; it simply shows how the Prophet responded to Jarir's difficulty with care, touch, and supplication."},"teachings":["The Prophet showed Jarir kindness by smiling at him.","Jarir shared a real personal difficulty with the Prophet.","The Prophet made dua for firmness, guidance, and being a guide.","The narration shows care for both practical ability and spiritual direction."],"related_hadiths":[{"id":"6089","book_id":"1","label":"Sahih Bukhari"},{"id":"154","book_id":"6","label":"Sunan Ibn Majah"},{"id":"160","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet smiled at Jarir and made dua for him to be firm, guided, and a guide for others."},"heading":{"title":"Hadith About the Prophet's Dua for Jarir bin Abdullah","description":"This Hadith about the Prophet's dua for Jarir bin Abdullah shows personal kindness and prayer. Jarir says that after he became Muslim, the Messenger of Allah never refused to see him, and whenever he saw him, he smiled at him. Jarir then complained that he could not sit firmly on a horse. The Prophet placed his hand on his chest and prayed, \"O Allah, make him firm and cause him to guide others and be rightly-guided.\" The core topic is dua and kindness. The report does not turn this into a general rule for every problem; it simply shows how the Prophet responded to Jarir's difficulty with care, touch, and supplication."},"teachings":["The Prophet showed Jarir kindness by smiling at him.","Jarir shared a real personal difficulty with the Prophet.","The Prophet made dua for firmness, guidance, and being a guide.","The narration shows care for both practical ability and spiritual direction."],"related_hadiths":[{"id":"6089","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"154","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"160","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E149" s="4" t="n"/>
@@ -3904,7 +3908,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Grief and Marital Love","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith recognizes the deep grief a woman may feel at the loss of her husband."},"heading":{"title":"Hadith About Grief and Love for a Husband","description":"This hadith about grief and love for a husband shows a very human moment. Hamnah bint Jahsh was told that her brother had been killed, and she responded with mercy for him and “Inna lillahi wa inna ilayhi raji’un.” When she was told that her husband had been killed, she said, “O grief!” The Messenger of Allah صلى الله عليه وسلم then said that a woman has a strong love for her husband which she does not have for anything else. The hadith does not blame her for feeling deeper grief. It recognizes the special emotional bond between husband and wife. The lesson is that Islam understands human feelings, while still guiding believers toward remembrance of Allah in loss."},"teachings":["The phrase “Inna lillahi wa inna ilayhi raji’un” is shown as a response to loss.","The hadith recognizes the deep love a wife may have for her husband.","Different losses may affect the heart in different ways.","Human grief is acknowledged in the Prophet’s صلى الله عليه وسلم words."],"related_hadiths":[{"id":"918b","book_id":"2","label":"Sahih Muslim"},{"id":"1283","book_id":"1","label":"Sahih Bukhari"},{"id":"1303","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Grief and Marital Love","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith recognizes the deep grief a woman may feel at the loss of her husband."},"heading":{"title":"Hadith About Grief and Love for a Husband","description":"This hadith about grief and love for a husband shows a very human moment. Hamnah bint Jahsh was told that her brother had been killed, and she responded with mercy for him and “Inna lillahi wa inna ilayhi raji’un.” When she was told that her husband had been killed, she said, “O grief!” The Messenger of Allah صلى الله عليه وسلم then said that a woman has a strong love for her husband which she does not have for anything else. The hadith does not blame her for feeling deeper grief. It recognizes the special emotional bond between husband and wife. The lesson is that Islam understands human feelings, while still guiding believers toward remembrance of Allah in loss."},"teachings":["The phrase “Inna lillahi wa inna ilayhi raji’un” is shown as a response to loss.","The hadith recognizes the deep love a wife may have for her husband.","Different losses may affect the heart in different ways.","Human grief is acknowledged in the Prophet’s صلى الله عليه وسلم words."],"related_hadiths":[{"id":"918b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1283","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1303","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E150" s="4" t="n"/>
@@ -3927,7 +3931,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Limits of Weeping","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows grief for Hamzah, then instructs the women to return home and stop weeping."},"heading":{"title":"Limits of Weeping in Mourning","description":"This hadith about the limits of weeping in mourning mentions women of Abdul-Ashhal weeping for their slain on the Day of Uhud. The Prophet صلى الله عليه وسلم said that Hamzah had no one to weep for him, so the women of the Ansar began weeping for Hamzah. Later, the Prophet صلى الله عليه وسلم woke up and asked why they had not gone home yet. He then instructed that they should go home and not weep for anyone who dies after that day. The text shows that grief happened, but it also shows a limit being placed on continuing it. The hadith teaches that mourning should not become an ongoing public practice beyond what is proper."},"teachings":["The hadith mentions weeping after loss, but also places limits on it.","The women were instructed to return home.","Mourning should not become an extended public display.","The Prophet صلى الله عليه وسلم guided people from grief toward restraint."],"related_hadiths":[{"id":"1303","book_id":"1","label":"Sahih Bukhari"},{"id":"1294","book_id":"1","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Limits of Weeping","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows grief for Hamzah, then instructs the women to return home and stop weeping."},"heading":{"title":"Limits of Weeping in Mourning","description":"This hadith about the limits of weeping in mourning mentions women of Abdul-Ashhal weeping for their slain on the Day of Uhud. The Prophet صلى الله عليه وسلم said that Hamzah had no one to weep for him, so the women of the Ansar began weeping for Hamzah. Later, the Prophet صلى الله عليه وسلم woke up and asked why they had not gone home yet. He then instructed that they should go home and not weep for anyone who dies after that day. The text shows that grief happened, but it also shows a limit being placed on continuing it. The hadith teaches that mourning should not become an ongoing public practice beyond what is proper."},"teachings":["The hadith mentions weeping after loss, but also places limits on it.","The women were instructed to return home.","Mourning should not become an extended public display.","The Prophet صلى الله عليه وسلم guided people from grief toward restraint."],"related_hadiths":[{"id":"1303","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1294","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E151" s="4" t="n"/>
@@ -3950,7 +3954,7 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forbidding Eulogies","description":"$book_name$ $hadith_number$ - $chapter_name$. This short hadith states that the Messenger of Allah forbade eulogies."},"heading":{"title":"Hadith About Eulogies in Islam","description":"This hadith about eulogies in Islam is short but direct. Ibn Abi Awfa narrated that the Messenger of Allah صلى الله عليه وسلم forbade eulogies. The text does not give a long explanation, so the safest understanding is to stay close to the words provided. It tells us that this kind of mourning speech was forbidden. Since the hadith is placed among narrations about grief, wailing, and mourning, the main point is connected to controlling how people speak about the dead. It warns against forms of public praise or lament that may cross the limits. A Muslim should speak carefully at times of death and avoid practices the Prophet صلى الله عليه وسلم forbade."},"teachings":["The Prophet صلى الله عليه وسلم forbade eulogies in this narration.","Speech about the dead should stay within Islamic limits.","Mourning should not become a display of excessive praise or lament.","A short hadith can still carry a clear practical warning."],"related_hadiths":[{"id":"1294","book_id":"1","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","label":"Sahih Muslim"},{"id":"1860","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forbidding Eulogies","description":"$book_name$ $hadith_number$ - $chapter_name$. This short hadith states that the Messenger of Allah forbade eulogies."},"heading":{"title":"Hadith About Eulogies in Islam","description":"This hadith about eulogies in Islam is short but direct. Ibn Abi Awfa narrated that the Messenger of Allah صلى الله عليه وسلم forbade eulogies. The text does not give a long explanation, so the safest understanding is to stay close to the words provided. It tells us that this kind of mourning speech was forbidden. Since the hadith is placed among narrations about grief, wailing, and mourning, the main point is connected to controlling how people speak about the dead. It warns against forms of public praise or lament that may cross the limits. A Muslim should speak carefully at times of death and avoid practices the Prophet صلى الله عليه وسلم forbade."},"teachings":["The Prophet صلى الله عليه وسلم forbade eulogies in this narration.","Speech about the dead should stay within Islamic limits.","Mourning should not become a display of excessive praise or lament.","A short hadith can still carry a clear practical warning."],"related_hadiths":[{"id":"1294","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"103a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1860","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E152" s="4" t="n"/>
@@ -3973,7 +3977,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Words of Wailing","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against exaggerated mourning words said over the deceased."},"heading":{"title":"Hadith About Words of Wailing","description":"This hadith about words of wailing gives examples of what people may say in excessive mourning: “O my strength,” “O he who clothed us,” “O my help,” and “O my rock.” The narration says the deceased is rebuked and asked whether he was really like that. The text then records a question about the verse that no bearer of burdens shall bear another’s burden, followed by the narrator’s firm response that he is reporting from the Messenger of Allah صلى الله عليه وسلم. The key lesson is to be careful with exaggerated cries over the dead. The hadith points to the danger of turning grief into loud claims and emotional slogans."},"teachings":["Exaggerated words of mourning are warned against in this narration.","The hadith gives examples of cries said over the deceased.","Grief should not lead to careless or inflated speech.","The narrator strongly defended the report he received from the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"1285","book_id":"1","label":"Sahih Bukhari"},{"id":"1292","book_id":"1","label":"Sahih Bukhari"},{"id":"927","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Words of Wailing","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against exaggerated mourning words said over the deceased."},"heading":{"title":"Hadith About Words of Wailing","description":"This hadith about words of wailing gives examples of what people may say in excessive mourning: “O my strength,” “O he who clothed us,” “O my help,” and “O my rock.” The narration says the deceased is rebuked and asked whether he was really like that. The text then records a question about the verse that no bearer of burdens shall bear another’s burden, followed by the narrator’s firm response that he is reporting from the Messenger of Allah صلى الله عليه وسلم. The key lesson is to be careful with exaggerated cries over the dead. The hadith points to the danger of turning grief into loud claims and emotional slogans."},"teachings":["Exaggerated words of mourning are warned against in this narration.","The hadith gives examples of cries said over the deceased.","Grief should not lead to careless or inflated speech.","The narrator strongly defended the report he received from the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"1285","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1292","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"927","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E153" s="4" t="n"/>
@@ -3996,7 +4000,7 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Weeping and Grave Punishment","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions a family weeping while the deceased woman was punished in her grave."},"heading":{"title":"Hadith About Weeping and Grave Punishment","description":"This hadith about weeping and grave punishment reports that a Jewish woman had died. The Prophet صلى الله عليه وسلم heard her family weeping over her and said that her family was weeping for her while she was being punished in her grave. The wording is specific. It mentions this woman, her family’s weeping, and her punishment in the grave. The hadith should not be used to deny every natural tear, especially because other narrations in this same set show the Prophet صلى الله عليه وسلم weeping. The safe lesson here is that death is serious, the grave is real, and people should not rely on the emotions of others after death. A person needs faith and deeds before meeting Allah."},"teachings":["The hadith reminds us that the grave is a serious stage after death.","Family weeping does not change the reality of a person’s condition after death.","The narration should be kept to its stated wording and setting.","A person should prepare for death before it arrives."],"related_hadiths":[{"id":"1285","book_id":"1","label":"Sahih Bukhari"},{"id":"1292","book_id":"1","label":"Sahih Bukhari"},{"id":"927","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Weeping and Grave Punishment","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions a family weeping while the deceased woman was punished in her grave."},"heading":{"title":"Hadith About Weeping and Grave Punishment","description":"This hadith about weeping and grave punishment reports that a Jewish woman had died. The Prophet صلى الله عليه وسلم heard her family weeping over her and said that her family was weeping for her while she was being punished in her grave. The wording is specific. It mentions this woman, her family’s weeping, and her punishment in the grave. The hadith should not be used to deny every natural tear, especially because other narrations in this same set show the Prophet صلى الله عليه وسلم weeping. The safe lesson here is that death is serious, the grave is real, and people should not rely on the emotions of others after death. A person needs faith and deeds before meeting Allah."},"teachings":["The hadith reminds us that the grave is a serious stage after death.","Family weeping does not change the reality of a person’s condition after death.","The narration should be kept to its stated wording and setting.","A person should prepare for death before it arrives."],"related_hadiths":[{"id":"1285","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1292","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"927","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E154" s="4" t="n"/>
@@ -4019,7 +4023,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fatimah and the Prophet’s Secret","description":"$book_name$ $hadith_number$ - $chapter_name$. Fatimah kept the Prophet’s secret, wept at his nearing death, and smiled at her honored rank among believing women."},"heading":{"title":"Hadith About Fatimah Keeping the Prophet’s Secret","description":"This Hadith about Fatimah highlights trust, family love, and the heavy news of the Prophet’s final illness. The main message is simple: Fatimah did not reveal the secret of the Messenger of Allah صلى الله عليه وسلم while he was alive, even when ‘Aishah asked her more than once. After his death, she explained that Jibra’il had reviewed the Qur’an with him twice that year, and the Prophet صلى الله عليه وسلم understood that his time was near. Fatimah wept because she heard that she would soon lose her father. She smiled because he gave her glad news that she would be the leader of the women of this Ummah. The Hadith teaches care with private words and love for the family of the Prophet صلى الله عليه وسلم."},"teachings":["A trusted person does not expose a private conversation without permission.","Sad news and happy news may come very close together in life.","The Prophet صلى الله عليه وسلم honored Fatimah with gentle words and glad tidings.","The review of the Qur’an with Jibra’il is mentioned as a sign connected to his nearing death."],"related_hadiths":[{"id":"1629","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1630","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1635","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fatimah and the Prophet’s Secret","description":"$book_name$ $hadith_number$ - $chapter_name$. Fatimah kept the Prophet’s secret, wept at his nearing death, and smiled at her honored rank among believing women."},"heading":{"title":"Hadith About Fatimah Keeping the Prophet’s Secret","description":"This Hadith about Fatimah highlights trust, family love, and the heavy news of the Prophet’s final illness. The main message is simple: Fatimah did not reveal the secret of the Messenger of Allah صلى الله عليه وسلم while he was alive, even when ‘Aishah asked her more than once. After his death, she explained that Jibra’il had reviewed the Qur’an with him twice that year, and the Prophet صلى الله عليه وسلم understood that his time was near. Fatimah wept because she heard that she would soon lose her father. She smiled because he gave her glad news that she would be the leader of the women of this Ummah. The Hadith teaches care with private words and love for the family of the Prophet صلى الله عليه وسلم."},"teachings":["A trusted person does not expose a private conversation without permission.","Sad news and happy news may come very close together in life.","The Prophet صلى الله عليه وسلم honored Fatimah with gentle words and glad tidings.","The review of the Qur’an with Jibra’il is mentioned as a sign connected to his nearing death."],"related_hadiths":[{"id":"1629","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1630","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1635","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E155" s="4" t="n"/>
@@ -4042,7 +4046,7 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Severe Pain","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah witnessed that no one suffered more pain than the Messenger of Allah, showing the hardship he bore."},"heading":{"title":"Hadith About the Prophet’s Pain in Illness","description":"This short Hadith about the Prophet’s pain shows how much suffering the Messenger of Allah صلى الله عليه وسلم went through during illness. ‘Aishah said she had never seen anyone suffer more pain than him. The wording is brief, but it carries a strong reminder: being beloved to Allah does not mean a person is untouched by pain. The Prophet صلى الله عليه وسلم faced severe pain, and this makes the experience of illness easier for believers to understand with patience. The Hadith does not give extra details here, so the lesson should stay close to the text. It simply tells us that the Prophet صلى الله عليه وسلم bore great physical hardship, and ‘Aishah saw it with her own eyes."},"teachings":["Great people may still face severe physical pain.","Illness is not a sign that someone is low in honor.","The Prophet صلى الله عليه وسلم experienced human pain in a real and visible way.","A short report can still carry a deep reminder about patience."],"related_hadiths":[{"id":"1623","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1629","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1630","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Severe Pain","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah witnessed that no one suffered more pain than the Messenger of Allah, showing the hardship he bore."},"heading":{"title":"Hadith About the Prophet’s Pain in Illness","description":"This short Hadith about the Prophet’s pain shows how much suffering the Messenger of Allah صلى الله عليه وسلم went through during illness. ‘Aishah said she had never seen anyone suffer more pain than him. The wording is brief, but it carries a strong reminder: being beloved to Allah does not mean a person is untouched by pain. The Prophet صلى الله عليه وسلم faced severe pain, and this makes the experience of illness easier for believers to understand with patience. The Hadith does not give extra details here, so the lesson should stay close to the text. It simply tells us that the Prophet صلى الله عليه وسلم bore great physical hardship, and ‘Aishah saw it with her own eyes."},"teachings":["Great people may still face severe physical pain.","Illness is not a sign that someone is low in honor.","The Prophet صلى الله عليه وسلم experienced human pain in a real and visible way.","A short report can still carry a deep reminder about patience."],"related_hadiths":[{"id":"1623","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1629","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1630","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E156" s="4" t="n"/>
@@ -4065,7 +4069,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Last Glance","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas saw the Prophet’s final glance on Monday while people prayed behind Abu Bakr."},"heading":{"title":"The Prophet’s Last Glance Before Death Hadith","description":"This Hadith about the Prophet’s last glance describes a moving moment seen by Anas bin Malik. On Monday, the Prophet صلى الله عليه وسلم drew back the curtain and looked at the people while they were praying behind Abu Bakr. Anas described his face as looking like a page of the Mushaf. Abu Bakr wanted to move, but the Prophet صلى الله عليه وسلم gestured for him to remain firm. Then the Prophet صلى الله عليه وسلم let the curtain fall, and he died at the end of that day. The Hadith keeps the focus on prayer, calm leadership, and the final public sight of the Messenger of Allah صلى الله عليه وسلم. It does not add a long speech; the gesture itself carried meaning."},"teachings":["The Prophet صلى الله عليه وسلم saw the community gathered in prayer near the end of his life.","Abu Bakr was leading the people in prayer in this report.","The Prophet صلى الله عليه وسلم gestured for Abu Bakr to stay in place.","Anas remembered the beauty and light of the Prophet’s face in that final glance."],"related_hadiths":[{"id":"1627","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1628","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1631","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Last Glance","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas saw the Prophet’s final glance on Monday while people prayed behind Abu Bakr."},"heading":{"title":"The Prophet’s Last Glance Before Death Hadith","description":"This Hadith about the Prophet’s last glance describes a moving moment seen by Anas bin Malik. On Monday, the Prophet صلى الله عليه وسلم drew back the curtain and looked at the people while they were praying behind Abu Bakr. Anas described his face as looking like a page of the Mushaf. Abu Bakr wanted to move, but the Prophet صلى الله عليه وسلم gestured for him to remain firm. Then the Prophet صلى الله عليه وسلم let the curtain fall, and he died at the end of that day. The Hadith keeps the focus on prayer, calm leadership, and the final public sight of the Messenger of Allah صلى الله عليه وسلم. It does not add a long speech; the gesture itself carried meaning."},"teachings":["The Prophet صلى الله عليه وسلم saw the community gathered in prayer near the end of his life.","Abu Bakr was leading the people in prayer in this report.","The Prophet صلى الله عليه وسلم gestured for Abu Bakr to stay in place.","Anas remembered the beauty and light of the Prophet’s face in that final glance."],"related_hadiths":[{"id":"1627","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1628","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1631","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E157" s="4" t="n"/>
@@ -4088,7 +4092,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer and Human Duty","description":"$book_name$ $hadith_number$ - $chapter_name$. In his final illness, the Prophet kept reminding people about prayer and those under their care."},"heading":{"title":"Hadith About Prayer in the Prophet’s Final Illness","description":"This Hadith about prayer records one of the last repeated concerns of the Messenger of Allah صلى الله عليه وسلم. During the illness in which he passed away, he kept saying: “The prayer, and those whom your hands possess.” The report shows that prayer remained a major matter in his final illness. It also shows care for people under authority and responsibility. The Hadith does not give a full legal discussion; it simply preserves the Prophet’s repeated words until his tongue could no longer utter them. That makes the reminder very direct. Salah is not a side matter, and people under one’s care should not be ignored, especially when someone has power over them."},"teachings":["Prayer was strongly emphasized during the Prophet’s final illness.","The Prophet صلى الله عليه وسلم reminded people about those under their care.","A short repeated reminder can show what matters deeply.","Responsibility toward people with less power is part of the message of this Hadith."],"related_hadiths":[{"id":"1634","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1624","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1627","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer and Human Duty","description":"$book_name$ $hadith_number$ - $chapter_name$. In his final illness, the Prophet kept reminding people about prayer and those under their care."},"heading":{"title":"Hadith About Prayer in the Prophet’s Final Illness","description":"This Hadith about prayer records one of the last repeated concerns of the Messenger of Allah صلى الله عليه وسلم. During the illness in which he passed away, he kept saying: “The prayer, and those whom your hands possess.” The report shows that prayer remained a major matter in his final illness. It also shows care for people under authority and responsibility. The Hadith does not give a full legal discussion; it simply preserves the Prophet’s repeated words until his tongue could no longer utter them. That makes the reminder very direct. Salah is not a side matter, and people under one’s care should not be ignored, especially when someone has power over them."},"teachings":["Prayer was strongly emphasized during the Prophet’s final illness.","The Prophet صلى الله عليه وسلم reminded people about those under their care.","A short repeated reminder can show what matters deeply.","Responsibility toward people with less power is part of the message of this Hadith."],"related_hadiths":[{"id":"1634","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1624","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1627","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E158" s="4" t="n"/>
@@ -4111,7 +4115,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aishah on Appointment Claim","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah questioned the claim that Ali was appointed, saying the Prophet died while resting in her lap."},"heading":{"title":"Hadith About Aishah and the Appointment Claim","description":"This Hadith discusses a claim mentioned in ‘Aishah’s presence: that ‘Ali had been appointed by the Prophet صلى الله عليه وسلم before his death. ‘Aishah responded by asking when that appointment happened. She described that the Prophet صلى الله عليه وسلم had been resting against her chest or in her lap, called for a basin, then became limp in her lap and died, while she did not even realize it at first. Her question was based on what she personally witnessed in his final moments. The Hadith should be read closely and not stretched beyond its wording. Its main point is her report about the Prophet’s passing and her challenge to a specific claim she heard."},"teachings":["Aishah answered a claim by referring to what she personally witnessed.","The Prophet صلى الله عليه وسلم passed away while close to Aishah in this report.","The Hadith warns against speaking with certainty about events without clear evidence.","The text focuses on the final moment, not a full political discussion."],"related_hadiths":[{"id":"1627","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1628","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1624","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aishah on Appointment Claim","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah questioned the claim that Ali was appointed, saying the Prophet died while resting in her lap."},"heading":{"title":"Hadith About Aishah and the Appointment Claim","description":"This Hadith discusses a claim mentioned in ‘Aishah’s presence: that ‘Ali had been appointed by the Prophet صلى الله عليه وسلم before his death. ‘Aishah responded by asking when that appointment happened. She described that the Prophet صلى الله عليه وسلم had been resting against her chest or in her lap, called for a basin, then became limp in her lap and died, while she did not even realize it at first. Her question was based on what she personally witnessed in his final moments. The Hadith should be read closely and not stretched beyond its wording. Its main point is her report about the Prophet’s passing and her challenge to a specific claim she heard."},"teachings":["Aishah answered a claim by referring to what she personally witnessed.","The Prophet صلى الله عليه وسلم passed away while close to Aishah in this report.","The Hadith warns against speaking with certainty about events without clear evidence.","The text focuses on the final moment, not a full political discussion."],"related_hadiths":[{"id":"1627","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1628","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1624","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E159" s="4" t="n"/>
@@ -4134,7 +4138,7 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr and Tawhid","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr reminded the people that Allah lives and never dies, while Muhammad had passed away."},"heading":{"title":"Hadith About Abu Bakr After the Prophet’s Death","description":"This Hadith about Abu Bakr after the Prophet’s death records a moment of shock and clarity. Some people said the Prophet صلى الله عليه وسلم had not died. Abu Bakr came, uncovered his face, kissed him between the eyes, and stated that the Messenger of Allah صلى الله عليه وسلم had indeed died. Then he stood before the people and reminded them: whoever worshiped Allah, Allah is alive and never dies; whoever worshiped Muhammad, Muhammad had died. He also recited the verse that Muhammad صلى الله عليه وسلم was a Messenger and that messengers had passed before him. The core teaching is firm Tawhid during grief. Love for the Prophet صلى الله عليه وسلم must remain tied to worship of Allah alone."},"teachings":["Deep grief should not make a person lose the truth of Tawhid.","Abu Bakr faced the painful reality with clear words.","The Prophet صلى الله عليه وسلم was honored, yet still a human Messenger who died.","Qur’an was used to steady the community at a moment of shock."],"related_hadiths":[{"id":"1628","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1631","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1635","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr and Tawhid","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr reminded the people that Allah lives and never dies, while Muhammad had passed away."},"heading":{"title":"Hadith About Abu Bakr After the Prophet’s Death","description":"This Hadith about Abu Bakr after the Prophet’s death records a moment of shock and clarity. Some people said the Prophet صلى الله عليه وسلم had not died. Abu Bakr came, uncovered his face, kissed him between the eyes, and stated that the Messenger of Allah صلى الله عليه وسلم had indeed died. Then he stood before the people and reminded them: whoever worshiped Allah, Allah is alive and never dies; whoever worshiped Muhammad, Muhammad had died. He also recited the verse that Muhammad صلى الله عليه وسلم was a Messenger and that messengers had passed before him. The core teaching is firm Tawhid during grief. Love for the Prophet صلى الله عليه وسلم must remain tied to worship of Allah alone."},"teachings":["Deep grief should not make a person lose the truth of Tawhid.","Abu Bakr faced the painful reality with clear words.","The Prophet صلى الله عليه وسلم was honored, yet still a human Messenger who died.","Qur’an was used to steady the community at a moment of shock."],"related_hadiths":[{"id":"1628","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1631","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1635","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E160" s="4" t="n"/>
@@ -4157,7 +4161,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Burial of the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. The Companions buried the Prophet where he died after groups offered the funeral prayer over him."},"heading":{"title":"Hadith About the Burial Place of the Prophet","description":"This Hadith about the burial of the Prophet صلى الله عليه وسلم gives several details from the time after his passing. The Companions sent for those who knew how to dig graves. Abu Talhah was found, and a grave with a niche was dug. People entered in groups and offered the funeral prayer over the Messenger of Allah صلى الله عليه وسلم, followed by women and then children, and no single person led them in that prayer. When the Muslims differed about the burial place, Abu Bakr reported that no Prophet passed away except that he was buried where he died. So the bed was lifted and the grave was dug in that place. The report stays focused on burial, prayer, and careful respect."},"teachings":["The Companions sought what was best when preparing the Prophet’s grave.","People offered funeral prayer over him in groups.","Abu Bakr used a heard statement to settle the burial-place question.","The Prophet صلى الله عليه وسلم was buried where he passed away, according to this report."],"related_hadiths":[{"id":"1627","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1630","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1631","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Burial of the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. The Companions buried the Prophet where he died after groups offered the funeral prayer over him."},"heading":{"title":"Hadith About the Burial Place of the Prophet","description":"This Hadith about the burial of the Prophet صلى الله عليه وسلم gives several details from the time after his passing. The Companions sent for those who knew how to dig graves. Abu Talhah was found, and a grave with a niche was dug. People entered in groups and offered the funeral prayer over the Messenger of Allah صلى الله عليه وسلم, followed by women and then children, and no single person led them in that prayer. When the Muslims differed about the burial place, Abu Bakr reported that no Prophet passed away except that he was buried where he died. So the bed was lifted and the grave was dug in that place. The report stays focused on burial, prayer, and careful respect."},"teachings":["The Companions sought what was best when preparing the Prophet’s grave.","People offered funeral prayer over him in groups.","Abu Bakr used a heard statement to settle the burial-place question.","The Prophet صلى الله عليه وسلم was buried where he passed away, according to this report."],"related_hadiths":[{"id":"1627","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1630","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1631","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E161" s="4" t="n"/>
@@ -4180,7 +4184,7 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Death Is Unavoidable","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet comforted Fatimah and reminded her that death is something no one can avoid."},"heading":{"title":"Hadith About Death Everyone Will Encounter","description":"This Hadith about death records Fatimah’s grief when she saw the Messenger of Allah صلى الله عليه وسلم suffering the agonies of death. She cried out because of the severity of his pain. The Prophet صلى الله عليه وسلم answered her with words of comfort: after that day, her father would suffer no more agony. Then he stated that what had come to him was something no one can avoid, the death that everyone will encounter until the Day of Resurrection. The Hadith speaks plainly. It does not hide the pain of death, but it also points to an end to worldly suffering for the Prophet صلى الله عليه وسلم. It reminds every reader that death is certain and should be faced with faith."},"teachings":["Death is a reality that no one can avoid.","The Prophet صلى الله عليه وسلم comforted Fatimah while he himself was in pain.","Worldly agony ended for the Prophet صلى الله عليه وسلم after that day.","Grief is shown in the report, but it is answered with a clear reminder."],"related_hadiths":[{"id":"1623","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1630","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1622","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Death Is Unavoidable","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet comforted Fatimah and reminded her that death is something no one can avoid."},"heading":{"title":"Hadith About Death Everyone Will Encounter","description":"This Hadith about death records Fatimah’s grief when she saw the Messenger of Allah صلى الله عليه وسلم suffering the agonies of death. She cried out because of the severity of his pain. The Prophet صلى الله عليه وسلم answered her with words of comfort: after that day, her father would suffer no more agony. Then he stated that what had come to him was something no one can avoid, the death that everyone will encounter until the Day of Resurrection. The Hadith speaks plainly. It does not hide the pain of death, but it also points to an end to worldly suffering for the Prophet صلى الله عليه وسلم. It reminds every reader that death is certain and should be faced with faith."},"teachings":["Death is a reality that no one can avoid.","The Prophet صلى الله عليه وسلم comforted Fatimah while he himself was in pain.","Worldly agony ended for the Prophet صلى الله عليه وسلم after that day.","Grief is shown in the report, but it is answered with a clear reminder."],"related_hadiths":[{"id":"1623","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1630","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1622","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E162" s="4" t="n"/>
@@ -4203,7 +4207,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Grief of Fatimah","description":"$book_name$ $hadith_number$ - $chapter_name$. Fatimah expressed deep grief after the Prophet passed away, remembering his closeness to Allah."},"heading":{"title":"Hadith About Fatimah’s Grief After the Prophet’s Death","description":"This Hadith about Fatimah’s grief shows how heavy the burial of the Messenger of Allah صلى الله عليه وسلم felt to those who loved him. Fatimah asked Anas how they were able to scatter dust over the Messenger of Allah صلى الله عليه وسلم. Another narration in the same report records her words after his death: she spoke of announcing his death to Jibra’il, his nearness to his Lord, Firdaws as his abode, and his answer to the call of his Lord. The narrator Thabit wept when narrating it. The Hadith teaches that love and grief can be real and visible. At the same time, Fatimah’s words point to the honor of the Prophet صلى الله عليه وسلم with his Lord."},"teachings":["Grief for the Prophet صلى الله عليه وسلم was deeply felt by his family and Companions.","Fatimah’s words show sadness together with belief in his honored return to Allah.","Remembering the Hereafter can sit beside tears in a moment of loss.","The narrator’s weeping shows the report carried strong emotion for later listeners too."],"related_hadiths":[{"id":"1629","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1631","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1628","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Grief of Fatimah","description":"$book_name$ $hadith_number$ - $chapter_name$. Fatimah expressed deep grief after the Prophet passed away, remembering his closeness to Allah."},"heading":{"title":"Hadith About Fatimah’s Grief After the Prophet’s Death","description":"This Hadith about Fatimah’s grief shows how heavy the burial of the Messenger of Allah صلى الله عليه وسلم felt to those who loved him. Fatimah asked Anas how they were able to scatter dust over the Messenger of Allah صلى الله عليه وسلم. Another narration in the same report records her words after his death: she spoke of announcing his death to Jibra’il, his nearness to his Lord, Firdaws as his abode, and his answer to the call of his Lord. The narrator Thabit wept when narrating it. The Hadith teaches that love and grief can be real and visible. At the same time, Fatimah’s words point to the honor of the Prophet صلى الله عليه وسلم with his Lord."},"teachings":["Grief for the Prophet صلى الله عليه وسلم was deeply felt by his family and Companions.","Fatimah’s words show sadness together with belief in his honored return to Allah.","Remembering the Hereafter can sit beside tears in a moment of loss.","The narrator’s weeping shows the report carried strong emotion for later listeners too."],"related_hadiths":[{"id":"1629","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1631","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1628","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E163" s="4" t="n"/>
@@ -4226,7 +4230,7 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Madinah’s Grief","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas described Madinah as bright when the Prophet entered and dark when he died."},"heading":{"title":"Hadith About Madinah After the Prophet’s Death","description":"This Hadith about Madinah after the Prophet’s death shares Anas’s memory of two opposite days. When the Messenger of Allah صلى الله عليه وسلم entered Al-Madinah, everything was lit up. When he died, everything seemed dark. Anas also said that as soon as they had dusted off their hands after burying him, they felt that their hearts had changed. The wording is emotional and personal. It shows how the Prophet’s presence shaped the hearts of the Companions and how his passing affected them deeply. The Hadith does not give a legal ruling. It gives a witness statement about loss, love, and the felt change after burying the Messenger of Allah صلى الله عليه وسلم."},"teachings":["The Prophet’s arrival brought great joy to Madinah in Anas’s memory.","His death brought deep sadness to the Companions.","The Companions felt a change in their hearts after his burial.","Love for the Prophet صلى الله عليه وسلم can be expressed through sincere grief."],"related_hadiths":[{"id":"1630","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1628","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1635","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Madinah’s Grief","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas described Madinah as bright when the Prophet entered and dark when he died."},"heading":{"title":"Hadith About Madinah After the Prophet’s Death","description":"This Hadith about Madinah after the Prophet’s death shares Anas’s memory of two opposite days. When the Messenger of Allah صلى الله عليه وسلم entered Al-Madinah, everything was lit up. When he died, everything seemed dark. Anas also said that as soon as they had dusted off their hands after burying him, they felt that their hearts had changed. The wording is emotional and personal. It shows how the Prophet’s presence shaped the hearts of the Companions and how his passing affected them deeply. The Hadith does not give a legal ruling. It gives a witness statement about loss, love, and the felt change after burying the Messenger of Allah صلى الله عليه وسلم."},"teachings":["The Prophet’s arrival brought great joy to Madinah in Anas’s memory.","His death brought deep sadness to the Companions.","The Companions felt a change in their hearts after his burial.","Love for the Prophet صلى الله عليه وسلم can be expressed through sincere grief."],"related_hadiths":[{"id":"1630","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1628","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1635","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E164" s="4" t="n"/>
@@ -4249,7 +4253,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Careful Speech","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar said they were guarded in speech during the Prophet’s lifetime, fearing revelation about them."},"heading":{"title":"Hadith About Guarded Speech in the Prophet’s Time","description":"This Hadith about guarded speech records a statement from Ibn ‘Umar. He said that during the lifetime of the Messenger of Allah صلى الله عليه وسلم, they were careful in speech and openness even with their wives, because they feared that Qur’an might be revealed about them. After the Prophet صلى الله عليه وسلم died, they began to speak freely. The report shows the strong sense of watchfulness that some Companions felt while revelation was still coming down. It should not be turned into a broad claim about all speech in every setting. The text simply contrasts their caution during the Prophet’s lifetime with their later freedom in speaking."},"teachings":["The Companions felt strong caution while revelation was being sent down.","Speech was treated seriously, even in private family life.","After the Prophet صلى الله عليه وسلم died, the situation changed because revelation had ceased.","The Hadith reminds a person to think before speaking."],"related_hadiths":[{"id":"1635","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1633","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1634","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Careful Speech","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar said they were guarded in speech during the Prophet’s lifetime, fearing revelation about them."},"heading":{"title":"Hadith About Guarded Speech in the Prophet’s Time","description":"This Hadith about guarded speech records a statement from Ibn ‘Umar. He said that during the lifetime of the Messenger of Allah صلى الله عليه وسلم, they were careful in speech and openness even with their wives, because they feared that Qur’an might be revealed about them. After the Prophet صلى الله عليه وسلم died, they began to speak freely. The report shows the strong sense of watchfulness that some Companions felt while revelation was still coming down. It should not be turned into a broad claim about all speech in every setting. The text simply contrasts their caution during the Prophet’s lifetime with their later freedom in speaking."},"teachings":["The Companions felt strong caution while revelation was being sent down.","Speech was treated seriously, even in private family life.","After the Prophet صلى الله عليه وسلم died, the situation changed because revelation had ceased.","The Hadith reminds a person to think before speaking."],"related_hadiths":[{"id":"1635","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1633","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1634","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E165" s="4" t="n"/>
@@ -4272,7 +4276,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Unity of Focus","description":"$book_name$ $hadith_number$ - $chapter_name$. Ubayy said the Companions had one focus with the Prophet, then looked in different directions after his death."},"heading":{"title":"Hadith About One Focus With the Prophet","description":"This Hadith about one focus with the Prophet صلى الله عليه وسلم comes from Ubayy bin Ka’b. He said that when they were with the Messenger of Allah صلى الله عليه وسلم, their direction was one. After he passed away, they started to look here and there, meaning their interests became different. The report is short but clear. It describes how the Prophet’s living presence gathered the community around one focus. After his death, the Companions faced new situations and different concerns. The Hadith should not be read as a detailed blame of every person. It is a simple reflection on how much the Prophet صلى الله عليه وسلم centered their hearts and attention."},"teachings":["The Prophet صلى الله عليه وسلم united the focus of his Companions.","After his death, new concerns and different interests appeared.","A strong leader can gather hearts around one direction.","The report reminds believers to seek steadiness after loss."],"related_hadiths":[{"id":"1632","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1634","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1631","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Unity of Focus","description":"$book_name$ $hadith_number$ - $chapter_name$. Ubayy said the Companions had one focus with the Prophet, then looked in different directions after his death."},"heading":{"title":"Hadith About One Focus With the Prophet","description":"This Hadith about one focus with the Prophet صلى الله عليه وسلم comes from Ubayy bin Ka’b. He said that when they were with the Messenger of Allah صلى الله عليه وسلم, their direction was one. After he passed away, they started to look here and there, meaning their interests became different. The report is short but clear. It describes how the Prophet’s living presence gathered the community around one focus. After his death, the Companions faced new situations and different concerns. The Hadith should not be read as a detailed blame of every person. It is a simple reflection on how much the Prophet صلى الله عليه وسلم centered their hearts and attention."},"teachings":["The Prophet صلى الله عليه وسلم united the focus of his Companions.","After his death, new concerns and different interests appeared.","A strong leader can gather hearts around one direction.","The report reminds believers to seek steadiness after loss."],"related_hadiths":[{"id":"1632","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1634","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1631","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E166" s="4" t="n"/>
@@ -4295,7 +4299,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Focus","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Salamah described how people’s gaze in prayer changed over time and during fitnah."},"heading":{"title":"Hadith About Looking in Prayer and Fitnah","description":"This Hadith about looking in prayer records Umm Salamah’s description of a change over time. In the time of the Messenger of Allah صلى الله عليه وسلم, a person’s gaze in prayer would not go beyond his feet. After the Prophet صلى الله عليه وسلم died, the gaze would not go beyond the place of prostration. After Abu Bakr died and ‘Umar was caliph, the gaze would not go beyond the Qiblah. Then in the time of ‘Uthman, when fitnah occurred, people began to look right and left. The Hadith links prayer focus with the state of people’s hearts and times. It should be explained carefully as a report of what she observed, not as a full ruling by itself."},"teachings":["Focus in prayer was described as stronger in earlier times.","Umm Salamah connected looking around with fitnah and change.","Prayer can show what is happening inside people’s hearts.","The report warns against distraction during salah."],"related_hadiths":[{"id":"1633","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1632","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1625","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Focus","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Salamah described how people’s gaze in prayer changed over time and during fitnah."},"heading":{"title":"Hadith About Looking in Prayer and Fitnah","description":"This Hadith about looking in prayer records Umm Salamah’s description of a change over time. In the time of the Messenger of Allah صلى الله عليه وسلم, a person’s gaze in prayer would not go beyond his feet. After the Prophet صلى الله عليه وسلم died, the gaze would not go beyond the place of prostration. After Abu Bakr died and ‘Umar was caliph, the gaze would not go beyond the Qiblah. Then in the time of ‘Uthman, when fitnah occurred, people began to look right and left. The Hadith links prayer focus with the state of people’s hearts and times. It should be explained carefully as a report of what she observed, not as a full ruling by itself."},"teachings":["Focus in prayer was described as stronger in earlier times.","Umm Salamah connected looking around with fitnah and change.","Prayer can show what is happening inside people’s hearts.","The report warns against distraction during salah."],"related_hadiths":[{"id":"1633","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1632","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1625","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E167" s="4" t="n"/>
@@ -4318,7 +4322,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Cessation of Revelation","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Ayman wept because revelation from heaven had ceased after the Prophet’s death."},"heading":{"title":"Hadith About Umm Ayman and the End of Revelation","description":"This Hadith about Umm Ayman shows the grief of the Companions after the Messenger of Allah صلى الله عليه وسلم passed away. Abu Bakr asked ‘Umar to visit Umm Ayman as the Prophet صلى الله عليه وسلم used to visit her. When they arrived, she wept. They reminded her that what is with Allah is better for His Messenger. She agreed, but explained that she was crying because revelation from heaven had ceased. Her words moved Abu Bakr and ‘Umar to tears as well. The Hadith teaches that their sadness was not only personal. They were also grieving the end of direct revelation. It is a gentle scene of visiting, remembering the Prophet صلى الله عليه وسلم, and sharing tears."},"teachings":["The Companions kept the Prophet’s habit of visiting Umm Ayman.","Umm Ayman knew Allah’s reward for His Messenger was better.","Her grief was tied to the end of revelation from heaven.","Shared tears can come from faith and love, not only from personal loss."],"related_hadiths":[{"id":"1631","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1632","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1627","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Cessation of Revelation","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Ayman wept because revelation from heaven had ceased after the Prophet’s death."},"heading":{"title":"Hadith About Umm Ayman and the End of Revelation","description":"This Hadith about Umm Ayman shows the grief of the Companions after the Messenger of Allah صلى الله عليه وسلم passed away. Abu Bakr asked ‘Umar to visit Umm Ayman as the Prophet صلى الله عليه وسلم used to visit her. When they arrived, she wept. They reminded her that what is with Allah is better for His Messenger. She agreed, but explained that she was crying because revelation from heaven had ceased. Her words moved Abu Bakr and ‘Umar to tears as well. The Hadith teaches that their sadness was not only personal. They were also grieving the end of direct revelation. It is a gentle scene of visiting, remembering the Prophet صلى الله عليه وسلم, and sharing tears."},"teachings":["The Companions kept the Prophet’s habit of visiting Umm Ayman.","Umm Ayman knew Allah’s reward for His Messenger was better.","Her grief was tied to the end of revelation from heaven.","Shared tears can come from faith and love, not only from personal loss."],"related_hadiths":[{"id":"1631","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1632","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1627","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E168" s="4" t="n"/>
@@ -4341,7 +4345,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blessings on Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that Friday is among the best days and urged many blessings upon him that day."},"heading":{"title":"Hadith About Sending Blessings on Friday","description":"This Hadith about sending blessings on Friday teaches a clear practice. The Messenger of Allah صلى الله عليه وسلم said that Friday is among the best of days. He mentioned that Adam was created on it, and that the Nafakhah and the swooning will occur on it. Then he told people to send a great deal of blessing upon him on that day, because their blessings are presented to him. When a man asked how that would happen after his body had decayed, the Prophet صلى الله عليه وسلم answered that Allah has forbidden the earth to consume the bodies of the Prophets. The main teaching is simple: increase salawat on Friday and believe what the Prophet صلى الله عليه وسلم stated about the Prophets’ bodies."},"teachings":["Friday has a special rank in this Hadith.","The Prophet صلى الله عليه وسلم asked believers to send many blessings upon him on Friday.","The blessings are presented to him, according to the text.","The earth does not consume the bodies of the Prophets, as stated in the Hadith."],"related_hadiths":[{"id":"1637","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1621","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1627","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blessings on Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that Friday is among the best days and urged many blessings upon him that day."},"heading":{"title":"Hadith About Sending Blessings on Friday","description":"This Hadith about sending blessings on Friday teaches a clear practice. The Messenger of Allah صلى الله عليه وسلم said that Friday is among the best of days. He mentioned that Adam was created on it, and that the Nafakhah and the swooning will occur on it. Then he told people to send a great deal of blessing upon him on that day, because their blessings are presented to him. When a man asked how that would happen after his body had decayed, the Prophet صلى الله عليه وسلم answered that Allah has forbidden the earth to consume the bodies of the Prophets. The main teaching is simple: increase salawat on Friday and believe what the Prophet صلى الله عليه وسلم stated about the Prophets’ bodies."},"teachings":["Friday has a special rank in this Hadith.","The Prophet صلى الله عليه وسلم asked believers to send many blessings upon him on Friday.","The blessings are presented to him, according to the text.","The earth does not consume the bodies of the Prophets, as stated in the Hadith."],"related_hadiths":[{"id":"1637","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1621","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1627","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E169" s="4" t="n"/>
@@ -4364,7 +4368,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Salawat on Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said blessings sent upon him on Friday are witnessed by angels and presented to him."},"heading":{"title":"Hadith About Salawat on Friday Witnessed by Angels","description":"This Hadith about salawat on Friday is close in meaning to another report in this batch, but it gives a special detail: Friday is witnessed by the angels. The Messenger of Allah صلى الله عليه وسلم told people to send a great deal of blessing upon him on Fridays. He said no one sends blessing upon him except that it is presented to him until the person finishes. When asked whether this also happens after death, he said yes. He then stated that Allah has forbidden the earth to consume the bodies of the Prophets, and the report says that the Prophet of Allah is alive and receives provision. The Hadith encourages frequent salawat with special attention to Friday."},"teachings":["Send many blessings upon the Prophet صلى الله عليه وسلم on Friday.","The Hadith says Friday is witnessed by angels.","Blessings sent upon him are presented to him until the person finishes.","The report affirms that the earth does not consume the bodies of the Prophets."],"related_hadiths":[{"id":"1636","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1627","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1635","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Salawat on Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said blessings sent upon him on Friday are witnessed by angels and presented to him."},"heading":{"title":"Hadith About Salawat on Friday Witnessed by Angels","description":"This Hadith about salawat on Friday is close in meaning to another report in this batch, but it gives a special detail: Friday is witnessed by the angels. The Messenger of Allah صلى الله عليه وسلم told people to send a great deal of blessing upon him on Fridays. He said no one sends blessing upon him except that it is presented to him until the person finishes. When asked whether this also happens after death, he said yes. He then stated that Allah has forbidden the earth to consume the bodies of the Prophets, and the report says that the Prophet of Allah is alive and receives provision. The Hadith encourages frequent salawat with special attention to Friday."},"teachings":["Send many blessings upon the Prophet صلى الله عليه وسلم on Friday.","The Hadith says Friday is witnessed by angels.","Blessings sent upon him are presented to him until the person finishes.","The report affirms that the earth does not consume the bodies of the Prophets."],"related_hadiths":[{"id":"1636","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1627","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1635","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E170" s="4" t="n"/>
@@ -4387,7 +4391,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward of Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah says fasting is for Him and He rewards it, while the fasting person has two joys."},"heading":{"title":"Hadith About Fasting Is for Allah","description":"This Hadith about fasting is for Allah explains the special honor of fasting. The Messenger of Allah صلى الله عليه وسلم said every good deed is multiplied, from ten times up to seven hundred times or as much as Allah wills. Then Allah says that fasting is different: “Fasting is for Me and I shall reward for it.” The reason given in the text is that the fasting person gives up desire and food for Allah’s sake. The Hadith also mentions two joys: one when the person breaks the fast and another when meeting the Lord. It even says the smell from the fasting person’s mouth is better before Allah than musk. The focus is sincerity, restraint, and hope in Allah’s reward."},"teachings":["Fasting has a special place among good deeds.","The fasting person gives up food and desire for Allah’s sake.","The Hadith mentions joy at iftar and joy when meeting Allah.","The smell from the fasting person’s mouth is honored before Allah in this report."],"related_hadiths":[{"id":"1639","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1640","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1746","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward of Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah says fasting is for Him and He rewards it, while the fasting person has two joys."},"heading":{"title":"Hadith About Fasting Is for Allah","description":"This Hadith about fasting is for Allah explains the special honor of fasting. The Messenger of Allah صلى الله عليه وسلم said every good deed is multiplied, from ten times up to seven hundred times or as much as Allah wills. Then Allah says that fasting is different: “Fasting is for Me and I shall reward for it.” The reason given in the text is that the fasting person gives up desire and food for Allah’s sake. The Hadith also mentions two joys: one when the person breaks the fast and another when meeting the Lord. It even says the smell from the fasting person’s mouth is better before Allah than musk. The focus is sincerity, restraint, and hope in Allah’s reward."},"teachings":["Fasting has a special place among good deeds.","The fasting person gives up food and desire for Allah’s sake.","The Hadith mentions joy at iftar and joy when meeting Allah.","The smell from the fasting person’s mouth is honored before Allah in this report."],"related_hadiths":[{"id":"1639","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1640","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1746","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E171" s="4" t="n"/>
@@ -4410,7 +4414,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fasting as a Shield","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet described fasting as a shield against the Fire, like a shield in battle."},"heading":{"title":"Hadith About Fasting as a Shield From the Fire","description":"This Hadith about fasting as a shield comes through a simple scene. ‘Uthman bin Abul-‘As offered Mutarrif milk, but Mutarrif said he was fasting. ‘Uthman then mentioned that he heard the Messenger of Allah صلى الله عليه وسلم say: “Fasting is a shield against the Fire just like the shield of anyone of you against fighting.” The image is easy to understand. A shield protects a person in battle, and fasting is described here as a shield against the Fire. The Hadith does not list every detail of how to fast. It focuses on the protective value of fasting and connects a daily act of worship to safety in the Hereafter."},"teachings":["Fasting is described as a shield against the Fire.","The comparison to a battle shield makes the teaching easy to picture.","Mutarrif’s fasting became the reason this reminder was mentioned.","The Hadith points to fasting as a serious act, not only leaving food."],"related_hadiths":[{"id":"1638","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1640","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1690","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fasting as a Shield","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet described fasting as a shield against the Fire, like a shield in battle."},"heading":{"title":"Hadith About Fasting as a Shield From the Fire","description":"This Hadith about fasting as a shield comes through a simple scene. ‘Uthman bin Abul-‘As offered Mutarrif milk, but Mutarrif said he was fasting. ‘Uthman then mentioned that he heard the Messenger of Allah صلى الله عليه وسلم say: “Fasting is a shield against the Fire just like the shield of anyone of you against fighting.” The image is easy to understand. A shield protects a person in battle, and fasting is described here as a shield against the Fire. The Hadith does not list every detail of how to fast. It focuses on the protective value of fasting and connects a daily act of worship to safety in the Hereafter."},"teachings":["Fasting is described as a shield against the Fire.","The comparison to a battle shield makes the teaching easy to picture.","Mutarrif’s fasting became the reason this reminder was mentioned.","The Hadith points to fasting as a serious act, not only leaving food."],"related_hadiths":[{"id":"1638","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1640","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1690","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E172" s="4" t="n"/>
@@ -4433,7 +4437,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gate of Rayyan","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said Paradise has a gate called Rayyan for those who used to fast."},"heading":{"title":"Hadith About Gate of Rayyan for Fasting People","description":"This Hadith about the gate of Rayyan gives glad news to those who used to fast. The Prophet صلى الله عليه وسلم said that in Paradise there is a gate called Rayyan. On the Day of Resurrection, a call will be made: “Where are those who used to fast?” Whoever is among them will enter it, and whoever enters it will never experience thirst again. The text is direct and hopeful. It does not name every type of fasting or every condition in this short report. It simply links the people of fasting with a special gate in Paradise and lasting relief from thirst. That makes the Hadith a strong reminder to value fasting with sincerity and consistency."},"teachings":["Paradise has a gate called Rayyan, according to this Hadith.","The call on the Day of Resurrection will be for those who used to fast.","Those who enter Rayyan will never experience thirst again.","The Hadith gives hope while keeping the focus on fasting."],"related_hadiths":[{"id":"1638","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1639","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1746","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gate of Rayyan","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said Paradise has a gate called Rayyan for those who used to fast."},"heading":{"title":"Hadith About Gate of Rayyan for Fasting People","description":"This Hadith about the gate of Rayyan gives glad news to those who used to fast. The Prophet صلى الله عليه وسلم said that in Paradise there is a gate called Rayyan. On the Day of Resurrection, a call will be made: “Where are those who used to fast?” Whoever is among them will enter it, and whoever enters it will never experience thirst again. The text is direct and hopeful. It does not name every type of fasting or every condition in this short report. It simply links the people of fasting with a special gate in Paradise and lasting relief from thirst. That makes the Hadith a strong reminder to value fasting with sincerity and consistency."},"teachings":["Paradise has a gate called Rayyan, according to this Hadith.","The call on the Day of Resurrection will be for those who used to fast.","Those who enter Rayyan will never experience thirst again.","The Hadith gives hope while keeping the focus on fasting."],"related_hadiths":[{"id":"1638","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1639","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1746","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E173" s="4" t="n"/>
@@ -4456,7 +4460,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Cupping While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn what this Hadith says about cupping during Ramadan and its link to breaking the fast."},"heading":{"title":"Cupping While Fasting: A Clear Hadith on Ramadan","description":"This Hadith focuses on cupping while fasting in Ramadan. Shaddad bin Aws was walking with the Messenger of Allah صلى الله عليه وسلم in Al-Baqi’ when they passed a man who was being cupped after eighteen nights of the month had passed. The Prophet صلى الله عليه وسلم then said that both the cupper and the one being cupped had broken their fast. The main lesson is that fasting is not only about staying away from food and drink; certain actions may also affect the fast. The Hadith gives a direct warning about this act in that situation. Anyone searching for a hadith about cupping while fasting will find this narration important because it gives a clear statement tied to Ramadan fasting."},"teachings":["Cupping during fasting is treated seriously in this narration.","The Hadith mentions both the cupper and the one being cupped.","Fasting requires care with actions beyond eating and drinking.","The event took place during Ramadan after eighteen nights had passed."],"related_hadiths":[{"id":"1682","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1691","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Cupping While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn what this Hadith says about cupping during Ramadan and its link to breaking the fast."},"heading":{"title":"Cupping While Fasting: A Clear Hadith on Ramadan","description":"This Hadith focuses on cupping while fasting in Ramadan. Shaddad bin Aws was walking with the Messenger of Allah صلى الله عليه وسلم in Al-Baqi’ when they passed a man who was being cupped after eighteen nights of the month had passed. The Prophet صلى الله عليه وسلم then said that both the cupper and the one being cupped had broken their fast. The main lesson is that fasting is not only about staying away from food and drink; certain actions may also affect the fast. The Hadith gives a direct warning about this act in that situation. Anyone searching for a hadith about cupping while fasting will find this narration important because it gives a clear statement tied to Ramadan fasting."},"teachings":["Cupping during fasting is treated seriously in this narration.","The Hadith mentions both the cupper and the one being cupped.","Fasting requires care with actions beyond eating and drinking.","The event took place during Ramadan after eighteen nights had passed."],"related_hadiths":[{"id":"1682","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1691","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E174" s="4" t="n"/>
@@ -4479,7 +4483,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Kissing During Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah رضي الله عنها reports that the Prophet صلى الله عليه وسلم used to kiss during the month of fasting."},"heading":{"title":"Kissing During Fasting Hadith Explained Simply","description":"This Hadith is about kissing during fasting. Aishah رضي الله عنها said that the Prophet صلى الله عليه وسلم used to kiss during the month of fasting. The narration is brief, so the explanation should also stay close to the text. It tells us about an action of the Prophet صلى الله عليه وسلم during the fasting month, without giving extra conditions in this wording. For people searching for a hadith about kissing while fasting, this report is one of the direct narrations on the topic. It should be read with care, especially because other narrations in the same topic mention self-control and desire. This specific Hadith simply reports the action during the month of fasting."},"teachings":["The Hadith reports that the Prophet صلى الله عليه وسلم kissed during the fasting month.","The narration is short and should not be expanded beyond its wording.","Questions about fasting may include actions beyond food and drink.","Aishah رضي الله عنها is the narrator of this report."],"related_hadiths":[{"id":"1684","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1685","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1687","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Kissing During Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah رضي الله عنها reports that the Prophet صلى الله عليه وسلم used to kiss during the month of fasting."},"heading":{"title":"Kissing During Fasting Hadith Explained Simply","description":"This Hadith is about kissing during fasting. Aishah رضي الله عنها said that the Prophet صلى الله عليه وسلم used to kiss during the month of fasting. The narration is brief, so the explanation should also stay close to the text. It tells us about an action of the Prophet صلى الله عليه وسلم during the fasting month, without giving extra conditions in this wording. For people searching for a hadith about kissing while fasting, this report is one of the direct narrations on the topic. It should be read with care, especially because other narrations in the same topic mention self-control and desire. This specific Hadith simply reports the action during the month of fasting."},"teachings":["The Hadith reports that the Prophet صلى الله عليه وسلم kissed during the fasting month.","The narration is short and should not be expanded beyond its wording.","Questions about fasting may include actions beyond food and drink.","Aishah رضي الله عنها is the narrator of this report."],"related_hadiths":[{"id":"1684","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1685","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1687","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E175" s="4" t="n"/>
@@ -4502,7 +4506,7 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Self-Control While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah رضي الله عنها mentions kissing while fasting and highlights the Prophet’s صلى الله عليه وسلم self-control."},"heading":{"title":"Self-Control While Fasting and Kissing Hadith","description":"This Hadith teaches about kissing while fasting and self-control. Aishah رضي الله عنها said that the Messenger of Allah صلى الله عليه وسلم used to kiss while he was fasting. Then she added a key point: who among you can control his desire as the Messenger of Allah صلى الله عليه وسلم used to control his desire? This wording makes self-control the heart of the Hadith. The narration does not only mention the action; it also points to the Prophet’s صلى الله عليه وسلم strong control over desire. For anyone searching for kissing while fasting hadith, this report shows that personal restraint matters. The text guides the reader to think carefully about desire, control, and fasting conduct."},"teachings":["The Prophet صلى الله عليه وسلم used to kiss while fasting, as reported by Aishah رضي الله عنها.","Aishah رضي الله عنها connected the matter to control of desire.","Fasting requires awareness of one’s own self-control.","The Hadith warns against copying an action without considering personal restraint."],"related_hadiths":[{"id":"1683","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1687","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1688","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Self-Control While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah رضي الله عنها mentions kissing while fasting and highlights the Prophet’s صلى الله عليه وسلم self-control."},"heading":{"title":"Self-Control While Fasting and Kissing Hadith","description":"This Hadith teaches about kissing while fasting and self-control. Aishah رضي الله عنها said that the Messenger of Allah صلى الله عليه وسلم used to kiss while he was fasting. Then she added a key point: who among you can control his desire as the Messenger of Allah صلى الله عليه وسلم used to control his desire? This wording makes self-control the heart of the Hadith. The narration does not only mention the action; it also points to the Prophet’s صلى الله عليه وسلم strong control over desire. For anyone searching for kissing while fasting hadith, this report shows that personal restraint matters. The text guides the reader to think carefully about desire, control, and fasting conduct."},"teachings":["The Prophet صلى الله عليه وسلم used to kiss while fasting, as reported by Aishah رضي الله عنها.","Aishah رضي الله عنها connected the matter to control of desire.","Fasting requires awareness of one’s own self-control.","The Hadith warns against copying an action without considering personal restraint."],"related_hadiths":[{"id":"1683","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1687","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1688","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E176" s="4" t="n"/>
@@ -4525,7 +4529,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet صلى الله عليه وسلم Kissed While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Hafsah رضي الله عنها reports that the Messenger of Allah صلى الله عليه وسلم used to kiss while fasting."},"heading":{"title":"Prophet صلى الله عليه وسلم Kissed While Fasting Hadith","description":"This Hadith is another report about kissing while fasting. Hafsah رضي الله عنها narrated that the Messenger of Allah صلى الله عليه وسلم used to kiss while he was fasting. The wording is simple and direct. It does not add a question, a condition, or a longer ruling in this specific text. Because of that, the explanation should remain simple too. The Hadith is useful for people searching for a hadith about the Prophet kissing while fasting. It confirms that this action is reported from the Prophet صلى الله عليه وسلم during fasting. At the same time, related narrations mention the matter of controlling desire, so the topic should be read with care and honesty."},"teachings":["Hafsah رضي الله عنها reported this action of the Prophet صلى الله عليه وسلم.","The Hadith directly mentions kissing while fasting.","The text should be understood without adding details not mentioned here.","Related narrations help show why self-control is part of this topic."],"related_hadiths":[{"id":"1683","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1684","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1687","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet صلى الله عليه وسلم Kissed While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Hafsah رضي الله عنها reports that the Messenger of Allah صلى الله عليه وسلم used to kiss while fasting."},"heading":{"title":"Prophet صلى الله عليه وسلم Kissed While Fasting Hadith","description":"This Hadith is another report about kissing while fasting. Hafsah رضي الله عنها narrated that the Messenger of Allah صلى الله عليه وسلم used to kiss while he was fasting. The wording is simple and direct. It does not add a question, a condition, or a longer ruling in this specific text. Because of that, the explanation should remain simple too. The Hadith is useful for people searching for a hadith about the Prophet kissing while fasting. It confirms that this action is reported from the Prophet صلى الله عليه وسلم during fasting. At the same time, related narrations mention the matter of controlling desire, so the topic should be read with care and honesty."},"teachings":["Hafsah رضي الله عنها reported this action of the Prophet صلى الله عليه وسلم.","The Hadith directly mentions kissing while fasting.","The text should be understood without adding details not mentioned here.","Related narrations help show why self-control is part of this topic."],"related_hadiths":[{"id":"1683","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1684","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1687","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E177" s="4" t="n"/>
@@ -4548,7 +4552,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning About Kissing While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith records a warning about a fasting couple who kissed while both were fasting."},"heading":{"title":"Warning About Kissing While Fasting Hadith","description":"This Hadith gives a warning about kissing while fasting. Maimunah, the freed female slave of the Messenger of Allah صلى الله عليه وسلم, said that the Prophet صلى الله عليه وسلم was asked about a man who kissed his wife while both of them were fasting. He replied that they had broken their fast. The narration is very direct, so the explanation should not soften or change the wording. It focuses on a specific question: a man kissed his wife while both were fasting. The answer given in this text is that they had broken their fast. People searching for whether kissing breaks the fast may find this narration, but it should be read together with the exact wording and related reports on control of desire."},"teachings":["The Hadith answers a direct question about a fasting couple.","The Prophet صلى الله عليه وسلم said in this narration that they had broken their fast.","The report shows that actions linked to desire can affect fasting.","The wording should be followed carefully without adding extra cases."],"related_hadiths":[{"id":"1684","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1687","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1688","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning About Kissing While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith records a warning about a fasting couple who kissed while both were fasting."},"heading":{"title":"Warning About Kissing While Fasting Hadith","description":"This Hadith gives a warning about kissing while fasting. Maimunah, the freed female slave of the Messenger of Allah صلى الله عليه وسلم, said that the Prophet صلى الله عليه وسلم was asked about a man who kissed his wife while both of them were fasting. He replied that they had broken their fast. The narration is very direct, so the explanation should not soften or change the wording. It focuses on a specific question: a man kissed his wife while both were fasting. The answer given in this text is that they had broken their fast. People searching for whether kissing breaks the fast may find this narration, but it should be read together with the exact wording and related reports on control of desire."},"teachings":["The Hadith answers a direct question about a fasting couple.","The Prophet صلى الله عليه وسلم said in this narration that they had broken their fast.","The report shows that actions linked to desire can affect fasting.","The wording should be followed carefully without adding extra cases."],"related_hadiths":[{"id":"1684","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1687","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1688","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E178" s="4" t="n"/>
@@ -4571,7 +4575,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Touching While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah رضي الله عنها says the Prophet صلى الله عليه وسلم touched while fasting and had strong control over desire."},"heading":{"title":"Touching While Fasting and Self-Control Hadith","description":"This Hadith discusses touching while fasting and makes self-control the key point. Al-Aswad and Masruq asked Aishah رضي الله عنها whether the Messenger of Allah صلى الله عليه وسلم used to touch his wife while fasting. She replied that he used to do that, and he was the strongest of them in controlling his desire. The narration does not just mention the action. It also points to the Prophet’s صلى الله عليه وسلم level of restraint. For those searching for touching while fasting hadith or desire control in Ramadan, this report gives a balanced wording. It shows that the action was reported, but the comment about control is part of the same answer and should not be ignored."},"teachings":["The companions asked Aishah رضي الله عنها a direct question about fasting.","She reported that the Prophet صلى الله عليه وسلم touched while fasting.","She stressed his strong control over desire.","The Hadith teaches caution when desire may be involved."],"related_hadiths":[{"id":"1684","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1686","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1688","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Touching While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah رضي الله عنها says the Prophet صلى الله عليه وسلم touched while fasting and had strong control over desire."},"heading":{"title":"Touching While Fasting and Self-Control Hadith","description":"This Hadith discusses touching while fasting and makes self-control the key point. Al-Aswad and Masruq asked Aishah رضي الله عنها whether the Messenger of Allah صلى الله عليه وسلم used to touch his wife while fasting. She replied that he used to do that, and he was the strongest of them in controlling his desire. The narration does not just mention the action. It also points to the Prophet’s صلى الله عليه وسلم level of restraint. For those searching for touching while fasting hadith or desire control in Ramadan, this report gives a balanced wording. It shows that the action was reported, but the comment about control is part of the same answer and should not be ignored."},"teachings":["The companions asked Aishah رضي الله عنها a direct question about fasting.","She reported that the Prophet صلى الله عليه وسلم touched while fasting.","She stressed his strong control over desire.","The Hadith teaches caution when desire may be involved."],"related_hadiths":[{"id":"1684","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1686","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1688","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E179" s="4" t="n"/>
@@ -4594,7 +4598,7 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Janabah Before Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah attributes the ruling about waking in impurity before fasting to the Prophet صلى الله عليه وسلم."},"heading":{"title":"Janabah Before Fasting Hadith and Its Wording","description":"This janabah before fasting hadith records Abu Hurairah saying that the statement about a person who wakes up in a state of sexual impurity and wants to fast was not from his own words. He swore by the Lord of the Ka‘bah and said that Muhammad صلى الله عليه وسلم said it. The focus of the narration is careful attribution. Abu Hurairah wanted the listener to know that he was not speaking from personal opinion in this report. The key search idea is fasting while in janabah. The text itself does not expand into a long ruling here; it mainly preserves who said the statement and how strongly Abu Hurairah connected it to the Prophet صلى الله عليه وسلم."},"teachings":["A narrator may clearly separate his own words from the Prophet’s words.","Religious statements should be attributed with care.","The Hadith centers on waking in sexual impurity while wanting to fast."],"related_hadiths":[{"id":"1925","book_id":"1","label":"Sahih Bukhari"},{"id":"1926","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Janabah Before Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah attributes the ruling about waking in impurity before fasting to the Prophet صلى الله عليه وسلم."},"heading":{"title":"Janabah Before Fasting Hadith and Its Wording","description":"This janabah before fasting hadith records Abu Hurairah saying that the statement about a person who wakes up in a state of sexual impurity and wants to fast was not from his own words. He swore by the Lord of the Ka‘bah and said that Muhammad صلى الله عليه وسلم said it. The focus of the narration is careful attribution. Abu Hurairah wanted the listener to know that he was not speaking from personal opinion in this report. The key search idea is fasting while in janabah. The text itself does not expand into a long ruling here; it mainly preserves who said the statement and how strongly Abu Hurairah connected it to the Prophet صلى الله عليه وسلم."},"teachings":["A narrator may clearly separate his own words from the Prophet’s words.","Religious statements should be attributed with care.","The Hadith centers on waking in sexual impurity while wanting to fast."],"related_hadiths":[{"id":"1925","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1926","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E180" s="4" t="n"/>
@@ -4617,7 +4621,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Why Fasting on the Two Eids Is Forbidden","description":"$book_name$ $hadith_number$ - $chapter_name$. Umar explains that Eid al-Fitr is for breaking the fast and Eid al-Adha is for eating from sacrifice."},"heading":{"title":"Fasting on Eid: The Meaning of Fitr and Adha","description":"This narration explains the hadith about fasting on Eid in a very easy way. Abu ‘Ubaid says he attended Eid with ‘Umar bin Khattab. ‘Umar began with the prayer before the sermon, then reminded people that the Messenger of Allah (صلى الله عليه وسلم) forbade fasting on two days: the Day of Fitr and the Day of Adha. The narration also gives the reason in plain words. Eid al-Fitr is the day when people break from their Ramadan fasts. Eid al-Adha is the day when people eat from the meat of their sacrifices. So this Hadith teaches that these days are not meant for personal fasting, but for following the Eid practice taught by the Prophet (صلى الله عليه وسلم)."},"teachings":["The Eid prayer came before the sermon in this report.","The Prophet (صلى الله عليه وسلم) forbade fasting on Eid al-Fitr and Eid al-Adha.","Eid al-Fitr is linked to breaking the fast after Ramadan.","Eid al-Adha is linked to eating from the sacrificial meat."],"related_hadiths":[{"id":"1990","book_id":"1","label":"Sahih Bukhari"},{"id":"1137","book_id":"2","label":"Sahih Muslim"},{"id":"2417","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Why Fasting on the Two Eids Is Forbidden","description":"$book_name$ $hadith_number$ - $chapter_name$. Umar explains that Eid al-Fitr is for breaking the fast and Eid al-Adha is for eating from sacrifice."},"heading":{"title":"Fasting on Eid: The Meaning of Fitr and Adha","description":"This narration explains the hadith about fasting on Eid in a very easy way. Abu ‘Ubaid says he attended Eid with ‘Umar bin Khattab. ‘Umar began with the prayer before the sermon, then reminded people that the Messenger of Allah (صلى الله عليه وسلم) forbade fasting on two days: the Day of Fitr and the Day of Adha. The narration also gives the reason in plain words. Eid al-Fitr is the day when people break from their Ramadan fasts. Eid al-Adha is the day when people eat from the meat of their sacrifices. So this Hadith teaches that these days are not meant for personal fasting, but for following the Eid practice taught by the Prophet (صلى الله عليه وسلم)."},"teachings":["The Eid prayer came before the sermon in this report.","The Prophet (صلى الله عليه وسلم) forbade fasting on Eid al-Fitr and Eid al-Adha.","Eid al-Fitr is linked to breaking the fast after Ramadan.","Eid al-Adha is linked to eating from the sacrificial meat."],"related_hadiths":[{"id":"1990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1137","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2417","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E181" s="4" t="n"/>
@@ -4640,7 +4644,7 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Fast Friday Alone","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet forbade fasting on Friday unless it is joined with Thursday or Saturday."},"heading":{"title":"Hadith About Fasting on Friday With Another Day","description":"This Hadith is often searched as hadith about fasting on Friday alone. Abu Hurairah narrates that the Messenger of Allah (صلى الله عليه وسلم) forbade fasting on a Friday unless it is joined with the day before it or the day after it. The wording is specific. It does not say that every Friday fast is forbidden. It says Friday should not be singled out by itself in this case. If a person fasts Thursday with it, or Saturday with it, the condition mentioned in the Hadith is met. The teaching is simple: voluntary fasting has guidance, and a Muslim should not choose special patterns without following the way the Prophet (صلى الله عليه وسلم) taught."},"teachings":["Friday should not be singled out for fasting by itself in this report.","A Friday fast may be joined with the day before or the day after.","The Hadith gives a clear exception, so the wording should be read carefully.","Voluntary worship should follow the Prophet’s guidance."],"related_hadiths":[{"id":"1985","book_id":"1","label":"Sahih Bukhari"},{"id":"1144b","book_id":"2","label":"Sahih Muslim"},{"id":"2420","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Fast Friday Alone","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet forbade fasting on Friday unless it is joined with Thursday or Saturday."},"heading":{"title":"Hadith About Fasting on Friday With Another Day","description":"This Hadith is often searched as hadith about fasting on Friday alone. Abu Hurairah narrates that the Messenger of Allah (صلى الله عليه وسلم) forbade fasting on a Friday unless it is joined with the day before it or the day after it. The wording is specific. It does not say that every Friday fast is forbidden. It says Friday should not be singled out by itself in this case. If a person fasts Thursday with it, or Saturday with it, the condition mentioned in the Hadith is met. The teaching is simple: voluntary fasting has guidance, and a Muslim should not choose special patterns without following the way the Prophet (صلى الله عليه وسلم) taught."},"teachings":["Friday should not be singled out for fasting by itself in this report.","A Friday fast may be joined with the day before or the day after.","The Hadith gives a clear exception, so the wording should be read carefully.","Voluntary worship should follow the Prophet’s guidance."],"related_hadiths":[{"id":"1985","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1144b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2420","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E182" s="4" t="n"/>
@@ -4663,7 +4667,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Frequent Friday Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Masud reports that he rarely saw the Prophet not fasting on Friday."},"heading":{"title":"Hadith on the Prophet Fasting on Friday","description":"This Hadith gives a different angle on fasting on Friday. ‘Abdullah bin Mas’ud says, “I rarely saw the Messenger of Allah (صلى الله عليه وسلم) not fasting on a Friday.” The text is a personal observation from a Companion. It does not say that Friday should always be singled out, and it does not mention whether another day was joined with it. So the safest explanation is to stay with what the wording says: Ibn Mas’ud observed the Prophet (صلى الله عليه وسلم) fasting on Fridays often. People searching for hadith about fasting on Friday should notice both sides of the reports: some narrations warn against singling out Friday, while this one records what Ibn Mas’ud saw from the Prophet’s practice."},"teachings":["Ibn Mas’ud reported what he personally observed.","The narration shows that the Prophet (صلى الله عليه وسلم) was often seen fasting on Friday.","The report does not state that Friday was fasted alone.","Different reports on Friday fasting should be read with care."],"related_hadiths":[{"id":"1985","book_id":"1","label":"Sahih Bukhari"},{"id":"1144b","book_id":"2","label":"Sahih Muslim"},{"id":"2420","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Frequent Friday Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Masud reports that he rarely saw the Prophet not fasting on Friday."},"heading":{"title":"Hadith on the Prophet Fasting on Friday","description":"This Hadith gives a different angle on fasting on Friday. ‘Abdullah bin Mas’ud says, “I rarely saw the Messenger of Allah (صلى الله عليه وسلم) not fasting on a Friday.” The text is a personal observation from a Companion. It does not say that Friday should always be singled out, and it does not mention whether another day was joined with it. So the safest explanation is to stay with what the wording says: Ibn Mas’ud observed the Prophet (صلى الله عليه وسلم) fasting on Fridays often. People searching for hadith about fasting on Friday should notice both sides of the reports: some narrations warn against singling out Friday, while this one records what Ibn Mas’ud saw from the Prophet’s practice."},"teachings":["Ibn Mas’ud reported what he personally observed.","The narration shows that the Prophet (صلى الله عليه وسلم) was often seen fasting on Friday.","The report does not state that Friday was fasted alone.","Different reports on Friday fasting should be read with care."],"related_hadiths":[{"id":"1985","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1144b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2420","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E183" s="4" t="n"/>
@@ -4686,7 +4690,7 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Fast Saturday Except Obligatory Fasts","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said not to fast Saturday except for obligatory fasts, even if one only finds a small thing to eat."},"heading":{"title":"Hadith About Fasting on Saturday","description":"This Hadith is about fasting on Saturday. ‘Abdullah bin Busr narrates that the Messenger of Allah (صلى الله عليه وسلم) said not to fast on Saturdays apart from days when fasting is obligatory. The wording then stresses the point with a strong image: if a person finds only grape stalks or the bark of a tree, he should suck on it. That means the report is not casual advice; it presents a serious instruction within the text. The narration also mentions another chain from ‘Abdullah bin Busr’s sister with similar wording. For users searching can you fast on Saturday in Islam, this Hadith is one of the key reports connected to that question."},"teachings":["The Hadith mentions not fasting Saturday except in obligatory fasting.","The wording strongly tells the person to break that Saturday fast.","A second chain reports a similar statement through ‘Abdullah bin Busr’s sister.","The narration is about Saturday specifically, not every voluntary fast."],"related_hadiths":[{"id":"744","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"2421","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Fast Saturday Except Obligatory Fasts","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said not to fast Saturday except for obligatory fasts, even if one only finds a small thing to eat."},"heading":{"title":"Hadith About Fasting on Saturday","description":"This Hadith is about fasting on Saturday. ‘Abdullah bin Busr narrates that the Messenger of Allah (صلى الله عليه وسلم) said not to fast on Saturdays apart from days when fasting is obligatory. The wording then stresses the point with a strong image: if a person finds only grape stalks or the bark of a tree, he should suck on it. That means the report is not casual advice; it presents a serious instruction within the text. The narration also mentions another chain from ‘Abdullah bin Busr’s sister with similar wording. For users searching can you fast on Saturday in Islam, this Hadith is one of the key reports connected to that question."},"teachings":["The Hadith mentions not fasting Saturday except in obligatory fasting.","The wording strongly tells the person to break that Saturday fast.","A second chain reports a similar statement through ‘Abdullah bin Busr’s sister.","The narration is about Saturday specifically, not every voluntary fast."],"related_hadiths":[{"id":"744","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"2421","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E184" s="4" t="n"/>
@@ -4709,7 +4713,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aishah’s Report on the Ten Days Fast","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports that she never saw the Prophet fasting the first ten days of Dhul-Hijjah."},"heading":{"title":"Aishah’s Hadith About Fasting the Ten Days of Dhul-Hijjah","description":"This narration is short but important for careful reading. Aswad narrates that ‘Aishah said, “I never saw the Messenger of Allah (صلى الله عليه وسلم) fasting the ten days.” The main search phrase is Aishah hadith fasting ten days of Dhul-Hijjah. The Hadith reports what ‘Aishah personally saw. It does not say that fasting in these days has no value, and it does not give a full ruling by itself. It simply records her observation. This helps readers avoid overstatement. When different narrations discuss the same season, each text should be explained on its own terms. Here, the direct lesson is about honest narration and staying within what was witnessed."},"teachings":["‘Aishah reported what she personally observed.","The Hadith says she never saw the Prophet (صلى الله عليه وسلم) fasting the ten days.","The narration should not be stretched beyond its wording.","Careful Hadith reading means keeping each report in its own wording."],"related_hadiths":[{"id":"2437","book_id":"4","label":"Sunan Abu Dawud"},{"id":"2417","book_id":"3","label":"Sunan an-Nasai"},{"id":"969","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aishah’s Report on the Ten Days Fast","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports that she never saw the Prophet fasting the first ten days of Dhul-Hijjah."},"heading":{"title":"Aishah’s Hadith About Fasting the Ten Days of Dhul-Hijjah","description":"This narration is short but important for careful reading. Aswad narrates that ‘Aishah said, “I never saw the Messenger of Allah (صلى الله عليه وسلم) fasting the ten days.” The main search phrase is Aishah hadith fasting ten days of Dhul-Hijjah. The Hadith reports what ‘Aishah personally saw. It does not say that fasting in these days has no value, and it does not give a full ruling by itself. It simply records her observation. This helps readers avoid overstatement. When different narrations discuss the same season, each text should be explained on its own terms. Here, the direct lesson is about honest narration and staying within what was witnessed."},"teachings":["‘Aishah reported what she personally observed.","The Hadith says she never saw the Prophet (صلى الله عليه وسلم) fasting the ten days.","The narration should not be stretched beyond its wording.","Careful Hadith reading means keeping each report in its own wording."],"related_hadiths":[{"id":"2437","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"2417","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"969","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E185" s="4" t="n"/>
@@ -4732,7 +4736,7 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Complete the Rest of Ashura","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet told those who had eaten and those who had not eaten to complete the rest of Ashura."},"heading":{"title":"Ashura Hadith About Completing the Day","description":"This Hadith shows a practical instruction on the Day of ‘Ashura. Muhammad bin Saifi says the Messenger of Allah (صلى الله عليه وسلم) asked whether anyone had eaten that day. Some had eaten and some had not. The Prophet (صلى الله عليه وسلم) told all of them to complete the rest of the day, meaning not to eat for the rest of it. He also told them to send word to the people around Al-Madinah so they would complete the rest of their day too. The main search term is Ashura complete the rest of the day hadith. The narration highlights obedience after receiving instruction, even if some people had already eaten earlier that day."},"teachings":["The Prophet (صلى الله عليه وسلم) asked whether people had eaten on ‘Ashura.","Those who had eaten and those who had not were told to complete the rest of the day.","The instruction was also sent to people around Al-Madinah.","The Hadith shows responding to guidance once it reaches a person."],"related_hadiths":[{"id":"1924","book_id":"1","label":"Sahih Bukhari"},{"id":"1960","book_id":"1","label":"Sahih Bukhari"},{"id":"1135","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Complete the Rest of Ashura","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet told those who had eaten and those who had not eaten to complete the rest of Ashura."},"heading":{"title":"Ashura Hadith About Completing the Day","description":"This Hadith shows a practical instruction on the Day of ‘Ashura. Muhammad bin Saifi says the Messenger of Allah (صلى الله عليه وسلم) asked whether anyone had eaten that day. Some had eaten and some had not. The Prophet (صلى الله عليه وسلم) told all of them to complete the rest of the day, meaning not to eat for the rest of it. He also told them to send word to the people around Al-Madinah so they would complete the rest of their day too. The main search term is Ashura complete the rest of the day hadith. The narration highlights obedience after receiving instruction, even if some people had already eaten earlier that day."},"teachings":["The Prophet (صلى الله عليه وسلم) asked whether people had eaten on ‘Ashura.","Those who had eaten and those who had not were told to complete the rest of the day.","The instruction was also sent to people around Al-Madinah.","The Hadith shows responding to guidance once it reaches a person."],"related_hadiths":[{"id":"1924","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1960","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1135","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E186" s="4" t="n"/>
@@ -4755,7 +4759,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fasting the Ninth of Muharram","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said that if he lived until the next year, he would fast the ninth day too."},"heading":{"title":"Hadith About Fasting the Ninth of Muharram","description":"This Hadith is often searched as fasting the 9th of Muharram hadith. Ibn ‘Abbas narrates that the Messenger of Allah (صلى الله عليه وسلم) said, “If I live until next year, I will fast the ninth day too.” The wording is short and focused. It shows an intention connected to ‘Ashura fasting: adding the ninth day. The narration does not include a long explanation, and it does not mention the eleventh day. So the content should stay with the exact wording: the Prophet (صلى الله عليه وسلم) expressed that he would fast the ninth if he lived until the next year. This teaches that even a brief Prophetic statement can guide how Muslims understand a recommended fast."},"teachings":["The Prophet (صلى الله عليه وسلم) mentioned fasting the ninth day.","His statement was tied to living until the next year.","The Hadith supports adding the ninth of Muharram to the Ashura fast.","The text does not mention extra days beyond the ninth."],"related_hadiths":[{"id":"1134a","book_id":"2","label":"Sahih Muslim"},{"id":"2445","book_id":"4","label":"Sunan Abu Dawud"},{"id":"755","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fasting the Ninth of Muharram","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said that if he lived until the next year, he would fast the ninth day too."},"heading":{"title":"Hadith About Fasting the Ninth of Muharram","description":"This Hadith is often searched as fasting the 9th of Muharram hadith. Ibn ‘Abbas narrates that the Messenger of Allah (صلى الله عليه وسلم) said, “If I live until next year, I will fast the ninth day too.” The wording is short and focused. It shows an intention connected to ‘Ashura fasting: adding the ninth day. The narration does not include a long explanation, and it does not mention the eleventh day. So the content should stay with the exact wording: the Prophet (صلى الله عليه وسلم) expressed that he would fast the ninth if he lived until the next year. This teaches that even a brief Prophetic statement can guide how Muslims understand a recommended fast."},"teachings":["The Prophet (صلى الله عليه وسلم) mentioned fasting the ninth day.","His statement was tied to living until the next year.","The Hadith supports adding the ninth of Muharram to the Ashura fast.","The text does not mention extra days beyond the ninth."],"related_hadiths":[{"id":"1134a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2445","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"755","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E187" s="4" t="n"/>
@@ -4778,7 +4782,7 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Balanced Fasting Without Self-Harm","description":"$book_name$ $hadith_number$ - $chapter_name$. Balanced fasting is taught through the Prophet’s correction of self-punishing hardship."},"heading":{"title":"Hadith About Balanced Fasting and Sacred Months","description":"This hadith about voluntary fasting shows that worship should not become self-punishment. The man had stopped eating during the day and had become thin and weak. The Prophet صلى الله عليه وسلم noticed his condition and asked why his body looked so weak. When the man said he only ate at night, the Prophet صلى الله عليه وسلم replied, “Who commanded you to punish yourself?” This makes the message clear: fasting is worship, but the body also has a right. The Prophet صلى الله عليه وسلم then guided him step by step: fast the month of patience, then add one, two, and three days, and fast the sacred months. The tone is gentle and measured, not harsh."},"teachings":["Fasting should not be turned into self-punishment.","The Prophet صلى الله عليه وسلم cared about a person’s physical condition while guiding worship.","Extra fasting can be increased in a measured way when a person is able.","The sacred months are mentioned here as times connected with fasting."],"related_hadiths":[{"id":"1742","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1744","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1745","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Balanced Fasting Without Self-Harm","description":"$book_name$ $hadith_number$ - $chapter_name$. Balanced fasting is taught through the Prophet’s correction of self-punishing hardship."},"heading":{"title":"Hadith About Balanced Fasting and Sacred Months","description":"This hadith about voluntary fasting shows that worship should not become self-punishment. The man had stopped eating during the day and had become thin and weak. The Prophet صلى الله عليه وسلم noticed his condition and asked why his body looked so weak. When the man said he only ate at night, the Prophet صلى الله عليه وسلم replied, “Who commanded you to punish yourself?” This makes the message clear: fasting is worship, but the body also has a right. The Prophet صلى الله عليه وسلم then guided him step by step: fast the month of patience, then add one, two, and three days, and fast the sacred months. The tone is gentle and measured, not harsh."},"teachings":["Fasting should not be turned into self-punishment.","The Prophet صلى الله عليه وسلم cared about a person’s physical condition while guiding worship.","Extra fasting can be increased in a measured way when a person is able.","The sacred months are mentioned here as times connected with fasting."],"related_hadiths":[{"id":"1742","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1744","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1745","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E188" s="4" t="n"/>
@@ -4801,7 +4805,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Narration on Fasting Rajab","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration states that the Prophet صلى الله عليه وسلم forbade fasting Rajab."},"heading":{"title":"Hadith About Fasting Rajab and Prophetic Prohibition","description":"This hadith about fasting Rajab is brief, so the explanation should stay close to the text. Ibn ‘Abbas narrated that the Prophet صلى الله عليه وسلم forbade fasting Rajab. The narration does not give a long reason, a list of exceptions, or a detailed ruling inside this wording. So the safest reading is to report what the text says without adding claims that are not here. For people searching “fasting Rajab hadith” or “did the Prophet forbid fasting Rajab,” this narration is often the direct text they want to read. It also reminds us that not every act people call worship should be followed unless it has guidance from the Prophet صلى الله عليه وسلم."},"teachings":["The narration directly mentions a prohibition connected with fasting Rajab.","The text is short, so extra details should not be added from it alone.","A Muslim should be careful about worship practices and follow prophetic guidance.","Questions about specific months should be treated with care."],"related_hadiths":[{"id":"1741","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1742","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1744","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Narration on Fasting Rajab","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration states that the Prophet صلى الله عليه وسلم forbade fasting Rajab."},"heading":{"title":"Hadith About Fasting Rajab and Prophetic Prohibition","description":"This hadith about fasting Rajab is brief, so the explanation should stay close to the text. Ibn ‘Abbas narrated that the Prophet صلى الله عليه وسلم forbade fasting Rajab. The narration does not give a long reason, a list of exceptions, or a detailed ruling inside this wording. So the safest reading is to report what the text says without adding claims that are not here. For people searching “fasting Rajab hadith” or “did the Prophet forbid fasting Rajab,” this narration is often the direct text they want to read. It also reminds us that not every act people call worship should be followed unless it has guidance from the Prophet صلى الله عليه وسلم."},"teachings":["The narration directly mentions a prohibition connected with fasting Rajab.","The text is short, so extra details should not be added from it alone.","A Muslim should be careful about worship practices and follow prophetic guidance.","Questions about specific months should be treated with care."],"related_hadiths":[{"id":"1741","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1742","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1744","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E189" s="4" t="n"/>
@@ -4824,7 +4828,7 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Guidance to Fast Shawwal","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet صلى الله عليه وسلم directing Usamah bin Zaid toward fasting Shawwal."},"heading":{"title":"Hadith About Fasting Shawwal and Following Prophetic Guidance","description":"This hadith about fasting Shawwal mentions Usamah bin Zaid, who used to fast during the sacred months. The Messenger of Allah صلى الله عليه وسلم told him, “Fast Shawwal.” After this advice, Usamah left fasting the sacred months in that pattern and continued to fast Shawwal until he died. The text shows a personal direction from the Prophet صلى الله عليه وسلم and a strong response from Usamah. It does not say that every person must copy the exact same change in every case. The safe lesson is that prophetic guidance shaped his worship, and he held to it steadily. For searches like “fast Shawwal hadith” and “Usamah bin Zaid fasting Shawwal,” this narration is directly relevant."},"teachings":["Usamah bin Zaid changed his practice after the Prophet’s صلى الله عليه وسلم instruction.","The hadith mentions Shawwal as a month connected with fasting.","Prophetic guidance should carry weight in shaping worship habits.","Steady practice is shown through Usamah’s continued fasting of Shawwal."],"related_hadiths":[{"id":"1716","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1741","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1742","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Guidance to Fast Shawwal","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet صلى الله عليه وسلم directing Usamah bin Zaid toward fasting Shawwal."},"heading":{"title":"Hadith About Fasting Shawwal and Following Prophetic Guidance","description":"This hadith about fasting Shawwal mentions Usamah bin Zaid, who used to fast during the sacred months. The Messenger of Allah صلى الله عليه وسلم told him, “Fast Shawwal.” After this advice, Usamah left fasting the sacred months in that pattern and continued to fast Shawwal until he died. The text shows a personal direction from the Prophet صلى الله عليه وسلم and a strong response from Usamah. It does not say that every person must copy the exact same change in every case. The safe lesson is that prophetic guidance shaped his worship, and he held to it steadily. For searches like “fast Shawwal hadith” and “Usamah bin Zaid fasting Shawwal,” this narration is directly relevant."},"teachings":["Usamah bin Zaid changed his practice after the Prophet’s صلى الله عليه وسلم instruction.","The hadith mentions Shawwal as a month connected with fasting.","Prophetic guidance should carry weight in shaping worship habits.","Steady practice is shown through Usamah’s continued fasting of Shawwal."],"related_hadiths":[{"id":"1716","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1741","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1742","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E190" s="4" t="n"/>
@@ -4847,7 +4851,7 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fasting as Zakat of the Body","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes fasting as the body’s zakat and half of patience."},"heading":{"title":"Fasting Is the Zakat of the Body Hadith","description":"This hadith about fasting explains its spiritual value using two clear phrases. The Messenger of Allah صلى الله عليه وسلم said that everything has a zakat, and the zakat of the body is fasting. In another wording in the same report, fasting is called half of patience. The wording links fasting with self-control, restraint, and care for the body in worship. It does not mean fasting replaces the financial zakat due on wealth; the hadith is speaking about the body. For people searching “zakat of the body is fasting hadith” or “fasting is half of patience,” this narration gives both phrases in one place and shows how fasting trains the believer."},"teachings":["Fasting is described as the zakat of the body.","The text connects fasting with patience.","The hadith presents fasting as a form of bodily worship.","The wording should not be mixed with financial zakat rules."],"related_hadiths":[{"id":"1638","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1641","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1741","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fasting as Zakat of the Body","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes fasting as the body’s zakat and half of patience."},"heading":{"title":"Fasting Is the Zakat of the Body Hadith","description":"This hadith about fasting explains its spiritual value using two clear phrases. The Messenger of Allah صلى الله عليه وسلم said that everything has a zakat, and the zakat of the body is fasting. In another wording in the same report, fasting is called half of patience. The wording links fasting with self-control, restraint, and care for the body in worship. It does not mean fasting replaces the financial zakat due on wealth; the hadith is speaking about the body. For people searching “zakat of the body is fasting hadith” or “fasting is half of patience,” this narration gives both phrases in one place and shows how fasting trains the believer."},"teachings":["Fasting is described as the zakat of the body.","The text connects fasting with patience.","The hadith presents fasting as a form of bodily worship.","The wording should not be mixed with financial zakat rules."],"related_hadiths":[{"id":"1638","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1641","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1741","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E191" s="4" t="n"/>
@@ -4870,7 +4874,7 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward for Feeding a Fasting Person","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith promises a reward like the fasting person for giving iftar without reducing their reward."},"heading":{"title":"Reward of Feeding a Fasting Person Hadith","description":"This hadith about feeding a fasting person is simple and full of hope. The Messenger of Allah صلى الله عليه وسلم said that whoever gives food to a fasting person to break the fast will have a reward like theirs. The hadith also protects the reward of the fasting person by saying nothing is taken away from their reward. This encourages generosity at iftar without making it a competition. Even the act of helping someone break their fast becomes a way to share in good. For searchers using terms like “reward of feeding fasting person hadith” or “iftar reward hadith,” this narration gives the main wording clearly."},"teachings":["Giving iftar to a fasting person is linked with great reward.","The fasting person’s own reward is not reduced.","The hadith encourages generosity around iftar time.","Helping others worship is itself a good deed."],"related_hadiths":[{"id":"1747","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1748","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1750","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward for Feeding a Fasting Person","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith promises a reward like the fasting person for giving iftar without reducing their reward."},"heading":{"title":"Reward of Feeding a Fasting Person Hadith","description":"This hadith about feeding a fasting person is simple and full of hope. The Messenger of Allah صلى الله عليه وسلم said that whoever gives food to a fasting person to break the fast will have a reward like theirs. The hadith also protects the reward of the fasting person by saying nothing is taken away from their reward. This encourages generosity at iftar without making it a competition. Even the act of helping someone break their fast becomes a way to share in good. For searchers using terms like “reward of feeding fasting person hadith” or “iftar reward hadith,” this narration gives the main wording clearly."},"teachings":["Giving iftar to a fasting person is linked with great reward.","The fasting person’s own reward is not reduced.","The hadith encourages generosity around iftar time.","Helping others worship is itself a good deed."],"related_hadiths":[{"id":"1747","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1748","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1750","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E192" s="4" t="n"/>
@@ -4893,7 +4897,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Hosts at Iftar","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith records a supplication made when the Prophet صلى الله عليه وسلم broke his fast with Sa’d."},"heading":{"title":"Dua When Fasting People Break Fast With You","description":"This hadith about iftar dua records what the Prophet صلى الله عليه وسلم said after breaking his fast with Sa’d bin Mu’adh. The words are a prayer for the host: may fasting people break their fast with you, may the righteous eat your food, and may the angels send blessings upon you. The narration shows gratitude expressed as dua, not just thanks in normal speech. It also links feeding guests and fasting people with a blessed gathering. The text does not give a long rule about every meal; it simply preserves this beautiful supplication. People searching “Aftara indakumus saimun dua” can find the wording and its meaning here."},"teachings":["The Prophet صلى الله عليه وسلم made dua for the host after iftar.","The supplication mentions fasting people, righteous eaters, and angels’ blessings.","Good hospitality can be answered with prayer.","The narration teaches a gentle way to thank someone after food."],"related_hadiths":[{"id":"1746","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1748","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1749","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Hosts at Iftar","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith records a supplication made when the Prophet صلى الله عليه وسلم broke his fast with Sa’d."},"heading":{"title":"Dua When Fasting People Break Fast With You","description":"This hadith about iftar dua records what the Prophet صلى الله عليه وسلم said after breaking his fast with Sa’d bin Mu’adh. The words are a prayer for the host: may fasting people break their fast with you, may the righteous eat your food, and may the angels send blessings upon you. The narration shows gratitude expressed as dua, not just thanks in normal speech. It also links feeding guests and fasting people with a blessed gathering. The text does not give a long rule about every meal; it simply preserves this beautiful supplication. People searching “Aftara indakumus saimun dua” can find the wording and its meaning here."},"teachings":["The Prophet صلى الله عليه وسلم made dua for the host after iftar.","The supplication mentions fasting people, righteous eaters, and angels’ blessings.","Good hospitality can be answered with prayer.","The narration teaches a gentle way to thank someone after food."],"related_hadiths":[{"id":"1746","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1748","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1749","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E193" s="4" t="n"/>
@@ -4916,7 +4920,7 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Angels Bless the Fasting Person","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says angels send blessings on a fasting person when food is eaten near him."},"heading":{"title":"Hadith About Angels Blessing the Fasting Person","description":"This hadith about the fasting person and angels comes from Umm ‘Umarah. The Prophet صلى الله عليه وسلم came to them, and food was served. Some people present were fasting. The Messenger of Allah صلى الله عليه وسلم then said that when food is eaten in the presence of a fasting person, the angels send blessings upon him. The lesson is closely tied to the scene: a fasting person remains patient while others eat. The hadith does not say to seek out hardship for show. It simply points to a blessing connected with patience during fasting. Search terms like “angels bless fasting person hadith” and “food eaten near fasting person” match this narration well."},"teachings":["A fasting person may receive angels’ blessings when food is eaten near him.","The hadith shows patience while others are eating.","The narration does not encourage showing off fasting.","The blessing is mentioned in a social setting where food was served."],"related_hadiths":[{"id":"1747","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1749","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1750","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Angels Bless the Fasting Person","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says angels send blessings on a fasting person when food is eaten near him."},"heading":{"title":"Hadith About Angels Blessing the Fasting Person","description":"This hadith about the fasting person and angels comes from Umm ‘Umarah. The Prophet صلى الله عليه وسلم came to them, and food was served. Some people present were fasting. The Messenger of Allah صلى الله عليه وسلم then said that when food is eaten in the presence of a fasting person, the angels send blessings upon him. The lesson is closely tied to the scene: a fasting person remains patient while others eat. The hadith does not say to seek out hardship for show. It simply points to a blessing connected with patience during fasting. Search terms like “angels bless fasting person hadith” and “food eaten near fasting person” match this narration well."},"teachings":["A fasting person may receive angels’ blessings when food is eaten near him.","The hadith shows patience while others are eating.","The narration does not encourage showing off fasting.","The blessing is mentioned in a social setting where food was served."],"related_hadiths":[{"id":"1747","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1749","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1750","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E194" s="4" t="n"/>
@@ -4939,7 +4943,7 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bilal’s Fasting and Angels’ Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the honor of Bilal’s fasting while others ate."},"heading":{"title":"Hadith About Bilal Fasting While Food Was Served","description":"This hadith about Bilal fasting gives a vivid picture of restraint. The Prophet صلى الله عليه وسلم invited Bilal to eat, but Bilal said he was fasting. The Prophet صلى الله عليه وسلم replied that they were eating their provision, while Bilal’s provision was in Paradise. He then mentioned that the bones of the fasting person glorify Allah and the angels seek forgiveness for him as long as food is eaten in front of him. The wording praises the fasting person’s state without blaming those who were eating. It teaches that fasting has hidden honor with Allah. Searchers looking for “Bilal fasting hadith” or “bones of fasting person glorify Allah” will find this narration."},"teachings":["Bilal remained fasting when invited to eat.","The Prophet صلى الله عليه وسلم spoke highly of the fasting person’s unseen reward.","The hadith mentions angels seeking forgiveness for the fasting person.","Those eating their provision were not criticized in the narration."],"related_hadiths":[{"id":"1748","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1750","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1753","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bilal’s Fasting and Angels’ Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the honor of Bilal’s fasting while others ate."},"heading":{"title":"Hadith About Bilal Fasting While Food Was Served","description":"This hadith about Bilal fasting gives a vivid picture of restraint. The Prophet صلى الله عليه وسلم invited Bilal to eat, but Bilal said he was fasting. The Prophet صلى الله عليه وسلم replied that they were eating their provision, while Bilal’s provision was in Paradise. He then mentioned that the bones of the fasting person glorify Allah and the angels seek forgiveness for him as long as food is eaten in front of him. The wording praises the fasting person’s state without blaming those who were eating. It teaches that fasting has hidden honor with Allah. Searchers looking for “Bilal fasting hadith” or “bones of fasting person glorify Allah” will find this narration."},"teachings":["Bilal remained fasting when invited to eat.","The Prophet صلى الله عليه وسلم spoke highly of the fasting person’s unseen reward.","The hadith mentions angels seeking forgiveness for the fasting person.","Those eating their provision were not criticized in the narration."],"related_hadiths":[{"id":"1748","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1750","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1753","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E195" s="4" t="n"/>
@@ -4962,7 +4966,7 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | What to Say When Invited While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches a simple reply when a fasting person is invited to eat."},"heading":{"title":"What to Say When Invited to Eat While Fasting","description":"This hadith about being invited to eat while fasting gives a short piece of etiquette. The Prophet صلى الله عليه وسلم said that if one of you is invited to food while fasting, he should say, “I am fasting.” The wording is calm and clear. It avoids awkwardness, excuses, or harsh refusal. A fasting person can explain his situation in a simple way. The hadith also protects good manners between host and guest. It does not say to shame the host or make the fast a public display. For searches like “I am fasting hadith” and “invited to eat while fasting,” this narration is the direct answer."},"teachings":["A fasting person may simply say, “I am fasting.”","The hadith teaches polite speech when refusing food due to fasting.","The host is not blamed in the wording.","Fasting should be handled with good manners in social settings."],"related_hadiths":[{"id":"1751","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1748","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1749","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | What to Say When Invited While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches a simple reply when a fasting person is invited to eat."},"heading":{"title":"What to Say When Invited to Eat While Fasting","description":"This hadith about being invited to eat while fasting gives a short piece of etiquette. The Prophet صلى الله عليه وسلم said that if one of you is invited to food while fasting, he should say, “I am fasting.” The wording is calm and clear. It avoids awkwardness, excuses, or harsh refusal. A fasting person can explain his situation in a simple way. The hadith also protects good manners between host and guest. It does not say to shame the host or make the fast a public display. For searches like “I am fasting hadith” and “invited to eat while fasting,” this narration is the direct answer."},"teachings":["A fasting person may simply say, “I am fasting.”","The hadith teaches polite speech when refusing food due to fasting.","The host is not blamed in the wording.","Fasting should be handled with good manners in social settings."],"related_hadiths":[{"id":"1751","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1748","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1749","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E196" s="4" t="n"/>
@@ -4985,7 +4989,7 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Accepting Food Invitation While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says a fasting person may accept an invitation and then eat or leave it."},"heading":{"title":"Hadith on Accepting an Invitation While Fasting","description":"This hadith about accepting an invitation while fasting gives balanced social guidance. The Prophet صلى الله عليه وسلم said that whoever is invited to food while fasting should accept the invitation. Then he said that if the person wants, he may eat, and if he wants, he may leave it. The text allows space for the fasting person’s choice. It also keeps the relationship with the host warm by encouraging acceptance of the invitation. The hadith does not force eating in every case, nor does it make refusing food the only option. It is useful for people searching “fasting person invited to eat hadith” or “accept invitation while fasting.”"},"teachings":["A fasting person is told to accept the food invitation.","The person may choose to eat or not eat.","The hadith keeps social ties in view while fasting.","The wording gives room for personal choice in that moment."],"related_hadiths":[{"id":"1750","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1746","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1747","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Accepting Food Invitation While Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says a fasting person may accept an invitation and then eat or leave it."},"heading":{"title":"Hadith on Accepting an Invitation While Fasting","description":"This hadith about accepting an invitation while fasting gives balanced social guidance. The Prophet صلى الله عليه وسلم said that whoever is invited to food while fasting should accept the invitation. Then he said that if the person wants, he may eat, and if he wants, he may leave it. The text allows space for the fasting person’s choice. It also keeps the relationship with the host warm by encouraging acceptance of the invitation. The hadith does not force eating in every case, nor does it make refusing food the only option. It is useful for people searching “fasting person invited to eat hadith” or “accept invitation while fasting.”"},"teachings":["A fasting person is told to accept the food invitation.","The person may choose to eat or not eat.","The hadith keeps social ties in view while fasting.","The wording gives room for personal choice in that moment."],"related_hadiths":[{"id":"1750","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1746","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1747","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E197" s="4" t="n"/>
@@ -5008,7 +5012,7 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Supplications Not Turned Back","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith names the just ruler, fasting person, and wronged person among accepted supplications."},"heading":{"title":"Hadith on Dua of the Fasting Person","description":"This hadith about dua while fasting mentions three people whose supplications are not turned back: a just ruler, a fasting person until he breaks the fast, and one who has been wronged. The wording then gives special detail about the supplication of the wronged person, saying it is raised, the gates of heaven are opened, and Allah promises help even after a while. The hadith gives hope, but it should be quoted with care and not used to make careless claims. For searchers looking for “dua of fasting person hadith” or “three supplications not rejected,” this narration gives the main list and the powerful wording."},"teachings":["The fasting person’s dua is honored until he breaks the fast.","Justice is praised through mention of the just ruler.","The supplication of the wronged person is given special emphasis.","Help may come after a while, as stated in the hadith."],"related_hadiths":[{"id":"1753","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3598","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1749","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Supplications Not Turned Back","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith names the just ruler, fasting person, and wronged person among accepted supplications."},"heading":{"title":"Hadith on Dua of the Fasting Person","description":"This hadith about dua while fasting mentions three people whose supplications are not turned back: a just ruler, a fasting person until he breaks the fast, and one who has been wronged. The wording then gives special detail about the supplication of the wronged person, saying it is raised, the gates of heaven are opened, and Allah promises help even after a while. The hadith gives hope, but it should be quoted with care and not used to make careless claims. For searchers looking for “dua of fasting person hadith” or “three supplications not rejected,” this narration gives the main list and the powerful wording."},"teachings":["The fasting person’s dua is honored until he breaks the fast.","Justice is praised through mention of the just ruler.","The supplication of the wronged person is given special emphasis.","Help may come after a while, as stated in the hadith."],"related_hadiths":[{"id":"1753","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3598","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1749","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E198" s="4" t="n"/>
@@ -5031,7 +5035,7 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Supplication at Breaking Fast","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says the fasting person’s supplication at iftar is not turned back."},"heading":{"title":"Dua at Iftar: Hadith on Supplication When Breaking Fast","description":"This hadith about dua at iftar teaches that the fasting person has a supplication at the time of breaking the fast that is not turned back. The report also mentions a dua heard from ‘Abdullah bin ‘Amr: “O Allah, I ask You by Your mercy, which encompasses all things, to forgive me.” The text brings together the time of iftar and asking Allah for forgiveness. It does not say this is the only dua a person may make at iftar. It simply shows a meaningful supplication connected to that moment. Searchers using “dua when breaking fast hadith” or “Allahumma inni as’aluka birahmatika” will find this narration."},"teachings":["The time of breaking the fast is linked with accepted supplication.","Asking Allah for forgiveness is shown in the reported dua.","The hadith encourages turning to Allah at iftar.","The narration does not limit a person to only one dua."],"related_hadiths":[{"id":"1752","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3598","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1747","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Supplication at Breaking Fast","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says the fasting person’s supplication at iftar is not turned back."},"heading":{"title":"Dua at Iftar: Hadith on Supplication When Breaking Fast","description":"This hadith about dua at iftar teaches that the fasting person has a supplication at the time of breaking the fast that is not turned back. The report also mentions a dua heard from ‘Abdullah bin ‘Amr: “O Allah, I ask You by Your mercy, which encompasses all things, to forgive me.” The text brings together the time of iftar and asking Allah for forgiveness. It does not say this is the only dua a person may make at iftar. It simply shows a meaningful supplication connected to that moment. Searchers using “dua when breaking fast hadith” or “Allahumma inni as’aluka birahmatika” will find this narration."},"teachings":["The time of breaking the fast is linked with accepted supplication.","Asking Allah for forgiveness is shown in the reported dua.","The hadith encourages turning to Allah at iftar.","The narration does not limit a person to only one dua."],"related_hadiths":[{"id":"1752","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3598","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1747","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E199" s="4" t="n"/>
@@ -5054,7 +5058,7 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eating Dates Before Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet صلى الله عليه وسلم eating dates before going out on Eid al-Fitr."},"heading":{"title":"Eating Dates Before Eid al-Fitr Prayer Hadith","description":"This hadith about Eid al-Fitr records a simple practice of the Prophet صلى الله عليه وسلم. Anas bin Malik narrated that the Prophet صلى الله عليه وسلم would not go out on the Day of Fitr until he had eaten some dates. The narration focuses on eating before going out. It does not give the number of dates in this wording, so that should not be added here. The message is easy to understand: Eid al-Fitr begins with breaking from the fasting pattern before leaving for the prayer. For people searching “eating dates before Eid prayer hadith” or “Prophet ate dates on Eid al-Fitr,” this narration gives the direct text."},"teachings":["The Prophet صلى الله عليه وسلم ate before going out on Eid al-Fitr.","The food mentioned in this wording is dates.","The narration marks a change from the Ramadan fasting routine.","No number of dates is mentioned in the provided text."],"related_hadiths":[{"id":"1755","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1756","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1722","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eating Dates Before Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet صلى الله عليه وسلم eating dates before going out on Eid al-Fitr."},"heading":{"title":"Eating Dates Before Eid al-Fitr Prayer Hadith","description":"This hadith about Eid al-Fitr records a simple practice of the Prophet صلى الله عليه وسلم. Anas bin Malik narrated that the Prophet صلى الله عليه وسلم would not go out on the Day of Fitr until he had eaten some dates. The narration focuses on eating before going out. It does not give the number of dates in this wording, so that should not be added here. The message is easy to understand: Eid al-Fitr begins with breaking from the fasting pattern before leaving for the prayer. For people searching “eating dates before Eid prayer hadith” or “Prophet ate dates on Eid al-Fitr,” this narration gives the direct text."},"teachings":["The Prophet صلى الله عليه وسلم ate before going out on Eid al-Fitr.","The food mentioned in this wording is dates.","The narration marks a change from the Ramadan fasting routine.","No number of dates is mentioned in the provided text."],"related_hadiths":[{"id":"1755","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1756","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1722","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E200" s="4" t="n"/>
@@ -5077,7 +5081,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Charity of Fitr Before Going Out","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions the Prophet صلى الله عليه وسلم giving companions from Fitr charity before going out."},"heading":{"title":"Hadith on Charity of Fitr Before Eid Outing","description":"This hadith about charity of Fitr mentions that the Prophet صلى الله عليه وسلم would not go out on the Day of Fitr until he had given his Companions some of the charity of Fitr to eat. The wording connects Eid morning with care for others and food from sadaqat al-Fitr. It does not provide all legal details about zakat al-Fitr, its amount, or timing beyond this scene. The main point is practical: before going out, there was attention to feeding from the charity of Fitr. Searchers using “charity of Fitr hadith” or “sadaqat al-Fitr before Eid prayer” will find this narration helpful."},"teachings":["The Prophet صلى الله عليه وسلم gave from the charity of Fitr before going out.","The hadith connects Eid morning with feeding others.","The narration shows care for the Companions’ food on that day.","Detailed zakat al-Fitr rules are not stated in this wording."],"related_hadiths":[{"id":"1754","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1756","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1827","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Charity of Fitr Before Going Out","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions the Prophet صلى الله عليه وسلم giving companions from Fitr charity before going out."},"heading":{"title":"Hadith on Charity of Fitr Before Eid Outing","description":"This hadith about charity of Fitr mentions that the Prophet صلى الله عليه وسلم would not go out on the Day of Fitr until he had given his Companions some of the charity of Fitr to eat. The wording connects Eid morning with care for others and food from sadaqat al-Fitr. It does not provide all legal details about zakat al-Fitr, its amount, or timing beyond this scene. The main point is practical: before going out, there was attention to feeding from the charity of Fitr. Searchers using “charity of Fitr hadith” or “sadaqat al-Fitr before Eid prayer” will find this narration helpful."},"teachings":["The Prophet صلى الله عليه وسلم gave from the charity of Fitr before going out.","The hadith connects Eid morning with feeding others.","The narration shows care for the Companions’ food on that day.","Detailed zakat al-Fitr rules are not stated in this wording."],"related_hadiths":[{"id":"1754","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1756","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1827","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E201" s="4" t="n"/>
@@ -5100,7 +5104,7 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eating on Fitr and Nahr","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith contrasts eating before Eid al-Fitr with eating after returning on the Day of Nahr."},"heading":{"title":"Hadith on Eating Before Fitr and After Nahr","description":"This hadith about Eid eating shows two different practices. On the Day of Fitr, the Messenger of Allah صلى الله عليه وسلم would not go out until he had eaten. On the Day of Nahr, he would not eat until he came back. The narration is clear because it compares two Eid days in one report. For Eid al-Fitr, eating comes before going out. For the Day of Nahr, eating is delayed until return. The hadith does not explain the reason inside this wording, so the explanation should not add one as if it were stated here. Search terms like “Eid Fitr eat before prayer hadith” match this report."},"teachings":["The Prophet صلى الله عليه وسلم ate before going out on Eid al-Fitr.","On the Day of Nahr, he ate after returning.","The hadith shows different practices for two Eid days.","The reason for the difference is not stated in this wording."],"related_hadiths":[{"id":"1754","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1755","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1722","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eating on Fitr and Nahr","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith contrasts eating before Eid al-Fitr with eating after returning on the Day of Nahr."},"heading":{"title":"Hadith on Eating Before Fitr and After Nahr","description":"This hadith about Eid eating shows two different practices. On the Day of Fitr, the Messenger of Allah صلى الله عليه وسلم would not go out until he had eaten. On the Day of Nahr, he would not eat until he came back. The narration is clear because it compares two Eid days in one report. For Eid al-Fitr, eating comes before going out. For the Day of Nahr, eating is delayed until return. The hadith does not explain the reason inside this wording, so the explanation should not add one as if it were stated here. Search terms like “Eid Fitr eat before prayer hadith” match this report."},"teachings":["The Prophet صلى الله عليه وسلم ate before going out on Eid al-Fitr.","On the Day of Nahr, he ate after returning.","The hadith shows different practices for two Eid days.","The reason for the difference is not stated in this wording."],"related_hadiths":[{"id":"1754","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1755","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1722","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E202" s="4" t="n"/>
@@ -5123,7 +5127,7 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Feeding for Deceased Owing Fasts","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says one poor person should be fed for each day owed by a deceased person."},"heading":{"title":"Hadith on Feeding for Missed Fasts After Death","description":"This hadith about missed fasts after death gives a specific instruction. The Messenger of Allah صلى الله عليه وسلم said that whoever dies owing the fasts of a month, one poor person should be fed on his behalf for each day. The wording focuses on feeding a poor person for each missed day. It does not mention every possible case of missed fasting, nor does it describe who must do it in detail. So the explanation should stay with the text. For searchers asking “what if someone dies owing fasts” or “feeding poor for missed fasts hadith,” this narration gives a direct answer from the wording provided."},"teachings":["A deceased person’s owed fasts are treated seriously in this narration.","The hadith mentions feeding one poor person for each missed day.","The wording is about a month of owed fasts.","Extra case details are not included in this text."],"related_hadiths":[{"id":"1758","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1759","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1760","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Feeding for Deceased Owing Fasts","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says one poor person should be fed for each day owed by a deceased person."},"heading":{"title":"Hadith on Feeding for Missed Fasts After Death","description":"This hadith about missed fasts after death gives a specific instruction. The Messenger of Allah صلى الله عليه وسلم said that whoever dies owing the fasts of a month, one poor person should be fed on his behalf for each day. The wording focuses on feeding a poor person for each missed day. It does not mention every possible case of missed fasting, nor does it describe who must do it in detail. So the explanation should stay with the text. For searchers asking “what if someone dies owing fasts” or “feeding poor for missed fasts hadith,” this narration gives a direct answer from the wording provided."},"teachings":["A deceased person’s owed fasts are treated seriously in this narration.","The hadith mentions feeding one poor person for each missed day.","The wording is about a month of owed fasts.","Extra case details are not included in this text."],"related_hadiths":[{"id":"1758","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1759","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1760","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E203" s="4" t="n"/>
@@ -5146,7 +5150,7 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Right Is Greater","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith compares owed fasts to debt and says Allah’s right is greater."},"heading":{"title":"Hadith on Fasting Debt and the Right of Allah","description":"This hadith about fasting debt after death records a woman asking about her sister, who died while owing two consecutive months of fasting. The Prophet صلى الله عليه وسلم answered with a comparison: if her sister had a debt, would she pay it? She said yes. He then said, “The right of Allah is greater.” The text teaches that owed worship should not be ignored. It uses a simple example everyone understands: debt. The narration does not give every legal detail about who must fast or feed in every situation. It simply shows that the obligation owed to Allah deserves serious attention. This fits searches like “right of Allah is greater hadith.”"},"teachings":["Owed fasts are compared to a debt in the Prophet’s صلى الله عليه وسلم answer.","The right of Allah is described as greater.","The woman’s concern for her deceased sister is treated seriously.","The hadith uses an easy example to explain responsibility."],"related_hadiths":[{"id":"1757","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1759","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1953","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Right Is Greater","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith compares owed fasts to debt and says Allah’s right is greater."},"heading":{"title":"Hadith on Fasting Debt and the Right of Allah","description":"This hadith about fasting debt after death records a woman asking about her sister, who died while owing two consecutive months of fasting. The Prophet صلى الله عليه وسلم answered with a comparison: if her sister had a debt, would she pay it? She said yes. He then said, “The right of Allah is greater.” The text teaches that owed worship should not be ignored. It uses a simple example everyone understands: debt. The narration does not give every legal detail about who must fast or feed in every situation. It simply shows that the obligation owed to Allah deserves serious attention. This fits searches like “right of Allah is greater hadith.”"},"teachings":["Owed fasts are compared to a debt in the Prophet’s صلى الله عليه وسلم answer.","The right of Allah is described as greater.","The woman’s concern for her deceased sister is treated seriously.","The hadith uses an easy example to explain responsibility."],"related_hadiths":[{"id":"1757","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1759","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1953","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E204" s="4" t="n"/>
@@ -5169,7 +5173,7 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fasting for Deceased Parent","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith allows fasting on behalf of a mother who died owing a fast."},"heading":{"title":"Hadith on Fasting on Behalf of a Deceased Mother","description":"This hadith about fasting on behalf of the deceased is very direct. A woman came to the Prophet صلى الله عليه وسلم and said that her mother had died while owing a fast. She asked, “Should I fast on her behalf?” The Prophet صلى الله عليه وسلم answered, “Yes.” The narration shows concern for a parent after death and gives a clear reply in this case. It does not describe every type of fast or every family situation, so it should not be stretched beyond its wording without scholar guidance. For searchers typing “can I fast for my deceased mother hadith” or “mother died owing fast,” this narration gives the exact core answer."},"teachings":["A woman asked about her mother who died owing a fast.","The Prophet صلى الله عليه وسلم answered that she may fast on her behalf.","The hadith shows care for a parent’s owed worship.","The wording is direct but does not cover every possible case."],"related_hadiths":[{"id":"1757","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1758","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1953","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fasting for Deceased Parent","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith allows fasting on behalf of a mother who died owing a fast."},"heading":{"title":"Hadith on Fasting on Behalf of a Deceased Mother","description":"This hadith about fasting on behalf of the deceased is very direct. A woman came to the Prophet صلى الله عليه وسلم and said that her mother had died while owing a fast. She asked, “Should I fast on her behalf?” The Prophet صلى الله عليه وسلم answered, “Yes.” The narration shows concern for a parent after death and gives a clear reply in this case. It does not describe every type of fast or every family situation, so it should not be stretched beyond its wording without scholar guidance. For searchers typing “can I fast for my deceased mother hadith” or “mother died owing fast,” this narration gives the exact core answer."},"teachings":["A woman asked about her mother who died owing a fast.","The Prophet صلى الله عليه وسلم answered that she may fast on her behalf.","The hadith shows care for a parent’s owed worship.","The wording is direct but does not cover every possible case."],"related_hadiths":[{"id":"1757","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1758","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1953","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E205" s="4" t="n"/>
@@ -5192,7 +5196,7 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | New Muslims Fasting Remaining Ramadan","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says Thaqif fasted what remained of Ramadan after becoming Muslim."},"heading":{"title":"Hadith on New Muslims Fasting the Rest of Ramadan","description":"This hadith about Ramadan fasting tells of the delegation of Thaqif who came to the Messenger of Allah صلى الله عليه وسلم in Ramadan to announce their Islam. A tent was set up for them in the mosque. When they became Muslim, they fasted what was left of the month. The wording focuses on what happened after Islam: they joined the remaining days of Ramadan fasting. It does not discuss making up earlier days before Islam in this text. So the message should stay simple: once they entered Islam during Ramadan, they fasted the rest of it. Searchers asking “new Muslim fasting Ramadan hadith” will find this narration directly relevant."},"teachings":["The delegation came to the Prophet صلى الله عليه وسلم during Ramadan.","After becoming Muslim, they fasted the remaining days of the month.","The narration shows immediate joining in Ramadan worship.","The text does not mention making up earlier days."],"related_hadiths":[{"id":"1641","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1638","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1758","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | New Muslims Fasting Remaining Ramadan","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says Thaqif fasted what remained of Ramadan after becoming Muslim."},"heading":{"title":"Hadith on New Muslims Fasting the Rest of Ramadan","description":"This hadith about Ramadan fasting tells of the delegation of Thaqif who came to the Messenger of Allah صلى الله عليه وسلم in Ramadan to announce their Islam. A tent was set up for them in the mosque. When they became Muslim, they fasted what was left of the month. The wording focuses on what happened after Islam: they joined the remaining days of Ramadan fasting. It does not discuss making up earlier days before Islam in this text. So the message should stay simple: once they entered Islam during Ramadan, they fasted the rest of it. Searchers asking “new Muslim fasting Ramadan hadith” will find this narration directly relevant."},"teachings":["The delegation came to the Prophet صلى الله عليه وسلم during Ramadan.","After becoming Muslim, they fasted the remaining days of the month.","The narration shows immediate joining in Ramadan worship.","The text does not mention making up earlier days."],"related_hadiths":[{"id":"1641","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1638","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1758","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E206" s="4" t="n"/>
@@ -5215,7 +5219,7 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Voluntary Fasting with Permission","description":"$book_name$ $hadith_number$ - $chapter_name$. Voluntary fasting outside Ramadan is linked with care, permission, and family rights when the husband is present."},"heading":{"title":"Hadith About Fasting Without Husband Permission","description":"This hadith about fasting without husband permission teaches a clear point about voluntary fasting outside Ramadan. The Prophet صلى الله عليه وسلم said that when a woman’s husband is present, she should not fast any day apart from Ramadan without his permission. The text focuses on non-Ramadan fasting, so the main lesson is about voluntary fasts, not the required fasts of Ramadan. It shows that worship should be practiced with awareness of family rights and responsibilities. The hadith does not lower the value of fasting. Rather, it places voluntary fasting within the balance of married life. A believer should love worship, but also avoid causing avoidable difficulty in the home."},"teachings":["Voluntary fasting outside Ramadan should be done with care for family rights.","The hadith specifically mentions the case when the husband is present.","Ramadan fasting is treated separately from optional fasting in this narration.","Worship should be balanced with duties toward people close to us."],"related_hadiths":[{"id":"1762","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1763","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Voluntary Fasting with Permission","description":"$book_name$ $hadith_number$ - $chapter_name$. Voluntary fasting outside Ramadan is linked with care, permission, and family rights when the husband is present."},"heading":{"title":"Hadith About Fasting Without Husband Permission","description":"This hadith about fasting without husband permission teaches a clear point about voluntary fasting outside Ramadan. The Prophet صلى الله عليه وسلم said that when a woman’s husband is present, she should not fast any day apart from Ramadan without his permission. The text focuses on non-Ramadan fasting, so the main lesson is about voluntary fasts, not the required fasts of Ramadan. It shows that worship should be practiced with awareness of family rights and responsibilities. The hadith does not lower the value of fasting. Rather, it places voluntary fasting within the balance of married life. A believer should love worship, but also avoid causing avoidable difficulty in the home."},"teachings":["Voluntary fasting outside Ramadan should be done with care for family rights.","The hadith specifically mentions the case when the husband is present.","Ramadan fasting is treated separately from optional fasting in this narration.","Worship should be balanced with duties toward people close to us."],"related_hadiths":[{"id":"1762","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1763","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E207" s="4" t="n"/>
@@ -5238,7 +5242,7 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women and Voluntary Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم forbade women from fasting without their husbands’ permission, showing balance in optional worship."},"heading":{"title":"Women Fasting Without Permission Hadith","description":"This women fasting without permission hadith gives a short but serious instruction. Abu Sa’eed narrated that the Messenger of Allah صلى الله عليه وسلم forbade women from fasting without the permission of their husbands. The text does not mention Ramadan directly, but it is placed with narrations about fasting permission, so the focus is on optional fasting. The lesson is not that fasting is disliked. Fasting remains an act of worship. The point here is that voluntary worship should not ignore the rights of marriage. A Muslim home needs mercy, communication, and balance. This hadith reminds believers that even good deeds should be done in a way that does not create harm or tension."},"teachings":["Optional fasting should be connected with communication in married life.","The narration points to the husband’s permission in this specific case.","Good deeds should not lead to neglecting close personal rights.","The Prophet صلى الله عليه وسلم taught balance between worship and household duties."],"related_hadiths":[{"id":"1761","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1763","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women and Voluntary Fasting","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم forbade women from fasting without their husbands’ permission, showing balance in optional worship."},"heading":{"title":"Women Fasting Without Permission Hadith","description":"This women fasting without permission hadith gives a short but serious instruction. Abu Sa’eed narrated that the Messenger of Allah صلى الله عليه وسلم forbade women from fasting without the permission of their husbands. The text does not mention Ramadan directly, but it is placed with narrations about fasting permission, so the focus is on optional fasting. The lesson is not that fasting is disliked. Fasting remains an act of worship. The point here is that voluntary worship should not ignore the rights of marriage. A Muslim home needs mercy, communication, and balance. This hadith reminds believers that even good deeds should be done in a way that does not create harm or tension."},"teachings":["Optional fasting should be connected with communication in married life.","The narration points to the husband’s permission in this specific case.","Good deeds should not lead to neglecting close personal rights.","The Prophet صلى الله عليه وسلم taught balance between worship and household duties."],"related_hadiths":[{"id":"1761","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1763","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E208" s="4" t="n"/>
@@ -5261,7 +5265,7 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Guest Fasting with Permission","description":"$book_name$ $hadith_number$ - $chapter_name$. A guest should not fast without the host people’s permission, teaching manners and care in social life."},"heading":{"title":"Hadith About Guest Fasting Permission","description":"This hadith about guest fasting permission teaches manners during a stay with other people. The Prophet صلى الله عليه وسلم said that if a man stays among a people, he should not fast without their permission. The wording points to a guest or someone living temporarily with a group. Fasting is an act of worship, but the hadith shows that worship should be done with good manners toward hosts. A host may prepare food, expect the guest to eat, or feel concerned if the guest refuses. The hadith does not give a long legal discussion. It simply teaches a clean social rule: when staying with others, be thoughtful and do not make personal worship a cause of awkwardness or trouble."},"teachings":["A guest should be considerate of the people hosting him.","Voluntary fasting can involve social manners when staying with others.","Permission helps avoid discomfort between guest and host.","Personal worship should not ignore the feelings of others."],"related_hadiths":[{"id":"1761","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1762","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Guest Fasting with Permission","description":"$book_name$ $hadith_number$ - $chapter_name$. A guest should not fast without the host people’s permission, teaching manners and care in social life."},"heading":{"title":"Hadith About Guest Fasting Permission","description":"This hadith about guest fasting permission teaches manners during a stay with other people. The Prophet صلى الله عليه وسلم said that if a man stays among a people, he should not fast without their permission. The wording points to a guest or someone living temporarily with a group. Fasting is an act of worship, but the hadith shows that worship should be done with good manners toward hosts. A host may prepare food, expect the guest to eat, or feel concerned if the guest refuses. The hadith does not give a long legal discussion. It simply teaches a clean social rule: when staying with others, be thoughtful and do not make personal worship a cause of awkwardness or trouble."},"teachings":["A guest should be considerate of the people hosting him.","Voluntary fasting can involve social manners when staying with others.","Permission helps avoid discomfort between guest and host.","Personal worship should not ignore the feelings of others."],"related_hadiths":[{"id":"1761","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1762","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E209" s="4" t="n"/>
@@ -5284,7 +5288,7 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward of the Grateful Eater","description":"$book_name$ $hadith_number$ - $chapter_name$. A grateful eater receives a reward like a patient fasting person, highlighting thankfulness in everyday blessings."},"heading":{"title":"Reward of Grateful Eater Hadith","description":"This reward of grateful eater hadith gives a simple but deep teaching. The Messenger of Allah صلى الله عليه وسلم said that a grateful eater will have a reward like that of a patient fasting person. The hadith mentions two qualities: gratitude and patience. The eater is praised because he is thankful, not simply because he eats. The fasting person is praised because he is patient, not simply because he is hungry. This helps us see that the state of the heart matters. Food can become a moment of worship when a person receives it with thankfulness. Fasting can become a strong act of worship when a person bears it with patience."},"teachings":["Gratitude while eating is given special value in this narration.","Patience while fasting is also praised clearly.","The hadith encourages a thankful heart in normal daily life.","Reward is connected to the inner quality behind the action."],"related_hadiths":[{"id":"1764","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1766","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward of the Grateful Eater","description":"$book_name$ $hadith_number$ - $chapter_name$. A grateful eater receives a reward like a patient fasting person, highlighting thankfulness in everyday blessings."},"heading":{"title":"Reward of Grateful Eater Hadith","description":"This reward of grateful eater hadith gives a simple but deep teaching. The Messenger of Allah صلى الله عليه وسلم said that a grateful eater will have a reward like that of a patient fasting person. The hadith mentions two qualities: gratitude and patience. The eater is praised because he is thankful, not simply because he eats. The fasting person is praised because he is patient, not simply because he is hungry. This helps us see that the state of the heart matters. Food can become a moment of worship when a person receives it with thankfulness. Fasting can become a strong act of worship when a person bears it with patience."},"teachings":["Gratitude while eating is given special value in this narration.","Patience while fasting is also praised clearly.","The hadith encourages a thankful heart in normal daily life.","Reward is connected to the inner quality behind the action."],"related_hadiths":[{"id":"1764","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1766","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E210" s="4" t="n"/>
@@ -5307,7 +5311,7 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seek Laylatul Qadr in Odd Nights","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم directed believers to seek Lailatul-Qadr in the last ten nights, especially the odd nights."},"heading":{"title":"Laylatul Qadr Odd Nights Hadith","description":"This Laylatul Qadr odd nights hadith gives a clear direction for Ramadan worship. Abu Sa’eed Al-Khudri said that they observed I’tikaf with the Messenger of Allah صلى الله عليه وسلم during the middle ten days of Ramadan. The Prophet صلى الله عليه وسلم then said that he had been shown Lailatul-Qadr and was caused to forget it. He told them to seek it in the last ten nights, on the odd-numbered nights. The hadith focuses on effort, searching, and worship in the last part of Ramadan. It does not name one fixed night here. Instead, it pushes believers to stay active and hopeful across the final odd nights."},"teachings":["Lailatul-Qadr should be sought in the last ten nights of Ramadan.","The hadith gives special focus to the odd-numbered nights.","I’tikaf is connected here with seeking Lailatul-Qadr.","Not knowing the exact night encourages continued worship."],"related_hadiths":[{"id":"1767","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1768","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seek Laylatul Qadr in Odd Nights","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم directed believers to seek Lailatul-Qadr in the last ten nights, especially the odd nights."},"heading":{"title":"Laylatul Qadr Odd Nights Hadith","description":"This Laylatul Qadr odd nights hadith gives a clear direction for Ramadan worship. Abu Sa’eed Al-Khudri said that they observed I’tikaf with the Messenger of Allah صلى الله عليه وسلم during the middle ten days of Ramadan. The Prophet صلى الله عليه وسلم then said that he had been shown Lailatul-Qadr and was caused to forget it. He told them to seek it in the last ten nights, on the odd-numbered nights. The hadith focuses on effort, searching, and worship in the last part of Ramadan. It does not name one fixed night here. Instead, it pushes believers to stay active and hopeful across the final odd nights."},"teachings":["Lailatul-Qadr should be sought in the last ten nights of Ramadan.","The hadith gives special focus to the odd-numbered nights.","I’tikaf is connected here with seeking Lailatul-Qadr.","Not knowing the exact night encourages continued worship."],"related_hadiths":[{"id":"1767","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1768","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E211" s="4" t="n"/>
@@ -5330,7 +5334,7 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Worship in the Last Ten Nights","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used to strive harder in worship during the last ten nights of Ramadan than at other times."},"heading":{"title":"Last Ten Nights of Ramadan Worship Hadith","description":"This last ten nights of Ramadan worship hadith shows the Prophet’s صلى الله عليه وسلم special effort near the end of Ramadan. Aishah said that the Prophet صلى الله عليه وسلم used to strive hard in worship in the last ten nights as he never did at any other time. The wording is simple and powerful. It does not list every act of worship in this narration. It highlights increased effort. The hadith teaches that the last ten nights are not ordinary nights for a believer. They deserve more focus, more worship, and more serious attention. It also shows that the Prophet صلى الله عليه وسلم gave these nights a special place through his own practice."},"teachings":["The last ten nights of Ramadan deserve extra effort in worship.","The Prophet صلى الله عليه وسلم gave these nights special attention.","The hadith encourages increased devotion without naming every act.","A believer can use the end of Ramadan for stronger worship."],"related_hadiths":[{"id":"1766","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1768","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Worship in the Last Ten Nights","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used to strive harder in worship during the last ten nights of Ramadan than at other times."},"heading":{"title":"Last Ten Nights of Ramadan Worship Hadith","description":"This last ten nights of Ramadan worship hadith shows the Prophet’s صلى الله عليه وسلم special effort near the end of Ramadan. Aishah said that the Prophet صلى الله عليه وسلم used to strive hard in worship in the last ten nights as he never did at any other time. The wording is simple and powerful. It does not list every act of worship in this narration. It highlights increased effort. The hadith teaches that the last ten nights are not ordinary nights for a believer. They deserve more focus, more worship, and more serious attention. It also shows that the Prophet صلى الله عليه وسلم gave these nights a special place through his own practice."},"teachings":["The last ten nights of Ramadan deserve extra effort in worship.","The Prophet صلى الله عليه وسلم gave these nights special attention.","The hadith encourages increased devotion without naming every act.","A believer can use the end of Ramadan for stronger worship."],"related_hadiths":[{"id":"1766","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1768","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E212" s="4" t="n"/>
@@ -5353,7 +5357,7 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Night Worship in Last Ten Days","description":"$book_name$ $hadith_number$ - $chapter_name$. When the last ten days began, the Prophet صلى الله عليه وسلم stayed up at night and woke his family for prayer."},"heading":{"title":"Prophet Stayed Up in Last Ten Nights Hadith","description":"This Prophet stayed up in last ten nights hadith gives a clear picture of Ramadan devotion in the home. Aishah said that when the last ten days of Ramadan began, the Prophet صلى الله عليه وسلم used to stay up at night, tighten his waist-wrap, and wake up his family. The narration shows personal worship and family encouragement together. It does not only speak about private effort. It also shows that the Prophet صلى الله عليه وسلم involved his family in prayer during these special nights. The phrase about tightening the waist-wrap points to serious effort in this text. The main lesson is simple: the last ten nights call for wakefulness, worship, and shared attention to Allah."},"teachings":["The Prophet صلى الله عليه وسلم stayed up at night during the last ten days of Ramadan.","He woke his family, showing care for their worship too.","The hadith points to serious effort during these nights.","Ramadan worship can include both personal and family devotion."],"related_hadiths":[{"id":"1766","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1767","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Night Worship in Last Ten Days","description":"$book_name$ $hadith_number$ - $chapter_name$. When the last ten days began, the Prophet صلى الله عليه وسلم stayed up at night and woke his family for prayer."},"heading":{"title":"Prophet Stayed Up in Last Ten Nights Hadith","description":"This Prophet stayed up in last ten nights hadith gives a clear picture of Ramadan devotion in the home. Aishah said that when the last ten days of Ramadan began, the Prophet صلى الله عليه وسلم used to stay up at night, tighten his waist-wrap, and wake up his family. The narration shows personal worship and family encouragement together. It does not only speak about private effort. It also shows that the Prophet صلى الله عليه وسلم involved his family in prayer during these special nights. The phrase about tightening the waist-wrap points to serious effort in this text. The main lesson is simple: the last ten nights call for wakefulness, worship, and shared attention to Allah."},"teachings":["The Prophet صلى الله عليه وسلم stayed up at night during the last ten days of Ramadan.","He woke his family, showing care for their worship too.","The hadith points to serious effort during these nights.","Ramadan worship can include both personal and family devotion."],"related_hadiths":[{"id":"1766","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1767","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E213" s="4" t="n"/>
@@ -5376,7 +5380,7 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Annual I'tikaf and Qur'an Review","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم observed I'tikaf yearly, and in his final year he observed it for twenty days."},"heading":{"title":"Prophet I'tikaf Every Year Hadith","description":"This Prophet I'tikaf every year hadith shows a repeated Ramadan practice. Abu Hurairah said that the Prophet صلى الله عليه وسلم used to observe I'tikaf for ten days every year. In the year in which he passed away, he observed I'tikaf for twenty days. The narration also says that the Qur'an would be reviewed with him once every year, but in that final year it was reviewed twice. The hadith connects I'tikaf with a strong focus on the Qur'an and worship. It does not ask every person to copy the final-year length in every situation. It reports what happened in the Prophet’s صلى الله عليه وسلم practice, showing regular devotion and a special increase in his final year."},"teachings":["The Prophet صلى الله عليه وسلم regularly observed I'tikaf for ten days each year.","In his final year, his I'tikaf was extended to twenty days.","The Qur'an review was also increased in that final year.","The hadith highlights consistency and added worship at special times."],"related_hadiths":[{"id":"1770","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1773","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Annual I'tikaf and Qur'an Review","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم observed I'tikaf yearly, and in his final year he observed it for twenty days."},"heading":{"title":"Prophet I'tikaf Every Year Hadith","description":"This Prophet I'tikaf every year hadith shows a repeated Ramadan practice. Abu Hurairah said that the Prophet صلى الله عليه وسلم used to observe I'tikaf for ten days every year. In the year in which he passed away, he observed I'tikaf for twenty days. The narration also says that the Qur'an would be reviewed with him once every year, but in that final year it was reviewed twice. The hadith connects I'tikaf with a strong focus on the Qur'an and worship. It does not ask every person to copy the final-year length in every situation. It reports what happened in the Prophet’s صلى الله عليه وسلم practice, showing regular devotion and a special increase in his final year."},"teachings":["The Prophet صلى الله عليه وسلم regularly observed I'tikaf for ten days each year.","In his final year, his I'tikaf was extended to twenty days.","The Qur'an review was also increased in that final year.","The hadith highlights consistency and added worship at special times."],"related_hadiths":[{"id":"1770","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1773","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E214" s="4" t="n"/>
@@ -5399,7 +5403,7 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Making Up I'tikaf","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم usually made I'tikaf in the last ten days, then observed twenty days the next year after travel."},"heading":{"title":"Making Up I'tikaf Hadith","description":"This making up I'tikaf hadith reports a clear event from the Prophet’s صلى الله عليه وسلم practice. Ubayy bin Ka’b narrated that the Prophet صلى الله عليه وسلم used to spend the last ten days of Ramadan in I'tikaf. One year he was traveling, so the following year he spent twenty days in I'tikaf. The text shows that I'tikaf in the last ten days was his regular habit. It also shows an increase the next year after a year in which travel took place. The hadith does not give a long rule for every missed act. It simply reports the Prophet’s صلى الله عليه وسلم action and shows care for this worship even when travel changed the usual routine."},"teachings":["The Prophet صلى الله عليه وسلم used to observe I'tikaf in the last ten days of Ramadan.","Travel affected his usual I'tikaf in one year.","The following year he observed twenty days of I'tikaf.","The hadith shows strong care for continuing this worship."],"related_hadiths":[{"id":"1769","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1773","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Making Up I'tikaf","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم usually made I'tikaf in the last ten days, then observed twenty days the next year after travel."},"heading":{"title":"Making Up I'tikaf Hadith","description":"This making up I'tikaf hadith reports a clear event from the Prophet’s صلى الله عليه وسلم practice. Ubayy bin Ka’b narrated that the Prophet صلى الله عليه وسلم used to spend the last ten days of Ramadan in I'tikaf. One year he was traveling, so the following year he spent twenty days in I'tikaf. The text shows that I'tikaf in the last ten days was his regular habit. It also shows an increase the next year after a year in which travel took place. The hadith does not give a long rule for every missed act. It simply reports the Prophet’s صلى الله عليه وسلم action and shows care for this worship even when travel changed the usual routine."},"teachings":["The Prophet صلى الله عليه وسلم used to observe I'tikaf in the last ten days of Ramadan.","Travel affected his usual I'tikaf in one year.","The following year he observed twenty days of I'tikaf.","The hadith shows strong care for continuing this worship."],"related_hadiths":[{"id":"1769","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1773","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E215" s="4" t="n"/>
@@ -5422,7 +5426,7 @@
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Starting I'tikaf After Subh","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم entered his I'tikaf place after Subh, then later observed ten days in Shawwal."},"heading":{"title":"Starting I'tikaf After Subh Hadith","description":"This starting I'tikaf after Subh hadith describes how the Prophet صلى الله عليه وسلم began I'tikaf in one reported event. Aishah said that when he wanted to start I'tikaf, he would pray Subh and then enter the place where he intended to observe I'tikaf. In this narration, he planned I'tikaf in the last ten days of Ramadan and ordered a tent to be set up. Then tents were also set up for Aishah, Hafsah, and Zainab. When he saw that, he asked whether righteousness was what they sought. He did not observe I'tikaf in Ramadan then, but observed ten days in Shawwal. The hadith highlights intention, order, and careful correction."},"teachings":["The Prophet صلى الله عليه وسلم entered his I'tikaf place after praying Subh in this narration.","A tent was prepared for his planned I'tikaf.","He questioned the motives when several tents appeared.","He later observed ten days of I'tikaf in Shawwal."],"related_hadiths":[{"id":"1773","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1776","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Starting I'tikaf After Subh","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم entered his I'tikaf place after Subh, then later observed ten days in Shawwal."},"heading":{"title":"Starting I'tikaf After Subh Hadith","description":"This starting I'tikaf after Subh hadith describes how the Prophet صلى الله عليه وسلم began I'tikaf in one reported event. Aishah said that when he wanted to start I'tikaf, he would pray Subh and then enter the place where he intended to observe I'tikaf. In this narration, he planned I'tikaf in the last ten days of Ramadan and ordered a tent to be set up. Then tents were also set up for Aishah, Hafsah, and Zainab. When he saw that, he asked whether righteousness was what they sought. He did not observe I'tikaf in Ramadan then, but observed ten days in Shawwal. The hadith highlights intention, order, and careful correction."},"teachings":["The Prophet صلى الله عليه وسلم entered his I'tikaf place after praying Subh in this narration.","A tent was prepared for his planned I'tikaf.","He questioned the motives when several tents appeared.","He later observed ten days of I'tikaf in Shawwal."],"related_hadiths":[{"id":"1773","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1776","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E216" s="4" t="n"/>
@@ -5445,7 +5449,7 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Vow to Perform I'tikaf","description":"$book_name$ $hadith_number$ - $chapter_name$. Umar asked about a vow to spend one night in I'tikaf, and the Prophet صلى الله عليه وسلم commanded him to fulfill it."},"heading":{"title":"Vow to Spend a Night in I'tikaf Hadith","description":"This vow to spend a night in I'tikaf hadith is about fulfilling a vow connected to worship. Umar had made a vow during the days of Ignorance to spend one night in I'tikaf. He asked the Prophet صلى الله عليه وسلم about it, and the Prophet صلى الله عليه وسلم commanded him to spend it in I'tikaf. The hadith does not mention many details about the vow, the place, or extra actions. It focuses on the Prophet’s صلى الله عليه وسلم answer. A vow related to I'tikaf was not treated as something to ignore. Umar asked before acting, and he was guided to carry it out. The simple lesson is to seek guidance and take vows seriously."},"teachings":["Umar asked the Prophet صلى الله عليه وسلم before acting on his vow.","The Prophet صلى الله عليه وسلم commanded him to fulfill the I'tikaf vow.","The narration shows seriousness in matters of vows.","A believer should seek guidance when unsure about worship."],"related_hadiths":[{"id":"1773","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1770","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Vow to Perform I'tikaf","description":"$book_name$ $hadith_number$ - $chapter_name$. Umar asked about a vow to spend one night in I'tikaf, and the Prophet صلى الله عليه وسلم commanded him to fulfill it."},"heading":{"title":"Vow to Spend a Night in I'tikaf Hadith","description":"This vow to spend a night in I'tikaf hadith is about fulfilling a vow connected to worship. Umar had made a vow during the days of Ignorance to spend one night in I'tikaf. He asked the Prophet صلى الله عليه وسلم about it, and the Prophet صلى الله عليه وسلم commanded him to spend it in I'tikaf. The hadith does not mention many details about the vow, the place, or extra actions. It focuses on the Prophet’s صلى الله عليه وسلم answer. A vow related to I'tikaf was not treated as something to ignore. Umar asked before acting, and he was guided to carry it out. The simple lesson is to seek guidance and take vows seriously."},"teachings":["Umar asked the Prophet صلى الله عليه وسلم before acting on his vow.","The Prophet صلى الله عليه وسلم commanded him to fulfill the I'tikaf vow.","The narration shows seriousness in matters of vows.","A believer should seek guidance when unsure about worship."],"related_hadiths":[{"id":"1773","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1770","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E217" s="4" t="n"/>
@@ -5468,7 +5472,7 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | I'tikaf in the Last Ten Days","description":"$book_name$ $hadith_number$ - $chapter_name$. The Messenger صلى الله عليه وسلم used to spend the last ten days of Ramadan in I'tikaf at a known place."},"heading":{"title":"I'tikaf in Last Ten Days of Ramadan Hadith","description":"This I'tikaf in last ten days of Ramadan hadith gives a simple report of the Prophet’s صلى الله عليه وسلم regular practice. Abdullah bin Umar narrated that the Messenger of Allah صلى الله عليه وسلم used to spend the last ten days of Ramadan in I'tikaf. Nafi' added that Abdullah bin Umar showed him the place where the Messenger of Allah صلى الله عليه وسلم used to observe I'tikaf. The hadith focuses on the timing and the remembered place of this worship. It does not add a list of rules. It shows that I'tikaf in the last ten days was a known practice from the Prophet صلى الله عليه وسلم and was remembered by his Companions with care."},"teachings":["The Prophet صلى الله عليه وسلم used to observe I'tikaf in the last ten days of Ramadan.","The place of his I'tikaf was remembered and shown by Ibn Umar.","The hadith highlights a repeated Ramadan practice.","I'tikaf is linked here with the final part of Ramadan."],"related_hadiths":[{"id":"1769","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1770","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | I'tikaf in the Last Ten Days","description":"$book_name$ $hadith_number$ - $chapter_name$. The Messenger صلى الله عليه وسلم used to spend the last ten days of Ramadan in I'tikaf at a known place."},"heading":{"title":"I'tikaf in Last Ten Days of Ramadan Hadith","description":"This I'tikaf in last ten days of Ramadan hadith gives a simple report of the Prophet’s صلى الله عليه وسلم regular practice. Abdullah bin Umar narrated that the Messenger of Allah صلى الله عليه وسلم used to spend the last ten days of Ramadan in I'tikaf. Nafi' added that Abdullah bin Umar showed him the place where the Messenger of Allah صلى الله عليه وسلم used to observe I'tikaf. The hadith focuses on the timing and the remembered place of this worship. It does not add a list of rules. It shows that I'tikaf in the last ten days was a known practice from the Prophet صلى الله عليه وسلم and was remembered by his Companions with care."},"teachings":["The Prophet صلى الله عليه وسلم used to observe I'tikaf in the last ten days of Ramadan.","The place of his I'tikaf was remembered and shown by Ibn Umar.","The hadith highlights a repeated Ramadan practice.","I'tikaf is linked here with the final part of Ramadan."],"related_hadiths":[{"id":"1769","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1770","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E218" s="4" t="n"/>
@@ -5491,7 +5495,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet’s I'tikaf Bedding","description":"$book_name$ $hadith_number$ - $chapter_name$. During I'tikaf, the Prophet’s صلى الله عليه وسلم bedding or bed was placed behind the Pillar of Repentance."},"heading":{"title":"Prophet’s Bedding During I'tikaf Hadith","description":"This Prophet’s bedding during I'tikaf hadith gives a small but vivid detail about the Prophet’s صلى الله عليه وسلم I'tikaf. Ibn Umar narrated that when the Prophet صلى الله عليه وسلم observed I'tikaf, his bedding would be spread for him, or his bed would be placed behind the Pillar of Repentance. The narration does not give a long teaching in direct words. It describes the practical setup of his stay in the mosque during I'tikaf. This helps readers picture I'tikaf as a real period of staying in a set place for worship. The hadith also shows that simple arrangements for rest were part of that stay, without turning it into comfort-seeking."},"teachings":["The Prophet صلى الله عليه وسلم had a set place arranged during I'tikaf.","His bedding or bed was placed behind the Pillar of Repentance.","The hadith shows the practical side of staying in I'tikaf.","I'tikaf involved worship while allowing simple needed arrangements."],"related_hadiths":[{"id":"1773","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1775","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet’s I'tikaf Bedding","description":"$book_name$ $hadith_number$ - $chapter_name$. During I'tikaf, the Prophet’s صلى الله عليه وسلم bedding or bed was placed behind the Pillar of Repentance."},"heading":{"title":"Prophet’s Bedding During I'tikaf Hadith","description":"This Prophet’s bedding during I'tikaf hadith gives a small but vivid detail about the Prophet’s صلى الله عليه وسلم I'tikaf. Ibn Umar narrated that when the Prophet صلى الله عليه وسلم observed I'tikaf, his bedding would be spread for him, or his bed would be placed behind the Pillar of Repentance. The narration does not give a long teaching in direct words. It describes the practical setup of his stay in the mosque during I'tikaf. This helps readers picture I'tikaf as a real period of staying in a set place for worship. The hadith also shows that simple arrangements for rest were part of that stay, without turning it into comfort-seeking."},"teachings":["The Prophet صلى الله عليه وسلم had a set place arranged during I'tikaf.","His bedding or bed was placed behind the Pillar of Repentance.","The hadith shows the practical side of staying in I'tikaf.","I'tikaf involved worship while allowing simple needed arrangements."],"related_hadiths":[{"id":"1773","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1775","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E219" s="4" t="n"/>
@@ -5514,7 +5518,7 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | I'tikaf in a Tent","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم observed I'tikaf in a tent and spoke to the people after moving the reed mat."},"heading":{"title":"I'tikaf in a Tent Hadith","description":"This I'tikaf in a tent hadith describes a scene from the Prophet’s صلى الله عليه وسلم I'tikaf. Abu Sa’eed Al-Khudri narrated that the Messenger of Allah صلى الله عليه وسلم observed I'tikaf in a Turkish tent, and over its door was a piece of reed matting. He moved the mat aside, put his head out, and spoke to the people. The hadith shows that I'tikaf included seclusion, but it was not complete silence from all people in every moment. In this report, the Prophet صلى الله عليه وسلم spoke to the people while remaining in the setting of I'tikaf. The focus stays on the described action: a tent, a covering, and communication with the people."},"teachings":["The Prophet صلى الله عليه وسلم observed I'tikaf in a tent in this narration.","A reed mat covered the doorway of the tent.","He moved the mat and spoke to the people.","The hadith shows a practical example of seclusion during I'tikaf."],"related_hadiths":[{"id":"1774","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1779","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | I'tikaf in a Tent","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم observed I'tikaf in a tent and spoke to the people after moving the reed mat."},"heading":{"title":"I'tikaf in a Tent Hadith","description":"This I'tikaf in a tent hadith describes a scene from the Prophet’s صلى الله عليه وسلم I'tikaf. Abu Sa’eed Al-Khudri narrated that the Messenger of Allah صلى الله عليه وسلم observed I'tikaf in a Turkish tent, and over its door was a piece of reed matting. He moved the mat aside, put his head out, and spoke to the people. The hadith shows that I'tikaf included seclusion, but it was not complete silence from all people in every moment. In this report, the Prophet صلى الله عليه وسلم spoke to the people while remaining in the setting of I'tikaf. The focus stays on the described action: a tent, a covering, and communication with the people."},"teachings":["The Prophet صلى الله عليه وسلم observed I'tikaf in a tent in this narration.","A reed mat covered the doorway of the tent.","He moved the mat and spoke to the people.","The hadith shows a practical example of seclusion during I'tikaf."],"related_hadiths":[{"id":"1774","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1779","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E220" s="4" t="n"/>
@@ -5537,7 +5541,7 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Leaving I'tikaf for Need","description":"$book_name$ $hadith_number$ - $chapter_name$. During I'tikaf, the Prophet صلى الله عليه وسلم would not enter the house except for a necessary need."},"heading":{"title":"Leaving I'tikaf for Need Hadith","description":"This leaving I'tikaf for need hadith teaches focus during I'tikaf. Aishah said she would enter the house to relieve herself, and if a sick person was there, she only asked about him while passing through. She also said that the Messenger of Allah صلى الله عليه وسلم would not enter the house except to relieve himself when they were observing I'tikaf. The hadith shows that I'tikaf is a time of staying devoted to worship, with leaving limited to a need mentioned in the text. It also shows restraint even in normal human concerns, such as asking about a sick person only while passing. The main idea is discipline and staying connected to the purpose of I'tikaf."},"teachings":["I'tikaf involves limiting exit from the place of worship.","The Prophet صلى الله عليه وسلم entered the house only for a needed reason in this report.","Aishah asked about the sick person only while passing through.","The hadith teaches focus and restraint during I'tikaf."],"related_hadiths":[{"id":"1778","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1777","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Leaving I'tikaf for Need","description":"$book_name$ $hadith_number$ - $chapter_name$. During I'tikaf, the Prophet صلى الله عليه وسلم would not enter the house except for a necessary need."},"heading":{"title":"Leaving I'tikaf for Need Hadith","description":"This leaving I'tikaf for need hadith teaches focus during I'tikaf. Aishah said she would enter the house to relieve herself, and if a sick person was there, she only asked about him while passing through. She also said that the Messenger of Allah صلى الله عليه وسلم would not enter the house except to relieve himself when they were observing I'tikaf. The hadith shows that I'tikaf is a time of staying devoted to worship, with leaving limited to a need mentioned in the text. It also shows restraint even in normal human concerns, such as asking about a sick person only while passing. The main idea is discipline and staying connected to the purpose of I'tikaf."},"teachings":["I'tikaf involves limiting exit from the place of worship.","The Prophet صلى الله عليه وسلم entered the house only for a needed reason in this report.","Aishah asked about the sick person only while passing through.","The hadith teaches focus and restraint during I'tikaf."],"related_hadiths":[{"id":"1778","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1777","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E221" s="4" t="n"/>
@@ -5560,7 +5564,7 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hair Washing During I'tikaf","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah washed and combed the Prophet’s صلى الله عليه وسلم hair while he remained in the mosque during I'tikaf."},"heading":{"title":"Washing Hair During I'tikaf Hadith","description":"This washing hair during I'tikaf hadith gives a practical detail from the home of the Prophet صلى الله عليه وسلم. Aishah said that the Messenger of Allah صلى الله عليه وسلم used to bring his head toward her while he was next door observing I'tikaf. She would wash it and comb his hair while she was in her apartment and menstruating, and he was in the mosque. The hadith shows a careful arrangement: he remained in the mosque, while she was in her room. It also mentions her menstrual state without treating her touch or service as a problem in this described act. The report is simple, practical, and tied closely to I'tikaf and personal care."},"teachings":["The Prophet صلى الله عليه وسلم remained in the mosque while his hair was washed and combed.","Aishah helped with his hair from her apartment.","The narration mentions that Aishah was menstruating at the time.","I'tikaf did not remove simple personal care in this report."],"related_hadiths":[{"id":"1776","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1780","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hair Washing During I'tikaf","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah washed and combed the Prophet’s صلى الله عليه وسلم hair while he remained in the mosque during I'tikaf."},"heading":{"title":"Washing Hair During I'tikaf Hadith","description":"This washing hair during I'tikaf hadith gives a practical detail from the home of the Prophet صلى الله عليه وسلم. Aishah said that the Messenger of Allah صلى الله عليه وسلم used to bring his head toward her while he was next door observing I'tikaf. She would wash it and comb his hair while she was in her apartment and menstruating, and he was in the mosque. The hadith shows a careful arrangement: he remained in the mosque, while she was in her room. It also mentions her menstrual state without treating her touch or service as a problem in this described act. The report is simple, practical, and tied closely to I'tikaf and personal care."},"teachings":["The Prophet صلى الله عليه وسلم remained in the mosque while his hair was washed and combed.","Aishah helped with his hair from her apartment.","The narration mentions that Aishah was menstruating at the time.","I'tikaf did not remove simple personal care in this report."],"related_hadiths":[{"id":"1776","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1780","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E222" s="4" t="n"/>
@@ -5583,7 +5587,7 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Doubt During I'tikaf","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم clarified Safiyyah’s identity to prevent doubt, warning that Satan can whisper into hearts."},"heading":{"title":"Safiyyah Visit During I'tikaf Hadith","description":"This Safiyyah visit during I'tikaf hadith teaches care in avoiding doubt. Safiyyah, the wife of the Prophet صلى الله عليه وسلم, visited him while he was in I'tikaf during the last ten days of Ramadan. She spoke with him in the evening, then stood to leave, and the Prophet صلى الله عليه وسلم got up to take her home. When two men from the Ansar passed by, he told them to take it easy and said that she was Safiyyah bint Huyai. They felt upset that such clarification was needed. The Prophet صلى الله عليه وسلم then explained that Satan flows through the son of Adam like blood, and he feared that doubt might be cast into their hearts. The hadith teaches clean conduct and clear speech."},"teachings":["Safiyyah visited the Prophet صلى الله عليه وسلم during his I'tikaf.","The Prophet صلى الله عليه وسلم accompanied her when she went back.","He clarified her identity to prevent possible doubt.","The hadith warns that Satan may cast suspicion into hearts."],"related_hadiths":[{"id":"1775","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1768","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Doubt During I'tikaf","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم clarified Safiyyah’s identity to prevent doubt, warning that Satan can whisper into hearts."},"heading":{"title":"Safiyyah Visit During I'tikaf Hadith","description":"This Safiyyah visit during I'tikaf hadith teaches care in avoiding doubt. Safiyyah, the wife of the Prophet صلى الله عليه وسلم, visited him while he was in I'tikaf during the last ten days of Ramadan. She spoke with him in the evening, then stood to leave, and the Prophet صلى الله عليه وسلم got up to take her home. When two men from the Ansar passed by, he told them to take it easy and said that she was Safiyyah bint Huyai. They felt upset that such clarification was needed. The Prophet صلى الله عليه وسلم then explained that Satan flows through the son of Adam like blood, and he feared that doubt might be cast into their hearts. The hadith teaches clean conduct and clear speech."},"teachings":["Safiyyah visited the Prophet صلى الله عليه وسلم during his I'tikaf.","The Prophet صلى الله عليه وسلم accompanied her when she went back.","He clarified her identity to prevent possible doubt.","The hadith warns that Satan may cast suspicion into hearts."],"related_hadiths":[{"id":"1775","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1768","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E223" s="4" t="n"/>
@@ -5606,7 +5610,7 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women Observing I'tikaf","description":"$book_name$ $hadith_number$ - $chapter_name$. A wife of the Prophet صلى الله عليه وسلم observed I'tikaf while seeing red and yellow discharge, using a basin."},"heading":{"title":"Women Observing I'tikaf Hadith","description":"This women observing I'tikaf hadith reports a specific situation from Aishah. She said that one of the wives of the Messenger of Allah صلى الله عليه وسلم observed I'tikaf with him. That wife used to see red and yellow discharge, and sometimes she would place a basin beneath her. The narration is practical and direct. It does not name the wife in this wording, and it does not give a long ruling discussion. It simply records that she observed I'tikaf with the Prophet صلى الله عليه وسلم while dealing with that discharge and using a basin. The hadith is often searched by people looking for I'tikaf for women, discharge during I'tikaf, and practical matters of worship."},"teachings":["One of the Prophet’s صلى الله عليه وسلم wives observed I'tikaf with him.","The narration mentions red and yellow discharge.","She sometimes used a basin beneath her.","The hadith gives a practical detail without adding extra conditions here."],"related_hadiths":[{"id":"1778","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1773","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women Observing I'tikaf","description":"$book_name$ $hadith_number$ - $chapter_name$. A wife of the Prophet صلى الله عليه وسلم observed I'tikaf while seeing red and yellow discharge, using a basin."},"heading":{"title":"Women Observing I'tikaf Hadith","description":"This women observing I'tikaf hadith reports a specific situation from Aishah. She said that one of the wives of the Messenger of Allah صلى الله عليه وسلم observed I'tikaf with him. That wife used to see red and yellow discharge, and sometimes she would place a basin beneath her. The narration is practical and direct. It does not name the wife in this wording, and it does not give a long ruling discussion. It simply records that she observed I'tikaf with the Prophet صلى الله عليه وسلم while dealing with that discharge and using a basin. The hadith is often searched by people looking for I'tikaf for women, discharge during I'tikaf, and practical matters of worship."},"teachings":["One of the Prophet’s صلى الله عليه وسلم wives observed I'tikaf with him.","The narration mentions red and yellow discharge.","She sometimes used a basin beneath her.","The hadith gives a practical detail without adding extra conditions here."],"related_hadiths":[{"id":"1778","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1773","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E224" s="4" t="n"/>
@@ -5629,7 +5633,7 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | I'tikaf and Reward","description":"$book_name$ $hadith_number$ - $chapter_name$. I'tikaf helps a believer stay away from sin and receive reward for good deeds."},"heading":{"title":"Hadith About I'tikaf and Reward for Good Deeds","description":"This Hadith about I'tikaf teaches that a person who observes I'tikaf is holding himself back from sin. The main idea is simple: when someone stays devoted to worship in I'tikaf, he is not only doing a private act of devotion, but also protecting himself from wrong actions. The Hadith also mentions reward, saying that he will be given a reward like one who does all kinds of good deeds. The wording focuses on two clear points: staying away from sin and receiving reward from Allah. It shows that I'tikaf is not only about staying in a place; it is about spiritual discipline, self-control, and using time for worship."},"teachings":["I'tikaf helps a person stay away from sinful actions.","Time spent in worship can become a means of great reward.","A believer benefits by removing himself from harmful habits and distractions.","Good deeds are not only actions done outside; sincere worship and restraint also matter."],"related_hadiths":[{"id":"2027","book_id":"1","label":"Sahih Bukhari"},{"id":"2044","book_id":"1","label":"Sahih Bukhari"},{"id":"1165f","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | I'tikaf and Reward","description":"$book_name$ $hadith_number$ - $chapter_name$. I'tikaf helps a believer stay away from sin and receive reward for good deeds."},"heading":{"title":"Hadith About I'tikaf and Reward for Good Deeds","description":"This Hadith about I'tikaf teaches that a person who observes I'tikaf is holding himself back from sin. The main idea is simple: when someone stays devoted to worship in I'tikaf, he is not only doing a private act of devotion, but also protecting himself from wrong actions. The Hadith also mentions reward, saying that he will be given a reward like one who does all kinds of good deeds. The wording focuses on two clear points: staying away from sin and receiving reward from Allah. It shows that I'tikaf is not only about staying in a place; it is about spiritual discipline, self-control, and using time for worship."},"teachings":["I'tikaf helps a person stay away from sinful actions.","Time spent in worship can become a means of great reward.","A believer benefits by removing himself from harmful habits and distractions.","Good deeds are not only actions done outside; sincere worship and restraint also matter."],"related_hadiths":[{"id":"2027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2044","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1165f","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E225" s="4" t="n"/>
@@ -5652,7 +5656,7 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Praying on the two Eid nights with hope in Allah is linked to life of the heart."},"heading":{"title":"Hadith About Praying on the Nights of Eid","description":"This Hadith about Eid night prayer speaks about spending the nights of the two Eids in voluntary prayer while seeking reward from Allah. The focus is not on celebration alone, but on keeping the heart connected to Allah even during joyful days. The Hadith says that the heart of such a person will not die on the Day when hearts will die. The wording connects prayer, sincerity, and the life of the heart. It reminds the believer that Eid is a time of happiness, but it can also be a time of worship. The key point is to pray for Allah's sake and hope for His reward."},"teachings":["Eid nights can be used for voluntary prayer and remembrance of Allah.","Seeking reward from Allah gives worship its proper direction.","A living heart is connected to worship, not only outward celebration.","Joy in Islam can be joined with devotion and gratitude."],"related_hadiths":[{"id":"2008","book_id":"1","label":"Sahih Bukhari"},{"id":"2014","book_id":"1","label":"Sahih Bukhari"},{"id":"957","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Praying on the two Eid nights with hope in Allah is linked to life of the heart."},"heading":{"title":"Hadith About Praying on the Nights of Eid","description":"This Hadith about Eid night prayer speaks about spending the nights of the two Eids in voluntary prayer while seeking reward from Allah. The focus is not on celebration alone, but on keeping the heart connected to Allah even during joyful days. The Hadith says that the heart of such a person will not die on the Day when hearts will die. The wording connects prayer, sincerity, and the life of the heart. It reminds the believer that Eid is a time of happiness, but it can also be a time of worship. The key point is to pray for Allah's sake and hope for His reward."},"teachings":["Eid nights can be used for voluntary prayer and remembrance of Allah.","Seeking reward from Allah gives worship its proper direction.","A living heart is connected to worship, not only outward celebration.","Joy in Islam can be joined with devotion and gratitude."],"related_hadiths":[{"id":"2008","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2014","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"957","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E226" s="4" t="n"/>
@@ -5675,7 +5679,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat and Justice","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Muadh to call people to faith, prayer, zakat, and fairness."},"heading":{"title":"Hadith About Zakat, Prayer, and the Dua of the Oppressed","description":"This Hadith about Zakat gives a clear order of calling people to Islam. The Prophet sent Muadh to Yemen and told him to begin with the testimony of faith. If they accepted that, he should teach them about the five daily prayers. If they obeyed that, he should teach them about Zakat: charity taken from the rich and returned to the poor among them. The Hadith also warns not to take the best of people's wealth and to fear the supplication of the oppressed. Its message is balanced: teach faith first, then prayer, then Zakat, while protecting people from unfair treatment."},"teachings":["Faith comes before other duties in calling people to Islam.","The five daily prayers are a required part of Muslim life.","Zakat is taken from the wealthy and given to the poor.","Those who collect dues must avoid oppression and unfair taking."],"related_hadiths":[{"id":"1496","book_id":"1","label":"Sahih Bukhari"},{"id":"4347","book_id":"1","label":"Sahih Bukhari"},{"id":"19a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat and Justice","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Muadh to call people to faith, prayer, zakat, and fairness."},"heading":{"title":"Hadith About Zakat, Prayer, and the Dua of the Oppressed","description":"This Hadith about Zakat gives a clear order of calling people to Islam. The Prophet sent Muadh to Yemen and told him to begin with the testimony of faith. If they accepted that, he should teach them about the five daily prayers. If they obeyed that, he should teach them about Zakat: charity taken from the rich and returned to the poor among them. The Hadith also warns not to take the best of people's wealth and to fear the supplication of the oppressed. Its message is balanced: teach faith first, then prayer, then Zakat, while protecting people from unfair treatment."},"teachings":["Faith comes before other duties in calling people to Islam.","The five daily prayers are a required part of Muslim life.","Zakat is taken from the wealthy and given to the poor.","Those who collect dues must avoid oppression and unfair taking."],"related_hadiths":[{"id":"1496","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4347","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"19a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E227" s="4" t="n"/>
@@ -5698,7 +5702,7 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Livestock Zakat Warning","description":"$book_name$ $hadith_number$ - $chapter_name$. Owners of camels, sheep, or cattle are warned not to neglect Zakat due on them."},"heading":{"title":"Hadith About Zakat on Camels, Sheep, and Cattle","description":"This Hadith about livestock Zakat warns owners of camels, sheep, and cattle who do not pay Zakat on them. The Hadith describes those animals coming on the Day of Resurrection as large and strong, butting their owner with horns and trampling him with hooves. The scene repeats until judgment is passed among people. The wording teaches that livestock is not just a source of worldly gain. When Zakat is due, it must be treated as a right connected to that wealth. The Hadith focuses on accountability and reminds owners that animals and property can become a witness against a person if their dues are ignored."},"teachings":["Livestock wealth has Zakat duties when the conditions apply.","Neglecting Zakat is shown as a serious act of wrongdoing.","Property can become a cause of harm if its rights are ignored.","A believer should handle wealth with responsibility before the Day of Judgment."],"related_hadiths":[{"id":"988a","book_id":"2","label":"Sahih Muslim"},{"id":"988b","book_id":"2","label":"Sahih Muslim"},{"id":"990a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Livestock Zakat Warning","description":"$book_name$ $hadith_number$ - $chapter_name$. Owners of camels, sheep, or cattle are warned not to neglect Zakat due on them."},"heading":{"title":"Hadith About Zakat on Camels, Sheep, and Cattle","description":"This Hadith about livestock Zakat warns owners of camels, sheep, and cattle who do not pay Zakat on them. The Hadith describes those animals coming on the Day of Resurrection as large and strong, butting their owner with horns and trampling him with hooves. The scene repeats until judgment is passed among people. The wording teaches that livestock is not just a source of worldly gain. When Zakat is due, it must be treated as a right connected to that wealth. The Hadith focuses on accountability and reminds owners that animals and property can become a witness against a person if their dues are ignored."},"teachings":["Livestock wealth has Zakat duties when the conditions apply.","Neglecting Zakat is shown as a serious act of wrongdoing.","Property can become a cause of harm if its rights are ignored.","A believer should handle wealth with responsibility before the Day of Judgment."],"related_hadiths":[{"id":"988a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"988b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"990a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E228" s="4" t="n"/>
@@ -5721,7 +5725,7 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hoarded Treasure and Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith warns that unpaid dues on animals and hoarded treasure bring accountability."},"heading":{"title":"Hadith About Hoarded Treasure and Unpaid Zakat","description":"This Hadith about hoarded treasure and unpaid Zakat brings together two types of wealth: animals whose dues were not paid and treasure that was hoarded. Camels, cattle, and sheep are described as coming against their owners. Hoarded treasure appears as a bald-headed snake, and the owner tries to flee from it. The snake says, I am your hoarded treasure. The message is clear and direct: wealth that is kept without paying its due can become a source of fear and punishment. This Hadith teaches that Zakat is not a small side matter. It is a right attached to wealth and a protection from blame."},"teachings":["Zakat must not be ignored on wealth that carries a due.","Hoarded treasure is warned against when its right is unpaid.","A person cannot escape the accountability of wealth by hiding from it.","The Hadith teaches fear of Allah in financial duties."],"related_hadiths":[{"id":"4659","book_id":"1","label":"Sahih Bukhari"},{"id":"6957","book_id":"1","label":"Sahih Bukhari"},{"id":"990a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hoarded Treasure and Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith warns that unpaid dues on animals and hoarded treasure bring accountability."},"heading":{"title":"Hadith About Hoarded Treasure and Unpaid Zakat","description":"This Hadith about hoarded treasure and unpaid Zakat brings together two types of wealth: animals whose dues were not paid and treasure that was hoarded. Camels, cattle, and sheep are described as coming against their owners. Hoarded treasure appears as a bald-headed snake, and the owner tries to flee from it. The snake says, I am your hoarded treasure. The message is clear and direct: wealth that is kept without paying its due can become a source of fear and punishment. This Hadith teaches that Zakat is not a small side matter. It is a right attached to wealth and a protection from blame."},"teachings":["Zakat must not be ignored on wealth that carries a due.","Hoarded treasure is warned against when its right is unpaid.","A person cannot escape the accountability of wealth by hiding from it.","The Hadith teaches fear of Allah in financial duties."],"related_hadiths":[{"id":"4659","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6957","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"990a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E229" s="4" t="n"/>
@@ -5744,7 +5748,7 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat Purifies Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar explains that paying Zakat makes wealth purified and usable in obedience."},"heading":{"title":"Hadith About Zakat as Purification of Wealth","description":"This narration about Zakat as purification of wealth records Ibn Umar's answer to a Bedouin who recited the verse about hoarding gold and silver. Ibn Umar said that the warning applies to one who hoards wealth and does not pay its Zakat. He then explained that when Zakat was revealed, Allah made it a purification of wealth. He also said that he would not mind having gold equal to Uhud if he knew its amount, paid Zakat on it, and used it in obedience to Allah. The core message is balanced: wealth itself is not condemned here. The problem is hoarding it without paying Zakat and without using it rightly."},"teachings":["Zakat is described as a purification of wealth.","Hoarding becomes blameworthy when the due Zakat is not paid.","Knowing one's wealth helps a person fulfill Zakat properly.","Wealth can be used in obedience to Allah when handled responsibly."],"related_hadiths":[{"id":"1403","book_id":"1","label":"Sahih Bukhari"},{"id":"4565","book_id":"1","label":"Sahih Bukhari"},{"id":"2481","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat Purifies Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar explains that paying Zakat makes wealth purified and usable in obedience."},"heading":{"title":"Hadith About Zakat as Purification of Wealth","description":"This narration about Zakat as purification of wealth records Ibn Umar's answer to a Bedouin who recited the verse about hoarding gold and silver. Ibn Umar said that the warning applies to one who hoards wealth and does not pay its Zakat. He then explained that when Zakat was revealed, Allah made it a purification of wealth. He also said that he would not mind having gold equal to Uhud if he knew its amount, paid Zakat on it, and used it in obedience to Allah. The core message is balanced: wealth itself is not condemned here. The problem is hoarding it without paying Zakat and without using it rightly."},"teachings":["Zakat is described as a purification of wealth.","Hoarding becomes blameworthy when the due Zakat is not paid.","Knowing one's wealth helps a person fulfill Zakat properly.","Wealth can be used in obedience to Allah when handled responsibly."],"related_hadiths":[{"id":"1403","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4565","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2481","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E230" s="4" t="n"/>
@@ -5767,7 +5771,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Paying What Is Due","description":"$book_name$ $hadith_number$ - $chapter_name$. Paying Zakat on wealth is described as fulfilling what is required."},"heading":{"title":"Hadith About Paying Zakat on Your Wealth","description":"This Hadith about paying Zakat on your wealth is short but direct. The Prophet is reported to have said that when a person pays Zakat on his wealth, he has done what is required of him. The Hadith focuses on the required financial duty. It does not discuss extra charity, personal gifts, or other acts. Its message is that Zakat is an obligation tied to wealth, and paying it means the person has fulfilled that required due. This is useful for readers searching for Zakat obligation hadith because it explains the basic idea in simple words: when Zakat is due, pay it properly and do not delay or ignore it."},"teachings":["Zakat is a required duty on wealth when it is due.","Paying Zakat fulfills the required right mentioned in this report.","A believer should treat Zakat as an obligation, not as a casual gift.","Financial worship includes giving what Allah has required."],"related_hadiths":[{"id":"1496","book_id":"1","label":"Sahih Bukhari"},{"id":"1403","book_id":"1","label":"Sahih Bukhari"},{"id":"2481","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Paying What Is Due","description":"$book_name$ $hadith_number$ - $chapter_name$. Paying Zakat on wealth is described as fulfilling what is required."},"heading":{"title":"Hadith About Paying Zakat on Your Wealth","description":"This Hadith about paying Zakat on your wealth is short but direct. The Prophet is reported to have said that when a person pays Zakat on his wealth, he has done what is required of him. The Hadith focuses on the required financial duty. It does not discuss extra charity, personal gifts, or other acts. Its message is that Zakat is an obligation tied to wealth, and paying it means the person has fulfilled that required due. This is useful for readers searching for Zakat obligation hadith because it explains the basic idea in simple words: when Zakat is due, pay it properly and do not delay or ignore it."},"teachings":["Zakat is a required duty on wealth when it is due.","Paying Zakat fulfills the required right mentioned in this report.","A believer should treat Zakat as an obligation, not as a casual gift.","Financial worship includes giving what Allah has required."],"related_hadiths":[{"id":"1496","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1403","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2481","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E231" s="4" t="n"/>
@@ -5790,7 +5794,7 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Dirhams","description":"$book_name$ $hadith_number$ - $chapter_name$. Horses and slaves are exempted, while dirhams have a stated Zakat amount."},"heading":{"title":"Hadith About Zakat on Dirhams, Horses, and Slaves","description":"This Hadith about Zakat on dirhams mentions two clear rulings in its wording. First, the Prophet says that Zakat on horses and slaves is exempted. Second, he gives a stated amount for dirhams: one quarter of one-tenth, explained in the report as one dirham from every forty dirhams. The text is about specific wealth categories, so the explanation should not go beyond that. It helps readers understand that Zakat is not treated the same for every item. Some things are exempted in this report, while money measured in dirhams has a set due. The core message is accuracy and fairness in paying Zakat."},"teachings":["The Hadith mentions exemption for horses and slaves.","The report gives a clear Zakat rate for dirhams.","Zakat duties differ by type of wealth.","A person should calculate financial dues carefully."],"related_hadiths":[{"id":"982a","book_id":"2","label":"Sahih Muslim"},{"id":"2469","book_id":"3","label":"Sunan an-Nasai"},{"id":"2478","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Dirhams","description":"$book_name$ $hadith_number$ - $chapter_name$. Horses and slaves are exempted, while dirhams have a stated Zakat amount."},"heading":{"title":"Hadith About Zakat on Dirhams, Horses, and Slaves","description":"This Hadith about Zakat on dirhams mentions two clear rulings in its wording. First, the Prophet says that Zakat on horses and slaves is exempted. Second, he gives a stated amount for dirhams: one quarter of one-tenth, explained in the report as one dirham from every forty dirhams. The text is about specific wealth categories, so the explanation should not go beyond that. It helps readers understand that Zakat is not treated the same for every item. Some things are exempted in this report, while money measured in dirhams has a set due. The core message is accuracy and fairness in paying Zakat."},"teachings":["The Hadith mentions exemption for horses and slaves.","The report gives a clear Zakat rate for dirhams.","Zakat duties differ by type of wealth.","A person should calculate financial dues carefully."],"related_hadiths":[{"id":"982a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2469","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"2478","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E232" s="4" t="n"/>
@@ -5813,7 +5817,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Dinars","description":"$book_name$ $hadith_number$ - $chapter_name$. The report mentions Zakat taken from twenty dinars and from forty dinars."},"heading":{"title":"Hadith About Zakat on Dinars and Gold Amounts","description":"This Hadith about Zakat on dinars reports that from every twenty dinars or more, the Prophet used to take half a dinar, and from forty dinars, one dinar. The wording gives a simple financial measure connected to Zakat on gold or dinar-based wealth. The text does not give a long explanation of all Zakat rules, so the teaching should stay with the stated amounts. The main idea is that wealth measured in dinars had a known due when it reached the mentioned level. For someone searching Zakat on dinars hadith, this report points to careful measurement, clear calculation, and paying the required share."},"teachings":["The Hadith gives stated amounts for Zakat on dinars.","Zakat requires knowing the amount of wealth owned.","Financial duties should be calculated, not guessed carelessly.","The report shows that money-based wealth has defined dues."],"related_hadiths":[{"id":"2478","book_id":"3","label":"Sunan an-Nasai"},{"id":"982a","book_id":"2","label":"Sahih Muslim"},{"id":"1496","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Dinars","description":"$book_name$ $hadith_number$ - $chapter_name$. The report mentions Zakat taken from twenty dinars and from forty dinars."},"heading":{"title":"Hadith About Zakat on Dinars and Gold Amounts","description":"This Hadith about Zakat on dinars reports that from every twenty dinars or more, the Prophet used to take half a dinar, and from forty dinars, one dinar. The wording gives a simple financial measure connected to Zakat on gold or dinar-based wealth. The text does not give a long explanation of all Zakat rules, so the teaching should stay with the stated amounts. The main idea is that wealth measured in dinars had a known due when it reached the mentioned level. For someone searching Zakat on dinars hadith, this report points to careful measurement, clear calculation, and paying the required share."},"teachings":["The Hadith gives stated amounts for Zakat on dinars.","Zakat requires knowing the amount of wealth owned.","Financial duties should be calculated, not guessed carelessly.","The report shows that money-based wealth has defined dues."],"related_hadiths":[{"id":"2478","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"982a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1496","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E233" s="4" t="n"/>
@@ -5836,7 +5840,7 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Minimum Zakat Threshold","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith states minimum amounts for dates, silver, and camels before Sadaqah is due."},"heading":{"title":"Hadith About Nisab for Dates, Silver, and Camels","description":"This Hadith about Nisab gives minimum amounts before Sadaqah is due. It says there is no Sadaqah on less than five Awsaq of dates, five Awaq of silver, and five camels. The focus is on thresholds. The Hadith teaches that Zakat and Sadaqah obligations mentioned here are not random; they are tied to measured amounts. A person who searches for minimum Zakat threshold hadith is usually trying to know when dues begin. This report answers that for the items named in the text. It does not discuss every kind of wealth, but it clearly mentions dates, silver, and camels."},"teachings":["The Hadith gives minimum thresholds for certain wealth types.","Dates, silver, and camels are specifically mentioned in the text.","Zakat-related dues are connected to measured amounts.","A person should know whether wealth reaches the stated threshold."],"related_hadiths":[{"id":"2479","book_id":"3","label":"Sunan an-Nasai"},{"id":"2485","book_id":"3","label":"Sunan an-Nasai"},{"id":"1496","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Minimum Zakat Threshold","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith states minimum amounts for dates, silver, and camels before Sadaqah is due."},"heading":{"title":"Hadith About Nisab for Dates, Silver, and Camels","description":"This Hadith about Nisab gives minimum amounts before Sadaqah is due. It says there is no Sadaqah on less than five Awsaq of dates, five Awaq of silver, and five camels. The focus is on thresholds. The Hadith teaches that Zakat and Sadaqah obligations mentioned here are not random; they are tied to measured amounts. A person who searches for minimum Zakat threshold hadith is usually trying to know when dues begin. This report answers that for the items named in the text. It does not discuss every kind of wealth, but it clearly mentions dates, silver, and camels."},"teachings":["The Hadith gives minimum thresholds for certain wealth types.","Dates, silver, and camels are specifically mentioned in the text.","Zakat-related dues are connected to measured amounts.","A person should know whether wealth reaches the stated threshold."],"related_hadiths":[{"id":"2479","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"2485","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"1496","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E234" s="4" t="n"/>
@@ -5859,7 +5863,7 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Paying Zakat Early","description":"$book_name$ $hadith_number$ - $chapter_name$. Abbas asked to pay Sadaqah before it was due, and permission was granted."},"heading":{"title":"Hadith About Paying Sadaqah Before It Is Due","description":"This Hadith about paying Sadaqah early mentions that Abbas asked the Prophet about paying his Sadaqah before it became due, and the Prophet granted him permission. The narration is short, so the explanation should remain close to it. The core topic is early payment of Zakat or Sadaqah. It shows that Abbas did not act on his own without asking; he sought permission first. The Hadith also shows that paying before the due time was allowed for him in this report. It does not give every condition or every case, so a reader should understand the basic teaching: early payment is mentioned with prophetic permission in this narration."},"teachings":["Abbas asked before paying his Sadaqah early.","The Prophet granted permission in the case mentioned.","A believer should seek guidance in financial worship.","The Hadith points to care in timing and duty."],"related_hadiths":[{"id":"1496","book_id":"1","label":"Sahih Bukhari"},{"id":"1497","book_id":"1","label":"Sahih Bukhari"},{"id":"2479","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Paying Zakat Early","description":"$book_name$ $hadith_number$ - $chapter_name$. Abbas asked to pay Sadaqah before it was due, and permission was granted."},"heading":{"title":"Hadith About Paying Sadaqah Before It Is Due","description":"This Hadith about paying Sadaqah early mentions that Abbas asked the Prophet about paying his Sadaqah before it became due, and the Prophet granted him permission. The narration is short, so the explanation should remain close to it. The core topic is early payment of Zakat or Sadaqah. It shows that Abbas did not act on his own without asking; he sought permission first. The Hadith also shows that paying before the due time was allowed for him in this report. It does not give every condition or every case, so a reader should understand the basic teaching: early payment is mentioned with prophetic permission in this narration."},"teachings":["Abbas asked before paying his Sadaqah early.","The Prophet granted permission in the case mentioned.","A believer should seek guidance in financial worship.","The Hadith points to care in timing and duty."],"related_hadiths":[{"id":"1496","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1497","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2479","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E235" s="4" t="n"/>
@@ -5882,7 +5886,7 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blessing the Zakat Giver","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet would make dua for those who brought the Sadaqah of their wealth."},"heading":{"title":"Hadith About Making Dua for the One Who Gives Sadaqah","description":"This Hadith about making dua for the Zakat giver shows the Prophet's gentle treatment of those who brought Sadaqah from their wealth. Abdullah bin Abu Awfa said that whenever a man brought Sadaqah to the Messenger of Allah, he would bless him. When Abdullah brought his own Sadaqah, the Prophet said, O Allah, send blessing upon the family of Abu Awfa. The message is warm and simple. Giving Sadaqah was received with dua, not cold formality. The Hadith teaches that fulfilling financial worship can be met with encouragement, kindness, and prayer for blessing."},"teachings":["The Prophet made dua for people who brought Sadaqah.","Those who give should be treated with kindness and encouragement.","Financial worship can be joined with prayer and blessing.","The Hadith shows appreciation for fulfilling Zakat or Sadaqah duties."],"related_hadiths":[{"id":"1497","book_id":"1","label":"Sahih Bukhari"},{"id":"4166","book_id":"1","label":"Sahih Bukhari"},{"id":"1496","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blessing the Zakat Giver","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet would make dua for those who brought the Sadaqah of their wealth."},"heading":{"title":"Hadith About Making Dua for the One Who Gives Sadaqah","description":"This Hadith about making dua for the Zakat giver shows the Prophet's gentle treatment of those who brought Sadaqah from their wealth. Abdullah bin Abu Awfa said that whenever a man brought Sadaqah to the Messenger of Allah, he would bless him. When Abdullah brought his own Sadaqah, the Prophet said, O Allah, send blessing upon the family of Abu Awfa. The message is warm and simple. Giving Sadaqah was received with dua, not cold formality. The Hadith teaches that fulfilling financial worship can be met with encouragement, kindness, and prayer for blessing."},"teachings":["The Prophet made dua for people who brought Sadaqah.","Those who give should be treated with kindness and encouragement.","Financial worship can be joined with prayer and blessing.","The Hadith shows appreciation for fulfilling Zakat or Sadaqah duties."],"related_hadiths":[{"id":"1497","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4166","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1496","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E236" s="4" t="n"/>
@@ -5905,7 +5909,7 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua When Giving Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. The report mentions a dua asking Allah to make Zakat a gain, not a loss."},"heading":{"title":"Hadith About Dua When Giving Zakat","description":"This report about dua when giving Zakat says that when giving Zakat, a person should not forget its reward and should say, Allahummaj'alha maghnaman wa la taj'alha maghrama, meaning: O Allah, make it a gain and do not make it a loss. The supplied text also marks this narration as Maudu'. Because of that label, the explanation should be careful. The safe point from the wording is that giving Zakat should be connected to hope in Allah, not regret. A believer gives while seeking reward from Allah. The report's wording also reminds the giver to see Zakat as an act of worship, not merely money leaving the hand."},"teachings":["The wording connects Zakat with hope for reward from Allah.","A giver should not treat Zakat as a loss in spirit.","The supplied text marks this narration as Maudu', so it should be presented with caution.","The report reminds readers to keep the heart focused when giving."],"related_hadiths":[{"id":"1497","book_id":"1","label":"Sahih Bukhari"},{"id":"1496","book_id":"1","label":"Sahih Bukhari"},{"id":"2008","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua When Giving Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. The report mentions a dua asking Allah to make Zakat a gain, not a loss."},"heading":{"title":"Hadith About Dua When Giving Zakat","description":"This report about dua when giving Zakat says that when giving Zakat, a person should not forget its reward and should say, Allahummaj'alha maghnaman wa la taj'alha maghrama, meaning: O Allah, make it a gain and do not make it a loss. The supplied text also marks this narration as Maudu'. Because of that label, the explanation should be careful. The safe point from the wording is that giving Zakat should be connected to hope in Allah, not regret. A believer gives while seeking reward from Allah. The report's wording also reminds the giver to see Zakat as an act of worship, not merely money leaving the hand."},"teachings":["The wording connects Zakat with hope for reward from Allah.","A giver should not treat Zakat as a loss in spirit.","The supplied text marks this narration as Maudu', so it should be presented with caution.","The report reminds readers to keep the heart focused when giving."],"related_hadiths":[{"id":"1497","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1496","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2008","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E237" s="4" t="n"/>
@@ -5928,7 +5932,7 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Camel Zakat Schedule","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet's written instruction lists Zakat amounts for different numbers of camels."},"heading":{"title":"Hadith About Camel Zakat Amounts","description":"This Hadith about camel Zakat amounts reports a written instruction concerning Sadaqat. It gives a step-by-step schedule: for five camels, one sheep; for ten, two sheep; for twenty, four sheep; then specific ages of camels are mentioned as the number increases. The Hadith is detailed, so the main lesson is order and precision in Zakat. It shows that the due is not left to personal guesswork. Different numbers of camels have different required payments. For anyone searching camel Zakat schedule hadith, this report is directly about the amounts and ages connected to camel ownership."},"teachings":["Camel Zakat is described with measured levels.","The report lists different dues as the number of camels increases.","Zakat requires careful calculation and correct categories.","Written instruction shows the importance of clarity in public financial duties."],"related_hadiths":[{"id":"2455","book_id":"3","label":"Sunan an-Nasai"},{"id":"990a","book_id":"2","label":"Sahih Muslim"},{"id":"1496","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Camel Zakat Schedule","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet's written instruction lists Zakat amounts for different numbers of camels."},"heading":{"title":"Hadith About Camel Zakat Amounts","description":"This Hadith about camel Zakat amounts reports a written instruction concerning Sadaqat. It gives a step-by-step schedule: for five camels, one sheep; for ten, two sheep; for twenty, four sheep; then specific ages of camels are mentioned as the number increases. The Hadith is detailed, so the main lesson is order and precision in Zakat. It shows that the due is not left to personal guesswork. Different numbers of camels have different required payments. For anyone searching camel Zakat schedule hadith, this report is directly about the amounts and ages connected to camel ownership."},"teachings":["Camel Zakat is described with measured levels.","The report lists different dues as the number of camels increases.","Zakat requires careful calculation and correct categories.","Written instruction shows the importance of clarity in public financial duties."],"related_hadiths":[{"id":"2455","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"990a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1496","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E238" s="4" t="n"/>
@@ -5951,7 +5955,7 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Camel Nisab and Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith explains no Sadaqah below five camels and then gives the camel Zakat levels."},"heading":{"title":"Hadith About Camel Nisab and Zakat Levels","description":"This Hadith about camel Nisab begins by saying there is no Sadaqah on less than five camels. It then lists the due amounts as camel numbers increase: one sheep from five to nine, two sheep from ten to fourteen, and more as the numbers rise. Later it names Bint Makhad, Bin Labun, Bint Labun, Hiqqah, and Jadha'ah in the schedule. The explanation should stay close to that structure. The Hadith teaches that camel Zakat has a clear starting point and detailed levels after that. It is about measured responsibility, not random giving."},"teachings":["There is no Sadaqah on fewer than five camels in this report.","The due changes as the number of camels increases.","The Hadith names specific camel ages for certain levels.","Zakat on livestock requires careful attention to the stated schedule."],"related_hadiths":[{"id":"2455","book_id":"3","label":"Sunan an-Nasai"},{"id":"990a","book_id":"2","label":"Sahih Muslim"},{"id":"1496","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Camel Nisab and Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith explains no Sadaqah below five camels and then gives the camel Zakat levels."},"heading":{"title":"Hadith About Camel Nisab and Zakat Levels","description":"This Hadith about camel Nisab begins by saying there is no Sadaqah on less than five camels. It then lists the due amounts as camel numbers increase: one sheep from five to nine, two sheep from ten to fourteen, and more as the numbers rise. Later it names Bint Makhad, Bin Labun, Bint Labun, Hiqqah, and Jadha'ah in the schedule. The explanation should stay close to that structure. The Hadith teaches that camel Zakat has a clear starting point and detailed levels after that. It is about measured responsibility, not random giving."},"teachings":["There is no Sadaqah on fewer than five camels in this report.","The due changes as the number of camels increases.","The Hadith names specific camel ages for certain levels.","Zakat on livestock requires careful attention to the stated schedule."],"related_hadiths":[{"id":"2455","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"990a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1496","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E239" s="4" t="n"/>
@@ -5974,7 +5978,7 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Camel Zakat Substitutions","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr's letter explains how camel Zakat may be adjusted when the required age is unavailable."},"heading":{"title":"Hadith About Camel Zakat Substitution and Fair Adjustment","description":"This Hadith about camel Zakat substitution reports a letter written by Abu Bakr to Anas. It begins by calling the Sadaqah an obligation that the Messenger of Allah enjoined upon Muslims. The letter then explains what to do when the exact camel age required for Zakat is not available. In some cases, another age of camel is accepted with two sheep or twenty dirhams added. In other cases, the Zakat collector gives back twenty dirhams or two sheep. The main teaching is fairness and practical adjustment. The obligation remains, but the report gives a clear way to handle real ownership situations."},"teachings":["The letter describes Sadaqah as an obligation upon Muslims.","If the exact required camel is not available, an adjusted substitute may be accepted.","The adjustment can involve sheep or dirhams depending on the case.","The Hadith shows fairness between the owner and the Zakat collector."],"related_hadiths":[{"id":"2455","book_id":"3","label":"Sunan an-Nasai"},{"id":"990a","book_id":"2","label":"Sahih Muslim"},{"id":"1496","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Camel Zakat Substitutions","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr's letter explains how camel Zakat may be adjusted when the required age is unavailable."},"heading":{"title":"Hadith About Camel Zakat Substitution and Fair Adjustment","description":"This Hadith about camel Zakat substitution reports a letter written by Abu Bakr to Anas. It begins by calling the Sadaqah an obligation that the Messenger of Allah enjoined upon Muslims. The letter then explains what to do when the exact camel age required for Zakat is not available. In some cases, another age of camel is accepted with two sheep or twenty dirhams added. In other cases, the Zakat collector gives back twenty dirhams or two sheep. The main teaching is fairness and practical adjustment. The obligation remains, but the report gives a clear way to handle real ownership situations."},"teachings":["The letter describes Sadaqah as an obligation upon Muslims.","If the exact required camel is not available, an adjusted substitute may be accepted.","The adjustment can involve sheep or dirhams depending on the case.","The Hadith shows fairness between the owner and the Zakat collector."],"related_hadiths":[{"id":"2455","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"990a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1496","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E240" s="4" t="n"/>
@@ -5997,7 +6001,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fair Zakat Collection","description":"$book_name$ $hadith_number$ - $chapter_name$. Zakat collection should be fair, avoiding herd tricks and not taking the best animal from a Muslim."},"heading":{"title":"Fair Zakat Collection in Islam","description":"This Hadith teaches fairness in Zakat collection. The Zakat collector carried an order from the Prophet صلى الله عليه وسلم that separate herds should not be gathered, and gathered herds should not be separated, just to reduce or change the Sadaqah due. The narration also shows that the collector refused to take a huge, fat she-camel because it was among the best of the man’s camels. Instead, he accepted one of lower quality. The main message is clear: Zakat should be taken with justice, not with pressure, greed, or tricks. This Hadith is often searched as a hadith about Zakat collector, fair Sadaqah, and not taking the best livestock in Zakat."},"teachings":["Zakat should be collected with fairness and care.","People should not manipulate livestock groups to avoid Sadaqah.","A collector should not take the best property unfairly.","Fear of answering before Allah should guide public duty."],"related_hadiths":[{"id":"1805","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1807","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1808","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fair Zakat Collection","description":"$book_name$ $hadith_number$ - $chapter_name$. Zakat collection should be fair, avoiding herd tricks and not taking the best animal from a Muslim."},"heading":{"title":"Fair Zakat Collection in Islam","description":"This Hadith teaches fairness in Zakat collection. The Zakat collector carried an order from the Prophet صلى الله عليه وسلم that separate herds should not be gathered, and gathered herds should not be separated, just to reduce or change the Sadaqah due. The narration also shows that the collector refused to take a huge, fat she-camel because it was among the best of the man’s camels. Instead, he accepted one of lower quality. The main message is clear: Zakat should be taken with justice, not with pressure, greed, or tricks. This Hadith is often searched as a hadith about Zakat collector, fair Sadaqah, and not taking the best livestock in Zakat."},"teachings":["Zakat should be collected with fairness and care.","People should not manipulate livestock groups to avoid Sadaqah.","A collector should not take the best property unfairly.","Fear of answering before Allah should guide public duty."],"related_hadiths":[{"id":"1805","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1807","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1808","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E241" s="4" t="n"/>
@@ -6020,7 +6024,7 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat Collector Ethics","description":"$book_name$ $hadith_number$ - $chapter_name$. The Zakat collector should act in a way that leaves people pleased, showing fairness and good conduct."},"heading":{"title":"Zakat Collector Ethics and Public Trust","description":"This short Hadith gives a strong lesson about the manners of a Zakat collector. The Messenger of Allah صلى الله عليه وسلم said that the collector should not return unless the people are pleased with him. The wording points to fairness, gentle dealing, and avoiding harm when taking Zakat. It does not mean pleasing people by ignoring what is due. Rather, within the Hadith text, the focus is on the collector’s conduct and how people feel after he deals with them. A person appointed over Sadaqah should not be harsh or unfair. This Hadith is useful for searches about Zakat collector hadith, Islamic financial ethics, and fairness in Sadaqah collection."},"teachings":["A Zakat collector should deal with people in a pleasing manner.","Public duty should be carried out with fairness.","Collecting Sadaqah should not become a cause of resentment.","Good manners matter when handling people’s wealth."],"related_hadiths":[{"id":"1801","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1808","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1809","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat Collector Ethics","description":"$book_name$ $hadith_number$ - $chapter_name$. The Zakat collector should act in a way that leaves people pleased, showing fairness and good conduct."},"heading":{"title":"Zakat Collector Ethics and Public Trust","description":"This short Hadith gives a strong lesson about the manners of a Zakat collector. The Messenger of Allah صلى الله عليه وسلم said that the collector should not return unless the people are pleased with him. The wording points to fairness, gentle dealing, and avoiding harm when taking Zakat. It does not mean pleasing people by ignoring what is due. Rather, within the Hadith text, the focus is on the collector’s conduct and how people feel after he deals with them. A person appointed over Sadaqah should not be harsh or unfair. This Hadith is useful for searches about Zakat collector hadith, Islamic financial ethics, and fairness in Sadaqah collection."},"teachings":["A Zakat collector should deal with people in a pleasing manner.","Public duty should be carried out with fairness.","Collecting Sadaqah should not become a cause of resentment.","Good manners matter when handling people’s wealth."],"related_hadiths":[{"id":"1801","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1808","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1809","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E242" s="4" t="n"/>
@@ -6043,7 +6047,7 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Cattle Zakat Rules","description":"$book_name$ $hadith_number$ - $chapter_name$. Mu'adh was sent to Yemen and ordered to take specific Zakat from every thirty and forty cows."},"heading":{"title":"Cattle Zakat Rules in the Hadith","description":"This Hadith explains a clear instruction given to Mu'adh bin Jabal when the Messenger of Allah صلى الله عليه وسلم sent him to Yemen. He was commanded to take a Musinnah from every forty cows, and a Tabi or Tabi'ah from every thirty. The teaching is focused on livestock Zakat, especially Zakat on cows. The Hadith gives fixed numbers and names of animals, showing that Zakat collection was not left to personal guessing. It had set measures. For someone searching for cattle Zakat hadith, Zakat on cows in Islam, or Tabi and Musinnah meaning, this narration is directly related to that topic."},"teachings":["Zakat on cattle has stated amounts in this narration.","Mu'adh was given clear instructions before collecting Zakat.","The Hadith mentions different animals for thirty and forty cows.","Zakat collection should follow set guidance, not personal choice."],"related_hadiths":[{"id":"1804","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1814","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1807","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Cattle Zakat Rules","description":"$book_name$ $hadith_number$ - $chapter_name$. Mu'adh was sent to Yemen and ordered to take specific Zakat from every thirty and forty cows."},"heading":{"title":"Cattle Zakat Rules in the Hadith","description":"This Hadith explains a clear instruction given to Mu'adh bin Jabal when the Messenger of Allah صلى الله عليه وسلم sent him to Yemen. He was commanded to take a Musinnah from every forty cows, and a Tabi or Tabi'ah from every thirty. The teaching is focused on livestock Zakat, especially Zakat on cows. The Hadith gives fixed numbers and names of animals, showing that Zakat collection was not left to personal guessing. It had set measures. For someone searching for cattle Zakat hadith, Zakat on cows in Islam, or Tabi and Musinnah meaning, this narration is directly related to that topic."},"teachings":["Zakat on cattle has stated amounts in this narration.","Mu'adh was given clear instructions before collecting Zakat.","The Hadith mentions different animals for thirty and forty cows.","Zakat collection should follow set guidance, not personal choice."],"related_hadiths":[{"id":"1804","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1814","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1807","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E243" s="4" t="n"/>
@@ -6066,7 +6070,7 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Cattle","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith states the Zakat due for thirty and forty cattle in simple fixed terms."},"heading":{"title":"Zakat on Cattle: Thirty and Forty","description":"This Hadith gives a direct rule about Zakat on cattle. The Prophet صلى الله عليه وسلم said that for thirty cattle, a Tabi or Tabi'ah is due, and for forty cattle, a Musinnah is due. The wording is simple and number-based, making the main teaching easy to understand. It is about measured Zakat, not random giving or taking. The collector and the owner both need clear guidance so that the duty is known. This narration is closely searched under cattle Zakat hadith, Zakat on cows, thirty cattle Zakat, and forty cattle Musinnah. Its focus is the fixed amount mentioned in the text."},"teachings":["The Hadith states a fixed Zakat amount for thirty cattle.","The Hadith states a different amount for forty cattle.","Zakat on livestock should be based on clear numbers.","The wording helps both collector and owner know the due amount."],"related_hadiths":[{"id":"1803","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1814","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1805","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Cattle","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith states the Zakat due for thirty and forty cattle in simple fixed terms."},"heading":{"title":"Zakat on Cattle: Thirty and Forty","description":"This Hadith gives a direct rule about Zakat on cattle. The Prophet صلى الله عليه وسلم said that for thirty cattle, a Tabi or Tabi'ah is due, and for forty cattle, a Musinnah is due. The wording is simple and number-based, making the main teaching easy to understand. It is about measured Zakat, not random giving or taking. The collector and the owner both need clear guidance so that the duty is known. This narration is closely searched under cattle Zakat hadith, Zakat on cows, thirty cattle Zakat, and forty cattle Musinnah. Its focus is the fixed amount mentioned in the text."},"teachings":["The Hadith states a fixed Zakat amount for thirty cattle.","The Hadith states a different amount for forty cattle.","Zakat on livestock should be based on clear numbers.","The wording helps both collector and owner know the due amount."],"related_hadiths":[{"id":"1803","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1814","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1805","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E244" s="4" t="n"/>
@@ -6089,7 +6093,7 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sheep Zakat Rules","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains sheep Zakat amounts and warns against unfair flock changes or defective animals."},"heading":{"title":"Sheep Zakat Rules and Fair Collection","description":"This Hadith reports a written instruction of the Messenger of Allah صلى الله عليه وسلم about Sadaqah. It explains the Zakat due on sheep: one sheep for forty up to one hundred and twenty, two for more than that up to two hundred, three for more than that up to three hundred, and then one for each hundred when the flock becomes many. The Hadith also says separate flocks should not be combined, and combined flocks should not be separated. It further states that a male goat, a very old animal, or a defective animal should not be taken for Sadaqah. This is a key Hadith for sheep Zakat, livestock Zakat, and fair Zakat collection."},"teachings":["The Hadith gives stated amounts for sheep Zakat.","Flocks should not be rearranged to change the Sadaqah due.","Defective or very old animals should not be taken as Sadaqah.","Written guidance helps protect fairness in Zakat collection."],"related_hadiths":[{"id":"1807","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1801","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1808","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sheep Zakat Rules","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains sheep Zakat amounts and warns against unfair flock changes or defective animals."},"heading":{"title":"Sheep Zakat Rules and Fair Collection","description":"This Hadith reports a written instruction of the Messenger of Allah صلى الله عليه وسلم about Sadaqah. It explains the Zakat due on sheep: one sheep for forty up to one hundred and twenty, two for more than that up to two hundred, three for more than that up to three hundred, and then one for each hundred when the flock becomes many. The Hadith also says separate flocks should not be combined, and combined flocks should not be separated. It further states that a male goat, a very old animal, or a defective animal should not be taken for Sadaqah. This is a key Hadith for sheep Zakat, livestock Zakat, and fair Zakat collection."},"teachings":["The Hadith gives stated amounts for sheep Zakat.","Flocks should not be rearranged to change the Sadaqah due.","Defective or very old animals should not be taken as Sadaqah.","Written guidance helps protect fairness in Zakat collection."],"related_hadiths":[{"id":"1807","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1801","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1808","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E245" s="4" t="n"/>
@@ -6112,7 +6116,7 @@
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sheep Flock Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains sheep Zakat, shared flocks, and limits on what collectors should accept."},"heading":{"title":"Sheep Flock Zakat and Shared Ownership","description":"This Hadith gives a detailed rule for sheep Zakat. It says one sheep is due for forty sheep up to one hundred and twenty. If there is one more, then two sheep are due up to two hundred. If there is one more, then three sheep are due up to three hundred. After that, for every hundred, one sheep is due. The Hadith also says not to separate a combined flock or combine separate flocks out of fear of Sadaqah. It adds that partners should pay in proportion to their shares. It also limits taking old, defective animals, or a male goat unless the collector wishes. This is central for searches about sheep Zakat hadith and shared flock Zakat."},"teachings":["Sheep Zakat is linked to stated flock numbers.","Flocks should not be changed just to affect Sadaqah.","Partners should pay based on their shares.","The collector should avoid unsuitable animals unless allowed by the text."],"related_hadiths":[{"id":"1805","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1801","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1808","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sheep Flock Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains sheep Zakat, shared flocks, and limits on what collectors should accept."},"heading":{"title":"Sheep Flock Zakat and Shared Ownership","description":"This Hadith gives a detailed rule for sheep Zakat. It says one sheep is due for forty sheep up to one hundred and twenty. If there is one more, then two sheep are due up to two hundred. If there is one more, then three sheep are due up to three hundred. After that, for every hundred, one sheep is due. The Hadith also says not to separate a combined flock or combine separate flocks out of fear of Sadaqah. It adds that partners should pay in proportion to their shares. It also limits taking old, defective animals, or a male goat unless the collector wishes. This is central for searches about sheep Zakat hadith and shared flock Zakat."},"teachings":["Sheep Zakat is linked to stated flock numbers.","Flocks should not be changed just to affect Sadaqah.","Partners should pay based on their shares.","The collector should avoid unsuitable animals unless allowed by the text."],"related_hadiths":[{"id":"1805","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1801","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1808","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E246" s="4" t="n"/>
@@ -6135,7 +6139,7 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Unjust Sadaqah Warning","description":"$book_name$ $hadith_number$ - $chapter_name$. Being unjust in Sadaqah is compared to withholding it, warning both giver and collector."},"heading":{"title":"Unjust Sadaqah Is a Serious Matter","description":"This Hadith gives a sharp warning: the one who is unjust in Sadaqah is like the one who withholds it. The statement is short, but its meaning is weighty. It shows that Sadaqah is not only about paying or collecting. It must also be handled with fairness. A person may wrong others by taking too much, refusing what is due, or acting unfairly in the process. The Hadith does not give extra details, so the safest explanation is to stay with the clear wording: injustice in Sadaqah is treated as a serious fault. This narration is often searched as unjust in Sadaqah hadith, withholding Zakat hadith, and fairness in Zakat."},"teachings":["Sadaqah must be handled with justice.","Being unfair in Sadaqah is strongly condemned.","Withholding Sadaqah and abusing it are both serious matters.","The Hadith warns against harm in giving or collecting."],"related_hadiths":[{"id":"1801","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1809","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1810","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Unjust Sadaqah Warning","description":"$book_name$ $hadith_number$ - $chapter_name$. Being unjust in Sadaqah is compared to withholding it, warning both giver and collector."},"heading":{"title":"Unjust Sadaqah Is a Serious Matter","description":"This Hadith gives a sharp warning: the one who is unjust in Sadaqah is like the one who withholds it. The statement is short, but its meaning is weighty. It shows that Sadaqah is not only about paying or collecting. It must also be handled with fairness. A person may wrong others by taking too much, refusing what is due, or acting unfairly in the process. The Hadith does not give extra details, so the safest explanation is to stay with the clear wording: injustice in Sadaqah is treated as a serious fault. This narration is often searched as unjust in Sadaqah hadith, withholding Zakat hadith, and fairness in Zakat."},"teachings":["Sadaqah must be handled with justice.","Being unfair in Sadaqah is strongly condemned.","Withholding Sadaqah and abusing it are both serious matters.","The Hadith warns against harm in giving or collecting."],"related_hadiths":[{"id":"1801","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1809","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1810","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E247" s="4" t="n"/>
@@ -6158,7 +6162,7 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Honest Zakat Worker","description":"$book_name$ $hadith_number$ - $chapter_name$. A sincere and fair Sadaqah worker is compared to one striving in Allah’s cause until returning home."},"heading":{"title":"Honest Zakat Worker and Sincere Service","description":"This Hadith speaks about the person appointed to collect Sadaqah. The Prophet صلى الله عليه وسلم said that the one who does this work with sincerity and fairness is like one who goes out to fight for the sake of Allah until he returns home. The text links reward and honor to two qualities: sincerity and fairness. It is not praise for every collector in every condition. It is praise for the one who carries out the duty in the right way. This Hadith is important for searches about honest Zakat worker, Sadaqah collector reward, and sincerity in Islamic public service. It reminds workers that their conduct matters."},"teachings":["A Sadaqah worker should act with sincerity.","Fairness is part of the praised service in this Hadith.","Public religious duty can carry great reward when done rightly.","The Hadith praises the worker until he returns home."],"related_hadiths":[{"id":"1802","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1808","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1811","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Honest Zakat Worker","description":"$book_name$ $hadith_number$ - $chapter_name$. A sincere and fair Sadaqah worker is compared to one striving in Allah’s cause until returning home."},"heading":{"title":"Honest Zakat Worker and Sincere Service","description":"This Hadith speaks about the person appointed to collect Sadaqah. The Prophet صلى الله عليه وسلم said that the one who does this work with sincerity and fairness is like one who goes out to fight for the sake of Allah until he returns home. The text links reward and honor to two qualities: sincerity and fairness. It is not praise for every collector in every condition. It is praise for the one who carries out the duty in the right way. This Hadith is important for searches about honest Zakat worker, Sadaqah collector reward, and sincerity in Islamic public service. It reminds workers that their conduct matters."},"teachings":["A Sadaqah worker should act with sincerity.","Fairness is part of the praised service in this Hadith.","Public religious duty can carry great reward when done rightly.","The Hadith praises the worker until he returns home."],"related_hadiths":[{"id":"1802","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1808","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1811","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E248" s="4" t="n"/>
@@ -6181,7 +6185,7 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stealing from Sadaqah","description":"$book_name$ $hadith_number$ - $chapter_name$. Stealing a camel or sheep from Sadaqah is warned against with a Day of Resurrection scene."},"heading":{"title":"Stealing from Sadaqah and Accountability","description":"This Hadith warns about Ghulul with Sadaqah, meaning stealing or taking from what belongs to Sadaqah. Umar reminded Abdullah bin Unais of the Prophet’s صلى الله عليه وسلم warning: whoever steals a camel or a sheep from it will be brought on the Day of Resurrection carrying it. The narration focuses on trust, public wealth, and accountability before Allah. It does not speak about small mistakes or unrelated wealth. It speaks about taking from Sadaqah dishonestly. The main lesson is that wealth collected for Sadaqah must be protected. This Hadith is highly relevant for searches about stealing from Zakat, Ghulul in Sadaqah, and accountability in Islam."},"teachings":["Sadaqah wealth must not be stolen or misused.","The Hadith warns of accountability on the Day of Resurrection.","Even a camel or sheep taken from Sadaqah is treated seriously.","Those handling Sadaqah should be honest and careful."],"related_hadiths":[{"id":"1808","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1811","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1809","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stealing from Sadaqah","description":"$book_name$ $hadith_number$ - $chapter_name$. Stealing a camel or sheep from Sadaqah is warned against with a Day of Resurrection scene."},"heading":{"title":"Stealing from Sadaqah and Accountability","description":"This Hadith warns about Ghulul with Sadaqah, meaning stealing or taking from what belongs to Sadaqah. Umar reminded Abdullah bin Unais of the Prophet’s صلى الله عليه وسلم warning: whoever steals a camel or a sheep from it will be brought on the Day of Resurrection carrying it. The narration focuses on trust, public wealth, and accountability before Allah. It does not speak about small mistakes or unrelated wealth. It speaks about taking from Sadaqah dishonestly. The main lesson is that wealth collected for Sadaqah must be protected. This Hadith is highly relevant for searches about stealing from Zakat, Ghulul in Sadaqah, and accountability in Islam."},"teachings":["Sadaqah wealth must not be stolen or misused.","The Hadith warns of accountability on the Day of Resurrection.","Even a camel or sheep taken from Sadaqah is treated seriously.","Those handling Sadaqah should be honest and careful."],"related_hadiths":[{"id":"1808","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1811","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1809","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E249" s="4" t="n"/>
@@ -6204,7 +6208,7 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Proper Sadaqah Distribution","description":"$book_name$ $hadith_number$ - $chapter_name$. Imran explains that Sadaqah was taken and placed as it was during the Prophet’s time."},"heading":{"title":"Proper Sadaqah Collection and Distribution","description":"This report shows the attitude of Imran bin Husain when he was appointed to collect Sadaqah. After he returned, someone asked, “Where is the wealth?” He replied, “Was it for wealth that you sent me?” Then he explained that they took it from where they used to take it during the time of the Messenger of Allah صلى الله عليه وسلم and placed it where they used to place it. The Hadith focuses on trust, proper collection, and proper distribution. It does not give a full list of recipients, so the explanation should stay with the text: Sadaqah was collected and distributed according to the known practice from the Prophet’s time."},"teachings":["Sadaqah should be collected from the proper place.","Sadaqah should be distributed where it belongs.","A collector should not treat Sadaqah as personal wealth.","Following the Prophet’s practice is central in this report."],"related_hadiths":[{"id":"1809","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1810","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1802","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Proper Sadaqah Distribution","description":"$book_name$ $hadith_number$ - $chapter_name$. Imran explains that Sadaqah was taken and placed as it was during the Prophet’s time."},"heading":{"title":"Proper Sadaqah Collection and Distribution","description":"This report shows the attitude of Imran bin Husain when he was appointed to collect Sadaqah. After he returned, someone asked, “Where is the wealth?” He replied, “Was it for wealth that you sent me?” Then he explained that they took it from where they used to take it during the time of the Messenger of Allah صلى الله عليه وسلم and placed it where they used to place it. The Hadith focuses on trust, proper collection, and proper distribution. It does not give a full list of recipients, so the explanation should stay with the text: Sadaqah was collected and distributed according to the known practice from the Prophet’s time."},"teachings":["Sadaqah should be collected from the proper place.","Sadaqah should be distributed where it belongs.","A collector should not treat Sadaqah as personal wealth.","Following the Prophet’s practice is central in this report."],"related_hadiths":[{"id":"1809","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1810","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1802","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E250" s="4" t="n"/>
@@ -6227,7 +6231,7 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Exemption from Sadaqah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet states an exemption from Sadaqah on horses and slaves."},"heading":{"title":"Exemption from Sadaqah on Horses and Slaves","description":"This Hadith reports that the Messenger of Allah صلى الله عليه وسلم said, “I have exempted you from having to pay Sadaqah on horses and slaves.” The focus is simple: horses and slaves are named as exempt in this narration. The Hadith does not discuss every kind of wealth. It does not describe extra cases or conditions. It gives a direct statement of exemption. This makes it a common search result for Zakat exemption hadith, no Zakat on horses and slaves, and Sadaqah rules in Islam. The teaching is that Zakat is not taken from every possession in the same way; some items are specifically mentioned as exempt here."},"teachings":["The Hadith states an exemption from Sadaqah on horses.","The Hadith states an exemption from Sadaqah on slaves.","Not every possession is treated the same in Sadaqah.","The wording is a direct statement from the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"1812","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1814","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1815","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Exemption from Sadaqah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet states an exemption from Sadaqah on horses and slaves."},"heading":{"title":"Exemption from Sadaqah on Horses and Slaves","description":"This Hadith reports that the Messenger of Allah صلى الله عليه وسلم said, “I have exempted you from having to pay Sadaqah on horses and slaves.” The focus is simple: horses and slaves are named as exempt in this narration. The Hadith does not discuss every kind of wealth. It does not describe extra cases or conditions. It gives a direct statement of exemption. This makes it a common search result for Zakat exemption hadith, no Zakat on horses and slaves, and Sadaqah rules in Islam. The teaching is that Zakat is not taken from every possession in the same way; some items are specifically mentioned as exempt here."},"teachings":["The Hadith states an exemption from Sadaqah on horses.","The Hadith states an exemption from Sadaqah on slaves.","Not every possession is treated the same in Sadaqah.","The wording is a direct statement from the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"1812","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1814","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1815","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E251" s="4" t="n"/>
@@ -6250,7 +6254,7 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat from Its Own Kind","description":"$book_name$ $hadith_number$ - $chapter_name$. Mu'adh was told to take grain from grain and livestock from the same kind of livestock."},"heading":{"title":"Zakat Taken from Its Own Kind","description":"This Hadith reports that when Mu'adh bin Jabal was sent to Yemen, the Messenger of Allah صلى الله عليه وسلم told him to take grains from grains, sheep from sheep, camels from camels, and cows from cows. The message is direct: the Sadaqah mentioned here is taken from the same kind as the wealth being assessed. The Hadith does not discuss replacement values or other payment forms, so the explanation should stay with its wording. It is a useful narration for searches about Zakat from same type, grain Zakat hadith, and livestock Zakat hadith. It shows a simple method for taking Zakat from the category in question."},"teachings":["The Hadith links Zakat to the same kind of wealth.","Grain is mentioned with grain.","Different livestock types are mentioned separately.","Mu'adh received clear instructions before collecting."],"related_hadiths":[{"id":"1803","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1804","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1815","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat from Its Own Kind","description":"$book_name$ $hadith_number$ - $chapter_name$. Mu'adh was told to take grain from grain and livestock from the same kind of livestock."},"heading":{"title":"Zakat Taken from Its Own Kind","description":"This Hadith reports that when Mu'adh bin Jabal was sent to Yemen, the Messenger of Allah صلى الله عليه وسلم told him to take grains from grains, sheep from sheep, camels from camels, and cows from cows. The message is direct: the Sadaqah mentioned here is taken from the same kind as the wealth being assessed. The Hadith does not discuss replacement values or other payment forms, so the explanation should stay with its wording. It is a useful narration for searches about Zakat from same type, grain Zakat hadith, and livestock Zakat hadith. It shows a simple method for taking Zakat from the category in question."},"teachings":["The Hadith links Zakat to the same kind of wealth.","Grain is mentioned with grain.","Different livestock types are mentioned separately.","Mu'adh received clear instructions before collecting."],"related_hadiths":[{"id":"1803","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1804","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1815","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E252" s="4" t="n"/>
@@ -6273,7 +6277,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Five Crops","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith names wheat, barley, dates, raisins, and corn as crops with prescribed Zakat."},"heading":{"title":"Zakat on Five Crops in the Hadith","description":"This Hadith states that the Messenger of Allah صلى الله عليه وسلم prescribed Zakat on five things: wheat, barley, dates, raisins, and corn. The narration is focused on produce and crops. It does not mention every possible crop or explain extra conditions. It simply lists these five items. For readers searching for Zakat on crops hadith, wheat barley dates raisins corn Zakat, or agricultural Zakat in Islam, this Hadith is directly connected. The wording also shows that crop Zakat was not left vague in this report; named items were mentioned. The safest way to explain it is to keep the focus on the five things named in the text."},"teachings":["The Hadith names five items linked to Zakat.","Wheat and barley are mentioned among them.","Dates, raisins, and corn are also mentioned.","The narration focuses on prescribed Zakat for these crops."],"related_hadiths":[{"id":"1814","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1816","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1817","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Five Crops","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith names wheat, barley, dates, raisins, and corn as crops with prescribed Zakat."},"heading":{"title":"Zakat on Five Crops in the Hadith","description":"This Hadith states that the Messenger of Allah صلى الله عليه وسلم prescribed Zakat on five things: wheat, barley, dates, raisins, and corn. The narration is focused on produce and crops. It does not mention every possible crop or explain extra conditions. It simply lists these five items. For readers searching for Zakat on crops hadith, wheat barley dates raisins corn Zakat, or agricultural Zakat in Islam, this Hadith is directly connected. The wording also shows that crop Zakat was not left vague in this report; named items were mentioned. The safest way to explain it is to keep the focus on the five things named in the text."},"teachings":["The Hadith names five items linked to Zakat.","Wheat and barley are mentioned among them.","Dates, raisins, and corn are also mentioned.","The narration focuses on prescribed Zakat for these crops."],"related_hadiths":[{"id":"1814","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1816","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1817","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E253" s="4" t="n"/>
@@ -6296,7 +6300,7 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Crop Zakat by Irrigation","description":"$book_name$ $hadith_number$ - $chapter_name$. Rain and spring-watered crops owe one-tenth, while manually watered crops owe half of one-tenth."},"heading":{"title":"Crop Zakat by Rain and Watering","description":"This Hadith explains crop Zakat based on how the crops are watered. The Messenger of Allah صلى الله عليه وسلم said that crops irrigated by the sky, meaning rain, and springs have one-tenth due. Crops irrigated by watering have one half of one-tenth due. The Hadith gives two clear categories. It does not describe every farming method, so the explanation should remain with the two types in the text. This narration is highly searched as crop Zakat irrigation hadith, one-tenth Zakat on crops, and agricultural Zakat rate. The main teaching is that the due amount differs depending on the water source named in the Hadith."},"teachings":["Rain and spring-watered crops are linked to one-tenth.","Watered crops are linked to half of one-tenth.","The Hadith connects crop Zakat to irrigation method.","Agricultural Sadaqah is shown with clear rates."],"related_hadiths":[{"id":"1817","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1818","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1819","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Crop Zakat by Irrigation","description":"$book_name$ $hadith_number$ - $chapter_name$. Rain and spring-watered crops owe one-tenth, while manually watered crops owe half of one-tenth."},"heading":{"title":"Crop Zakat by Rain and Watering","description":"This Hadith explains crop Zakat based on how the crops are watered. The Messenger of Allah صلى الله عليه وسلم said that crops irrigated by the sky, meaning rain, and springs have one-tenth due. Crops irrigated by watering have one half of one-tenth due. The Hadith gives two clear categories. It does not describe every farming method, so the explanation should remain with the two types in the text. This narration is highly searched as crop Zakat irrigation hadith, one-tenth Zakat on crops, and agricultural Zakat rate. The main teaching is that the due amount differs depending on the water source named in the Hadith."},"teachings":["Rain and spring-watered crops are linked to one-tenth.","Watered crops are linked to half of one-tenth.","The Hadith connects crop Zakat to irrigation method.","Agricultural Sadaqah is shown with clear rates."],"related_hadiths":[{"id":"1817","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1818","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1819","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E254" s="4" t="n"/>
@@ -6319,7 +6323,7 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Agricultural Zakat Rate","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith sets one-tenth for naturally watered crops and half of one-tenth for animal-watered crops."},"heading":{"title":"Agricultural Zakat Rate by Water Source","description":"This Hadith gives a clear rule for agricultural Zakat. The Prophet صلى الله عليه وسلم said that whatever is watered by the sky, rivers, and springs, or draws water through deep roots, has one-tenth due. Whatever is irrigated by animals, meaning by artificial means in the translation, has half of one-tenth due. The Hadith is about the rate of Zakat on crops and produce based on water source. It does not speak about every detail of farming, so we should not add details beyond the text. This is a key search topic for agricultural Zakat rate, rain-fed crop Zakat, and half-tenth crop Zakat hadith."},"teachings":["Naturally watered crops are linked to one-tenth.","Animal-irrigated crops are linked to half of one-tenth.","The water source affects the stated Zakat rate.","The Hadith gives a clear and simple measure."],"related_hadiths":[{"id":"1816","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1818","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1819","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Agricultural Zakat Rate","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith sets one-tenth for naturally watered crops and half of one-tenth for animal-watered crops."},"heading":{"title":"Agricultural Zakat Rate by Water Source","description":"This Hadith gives a clear rule for agricultural Zakat. The Prophet صلى الله عليه وسلم said that whatever is watered by the sky, rivers, and springs, or draws water through deep roots, has one-tenth due. Whatever is irrigated by animals, meaning by artificial means in the translation, has half of one-tenth due. The Hadith is about the rate of Zakat on crops and produce based on water source. It does not speak about every detail of farming, so we should not add details beyond the text. This is a key search topic for agricultural Zakat rate, rain-fed crop Zakat, and half-tenth crop Zakat hadith."},"teachings":["Naturally watered crops are linked to one-tenth.","Animal-irrigated crops are linked to half of one-tenth.","The water source affects the stated Zakat rate.","The Hadith gives a clear and simple measure."],"related_hadiths":[{"id":"1816","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1818","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1819","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E255" s="4" t="n"/>
@@ -6342,7 +6346,7 @@
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rain-Fed Crop Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. Mu'adh was ordered to take one-tenth from naturally watered crops and half from bucket-watered crops."},"heading":{"title":"Rain-Fed Crop Zakat and Bucket Watering","description":"This Hadith reports that Mu'adh bin Jabal was sent to Yemen and ordered to take one-tenth from what was irrigated by deep roots, and half of one-tenth from what was irrigated by buckets. The added explanation in the narration describes terms linked to rain water, deep roots, valley water, and lesser flow. The main point is the same: crop Zakat changes according to how the crop receives water. This is useful for searches about rain-fed crop Zakat, bucket irrigated crops Zakat, and Mu'adh Yemen crop Zakat hadith. The Hadith keeps the rate tied to the water method named in the text."},"teachings":["Mu'adh was ordered to take crop Zakat in Yemen.","Deep-rooted or naturally watered crops are linked to one-tenth.","Bucket-watered crops are linked to half of one-tenth.","The narration explains several water-related crop terms."],"related_hadiths":[{"id":"1816","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1817","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1819","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rain-Fed Crop Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. Mu'adh was ordered to take one-tenth from naturally watered crops and half from bucket-watered crops."},"heading":{"title":"Rain-Fed Crop Zakat and Bucket Watering","description":"This Hadith reports that Mu'adh bin Jabal was sent to Yemen and ordered to take one-tenth from what was irrigated by deep roots, and half of one-tenth from what was irrigated by buckets. The added explanation in the narration describes terms linked to rain water, deep roots, valley water, and lesser flow. The main point is the same: crop Zakat changes according to how the crop receives water. This is useful for searches about rain-fed crop Zakat, bucket irrigated crops Zakat, and Mu'adh Yemen crop Zakat hadith. The Hadith keeps the rate tied to the water method named in the text."},"teachings":["Mu'adh was ordered to take crop Zakat in Yemen.","Deep-rooted or naturally watered crops are linked to one-tenth.","Bucket-watered crops are linked to half of one-tenth.","The narration explains several water-related crop terms."],"related_hadiths":[{"id":"1816","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1817","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1819","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E256" s="4" t="n"/>
@@ -6365,7 +6369,7 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Assessing Fruits for Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet used to send someone to assess people’s vineyards and fruits."},"heading":{"title":"Assessing Vineyards and Fruits for Zakat","description":"This Hadith states that the Prophet صلى الله عليه وسلم used to send someone to the people to assess their vineyards and fruits. The wording is short and focused. It shows that produce was not always handled without checking or estimation. Someone was sent to assess it. The Hadith does not mention the detailed rate here, so the explanation should not add one from outside this text. Its core topic is assessing fruits and vineyards in relation to Sadaqah or Zakat. Searchers may look for fruit assessment hadith, vineyard Zakat hadith, or Kharṣ in Zakat. The main lesson is that crop and fruit matters were handled with an organized assessment."},"teachings":["The Prophet صلى الله عليه وسلم sent someone to assess fruits.","Vineyards are specifically mentioned in the Hadith.","Assessment was part of handling produce in this report.","The narration points to order in dealing with crop wealth."],"related_hadiths":[{"id":"1820","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1816","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1817","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Assessing Fruits for Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet used to send someone to assess people’s vineyards and fruits."},"heading":{"title":"Assessing Vineyards and Fruits for Zakat","description":"This Hadith states that the Prophet صلى الله عليه وسلم used to send someone to the people to assess their vineyards and fruits. The wording is short and focused. It shows that produce was not always handled without checking or estimation. Someone was sent to assess it. The Hadith does not mention the detailed rate here, so the explanation should not add one from outside this text. Its core topic is assessing fruits and vineyards in relation to Sadaqah or Zakat. Searchers may look for fruit assessment hadith, vineyard Zakat hadith, or Kharṣ in Zakat. The main lesson is that crop and fruit matters were handled with an organized assessment."},"teachings":["The Prophet صلى الله عليه وسلم sent someone to assess fruits.","Vineyards are specifically mentioned in the Hadith.","Assessment was part of handling produce in this report.","The narration points to order in dealing with crop wealth."],"related_hadiths":[{"id":"1820","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1816","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1817","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E257" s="4" t="n"/>
@@ -6388,7 +6392,7 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fair Produce Assessment","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Rawahah assessed Khaibar’s date palms and offered a fair split, which the people accepted."},"heading":{"title":"Fair Produce Assessment at Khaibar","description":"This Hadith describes the agreement after Khaibar. The land was worked by the people of Khaibar, with half the produce for them and half for the Prophet صلى الله عليه وسلم. When date harvest time came, Ibn Rawahah was sent to assess the date palms. When they said he had demanded too much, he replied that he would assess the palms and give them half of what he had stated. They then said this was fair and agreed to accept his assessment. The Hadith shows fairness in produce assessment and shared harvest dealing. It is often searched as Khaibar date palms hadith, Ibn Rawahah assessment, and fair crop sharing in Islam."},"teachings":["Produce sharing was based on an agreed half-and-half arrangement.","Ibn Rawahah assessed the date palms at harvest time.","When challenged, he offered a fair way to apply the assessment.","The people accepted the assessment after seeing its fairness."],"related_hadiths":[{"id":"1819","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1809","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1802","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fair Produce Assessment","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Rawahah assessed Khaibar’s date palms and offered a fair split, which the people accepted."},"heading":{"title":"Fair Produce Assessment at Khaibar","description":"This Hadith describes the agreement after Khaibar. The land was worked by the people of Khaibar, with half the produce for them and half for the Prophet صلى الله عليه وسلم. When date harvest time came, Ibn Rawahah was sent to assess the date palms. When they said he had demanded too much, he replied that he would assess the palms and give them half of what he had stated. They then said this was fair and agreed to accept his assessment. The Hadith shows fairness in produce assessment and shared harvest dealing. It is often searched as Khaibar date palms hadith, Ibn Rawahah assessment, and fair crop sharing in Islam."},"teachings":["Produce sharing was based on an agreed half-and-half arrangement.","Ibn Rawahah assessed the date palms at harvest time.","When challenged, he offered a fair way to apply the assessment.","The people accepted the assessment after seeing its fairness."],"related_hadiths":[{"id":"1819","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1809","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1802","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E258" s="4" t="n"/>
@@ -6411,7 +6415,7 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Give Better Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Charity should be given with care, not with poor items one would not choose for oneself."},"heading":{"title":"Give Better Charity: A Hadith on Sincere Giving","description":"This Hadith teaches a clear lesson about giving charity in Islam. A man had hung up a bunch of dates, but the dates were rotten and shriveled. The Messenger of Allah صلى الله عليه وسلم pointed to them and said that if the owner wanted to give charity, he should have given something better. The main message is simple: charity is not just about giving something away; it is about giving with respect and honesty. The Hadith about giving good charity reminds us not to choose the worst part of our wealth for others. When a person gives, the gift should show care, not neglect. This is a strong reminder about sincerity in sadaqah."},"teachings":["Charity should be given from what is decent and acceptable.","A person should not choose poor-quality items while giving to others.","Giving charity requires sincerity, care, and respect for the recipient.","The Hadith warns against treating charity as a place to discard unwanted goods."],"related_hadiths":[{"id":"1822","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1827","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1834","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Give Better Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Charity should be given with care, not with poor items one would not choose for oneself."},"heading":{"title":"Give Better Charity: A Hadith on Sincere Giving","description":"This Hadith teaches a clear lesson about giving charity in Islam. A man had hung up a bunch of dates, but the dates were rotten and shriveled. The Messenger of Allah صلى الله عليه وسلم pointed to them and said that if the owner wanted to give charity, he should have given something better. The main message is simple: charity is not just about giving something away; it is about giving with respect and honesty. The Hadith about giving good charity reminds us not to choose the worst part of our wealth for others. When a person gives, the gift should show care, not neglect. This is a strong reminder about sincerity in sadaqah."},"teachings":["Charity should be given from what is decent and acceptable.","A person should not choose poor-quality items while giving to others.","Giving charity requires sincerity, care, and respect for the recipient.","The Hadith warns against treating charity as a place to discard unwanted goods."],"related_hadiths":[{"id":"1822","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1827","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1834","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E259" s="4" t="n"/>
@@ -6434,7 +6438,7 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Give Bad Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Give charity from what is good, not from what you would dislike receiving yourself."},"heading":{"title":"Do Not Give Bad Charity: Meaning of Al-Baqarah 2:267","description":"This Hadith explains the verse that tells believers not to aim at what is bad when spending in charity. The Ansar used to hang bunches of dates in the mosque so poor emigrants could eat from them. One person mixed in rotten and shriveled dates, thinking it was allowed because there were many good bunches already there. The verse came about this action. The message is direct: do not give others what you would not like to receive. The Hadith about bad charity also reminds us that Allah has no need of our charity. So giving should be done with honesty, not with the aim of hiding poor items among better ones."},"teachings":["Do not deliberately give bad or unwanted items in charity.","A believer should think about what they themselves would accept before giving.","Charity should not be used to hide low-quality goods among better ones.","Allah has no need of charity, so the giver should focus on sincerity."],"related_hadiths":[{"id":"1821","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1827","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1835","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Give Bad Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Give charity from what is good, not from what you would dislike receiving yourself."},"heading":{"title":"Do Not Give Bad Charity: Meaning of Al-Baqarah 2:267","description":"This Hadith explains the verse that tells believers not to aim at what is bad when spending in charity. The Ansar used to hang bunches of dates in the mosque so poor emigrants could eat from them. One person mixed in rotten and shriveled dates, thinking it was allowed because there were many good bunches already there. The verse came about this action. The message is direct: do not give others what you would not like to receive. The Hadith about bad charity also reminds us that Allah has no need of our charity. So giving should be done with honesty, not with the aim of hiding poor items among better ones."},"teachings":["Do not deliberately give bad or unwanted items in charity.","A believer should think about what they themselves would accept before giving.","Charity should not be used to hide low-quality goods among better ones.","Allah has no need of charity, so the giver should focus on sincerity."],"related_hadiths":[{"id":"1821","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1827","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1835","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E260" s="4" t="n"/>
@@ -6457,7 +6461,7 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Bees","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم instructed the owner of bees to give one-tenth and granted protection."},"heading":{"title":"Zakat on Bees: One-Tenth from Honey Produce","description":"This Hadith speaks about a man who told the Messenger of Allah صلى الله عليه وسلم that he had bees. The Prophet صلى الله عليه وسلم told him to give one-tenth. The man then asked the Prophet صلى الله عليه وسلم to protect it for him, and the Prophet صلى الله عليه وسلم protected it. The core topic is zakat on bees and honey, based only on what appears in the narration. The teaching is short but clear: when a person has produce or benefit, there may be a duty connected to it. The Hadith also shows that the man did not act on guesswork. He asked the Prophet صلى الله عليه وسلم directly and followed the answer. This makes the narration important for searches about honey zakat in Islam."},"teachings":["A person should ask about financial duties when unsure.","The Prophet صلى الله عليه وسلم instructed the owner of bees to give one-tenth.","The narration connects ownership of bees with a duty to give.","The man sought guidance and protection instead of deciding alone."],"related_hadiths":[{"id":"1824","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1831","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1832","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Bees","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم instructed the owner of bees to give one-tenth and granted protection."},"heading":{"title":"Zakat on Bees: One-Tenth from Honey Produce","description":"This Hadith speaks about a man who told the Messenger of Allah صلى الله عليه وسلم that he had bees. The Prophet صلى الله عليه وسلم told him to give one-tenth. The man then asked the Prophet صلى الله عليه وسلم to protect it for him, and the Prophet صلى الله عليه وسلم protected it. The core topic is zakat on bees and honey, based only on what appears in the narration. The teaching is short but clear: when a person has produce or benefit, there may be a duty connected to it. The Hadith also shows that the man did not act on guesswork. He asked the Prophet صلى الله عليه وسلم directly and followed the answer. This makes the narration important for searches about honey zakat in Islam."},"teachings":["A person should ask about financial duties when unsure.","The Prophet صلى الله عليه وسلم instructed the owner of bees to give one-tenth.","The narration connects ownership of bees with a duty to give.","The man sought guidance and protection instead of deciding alone."],"related_hadiths":[{"id":"1824","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1831","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1832","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E261" s="4" t="n"/>
@@ -6480,7 +6484,7 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One-Tenth of Honey","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم took one-tenth of honey, showing a duty tied to honey produce."},"heading":{"title":"One-Tenth of Honey: A Hadith on Honey Zakat","description":"This Hadith states that the Prophet صلى الله عليه وسلم took one-tenth of honey as zakat. The wording is brief, but the meaning is focused. It links honey with a one-tenth payment. For people searching for zakat on honey hadith or honey ushr in Islam, this narration is directly about that topic. The Hadith does not give extra details about amount, conditions, or timing in this text, so the explanation should stay within the words given. What can be learned is that honey was treated as something from which one-tenth was taken. It also shows that zakat and charity matters were not left vague, but were applied in real cases."},"teachings":["The Prophet صلى الله عليه وسلم took one-tenth from honey.","Honey produce is directly mentioned in connection with zakat.","The narration gives a clear amount: one-tenth.","Financial duties in Islam may apply to specific forms of produce."],"related_hadiths":[{"id":"1823","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1831","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1833","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One-Tenth of Honey","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم took one-tenth of honey, showing a duty tied to honey produce."},"heading":{"title":"One-Tenth of Honey: A Hadith on Honey Zakat","description":"This Hadith states that the Prophet صلى الله عليه وسلم took one-tenth of honey as zakat. The wording is brief, but the meaning is focused. It links honey with a one-tenth payment. For people searching for zakat on honey hadith or honey ushr in Islam, this narration is directly about that topic. The Hadith does not give extra details about amount, conditions, or timing in this text, so the explanation should stay within the words given. What can be learned is that honey was treated as something from which one-tenth was taken. It also shows that zakat and charity matters were not left vague, but were applied in real cases."},"teachings":["The Prophet صلى الله عليه وسلم took one-tenth from honey.","Honey produce is directly mentioned in connection with zakat.","The narration gives a clear amount: one-tenth.","Financial duties in Islam may apply to specific forms of produce."],"related_hadiths":[{"id":"1823","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1831","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1833","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E262" s="4" t="n"/>
@@ -6503,7 +6507,7 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sadaqatul-Fitr for Every Muslim","description":"$book_name$ $hadith_number$ - $chapter_name$. Sadaqatul-Fitr was set as one Sa for every Muslim, free or slave, male or female."},"heading":{"title":"Sadaqatul-Fitr for Every Muslim: One Sa of Food","description":"This Hadith explains who was included in Sadaqatul-Fitr and what amount was given. The Messenger of Allah صلى الله عليه وسلم enjoined one Sa of barley or one Sa of dates for every Muslim. The narration names free people and slaves, males and females. The core topic is Zakatul-Fitr obligation, because the text uses strong wording about it being prescribed. It also shows that this charity was not limited to one social group. The Hadith keeps the focus on Muslims as a community and mentions a shared act before Eid. For readers searching for Sadaqatul-Fitr hadith, this narration gives both the amount and the people included in the command."},"teachings":["Sadaqatul-Fitr was enjoined upon every Muslim named in the narration.","The amount stated is one Sa of barley or one Sa of dates.","The Hadith includes free and enslaved people, males and females.","Zakatul-Fitr is shown as a community-wide act of giving."],"related_hadiths":[{"id":"1825","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1827","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1829","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sadaqatul-Fitr for Every Muslim","description":"$book_name$ $hadith_number$ - $chapter_name$. Sadaqatul-Fitr was set as one Sa for every Muslim, free or slave, male or female."},"heading":{"title":"Sadaqatul-Fitr for Every Muslim: One Sa of Food","description":"This Hadith explains who was included in Sadaqatul-Fitr and what amount was given. The Messenger of Allah صلى الله عليه وسلم enjoined one Sa of barley or one Sa of dates for every Muslim. The narration names free people and slaves, males and females. The core topic is Zakatul-Fitr obligation, because the text uses strong wording about it being prescribed. It also shows that this charity was not limited to one social group. The Hadith keeps the focus on Muslims as a community and mentions a shared act before Eid. For readers searching for Sadaqatul-Fitr hadith, this narration gives both the amount and the people included in the command."},"teachings":["Sadaqatul-Fitr was enjoined upon every Muslim named in the narration.","The amount stated is one Sa of barley or one Sa of dates.","The Hadith includes free and enslaved people, males and females.","Zakatul-Fitr is shown as a community-wide act of giving."],"related_hadiths":[{"id":"1825","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1827","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1829","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E263" s="4" t="n"/>
@@ -6526,7 +6530,7 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Continuing Sadaqatul-Fitr","description":"$book_name$ $hadith_number$ - $chapter_name$. The Companions continued Sadaqatul-Fitr after the command of Zakat was revealed."},"heading":{"title":"Continuing Sadaqatul-Fitr: A Hadith on Practice After Zakat","description":"This Hadith reports that the Messenger of Allah صلى الله عليه وسلم enjoined Sadaqatul-Fitr before the command of Zakat was revealed. Qais bin Saad said that after Zakat was revealed, the Prophet صلى الله عليه وسلم neither ordered them nor forbade them regarding it, so they continued doing it. The main topic is continuing Sadaqatul-Fitr. The wording is careful and should be read carefully. The Hadith does not say that the practice ended. It says the Companions kept doing it. This makes it useful for searches about Sadaqatul-Fitr after zakat was revealed. The narration also shows how the Companions held on to a practice they had received from the Prophet صلى الله عليه وسلم."},"teachings":["Sadaqatul-Fitr was enjoined before the command of Zakat was revealed.","After Zakat was revealed, the Prophet صلى الله عليه وسلم did not forbid them from paying it.","The Companions continued the practice.","The Hadith shows careful attention to what was ordered, not ordered, and not forbidden."],"related_hadiths":[{"id":"1825","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1827","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1829","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Continuing Sadaqatul-Fitr","description":"$book_name$ $hadith_number$ - $chapter_name$. The Companions continued Sadaqatul-Fitr after the command of Zakat was revealed."},"heading":{"title":"Continuing Sadaqatul-Fitr: A Hadith on Practice After Zakat","description":"This Hadith reports that the Messenger of Allah صلى الله عليه وسلم enjoined Sadaqatul-Fitr before the command of Zakat was revealed. Qais bin Saad said that after Zakat was revealed, the Prophet صلى الله عليه وسلم neither ordered them nor forbade them regarding it, so they continued doing it. The main topic is continuing Sadaqatul-Fitr. The wording is careful and should be read carefully. The Hadith does not say that the practice ended. It says the Companions kept doing it. This makes it useful for searches about Sadaqatul-Fitr after zakat was revealed. The narration also shows how the Companions held on to a practice they had received from the Prophet صلى الله عليه وسلم."},"teachings":["Sadaqatul-Fitr was enjoined before the command of Zakat was revealed.","After Zakat was revealed, the Prophet صلى الله عليه وسلم did not forbid them from paying it.","The Companions continued the practice.","The Hadith shows careful attention to what was ordered, not ordered, and not forbidden."],"related_hadiths":[{"id":"1825","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1827","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1829","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E264" s="4" t="n"/>
@@ -6549,7 +6553,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wasq Equals Sixty Sa","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم is reported to have said that one Wasq equals sixty Sa."},"heading":{"title":"Wasq Equals Sixty Sa: A Hadith on Islamic Measures","description":"This Hadith gives a short but important measurement. Abu Saeed narrated and attributed to the Prophet صلى الله عليه وسلم that a Wasq is sixty Sa. The core topic is Islamic measurement, especially the link between Wasq and Sa. The narration does not explain Zakatul-Fitr or crop zakat by itself, but it gives a measure that appears in discussions of food and produce. For search terms like Wasq equals sixty Sa or Islamic measures in Hadith, this text is direct. It reminds readers that older measures were known and defined. The Hadith is brief, so the safest explanation is also brief: one Wasq is equal to sixty Sa according to the wording provided."},"teachings":["A Wasq is described as sixty Sa.","The Hadith gives a clear measurement rather than a long ruling.","Knowing measures helps understand narrations about food and produce.","The wording should be kept simple because the narration itself is short."],"related_hadiths":[{"id":"1833","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1825","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1829","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wasq Equals Sixty Sa","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم is reported to have said that one Wasq equals sixty Sa."},"heading":{"title":"Wasq Equals Sixty Sa: A Hadith on Islamic Measures","description":"This Hadith gives a short but important measurement. Abu Saeed narrated and attributed to the Prophet صلى الله عليه وسلم that a Wasq is sixty Sa. The core topic is Islamic measurement, especially the link between Wasq and Sa. The narration does not explain Zakatul-Fitr or crop zakat by itself, but it gives a measure that appears in discussions of food and produce. For search terms like Wasq equals sixty Sa or Islamic measures in Hadith, this text is direct. It reminds readers that older measures were known and defined. The Hadith is brief, so the safest explanation is also brief: one Wasq is equal to sixty Sa according to the wording provided."},"teachings":["A Wasq is described as sixty Sa.","The Hadith gives a clear measurement rather than a long ruling.","Knowing measures helps understand narrations about food and produce.","The wording should be kept simple because the narration itself is short."],"related_hadiths":[{"id":"1833","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1825","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1829","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E265" s="4" t="n"/>
@@ -6572,7 +6576,7 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Choosing a Spouse for Marriage","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith highlights guidance on choosing a spouse and the hoped-for blessings of marriage."},"heading":{"title":"Hadith About Choosing a Spouse for Marriage","description":"This hadith gives direct guidance about marriage and choosing a spouse. The Prophet advised marrying virgins and mentioned three qualities in this narration: sweeter speech, more ability to bear children, and being pleased with little. The core message is about marriage choice and what may help build a simple and stable married life. A person searching for a hadith about choosing a wife in Islam will find that this report speaks in clear, practical terms. It does not list every factor in marriage, and it should not be stretched beyond the words given here. The hadith focuses only on this specific advice about marriage preference and family life."},"teachings":["Marriage choices should be made with care and purpose.","The hadith connects marriage with family growth and simple living.","Being pleased with little is mentioned as a good quality in married life.","The text gives a specific recommendation and should not be expanded beyond its wording."],"related_hadiths":[{"id":"1863","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1870","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1871","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Choosing a Spouse for Marriage","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith highlights guidance on choosing a spouse and the hoped-for blessings of marriage."},"heading":{"title":"Hadith About Choosing a Spouse for Marriage","description":"This hadith gives direct guidance about marriage and choosing a spouse. The Prophet advised marrying virgins and mentioned three qualities in this narration: sweeter speech, more ability to bear children, and being pleased with little. The core message is about marriage choice and what may help build a simple and stable married life. A person searching for a hadith about choosing a wife in Islam will find that this report speaks in clear, practical terms. It does not list every factor in marriage, and it should not be stretched beyond the words given here. The hadith focuses only on this specific advice about marriage preference and family life."},"teachings":["Marriage choices should be made with care and purpose.","The hadith connects marriage with family growth and simple living.","Being pleased with little is mentioned as a good quality in married life.","The text gives a specific recommendation and should not be expanded beyond its wording."],"related_hadiths":[{"id":"1863","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1870","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1871","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E266" s="4" t="n"/>
@@ -6595,7 +6599,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Marriage and Purity","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith links marriage with purity and gives a direct instruction about marrying free women."},"heading":{"title":"Hadith About Marriage and Purity in Islam","description":"This hadith focuses on marriage and purity. Anas bin Malik narrated that the Prophet said whoever wants to meet Allah pure and purified should marry free women. The wording is short, direct, and serious. For someone searching for a hadith about marriage and purity, the main point is that marriage is presented here as a way connected to chastity and a clean religious life. The hadith does not explain every detail of marriage law, and it does not discuss every type of marriage situation. It simply gives a clear direction tied to purity before Allah. The safest explanation is to stay close to that message."},"teachings":["Marriage is connected in this hadith with purity before Allah.","The hadith encourages a lawful and clean path in personal life.","The wording gives direct guidance without adding extra conditions in the text.","A believer should treat marriage as a serious religious matter."],"related_hadiths":[{"id":"1863","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1879","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1880","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Marriage and Purity","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith links marriage with purity and gives a direct instruction about marrying free women."},"heading":{"title":"Hadith About Marriage and Purity in Islam","description":"This hadith focuses on marriage and purity. Anas bin Malik narrated that the Prophet said whoever wants to meet Allah pure and purified should marry free women. The wording is short, direct, and serious. For someone searching for a hadith about marriage and purity, the main point is that marriage is presented here as a way connected to chastity and a clean religious life. The hadith does not explain every detail of marriage law, and it does not discuss every type of marriage situation. It simply gives a clear direction tied to purity before Allah. The safest explanation is to stay close to that message."},"teachings":["Marriage is connected in this hadith with purity before Allah.","The hadith encourages a lawful and clean path in personal life.","The wording gives direct guidance without adding extra conditions in the text.","A believer should treat marriage as a serious religious matter."],"related_hadiths":[{"id":"1863","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1879","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1880","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E267" s="4" t="n"/>
@@ -6618,7 +6622,7 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Looking Before Marriage","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows that looking at a woman before proposal may be allowed when marriage is intended."},"heading":{"title":"Hadith About Looking at a Prospective Bride","description":"This hadith speaks about looking at a woman when a man has a real intention to propose marriage. Muhammad bin Salamah said he wanted to marry a woman and looked at her. When someone questioned him, he replied with the Prophet’s statement that if Allah places in a man’s heart the proposal of a woman, there is nothing wrong with him looking at her. The main message is about a serious marriage proposal, not casual looking. A person searching for hadith about seeing a prospective bride should notice this limit clearly. The text connects the permission to a marriage intention, so the explanation should stay within that boundary."},"teachings":["Looking is mentioned here in the setting of a serious marriage proposal.","The hadith does not support casual or purposeless looking.","A proposal intention changes the context of the action mentioned.","Questions about marriage should be handled with care and evidence."],"related_hadiths":[{"id":"1865","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1866","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1867","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Looking Before Marriage","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows that looking at a woman before proposal may be allowed when marriage is intended."},"heading":{"title":"Hadith About Looking at a Prospective Bride","description":"This hadith speaks about looking at a woman when a man has a real intention to propose marriage. Muhammad bin Salamah said he wanted to marry a woman and looked at her. When someone questioned him, he replied with the Prophet’s statement that if Allah places in a man’s heart the proposal of a woman, there is nothing wrong with him looking at her. The main message is about a serious marriage proposal, not casual looking. A person searching for hadith about seeing a prospective bride should notice this limit clearly. The text connects the permission to a marriage intention, so the explanation should stay within that boundary."},"teachings":["Looking is mentioned here in the setting of a serious marriage proposal.","The hadith does not support casual or purposeless looking.","A proposal intention changes the context of the action mentioned.","Questions about marriage should be handled with care and evidence."],"related_hadiths":[{"id":"1865","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1866","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1867","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E268" s="4" t="n"/>
@@ -6641,7 +6645,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Consent and Looking Before Marriage","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows looking before marriage with seriousness, family involvement, and respect."},"heading":{"title":"Hadith About Looking Before Marriage With Respect","description":"This hadith gives a fuller story about looking at a woman before marriage. Mughirah bin Shubah told the Prophet about a woman he wanted to propose to. The Prophet told him to look at her, saying that it was more likely to create love between them. Mughirah then went through her parents and told them what the Prophet had said. They seemed uneasy, but the woman herself said that if the Messenger of Allah had told him to do it, then he could look. The main topic is looking before marriage in Islam, but the narration also shows seriousness, family setting, and respect for the woman’s concern."},"teachings":["Looking before marriage is linked here to a real proposal.","The woman’s response is shown as important in the story.","The family setting was part of how the proposal was handled.","The purpose mentioned is to help love grow between the couple."],"related_hadiths":[{"id":"1864","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1865","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1871","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Consent and Looking Before Marriage","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows looking before marriage with seriousness, family involvement, and respect."},"heading":{"title":"Hadith About Looking Before Marriage With Respect","description":"This hadith gives a fuller story about looking at a woman before marriage. Mughirah bin Shubah told the Prophet about a woman he wanted to propose to. The Prophet told him to look at her, saying that it was more likely to create love between them. Mughirah then went through her parents and told them what the Prophet had said. They seemed uneasy, but the woman herself said that if the Messenger of Allah had told him to do it, then he could look. The main topic is looking before marriage in Islam, but the narration also shows seriousness, family setting, and respect for the woman’s concern."},"teachings":["Looking before marriage is linked here to a real proposal.","The woman’s response is shown as important in the story.","The family setting was part of how the proposal was handled.","The purpose mentioned is to help love grow between the couple."],"related_hadiths":[{"id":"1864","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1865","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1871","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E269" s="4" t="n"/>
@@ -6664,7 +6668,7 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Respect in Marriage Proposals","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith repeats the rule that a man should not propose over his brother’s proposal."},"heading":{"title":"Hadith About Respecting an Existing Marriage Proposal","description":"This narration from Ibn Umar gives the same clear teaching: a man should not propose to a woman to whom his brother has already proposed. The main topic is marriage proposal etiquette in Islam. The hadith protects the proposal process from unfair competition and personal harm. It also teaches that marriage is not only about desire; it must be approached with manners and respect. The wording is brief, so we should not add conditions that are not present in the text. A person searching for do not propose over your brother hadith will find the core message here: do not step into a proposal that is already underway."},"teachings":["Existing proposals should be respected.","A Muslim should avoid causing tension in marriage talks.","The hadith teaches restraint before marriage.","Fair conduct matters even before the marriage contract."],"related_hadiths":[{"id":"1867","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1869","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1871","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Respect in Marriage Proposals","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith repeats the rule that a man should not propose over his brother’s proposal."},"heading":{"title":"Hadith About Respecting an Existing Marriage Proposal","description":"This narration from Ibn Umar gives the same clear teaching: a man should not propose to a woman to whom his brother has already proposed. The main topic is marriage proposal etiquette in Islam. The hadith protects the proposal process from unfair competition and personal harm. It also teaches that marriage is not only about desire; it must be approached with manners and respect. The wording is brief, so we should not add conditions that are not present in the text. A person searching for do not propose over your brother hadith will find the core message here: do not step into a proposal that is already underway."},"teachings":["Existing proposals should be respected.","A Muslim should avoid causing tension in marriage talks.","The hadith teaches restraint before marriage.","Fair conduct matters even before the marriage contract."],"related_hadiths":[{"id":"1867","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1869","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1871","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E270" s="4" t="n"/>
@@ -6687,7 +6691,7 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Marriage Guardian in Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that a valid marriage is tied to the role of a guardian in the marriage contract."},"heading":{"title":"Marriage Guardian in Islam: No Nikah Without a Wali","description":"This Hadith about wali in marriage gives a clear and short rule: there is no marriage except with a guardian. The core message is about the place of a guardian in the marriage contract. It does not give many details here, but its wording is direct. A Muslim marriage is not treated as a private arrangement between two people only. The guardian has a role in making the nikah open, serious, and properly handled. For someone searching for hadith about guardian in marriage, this narration shows that the Prophet صلى الله عليه وسلم connected nikah with a wali. The focus is not on making marriage hard, but on giving the marriage contract the care and order it deserves."},"teachings":["A guardian has a stated role in the marriage contract.","Nikah is presented as a serious contract, not a casual private act.","The wording teaches that marriage should be handled with proper responsibility."],"related_hadiths":[{"id":"1879","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1880","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1882","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Marriage Guardian in Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that a valid marriage is tied to the role of a guardian in the marriage contract."},"heading":{"title":"Marriage Guardian in Islam: No Nikah Without a Wali","description":"This Hadith about wali in marriage gives a clear and short rule: there is no marriage except with a guardian. The core message is about the place of a guardian in the marriage contract. It does not give many details here, but its wording is direct. A Muslim marriage is not treated as a private arrangement between two people only. The guardian has a role in making the nikah open, serious, and properly handled. For someone searching for hadith about guardian in marriage, this narration shows that the Prophet صلى الله عليه وسلم connected nikah with a wali. The focus is not on making marriage hard, but on giving the marriage contract the care and order it deserves."},"teachings":["A guardian has a stated role in the marriage contract.","Nikah is presented as a serious contract, not a casual private act.","The wording teaches that marriage should be handled with proper responsibility."],"related_hadiths":[{"id":"1879","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1880","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1882","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E271" s="4" t="n"/>
@@ -6710,7 +6714,7 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women and Marriage Arrangement","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns against a woman arranging another woman's marriage or arranging her own marriage."},"heading":{"title":"Hadith About Arranging Marriage and the Role of a Guardian","description":"This Hadith about arranging marriage explains that a woman should not arrange the marriage of another woman, and she should not arrange her own marriage. The wording is strong, so the explanation should stay close to the text. The Hadith links proper marriage arrangement with modesty, order, and a recognized process. It also shows that nikah is not meant to be handled in a hidden or loose way. For readers searching for hadith about woman arranging her own marriage, the key point is that the Prophet صلى الله عليه وسلم warned against bypassing the proper marriage process. The narration does not discuss every case or detail. It simply gives a clear warning about self-arranged marriage in this wording."},"teachings":["A marriage should not be arranged in a loose or hidden manner.","The Hadith warns against a woman arranging her own marriage.","The wording supports the need for a proper process in nikah."],"related_hadiths":[{"id":"1881","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1879","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1880","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women and Marriage Arrangement","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns against a woman arranging another woman's marriage or arranging her own marriage."},"heading":{"title":"Hadith About Arranging Marriage and the Role of a Guardian","description":"This Hadith about arranging marriage explains that a woman should not arrange the marriage of another woman, and she should not arrange her own marriage. The wording is strong, so the explanation should stay close to the text. The Hadith links proper marriage arrangement with modesty, order, and a recognized process. It also shows that nikah is not meant to be handled in a hidden or loose way. For readers searching for hadith about woman arranging her own marriage, the key point is that the Prophet صلى الله عليه وسلم warned against bypassing the proper marriage process. The narration does not discuss every case or detail. It simply gives a clear warning about self-arranged marriage in this wording."},"teachings":["A marriage should not be arranged in a loose or hidden manner.","The Hadith warns against a woman arranging her own marriage.","The wording supports the need for a proper process in nikah."],"related_hadiths":[{"id":"1881","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1879","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1880","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E272" s="4" t="n"/>
@@ -6733,7 +6737,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shighar Prohibition","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith gives a brief report that the Messenger of Allah forbade Shighar."},"heading":{"title":"Shighar in Islam: A Clear Prohibition in Marriage","description":"This Hadith about Shighar is short, but its message is clear. Abu Hurairah said that the Messenger of Allah صلى الله عليه وسلم forbade Shighar. The narration does not explain Shighar in this wording, so the explanation should not add extra details beyond the text. In the nearby narration, Shighar is described as a marriage exchange with no dower, but this Hadith itself simply records the prohibition. For users searching for Shighar in Islam or hadith forbidding Shighar, this report shows that marriage must not be built on a practice the Prophet صلى الله عليه وسلم forbade. It points to the need for fairness, proper marriage terms, and respect for the marriage contract."},"teachings":["The Messenger of Allah صلى الله عليه وسلم forbade Shighar.","Marriage terms should not be based on a forbidden practice.","The Hadith keeps the matter simple and direct."],"related_hadiths":[{"id":"1883","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1885","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1886","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shighar Prohibition","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith gives a brief report that the Messenger of Allah forbade Shighar."},"heading":{"title":"Shighar in Islam: A Clear Prohibition in Marriage","description":"This Hadith about Shighar is short, but its message is clear. Abu Hurairah said that the Messenger of Allah صلى الله عليه وسلم forbade Shighar. The narration does not explain Shighar in this wording, so the explanation should not add extra details beyond the text. In the nearby narration, Shighar is described as a marriage exchange with no dower, but this Hadith itself simply records the prohibition. For users searching for Shighar in Islam or hadith forbidding Shighar, this report shows that marriage must not be built on a practice the Prophet صلى الله عليه وسلم forbade. It points to the need for fairness, proper marriage terms, and respect for the marriage contract."},"teachings":["The Messenger of Allah صلى الله عليه وسلم forbade Shighar.","Marriage terms should not be based on a forbidden practice.","The Hadith keeps the matter simple and direct."],"related_hadiths":[{"id":"1883","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1885","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1886","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E273" s="4" t="n"/>
@@ -6756,7 +6760,7 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Shighar","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith states that Shighar has no place in Islam."},"heading":{"title":"No Shighar in Islam: A Marriage Hadith With a Clear Message","description":"This Hadith about no Shighar in Islam states the matter in very plain words: there is no Shighar in Islam. The narration is short, but it carries a strong message about the marriage contract. Shighar is not presented here as a valid Islamic way to marry. The focus is on rejecting this practice, not on listing every detail of marriage law. For someone searching for no Shighar in Islam hadith, this narration gives a direct answer from the Prophet صلى الله عليه وسلم. It also connects with the wider topic of mahr and fair marriage terms, because Shighar is discussed in the nearby reports as a marriage exchange without dower."},"teachings":["Shighar is rejected in Islam.","The Hadith gives a clear rule in very few words.","Marriage should not follow a form the Prophet صلى الله عليه وسلم rejected."],"related_hadiths":[{"id":"1883","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1884","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1887","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Shighar","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith states that Shighar has no place in Islam."},"heading":{"title":"No Shighar in Islam: A Marriage Hadith With a Clear Message","description":"This Hadith about no Shighar in Islam states the matter in very plain words: there is no Shighar in Islam. The narration is short, but it carries a strong message about the marriage contract. Shighar is not presented here as a valid Islamic way to marry. The focus is on rejecting this practice, not on listing every detail of marriage law. For someone searching for no Shighar in Islam hadith, this narration gives a direct answer from the Prophet صلى الله عليه وسلم. It also connects with the wider topic of mahr and fair marriage terms, because Shighar is discussed in the nearby reports as a marriage exchange without dower."},"teachings":["Shighar is rejected in Islam.","The Hadith gives a clear rule in very few words.","Marriage should not follow a form the Prophet صلى الله عليه وسلم rejected."],"related_hadiths":[{"id":"1883","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1884","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1887","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E274" s="4" t="n"/>
@@ -6779,7 +6783,7 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Dowry","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions the dowry of the wives of the Prophet as twelve Uqiyyah and a Nash."},"heading":{"title":"Dowry of the Prophet's Wives: A Simple Hadith on Mahr","description":"This Hadith about the dowry of the Prophet's wives gives a specific amount reported by Aishah. Abu Salamah asked her how much the dowry of the wives of the Prophet صلى الله عليه وسلم was. She answered that it was twelve Uqiyyah and a Nash, then explained that a Nash is half an Uqiyyah, making the total five hundred Dirham. The main topic is mahr in Islam, and the narration gives a measured example rather than a long discussion. It helps readers see that dowry was known, named, and counted. The Hadith does not say that every dowry must be this amount. It simply reports what Aishah said about the dowry given to the Prophet's wives."},"teachings":["The dowry of the Prophet's wives is reported with a clear amount.","The narration shows that mahr was recognized and counted.","The Hadith gives an example without stating that every dowry must be the same."],"related_hadiths":[{"id":"1887","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1888","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1889","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Dowry","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions the dowry of the wives of the Prophet as twelve Uqiyyah and a Nash."},"heading":{"title":"Dowry of the Prophet's Wives: A Simple Hadith on Mahr","description":"This Hadith about the dowry of the Prophet's wives gives a specific amount reported by Aishah. Abu Salamah asked her how much the dowry of the wives of the Prophet صلى الله عليه وسلم was. She answered that it was twelve Uqiyyah and a Nash, then explained that a Nash is half an Uqiyyah, making the total five hundred Dirham. The main topic is mahr in Islam, and the narration gives a measured example rather than a long discussion. It helps readers see that dowry was known, named, and counted. The Hadith does not say that every dowry must be this amount. It simply reports what Aishah said about the dowry given to the Prophet's wives."},"teachings":["The dowry of the Prophet's wives is reported with a clear amount.","The narration shows that mahr was recognized and counted.","The Hadith gives an example without stating that every dowry must be the same."],"related_hadiths":[{"id":"1887","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1888","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1889","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E275" s="4" t="n"/>
@@ -6802,7 +6806,7 @@
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Moderate Dowry","description":"$book_name$ $hadith_number$ - $chapter_name$. This report from Umar warns against extreme dowries and mentions the dowry practice of the Prophet."},"heading":{"title":"Moderate Dowry in Islam: Umar's Warning Against Excess","description":"This Hadith report about moderate dowry in Islam shares the words of Umar bin Khattab. He warned people not to go to extremes with the dowries of women. His reason was clear: if a high dowry were a sign of honor in this world or taqwa before Allah, then the Prophet صلى الله عليه وسلم would have been more deserving of it. Umar then mentioned that the Prophet did not give any of his wives, and none of his daughters were given, more than twelve Uqiyyah. The report also warns that a heavy dowry can create resentment and hardship. The message is not that dowry has no value. It is that mahr should not become a burden or a source of bitterness."},"teachings":["Dowry should not be pushed to extremes.","A high dowry is not presented here as a sign of taqwa.","A heavy dowry may lead to resentment and hardship."],"related_hadiths":[{"id":"1886","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1888","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1889","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Moderate Dowry","description":"$book_name$ $hadith_number$ - $chapter_name$. This report from Umar warns against extreme dowries and mentions the dowry practice of the Prophet."},"heading":{"title":"Moderate Dowry in Islam: Umar's Warning Against Excess","description":"This Hadith report about moderate dowry in Islam shares the words of Umar bin Khattab. He warned people not to go to extremes with the dowries of women. His reason was clear: if a high dowry were a sign of honor in this world or taqwa before Allah, then the Prophet صلى الله عليه وسلم would have been more deserving of it. Umar then mentioned that the Prophet did not give any of his wives, and none of his daughters were given, more than twelve Uqiyyah. The report also warns that a heavy dowry can create resentment and hardship. The message is not that dowry has no value. It is that mahr should not become a burden or a source of bitterness."},"teachings":["Dowry should not be pushed to extremes.","A high dowry is not presented here as a sign of taqwa.","A heavy dowry may lead to resentment and hardship."],"related_hadiths":[{"id":"1886","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1888","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1889","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E276" s="4" t="n"/>
@@ -6825,7 +6829,7 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Simple Dowry","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith reports that the Prophet permitted a marriage with a pair of sandals as the dower."},"heading":{"title":"Simple Dowry Hadith: Marriage With a Pair of Sandals","description":"This Hadith about simple dowry in Islam reports that a man from Banu Fazarah got married for a pair of sandals, and the Prophet صلى الله عليه وسلم permitted his marriage. The narration is brief, so the message should stay simple. It shows that the value of mahr mentioned in a marriage could be modest. It also fits with the nearby reports that warn against making dowry heavy and difficult. For someone searching for low mahr hadith or simple dowry hadith, this narration is often remembered because the item was very small in value. The Hadith does not cancel the idea of dowry. It shows that marriage was allowed even when the dower was simple."},"teachings":["A marriage was permitted with a very simple dower.","The Hadith shows that mahr does not have to be heavy.","The narration supports ease in marriage when the contract is valid."],"related_hadiths":[{"id":"1886","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1887","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1889","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Simple Dowry","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith reports that the Prophet permitted a marriage with a pair of sandals as the dower."},"heading":{"title":"Simple Dowry Hadith: Marriage With a Pair of Sandals","description":"This Hadith about simple dowry in Islam reports that a man from Banu Fazarah got married for a pair of sandals, and the Prophet صلى الله عليه وسلم permitted his marriage. The narration is brief, so the message should stay simple. It shows that the value of mahr mentioned in a marriage could be modest. It also fits with the nearby reports that warn against making dowry heavy and difficult. For someone searching for low mahr hadith or simple dowry hadith, this narration is often remembered because the item was very small in value. The Hadith does not cancel the idea of dowry. It shows that marriage was allowed even when the dower was simple."},"teachings":["A marriage was permitted with a very simple dower.","The Hadith shows that mahr does not have to be heavy.","The narration supports ease in marriage when the contract is valid."],"related_hadiths":[{"id":"1886","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1887","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1889","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E277" s="4" t="n"/>
@@ -6848,7 +6852,7 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Quran as Mahr","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows the Prophet asking for a gift, even an iron ring, then marrying a man for what he knew of the Quran."},"heading":{"title":"Quran as Mahr Hadith: Give Something, Even an Iron Ring","description":"This Hadith about Quran as mahr tells a simple story. A woman came to the Prophet صلى الله عليه وسلم, and he asked who would marry her. A man said he would. The Prophet told him to give her something, even an iron ring. When the man said he did not have one, the Prophet said that he married her to him for what he knew of the Quran. The main lesson is that the marriage contract still looked for something to be given, but the matter was not made impossible for a person with very little wealth. For searches like iron ring mahr hadith or Quran as dowry hadith, this narration shows ease while still treating marriage seriously."},"teachings":["The Prophet صلى الله عليه وسلم first asked the man to give something as mahr.","Even a small item like an iron ring was mentioned.","When the man had nothing, what he knew of the Quran was accepted in this case."],"related_hadiths":[{"id":"1888","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1887","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1886","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Quran as Mahr","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows the Prophet asking for a gift, even an iron ring, then marrying a man for what he knew of the Quran."},"heading":{"title":"Quran as Mahr Hadith: Give Something, Even an Iron Ring","description":"This Hadith about Quran as mahr tells a simple story. A woman came to the Prophet صلى الله عليه وسلم, and he asked who would marry her. A man said he would. The Prophet told him to give her something, even an iron ring. When the man said he did not have one, the Prophet said that he married her to him for what he knew of the Quran. The main lesson is that the marriage contract still looked for something to be given, but the matter was not made impossible for a person with very little wealth. For searches like iron ring mahr hadith or Quran as dowry hadith, this narration shows ease while still treating marriage seriously."},"teachings":["The Prophet صلى الله عليه وسلم first asked the man to give something as mahr.","Even a small item like an iron ring was mentioned.","When the man had nothing, what he knew of the Quran was accepted in this case."],"related_hadiths":[{"id":"1888","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1887","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1886","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E278" s="4" t="n"/>
@@ -6871,7 +6875,7 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Conveying Allah's Message","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet sought help to convey Allah's message when Quraysh stopped him from speaking openly."},"heading":{"title":"Hadith About Conveying Allah's Message","description":"This Hadith shows the Prophet's strong effort to convey the message of his Lord, even when he faced opposition from Quraysh. During the Hajj season, he would meet people and ask if anyone could take him to their people so he could share the speech of Allah. The main lesson is about dawah, patience, and seeking a path to share the truth. The Hadith does not describe anger or revenge. It simply shows steady effort in delivering the message. For anyone searching for a hadith about conveying Islam, this narration gives a clear picture of sincere mission, courage, and dependence on help from Allah."},"teachings":["The Prophet continued conveying Allah's message even when people tried to stop him.","Dawah can require patience, effort, and seeking lawful support.","The message being conveyed was described as the speech of the Lord.","Opposition did not stop the Prophet from looking for another way to reach people."],"related_hadiths":[{"id":"67","book_id":"1","label":"Sahih Bukhari"},{"id":"3461","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Conveying Allah's Message","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet sought help to convey Allah's message when Quraysh stopped him from speaking openly."},"heading":{"title":"Hadith About Conveying Allah's Message","description":"This Hadith shows the Prophet's strong effort to convey the message of his Lord, even when he faced opposition from Quraysh. During the Hajj season, he would meet people and ask if anyone could take him to their people so he could share the speech of Allah. The main lesson is about dawah, patience, and seeking a path to share the truth. The Hadith does not describe anger or revenge. It simply shows steady effort in delivering the message. For anyone searching for a hadith about conveying Islam, this narration gives a clear picture of sincere mission, courage, and dependence on help from Allah."},"teachings":["The Prophet continued conveying Allah's message even when people tried to stop him.","Dawah can require patience, effort, and seeking lawful support.","The message being conveyed was described as the speech of the Lord.","Opposition did not stop the Prophet from looking for another way to reach people."],"related_hadiths":[{"id":"67","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3461","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E279" s="4" t="n"/>
@@ -6894,7 +6898,7 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah Forgives and Relieves","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah's affairs include forgiving sins, easing distress, raising some people and lowering others."},"heading":{"title":"Hadith About Allah Forgiving Sins and Relieving Distress","description":"This Hadith explains part of the meaning of the verse, \"Every day He is engaged in some affair.\" The Prophet mentioned that Allah's affairs include forgiving sins, relieving distress, raising some people, and bringing others low. The wording teaches hope, humility, and awareness of Allah's power. A believer should not think that hardship is beyond Allah's relief, or that sin is beyond Allah's forgiveness when a person turns back to Him. At the same time, the Hadith reminds us that honor and lowering are in Allah's control. For people searching for a hadith about Allah forgiving sins, this narration gives a short and powerful reminder of His mercy and authority."},"teachings":["Allah forgives sins as part of His ongoing affairs.","Relief from distress is from Allah.","Status and honor are in Allah's control.","The Hadith encourages hope without making a person careless about sin."],"related_hadiths":[{"id":"1145","book_id":"1","label":"Sahih Bukhari"},{"id":"7507","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah Forgives and Relieves","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah's affairs include forgiving sins, easing distress, raising some people and lowering others."},"heading":{"title":"Hadith About Allah Forgiving Sins and Relieving Distress","description":"This Hadith explains part of the meaning of the verse, \"Every day He is engaged in some affair.\" The Prophet mentioned that Allah's affairs include forgiving sins, relieving distress, raising some people, and bringing others low. The wording teaches hope, humility, and awareness of Allah's power. A believer should not think that hardship is beyond Allah's relief, or that sin is beyond Allah's forgiveness when a person turns back to Him. At the same time, the Hadith reminds us that honor and lowering are in Allah's control. For people searching for a hadith about Allah forgiving sins, this narration gives a short and powerful reminder of His mercy and authority."},"teachings":["Allah forgives sins as part of His ongoing affairs.","Relief from distress is from Allah.","Status and honor are in Allah's control.","The Hadith encourages hope without making a person careless about sin."],"related_hadiths":[{"id":"1145","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7507","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E280" s="4" t="n"/>
@@ -6917,7 +6921,7 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward for a Good Practice","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever starts a good practice receives its reward and the reward of those who follow it."},"heading":{"title":"Hadith About Starting a Good Practice","description":"This Hadith teaches that a person's influence can continue after an action begins. Whoever introduces a good practice that others follow receives its reward and a reward like those who act on it, without reducing their reward. The Hadith also warns that introducing a bad practice carries a burden of sin like those who follow it, without reducing their burden. The core message is responsibility. Our choices can guide people toward good or pull them toward harm. For anyone searching for a hadith about good practice and bad practice, this narration explains that influence is not small. It can carry ongoing reward or ongoing sin."},"teachings":["A good practice followed by others can become a source of continuing reward.","The reward of followers is not reduced when the first person is rewarded.","A bad practice followed by others brings serious responsibility.","People should think carefully before encouraging others toward any action."],"related_hadiths":[{"id":"1017a","book_id":"2","label":"Sahih Muslim"},{"id":"2674","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward for a Good Practice","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever starts a good practice receives its reward and the reward of those who follow it."},"heading":{"title":"Hadith About Starting a Good Practice","description":"This Hadith teaches that a person's influence can continue after an action begins. Whoever introduces a good practice that others follow receives its reward and a reward like those who act on it, without reducing their reward. The Hadith also warns that introducing a bad practice carries a burden of sin like those who follow it, without reducing their burden. The core message is responsibility. Our choices can guide people toward good or pull them toward harm. For anyone searching for a hadith about good practice and bad practice, this narration explains that influence is not small. It can carry ongoing reward or ongoing sin."},"teachings":["A good practice followed by others can become a source of continuing reward.","The reward of followers is not reduced when the first person is rewarded.","A bad practice followed by others brings serious responsibility.","People should think carefully before encouraging others toward any action."],"related_hadiths":[{"id":"1017a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2674","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E281" s="4" t="n"/>
@@ -6940,7 +6944,7 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Inspiring Charity and Good","description":"$book_name$ $hadith_number$ - $chapter_name$. One act of giving encouraged a whole gathering to give charity, showing the reward of good example."},"heading":{"title":"Hadith About Charity and Starting Good","description":"This Hadith gives a clear example of how one good action can inspire many others. A man came to the Prophet, and the Prophet encouraged people to give charity to him. When one man offered something, the whole gathering followed and gave, whether little or much. Then the Prophet explained the rule: whoever begins a good practice that others follow receives a full reward and a reward like those who follow it, without reducing their reward. The same applies in the opposite direction for a bad practice. This hadith about charity and good example shows that even a small first step can encourage others to do good."},"teachings":["Giving charity can encourage others to give as well.","A good example may open the door for wider good.","The amount given may be little or much, but people still shared what they could.","A person should avoid becoming the cause of a bad practice."],"related_hadiths":[{"id":"1017a","book_id":"2","label":"Sahih Muslim"},{"id":"1427","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Inspiring Charity and Good","description":"$book_name$ $hadith_number$ - $chapter_name$. One act of giving encouraged a whole gathering to give charity, showing the reward of good example."},"heading":{"title":"Hadith About Charity and Starting Good","description":"This Hadith gives a clear example of how one good action can inspire many others. A man came to the Prophet, and the Prophet encouraged people to give charity to him. When one man offered something, the whole gathering followed and gave, whether little or much. Then the Prophet explained the rule: whoever begins a good practice that others follow receives a full reward and a reward like those who follow it, without reducing their reward. The same applies in the opposite direction for a bad practice. This hadith about charity and good example shows that even a small first step can encourage others to do good."},"teachings":["Giving charity can encourage others to give as well.","A good example may open the door for wider good.","The amount given may be little or much, but people still shared what they could.","A person should avoid becoming the cause of a bad practice."],"related_hadiths":[{"id":"1017a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1427","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E282" s="4" t="n"/>
@@ -6963,7 +6967,7 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Calling to Guidance or Misguidance","description":"$book_name$ $hadith_number$ - $chapter_name$. A caller to guidance gains reward, while a caller to misguidance bears a share of sin."},"heading":{"title":"Hadith About Calling to Guidance","description":"This Hadith speaks directly about the effect of calling people toward guidance or misguidance. The Prophet said that a caller who invites people to misguidance and is followed will carry a burden of sin like those who follow him, without reducing their burden. A caller who invites people to true guidance and is followed will receive a reward like those who follow him, without reducing their reward. This is a clear warning about influence. Words, advice, teaching, and public calls matter. For anyone searching for a hadith about calling to guidance, this narration teaches that guiding others to good is valuable, while leading others toward error is dangerous."},"teachings":["Calling people to true guidance can bring reward when they follow it.","Calling people to misguidance brings responsibility when they follow it.","The reward or sin of followers is not reduced.","A person should be careful about what they invite others to do."],"related_hadiths":[{"id":"2674","book_id":"2","label":"Sahih Muslim"},{"id":"1017a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Calling to Guidance or Misguidance","description":"$book_name$ $hadith_number$ - $chapter_name$. A caller to guidance gains reward, while a caller to misguidance bears a share of sin."},"heading":{"title":"Hadith About Calling to Guidance","description":"This Hadith speaks directly about the effect of calling people toward guidance or misguidance. The Prophet said that a caller who invites people to misguidance and is followed will carry a burden of sin like those who follow him, without reducing their burden. A caller who invites people to true guidance and is followed will receive a reward like those who follow him, without reducing their reward. This is a clear warning about influence. Words, advice, teaching, and public calls matter. For anyone searching for a hadith about calling to guidance, this narration teaches that guiding others to good is valuable, while leading others toward error is dangerous."},"teachings":["Calling people to true guidance can bring reward when they follow it.","Calling people to misguidance brings responsibility when they follow it.","The reward or sin of followers is not reduced.","A person should be careful about what they invite others to do."],"related_hadiths":[{"id":"2674","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1017a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E283" s="4" t="n"/>
@@ -6986,7 +6990,7 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward for Calling to Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever calls to true guidance receives reward like those who follow, without reducing theirs."},"heading":{"title":"Hadith About Reward for Calling to Guidance","description":"This Hadith explains the value and responsibility of inviting people. Whoever calls people to true guidance receives a reward like the reward of those who follow him, without taking anything away from their reward. Whoever calls people to misguidance carries sin like the sins of those who follow him, without reducing their sins. The message is simple: guidance and misguidance both have effects beyond the first speaker. A person may say something, teach something, or encourage something, and others may act on it. This hadith about reward for guiding others reminds us to speak and invite with care, sincerity, and truth."},"teachings":["Calling to true guidance can bring reward when people follow it.","The followers keep their own reward fully.","Calling to misguidance brings a share of sin if people follow it.","A person's words can have lasting effects."],"related_hadiths":[{"id":"2674","book_id":"2","label":"Sahih Muslim"},{"id":"3461","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward for Calling to Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever calls to true guidance receives reward like those who follow, without reducing theirs."},"heading":{"title":"Hadith About Reward for Calling to Guidance","description":"This Hadith explains the value and responsibility of inviting people. Whoever calls people to true guidance receives a reward like the reward of those who follow him, without taking anything away from their reward. Whoever calls people to misguidance carries sin like the sins of those who follow him, without reducing their sins. The message is simple: guidance and misguidance both have effects beyond the first speaker. A person may say something, teach something, or encourage something, and others may act on it. This hadith about reward for guiding others reminds us to speak and invite with care, sincerity, and truth."},"teachings":["Calling to true guidance can bring reward when people follow it.","The followers keep their own reward fully.","Calling to misguidance brings a share of sin if people follow it.","A person's words can have lasting effects."],"related_hadiths":[{"id":"2674","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"3461","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E284" s="4" t="n"/>
@@ -7009,7 +7013,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Impact of Good and Evil Practices","description":"$book_name$ $hadith_number$ - $chapter_name$. Good and evil practices can continue through others, bringing reward or burden after a person."},"heading":{"title":"Hadith About Good and Evil Practices","description":"This Hadith teaches that a practice may continue after the one who began it. If someone introduces a good practice and people act upon it after him, he receives its reward and a reward like theirs, without reducing their reward. If someone introduces an evil practice and people follow it after him, he carries its burden and a burden like theirs, without reducing their burden. The focus is not only on the first action, but on what that action leads others to do. For anyone searching for a hadith about good and evil practices, this narration gives a balanced reminder: influence can be a door to reward or a source of sin."},"teachings":["Good influence can continue after a person.","The reward of those who follow good is not reduced.","Evil influence can also continue after a person.","A person should think about the effects of what they begin."],"related_hadiths":[{"id":"1017a","book_id":"2","label":"Sahih Muslim"},{"id":"2697","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Impact of Good and Evil Practices","description":"$book_name$ $hadith_number$ - $chapter_name$. Good and evil practices can continue through others, bringing reward or burden after a person."},"heading":{"title":"Hadith About Good and Evil Practices","description":"This Hadith teaches that a practice may continue after the one who began it. If someone introduces a good practice and people act upon it after him, he receives its reward and a reward like theirs, without reducing their reward. If someone introduces an evil practice and people follow it after him, he carries its burden and a burden like theirs, without reducing their burden. The focus is not only on the first action, but on what that action leads others to do. For anyone searching for a hadith about good and evil practices, this narration gives a balanced reminder: influence can be a door to reward or a source of sin."},"teachings":["Good influence can continue after a person.","The reward of those who follow good is not reduced.","Evil influence can also continue after a person.","A person should think about the effects of what they begin."],"related_hadiths":[{"id":"1017a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2697","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E285" s="4" t="n"/>
@@ -7032,7 +7036,7 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Accountability for What We Invite To","description":"$book_name$ $hadith_number$ - $chapter_name$. Every caller will stand with what he called to, even if he invited only one person."},"heading":{"title":"Hadith About Accountability for Calling Others","description":"This Hadith gives a strong warning about inviting others toward anything. The Prophet said that every caller who invites people to something will be made to stand on the Day of Resurrection next to what he called to, even if he only called one person. The Hadith does not limit the warning to large crowds. Even one person matters. This makes the topic of influence very serious. Advice, speech, teaching, and invitation should not be treated lightly. For anyone searching for a hadith about accountability for calling others, this narration teaches that a person is connected to what he encourages others to follow."},"teachings":["A caller is accountable for what he invites others toward.","Even calling one person is treated seriously in this Hadith.","The Day of Resurrection is mentioned as the place of this accountability.","A person should be careful before encouraging others toward any path."],"related_hadiths":[{"id":"2674","book_id":"2","label":"Sahih Muslim"},{"id":"1017a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Accountability for What We Invite To","description":"$book_name$ $hadith_number$ - $chapter_name$. Every caller will stand with what he called to, even if he invited only one person."},"heading":{"title":"Hadith About Accountability for Calling Others","description":"This Hadith gives a strong warning about inviting others toward anything. The Prophet said that every caller who invites people to something will be made to stand on the Day of Resurrection next to what he called to, even if he only called one person. The Hadith does not limit the warning to large crowds. Even one person matters. This makes the topic of influence very serious. Advice, speech, teaching, and invitation should not be treated lightly. For anyone searching for a hadith about accountability for calling others, this narration teaches that a person is connected to what he encourages others to follow."},"teachings":["A caller is accountable for what he invites others toward.","Even calling one person is treated seriously in this Hadith.","The Day of Resurrection is mentioned as the place of this accountability.","A person should be careful before encouraging others toward any path."],"related_hadiths":[{"id":"2674","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1017a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E286" s="4" t="n"/>
@@ -7055,7 +7059,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reviving a Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Reviving a Sunnah that people act upon brings reward, while introducing Bid'ah brings burden."},"heading":{"title":"Hadith About Reviving a Sunnah","description":"This Hadith speaks about reviving a Sunnah of the Prophet and the danger of introducing Bid'ah. Whoever revives a Sunnah that people then act upon receives a reward like those who act on it, without reducing their reward. In contrast, whoever introduces an innovation that people act upon carries burdens like those who follow it, without reducing their burden. The Hadith focuses on what people act upon after being shown a way. It teaches care in religious practice and respect for the Sunnah. For people searching for a hadith about reviving Sunnah, this narration connects love for Sunnah with responsible action."},"teachings":["Reviving a Sunnah can lead to reward when people act upon it.","The reward of those who follow the Sunnah is not reduced.","Introducing Bid'ah that others act upon brings a burden of sin.","Religious influence should be tied to the Sunnah, not personal invention."],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"1017a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reviving a Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Reviving a Sunnah that people act upon brings reward, while introducing Bid'ah brings burden."},"heading":{"title":"Hadith About Reviving a Sunnah","description":"This Hadith speaks about reviving a Sunnah of the Prophet and the danger of introducing Bid'ah. Whoever revives a Sunnah that people then act upon receives a reward like those who act on it, without reducing their reward. In contrast, whoever introduces an innovation that people act upon carries burdens like those who follow it, without reducing their burden. The Hadith focuses on what people act upon after being shown a way. It teaches care in religious practice and respect for the Sunnah. For people searching for a hadith about reviving Sunnah, this narration connects love for Sunnah with responsible action."},"teachings":["Reviving a Sunnah can lead to reward when people act upon it.","The reward of those who follow the Sunnah is not reduced.","Introducing Bid'ah that others act upon brings a burden of sin.","Religious influence should be tied to the Sunnah, not personal invention."],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1017a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E287" s="4" t="n"/>
@@ -7078,7 +7082,7 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward for Reviving a Forgotten Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever revives a Sunnah that died out gains reward like those who act on it."},"heading":{"title":"Hadith About Reviving a Forgotten Sunnah","description":"This Hadith speaks about reviving a Sunnah of the Prophet after it has died out among people. The Prophet said that the one who revives it receives a reward like those who act upon it, without reducing their reward. The Hadith also warns against introducing a Bid'ah that Allah and His Messenger are not pleased with. If people act upon it, the one who introduced it carries a sin like theirs, without reducing their sins. This hadith about forgotten Sunnah teaches love for the Prophet's way and caution in religion. It encourages returning to the Sunnah, not making disliked religious innovations."},"teachings":["A Sunnah that has died out can be revived and practiced again.","People who act on that revived Sunnah keep their full reward.","Introducing a displeasing Bid'ah brings serious responsibility.","A person should care about whether Allah and His Messenger are pleased with an act."],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"1017a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward for Reviving a Forgotten Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever revives a Sunnah that died out gains reward like those who act on it."},"heading":{"title":"Hadith About Reviving a Forgotten Sunnah","description":"This Hadith speaks about reviving a Sunnah of the Prophet after it has died out among people. The Prophet said that the one who revives it receives a reward like those who act upon it, without reducing their reward. The Hadith also warns against introducing a Bid'ah that Allah and His Messenger are not pleased with. If people act upon it, the one who introduced it carries a sin like theirs, without reducing their sins. This hadith about forgotten Sunnah teaches love for the Prophet's way and caution in religion. It encourages returning to the Sunnah, not making disliked religious innovations."},"teachings":["A Sunnah that has died out can be revived and practiced again.","People who act on that revived Sunnah keep their full reward.","Introducing a displeasing Bid'ah brings serious responsibility.","A person should care about whether Allah and His Messenger are pleased with an act."],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1017a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E288" s="4" t="n"/>
@@ -7101,7 +7105,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learn and Teach the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. The best or most excellent people are those who learn the Qur'an and teach it."},"heading":{"title":"Hadith About Learning and Teaching the Qur'an","description":"This Hadith highlights the honor of learning and teaching the Qur'an. The narration mentions two wordings from two narrators: one says, \"The best of you,\" and the other says, \"The most excellent of you is the one who learns the Qur'an and teaches it.\" The meaning is clear in both wordings. A person is raised in goodness by connecting with the Qur'an through learning and then sharing that learning with others. This does not need complicated explanation. The Hadith encourages a living relationship with the Qur'an. For anyone searching for a hadith about learning Quran, this is one of the clearest narrations on the value of learning and teaching."},"teachings":["Learning the Qur'an is a highly praised act.","Teaching the Qur'an to others is also highly praised.","The Hadith links excellence with both learning and teaching.","The narration preserves the wording differences of two narrators."],"related_hadiths":[{"id":"5027","book_id":"1","label":"Sahih Bukhari"},{"id":"1452","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learn and Teach the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. The best or most excellent people are those who learn the Qur'an and teach it."},"heading":{"title":"Hadith About Learning and Teaching the Qur'an","description":"This Hadith highlights the honor of learning and teaching the Qur'an. The narration mentions two wordings from two narrators: one says, \"The best of you,\" and the other says, \"The most excellent of you is the one who learns the Qur'an and teaches it.\" The meaning is clear in both wordings. A person is raised in goodness by connecting with the Qur'an through learning and then sharing that learning with others. This does not need complicated explanation. The Hadith encourages a living relationship with the Qur'an. For anyone searching for a hadith about learning Quran, this is one of the clearest narrations on the value of learning and teaching."},"teachings":["Learning the Qur'an is a highly praised act.","Teaching the Qur'an to others is also highly praised.","The Hadith links excellence with both learning and teaching.","The narration preserves the wording differences of two narrators."],"related_hadiths":[{"id":"5027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1452","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E289" s="4" t="n"/>
@@ -7124,7 +7128,7 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Excellence of Teaching Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. The most excellent person is the one who learns the Qur'an and teaches it."},"heading":{"title":"Hadith About the Excellence of Learning Qur'an","description":"This Hadith gives a short and direct message: the most excellent among people are those who learn the Qur'an and teach it. It does not only mention personal reading. It joins learning with teaching. This shows that Qur'an knowledge is not meant to stay locked inside a person when there is a chance to pass it on properly. The Hadith is simple, but its meaning is deep for daily life. A person can begin with learning one verse, correcting recitation, or helping someone else learn what they know. For users searching for the best of you learn Quran and teach it hadith, this narration gives the exact teaching in clear words."},"teachings":["The Qur'an should be learned with care.","Teaching the Qur'an is a praised act.","Excellence is linked with serving the Qur'an.","The Hadith encourages sharing Qur'an knowledge with others."],"related_hadiths":[{"id":"5027","book_id":"1","label":"Sahih Bukhari"},{"id":"1452","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Excellence of Teaching Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. The most excellent person is the one who learns the Qur'an and teaches it."},"heading":{"title":"Hadith About the Excellence of Learning Qur'an","description":"This Hadith gives a short and direct message: the most excellent among people are those who learn the Qur'an and teach it. It does not only mention personal reading. It joins learning with teaching. This shows that Qur'an knowledge is not meant to stay locked inside a person when there is a chance to pass it on properly. The Hadith is simple, but its meaning is deep for daily life. A person can begin with learning one verse, correcting recitation, or helping someone else learn what they know. For users searching for the best of you learn Quran and teach it hadith, this narration gives the exact teaching in clear words."},"teachings":["The Qur'an should be learned with care.","Teaching the Qur'an is a praised act.","Excellence is linked with serving the Qur'an.","The Hadith encourages sharing Qur'an knowledge with others."],"related_hadiths":[{"id":"5027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1452","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E290" s="4" t="n"/>
@@ -7147,7 +7151,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Teaching Qur'an in Practice","description":"$book_name$ $hadith_number$ - $chapter_name$. The best people learn and teach the Qur'an, and the narrator acted on this teaching."},"heading":{"title":"Hadith About Teaching the Qur'an to Others","description":"This Hadith repeats the great teaching that the best of people are those who learn the Qur'an and teach it. What makes this narration stand out is the action that follows. The narrator says that he was taken by the hand and made to sit in a place where he began teaching Qur'an. The Hadith therefore shows both the statement and a practical response to it. It is not only about admiring Qur'an teachers from a distance. It points toward action. For anyone searching for a hadith about teaching Quran, this narration reminds us that learning can lead to service when a person is able to teach correctly."},"teachings":["Learning and teaching the Qur'an is described as a mark of goodness.","The narrator responded by teaching Qur'an.","Good knowledge can lead to direct service.","Teaching should be connected to what a person has learned."],"related_hadiths":[{"id":"5027","book_id":"1","label":"Sahih Bukhari"},{"id":"1452","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Teaching Qur'an in Practice","description":"$book_name$ $hadith_number$ - $chapter_name$. The best people learn and teach the Qur'an, and the narrator acted on this teaching."},"heading":{"title":"Hadith About Teaching the Qur'an to Others","description":"This Hadith repeats the great teaching that the best of people are those who learn the Qur'an and teach it. What makes this narration stand out is the action that follows. The narrator says that he was taken by the hand and made to sit in a place where he began teaching Qur'an. The Hadith therefore shows both the statement and a practical response to it. It is not only about admiring Qur'an teachers from a distance. It points toward action. For anyone searching for a hadith about teaching Quran, this narration reminds us that learning can lead to service when a person is able to teach correctly."},"teachings":["Learning and teaching the Qur'an is described as a mark of goodness.","The narrator responded by teaching Qur'an.","Good knowledge can lead to direct service.","Teaching should be connected to what a person has learned."],"related_hadiths":[{"id":"5027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1452","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E291" s="4" t="n"/>
@@ -7170,7 +7174,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The People of the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. The people of the Qur'an are described as Allah's special people among mankind."},"heading":{"title":"Hadith About the People of the Qur'an","description":"This Hadith gives a beautiful description of the people of the Qur'an. The Prophet said that Allah has His own people among mankind. When the Companions asked who they are, he said they are the people of the Qur'an, the people of Allah and those closest to Him. The wording points to honor for those connected to the Qur'an. The Hadith does not explain every detail of what makes someone from the people of the Qur'an, so the explanation should stay close to the text. For anyone searching for a hadith about people of Quran, this narration clearly shows the special rank attached to the Qur'an."},"teachings":["Allah has special people among mankind.","The people of the Qur'an are given a special description in this Hadith.","Being connected to the Qur'an is a source of honor.","The Companions asked for clarity, and the Prophet answered directly."],"related_hadiths":[{"id":"5027","book_id":"1","label":"Sahih Bukhari"},{"id":"2914","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The People of the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. The people of the Qur'an are described as Allah's special people among mankind."},"heading":{"title":"Hadith About the People of the Qur'an","description":"This Hadith gives a beautiful description of the people of the Qur'an. The Prophet said that Allah has His own people among mankind. When the Companions asked who they are, he said they are the people of the Qur'an, the people of Allah and those closest to Him. The wording points to honor for those connected to the Qur'an. The Hadith does not explain every detail of what makes someone from the people of the Qur'an, so the explanation should stay close to the text. For anyone searching for a hadith about people of Quran, this narration clearly shows the special rank attached to the Qur'an."},"teachings":["Allah has special people among mankind.","The people of the Qur'an are given a special description in this Hadith.","Being connected to the Qur'an is a source of honor.","The Companions asked for clarity, and the Prophet answered directly."],"related_hadiths":[{"id":"5027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2914","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E292" s="4" t="n"/>
@@ -7193,7 +7197,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Memorizing the Qur'an and Intercession","description":"$book_name$ $hadith_number$ - $chapter_name$. The one who reads and memorizes the Qur'an is promised Paradise and intercession for family."},"heading":{"title":"Hadith About Memorizing the Qur'an","description":"This Hadith speaks about the great reward mentioned for the one who reads the Qur'an and memorizes it. The Prophet said that Allah will admit such a person to Paradise and allow him to intercede for ten family members who had deserved Hell. Because this is a specific statement from the Hadith, it should be understood with care and not expanded beyond the wording. The main focus is the virtue of Qur'an memorization and the honor given to the one who carries the Qur'an. For users searching for a hadith about memorizing Quran and intercession, this narration gives a direct text on that reward."},"teachings":["Reading and memorizing the Qur'an is linked to a great reward in this Hadith.","The Hadith mentions admission to Paradise for the one described.","The Hadith mentions intercession for ten family members.","The wording should be kept as stated, without adding extra promises."],"related_hadiths":[{"id":"2905","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"2914","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Memorizing the Qur'an and Intercession","description":"$book_name$ $hadith_number$ - $chapter_name$. The one who reads and memorizes the Qur'an is promised Paradise and intercession for family."},"heading":{"title":"Hadith About Memorizing the Qur'an","description":"This Hadith speaks about the great reward mentioned for the one who reads the Qur'an and memorizes it. The Prophet said that Allah will admit such a person to Paradise and allow him to intercede for ten family members who had deserved Hell. Because this is a specific statement from the Hadith, it should be understood with care and not expanded beyond the wording. The main focus is the virtue of Qur'an memorization and the honor given to the one who carries the Qur'an. For users searching for a hadith about memorizing Quran and intercession, this narration gives a direct text on that reward."},"teachings":["Reading and memorizing the Qur'an is linked to a great reward in this Hadith.","The Hadith mentions admission to Paradise for the one described.","The Hadith mentions intercession for ten family members.","The wording should be kept as stated, without adding extra promises."],"related_hadiths":[{"id":"2905","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"2914","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E293" s="4" t="n"/>
@@ -7216,7 +7220,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learning Qur'an and Acting Upon It","description":"$book_name$ $hadith_number$ - $chapter_name$. The Qur'an acted upon is like musk spreading fragrance everywhere."},"heading":{"title":"Hadith About Learning and Acting Upon the Qur'an","description":"This Hadith teaches that learning the Qur'an should lead to recitation and action. The Prophet told people to learn the Qur'an, recite it, and go to bed. Then he gave two examples. The one who learns it and stands with it is like a sack filled with musk, spreading fragrance everywhere. The one who learns it but sleeps while it is in his heart is like a tied sack of musk whose fragrance does not come out. The main message is not only memorizing or holding the Qur'an inside, but letting its good effect appear through action. This hadith about acting upon the Qur'an is a strong reminder to live what is learned."},"teachings":["Learning the Qur'an should be joined with recitation.","Acting upon the Qur'an spreads benefit like fragrance.","Keeping Qur'an knowledge unused is compared to tied-up musk.","The Hadith encourages a living relationship with the Qur'an."],"related_hadiths":[{"id":"5020","book_id":"1","label":"Sahih Bukhari"},{"id":"5027","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learning Qur'an and Acting Upon It","description":"$book_name$ $hadith_number$ - $chapter_name$. The Qur'an acted upon is like musk spreading fragrance everywhere."},"heading":{"title":"Hadith About Learning and Acting Upon the Qur'an","description":"This Hadith teaches that learning the Qur'an should lead to recitation and action. The Prophet told people to learn the Qur'an, recite it, and go to bed. Then he gave two examples. The one who learns it and stands with it is like a sack filled with musk, spreading fragrance everywhere. The one who learns it but sleeps while it is in his heart is like a tied sack of musk whose fragrance does not come out. The main message is not only memorizing or holding the Qur'an inside, but letting its good effect appear through action. This hadith about acting upon the Qur'an is a strong reminder to live what is learned."},"teachings":["Learning the Qur'an should be joined with recitation.","Acting upon the Qur'an spreads benefit like fragrance.","Keeping Qur'an knowledge unused is compared to tied-up musk.","The Hadith encourages a living relationship with the Qur'an."],"related_hadiths":[{"id":"5020","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E294" s="4" t="n"/>
@@ -7239,7 +7243,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah Raises People by the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. Knowledge of Allah's Book raised Ibn Abza in status despite social background."},"heading":{"title":"Hadith About Allah Raising People by the Qur'an","description":"This Hadith shows how the Qur'an raises people in status. Nafi' appointed Ibn Abza over the people of the valley. When Umar asked about him, Nafi' explained that he had great knowledge of the Book of Allah, knew the rules of inheritance, and was a good judge. Umar then mentioned the Prophet's saying: Allah raises some people by this Book and brings others low by it. The Hadith does not praise status based on lineage or social rank. It points to the honor of knowledge of the Qur'an. For users searching for a hadith Allah raises people by Quran, this narration gives a clear example."},"teachings":["Knowledge of the Qur'an can raise a person in status.","Useful religious knowledge was considered in leadership.","Umar accepted the Prophet's teaching about the Qur'an raising people.","The Hadith shows honor tied to knowledge, not only social background."],"related_hadiths":[{"id":"817","book_id":"2","label":"Sahih Muslim"},{"id":"5027","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah Raises People by the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. Knowledge of Allah's Book raised Ibn Abza in status despite social background."},"heading":{"title":"Hadith About Allah Raising People by the Qur'an","description":"This Hadith shows how the Qur'an raises people in status. Nafi' appointed Ibn Abza over the people of the valley. When Umar asked about him, Nafi' explained that he had great knowledge of the Book of Allah, knew the rules of inheritance, and was a good judge. Umar then mentioned the Prophet's saying: Allah raises some people by this Book and brings others low by it. The Hadith does not praise status based on lineage or social rank. It points to the honor of knowledge of the Qur'an. For users searching for a hadith Allah raises people by Quran, this narration gives a clear example."},"teachings":["Knowledge of the Qur'an can raise a person in status.","Useful religious knowledge was considered in leadership.","Umar accepted the Prophet's teaching about the Qur'an raising people.","The Hadith shows honor tied to knowledge, not only social background."],"related_hadiths":[{"id":"817","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"5027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E295" s="4" t="n"/>
@@ -7262,7 +7266,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learning One Verse","description":"$book_name$ $hadith_number$ - $chapter_name$. Learning one verse or one matter of knowledge is described as better than many voluntary prayers."},"heading":{"title":"Hadith About Learning One Verse of the Qur'an","description":"This Hadith encourages seeking knowledge in a very direct way. The Prophet told Abu Dharr that going out in the morning to learn one verse from the Book of Allah is better for him than praying one hundred Rak'ah. He also said that going out to learn one matter of knowledge, whether it is acted upon or not, is better for him than praying one thousand Rak'ah. The Hadith compares learning with large amounts of prayer to show the value of knowledge. It does not reduce the value of prayer; rather, it highlights the special place of learning. This hadith about learning one verse is a clear push to seek knowledge."},"teachings":["Learning even one verse from the Qur'an has great value.","A matter of knowledge is praised, whether or not it is acted upon immediately.","The Hadith encourages going out to seek knowledge.","Knowledge is shown as a valuable act of worship."],"related_hadiths":[{"id":"71","book_id":"1","label":"Sahih Bukhari"},{"id":"224","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learning One Verse","description":"$book_name$ $hadith_number$ - $chapter_name$. Learning one verse or one matter of knowledge is described as better than many voluntary prayers."},"heading":{"title":"Hadith About Learning One Verse of the Qur'an","description":"This Hadith encourages seeking knowledge in a very direct way. The Prophet told Abu Dharr that going out in the morning to learn one verse from the Book of Allah is better for him than praying one hundred Rak'ah. He also said that going out to learn one matter of knowledge, whether it is acted upon or not, is better for him than praying one thousand Rak'ah. The Hadith compares learning with large amounts of prayer to show the value of knowledge. It does not reduce the value of prayer; rather, it highlights the special place of learning. This hadith about learning one verse is a clear push to seek knowledge."},"teachings":["Learning even one verse from the Qur'an has great value.","A matter of knowledge is praised, whether or not it is acted upon immediately.","The Hadith encourages going out to seek knowledge.","Knowledge is shown as a valuable act of worship."],"related_hadiths":[{"id":"71","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"224","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E296" s="4" t="n"/>
@@ -7285,7 +7289,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Understanding the Religion","description":"$book_name$ $hadith_number$ - $chapter_name$. When Allah wills good for someone, He gives that person understanding of the religion."},"heading":{"title":"Hadith About Understanding the Religion","description":"This Hadith is short, but it carries a strong meaning about knowledge and guidance. The Prophet said that when Allah wills good for a person, He causes that person to understand the religion. The Hadith connects goodness from Allah with fiqh, meaning sound understanding of the religion. It is not only about collecting information. It is about being granted understanding that helps a person know the religion properly. For anyone searching for the hadith whom Allah intends good, this narration is one of the clearest texts on the value of religious understanding. It encourages believers to seek knowledge while knowing that true understanding is a gift from Allah."},"teachings":["Understanding the religion is a sign of good from Allah.","Religious knowledge should lead to sound understanding.","A person should seek knowledge while depending on Allah for understanding.","The Hadith gives a simple measure of the value of fiqh in religion."],"related_hadiths":[{"id":"71","book_id":"1","label":"Sahih Bukhari"},{"id":"224","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Understanding the Religion","description":"$book_name$ $hadith_number$ - $chapter_name$. When Allah wills good for someone, He gives that person understanding of the religion."},"heading":{"title":"Hadith About Understanding the Religion","description":"This Hadith is short, but it carries a strong meaning about knowledge and guidance. The Prophet said that when Allah wills good for a person, He causes that person to understand the religion. The Hadith connects goodness from Allah with fiqh, meaning sound understanding of the religion. It is not only about collecting information. It is about being granted understanding that helps a person know the religion properly. For anyone searching for the hadith whom Allah intends good, this narration is one of the clearest texts on the value of religious understanding. It encourages believers to seek knowledge while knowing that true understanding is a gift from Allah."},"teachings":["Understanding the religion is a sign of good from Allah.","Religious knowledge should lead to sound understanding.","A person should seek knowledge while depending on Allah for understanding.","The Hadith gives a simple measure of the value of fiqh in religion."],"related_hadiths":[{"id":"71","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"224","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E297" s="4" t="n"/>
@@ -7308,7 +7312,7 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Hurairah on Sharing Hadith","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah explains why he narrated Hadith, pointing to verses that warn against hiding revealed truth."},"heading":{"title":"Concealing Knowledge in Islam: Abu Hurairah’s Reason","description":"This narration explains why Abu Hurairah narrated from the Prophet. He says that if not for two verses in the Book of Allah, he would not have narrated anything from him. The verses quoted in the text speak about people who conceal what Allah sent down and trade guidance for a small worldly gain. This makes the main message very clear: concealing knowledge in Islam is treated as a serious matter, especially when the knowledge is from revelation. Abu Hurairah’s statement shows that he saw narration as a duty connected to the Qur’an’s warning. The Hadith also points to the danger of using silence for worldly benefit when truth should be shared."},"teachings":["Abu Hurairah linked narrating Hadith with the warning against hiding revelation.","Worldly gain is not a valid reason to conceal religious truth.","The quoted verses describe painful accountability for those who hide what Allah revealed.","Sharing knowledge can be an act of responding to Allah’s command."],"related_hadiths":[{"id":"261","book_id":"6","label":"Sunan Ibn Majah"},{"id":"263","book_id":"6","label":"Sunan Ibn Majah"},{"id":"264","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Hurairah on Sharing Hadith","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah explains why he narrated Hadith, pointing to verses that warn against hiding revealed truth."},"heading":{"title":"Concealing Knowledge in Islam: Abu Hurairah’s Reason","description":"This narration explains why Abu Hurairah narrated from the Prophet. He says that if not for two verses in the Book of Allah, he would not have narrated anything from him. The verses quoted in the text speak about people who conceal what Allah sent down and trade guidance for a small worldly gain. This makes the main message very clear: concealing knowledge in Islam is treated as a serious matter, especially when the knowledge is from revelation. Abu Hurairah’s statement shows that he saw narration as a duty connected to the Qur’an’s warning. The Hadith also points to the danger of using silence for worldly benefit when truth should be shared."},"teachings":["Abu Hurairah linked narrating Hadith with the warning against hiding revelation.","Worldly gain is not a valid reason to conceal religious truth.","The quoted verses describe painful accountability for those who hide what Allah revealed.","Sharing knowledge can be an act of responding to Allah’s command."],"related_hadiths":[{"id":"261","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"263","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"264","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E298" s="4" t="n"/>
@@ -7331,7 +7335,7 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Concealing Hadith During Fitnah","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration warns that hiding Hadith is like hiding what Allah revealed, while noting its provided grade."},"heading":{"title":"Hadith About Concealing Hadith and Revealed Knowledge","description":"This narration says that when the later people of this Ummah curse the earlier people, whoever conceals a Hadith has concealed what Allah revealed. The provided text also marks this narration as Maudu, so it should not be treated the same way as a sound report. Still, the wording itself centers on the idea of concealing Hadith and hiding revealed knowledge. The message inside the wording is about the danger of silence when a Hadith is relevant to confusion or disrespect. It connects Hadith with what Allah revealed, showing that religious reports are not something to hide for personal comfort. Because the grade is stated as Maudu in the input, the explanation should stay careful and not build extra rulings from it."},"teachings":["The wording warns against hiding Hadith when people need religious clarity.","The text connects concealing Hadith with concealing revealed knowledge.","The provided grade is Maudu, so the narration should be handled with care.","The narration focuses on the danger of silence during harmful speech about earlier Muslims."],"related_hadiths":[{"id":"261","book_id":"6","label":"Sunan Ibn Majah"},{"id":"262","book_id":"6","label":"Sunan Ibn Majah"},{"id":"264","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Concealing Hadith During Fitnah","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration warns that hiding Hadith is like hiding what Allah revealed, while noting its provided grade."},"heading":{"title":"Hadith About Concealing Hadith and Revealed Knowledge","description":"This narration says that when the later people of this Ummah curse the earlier people, whoever conceals a Hadith has concealed what Allah revealed. The provided text also marks this narration as Maudu, so it should not be treated the same way as a sound report. Still, the wording itself centers on the idea of concealing Hadith and hiding revealed knowledge. The message inside the wording is about the danger of silence when a Hadith is relevant to confusion or disrespect. It connects Hadith with what Allah revealed, showing that religious reports are not something to hide for personal comfort. Because the grade is stated as Maudu in the input, the explanation should stay careful and not build extra rulings from it."},"teachings":["The wording warns against hiding Hadith when people need religious clarity.","The text connects concealing Hadith with concealing revealed knowledge.","The provided grade is Maudu, so the narration should be handled with care.","The narration focuses on the danger of silence during harmful speech about earlier Muslims."],"related_hadiths":[{"id":"261","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"262","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"264","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E299" s="4" t="n"/>
@@ -7354,7 +7358,7 @@
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Toilet Exit Dua and Gratitude","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the toilet exit dua that praises Allah for removing harm and giving health."},"heading":{"title":"Toilet Exit Dua: Gratitude After Relief","description":"This Hadith teaches a short toilet exit dua that the Prophet used to say after leaving the toilet. The words praise Allah for removing impurity and granting good health. The main lesson is simple: even after a private and normal human need, a believer can remember Allah with gratitude. The dua also shows that health, cleanliness, and relief are blessings from Allah, not things to take lightly. The wording in the Hadith does not add a long ruling or extra condition. It simply shows what the Prophet said when he exited the toilet, making it a helpful Sunnah phrase for daily life."},"teachings":["Thank Allah after relief and cleanliness.","Good health is a blessing worth remembering.","Short daily duas can keep the heart connected to Allah.","The Prophet taught gratitude even in ordinary moments."],"related_hadiths":[{"id":"302","book_id":"6","label":"Sunan Ibn Majah"},{"id":"303","book_id":"6","label":"Sunan Ibn Majah"},{"id":"313","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Toilet Exit Dua and Gratitude","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the toilet exit dua that praises Allah for removing harm and giving health."},"heading":{"title":"Toilet Exit Dua: Gratitude After Relief","description":"This Hadith teaches a short toilet exit dua that the Prophet used to say after leaving the toilet. The words praise Allah for removing impurity and granting good health. The main lesson is simple: even after a private and normal human need, a believer can remember Allah with gratitude. The dua also shows that health, cleanliness, and relief are blessings from Allah, not things to take lightly. The wording in the Hadith does not add a long ruling or extra condition. It simply shows what the Prophet said when he exited the toilet, making it a helpful Sunnah phrase for daily life."},"teachings":["Thank Allah after relief and cleanliness.","Good health is a blessing worth remembering.","Short daily duas can keep the heart connected to Allah.","The Prophet taught gratitude even in ordinary moments."],"related_hadiths":[{"id":"302","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"303","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"313","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E300" s="4" t="n"/>
@@ -7377,7 +7381,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Remembering Allah Always","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear Hadith showing that the Prophet remembered Allah in all circumstances."},"heading":{"title":"Remembering Allah in All Circumstances","description":"This Hadith gives a broad and beautiful picture of dhikr in daily life. Aishah narrated that the Messenger of Allah used to remember Allah in all circumstances. The wording is short, but its meaning is easy to feel: remembrance of Allah was not limited to one place, one mood, or one part of the day. It was part of his normal life. This Hadith does not list every form of remembrance, so the explanation should stay close to the text. It simply teaches that remembering Allah is something a believer should keep close in many situations, with respect and awareness."},"teachings":["Remembering Allah should be part of daily life.","Dhikr is not limited to one time or place.","The Prophet kept his heart connected to Allah in all circumstances.","A short report can teach a wide daily habit."],"related_hadiths":[{"id":"301","book_id":"6","label":"Sunan Ibn Majah"},{"id":"303","book_id":"6","label":"Sunan Ibn Majah"},{"id":"313","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Remembering Allah Always","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear Hadith showing that the Prophet remembered Allah in all circumstances."},"heading":{"title":"Remembering Allah in All Circumstances","description":"This Hadith gives a broad and beautiful picture of dhikr in daily life. Aishah narrated that the Messenger of Allah used to remember Allah in all circumstances. The wording is short, but its meaning is easy to feel: remembrance of Allah was not limited to one place, one mood, or one part of the day. It was part of his normal life. This Hadith does not list every form of remembrance, so the explanation should stay close to the text. It simply teaches that remembering Allah is something a believer should keep close in many situations, with respect and awareness."},"teachings":["Remembering Allah should be part of daily life.","Dhikr is not limited to one time or place.","The Prophet kept his heart connected to Allah in all circumstances.","A short report can teach a wide daily habit."],"related_hadiths":[{"id":"301","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"303","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"313","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E301" s="4" t="n"/>
@@ -7400,7 +7404,7 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Removing the Ring Before Toilet","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith reports that the Prophet took off his ring before entering the toilet."},"heading":{"title":"Toilet Etiquette: Taking Off the Ring","description":"This Hadith mentions a specific act from the Prophet when entering the toilet: he would take off his ring. The text does not explain the reason, so it is best to keep the explanation simple and close to the narration. It shows care and respect before entering a place used for relieving oneself. As a toilet etiquette Hadith, it reminds the reader that Islam teaches manners even in private matters. The report is not a long legal discussion. It only gives one clear action connected to entering the toilet, and that action reflects careful conduct in daily cleanliness."},"teachings":["The Prophet showed care before entering the toilet.","Private habits can still have manners and discipline.","The Hadith teaches a specific act without adding extra reasons.","Toilet etiquette is part of daily Islamic practice."],"related_hadiths":[{"id":"301","book_id":"6","label":"Sunan Ibn Majah"},{"id":"302","book_id":"6","label":"Sunan Ibn Majah"},{"id":"313","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Removing the Ring Before Toilet","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith reports that the Prophet took off his ring before entering the toilet."},"heading":{"title":"Toilet Etiquette: Taking Off the Ring","description":"This Hadith mentions a specific act from the Prophet when entering the toilet: he would take off his ring. The text does not explain the reason, so it is best to keep the explanation simple and close to the narration. It shows care and respect before entering a place used for relieving oneself. As a toilet etiquette Hadith, it reminds the reader that Islam teaches manners even in private matters. The report is not a long legal discussion. It only gives one clear action connected to entering the toilet, and that action reflects careful conduct in daily cleanliness."},"teachings":["The Prophet showed care before entering the toilet.","Private habits can still have manners and discipline.","The Hadith teaches a specific act without adding extra reasons.","Toilet etiquette is part of daily Islamic practice."],"related_hadiths":[{"id":"301","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"302","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"313","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E302" s="4" t="n"/>
@@ -7423,7 +7427,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Urinating in the Wash Area","description":"$book_name$ $hadith_number$ - $chapter_name$. A narration warning against urinating in a wash area because it may lead to troubling thoughts."},"heading":{"title":"Urinating in the Wash Area and Cleanliness","description":"This Hadith discusses urinating in a wash area and links it with insinuating thoughts. The narration is marked Da'if in the provided text, and it also includes a comment from Ibn Majah about the type of wash area meant. The added note says the concern applied to soft ground, while built baths made of plaster, Saruj, and tar could be cleaned by pouring water over the urine. So the core message here is tied to purity, cleanliness, and avoiding causes of doubt. The text should not be stretched beyond that. It gives a warning, then records a practical explanation about different wash surfaces."},"teachings":["Cleanliness matters in places used for washing.","A person should avoid actions that may lead to doubt about purity.","The narration includes a note distinguishing soft ground from washable surfaces.","Pouring water over a washable surface is mentioned as a way to clear it."],"related_hadiths":[{"id":"310","book_id":"6","label":"Sunan Ibn Majah"},{"id":"313","book_id":"6","label":"Sunan Ibn Majah"},{"id":"316","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Urinating in the Wash Area","description":"$book_name$ $hadith_number$ - $chapter_name$. A narration warning against urinating in a wash area because it may lead to troubling thoughts."},"heading":{"title":"Urinating in the Wash Area and Cleanliness","description":"This Hadith discusses urinating in a wash area and links it with insinuating thoughts. The narration is marked Da'if in the provided text, and it also includes a comment from Ibn Majah about the type of wash area meant. The added note says the concern applied to soft ground, while built baths made of plaster, Saruj, and tar could be cleaned by pouring water over the urine. So the core message here is tied to purity, cleanliness, and avoiding causes of doubt. The text should not be stretched beyond that. It gives a warning, then records a practical explanation about different wash surfaces."},"teachings":["Cleanliness matters in places used for washing.","A person should avoid actions that may lead to doubt about purity.","The narration includes a note distinguishing soft ground from washable surfaces.","Pouring water over a washable surface is mentioned as a way to clear it."],"related_hadiths":[{"id":"310","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"313","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"316","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E303" s="4" t="n"/>
@@ -7446,7 +7450,7 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aishah on Sitting to Urinate","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah says she saw the Prophet urinating while sitting down."},"heading":{"title":"Sitting to Urinate Hadith from Aishah","description":"This Hadith presents Aishah's statement about what she saw from the Messenger of Allah. She says that if someone tells you he urinated while standing, do not believe him, because she saw him urinating while sitting down. The wording shows her direct observation. It should not be mixed carelessly with other reports in the batch that mention a separate incident of standing. As a sitting to urinate hadith, it highlights the practice Aishah witnessed. The explanation should remain fair: the Hadith is about her report and what she personally observed from the Prophet in this matter."},"teachings":["Aishah reported what she personally saw.","The narration points to sitting while urinating as what she observed.","Different reports should be handled carefully without forcing them together.","Companions preserved details of the Prophet's daily conduct."],"related_hadiths":[{"id":"308","book_id":"6","label":"Sunan Ibn Majah"},{"id":"309","book_id":"6","label":"Sunan Ibn Majah"},{"id":"305","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aishah on Sitting to Urinate","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah says she saw the Prophet urinating while sitting down."},"heading":{"title":"Sitting to Urinate Hadith from Aishah","description":"This Hadith presents Aishah's statement about what she saw from the Messenger of Allah. She says that if someone tells you he urinated while standing, do not believe him, because she saw him urinating while sitting down. The wording shows her direct observation. It should not be mixed carelessly with other reports in the batch that mention a separate incident of standing. As a sitting to urinate hadith, it highlights the practice Aishah witnessed. The explanation should remain fair: the Hadith is about her report and what she personally observed from the Prophet in this matter."},"teachings":["Aishah reported what she personally saw.","The narration points to sitting while urinating as what she observed.","Different reports should be handled carefully without forcing them together.","Companions preserved details of the Prophet's daily conduct."],"related_hadiths":[{"id":"308","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"309","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"305","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E304" s="4" t="n"/>
@@ -7469,7 +7473,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prohibition of Standing Urination","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir reports a prohibition on urinating while standing, with added comments in the narration."},"heading":{"title":"Prohibition of Urinating While Standing","description":"This Hadith says that Jabir bin Abdullah narrated that the Messenger of Allah forbade urinating while standing. The provided text marks the narration as Da'if. It also records later comments about the narration of Aishah and the custom of Arabs, including a mention of another report about sitting to urinate. The main point in the direct wording is the prohibition reported by Jabir. Since the text itself includes grading and comments, a careful explanation should mention them without adding outside rulings. For searches like prohibition of urinating while standing hadith, this narration is directly connected to that phrase."},"teachings":["The reported wording forbids urinating while standing.","The provided text marks this narration as Da'if.","The narration includes comments about how people understood the issue.","The topic should be handled carefully because nearby reports mention different details."],"related_hadiths":[{"id":"307","book_id":"6","label":"Sunan Ibn Majah"},{"id":"308","book_id":"6","label":"Sunan Ibn Majah"},{"id":"306","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prohibition of Standing Urination","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir reports a prohibition on urinating while standing, with added comments in the narration."},"heading":{"title":"Prohibition of Urinating While Standing","description":"This Hadith says that Jabir bin Abdullah narrated that the Messenger of Allah forbade urinating while standing. The provided text marks the narration as Da'if. It also records later comments about the narration of Aishah and the custom of Arabs, including a mention of another report about sitting to urinate. The main point in the direct wording is the prohibition reported by Jabir. Since the text itself includes grading and comments, a careful explanation should mention them without adding outside rulings. For searches like prohibition of urinating while standing hadith, this narration is directly connected to that phrase."},"teachings":["The reported wording forbids urinating while standing.","The provided text marks this narration as Da'if.","The narration includes comments about how people understood the issue.","The topic should be handled carefully because nearby reports mention different details."],"related_hadiths":[{"id":"307","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"308","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"306","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E305" s="4" t="n"/>
@@ -7492,7 +7496,7 @@
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Clean Yourself with the Left Hand","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith tells the believer to clean with the left hand, not the right hand."},"heading":{"title":"Clean Yourself with the Left Hand","description":"This Hadith gives a direct instruction about istinja, or cleaning oneself after relieving oneself. The Messenger of Allah said that when anyone cleans himself, he should not clean himself with his right hand. He should clean himself with his left hand. The wording is simple, practical, and easy to apply. It does not include extra details about other matters. For the search term clean yourself with left hand hadith, this narration is a direct match. The main teaching is that personal cleanliness should follow the manners taught by the Prophet, even in actions that are private and routine."},"teachings":["Use the left hand for cleaning after relieving oneself.","Do not use the right hand for this act.","Islamic manners include private cleanliness.","The Hadith gives a clear and practical instruction."],"related_hadiths":[{"id":"310","book_id":"6","label":"Sunan Ibn Majah"},{"id":"313","book_id":"6","label":"Sunan Ibn Majah"},{"id":"316","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Clean Yourself with the Left Hand","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith tells the believer to clean with the left hand, not the right hand."},"heading":{"title":"Clean Yourself with the Left Hand","description":"This Hadith gives a direct instruction about istinja, or cleaning oneself after relieving oneself. The Messenger of Allah said that when anyone cleans himself, he should not clean himself with his right hand. He should clean himself with his left hand. The wording is simple, practical, and easy to apply. It does not include extra details about other matters. For the search term clean yourself with left hand hadith, this narration is a direct match. The main teaching is that personal cleanliness should follow the manners taught by the Prophet, even in actions that are private and routine."},"teachings":["Use the left hand for cleaning after relieving oneself.","Do not use the right hand for this act.","Islamic manners include private cleanliness.","The Hadith gives a clear and practical instruction."],"related_hadiths":[{"id":"310","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"313","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"316","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E306" s="4" t="n"/>
@@ -7515,7 +7519,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Toilet Manners and Qiblah Respect","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet forbade drinking while standing and facing the Qiblah while urinating."},"heading":{"title":"Hadith About Facing Qiblah While Urinating","description":"This hadith about facing Qiblah while urinating teaches care in two daily actions: drinking and relieving oneself. Abu Sa'eed Al-Khudri reports that the Messenger of Allah forbade him from drinking while standing and from urinating while facing the Qiblah. The wording is direct and simple. It shows that toilet etiquette in Islam is not treated as a small matter with no meaning. Even private actions are guided by respect, self-control, and awareness of sacred direction. The hadith does not give extra details here, so the explanation should stay close to the text. Its main lesson is that a believer tries to follow Prophetic manners in ordinary habits too."},"teachings":["Avoid facing the Qiblah when urinating, as stated in this narration.","The Prophet taught manners even in private daily actions.","Drinking while standing is discouraged in this report.","Respect for the Qiblah should be kept in mind outside prayer too."],"related_hadiths":[{"id":"144","book_id":"1","label":"Sahih Bukhari"},{"id":"264a","book_id":"2","label":"Sahih Muslim"},{"id":"2024a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Toilet Manners and Qiblah Respect","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet forbade drinking while standing and facing the Qiblah while urinating."},"heading":{"title":"Hadith About Facing Qiblah While Urinating","description":"This hadith about facing Qiblah while urinating teaches care in two daily actions: drinking and relieving oneself. Abu Sa'eed Al-Khudri reports that the Messenger of Allah forbade him from drinking while standing and from urinating while facing the Qiblah. The wording is direct and simple. It shows that toilet etiquette in Islam is not treated as a small matter with no meaning. Even private actions are guided by respect, self-control, and awareness of sacred direction. The hadith does not give extra details here, so the explanation should stay close to the text. Its main lesson is that a believer tries to follow Prophetic manners in ordinary habits too."},"teachings":["Avoid facing the Qiblah when urinating, as stated in this narration.","The Prophet taught manners even in private daily actions.","Drinking while standing is discouraged in this report.","Respect for the Qiblah should be kept in mind outside prayer too."],"related_hadiths":[{"id":"144","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"264a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2024a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E307" s="4" t="n"/>
@@ -7538,7 +7542,7 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Constructed Toilet and Qiblah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports seeing the Prophet in a constructed toilet facing the Qiblah."},"heading":{"title":"Hadith About Constructed Toilet and Qiblah Direction","description":"This hadith about constructed toilet and Qiblah direction includes two parts. First, Ibn Umar says that he saw the Messenger of Allah in his constructed toilet facing the Qiblah. The translation also marks the report as Da'if. Then Eisa says he mentioned this to Sha'bi, and Sha'bi answered by bringing together the reports of Ibn Umar and Abu Hurairah. In the wording quoted here, Abu Hurairah’s statement is linked to the desert: do not face the Qiblah or turn one’s back toward it. Ibn Umar’s statement is linked to a constructed toilet. The explanation should stay with this text and not turn it into a broad ruling beyond what is stated."},"teachings":["The narration is marked Da'if in the provided translation.","The report separates an open desert setting from a constructed toilet setting.","Sha'bi tried to understand both narrations without rejecting either wording.","Careful reading helps avoid mixing different situations."],"related_hadiths":[{"id":"144","book_id":"1","label":"Sahih Bukhari"},{"id":"145","book_id":"1","label":"Sahih Bukhari"},{"id":"264a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Constructed Toilet and Qiblah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports seeing the Prophet in a constructed toilet facing the Qiblah."},"heading":{"title":"Hadith About Constructed Toilet and Qiblah Direction","description":"This hadith about constructed toilet and Qiblah direction includes two parts. First, Ibn Umar says that he saw the Messenger of Allah in his constructed toilet facing the Qiblah. The translation also marks the report as Da'if. Then Eisa says he mentioned this to Sha'bi, and Sha'bi answered by bringing together the reports of Ibn Umar and Abu Hurairah. In the wording quoted here, Abu Hurairah’s statement is linked to the desert: do not face the Qiblah or turn one’s back toward it. Ibn Umar’s statement is linked to a constructed toilet. The explanation should stay with this text and not turn it into a broad ruling beyond what is stated."},"teachings":["The narration is marked Da'if in the provided translation.","The report separates an open desert setting from a constructed toilet setting.","Sha'bi tried to understand both narrations without rejecting either wording.","Careful reading helps avoid mixing different situations."],"related_hadiths":[{"id":"144","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"145","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"264a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E308" s="4" t="n"/>
@@ -7561,7 +7565,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Facing Qiblah in Toilet Seat","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports a Da'if narration about turning the Prophet’s toilet seat toward the Qiblah."},"heading":{"title":"Hadith About Facing Qiblah With the Toilet Seat","description":"This hadith about facing Qiblah in toilet etiquette is reported from Aishah. The narration says that some people were mentioned before the Messenger of Allah because they disliked facing the Qiblah with their private parts. The Prophet then said, according to this report, to turn his seat in the toilet toward the Qiblah. The provided translation clearly marks this narration as Da'if, so it should be handled with caution. The text itself is mainly about a discussion of toilet direction and the Prophet’s response in that report. It should not be stretched into claims beyond the wording given here."},"teachings":["The translation marks this narration as Da'if.","The report is about facing the Qiblah in a toilet setting.","Aishah narrates a specific response connected to the Prophet’s seat.","Weak reports should be presented carefully without overstating them."],"related_hadiths":[{"id":"144","book_id":"1","label":"Sahih Bukhari"},{"id":"264a","book_id":"2","label":"Sahih Muslim"},{"id":"266a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Facing Qiblah in Toilet Seat","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports a Da'if narration about turning the Prophet’s toilet seat toward the Qiblah."},"heading":{"title":"Hadith About Facing Qiblah With the Toilet Seat","description":"This hadith about facing Qiblah in toilet etiquette is reported from Aishah. The narration says that some people were mentioned before the Messenger of Allah because they disliked facing the Qiblah with their private parts. The Prophet then said, according to this report, to turn his seat in the toilet toward the Qiblah. The provided translation clearly marks this narration as Da'if, so it should be handled with caution. The text itself is mainly about a discussion of toilet direction and the Prophet’s response in that report. It should not be stretched into claims beyond the wording given here."},"teachings":["The translation marks this narration as Da'if.","The report is about facing the Qiblah in a toilet setting.","Aishah narrates a specific response connected to the Prophet’s seat.","Weak reports should be presented carefully without overstating them."],"related_hadiths":[{"id":"144","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"264a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"266a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E309" s="4" t="n"/>
@@ -7584,7 +7588,7 @@
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Urinating and Qiblah Direction","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir reports the Prophet forbade facing the Qiblah when urinating, then saw him facing it later."},"heading":{"title":"Hadith About Urinating While Facing the Qiblah","description":"This hadith about urinating while facing the Qiblah comes through Jabir. He first says that the Messenger of Allah forbade facing the Qiblah when urinating. Then he adds that he saw the Prophet one year before he died facing the Qiblah while urinating. The narration contains both points, so the explanation should not ignore either side. It is connected to Islamic toilet etiquette, Qiblah direction, and personal cleanliness manners. The text does not give a long explanation of why Jabir saw this later action, so it is best to present the hadith exactly as it comes: a prohibition is mentioned, followed by Jabir’s later observation."},"teachings":["Jabir reports a prohibition about facing the Qiblah while urinating.","The same report also mentions Jabir’s later observation of the Prophet.","The hadith should be read with both parts kept together.","Toilet manners in Islam are discussed through precise reports."],"related_hadiths":[{"id":"144","book_id":"1","label":"Sahih Bukhari"},{"id":"264a","book_id":"2","label":"Sahih Muslim"},{"id":"145","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Urinating and Qiblah Direction","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir reports the Prophet forbade facing the Qiblah when urinating, then saw him facing it later."},"heading":{"title":"Hadith About Urinating While Facing the Qiblah","description":"This hadith about urinating while facing the Qiblah comes through Jabir. He first says that the Messenger of Allah forbade facing the Qiblah when urinating. Then he adds that he saw the Prophet one year before he died facing the Qiblah while urinating. The narration contains both points, so the explanation should not ignore either side. It is connected to Islamic toilet etiquette, Qiblah direction, and personal cleanliness manners. The text does not give a long explanation of why Jabir saw this later action, so it is best to present the hadith exactly as it comes: a prohibition is mentioned, followed by Jabir’s later observation."},"teachings":["Jabir reports a prohibition about facing the Qiblah while urinating.","The same report also mentions Jabir’s later observation of the Prophet.","The hadith should be read with both parts kept together.","Toilet manners in Islam are discussed through precise reports."],"related_hadiths":[{"id":"144","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"264a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"145","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E310" s="4" t="n"/>
@@ -7607,7 +7611,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Removing Urine Drops","description":"$book_name$ $hadith_number$ - $chapter_name$. A Da'if narration mentions squeezing three times after urinating to remove remaining drops."},"heading":{"title":"Hadith About Removing Remaining Urine Drops","description":"This hadith about removing urine drops is narrated from Eisa bin Yazdad Al-Yamani from his father. The wording says that when anyone urinates, he should squeeze his private part three times to remove the remaining urine drops. The provided translation marks this narration as Da'if, so the content should be presented with care. The main topic is urine hygiene and cleanliness after using the toilet. The narration points to concern about leftover drops, but because the grading in the input says Da'if, it should not be stated in a strong way beyond the report. Its simple message is about paying attention to cleanliness after urination."},"teachings":["The translation marks this narration as Da'if.","The report focuses on care after urinating.","Cleanliness from urine is treated as an important concern.","Weak narrations should not be presented with strong claims."],"related_hadiths":[{"id":"218","book_id":"1","label":"Sahih Bukhari"},{"id":"292a","book_id":"2","label":"Sahih Muslim"},{"id":"20","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Removing Urine Drops","description":"$book_name$ $hadith_number$ - $chapter_name$. A Da'if narration mentions squeezing three times after urinating to remove remaining drops."},"heading":{"title":"Hadith About Removing Remaining Urine Drops","description":"This hadith about removing urine drops is narrated from Eisa bin Yazdad Al-Yamani from his father. The wording says that when anyone urinates, he should squeeze his private part three times to remove the remaining urine drops. The provided translation marks this narration as Da'if, so the content should be presented with care. The main topic is urine hygiene and cleanliness after using the toilet. The narration points to concern about leftover drops, but because the grading in the input says Da'if, it should not be stated in a strong way beyond the report. Its simple message is about paying attention to cleanliness after urination."},"teachings":["The translation marks this narration as Da'if.","The report focuses on care after urinating.","Cleanliness from urine is treated as an important concern.","Weak narrations should not be presented with strong claims."],"related_hadiths":[{"id":"218","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"292a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"20","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E311" s="4" t="n"/>
@@ -7630,7 +7634,7 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu After Urinating","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said he was not commanded to perform wudu every time he urinated."},"heading":{"title":"Hadith About Wudu After Urinating","description":"This hadith about wudu after urinating shows the Prophet teaching by correcting a helpful action. Aishah says that the Prophet went out to urinate, and Umar followed him with water. When the Prophet asked what it was, Umar said it was water. The Prophet then said that he had not been commanded to perform ablution every time he urinated. He also said that if he did that, it would have become a Sunnah. The hadith is important because it shows care in not making a regular religious practice from something not commanded. It also teaches that love for cleanliness should stay within the limits of what is taught."},"teachings":["The Prophet was not commanded to make wudu after every urination.","A repeated Prophetic action could be taken as Sunnah.","Good intentions still need guidance from the Prophet’s teaching.","The narration shows care in not adding a regular practice without command."],"related_hadiths":[{"id":"42","book_id":"4","label":"Sunan Abu Dawud"},{"id":"274a","book_id":"2","label":"Sahih Muslim"},{"id":"214","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu After Urinating","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said he was not commanded to perform wudu every time he urinated."},"heading":{"title":"Hadith About Wudu After Urinating","description":"This hadith about wudu after urinating shows the Prophet teaching by correcting a helpful action. Aishah says that the Prophet went out to urinate, and Umar followed him with water. When the Prophet asked what it was, Umar said it was water. The Prophet then said that he had not been commanded to perform ablution every time he urinated. He also said that if he did that, it would have become a Sunnah. The hadith is important because it shows care in not making a regular religious practice from something not commanded. It also teaches that love for cleanliness should stay within the limits of what is taught."},"teachings":["The Prophet was not commanded to make wudu after every urination.","A repeated Prophetic action could be taken as Sunnah.","Good intentions still need guidance from the Prophet’s teaching.","The narration shows care in not adding a regular practice without command."],"related_hadiths":[{"id":"42","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"214","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E312" s="4" t="n"/>
@@ -7653,7 +7657,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Public Harm","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet warned against relieving oneself in water sources, shade, and roads."},"heading":{"title":"Hadith About Avoiding Public Harm When Relieving Oneself","description":"This hadith about avoiding public harm when relieving oneself teaches respect for shared spaces. Mu'adh bin Jabal reports that he heard the Messenger of Allah say to beware of three things that provoke curses: relieving oneself in watering places, in places of shade, and in the middle of the road. The wording connects toilet etiquette with public manners. It is not only about personal cleanliness; it is also about not harming others where they drink, rest, or pass by. The hadith also shows that Companions discussed reports carefully. The main teaching is clear: a Muslim should avoid making public places dirty or harmful for people."},"teachings":["Do not relieve yourself in watering places used by others.","Do not spoil shaded places where people may rest.","Do not relieve yourself in the middle of the road.","Public cleanliness is part of good manners in this narration."],"related_hadiths":[{"id":"26","book_id":"4","label":"Sunan Abu Dawud"},{"id":"269a","book_id":"2","label":"Sahih Muslim"},{"id":"246","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Public Harm","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet warned against relieving oneself in water sources, shade, and roads."},"heading":{"title":"Hadith About Avoiding Public Harm When Relieving Oneself","description":"This hadith about avoiding public harm when relieving oneself teaches respect for shared spaces. Mu'adh bin Jabal reports that he heard the Messenger of Allah say to beware of three things that provoke curses: relieving oneself in watering places, in places of shade, and in the middle of the road. The wording connects toilet etiquette with public manners. It is not only about personal cleanliness; it is also about not harming others where they drink, rest, or pass by. The hadith also shows that Companions discussed reports carefully. The main teaching is clear: a Muslim should avoid making public places dirty or harmful for people."},"teachings":["Do not relieve yourself in watering places used by others.","Do not spoil shaded places where people may rest.","Do not relieve yourself in the middle of the road.","Public cleanliness is part of good manners in this narration."],"related_hadiths":[{"id":"26","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"269a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"246","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E313" s="4" t="n"/>
@@ -7676,7 +7680,7 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Road Safety and Cleanliness","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet warned against resting, praying, or relieving oneself in the middle of the road."},"heading":{"title":"Hadith About Relieving Oneself in the Middle of the Road","description":"This hadith about relieving oneself in the middle of the road gives a practical warning. Jabir bin Abdullah reports that the Messenger of Allah warned against stopping to rest and praying in the middle of the road. The reason mentioned in the text is that the road can be a refuge for snakes and carnivorous animals. He also warned against relieving oneself in the middle of the road, calling it an act that provokes curses. The hadith connects safety, prayer location, and public cleanliness. Its lesson is easy to understand: do not use shared roads in a way that harms people or exposes yourself to danger."},"teachings":["Avoid resting in the middle of the road.","Avoid praying in a road where danger is mentioned in the text.","Do not relieve yourself in the middle of the road.","Shared paths should be kept safe and clean."],"related_hadiths":[{"id":"26","book_id":"4","label":"Sunan Abu Dawud"},{"id":"269a","book_id":"2","label":"Sahih Muslim"},{"id":"246","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Road Safety and Cleanliness","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet warned against resting, praying, or relieving oneself in the middle of the road."},"heading":{"title":"Hadith About Relieving Oneself in the Middle of the Road","description":"This hadith about relieving oneself in the middle of the road gives a practical warning. Jabir bin Abdullah reports that the Messenger of Allah warned against stopping to rest and praying in the middle of the road. The reason mentioned in the text is that the road can be a refuge for snakes and carnivorous animals. He also warned against relieving oneself in the middle of the road, calling it an act that provokes curses. The hadith connects safety, prayer location, and public cleanliness. Its lesson is easy to understand: do not use shared roads in a way that harms people or exposes yourself to danger."},"teachings":["Avoid resting in the middle of the road.","Avoid praying in a road where danger is mentioned in the text.","Do not relieve yourself in the middle of the road.","Shared paths should be kept safe and clean."],"related_hadiths":[{"id":"26","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"269a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"246","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E314" s="4" t="n"/>
@@ -7699,7 +7703,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Prayer or Toilet on Roads","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet forbade praying, defecating, or urinating in the middle of the road."},"heading":{"title":"Hadith About Praying or Relieving Oneself on the Road","description":"This hadith about praying or relieving oneself on the road is short and direct. Salim narrates from his father that the Prophet forbade praying in the middle of the road, defecating there, or urinating there. The wording does not give extra detail in this report, but the message is clear. Roads are shared spaces. They are not suitable places for actions that block, dirty, or disturb people. The hadith is closely tied to public cleanliness in Islam, road manners, and toilet etiquette. It teaches that worship and personal needs should be handled in proper places, not in a way that harms or troubles others."},"teachings":["Do not pray in the middle of the road.","Do not defecate in the middle of the road.","Do not urinate in the middle of the road.","Shared public paths deserve respect and cleanliness."],"related_hadiths":[{"id":"26","book_id":"4","label":"Sunan Abu Dawud"},{"id":"269a","book_id":"2","label":"Sahih Muslim"},{"id":"246","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Prayer or Toilet on Roads","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet forbade praying, defecating, or urinating in the middle of the road."},"heading":{"title":"Hadith About Praying or Relieving Oneself on the Road","description":"This hadith about praying or relieving oneself on the road is short and direct. Salim narrates from his father that the Prophet forbade praying in the middle of the road, defecating there, or urinating there. The wording does not give extra detail in this report, but the message is clear. Roads are shared spaces. They are not suitable places for actions that block, dirty, or disturb people. The hadith is closely tied to public cleanliness in Islam, road manners, and toilet etiquette. It teaches that worship and personal needs should be handled in proper places, not in a way that harms or troubles others."},"teachings":["Do not pray in the middle of the road.","Do not defecate in the middle of the road.","Do not urinate in the middle of the road.","Shared public paths deserve respect and cleanliness."],"related_hadiths":[{"id":"26","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"269a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"246","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E315" s="4" t="n"/>
@@ -7722,7 +7726,7 @@
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Privacy When Relieving Oneself","description":"$book_name$ $hadith_number$ - $chapter_name$. Mughirah reports that the Prophet would go far away when relieving himself."},"heading":{"title":"Hadith About Privacy When Relieving Oneself","description":"This hadith about privacy when relieving oneself is narrated by Mughirah bin Shu'bah. He says that whenever the Prophet went to relieve himself, he would go far away. The wording is brief, but the meaning is practical and clear. The Prophet chose distance when attending to private needs. This shows modesty, privacy, and care not to expose what should be hidden. For readers searching for toilet etiquette in Islam, this hadith gives a simple Prophetic habit: keep private matters private. It does not mention a special place, long explanation, or extra ruling. It only tells us that the Prophet would move away when he needed to relieve himself."},"teachings":["The Prophet would go far away to relieve himself.","Privacy is part of toilet etiquette in this narration.","Private needs should be handled away from people.","Modesty can be shown through simple daily habits."],"related_hadiths":[{"id":"274a","book_id":"2","label":"Sahih Muslim"},{"id":"2","book_id":"4","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Privacy When Relieving Oneself","description":"$book_name$ $hadith_number$ - $chapter_name$. Mughirah reports that the Prophet would go far away when relieving himself."},"heading":{"title":"Hadith About Privacy When Relieving Oneself","description":"This hadith about privacy when relieving oneself is narrated by Mughirah bin Shu'bah. He says that whenever the Prophet went to relieve himself, he would go far away. The wording is brief, but the meaning is practical and clear. The Prophet chose distance when attending to private needs. This shows modesty, privacy, and care not to expose what should be hidden. For readers searching for toilet etiquette in Islam, this hadith gives a simple Prophetic habit: keep private matters private. It does not mention a special place, long explanation, or extra ruling. It only tells us that the Prophet would move away when he needed to relieve himself."},"teachings":["The Prophet would go far away to relieve himself.","Privacy is part of toilet etiquette in this narration.","Private needs should be handled away from people.","Modesty can be shown through simple daily habits."],"related_hadiths":[{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E316" s="4" t="n"/>
@@ -7745,7 +7749,7 @@
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Going Far for Privacy","description":"$book_name$ $hadith_number$ - $chapter_name$. Ya'la bin Murrah reports that the Prophet would go far away to relieve himself."},"heading":{"title":"Hadith About Going Far Away to Relieve Oneself","description":"This hadith about going far away to relieve oneself is narrated from Ya'la bin Murrah. The narration says that when the Prophet went to relieve himself, he would go far away. It is a clear report about privacy and modesty. The action itself is simple, but it teaches a strong everyday manner: keep private acts away from people’s sight. It also connects to Islamic bathroom manners and personal dignity. The hadith does not add details about water, direction, or location type. Its focus is distance. A believer can learn from it that modesty is not only in speech or clothing, but also in how private needs are handled."},"teachings":["The Prophet would go far away when relieving himself.","Distance helped preserve privacy.","The hadith teaches modesty in private actions.","Simple habits can reflect good Islamic manners."],"related_hadiths":[{"id":"274a","book_id":"2","label":"Sahih Muslim"},{"id":"2","book_id":"4","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Going Far for Privacy","description":"$book_name$ $hadith_number$ - $chapter_name$. Ya'la bin Murrah reports that the Prophet would go far away to relieve himself."},"heading":{"title":"Hadith About Going Far Away to Relieve Oneself","description":"This hadith about going far away to relieve oneself is narrated from Ya'la bin Murrah. The narration says that when the Prophet went to relieve himself, he would go far away. It is a clear report about privacy and modesty. The action itself is simple, but it teaches a strong everyday manner: keep private acts away from people’s sight. It also connects to Islamic bathroom manners and personal dignity. The hadith does not add details about water, direction, or location type. Its focus is distance. A believer can learn from it that modesty is not only in speech or clothing, but also in how private needs are handled."},"teachings":["The Prophet would go far away when relieving himself.","Distance helped preserve privacy.","The hadith teaches modesty in private actions.","Simple habits can reflect good Islamic manners."],"related_hadiths":[{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E317" s="4" t="n"/>
@@ -7768,7 +7772,7 @@
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hajj Journey Privacy","description":"$book_name$ $hadith_number$ - $chapter_name$. During Hajj, the Prophet went far away when he needed to relieve himself."},"heading":{"title":"Hadith About Privacy During Hajj Journey","description":"This hadith about privacy during Hajj journey is narrated by Abdur-Rahman bin Abu Qurad. He says that he performed Hajj with the Prophet, and when the Prophet went to relieve himself, he went far away. The wording is short, but it shows the same Prophetic manner found in other reports: privacy was kept even during travel and public movement. The setting mentioned here is Hajj, yet the focus stays on relieving oneself away from people. The hadith does not add wider Hajj rulings, so the explanation should remain with the text. It teaches modesty, distance, and respect for what should remain private."},"teachings":["The Prophet went far away to relieve himself during Hajj travel.","Privacy was maintained even while traveling with others.","The narration highlights modesty in personal needs.","The text focuses on distance, not wider Hajj rules."],"related_hadiths":[{"id":"274a","book_id":"2","label":"Sahih Muslim"},{"id":"2","book_id":"4","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hajj Journey Privacy","description":"$book_name$ $hadith_number$ - $chapter_name$. During Hajj, the Prophet went far away when he needed to relieve himself."},"heading":{"title":"Hadith About Privacy During Hajj Journey","description":"This hadith about privacy during Hajj journey is narrated by Abdur-Rahman bin Abu Qurad. He says that he performed Hajj with the Prophet, and when the Prophet went to relieve himself, he went far away. The wording is short, but it shows the same Prophetic manner found in other reports: privacy was kept even during travel and public movement. The setting mentioned here is Hajj, yet the focus stays on relieving oneself away from people. The hadith does not add wider Hajj rulings, so the explanation should remain with the text. It teaches modesty, distance, and respect for what should remain private."},"teachings":["The Prophet went far away to relieve himself during Hajj travel.","Privacy was maintained even while traveling with others.","The narration highlights modesty in personal needs.","The text focuses on distance, not wider Hajj rules."],"related_hadiths":[{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E318" s="4" t="n"/>
@@ -7791,7 +7795,7 @@
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Concealment During Travel","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir reports that the Prophet would go out of sight before relieving himself on a journey."},"heading":{"title":"Hadith About Concealment When Relieving Oneself","description":"This hadith about concealment when relieving oneself is narrated by Jabir. He says that they went out on a journey with the Messenger of Allah, and the Prophet would not relieve himself until he had disappeared and could not be seen by anyone. This wording is stronger than simply saying he went far away. It clearly mentions being hidden from sight. The main topic is Islamic toilet etiquette and privacy. The Prophet’s practice in this report teaches that personal needs should be handled with modesty. The hadith does not mention direction, water, or speech. It focuses on being unseen before relieving oneself."},"teachings":["The Prophet would not relieve himself until he was out of sight.","Privacy is directly mentioned in this narration.","Travel did not remove the need for modesty.","Concealment is part of proper toilet manners in the text."],"related_hadiths":[{"id":"274a","book_id":"2","label":"Sahih Muslim"},{"id":"2","book_id":"4","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Concealment During Travel","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir reports that the Prophet would go out of sight before relieving himself on a journey."},"heading":{"title":"Hadith About Concealment When Relieving Oneself","description":"This hadith about concealment when relieving oneself is narrated by Jabir. He says that they went out on a journey with the Messenger of Allah, and the Prophet would not relieve himself until he had disappeared and could not be seen by anyone. This wording is stronger than simply saying he went far away. It clearly mentions being hidden from sight. The main topic is Islamic toilet etiquette and privacy. The Prophet’s practice in this report teaches that personal needs should be handled with modesty. The hadith does not mention direction, water, or speech. It focuses on being unseen before relieving oneself."},"teachings":["The Prophet would not relieve himself until he was out of sight.","Privacy is directly mentioned in this narration.","Travel did not remove the need for modesty.","Concealment is part of proper toilet manners in the text."],"related_hadiths":[{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E319" s="4" t="n"/>
@@ -7814,7 +7818,7 @@
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Far Away for Private Needs","description":"$book_name$ $hadith_number$ - $chapter_name$. Bilal bin Al-Harith reports that the Prophet went far away when he wanted to relieve himself."},"heading":{"title":"Hadith About Going Far Away for Private Needs","description":"This hadith about going far away for private needs is narrated from Bilal bin Al-Harith Al-Muzani. It says that when the Messenger of Allah wanted to relieve himself, he would go far away. The narration is short, but it is clear in meaning. It highlights modesty and privacy in a very human daily matter. For readers searching for toilet etiquette in Islam, this report gives a simple Prophetic pattern: do not expose private needs to others. The text does not add reasons or conditions, so we should not add them as if they are part of the hadith. The lesson stays with distance and privacy."},"teachings":["The Prophet would go far away before relieving himself.","The narration teaches privacy in personal matters.","Toilet manners are part of daily Islamic conduct.","The report should be understood through its simple wording."],"related_hadiths":[{"id":"274a","book_id":"2","label":"Sahih Muslim"},{"id":"2","book_id":"4","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Far Away for Private Needs","description":"$book_name$ $hadith_number$ - $chapter_name$. Bilal bin Al-Harith reports that the Prophet went far away when he wanted to relieve himself."},"heading":{"title":"Hadith About Going Far Away for Private Needs","description":"This hadith about going far away for private needs is narrated from Bilal bin Al-Harith Al-Muzani. It says that when the Messenger of Allah wanted to relieve himself, he would go far away. The narration is short, but it is clear in meaning. It highlights modesty and privacy in a very human daily matter. For readers searching for toilet etiquette in Islam, this report gives a simple Prophetic pattern: do not expose private needs to others. The text does not add reasons or conditions, so we should not add them as if they are part of the hadith. The lesson stays with distance and privacy."},"teachings":["The Prophet would go far away before relieving himself.","The narration teaches privacy in personal matters.","Toilet manners are part of daily Islamic conduct.","The report should be understood through its simple wording."],"related_hadiths":[{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E320" s="4" t="n"/>
@@ -7837,7 +7841,7 @@
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Odd Stones and Concealment","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught odd-numbered cleaning stones and concealment when going to the toilet."},"heading":{"title":"Hadith About Odd Stones and Concealment in Toilet Etiquette","description":"This hadith about odd stones and concealment brings several manners together. Abu Hurairah narrates that the Prophet said whoever uses stones to clean himself should use an odd number. The report also mentions what to do with food particles removed from between the teeth. Then it says that whoever goes to the toilet should conceal himself. If he finds only a pile of sand, he should use it for cover. The wording also says that Shaitan plays with the backside of the son of Adam. The repeated phrase, “whoever does that has done well, and whoever does not, there is no harm,” should be kept in the explanation because it is part of the text."},"teachings":["Using an odd number of stones for cleaning is praised in this report.","The hadith encourages concealment when going to the toilet.","Even a pile of sand may be used as cover if nothing else is found.","The narration includes the phrase that whoever does it has done well, and whoever does not, there is no harm."],"related_hadiths":[{"id":"162","book_id":"1","label":"Sahih Bukhari"},{"id":"262a","book_id":"2","label":"Sahih Muslim"},{"id":"35","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Odd Stones and Concealment","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught odd-numbered cleaning stones and concealment when going to the toilet."},"heading":{"title":"Hadith About Odd Stones and Concealment in Toilet Etiquette","description":"This hadith about odd stones and concealment brings several manners together. Abu Hurairah narrates that the Prophet said whoever uses stones to clean himself should use an odd number. The report also mentions what to do with food particles removed from between the teeth. Then it says that whoever goes to the toilet should conceal himself. If he finds only a pile of sand, he should use it for cover. The wording also says that Shaitan plays with the backside of the son of Adam. The repeated phrase, “whoever does that has done well, and whoever does not, there is no harm,” should be kept in the explanation because it is part of the text."},"teachings":["Using an odd number of stones for cleaning is praised in this report.","The hadith encourages concealment when going to the toilet.","Even a pile of sand may be used as cover if nothing else is found.","The narration includes the phrase that whoever does it has done well, and whoever does not, there is no harm."],"related_hadiths":[{"id":"162","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"262a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"35","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E321" s="4" t="n"/>
@@ -7860,7 +7864,7 @@
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Odd Number in Personal Manners","description":"$book_name$ $hadith_number$ - $chapter_name$. A similar report adds using kohl an odd number of times and swallowing food particles dislodged by the tongue."},"heading":{"title":"Hadith About Odd Numbers in Personal Manners","description":"This hadith about odd numbers in personal manners is a similar report through Abdul-Malik bin As-Sabbah. It adds that whoever applies kohl to the eyes should do so an odd number of times. The wording says that whoever does this has done well, and whoever does not, there is no harm. It also repeats that whoever dislodges a food particle with the tongue should swallow it. The report is connected to personal care, simple cleanliness, and daily manners. The key point is not to make claims beyond the text. The narration praises the odd-numbered practice in these actions, while also saying there is no harm for one who does not do it."},"teachings":["Applying kohl an odd number of times is praised in this report.","The narration says there is no harm for one who does not do it.","Food dislodged by the tongue is to be swallowed in this wording.","The hadith teaches small daily manners in simple terms."],"related_hadiths":[{"id":"162","book_id":"1","label":"Sahih Bukhari"},{"id":"262a","book_id":"2","label":"Sahih Muslim"},{"id":"35","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Odd Number in Personal Manners","description":"$book_name$ $hadith_number$ - $chapter_name$. A similar report adds using kohl an odd number of times and swallowing food particles dislodged by the tongue."},"heading":{"title":"Hadith About Odd Numbers in Personal Manners","description":"This hadith about odd numbers in personal manners is a similar report through Abdul-Malik bin As-Sabbah. It adds that whoever applies kohl to the eyes should do so an odd number of times. The wording says that whoever does this has done well, and whoever does not, there is no harm. It also repeats that whoever dislodges a food particle with the tongue should swallow it. The report is connected to personal care, simple cleanliness, and daily manners. The key point is not to make claims beyond the text. The narration praises the odd-numbered practice in these actions, while also saying there is no harm for one who does not do it."},"teachings":["Applying kohl an odd number of times is praised in this report.","The narration says there is no harm for one who does not do it.","Food dislodged by the tongue is to be swallowed in this wording.","The hadith teaches small daily manners in simple terms."],"related_hadiths":[{"id":"162","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"262a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"35","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E322" s="4" t="n"/>
@@ -7883,7 +7887,7 @@
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Concealment Behind Trees","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet concealed himself behind two small date-palm trees before relieving himself."},"heading":{"title":"Hadith About Concealment Behind Trees When Relieving Oneself","description":"This hadith about concealment behind trees when relieving oneself is narrated from Ya'la bin Murrah through his father. He says he was with the Prophet on a journey when the Prophet wanted to relieve himself. The Prophet told him to go to two small date-palm trees and tell them that the Messenger of Allah ordered them to come together. They came together, and the Prophet concealed himself behind them and relieved himself. Then he told him to command them to return, and they returned to their places. The narration’s main lesson in toilet etiquette is concealment. It also reports a special event, so the wording should be kept as it is without adding extra claims."},"teachings":["The Prophet sought concealment before relieving himself.","The narration mentions two small date-palm trees coming together by his command.","Afterward, the trees returned to their places as stated in the report.","The practical theme of the hadith is privacy during a private need."],"related_hadiths":[{"id":"274a","book_id":"2","label":"Sahih Muslim"},{"id":"2","book_id":"4","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Concealment Behind Trees","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet concealed himself behind two small date-palm trees before relieving himself."},"heading":{"title":"Hadith About Concealment Behind Trees When Relieving Oneself","description":"This hadith about concealment behind trees when relieving oneself is narrated from Ya'la bin Murrah through his father. He says he was with the Prophet on a journey when the Prophet wanted to relieve himself. The Prophet told him to go to two small date-palm trees and tell them that the Messenger of Allah ordered them to come together. They came together, and the Prophet concealed himself behind them and relieved himself. Then he told him to command them to return, and they returned to their places. The narration’s main lesson in toilet etiquette is concealment. It also reports a special event, so the wording should be kept as it is without adding extra claims."},"teachings":["The Prophet sought concealment before relieving himself.","The narration mentions two small date-palm trees coming together by his command.","Afterward, the trees returned to their places as stated in the report.","The practical theme of the hadith is privacy during a private need."],"related_hadiths":[{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E323" s="4" t="n"/>
@@ -7906,7 +7910,7 @@
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hillock or Date-Palm Cover","description":"$book_name$ $hadith_number$ - $chapter_name$. Abdullah bin Ja'far says the Prophet liked a hillock or date-palm stand for concealment."},"heading":{"title":"Hadith About the Prophet’s Preferred Cover When Relieving Himself","description":"This hadith about the Prophet’s preferred cover when relieving himself is narrated by Abdullah bin Ja'far. He says that the thing the Prophet most liked to conceal himself behind when relieving himself was a hillock or a stand of date-palm trees. The wording is focused on concealment, not on a long list of bathroom rules. A hillock or date-palm stand would provide cover from people’s sight. This makes the hadith closely linked to privacy, modesty, and toilet etiquette in Islam. Since the report only mentions what the Prophet liked as cover, the explanation should stay with that simple meaning: he preferred a place that helped him remain unseen."},"teachings":["The Prophet liked to use cover when relieving himself.","A hillock is mentioned as one form of cover.","A stand of date-palm trees is also mentioned as cover.","The hadith highlights privacy and modesty in personal needs."],"related_hadiths":[{"id":"274a","book_id":"2","label":"Sahih Muslim"},{"id":"2","book_id":"4","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hillock or Date-Palm Cover","description":"$book_name$ $hadith_number$ - $chapter_name$. Abdullah bin Ja'far says the Prophet liked a hillock or date-palm stand for concealment."},"heading":{"title":"Hadith About the Prophet’s Preferred Cover When Relieving Himself","description":"This hadith about the Prophet’s preferred cover when relieving himself is narrated by Abdullah bin Ja'far. He says that the thing the Prophet most liked to conceal himself behind when relieving himself was a hillock or a stand of date-palm trees. The wording is focused on concealment, not on a long list of bathroom rules. A hillock or date-palm stand would provide cover from people’s sight. This makes the hadith closely linked to privacy, modesty, and toilet etiquette in Islam. Since the report only mentions what the Prophet liked as cover, the explanation should stay with that simple meaning: he preferred a place that helped him remain unseen."},"teachings":["The Prophet liked to use cover when relieving himself.","A hillock is mentioned as one form of cover.","A stand of date-palm trees is also mentioned as cover.","The hadith highlights privacy and modesty in personal needs."],"related_hadiths":[{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"20","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E324" s="4" t="n"/>
@@ -7929,7 +7933,7 @@
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Companion of the Quran and Rising Degrees","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn about the companion of the Quran being told to recite and rise one degree for each verse."},"heading":{"title":"Hadith About the Companion of the Quran and Rising Degrees","description":"This Hadith speaks about the companion of the Quran in Paradise. The Messenger of Allah صلى الله عليه وسلم said that it will be said to that person: “Recite and rise one degree for every Verse,” until he recites the last thing that he knows. The text connects Quran companionship with rising by recitation in Paradise. We should stay with the wording and not add details beyond it. People search for recite and rise hadith, companion of the Quran hadith, and one degree for every verse hadith. The teaching is that knowing and keeping the Quran matters deeply. It also encourages Muslims to build a real connection with the Quran through recitation and memory."},"teachings":["The Hadith honors the companion of the Quran.","The person is told to recite and rise by each verse.","The wording encourages a lasting bond with the Quran.","What a person knows of the Quran is mentioned in the final rise."],"related_hadiths":[{"id":"3779","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1464","book_id":"4","label":"Sunan Abu Dawud"},{"id":"2914","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Companion of the Quran and Rising Degrees","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn about the companion of the Quran being told to recite and rise one degree for each verse."},"heading":{"title":"Hadith About the Companion of the Quran and Rising Degrees","description":"This Hadith speaks about the companion of the Quran in Paradise. The Messenger of Allah صلى الله عليه وسلم said that it will be said to that person: “Recite and rise one degree for every Verse,” until he recites the last thing that he knows. The text connects Quran companionship with rising by recitation in Paradise. We should stay with the wording and not add details beyond it. People search for recite and rise hadith, companion of the Quran hadith, and one degree for every verse hadith. The teaching is that knowing and keeping the Quran matters deeply. It also encourages Muslims to build a real connection with the Quran through recitation and memory."},"teachings":["The Hadith honors the companion of the Quran.","The person is told to recite and rise by each verse.","The wording encourages a lasting bond with the Quran.","What a person knows of the Quran is mentioned in the final rise."],"related_hadiths":[{"id":"3779","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1464","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"2914","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E325" s="4" t="n"/>
@@ -7952,7 +7956,7 @@
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praise That Allah Rewards","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how one sincere phrase of praise was written as said, with reward kept by Allah until meeting Him."},"heading":{"title":"Hadith About Alhamdulillah: A Praise Allah Ordered to Be Written","description":"This hadith shows the value of praising Allah with words that honor His greatness. A servant said: Ya Rabb, Lakal-hamdu kama yanbagi li-jalali Wajhika wa li azima sultanika. The angels did not know how to record this praise, so they went up and asked Allah. Allah already knew what His servant had said, yet He asked them to repeat it. Then Allah told them to write it exactly as the servant said it, and He would reward him for it when he meets Him. The main lesson is simple: sincere praise of Allah is not a small thing. Alhamdulillah, praise of Allah, and dhikr can carry meaning greater than we can measure."},"teachings":["Praising Allah with sincere words is recorded by the angels.","Allah knows what His servant says, even before the angels report it.","Some words of praise carry a reward that Allah keeps with Him until the servant meets Him."],"related_hadiths":[{"id":"6405","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praise That Allah Rewards","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how one sincere phrase of praise was written as said, with reward kept by Allah until meeting Him."},"heading":{"title":"Hadith About Alhamdulillah: A Praise Allah Ordered to Be Written","description":"This hadith shows the value of praising Allah with words that honor His greatness. A servant said: Ya Rabb, Lakal-hamdu kama yanbagi li-jalali Wajhika wa li azima sultanika. The angels did not know how to record this praise, so they went up and asked Allah. Allah already knew what His servant had said, yet He asked them to repeat it. Then Allah told them to write it exactly as the servant said it, and He would reward him for it when he meets Him. The main lesson is simple: sincere praise of Allah is not a small thing. Alhamdulillah, praise of Allah, and dhikr can carry meaning greater than we can measure."},"teachings":["Praising Allah with sincere words is recorded by the angels.","Allah knows what His servant says, even before the angels report it.","Some words of praise carry a reward that Allah keeps with Him until the servant meets Him."],"related_hadiths":[{"id":"6405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E326" s="4" t="n"/>
@@ -7975,7 +7979,7 @@
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praise That Reached the Throne","description":"$book_name$ $hadith_number$ - $chapter_name$. A man praised Allah in prayer, and the Prophet said heaven’s gates opened for that blessed praise."},"heading":{"title":"Hadith About Alhamdulillah in Prayer: Blessed Praise That Rises High","description":"This hadith focuses on a short phrase of praise said during prayer: Alhamdu lillahi hamdan kathiran tayyiban mubarakan fihi. A man said it while praying with the Prophet صلى الله عليه وسلم. After the prayer, the Prophet صلى الله عليه وسلم asked who had said it. The man replied that he only intended good. The Prophet صلى الله عليه وسلم then explained that the gates of heaven were opened for this praise and nothing stopped it from reaching the Throne. The message is clear and moving: praising Allah with good intention has great worth. This hadith about Alhamdulillah teaches that words of praise can rise high when they are spoken with faith and a clean aim."},"teachings":["Good words said in prayer can have great weight with Allah.","The man’s intention was good, and the Prophet صلى الله عليه وسلم accepted that statement.","The phrase of praise was honored by the opening of the gates of heaven."],"related_hadiths":[{"id":"6405","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"},{"id":"3464","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praise That Reached the Throne","description":"$book_name$ $hadith_number$ - $chapter_name$. A man praised Allah in prayer, and the Prophet said heaven’s gates opened for that blessed praise."},"heading":{"title":"Hadith About Alhamdulillah in Prayer: Blessed Praise That Rises High","description":"This hadith focuses on a short phrase of praise said during prayer: Alhamdu lillahi hamdan kathiran tayyiban mubarakan fihi. A man said it while praying with the Prophet صلى الله عليه وسلم. After the prayer, the Prophet صلى الله عليه وسلم asked who had said it. The man replied that he only intended good. The Prophet صلى الله عليه وسلم then explained that the gates of heaven were opened for this praise and nothing stopped it from reaching the Throne. The message is clear and moving: praising Allah with good intention has great worth. This hadith about Alhamdulillah teaches that words of praise can rise high when they are spoken with faith and a clean aim."},"teachings":["Good words said in prayer can have great weight with Allah.","The man’s intention was good, and the Prophet صلى الله عليه وسلم accepted that statement.","The phrase of praise was honored by the opening of the gates of heaven."],"related_hadiths":[{"id":"6405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3464","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E327" s="4" t="n"/>
@@ -7998,7 +8002,7 @@
       </c>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praise Allah in Every Moment","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet praised Allah when seeing what he liked and also praised Him in every disliked state."},"heading":{"title":"Hadith About Alhamdulillah Ala Kulli Hal: Gratitude in Every State","description":"This hadith teaches a simple daily habit from the Prophet صلى الله عليه وسلم. When he saw something he liked, he would say: Al-hamdu lillahil-ladhi bi ni matihi tatimmus-salihat. This means he praised Allah by whose grace good things are completed. When he saw something he disliked, he would say: Al-hamdu lillahi ala kulli hal, meaning praise is to Allah in all circumstances. The hadith does not tell us to deny sadness or dislike. It shows that praise of Allah remains part of the believer’s speech in both pleasant and unpleasant moments. This is a clear hadith about gratitude, Alhamdulillah, and remembering Allah through changing situations."},"teachings":["The Prophet صلى الله عليه وسلم praised Allah when seeing something pleasing.","The Prophet صلى الله عليه وسلم also praised Allah when seeing something disliked.","A believer can keep Alhamdulillah on the tongue in different life situations."],"related_hadiths":[{"id":"6407","book_id":"1","label":"Sahih Bukhari"},{"id":"6405","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praise Allah in Every Moment","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet praised Allah when seeing what he liked and also praised Him in every disliked state."},"heading":{"title":"Hadith About Alhamdulillah Ala Kulli Hal: Gratitude in Every State","description":"This hadith teaches a simple daily habit from the Prophet صلى الله عليه وسلم. When he saw something he liked, he would say: Al-hamdu lillahil-ladhi bi ni matihi tatimmus-salihat. This means he praised Allah by whose grace good things are completed. When he saw something he disliked, he would say: Al-hamdu lillahi ala kulli hal, meaning praise is to Allah in all circumstances. The hadith does not tell us to deny sadness or dislike. It shows that praise of Allah remains part of the believer’s speech in both pleasant and unpleasant moments. This is a clear hadith about gratitude, Alhamdulillah, and remembering Allah through changing situations."},"teachings":["The Prophet صلى الله عليه وسلم praised Allah when seeing something pleasing.","The Prophet صلى الله عليه وسلم also praised Allah when seeing something disliked.","A believer can keep Alhamdulillah on the tongue in different life situations."],"related_hadiths":[{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E328" s="4" t="n"/>
@@ -8021,7 +8025,7 @@
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praise and Seeking Refuge","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet praised Allah in all states and sought refuge from the condition of the people of Hell."},"heading":{"title":"Hadith About Alhamdulillah Ala Kulli Hal and Seeking Allah’s Protection","description":"This hadith gives a short supplication the Prophet صلى الله عليه وسلم used to say: Al-hamdu lillahi ala kulli hal. Rabbi a udhu bika min hali ahlin-nar. In English, it means praise is to Allah in all circumstances, and then seeking refuge with Allah from the situation of the people of Hell. The wording joins two meanings together. First, the servant praises Allah in every state. Second, the servant turns to Allah for protection from a terrible condition. The hadith is not long, but it gives the heart a strong reminder. Praise of Allah and asking Allah for safety can be part of one simple daily dhikr."},"teachings":["The Prophet صلى الله عليه وسلم praised Allah in all circumstances.","Seeking refuge with Allah is part of humble supplication.","A short dhikr can combine praise and a request for protection."],"related_hadiths":[{"id":"6407","book_id":"1","label":"Sahih Bukhari"},{"id":"6306","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praise and Seeking Refuge","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet praised Allah in all states and sought refuge from the condition of the people of Hell."},"heading":{"title":"Hadith About Alhamdulillah Ala Kulli Hal and Seeking Allah’s Protection","description":"This hadith gives a short supplication the Prophet صلى الله عليه وسلم used to say: Al-hamdu lillahi ala kulli hal. Rabbi a udhu bika min hali ahlin-nar. In English, it means praise is to Allah in all circumstances, and then seeking refuge with Allah from the situation of the people of Hell. The wording joins two meanings together. First, the servant praises Allah in every state. Second, the servant turns to Allah for protection from a terrible condition. The hadith is not long, but it gives the heart a strong reminder. Praise of Allah and asking Allah for safety can be part of one simple daily dhikr."},"teachings":["The Prophet صلى الله عليه وسلم praised Allah in all circumstances.","Seeking refuge with Allah is part of humble supplication.","A short dhikr can combine praise and a request for protection."],"related_hadiths":[{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E329" s="4" t="n"/>
@@ -8044,7 +8048,7 @@
       </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Alhamdulillah After Blessings","description":"$book_name$ $hadith_number$ - $chapter_name$. Saying Alhamdulillah after receiving a blessing is described as better than the blessing received."},"heading":{"title":"Hadith About Alhamdulillah After a Blessing: The Gift of Gratitude","description":"This hadith teaches the high value of saying Alhamdulillah after receiving a blessing from Allah. The Prophet صلى الله عليه وسلم said that when Allah gives a servant a blessing and the servant says Alhamdulillah, what he gives through that praise is better than what he received. The hadith keeps the focus on a very simple action: noticing a blessing and praising Allah for it. It does not need a long speech. One sincere Alhamdulillah can turn the heart back to the One who gave the blessing. This is why people search for hadith about gratitude, blessing, and Alhamdulillah. The hadith shows that praise itself is a great gift."},"teachings":["A blessing should lead the servant to praise Allah.","Saying Alhamdulillah after a blessing has great worth.","Gratitude is shown through simple, sincere words of praise."],"related_hadiths":[{"id":"6405","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Alhamdulillah After Blessings","description":"$book_name$ $hadith_number$ - $chapter_name$. Saying Alhamdulillah after receiving a blessing is described as better than the blessing received."},"heading":{"title":"Hadith About Alhamdulillah After a Blessing: The Gift of Gratitude","description":"This hadith teaches the high value of saying Alhamdulillah after receiving a blessing from Allah. The Prophet صلى الله عليه وسلم said that when Allah gives a servant a blessing and the servant says Alhamdulillah, what he gives through that praise is better than what he received. The hadith keeps the focus on a very simple action: noticing a blessing and praising Allah for it. It does not need a long speech. One sincere Alhamdulillah can turn the heart back to the One who gave the blessing. This is why people search for hadith about gratitude, blessing, and Alhamdulillah. The hadith shows that praise itself is a great gift."},"teachings":["A blessing should lead the servant to praise Allah.","Saying Alhamdulillah after a blessing has great worth.","Gratitude is shown through simple, sincere words of praise."],"related_hadiths":[{"id":"6405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E330" s="4" t="n"/>
@@ -8067,7 +8071,7 @@
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Beloved Words of Dhikr","description":"$book_name$ $hadith_number$ - $chapter_name$. Two easy words of dhikr are light on the tongue, heavy in the Balance, and beloved to the Most Merciful."},"heading":{"title":"Hadith About SubhanAllahi Wa Bihamdihi: Light on the Tongue, Heavy in the Balance","description":"This famous hadith teaches the value of two phrases: Subhan-Allahi wa bi hamdihi and Subhan-Allahil-Azim. The Prophet صلى الله عليه وسلم described them in three clear ways. They are light on the tongue, heavy in the Balance, and beloved to the Most Merciful. This makes the hadith easy to remember and easy to act on. The words are not hard to say, but the hadith tells us they carry great weight. It is a strong reminder that dhikr does not have to be long to be meaningful. A believer can say these words often, while knowing the Prophet صلى الله عليه وسلم described them as beloved to Allah, the Most Merciful."},"teachings":["Some words of dhikr are easy to say but heavy in the Balance.","Subhan-Allahi wa bi hamdihi and Subhan-Allahil-Azim are beloved to the Most Merciful.","The tongue can earn great reward through short words of remembrance."],"related_hadiths":[{"id":"6406","book_id":"1","label":"Sahih Bukhari"},{"id":"6405","book_id":"1","label":"Sahih Bukhari"},{"id":"3464","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Beloved Words of Dhikr","description":"$book_name$ $hadith_number$ - $chapter_name$. Two easy words of dhikr are light on the tongue, heavy in the Balance, and beloved to the Most Merciful."},"heading":{"title":"Hadith About SubhanAllahi Wa Bihamdihi: Light on the Tongue, Heavy in the Balance","description":"This famous hadith teaches the value of two phrases: Subhan-Allahi wa bi hamdihi and Subhan-Allahil-Azim. The Prophet صلى الله عليه وسلم described them in three clear ways. They are light on the tongue, heavy in the Balance, and beloved to the Most Merciful. This makes the hadith easy to remember and easy to act on. The words are not hard to say, but the hadith tells us they carry great weight. It is a strong reminder that dhikr does not have to be long to be meaningful. A believer can say these words often, while knowing the Prophet صلى الله عليه وسلم described them as beloved to Allah, the Most Merciful."},"teachings":["Some words of dhikr are easy to say but heavy in the Balance.","Subhan-Allahi wa bi hamdihi and Subhan-Allahil-Azim are beloved to the Most Merciful.","The tongue can earn great reward through short words of remembrance."],"related_hadiths":[{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3464","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E331" s="4" t="n"/>
@@ -8090,7 +8094,7 @@
       </c>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr That Plants Trees in Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. Four words of remembrance are described as a better planting, with a tree planted in Paradise for each."},"heading":{"title":"Hadith About Trees in Jannah: SubhanAllah, Alhamdulillah, La Ilaha Illallah, Allahu Akbar","description":"This hadith begins with Abu Hurairah planting a plant. The Prophet صلى الله عليه وسلم saw him and asked what he was planting. Then the Prophet صلى الله عليه وسلم guided him to a better kind of planting: saying Subhan-Allah, wal-hamdu-lillah, wa la ilaha illallah, wa Allahu Akbar. For each one of these statements, a tree is planted for the person in Paradise. The teaching is very direct. A person may plant something in this world, but the Prophet صلى الله عليه وسلم pointed to words of dhikr that bring a planting in Paradise. This hadith about trees in Jannah makes daily remembrance feel close and practical. The words are short, known, and full of praise."},"teachings":["The Prophet صلى الله عليه وسلم guided Abu Hurairah to a better form of planting.","Each of the four phrases mentioned is linked to a tree in Paradise.","Simple words of dhikr can be a means of lasting reward."],"related_hadiths":[{"id":"3464","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"6403","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr That Plants Trees in Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. Four words of remembrance are described as a better planting, with a tree planted in Paradise for each."},"heading":{"title":"Hadith About Trees in Jannah: SubhanAllah, Alhamdulillah, La Ilaha Illallah, Allahu Akbar","description":"This hadith begins with Abu Hurairah planting a plant. The Prophet صلى الله عليه وسلم saw him and asked what he was planting. Then the Prophet صلى الله عليه وسلم guided him to a better kind of planting: saying Subhan-Allah, wal-hamdu-lillah, wa la ilaha illallah, wa Allahu Akbar. For each one of these statements, a tree is planted for the person in Paradise. The teaching is very direct. A person may plant something in this world, but the Prophet صلى الله عليه وسلم pointed to words of dhikr that bring a planting in Paradise. This hadith about trees in Jannah makes daily remembrance feel close and practical. The words are short, known, and full of praise."},"teachings":["The Prophet صلى الله عليه وسلم guided Abu Hurairah to a better form of planting.","Each of the four phrases mentioned is linked to a tree in Paradise.","Simple words of dhikr can be a means of lasting reward."],"related_hadiths":[{"id":"3464","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"6403","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E332" s="4" t="n"/>
@@ -8113,7 +8117,7 @@
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Weighty Words of Tasbih","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught four phrases of tasbih, repeated three times, described as greater and heavier."},"heading":{"title":"Hadith About SubhanAllahi Adada Khalqihi: Four Powerful Words of Tasbih","description":"This hadith tells us about Juwairiyah remembering Allah after the morning prayer. The Prophet صلى الله عليه وسلم passed by her, then returned later while she was still remembering Allah. He told her that he had said four words three times since leaving her, and that they were greater and weighed more heavily than what she had said. The phrases are: Subhan-Allahi adada khalqihi, Subhan-Allahi rida nafsihi, Subhan-Allahi zinata arshihi, and Subhan-Allah midada kalimatihi. The hadith does not lessen her remembrance. Rather, it teaches a concise form of tasbih with great weight. It is a clear hadith about powerful dhikr, tasbih, and remembering Allah with broad praise."},"teachings":["The Prophet صلى الله عليه وسلم taught a concise form of tasbih with great weight.","Juwairiyah was engaged in remembering Allah for a long period.","Some short phrases of dhikr can carry a meaning greater than their length."],"related_hadiths":[{"id":"6406","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"},{"id":"3464","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Weighty Words of Tasbih","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught four phrases of tasbih, repeated three times, described as greater and heavier."},"heading":{"title":"Hadith About SubhanAllahi Adada Khalqihi: Four Powerful Words of Tasbih","description":"This hadith tells us about Juwairiyah remembering Allah after the morning prayer. The Prophet صلى الله عليه وسلم passed by her, then returned later while she was still remembering Allah. He told her that he had said four words three times since leaving her, and that they were greater and weighed more heavily than what she had said. The phrases are: Subhan-Allahi adada khalqihi, Subhan-Allahi rida nafsihi, Subhan-Allahi zinata arshihi, and Subhan-Allah midada kalimatihi. The hadith does not lessen her remembrance. Rather, it teaches a concise form of tasbih with great weight. It is a clear hadith about powerful dhikr, tasbih, and remembering Allah with broad praise."},"teachings":["The Prophet صلى الله عليه وسلم taught a concise form of tasbih with great weight.","Juwairiyah was engaged in remembering Allah for a long period.","Some short phrases of dhikr can carry a meaning greater than their length."],"related_hadiths":[{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3464","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E333" s="4" t="n"/>
@@ -8136,7 +8140,7 @@
       </c>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr Around the Throne","description":"$book_name$ $hadith_number$ - $chapter_name$. Tasbih, tahlil, and tahmid are described as revolving around the Throne and reminding of their speaker."},"heading":{"title":"Hadith About Dhikr Around the Throne: Remembrance That Speaks for You","description":"This hadith describes the mention of Allah’s glory through tasbih, tahlil, and tahmid. The Prophet صلى الله عليه وسلم said these words revolve around the Throne, buzzing like bees, and they remind of the person who said them. Then he asked whether any one of us would like to have something that reminds of him in the presence of Allah. The picture in the hadith is powerful, but the teaching is simple: words of remembrance are not lost. Dhikr connects the servant to Allah in a way the servant may not fully see. This hadith about remembrance encourages regular tasbih, tahmid, and words that glorify Allah."},"teachings":["Tasbih, tahlil, and tahmid are mentioned as words that glorify Allah.","The hadith describes these words as revolving around the Throne.","Dhikr can remind of the one who said it in the presence of Allah."],"related_hadiths":[{"id":"6407","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"},{"id":"6405","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr Around the Throne","description":"$book_name$ $hadith_number$ - $chapter_name$. Tasbih, tahlil, and tahmid are described as revolving around the Throne and reminding of their speaker."},"heading":{"title":"Hadith About Dhikr Around the Throne: Remembrance That Speaks for You","description":"This hadith describes the mention of Allah’s glory through tasbih, tahlil, and tahmid. The Prophet صلى الله عليه وسلم said these words revolve around the Throne, buzzing like bees, and they remind of the person who said them. Then he asked whether any one of us would like to have something that reminds of him in the presence of Allah. The picture in the hadith is powerful, but the teaching is simple: words of remembrance are not lost. Dhikr connects the servant to Allah in a way the servant may not fully see. This hadith about remembrance encourages regular tasbih, tahmid, and words that glorify Allah."},"teachings":["Tasbih, tahlil, and tahmid are mentioned as words that glorify Allah.","The hadith describes these words as revolving around the Throne.","Dhikr can remind of the one who said it in the presence of Allah."],"related_hadiths":[{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E334" s="4" t="n"/>
@@ -8159,7 +8163,7 @@
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shared Wudu from One Vessel","description":"$book_name$ $hadith_number$ - $chapter_name$. Men and women performed wudu from one vessel in the Prophet’s time, showing shared use of clean water for ablution."},"heading":{"title":"Hadith About Wudu from One Vessel","description":"This hadith about wudu from one vessel shows a simple scene from the time of the Messenger of Allah. Ibn Umar said that men and women used to perform ablution from a single vessel. The main point in the text is not a long legal debate, but the basic practice of using one container of water for purification. The hadith keeps the focus on wudu, shared water, and the ease of daily worship. It also shows that the water itself remained usable for ablution even when more than one person used the same vessel. A reader searching for men and women wudu together should understand the wording carefully and avoid adding details that are not in the narration."},"teachings":["Shared water could be used for ablution in the situation described.","The Companions preserved simple details of daily worship.","The text teaches ease in using available clean water for wudu."],"related_hadiths":[{"id":"193","book_id":"1","label":"Sahih Bukhari"},{"id":"376","book_id":"6","label":"Sunan Ibn Majah"},{"id":"370","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shared Wudu from One Vessel","description":"$book_name$ $hadith_number$ - $chapter_name$. Men and women performed wudu from one vessel in the Prophet’s time, showing shared use of clean water for ablution."},"heading":{"title":"Hadith About Wudu from One Vessel","description":"This hadith about wudu from one vessel shows a simple scene from the time of the Messenger of Allah. Ibn Umar said that men and women used to perform ablution from a single vessel. The main point in the text is not a long legal debate, but the basic practice of using one container of water for purification. The hadith keeps the focus on wudu, shared water, and the ease of daily worship. It also shows that the water itself remained usable for ablution even when more than one person used the same vessel. A reader searching for men and women wudu together should understand the wording carefully and avoid adding details that are not in the narration."},"teachings":["Shared water could be used for ablution in the situation described.","The Companions preserved simple details of daily worship.","The text teaches ease in using available clean water for wudu."],"related_hadiths":[{"id":"193","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"376","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"370","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E335" s="4" t="n"/>
@@ -8182,7 +8186,7 @@
       </c>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Easy Dhikr for the Weak","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Hani asked for a deed, and the Prophet taught takbir, tahmid, and tasbih one hundred times each."},"heading":{"title":"Hadith About Easy Dhikr: Allahu Akbar, Alhamdulillah, and SubhanAllah 100 Times","description":"In this hadith, Umm Hani came to the Prophet صلى الله عليه وسلم and asked him to guide her to a good deed because she had become old, weak, and overweight. The Prophet صلى الله عليه وسلم gave her an action of the tongue: say Allahu Akbar one hundred times, Alhamdulillah one hundred times, and SubhanAllah one hundred times. He then described this dhikr as better than one hundred horses prepared for the sake of Allah, better than one hundred sacrificial camels, and better than freeing one hundred slaves. The hadith shows that remembrance of Allah is accessible even when the body is weak. It is a strong hadith about easy dhikr and the value of repeated praise."},"teachings":["The Prophet صلى الله عليه وسلم gave Umm Hani a deed suited to her condition.","Takbir, tahmid, and tasbih were each taught one hundred times.","Dhikr is an accessible deed for someone who is old or physically weak."],"related_hadiths":[{"id":"6403","book_id":"1","label":"Sahih Bukhari"},{"id":"6405","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Easy Dhikr for the Weak","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Hani asked for a deed, and the Prophet taught takbir, tahmid, and tasbih one hundred times each."},"heading":{"title":"Hadith About Easy Dhikr: Allahu Akbar, Alhamdulillah, and SubhanAllah 100 Times","description":"In this hadith, Umm Hani came to the Prophet صلى الله عليه وسلم and asked him to guide her to a good deed because she had become old, weak, and overweight. The Prophet صلى الله عليه وسلم gave her an action of the tongue: say Allahu Akbar one hundred times, Alhamdulillah one hundred times, and SubhanAllah one hundred times. He then described this dhikr as better than one hundred horses prepared for the sake of Allah, better than one hundred sacrificial camels, and better than freeing one hundred slaves. The hadith shows that remembrance of Allah is accessible even when the body is weak. It is a strong hadith about easy dhikr and the value of repeated praise."},"teachings":["The Prophet صلى الله عليه وسلم gave Umm Hani a deed suited to her condition.","Takbir, tahmid, and tasbih were each taught one hundred times.","Dhikr is an accessible deed for someone who is old or physically weak."],"related_hadiths":[{"id":"6403","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E336" s="4" t="n"/>
@@ -8205,7 +8209,7 @@
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four of the Best Words","description":"$book_name$ $hadith_number$ - $chapter_name$. Four words are described as the best speech, and it does not matter which one you begin with."},"heading":{"title":"Hadith About the Four Best Words: SubhanAllah, Alhamdulillah, La Ilaha Illallah, Allahu Akbar","description":"This hadith names four statements as the best of words: Subhan-Allah, wal-Hamdu-Lillah, wa la ilaha illallah, wa Allahu Akbar. The Prophet صلى الله عليه وسلم also said that it does not matter which of them a person begins with. The hadith is short, but it gives a clear set of words for daily remembrance. Each phrase carries praise, glorification, belief in Allah’s oneness, and magnifying Allah. The focus is not on a hard method or long order. The Prophet صلى الله عليه وسلم made it easy by saying a person may start with any of them. This hadith about dhikr is simple, easy to teach, and easy to practice."},"teachings":["The Prophet صلى الله عليه وسلم named four phrases as the best of words.","A person may begin with any of the four phrases mentioned.","Daily dhikr can be simple and easy to remember."],"related_hadiths":[{"id":"6403","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"},{"id":"3464","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four of the Best Words","description":"$book_name$ $hadith_number$ - $chapter_name$. Four words are described as the best speech, and it does not matter which one you begin with."},"heading":{"title":"Hadith About the Four Best Words: SubhanAllah, Alhamdulillah, La Ilaha Illallah, Allahu Akbar","description":"This hadith names four statements as the best of words: Subhan-Allah, wal-Hamdu-Lillah, wa la ilaha illallah, wa Allahu Akbar. The Prophet صلى الله عليه وسلم also said that it does not matter which of them a person begins with. The hadith is short, but it gives a clear set of words for daily remembrance. Each phrase carries praise, glorification, belief in Allah’s oneness, and magnifying Allah. The focus is not on a hard method or long order. The Prophet صلى الله عليه وسلم made it easy by saying a person may start with any of them. This hadith about dhikr is simple, easy to teach, and easy to practice."},"teachings":["The Prophet صلى الله عليه وسلم named four phrases as the best of words.","A person may begin with any of the four phrases mentioned.","Daily dhikr can be simple and easy to remember."],"related_hadiths":[{"id":"6403","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3464","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E337" s="4" t="n"/>
@@ -8228,7 +8232,7 @@
       </c>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | SubhanAllahi Wa Bihamdihi 100 Times","description":"$book_name$ $hadith_number$ - $chapter_name$. Saying SubhanAllahi wa bihamdihi one hundred times is linked to forgiveness, even like sea foam."},"heading":{"title":"Hadith About SubhanAllahi Wa Bihamdihi 100 Times and Forgiveness","description":"This hadith gives a clear promise in the Prophet’s صلى الله عليه وسلم words. Whoever says Subhan Allahi wa bi hamdihi one hundred times, his sins will be forgiven even if they were like the foam of the sea. The wording is direct, and the action is simple. The dhikr means glorifying Allah with praise. A person can say it without needing a special setting in this text. The hadith is often searched by people looking for SubhanAllahi wa bihamdihi benefits, but the main point is the Prophet’s صلى الله عليه وسلم statement: one hundred times is linked to forgiveness. This hadith reminds us that the tongue can be used for words beloved to Allah."},"teachings":["The phrase Subhan Allahi wa bi hamdihi is a form of tasbih and praise.","The hadith mentions saying it one hundred times.","The Prophet صلى الله عليه وسلم linked this dhikr to forgiveness, even if sins were like sea foam."],"related_hadiths":[{"id":"6405","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"},{"id":"3464","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | SubhanAllahi Wa Bihamdihi 100 Times","description":"$book_name$ $hadith_number$ - $chapter_name$. Saying SubhanAllahi wa bihamdihi one hundred times is linked to forgiveness, even like sea foam."},"heading":{"title":"Hadith About SubhanAllahi Wa Bihamdihi 100 Times and Forgiveness","description":"This hadith gives a clear promise in the Prophet’s صلى الله عليه وسلم words. Whoever says Subhan Allahi wa bi hamdihi one hundred times, his sins will be forgiven even if they were like the foam of the sea. The wording is direct, and the action is simple. The dhikr means glorifying Allah with praise. A person can say it without needing a special setting in this text. The hadith is often searched by people looking for SubhanAllahi wa bihamdihi benefits, but the main point is the Prophet’s صلى الله عليه وسلم statement: one hundred times is linked to forgiveness. This hadith reminds us that the tongue can be used for words beloved to Allah."},"teachings":["The phrase Subhan Allahi wa bi hamdihi is a form of tasbih and praise.","The hadith mentions saying it one hundred times.","The Prophet صلى الله عليه وسلم linked this dhikr to forgiveness, even if sins were like sea foam."],"related_hadiths":[{"id":"6405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3464","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E338" s="4" t="n"/>
@@ -8251,7 +8255,7 @@
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr That Sheds Sins","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught four words of dhikr that shed sins like a tree sheds its leaves."},"heading":{"title":"Hadith About Dhikr Removing Sins: Words That Shed Faults Like Leaves","description":"In this hadith, the Prophet صلى الله عليه وسلم told Abu Darda to recite Subhan-Allah, wal-Hamdu-Lillah, wa la ilaha illallah, and Allahu Akbar. He then said these words shed sins like a tree sheds its leaves. The image is simple and easy to understand. Leaves fall from a tree, and in the same way this dhikr is described as causing sins to fall away. The hadith gives hope through words that are known and easy to say. It also keeps the focus on remembrance of Allah, not on complex actions. This is a helpful hadith about dhikr, forgiveness, and using the tongue for words that draw a person back to Allah."},"teachings":["The Prophet صلى الله عليه وسلم advised Abu Darda to recite four phrases of dhikr.","These words are described as shedding sins like leaves fall from a tree.","Dhikr is a means of turning the tongue toward Allah."],"related_hadiths":[{"id":"6405","book_id":"1","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr That Sheds Sins","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught four words of dhikr that shed sins like a tree sheds its leaves."},"heading":{"title":"Hadith About Dhikr Removing Sins: Words That Shed Faults Like Leaves","description":"In this hadith, the Prophet صلى الله عليه وسلم told Abu Darda to recite Subhan-Allah, wal-Hamdu-Lillah, wa la ilaha illallah, and Allahu Akbar. He then said these words shed sins like a tree sheds its leaves. The image is simple and easy to understand. Leaves fall from a tree, and in the same way this dhikr is described as causing sins to fall away. The hadith gives hope through words that are known and easy to say. It also keeps the focus on remembrance of Allah, not on complex actions. This is a helpful hadith about dhikr, forgiveness, and using the tongue for words that draw a person back to Allah."},"teachings":["The Prophet صلى الله عليه وسلم advised Abu Darda to recite four phrases of dhikr.","These words are described as shedding sins like leaves fall from a tree.","Dhikr is a means of turning the tongue toward Allah."],"related_hadiths":[{"id":"6405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E339" s="4" t="n"/>
@@ -8274,7 +8278,7 @@
       </c>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istighfar in One Gathering","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar counted the Prophet saying a repentance supplication one hundred times in a gathering."},"heading":{"title":"Hadith About Rabbighfirli Wa Tub Alayya: Istighfar 100 Times in a Gathering","description":"This hadith shows how often the Prophet صلى الله عليه وسلم sought forgiveness in one sitting. Ibn Umar said they used to count the Messenger of Allah صلى الله عليه وسلم saying one hundred times in a gathering: Rabbighfirli wa tub alayya innaka Antat-Tawwabur-Rahim. The meaning is: O Allah, forgive me and accept my repentance, for You are the Accepter of repentance, the Most Merciful. The hadith is simple and very practical. It teaches that seeking forgiveness is not only for rare moments. It can be repeated often, even in a gathering. This hadith about istighfar gives a clear phrase to say and shows the Prophet’s صلى الله عليه وسلم regular habit of asking Allah for forgiveness and repentance."},"teachings":["The Prophet صلى الله عليه وسلم repeated a supplication for forgiveness in a gathering.","The phrase asks Allah for forgiveness and acceptance of repentance.","Ibn Umar and others counted this supplication one hundred times."],"related_hadiths":[{"id":"6306","book_id":"1","label":"Sahih Bukhari"},{"id":"6307","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istighfar in One Gathering","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar counted the Prophet saying a repentance supplication one hundred times in a gathering."},"heading":{"title":"Hadith About Rabbighfirli Wa Tub Alayya: Istighfar 100 Times in a Gathering","description":"This hadith shows how often the Prophet صلى الله عليه وسلم sought forgiveness in one sitting. Ibn Umar said they used to count the Messenger of Allah صلى الله عليه وسلم saying one hundred times in a gathering: Rabbighfirli wa tub alayya innaka Antat-Tawwabur-Rahim. The meaning is: O Allah, forgive me and accept my repentance, for You are the Accepter of repentance, the Most Merciful. The hadith is simple and very practical. It teaches that seeking forgiveness is not only for rare moments. It can be repeated often, even in a gathering. This hadith about istighfar gives a clear phrase to say and shows the Prophet’s صلى الله عليه وسلم regular habit of asking Allah for forgiveness and repentance."},"teachings":["The Prophet صلى الله عليه وسلم repeated a supplication for forgiveness in a gathering.","The phrase asks Allah for forgiveness and acceptance of repentance.","Ibn Umar and others counted this supplication one hundred times."],"related_hadiths":[{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6307","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E340" s="4" t="n"/>
@@ -8297,7 +8301,7 @@
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Daily Istighfar 100 Times","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said he sought Allah’s forgiveness and repented to Him one hundred times each day."},"heading":{"title":"Hadith About Istighfar 100 Times a Day: The Prophet’s Daily Repentance","description":"This hadith is short, but it carries a strong daily lesson. Abu Hurairah narrated that the Messenger of Allah صلى الله عليه وسلم said: I seek the forgiveness of Allah and repent to Him one hundred times each day. The words show repeated istighfar and tawbah. The Prophet صلى الله عليه وسلم did not present seeking forgiveness as something distant or unusual. In this narration, it is a daily action repeated many times. For anyone searching for hadith about istighfar, this text gives a clear model: ask Allah for forgiveness and turn back to Him often. The hadith does not list extra details here. It simply shows the Prophet’s صلى الله عليه وسلم frequent return to Allah through repentance."},"teachings":["The Prophet صلى الله عليه وسلم said he sought Allah’s forgiveness one hundred times daily.","Istighfar and repentance are joined together in this narration.","Seeking forgiveness can be a regular daily habit."],"related_hadiths":[{"id":"6306","book_id":"1","label":"Sahih Bukhari"},{"id":"6307","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Daily Istighfar 100 Times","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said he sought Allah’s forgiveness and repented to Him one hundred times each day."},"heading":{"title":"Hadith About Istighfar 100 Times a Day: The Prophet’s Daily Repentance","description":"This hadith is short, but it carries a strong daily lesson. Abu Hurairah narrated that the Messenger of Allah صلى الله عليه وسلم said: I seek the forgiveness of Allah and repent to Him one hundred times each day. The words show repeated istighfar and tawbah. The Prophet صلى الله عليه وسلم did not present seeking forgiveness as something distant or unusual. In this narration, it is a daily action repeated many times. For anyone searching for hadith about istighfar, this text gives a clear model: ask Allah for forgiveness and turn back to Him often. The hadith does not list extra details here. It simply shows the Prophet’s صلى الله عليه وسلم frequent return to Allah through repentance."},"teachings":["The Prophet صلى الله عليه وسلم said he sought Allah’s forgiveness one hundred times daily.","Istighfar and repentance are joined together in this narration.","Seeking forgiveness can be a regular daily habit."],"related_hadiths":[{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6307","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E341" s="4" t="n"/>
@@ -8320,7 +8324,7 @@
       </c>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istighfar 70 Times Daily","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said he sought Allah’s forgiveness and repented to Him seventy times each day."},"heading":{"title":"Hadith About Istighfar 70 Times a Day: Frequent Return to Allah","description":"This narration states that the Messenger of Allah صلى الله عليه وسلم said: I seek the forgiveness of Allah and repent to Him seventy times each day. The hadith highlights repeated istighfar and tawbah in daily life. It does not give a long instruction or a complex method. It simply reports how often the Prophet صلى الله عليه وسلم turned to Allah with words of forgiveness and repentance. For a reader, the lesson is easy to understand: seeking forgiveness should not be delayed until a special moment. It can be repeated during the day. This hadith about istighfar 70 times a day gives a direct example of frequent remembrance through asking Allah to forgive and accepting one’s return."},"teachings":["The Prophet صلى الله عليه وسلم mentioned seeking forgiveness seventy times each day.","Repentance to Allah is included with asking forgiveness.","Daily istighfar can be repeated often in simple words."],"related_hadiths":[{"id":"6307","book_id":"1","label":"Sahih Bukhari"},{"id":"6306","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istighfar 70 Times Daily","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said he sought Allah’s forgiveness and repented to Him seventy times each day."},"heading":{"title":"Hadith About Istighfar 70 Times a Day: Frequent Return to Allah","description":"This narration states that the Messenger of Allah صلى الله عليه وسلم said: I seek the forgiveness of Allah and repent to Him seventy times each day. The hadith highlights repeated istighfar and tawbah in daily life. It does not give a long instruction or a complex method. It simply reports how often the Prophet صلى الله عليه وسلم turned to Allah with words of forgiveness and repentance. For a reader, the lesson is easy to understand: seeking forgiveness should not be delayed until a special moment. It can be repeated during the day. This hadith about istighfar 70 times a day gives a direct example of frequent remembrance through asking Allah to forgive and accepting one’s return."},"teachings":["The Prophet صلى الله عليه وسلم mentioned seeking forgiveness seventy times each day.","Repentance to Allah is included with asking forgiveness.","Daily istighfar can be repeated often in simple words."],"related_hadiths":[{"id":"6307","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E342" s="4" t="n"/>
@@ -8343,7 +8347,7 @@
       </c>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istighfar After Harsh Speech","description":"$book_name$ $hadith_number$ - $chapter_name$. Hudhaifah mentioned harsh speech with family, and the Prophet guided him to daily istighfar."},"heading":{"title":"Hadith About Istighfar and Family Speech: Seeking Forgiveness 70 Times Daily","description":"This hadith connects istighfar with a real personal struggle. Hudhaifah said he was harsh in the way he spoke to his family, though not to others. He mentioned this to the Prophet صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم replied by directing him to seek forgiveness, saying he should ask Allah to forgive him seventy times each day. The hadith stays focused on the issue mentioned: harsh speech toward family and the remedy of seeking forgiveness. It does not give a long list of family rulings. It gives a direct spiritual response. This hadith about istighfar reminds us that when a person notices a fault in speech, turning to Allah in forgiveness is part of the response."},"teachings":["Hudhaifah honestly mentioned his harsh speech toward his family.","The Prophet صلى الله عليه وسلم directed him to seek Allah’s forgiveness.","Daily istighfar was given as a response to a personal fault."],"related_hadiths":[{"id":"6307","book_id":"1","label":"Sahih Bukhari"},{"id":"6306","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istighfar After Harsh Speech","description":"$book_name$ $hadith_number$ - $chapter_name$. Hudhaifah mentioned harsh speech with family, and the Prophet guided him to daily istighfar."},"heading":{"title":"Hadith About Istighfar and Family Speech: Seeking Forgiveness 70 Times Daily","description":"This hadith connects istighfar with a real personal struggle. Hudhaifah said he was harsh in the way he spoke to his family, though not to others. He mentioned this to the Prophet صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم replied by directing him to seek forgiveness, saying he should ask Allah to forgive him seventy times each day. The hadith stays focused on the issue mentioned: harsh speech toward family and the remedy of seeking forgiveness. It does not give a long list of family rulings. It gives a direct spiritual response. This hadith about istighfar reminds us that when a person notices a fault in speech, turning to Allah in forgiveness is part of the response."},"teachings":["Hudhaifah honestly mentioned his harsh speech toward his family.","The Prophet صلى الله عليه وسلم directed him to seek Allah’s forgiveness.","Daily istighfar was given as a response to a personal fault."],"related_hadiths":[{"id":"6307","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E343" s="4" t="n"/>
@@ -8366,7 +8370,7 @@
       </c>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Record Full of Istighfar","description":"$book_name$ $hadith_number$ - $chapter_name$. Glad tidings are given to those who find much seeking forgiveness in their record of deeds."},"heading":{"title":"Hadith About a Record Full of Istighfar: Glad Tidings for Seeking Forgiveness","description":"This hadith gives hope to the one who often asks Allah for forgiveness. The Prophet صلى الله عليه وسلم said: Glad tidings to those who find a lot of seeking forgiveness in the record of their deeds. The wording points to the record that a person will see, and it highlights frequent istighfar as something good to find there. The hadith does not mention a special time, place, or fixed phrase in this text. Its main message is to make seeking forgiveness common in one’s life. A record with much istighfar is described with glad tidings. This hadith about istighfar encourages the believer to fill the day with humble words of return to Allah."},"teachings":["Much istighfar in the record of deeds is praised in the hadith.","The Prophet صلى الله عليه وسلم gave glad tidings to those who seek forgiveness often.","The hadith encourages frequent asking of Allah’s forgiveness."],"related_hadiths":[{"id":"6306","book_id":"1","label":"Sahih Bukhari"},{"id":"6307","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Record Full of Istighfar","description":"$book_name$ $hadith_number$ - $chapter_name$. Glad tidings are given to those who find much seeking forgiveness in their record of deeds."},"heading":{"title":"Hadith About a Record Full of Istighfar: Glad Tidings for Seeking Forgiveness","description":"This hadith gives hope to the one who often asks Allah for forgiveness. The Prophet صلى الله عليه وسلم said: Glad tidings to those who find a lot of seeking forgiveness in the record of their deeds. The wording points to the record that a person will see, and it highlights frequent istighfar as something good to find there. The hadith does not mention a special time, place, or fixed phrase in this text. Its main message is to make seeking forgiveness common in one’s life. A record with much istighfar is described with glad tidings. This hadith about istighfar encourages the believer to fill the day with humble words of return to Allah."},"teachings":["Much istighfar in the record of deeds is praised in the hadith.","The Prophet صلى الله عليه وسلم gave glad tidings to those who seek forgiveness often.","The hadith encourages frequent asking of Allah’s forgiveness."],"related_hadiths":[{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6307","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E344" s="4" t="n"/>
@@ -8389,7 +8393,7 @@
       </c>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Relief Through Istighfar","description":"$book_name$ $hadith_number$ - $chapter_name$. Persisting in istighfar is linked to relief from worry, a way out of hardship, and unexpected provision."},"heading":{"title":"Hadith About Istighfar for Relief: A Way Out from Worry and Hardship","description":"This hadith speaks about persistence in asking Allah for forgiveness. The Prophet صلى الله عليه وسلم said that whoever keeps to istighfar, Allah will grant him relief from every worry, a way out from every hardship, and provision from sources he could not imagine. The hadith uses strong words, so the explanation should stay close to the text. It teaches that constant seeking of forgiveness is linked to relief, exit from difficulty, and unexpected provision. It does not tell a person to ignore effort or responsibility. It highlights istighfar as a means of help from Allah. This is why people often search for hadith about istighfar for rizq, worry, and hardship."},"teachings":["The hadith encourages persistence in seeking Allah’s forgiveness.","Istighfar is linked to relief from worry and a way out of hardship.","The hadith mentions provision from sources a person did not expect."],"related_hadiths":[{"id":"6306","book_id":"1","label":"Sahih Bukhari"},{"id":"6307","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Relief Through Istighfar","description":"$book_name$ $hadith_number$ - $chapter_name$. Persisting in istighfar is linked to relief from worry, a way out of hardship, and unexpected provision."},"heading":{"title":"Hadith About Istighfar for Relief: A Way Out from Worry and Hardship","description":"This hadith speaks about persistence in asking Allah for forgiveness. The Prophet صلى الله عليه وسلم said that whoever keeps to istighfar, Allah will grant him relief from every worry, a way out from every hardship, and provision from sources he could not imagine. The hadith uses strong words, so the explanation should stay close to the text. It teaches that constant seeking of forgiveness is linked to relief, exit from difficulty, and unexpected provision. It does not tell a person to ignore effort or responsibility. It highlights istighfar as a means of help from Allah. This is why people often search for hadith about istighfar for rizq, worry, and hardship."},"teachings":["The hadith encourages persistence in seeking Allah’s forgiveness.","Istighfar is linked to relief from worry and a way out of hardship.","The hadith mentions provision from sources a person did not expect."],"related_hadiths":[{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6307","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E345" s="4" t="n"/>
@@ -8412,7 +8416,7 @@
       </c>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shared Vessel and Gentle Practice","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Subyah described her hand touching the Prophet’s hand during wudu from one vessel, showing a simple shared ablution scene."},"heading":{"title":"Umm Subyah Hadith on Wudu from One Vessel","description":"This hadith on wudu from one vessel gives a close and humble picture of ablution. Umm Subyah Al-Juhaniyyah said that her hand would often touch the hand of the Messenger of Allah while they were performing ablution from a single vessel. The teaching is based on that clear wording: one vessel, shared use, and wudu. The narration does not ask us to add extra stories or wider rulings beyond what is said. It simply records that this happened during ablution. For people searching for the Umm Subyah hadith or hand touching during wudu, the key message is that the water vessel was shared and the act remained connected to purification."},"teachings":["The narration shows shared use of one vessel during wudu.","It records a practical moment of ablution without extra detail.","The focus stays on purification and the use of available water."],"related_hadiths":[{"id":"193","book_id":"1","label":"Sahih Bukhari"},{"id":"376","book_id":"6","label":"Sunan Ibn Majah"},{"id":"370","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shared Vessel and Gentle Practice","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Subyah described her hand touching the Prophet’s hand during wudu from one vessel, showing a simple shared ablution scene."},"heading":{"title":"Umm Subyah Hadith on Wudu from One Vessel","description":"This hadith on wudu from one vessel gives a close and humble picture of ablution. Umm Subyah Al-Juhaniyyah said that her hand would often touch the hand of the Messenger of Allah while they were performing ablution from a single vessel. The teaching is based on that clear wording: one vessel, shared use, and wudu. The narration does not ask us to add extra stories or wider rulings beyond what is said. It simply records that this happened during ablution. For people searching for the Umm Subyah hadith or hand touching during wudu, the key message is that the water vessel was shared and the act remained connected to purification."},"teachings":["The narration shows shared use of one vessel during wudu.","It records a practical moment of ablution without extra detail.","The focus stays on purification and the use of available water."],"related_hadiths":[{"id":"193","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"376","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"370","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E346" s="4" t="n"/>
@@ -8435,7 +8439,7 @@
       </c>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rejoice in Good and Seek Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asked Allah to make him among those who rejoice at good and seek forgiveness after wrong."},"heading":{"title":"Hadith About Repentance: Rejoicing in Good and Seeking Forgiveness After Wrong","description":"This hadith gives a short dua of the Prophet صلى الله عليه وسلم: O Allah, make me one of those who, if they do good deeds, they rejoice, and if they do bad deeds, they seek forgiveness. The wording teaches balance. Good deeds should bring a believer joy, but wrongdoing should lead to istighfar, not pride or neglect. The hadith does not describe the good deed or the bad deed in detail. It focuses on the servant’s response to both. When good happens, the heart feels glad. When wrong happens, the servant asks Allah for forgiveness. This hadith about repentance is simple, gentle, and useful for daily self-checking."},"teachings":["The Prophet صلى الله عليه وسلم asked Allah to make him among people who rejoice after doing good.","The same dua asks to be among those who seek forgiveness after doing wrong.","A believer’s response to mistakes should include istighfar."],"related_hadiths":[{"id":"6306","book_id":"1","label":"Sahih Bukhari"},{"id":"6307","book_id":"1","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rejoice in Good and Seek Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asked Allah to make him among those who rejoice at good and seek forgiveness after wrong."},"heading":{"title":"Hadith About Repentance: Rejoicing in Good and Seeking Forgiveness After Wrong","description":"This hadith gives a short dua of the Prophet صلى الله عليه وسلم: O Allah, make me one of those who, if they do good deeds, they rejoice, and if they do bad deeds, they seek forgiveness. The wording teaches balance. Good deeds should bring a believer joy, but wrongdoing should lead to istighfar, not pride or neglect. The hadith does not describe the good deed or the bad deed in detail. It focuses on the servant’s response to both. When good happens, the heart feels glad. When wrong happens, the servant asks Allah for forgiveness. This hadith about repentance is simple, gentle, and useful for daily self-checking."},"teachings":["The Prophet صلى الله عليه وسلم asked Allah to make him among people who rejoice after doing good.","The same dua asks to be among those who seek forgiveness after doing wrong.","A believer’s response to mistakes should include istighfar."],"related_hadiths":[{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6307","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6407","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E347" s="4" t="n"/>
@@ -8458,7 +8462,7 @@
       </c>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Mercy and Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how Allah rewards good deeds, forgives sins, and welcomes servants who draw near without shirk."},"heading":{"title":"Hadith About Allah’s Mercy, Reward, and Forgiveness","description":"This Hadith Qudsi teaches a hopeful message about Allah’s mercy and forgiveness. A good deed is rewarded ten times and even more, while a bad deed is counted as one, or Allah may forgive it. The Hadith also shows that when a servant draws near to Allah, Allah responds with even greater nearness. This makes the believer feel encouraged to start with small steps of worship, repentance, and sincere return. The final part gives strong hope to the person who avoids shirk. Even if someone meets Allah with sins as great as the earth, Allah mentions forgiveness equal to that, as long as the person did not associate anything with Him in worship."},"teachings":["A single good deed is rewarded with ten like it and more.","A bad deed is counted as one, or Allah may forgive it.","Drawing near to Allah is met with greater mercy from Him.","Avoiding shirk is tied to the hope of vast forgiveness."],"related_hadiths":[{"id":"7405","book_id":"1","label":"Sahih Bukhari"},{"id":"7404","book_id":"1","label":"Sahih Bukhari"},{"id":"7422","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Mercy and Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how Allah rewards good deeds, forgives sins, and welcomes servants who draw near without shirk."},"heading":{"title":"Hadith About Allah’s Mercy, Reward, and Forgiveness","description":"This Hadith Qudsi teaches a hopeful message about Allah’s mercy and forgiveness. A good deed is rewarded ten times and even more, while a bad deed is counted as one, or Allah may forgive it. The Hadith also shows that when a servant draws near to Allah, Allah responds with even greater nearness. This makes the believer feel encouraged to start with small steps of worship, repentance, and sincere return. The final part gives strong hope to the person who avoids shirk. Even if someone meets Allah with sins as great as the earth, Allah mentions forgiveness equal to that, as long as the person did not associate anything with Him in worship."},"teachings":["A single good deed is rewarded with ten like it and more.","A bad deed is counted as one, or Allah may forgive it.","Drawing near to Allah is met with greater mercy from Him.","Avoiding shirk is tied to the hope of vast forgiveness."],"related_hadiths":[{"id":"7405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7404","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7422","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E348" s="4" t="n"/>
@@ -8481,7 +8485,7 @@
       </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Good Thoughts of Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful Hadith on remembering Allah, thinking well of Him, and drawing near through sincere dhikr."},"heading":{"title":"I Am as My Servant Thinks of Me: A Hadith About Dhikr","description":"This Hadith focuses on dhikr and having a good thought of Allah. Allah says He is as His servant thinks of Him, and He is with the servant when the servant mentions Him. The Hadith mentions private remembrance and public remembrance. If a person remembers Allah alone, Allah mentions him to Himself. If he remembers Allah in a gathering, Allah mentions him in a better gathering. It also repeats the beautiful meaning of drawing near to Allah: when the servant moves toward Allah, Allah’s response is greater. This makes dhikr feel close and personal. Remembering Allah is not just words on the tongue; it is a way of turning back to Him with trust and hope."},"teachings":["A believer should think well of Allah while remembering Him.","Allah is with the servant when the servant mentions Him.","Private and public dhikr both have honored mention with Allah.","Small steps toward Allah are met with greater nearness from Him."],"related_hadiths":[{"id":"7405","book_id":"1","label":"Sahih Bukhari"},{"id":"7505","book_id":"1","label":"Sahih Bukhari"},{"id":"7404","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Good Thoughts of Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful Hadith on remembering Allah, thinking well of Him, and drawing near through sincere dhikr."},"heading":{"title":"I Am as My Servant Thinks of Me: A Hadith About Dhikr","description":"This Hadith focuses on dhikr and having a good thought of Allah. Allah says He is as His servant thinks of Him, and He is with the servant when the servant mentions Him. The Hadith mentions private remembrance and public remembrance. If a person remembers Allah alone, Allah mentions him to Himself. If he remembers Allah in a gathering, Allah mentions him in a better gathering. It also repeats the beautiful meaning of drawing near to Allah: when the servant moves toward Allah, Allah’s response is greater. This makes dhikr feel close and personal. Remembering Allah is not just words on the tongue; it is a way of turning back to Him with trust and hope."},"teachings":["A believer should think well of Allah while remembering Him.","Allah is with the servant when the servant mentions Him.","Private and public dhikr both have honored mention with Allah.","Small steps toward Allah are met with greater nearness from Him."],"related_hadiths":[{"id":"7405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7505","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7404","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E349" s="4" t="n"/>
@@ -8504,7 +8508,7 @@
       </c>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Treasure of Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn why La hawla wa la quwwata illa billah is called one of the treasures of Paradise."},"heading":{"title":"La Hawla Wa La Quwwata Illa Billah: Treasure of Paradise Hadith","description":"This Hadith teaches the value of saying La hawla wa la quwwata illa billah, which means there is no power and no strength except with Allah. Abu Musa was already saying these words when the Prophet heard him. The Prophet then called him by name and asked if he should guide him to a word from the treasures of Paradise. When Abu Musa said yes, the Prophet told him to say this phrase. The Hadith keeps the lesson very clear. This dhikr reminds a person that strength, ability, change, and help are all by Allah. It is short, easy to say, and carries a great meaning."},"teachings":["La hawla wa la quwwata illa billah is one of the treasures of Paradise.","A short dhikr can carry a deep meaning.","True power and strength belong to Allah.","The Prophet taught useful words in a simple and caring way."],"related_hadiths":[{"id":"6384","book_id":"1","label":"Sahih Bukhari"},{"id":"6610","book_id":"1","label":"Sahih Bukhari"},{"id":"7386","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Treasure of Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn why La hawla wa la quwwata illa billah is called one of the treasures of Paradise."},"heading":{"title":"La Hawla Wa La Quwwata Illa Billah: Treasure of Paradise Hadith","description":"This Hadith teaches the value of saying La hawla wa la quwwata illa billah, which means there is no power and no strength except with Allah. Abu Musa was already saying these words when the Prophet heard him. The Prophet then called him by name and asked if he should guide him to a word from the treasures of Paradise. When Abu Musa said yes, the Prophet told him to say this phrase. The Hadith keeps the lesson very clear. This dhikr reminds a person that strength, ability, change, and help are all by Allah. It is short, easy to say, and carries a great meaning."},"teachings":["La hawla wa la quwwata illa billah is one of the treasures of Paradise.","A short dhikr can carry a deep meaning.","True power and strength belong to Allah.","The Prophet taught useful words in a simple and caring way."],"related_hadiths":[{"id":"6384","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6610","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7386","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E350" s="4" t="n"/>
@@ -8527,7 +8531,7 @@
       </c>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Hawla Dhikr","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear Hadith showing La hawla wa la quwwata illa billah as a treasure from Paradise."},"heading":{"title":"La Hawla Wa La Quwwata Illa Billah and the Core Topic of Dhikr","description":"This Hadith gives a direct lesson about the dhikr La hawla wa la quwwata illa billah. Abu Dharr reports that the Messenger of Allah asked if he should tell him about a treasure from the treasures of Paradise. When Abu Dharr said yes, the Prophet gave this short phrase as the answer. The wording is simple, but the meaning is strong. It teaches that a believer should not see power and strength as independent from Allah. For someone searching for the La hawla wa la quwwata illa billah Hadith, this narration shows why Muslims often say it during need, weakness, effort, or remembrance."},"teachings":["The phrase La hawla wa la quwwata illa billah is highly valued.","A treasure of Paradise can be found in a short statement of dhikr.","The believer is reminded that strength is only with Allah.","The Prophet taught Abu Dharr words that are easy to remember."],"related_hadiths":[{"id":"6384","book_id":"1","label":"Sahih Bukhari"},{"id":"6610","book_id":"1","label":"Sahih Bukhari"},{"id":"7386","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Hawla Dhikr","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear Hadith showing La hawla wa la quwwata illa billah as a treasure from Paradise."},"heading":{"title":"La Hawla Wa La Quwwata Illa Billah and the Core Topic of Dhikr","description":"This Hadith gives a direct lesson about the dhikr La hawla wa la quwwata illa billah. Abu Dharr reports that the Messenger of Allah asked if he should tell him about a treasure from the treasures of Paradise. When Abu Dharr said yes, the Prophet gave this short phrase as the answer. The wording is simple, but the meaning is strong. It teaches that a believer should not see power and strength as independent from Allah. For someone searching for the La hawla wa la quwwata illa billah Hadith, this narration shows why Muslims often say it during need, weakness, effort, or remembrance."},"teachings":["The phrase La hawla wa la quwwata illa billah is highly valued.","A treasure of Paradise can be found in a short statement of dhikr.","The believer is reminded that strength is only with Allah.","The Prophet taught Abu Dharr words that are easy to remember."],"related_hadiths":[{"id":"6384","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6610","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7386","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E351" s="4" t="n"/>
@@ -8550,7 +8554,7 @@
       </c>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Say La Hawla Often","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet advised saying La hawla wa la quwwata illa billah often as a treasure of Paradise."},"heading":{"title":"Say La Hawla Wa La Quwwata Illa Billah Often","description":"This Hadith is about frequent dhikr. Hazim bin Harmalah passed by the Prophet, and the Prophet directly advised him to say often La hawla wa la quwwata illa billah. The reason given in the Hadith is clear: it is one of the treasures of Paradise. The phrase means there is no power and no strength except with Allah. This makes the dhikr useful for daily life because it reminds a person that every ability, every step, and every form of strength comes only by Allah’s help. The Hadith does not make the phrase hard or long. It teaches a short remembrance that can be repeated often."},"teachings":["The Prophet advised saying this dhikr often.","La hawla wa la quwwata illa billah is one of the treasures of Paradise.","Repeated dhikr helps a person remember reliance on Allah.","Short phrases of remembrance can be part of daily worship."],"related_hadiths":[{"id":"6384","book_id":"1","label":"Sahih Bukhari"},{"id":"6610","book_id":"1","label":"Sahih Bukhari"},{"id":"7386","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Say La Hawla Often","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet advised saying La hawla wa la quwwata illa billah often as a treasure of Paradise."},"heading":{"title":"Say La Hawla Wa La Quwwata Illa Billah Often","description":"This Hadith is about frequent dhikr. Hazim bin Harmalah passed by the Prophet, and the Prophet directly advised him to say often La hawla wa la quwwata illa billah. The reason given in the Hadith is clear: it is one of the treasures of Paradise. The phrase means there is no power and no strength except with Allah. This makes the dhikr useful for daily life because it reminds a person that every ability, every step, and every form of strength comes only by Allah’s help. The Hadith does not make the phrase hard or long. It teaches a short remembrance that can be repeated often."},"teachings":["The Prophet advised saying this dhikr often.","La hawla wa la quwwata illa billah is one of the treasures of Paradise.","Repeated dhikr helps a person remember reliance on Allah.","Short phrases of remembrance can be part of daily worship."],"related_hadiths":[{"id":"6384","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6610","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7386","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E352" s="4" t="n"/>
@@ -8573,7 +8577,7 @@
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Calling Upon Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. A direct reminder that neglecting dua is serious, because Allah loves to be called upon."},"heading":{"title":"Whoever Does Not Call Upon Allah: Hadith About Dua","description":"This Hadith gives a serious reminder about dua. The Messenger of Allah said that whoever does not call upon Allah, Allah will be angry with him. The wording is short, but it has a strong message. Dua is not only for hard times. It is a sign that the servant knows his need and turns to Allah. A person searching for the Hadith about calling upon Allah should understand the core point: leaving dua is not a small matter in this narration. Calling on Allah shows humility, need, and trust. The Hadith does not mention a specific time or wording, so the lesson stays general and easy to apply."},"teachings":["A Muslim should not neglect calling upon Allah.","Dua shows need, humility, and turning to Allah.","The Hadith warns that leaving dua is serious.","Supplication is part of a living connection with Allah."],"related_hadiths":[{"id":"3373","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3372","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Calling Upon Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. A direct reminder that neglecting dua is serious, because Allah loves to be called upon."},"heading":{"title":"Whoever Does Not Call Upon Allah: Hadith About Dua","description":"This Hadith gives a serious reminder about dua. The Messenger of Allah said that whoever does not call upon Allah, Allah will be angry with him. The wording is short, but it has a strong message. Dua is not only for hard times. It is a sign that the servant knows his need and turns to Allah. A person searching for the Hadith about calling upon Allah should understand the core point: leaving dua is not a small matter in this narration. Calling on Allah shows humility, need, and trust. The Hadith does not mention a specific time or wording, so the lesson stays general and easy to apply."},"teachings":["A Muslim should not neglect calling upon Allah.","Dua shows need, humility, and turning to Allah.","The Hadith warns that leaving dua is serious.","Supplication is part of a living connection with Allah."],"related_hadiths":[{"id":"3373","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"3372","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E353" s="4" t="inlineStr">
@@ -8600,7 +8604,7 @@
       </c>
       <c r="D354" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Is Worship","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that supplication is worship and recited the verse: Invoke Me, I will respond."},"heading":{"title":"Supplication Is Worship: A Hadith About Dua","description":"This Hadith states the core topic in very clear words: supplication is worship. The Prophet then recited the verse in which Allah says, Invoke Me, I will respond to you. The message is simple and powerful. Dua is not just asking for things; it is an act of worship itself. When a person raises his need to Allah, he is showing that Allah is the One who hears, gives, guides, and responds. For readers searching for supplication is worship Hadith, this narration is one of the clearest texts on the place of dua in Islam. It teaches that turning to Allah through dua is part of worship, not separate from it."},"teachings":["Dua is described as worship.","Allah commands His servants to invoke Him.","The Hadith connects supplication with Allah’s response.","Asking Allah is itself an act of devotion."],"related_hadiths":[{"id":"3372","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Is Worship","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that supplication is worship and recited the verse: Invoke Me, I will respond."},"heading":{"title":"Supplication Is Worship: A Hadith About Dua","description":"This Hadith states the core topic in very clear words: supplication is worship. The Prophet then recited the verse in which Allah says, Invoke Me, I will respond to you. The message is simple and powerful. Dua is not just asking for things; it is an act of worship itself. When a person raises his need to Allah, he is showing that Allah is the One who hears, gives, guides, and responds. For readers searching for supplication is worship Hadith, this narration is one of the clearest texts on the place of dua in Islam. It teaches that turning to Allah through dua is part of worship, not separate from it."},"teachings":["Dua is described as worship.","Allah commands His servants to invoke Him.","The Hadith connects supplication with Allah’s response.","Asking Allah is itself an act of devotion."],"related_hadiths":[{"id":"3372","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E354" s="4" t="inlineStr">
@@ -8627,7 +8631,7 @@
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Nobility of Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that nothing is more noble to Allah than sincere supplication."},"heading":{"title":"Nothing More Noble to Allah Than Supplication","description":"This Hadith highlights the honor of dua. The Prophet said there is nothing more noble to Allah than supplication. The Hadith is brief, but it makes the status of dua easy to understand. Supplication is not a weak act or a last choice. It is a noble act in which the servant turns to Allah and asks from Him. For someone searching for the Hadith nothing more noble than dua, the key lesson is that Allah values the servant’s act of calling upon Him. The text does not list a certain wording, time, or place. It keeps the message open: make dua, because supplication has a high place with Allah."},"teachings":["Supplication has a noble place with Allah.","Calling upon Allah is an honored act.","Dua should not be treated as unimportant.","The Hadith encourages the servant to ask Allah directly."],"related_hadiths":[{"id":"3372","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3373","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Nobility of Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that nothing is more noble to Allah than sincere supplication."},"heading":{"title":"Nothing More Noble to Allah Than Supplication","description":"This Hadith highlights the honor of dua. The Prophet said there is nothing more noble to Allah than supplication. The Hadith is brief, but it makes the status of dua easy to understand. Supplication is not a weak act or a last choice. It is a noble act in which the servant turns to Allah and asks from Him. For someone searching for the Hadith nothing more noble than dua, the key lesson is that Allah values the servant’s act of calling upon Him. The text does not list a certain wording, time, or place. It keeps the message open: make dua, because supplication has a high place with Allah."},"teachings":["Supplication has a noble place with Allah.","Calling upon Allah is an honored act.","Dua should not be treated as unimportant.","The Hadith encourages the servant to ask Allah directly."],"related_hadiths":[{"id":"3372","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"3373","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr">
@@ -8654,7 +8658,7 @@
       </c>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ablution Together for Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah narrated that she and the Prophet performed wudu together for prayer, showing a clear example of shared ablution."},"heading":{"title":"Aishah Hadith About Performing Wudu Together","description":"This Aishah hadith about performing wudu together is brief, but it carries a clear lesson. The report says that the Prophet and Aishah used to perform ablution together for prayer. The wording links wudu directly with prayer, showing preparation before standing before Allah. It also shows that ablution could be done together in the situation mentioned, without the text adding any further details. For someone searching for Prophet and Aishah wudu together, the safest reading is to stay with the narration itself: they performed wudu together, and the purpose mentioned was prayer. The hadith teaches practical care for purification before salah in a simple household setting."},"teachings":["Wudu is directly connected to preparation for prayer.","The Prophet and Aishah performed ablution together as stated in the report.","The text teaches simplicity in preparing for salah."],"related_hadiths":[{"id":"193","book_id":"1","label":"Sahih Bukhari"},{"id":"376","book_id":"6","label":"Sunan Ibn Majah"},{"id":"401","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ablution Together for Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah narrated that she and the Prophet performed wudu together for prayer, showing a clear example of shared ablution."},"heading":{"title":"Aishah Hadith About Performing Wudu Together","description":"This Aishah hadith about performing wudu together is brief, but it carries a clear lesson. The report says that the Prophet and Aishah used to perform ablution together for prayer. The wording links wudu directly with prayer, showing preparation before standing before Allah. It also shows that ablution could be done together in the situation mentioned, without the text adding any further details. For someone searching for Prophet and Aishah wudu together, the safest reading is to stay with the narration itself: they performed wudu together, and the purpose mentioned was prayer. The hadith teaches practical care for purification before salah in a simple household setting."},"teachings":["Wudu is directly connected to preparation for prayer.","The Prophet and Aishah performed ablution together as stated in the report.","The text teaches simplicity in preparing for salah."],"related_hadiths":[{"id":"193","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"376","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"401","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E356" s="4" t="n"/>
@@ -8677,7 +8681,7 @@
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Dua for Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. A rich prophetic supplication asking Allah for help, guidance, gratitude, repentance, and a sound heart."},"heading":{"title":"Rabbi A’inni Wa La Tu’in Alayya: Prophetic Dua for Guidance","description":"This Hadith gives a long prophetic dua filled with requests for Allah’s help. The Prophet asked Allah for help, support, guidance, and ease in following guidance. He also asked Allah to help him against those who wronged him. The dua then turns to the inner life of the believer: gratitude, remembrance, fear of Allah, obedience, humility, and returning to Him. It also asks for accepted repentance, sins to be washed away, supplication to be answered, the heart to be guided, the tongue to speak truth, proof to be firm, and resentment to be removed from the heart. This makes the Hadith a beautiful dua for guidance, repentance, and a clean heart."},"teachings":["A believer may ask Allah for help, support, and guidance.","The dua teaches gratitude, remembrance, humility, and obedience.","Repentance, forgiveness, and a guided heart are central requests.","The Prophet asked Allah to remove resentment from the heart."],"related_hadiths":[{"id":"2721a","book_id":"2","label":"Sahih Muslim"},{"id":"7464","book_id":"1","label":"Sahih Bukhari"},{"id":"7385","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Dua for Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. A rich prophetic supplication asking Allah for help, guidance, gratitude, repentance, and a sound heart."},"heading":{"title":"Rabbi A’inni Wa La Tu’in Alayya: Prophetic Dua for Guidance","description":"This Hadith gives a long prophetic dua filled with requests for Allah’s help. The Prophet asked Allah for help, support, guidance, and ease in following guidance. He also asked Allah to help him against those who wronged him. The dua then turns to the inner life of the believer: gratitude, remembrance, fear of Allah, obedience, humility, and returning to Him. It also asks for accepted repentance, sins to be washed away, supplication to be answered, the heart to be guided, the tongue to speak truth, proof to be firm, and resentment to be removed from the heart. This makes the Hadith a beautiful dua for guidance, repentance, and a clean heart."},"teachings":["A believer may ask Allah for help, support, and guidance.","The dua teaches gratitude, remembrance, humility, and obedience.","Repentance, forgiveness, and a guided heart are central requests.","The Prophet asked Allah to remove resentment from the heart."],"related_hadiths":[{"id":"2721a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"7464","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7385","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E357" s="4" t="n"/>
@@ -8700,7 +8704,7 @@
       </c>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Debt Relief","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught a powerful dua asking Allah to settle debts and remove need."},"heading":{"title":"Dua to Pay Off Debt and Be Free from Want","description":"This Hadith tells how Fatimah came to the Prophet asking for a servant. He first said he did not have anything to give her. Later, he came to her and asked whether what she requested was dearer to her, or something better than that. She chose what was better, and the Prophet taught her a dua. The supplication begins by praising Allah as Lord of the seven heavens, Lord of the Mighty Throne, Lord of everything, and Revealer of the Tawrah, Injil, and Qur’an. It mentions Allah as the First, the Last, the Most High, and the Most Near. Then it asks Allah to settle debts and make the person free of want."},"teachings":["The Prophet taught dua as something better in this situation.","The dua begins with praise of Allah before asking.","A person may ask Allah to settle debts.","A person may ask Allah to be free from want."],"related_hadiths":[{"id":"6369","book_id":"1","label":"Sahih Bukhari"},{"id":"2397","book_id":"1","label":"Sahih Bukhari"},{"id":"6368","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Debt Relief","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught a powerful dua asking Allah to settle debts and remove need."},"heading":{"title":"Dua to Pay Off Debt and Be Free from Want","description":"This Hadith tells how Fatimah came to the Prophet asking for a servant. He first said he did not have anything to give her. Later, he came to her and asked whether what she requested was dearer to her, or something better than that. She chose what was better, and the Prophet taught her a dua. The supplication begins by praising Allah as Lord of the seven heavens, Lord of the Mighty Throne, Lord of everything, and Revealer of the Tawrah, Injil, and Qur’an. It mentions Allah as the First, the Last, the Most High, and the Most Near. Then it asks Allah to settle debts and make the person free of want."},"teachings":["The Prophet taught dua as something better in this situation.","The dua begins with praise of Allah before asking.","A person may ask Allah to settle debts.","A person may ask Allah to be free from want."],"related_hadiths":[{"id":"6369","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2397","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6368","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E358" s="4" t="n"/>
@@ -8723,7 +8727,7 @@
       </c>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. A short prophetic dua asking Allah for guidance, piety, chastity, and affluence."},"heading":{"title":"Allahumma Inni As’alukal Huda Wat-Tuqa: Dua for Guidance","description":"This Hadith shares a short dua the Prophet used to say. The words ask Allah for four things: guidance, piety, chastity, and affluence. The beauty of this supplication is that it covers both the heart and daily life in a few words. Guidance helps a person know and follow the right way. Piety points to living with awareness of Allah. Chastity asks for purity and self-control. Affluence, as mentioned in the translation, asks Allah for freedom from need. For readers searching for Allahumma inni as’alukal huda wat-tuqa, this Hadith is a simple prophetic dua that can be learned and repeated with clear meaning."},"teachings":["The Prophet asked Allah for guidance.","Piety is a key request in this dua.","The dua includes chastity and self-control.","The Prophet also asked Allah for affluence."],"related_hadiths":[{"id":"2721a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. A short prophetic dua asking Allah for guidance, piety, chastity, and affluence."},"heading":{"title":"Allahumma Inni As’alukal Huda Wat-Tuqa: Dua for Guidance","description":"This Hadith shares a short dua the Prophet used to say. The words ask Allah for four things: guidance, piety, chastity, and affluence. The beauty of this supplication is that it covers both the heart and daily life in a few words. Guidance helps a person know and follow the right way. Piety points to living with awareness of Allah. Chastity asks for purity and self-control. Affluence, as mentioned in the translation, asks Allah for freedom from need. For readers searching for Allahumma inni as’alukal huda wat-tuqa, this Hadith is a simple prophetic dua that can be learned and repeated with clear meaning."},"teachings":["The Prophet asked Allah for guidance.","Piety is a key request in this dua.","The dua includes chastity and self-control.","The Prophet also asked Allah for affluence."],"related_hadiths":[{"id":"2721a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr">
@@ -8750,7 +8754,7 @@
       </c>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Beneficial Knowledge","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asked Allah for beneficial knowledge, more knowledge, gratitude, and safety from the Fire."},"heading":{"title":"Dua for Beneficial Knowledge and Increase in Knowledge","description":"This Hadith teaches a prophetic dua about knowledge. The Prophet asked Allah to benefit him by what He had taught him, to teach him what would benefit him, and to increase him in knowledge. The wording shows that knowledge is not only about having information. The servant asks Allah to make knowledge useful and to give more of what benefits. The dua also includes praise to Allah in every situation and seeking refuge with Allah from the torment of the Fire. For people searching for a dua for beneficial knowledge, this Hadith gives a direct and easy wording. It connects learning, benefit, gratitude, and seeking protection from punishment."},"teachings":["A believer should ask Allah for knowledge that benefits.","Knowledge should be useful, not only memorized.","The Prophet asked Allah to increase him in knowledge.","The dua includes praising Allah in all situations."],"related_hadiths":[{"id":"250","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Beneficial Knowledge","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asked Allah for beneficial knowledge, more knowledge, gratitude, and safety from the Fire."},"heading":{"title":"Dua for Beneficial Knowledge and Increase in Knowledge","description":"This Hadith teaches a prophetic dua about knowledge. The Prophet asked Allah to benefit him by what He had taught him, to teach him what would benefit him, and to increase him in knowledge. The wording shows that knowledge is not only about having information. The servant asks Allah to make knowledge useful and to give more of what benefits. The dua also includes praise to Allah in every situation and seeking refuge with Allah from the torment of the Fire. For people searching for a dua for beneficial knowledge, this Hadith gives a direct and easy wording. It connects learning, benefit, gratitude, and seeking protection from punishment."},"teachings":["A believer should ask Allah for knowledge that benefits.","Knowledge should be useful, not only memorized.","The Prophet asked Allah to increase him in knowledge.","The dua includes praising Allah in all situations."],"related_hadiths":[{"id":"250","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E360" s="4" t="inlineStr">
@@ -8777,7 +8781,7 @@
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Steadfast Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet often asked Allah to keep his heart firm upon the religion."},"heading":{"title":"Allahumma Thabbit Qalbi Ala Dinik: Dua for a Steadfast Heart","description":"This Hadith teaches a short dua the Prophet often used to say: O Allah, make my heart steadfast in Your religion. A man asked why the Prophet feared for them when they had believed in him and accepted the message he brought. The Prophet answered that hearts are between two of the fingers of the Most Merciful, and He controls them. The Hadith points to the need to ask Allah for firmness, even after faith. It does not teach overconfidence. Instead, it teaches humble reliance on Allah. For readers searching for Allahumma thabbit qalbi ala dinik, this narration shows why asking for a steady heart is important."},"teachings":["The Prophet often asked Allah for a firm heart.","Faith should be joined with humble reliance on Allah.","Hearts are under Allah’s control.","A believer should ask Allah to remain steadfast on the religion."],"related_hadiths":[{"id":"3587","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"2564b","book_id":"2","label":"Sahih Muslim"},{"id":"3984","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Steadfast Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet often asked Allah to keep his heart firm upon the religion."},"heading":{"title":"Allahumma Thabbit Qalbi Ala Dinik: Dua for a Steadfast Heart","description":"This Hadith teaches a short dua the Prophet often used to say: O Allah, make my heart steadfast in Your religion. A man asked why the Prophet feared for them when they had believed in him and accepted the message he brought. The Prophet answered that hearts are between two of the fingers of the Most Merciful, and He controls them. The Hadith points to the need to ask Allah for firmness, even after faith. It does not teach overconfidence. Instead, it teaches humble reliance on Allah. For readers searching for Allahumma thabbit qalbi ala dinik, this narration shows why asking for a steady heart is important."},"teachings":["The Prophet often asked Allah for a firm heart.","Faith should be joined with humble reliance on Allah.","Hearts are under Allah’s control.","A believer should ask Allah to remain steadfast on the religion."],"related_hadiths":[{"id":"3587","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"2564b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"3984","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E361" s="4" t="n"/>
@@ -8800,7 +8804,7 @@
       </c>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr was taught a prayer asking Allah for forgiveness and mercy after admitting personal wrong."},"heading":{"title":"Allahumma Inni Zalamtu Nafsi: Dua for Forgiveness in Prayer","description":"This Hadith tells how Abu Bakr asked the Messenger of Allah to teach him a supplication to say during prayer. The Prophet taught him a dua that begins with admitting personal wrong: O Allah, I have wronged myself greatly. The supplication then states that no one forgives sins except Allah. After that, the servant asks for forgiveness from Allah and asks for mercy. The dua ends by calling Allah the Oft-Forgiving, Most Merciful. For readers searching for Allahumma inni zalamtu nafsi, this Hadith gives a clear wording for repentance and humility in prayer. It teaches that asking forgiveness begins with honesty before Allah."},"teachings":["A person may ask for a dua to say during prayer.","The dua begins with admitting one’s own wrong.","Only Allah forgives sins.","The servant asks Allah for forgiveness and mercy."],"related_hadiths":[{"id":"7387","book_id":"1","label":"Sahih Bukhari"},{"id":"7464","book_id":"1","label":"Sahih Bukhari"},{"id":"7385","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr was taught a prayer asking Allah for forgiveness and mercy after admitting personal wrong."},"heading":{"title":"Allahumma Inni Zalamtu Nafsi: Dua for Forgiveness in Prayer","description":"This Hadith tells how Abu Bakr asked the Messenger of Allah to teach him a supplication to say during prayer. The Prophet taught him a dua that begins with admitting personal wrong: O Allah, I have wronged myself greatly. The supplication then states that no one forgives sins except Allah. After that, the servant asks for forgiveness from Allah and asks for mercy. The dua ends by calling Allah the Oft-Forgiving, Most Merciful. For readers searching for Allahumma inni zalamtu nafsi, this Hadith gives a clear wording for repentance and humility in prayer. It teaches that asking forgiveness begins with honesty before Allah."},"teachings":["A person may ask for a dua to say during prayer.","The dua begins with admitting one’s own wrong.","Only Allah forgives sins.","The servant asks Allah for forgiveness and mercy."],"related_hadiths":[{"id":"7387","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7464","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7385","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E362" s="4" t="n"/>
@@ -8823,7 +8827,7 @@
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Complete Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. A broad prophetic dua asking for forgiveness, mercy, acceptance, Paradise, safety, and rectified affairs."},"heading":{"title":"A Complete Dua for Forgiveness, Mercy, and Rectified Affairs","description":"This Hadith contains two clear lessons. First, when the Companions stood as the Prophet came out leaning on a stick, he told them not to do what the Persians do for their leaders. This points to humility and not treating leaders with empty display. Then they asked the Messenger of Allah to pray for them. He made a broad dua: O Allah, forgive us, have mercy on us, be pleased with us, accept from us, admit us to Paradise, save us from the Fire, and rectify all our affairs. When they seemed to want more, he said he had summed everything for them. The dua is short, but it gathers many needs."},"teachings":["The Prophet discouraged standing in the manner mentioned for leaders.","The Companions asked the Prophet to pray for them.","The dua gathers forgiveness, mercy, acceptance, Paradise, and safety from Hell.","Asking Allah to rectify all affairs is a broad and useful request."],"related_hadiths":[{"id":"3372","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"7464","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Complete Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. A broad prophetic dua asking for forgiveness, mercy, acceptance, Paradise, safety, and rectified affairs."},"heading":{"title":"A Complete Dua for Forgiveness, Mercy, and Rectified Affairs","description":"This Hadith contains two clear lessons. First, when the Companions stood as the Prophet came out leaning on a stick, he told them not to do what the Persians do for their leaders. This points to humility and not treating leaders with empty display. Then they asked the Messenger of Allah to pray for them. He made a broad dua: O Allah, forgive us, have mercy on us, be pleased with us, accept from us, admit us to Paradise, save us from the Fire, and rectify all our affairs. When they seemed to want more, he said he had summed everything for them. The dua is short, but it gathers many needs."},"teachings":["The Prophet discouraged standing in the manner mentioned for leaders.","The Companions asked the Prophet to pray for them.","The dua gathers forgiveness, mercy, acceptance, Paradise, and safety from Hell.","Asking Allah to rectify all affairs is a broad and useful request."],"related_hadiths":[{"id":"3372","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"7464","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
@@ -8850,7 +8854,7 @@
       </c>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Refuge from Four Things","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet sought refuge from useless knowledge, a heart without fear, an unsatisfied soul, and unheard dua."},"heading":{"title":"Dua Against Knowledge That Does Not Benefit","description":"This Hadith teaches a supplication seeking refuge from four harmful states. The Prophet asked Allah for protection from knowledge that does not benefit, a heart that does not fear Allah, a soul that is never satisfied, and a supplication that is not heard. The wording shows that not every outward good becomes helpful unless Allah gives benefit and acceptance. Knowledge should guide a person. The heart should have fear of Allah. The soul should not be endless in its wants. Dua should be made in a way that seeks Allah’s hearing and acceptance. For readers searching for the dua against knowledge that does not benefit, this Hadith gives the full meaning in a short form."},"teachings":["Knowledge should be beneficial.","A heart should have fear of Allah.","The soul should not be left in endless dissatisfaction.","A believer may seek refuge from a supplication that is not heard."],"related_hadiths":[{"id":"250","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Refuge from Four Things","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet sought refuge from useless knowledge, a heart without fear, an unsatisfied soul, and unheard dua."},"heading":{"title":"Dua Against Knowledge That Does Not Benefit","description":"This Hadith teaches a supplication seeking refuge from four harmful states. The Prophet asked Allah for protection from knowledge that does not benefit, a heart that does not fear Allah, a soul that is never satisfied, and a supplication that is not heard. The wording shows that not every outward good becomes helpful unless Allah gives benefit and acceptance. Knowledge should guide a person. The heart should have fear of Allah. The soul should not be endless in its wants. Dua should be made in a way that seeks Allah’s hearing and acceptance. For readers searching for the dua against knowledge that does not benefit, this Hadith gives the full meaning in a short form."},"teachings":["Knowledge should be beneficial.","A heart should have fear of Allah.","The soul should not be left in endless dissatisfaction.","A believer may seek refuge from a supplication that is not heard."],"related_hadiths":[{"id":"250","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E364" s="4" t="inlineStr">
@@ -8877,7 +8881,7 @@
       </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Protection from Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. A prophetic dua seeking refuge from trials of Fire, grave, wealth, poverty, Dajjal, sin, debt, and laziness."},"heading":{"title":"Dua for Protection from Trials, Sin, and Debt","description":"This Hadith records a supplication the Prophet used to make. He sought refuge with Allah from the trial and torment of the Fire, the trial and torment of the grave, the evil of the trial of richness and poverty, and the evil of the trial of the False Christ. He then asked Allah to wash away his sins with snow and hail, cleanse his heart from sins like a white garment is cleansed from dirt, and place distance between him and his sins like the distance between east and west. The dua also seeks refuge from laziness, old age, sins, and debt. It is a wide dua for protection and purification."},"teachings":["The Prophet sought refuge from major trials.","The dua asks Allah to cleanse sins and purify the heart.","Both richness and poverty can be trials.","The Prophet sought refuge from laziness, old age, sins, and debt."],"related_hadiths":[{"id":"6368","book_id":"1","label":"Sahih Bukhari"},{"id":"6375","book_id":"1","label":"Sahih Bukhari"},{"id":"589","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Protection from Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. A prophetic dua seeking refuge from trials of Fire, grave, wealth, poverty, Dajjal, sin, debt, and laziness."},"heading":{"title":"Dua for Protection from Trials, Sin, and Debt","description":"This Hadith records a supplication the Prophet used to make. He sought refuge with Allah from the trial and torment of the Fire, the trial and torment of the grave, the evil of the trial of richness and poverty, and the evil of the trial of the False Christ. He then asked Allah to wash away his sins with snow and hail, cleanse his heart from sins like a white garment is cleansed from dirt, and place distance between him and his sins like the distance between east and west. The dua also seeks refuge from laziness, old age, sins, and debt. It is a wide dua for protection and purification."},"teachings":["The Prophet sought refuge from major trials.","The dua asks Allah to cleanse sins and purify the heart.","Both richness and poverty can be trials.","The Prophet sought refuge from laziness, old age, sins, and debt."],"related_hadiths":[{"id":"6368","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6375","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"589","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E365" s="4" t="n"/>
@@ -8900,7 +8904,7 @@
       </c>
       <c r="D366" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Refuge from Evil","description":"$book_name$ $hadith_number$ - $chapter_name$. A short prophetic dua seeking Allah’s protection from the evil of what one has done and not done."},"heading":{"title":"Dua from the Evil of What I Have Done and Not Done","description":"This Hadith gives a short supplication reported by Aishah. Farwah bin Nawfal asked her about a dua that the Messenger of Allah used to say. She replied that he used to say: O Allah, I seek refuge with You from the evil of what I have done and the evil of what I have not done. The wording is brief, but it covers a wide concern. A person asks Allah for protection from the harm tied to past actions and from harm linked to what has not yet happened or has not yet been done. For readers searching for this prophetic dua, the lesson is simple: ask Allah for protection from evil in every direction."},"teachings":["The Prophet used to seek refuge with Allah from evil.","The dua includes the evil of past actions.","The dua also includes the evil of what has not been done.","A short supplication can cover a wide need for protection."],"related_hadiths":[{"id":"6368","book_id":"1","label":"Sahih Bukhari"},{"id":"2823","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Refuge from Evil","description":"$book_name$ $hadith_number$ - $chapter_name$. A short prophetic dua seeking Allah’s protection from the evil of what one has done and not done."},"heading":{"title":"Dua from the Evil of What I Have Done and Not Done","description":"This Hadith gives a short supplication reported by Aishah. Farwah bin Nawfal asked her about a dua that the Messenger of Allah used to say. She replied that he used to say: O Allah, I seek refuge with You from the evil of what I have done and the evil of what I have not done. The wording is brief, but it covers a wide concern. A person asks Allah for protection from the harm tied to past actions and from harm linked to what has not yet happened or has not yet been done. For readers searching for this prophetic dua, the lesson is simple: ask Allah for protection from evil in every direction."},"teachings":["The Prophet used to seek refuge with Allah from evil.","The dua includes the evil of past actions.","The dua also includes the evil of what has not been done.","A short supplication can cover a wide need for protection."],"related_hadiths":[{"id":"6368","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2823","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E366" s="4" t="inlineStr">
@@ -8927,7 +8931,7 @@
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu with Nabidh Water","description":"$book_name$ $hadith_number$ - $chapter_name$. On the night of the jinn, the Prophet used nabidh described as good dates and pure water for ablution."},"heading":{"title":"Hadith About Wudu with Nabidh Water","description":"This hadith about wudu with nabidh water describes a specific moment on the night of the jinn. The Messenger of Allah asked Abdullah bin Masud if he had water for ablution. Ibn Masud said he only had some nabidh in a vessel. The Prophet described it as good dates and pure water, and the narration says he performed ablution with it. The explanation should stay close to that wording. The text presents nabidh here as water mixed with dates, and the translation itself clarifies that there was no harm from the mixing of the two. It does not open a general discussion about every drink or every condition. The core point is ablution with the available pure water mixture mentioned in the report."},"teachings":["The Prophet asked for water before performing ablution.","The nabidh in this report is described as good dates and pure water.","The narration shows use of available water for wudu in that specific case."],"related_hadiths":[{"id":"84","book_id":"4","label":"Sunan Abu Dawud"},{"id":"450a","book_id":"2","label":"Sahih Muslim"},{"id":"85","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu with Nabidh Water","description":"$book_name$ $hadith_number$ - $chapter_name$. On the night of the jinn, the Prophet used nabidh described as good dates and pure water for ablution."},"heading":{"title":"Hadith About Wudu with Nabidh Water","description":"This hadith about wudu with nabidh water describes a specific moment on the night of the jinn. The Messenger of Allah asked Abdullah bin Masud if he had water for ablution. Ibn Masud said he only had some nabidh in a vessel. The Prophet described it as good dates and pure water, and the narration says he performed ablution with it. The explanation should stay close to that wording. The text presents nabidh here as water mixed with dates, and the translation itself clarifies that there was no harm from the mixing of the two. It does not open a general discussion about every drink or every condition. The core point is ablution with the available pure water mixture mentioned in the report."},"teachings":["The Prophet asked for water before performing ablution.","The nabidh in this report is described as good dates and pure water.","The narration shows use of available water for wudu in that specific case."],"related_hadiths":[{"id":"84","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"450a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"85","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E367" s="4" t="n"/>
@@ -8950,7 +8954,7 @@
       </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Refuge from Major Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught this dua like a Surah, seeking refuge from Hell, the grave, Dajjal, and life and death trials."},"heading":{"title":"Dua for Protection from Hell, the Grave, Dajjal, and Trials","description":"This Hadith shows the importance of a specific supplication. Ibn Abbas said the Messenger of Allah used to teach them this dua just as he would teach them a Surah from the Qur’an. The dua seeks refuge with Allah from the torment of Hell, the torment of the grave, the trial of the False Christ, and the trials of life and death. The way it was taught shows that these words were treated with care and attention. For readers searching for the dua protection from Hell and grave, this Hadith gives a clear prophetic wording. It teaches the believer to ask Allah for safety from serious trials seen and unseen."},"teachings":["The Prophet taught this supplication with great care.","The dua seeks refuge from the torment of Hell.","The dua seeks refuge from the torment of the grave.","The dua includes protection from Dajjal and the trials of life and death."],"related_hadiths":[{"id":"589","book_id":"2","label":"Sahih Muslim"},{"id":"6368","book_id":"1","label":"Sahih Bukhari"},{"id":"6375","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Refuge from Major Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught this dua like a Surah, seeking refuge from Hell, the grave, Dajjal, and life and death trials."},"heading":{"title":"Dua for Protection from Hell, the Grave, Dajjal, and Trials","description":"This Hadith shows the importance of a specific supplication. Ibn Abbas said the Messenger of Allah used to teach them this dua just as he would teach them a Surah from the Qur’an. The dua seeks refuge with Allah from the torment of Hell, the torment of the grave, the trial of the False Christ, and the trials of life and death. The way it was taught shows that these words were treated with care and attention. For readers searching for the dua protection from Hell and grave, this Hadith gives a clear prophetic wording. It teaches the believer to ask Allah for safety from serious trials seen and unseen."},"teachings":["The Prophet taught this supplication with great care.","The dua seeks refuge from the torment of Hell.","The dua seeks refuge from the torment of the grave.","The dua includes protection from Dajjal and the trials of life and death."],"related_hadiths":[{"id":"589","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"6368","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6375","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E368" s="4" t="n"/>
@@ -8973,7 +8977,7 @@
       </c>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua in Sujood and Praising Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn a heartfelt dua in sujood seeking Allah’s pleasure, forgiveness, and protection from His wrath."},"heading":{"title":"Dua in Sujood: Seeking Allah’s Pleasure and Forgiveness","description":"This Hadith teaches a powerful dua in sujood. Aishah noticed that the Messenger of Allah was not in bed, then found him in the Masjid while he was prostrating. His words show deep humility before Allah. The main lesson is that a servant seeks safety with Allah alone: from His wrath through His pleasure, from His punishment through His forgiveness, and from Allah through Allah. The phrase “I cannot praise You enough” teaches that Allah’s greatness is beyond full human praise. This dua in sujood is simple in wording but very deep in meaning. It reminds the believer to ask Allah with respect, need, and honest love."},"teachings":["Sujood is a place for humble supplication to Allah.","A believer seeks Allah’s pleasure and forgiveness.","No human praise can fully cover Allah’s greatness.","The Prophet’s supplication shows deep need before Allah."],"related_hadiths":[{"id":"486a","book_id":"2","label":"Sahih Muslim"},{"id":"817","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua in Sujood and Praising Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn a heartfelt dua in sujood seeking Allah’s pleasure, forgiveness, and protection from His wrath."},"heading":{"title":"Dua in Sujood: Seeking Allah’s Pleasure and Forgiveness","description":"This Hadith teaches a powerful dua in sujood. Aishah noticed that the Messenger of Allah was not in bed, then found him in the Masjid while he was prostrating. His words show deep humility before Allah. The main lesson is that a servant seeks safety with Allah alone: from His wrath through His pleasure, from His punishment through His forgiveness, and from Allah through Allah. The phrase “I cannot praise You enough” teaches that Allah’s greatness is beyond full human praise. This dua in sujood is simple in wording but very deep in meaning. It reminds the believer to ask Allah with respect, need, and honest love."},"teachings":["Sujood is a place for humble supplication to Allah.","A believer seeks Allah’s pleasure and forgiveness.","No human praise can fully cover Allah’s greatness.","The Prophet’s supplication shows deep need before Allah."],"related_hadiths":[{"id":"486a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"817","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E369" s="4" t="n"/>
@@ -8996,7 +9000,7 @@
       </c>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Refuge from Poverty and Wrongdoing","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear dua asking Allah for protection from poverty, humiliation, injustice, and being wronged."},"heading":{"title":"Seek Refuge with Allah from Poverty, Humiliation, and Injustice","description":"This Hadith gives a short and direct dua for protection. The Messenger of Allah taught believers to seek refuge with Allah from poverty, insufficiency, and humiliation. He also taught them to seek protection from wronging others and from being wronged. The core topic is seeking refuge with Allah in matters that can harm faith, dignity, and relationships. The wording keeps both sides in view: a person should not be an oppressor, and should also ask Allah for safety from oppression. This makes the dua balanced and honest. It is not only about personal comfort; it is also about staying away from injustice toward other people."},"teachings":["Ask Allah for protection from hardship and humiliation.","Avoid wronging others in words or actions.","Seek Allah’s help when fearing injustice.","A good dua includes care for both self and others."],"related_hadiths":[{"id":"6347","book_id":"1","label":"Sahih Bukhari"},{"id":"2707","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Refuge from Poverty and Wrongdoing","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear dua asking Allah for protection from poverty, humiliation, injustice, and being wronged."},"heading":{"title":"Seek Refuge with Allah from Poverty, Humiliation, and Injustice","description":"This Hadith gives a short and direct dua for protection. The Messenger of Allah taught believers to seek refuge with Allah from poverty, insufficiency, and humiliation. He also taught them to seek protection from wronging others and from being wronged. The core topic is seeking refuge with Allah in matters that can harm faith, dignity, and relationships. The wording keeps both sides in view: a person should not be an oppressor, and should also ask Allah for safety from oppression. This makes the dua balanced and honest. It is not only about personal comfort; it is also about staying away from injustice toward other people."},"teachings":["Ask Allah for protection from hardship and humiliation.","Avoid wronging others in words or actions.","Seek Allah’s help when fearing injustice.","A good dua includes care for both self and others."],"related_hadiths":[{"id":"6347","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2707","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E370" s="4" t="n"/>
@@ -9019,7 +9023,7 @@
       </c>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Protection from Cowardice and Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. A supplication seeking Allah’s refuge from cowardice, miserliness, old age, grave punishment, and heart trials."},"heading":{"title":"Seeking Refuge from Cowardice, Miserliness, and Trials of the Heart","description":"This Hadith mentions matters from which the Prophet used to seek refuge with Allah. They include cowardice, miserliness, old age, the torment of the grave, and the tribulation of the heart. The narration also includes Waki’s explanation that the tribulation of the heart means a person dying upon a state of fitnah without seeking Allah’s forgiveness. The core topic is protection through dua. The wording shows that a believer should care about inner weakness as well as outer hardship. Cowardice and miserliness affect behavior, while the tribulation of the heart affects a person’s state before Allah. The Hadith points the heart back to Allah for safety."},"teachings":["Seek Allah’s refuge from harmful traits like cowardice and miserliness.","Ask Allah for safety from grave punishment.","The state of the heart matters deeply.","Seeking forgiveness is important before death."],"related_hadiths":[{"id":"5447","book_id":"3","label":"Sunan an-Nasai"},{"id":"6365","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Protection from Cowardice and Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. A supplication seeking Allah’s refuge from cowardice, miserliness, old age, grave punishment, and heart trials."},"heading":{"title":"Seeking Refuge from Cowardice, Miserliness, and Trials of the Heart","description":"This Hadith mentions matters from which the Prophet used to seek refuge with Allah. They include cowardice, miserliness, old age, the torment of the grave, and the tribulation of the heart. The narration also includes Waki’s explanation that the tribulation of the heart means a person dying upon a state of fitnah without seeking Allah’s forgiveness. The core topic is protection through dua. The wording shows that a believer should care about inner weakness as well as outer hardship. Cowardice and miserliness affect behavior, while the tribulation of the heart affects a person’s state before Allah. The Hadith points the heart back to Allah for safety."},"teachings":["Seek Allah’s refuge from harmful traits like cowardice and miserliness.","Ask Allah for safety from grave punishment.","The state of the heart matters deeply.","Seeking forgiveness is important before death."],"related_hadiths":[{"id":"5447","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"6365","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E371" s="4" t="n"/>
@@ -9042,7 +9046,7 @@
       </c>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Comprehensive Dua for All Good","description":"$book_name$ $hadith_number$ - $chapter_name$. A wide supplication asking Allah for all good, protection from all evil, Paradise, and a good decree."},"heading":{"title":"Comprehensive Dua for All Good in This World and the Hereafter","description":"This Hadith contains a broad supplication taught to Aishah. It asks Allah for all good, both immediate and later, known and unknown. It also seeks refuge from all evil, immediate and later, known and unknown. The dua then asks for the good that Allah’s slave and Prophet asked for, and seeks protection from the evil from which he sought protection. It includes asking for Paradise and for words and deeds that bring one closer to it. It also seeks refuge from Hell and from words and deeds that bring one closer to it. The ending asks Allah to make every decree concerning the person good."},"teachings":["Ask Allah for good that you know and do not know.","Seek Allah’s protection from evil that you know and do not know.","Paradise is sought along with words and deeds that lead toward it.","A believer asks Allah to make His decree good for them."],"related_hadiths":[{"id":"6306","book_id":"1","label":"Sahih Bukhari"},{"id":"3832","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Comprehensive Dua for All Good","description":"$book_name$ $hadith_number$ - $chapter_name$. A wide supplication asking Allah for all good, protection from all evil, Paradise, and a good decree."},"heading":{"title":"Comprehensive Dua for All Good in This World and the Hereafter","description":"This Hadith contains a broad supplication taught to Aishah. It asks Allah for all good, both immediate and later, known and unknown. It also seeks refuge from all evil, immediate and later, known and unknown. The dua then asks for the good that Allah’s slave and Prophet asked for, and seeks protection from the evil from which he sought protection. It includes asking for Paradise and for words and deeds that bring one closer to it. It also seeks refuge from Hell and from words and deeds that bring one closer to it. The ending asks Allah to make every decree concerning the person good."},"teachings":["Ask Allah for good that you know and do not know.","Seek Allah’s protection from evil that you know and do not know.","Paradise is sought along with words and deeds that lead toward it.","A believer asks Allah to make His decree good for them."],"related_hadiths":[{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3832","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E372" s="4" t="n"/>
@@ -9065,7 +9069,7 @@
       </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Asking for Paradise in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. A simple prayer focus: ask Allah for Paradise and seek His refuge from Hell during salah."},"heading":{"title":"Asking for Paradise and Seeking Refuge from Hell in Prayer","description":"This Hadith shows that a simple dua in prayer can still carry the heart of the matter. The Messenger of Allah asked a man what he said during prayer. The man replied that after Tashahhud he asked Allah for Paradise and sought refuge from Hell. He also said that he did not understand the whispering of the Prophet or Muadh. The Prophet answered that their whispering was about those same two things: Paradise and Hell. The core teaching is clear. The believer should ask Allah for Paradise and seek safety from Hell. The Hadith also comforts people who may use simple words in dua when the meaning is sound."},"teachings":["Asking for Paradise is a clear and worthy dua.","Seeking refuge from Hell is part of serious supplication.","Simple words can carry deep meaning in prayer.","The focus of dua should point toward the Hereafter."],"related_hadiths":[{"id":"589","book_id":"2","label":"Sahih Muslim"},{"id":"832","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Asking for Paradise in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. A simple prayer focus: ask Allah for Paradise and seek His refuge from Hell during salah."},"heading":{"title":"Asking for Paradise and Seeking Refuge from Hell in Prayer","description":"This Hadith shows that a simple dua in prayer can still carry the heart of the matter. The Messenger of Allah asked a man what he said during prayer. The man replied that after Tashahhud he asked Allah for Paradise and sought refuge from Hell. He also said that he did not understand the whispering of the Prophet or Muadh. The Prophet answered that their whispering was about those same two things: Paradise and Hell. The core teaching is clear. The believer should ask Allah for Paradise and seek safety from Hell. The Hadith also comforts people who may use simple words in dua when the meaning is sound."},"teachings":["Asking for Paradise is a clear and worthy dua.","Seeking refuge from Hell is part of serious supplication.","Simple words can carry deep meaning in prayer.","The focus of dua should point toward the Hereafter."],"related_hadiths":[{"id":"589","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"832","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E373" s="4" t="n"/>
@@ -9088,7 +9092,7 @@
       </c>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Dua for Forgiveness and Safety","description":"$book_name$ $hadith_number$ - $chapter_name$. The best supplication is to ask Allah for forgiveness and safety in this world and the Hereafter."},"heading":{"title":"Best Dua for Forgiveness and Safety in This World and the Hereafter","description":"This Hadith repeats one answer three times, which makes its message easy to remember. A man asked the Prophet which supplication is best. The Prophet told him to ask his Lord for forgiveness and to be kept safe and sound in this world and in the Hereafter. The man came again the next day and the third day, and the Prophet gave the same answer. On the third day, he added that if a person is forgiven and kept safe and sound in this world and the Hereafter, he has succeeded. The core topic is forgiveness and well-being. This dua joins spiritual need with safety in both lives."},"teachings":["Forgiveness is one of the best things to ask from Allah.","Safety and well-being are also important in dua.","The same important dua may be repeated often.","Success is tied to forgiveness and safety in both lives."],"related_hadiths":[{"id":"1747","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6306","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Dua for Forgiveness and Safety","description":"$book_name$ $hadith_number$ - $chapter_name$. The best supplication is to ask Allah for forgiveness and safety in this world and the Hereafter."},"heading":{"title":"Best Dua for Forgiveness and Safety in This World and the Hereafter","description":"This Hadith repeats one answer three times, which makes its message easy to remember. A man asked the Prophet which supplication is best. The Prophet told him to ask his Lord for forgiveness and to be kept safe and sound in this world and in the Hereafter. The man came again the next day and the third day, and the Prophet gave the same answer. On the third day, he added that if a person is forgiven and kept safe and sound in this world and the Hereafter, he has succeeded. The core topic is forgiveness and well-being. This dua joins spiritual need with safety in both lives."},"teachings":["Forgiveness is one of the best things to ask from Allah.","Safety and well-being are also important in dua.","The same important dua may be repeated often.","Success is tied to forgiveness and safety in both lives."],"related_hadiths":[{"id":"1747","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E374" s="4" t="n"/>
@@ -9111,7 +9115,7 @@
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Truthfulness and Brotherhood","description":"$book_name$ $hadith_number$ - $chapter_name$. Hold to truth, avoid lying, ask Allah for well-being, and live as brothers without envy or hatred."},"heading":{"title":"Truthfulness, Mu'afah, and Muslim Brotherhood","description":"This Hadith brings together personal truth and social peace. Abu Bakr said that the Messenger of Allah had stood in that place the year before, then he wept and shared the teaching. The Prophet said to adhere to truth, because truth comes with righteousness and they lead to Paradise. He warned against lying, because lying comes with immorality and they lead to Hell. He also told people to ask Allah for Al-Mu'afah, saying that after certainty, no one is given anything better than Mu'afah. The Hadith then moves to relationships: do not envy, hate, sever ties, or turn away from one another. Be brothers as slaves of Allah."},"teachings":["Truth is tied to righteousness.","Lying is tied to immorality.","Ask Allah for Mu'afah after certainty.","Avoid envy, hatred, broken ties, and turning away."],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2607a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Truthfulness and Brotherhood","description":"$book_name$ $hadith_number$ - $chapter_name$. Hold to truth, avoid lying, ask Allah for well-being, and live as brothers without envy or hatred."},"heading":{"title":"Truthfulness, Mu'afah, and Muslim Brotherhood","description":"This Hadith brings together personal truth and social peace. Abu Bakr said that the Messenger of Allah had stood in that place the year before, then he wept and shared the teaching. The Prophet said to adhere to truth, because truth comes with righteousness and they lead to Paradise. He warned against lying, because lying comes with immorality and they lead to Hell. He also told people to ask Allah for Al-Mu'afah, saying that after certainty, no one is given anything better than Mu'afah. The Hadith then moves to relationships: do not envy, hate, sever ties, or turn away from one another. Be brothers as slaves of Allah."},"teachings":["Truth is tied to righteousness.","Lying is tied to immorality.","Ask Allah for Mu'afah after certainty.","Avoid envy, hatred, broken ties, and turning away."],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2607a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E375" s="4" t="n"/>
@@ -9134,7 +9138,7 @@
       </c>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pure Water Mixed with Dates","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet called the nabidh good dates and pure water, then had it poured for him and performed ablution with it."},"heading":{"title":"Hadith on Nabidh and Pure Water for Wudu","description":"This hadith on nabidh and pure water for wudu repeats the same main idea through another narration. On the night of the jinn, the Messenger of Allah asked Ibn Masud whether he had water. Ibn Masud said he had only nabidh in a large water skin. The Prophet replied, good dates and pure water, then told him to pour it. The report then says that ablution was performed with it. The wording matters here because the translation explains the meaning as no harm from mixing the two. So the hadith should be understood around that clear point: the liquid mentioned was connected to dates and pure water, and it was used for ablution in that narrated case."},"teachings":["The Prophet asked about water before wudu.","The mixture is described in the hadith as good dates and pure water.","The narration shows the water was poured for ablution."],"related_hadiths":[{"id":"84","book_id":"4","label":"Sunan Abu Dawud"},{"id":"450a","book_id":"2","label":"Sahih Muslim"},{"id":"85","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pure Water Mixed with Dates","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet called the nabidh good dates and pure water, then had it poured for him and performed ablution with it."},"heading":{"title":"Hadith on Nabidh and Pure Water for Wudu","description":"This hadith on nabidh and pure water for wudu repeats the same main idea through another narration. On the night of the jinn, the Messenger of Allah asked Ibn Masud whether he had water. Ibn Masud said he had only nabidh in a large water skin. The Prophet replied, good dates and pure water, then told him to pour it. The report then says that ablution was performed with it. The wording matters here because the translation explains the meaning as no harm from mixing the two. So the hadith should be understood around that clear point: the liquid mentioned was connected to dates and pure water, and it was used for ablution in that narrated case."},"teachings":["The Prophet asked about water before wudu.","The mixture is described in the hadith as good dates and pure water.","The narration shows the water was poured for ablution."],"related_hadiths":[{"id":"84","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"450a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"85","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E376" s="4" t="n"/>
@@ -9157,7 +9161,7 @@
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Laylatul Qadr Dua for Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Aishah to ask Allah’s pardon on Laylatul Qadr with a short, beloved dua."},"heading":{"title":"Laylatul Qadr Dua: Allahumma Innaka Afuwwun","description":"This Hadith gives the well-known Laylatul Qadr dua. Aishah asked the Messenger of Allah what she should say if she came upon Laylatul Qadr. He told her to say: “O Allah, You are Forgiving and love forgiveness, so forgive me.” The wording is short, clear, and full of need. The core topic is forgiveness on Laylatul Qadr. The dua begins by praising Allah as Al-Afuww, the Forgiving, then mentions that Allah loves forgiveness, then asks directly for pardon. The Hadith does not add a long list of requests. It teaches that on a blessed night, a servant should turn to Allah and ask for His forgiveness with humility."},"teachings":["Ask Allah for forgiveness on Laylatul Qadr.","Use Allah’s beautiful attribute Al-Afuww in dua.","A short dua can be very meaningful.","The Prophet taught Aishah a clear supplication for this night."],"related_hadiths":[{"id":"3513","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"2017","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Laylatul Qadr Dua for Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Aishah to ask Allah’s pardon on Laylatul Qadr with a short, beloved dua."},"heading":{"title":"Laylatul Qadr Dua: Allahumma Innaka Afuwwun","description":"This Hadith gives the well-known Laylatul Qadr dua. Aishah asked the Messenger of Allah what she should say if she came upon Laylatul Qadr. He told her to say: “O Allah, You are Forgiving and love forgiveness, so forgive me.” The wording is short, clear, and full of need. The core topic is forgiveness on Laylatul Qadr. The dua begins by praising Allah as Al-Afuww, the Forgiving, then mentions that Allah loves forgiveness, then asks directly for pardon. The Hadith does not add a long list of requests. It teaches that on a blessed night, a servant should turn to Allah and ask for His forgiveness with humility."},"teachings":["Ask Allah for forgiveness on Laylatul Qadr.","Use Allah’s beautiful attribute Al-Afuww in dua.","A short dua can be very meaningful.","The Prophet taught Aishah a clear supplication for this night."],"related_hadiths":[{"id":"3513","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"2017","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E377" s="4" t="n"/>
@@ -9180,7 +9184,7 @@
       </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mu'afah Dua in Dunya and Akhirah","description":"$book_name$ $hadith_number$ - $chapter_name$. A person can ask no better supplication than Mu'afah in this world and the Hereafter."},"heading":{"title":"Mu'afah Dua: Asking Allah for Well-Being in Dunya and Akhirah","description":"This Hadith gives one short dua and describes its great value. The Messenger of Allah said that there is no supplication a person can say that is better than asking Allah for Al-Mu'afah in this world and in the Hereafter. The core topic is well-being and safety from harm. The wording covers both lives, not only comfort in the present. It teaches the believer to ask Allah for protection, ease, and soundness in a wide way. The Hadith does not list every detail of Mu'afah, so the explanation should stay broad. The main point is to make this dua often and to remember both dunya and akhirah when asking Allah."},"teachings":["Ask Allah for Mu'afah in this world and the Hereafter.","Short supplications can carry wide meaning.","A believer should remember both lives in dua.","Well-being is a blessing to ask from Allah."],"related_hadiths":[{"id":"1747","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6306","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mu'afah Dua in Dunya and Akhirah","description":"$book_name$ $hadith_number$ - $chapter_name$. A person can ask no better supplication than Mu'afah in this world and the Hereafter."},"heading":{"title":"Mu'afah Dua: Asking Allah for Well-Being in Dunya and Akhirah","description":"This Hadith gives one short dua and describes its great value. The Messenger of Allah said that there is no supplication a person can say that is better than asking Allah for Al-Mu'afah in this world and in the Hereafter. The core topic is well-being and safety from harm. The wording covers both lives, not only comfort in the present. It teaches the believer to ask Allah for protection, ease, and soundness in a wide way. The Hadith does not list every detail of Mu'afah, so the explanation should stay broad. The main point is to make this dua often and to remember both dunya and akhirah when asking Allah."},"teachings":["Ask Allah for Mu'afah in this world and the Hereafter.","Short supplications can carry wide meaning.","A believer should remember both lives in dua.","Well-being is a blessing to ask from Allah."],"related_hadiths":[{"id":"1747","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"6306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E378" s="4" t="n"/>
@@ -9203,7 +9207,7 @@
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mercy for Prophet Hud","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet made a mercy-filled statement for himself, the believers, and his brother of 'Ad."},"heading":{"title":"Mercy for Prophet Hud: “May Allah Have Mercy on Us and Our Brother of 'Ad”","description":"This Hadith is short, but its wording is gentle. Ibn Abbas narrated that the Messenger of Allah said: “May Allah have mercy on us and on our brother of 'Ad.” The translation explains that the brother of 'Ad refers to Prophet Hud, peace be upon him. The core topic is mercy. The Prophet included “us” and “our brother of 'Ad” in a prayer for Allah’s mercy. The Hadith does not give a long story here, so the meaning should stay close to the text. It shows a way of speaking about a prophet with brotherhood and mercy. It also reminds the reader that mercy is something to ask from Allah."},"teachings":["Ask Allah for mercy.","Speak about prophets with respect.","The Prophet referred to Hud as a brother of 'Ad.","Short statements of mercy can carry a warm meaning."],"related_hadiths":[{"id":"3375","book_id":"1","label":"Sahih Bukhari"},{"id":"151","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mercy for Prophet Hud","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet made a mercy-filled statement for himself, the believers, and his brother of 'Ad."},"heading":{"title":"Mercy for Prophet Hud: “May Allah Have Mercy on Us and Our Brother of 'Ad”","description":"This Hadith is short, but its wording is gentle. Ibn Abbas narrated that the Messenger of Allah said: “May Allah have mercy on us and on our brother of 'Ad.” The translation explains that the brother of 'Ad refers to Prophet Hud, peace be upon him. The core topic is mercy. The Prophet included “us” and “our brother of 'Ad” in a prayer for Allah’s mercy. The Hadith does not give a long story here, so the meaning should stay close to the text. It shows a way of speaking about a prophet with brotherhood and mercy. It also reminds the reader that mercy is something to ask from Allah."},"teachings":["Ask Allah for mercy.","Speak about prophets with respect.","The Prophet referred to Hud as a brother of 'Ad.","Short statements of mercy can carry a warm meaning."],"related_hadiths":[{"id":"3375","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"151","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E379" s="4" t="n"/>
@@ -9226,7 +9230,7 @@
       </c>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ism al-Azam in Three Surahs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Greatest Name of Allah is mentioned as being in Al-Baqarah, Al Imran, and Ta-Ha."},"heading":{"title":"Ism al-Azam in Al-Baqarah, Al Imran, and Ta-Ha","description":"This Hadith mentions that the Greatest Name of Allah, by which He responds when called upon, is in three Surahs: Al-Baqarah, Al Imran, and Ta-Ha. The narration also mentions another chain with something similar from Abu Umamah from the Prophet. The core topic is Ism al-Azam. The safe explanation is to stay with what the Hadith says: it points to these three Surahs and connects the Greatest Name with calling upon Allah. It does not require guessing a single exact word in this explanation. The Hadith encourages careful attention to Allah’s names and to the Quranic passages where they appear, especially when making dua."},"teachings":["The Hadith points to Allah’s Greatest Name in three Surahs.","Calling upon Allah by His names is part of supplication.","The narration connects Ism al-Azam with Allah’s response.","Avoid guessing beyond the wording of the Hadith."],"related_hadiths":[{"id":"3475","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1495","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ism al-Azam in Three Surahs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Greatest Name of Allah is mentioned as being in Al-Baqarah, Al Imran, and Ta-Ha."},"heading":{"title":"Ism al-Azam in Al-Baqarah, Al Imran, and Ta-Ha","description":"This Hadith mentions that the Greatest Name of Allah, by which He responds when called upon, is in three Surahs: Al-Baqarah, Al Imran, and Ta-Ha. The narration also mentions another chain with something similar from Abu Umamah from the Prophet. The core topic is Ism al-Azam. The safe explanation is to stay with what the Hadith says: it points to these three Surahs and connects the Greatest Name with calling upon Allah. It does not require guessing a single exact word in this explanation. The Hadith encourages careful attention to Allah’s names and to the Quranic passages where they appear, especially when making dua."},"teachings":["The Hadith points to Allah’s Greatest Name in three Surahs.","Calling upon Allah by His names is part of supplication.","The narration connects Ism al-Azam with Allah’s response.","Avoid guessing beyond the wording of the Hadith."],"related_hadiths":[{"id":"3475","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1495","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E380" s="4" t="n"/>
@@ -9249,7 +9253,7 @@
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Asking by Allah the One","description":"$book_name$ $hadith_number$ - $chapter_name$. A man asked Allah by His oneness, and the Prophet said he asked by Allah’s Greatest Name."},"heading":{"title":"Asking Allah by His Oneness: A Dua Linked to Ism al-Azam","description":"This Hadith describes a man making dua by affirming Allah as the One, the Self-Sufficient Master, who does not beget, was not begotten, and has no equal. The Prophet heard him and said that he had asked Allah by His Greatest Name, which, if Allah is asked by it, He gives, and if called upon by it, He answers. The core topic is tawhid in dua. The wording shows that praise and belief in Allah’s oneness can be part of supplication. The explanation should stay close to the text: this specific wording was praised by the Prophet as asking by Allah’s Greatest Name. It is a strong reminder to begin dua with clear faith."},"teachings":["Affirm Allah’s oneness when making dua.","The man’s wording was praised by the Prophet.","Allah has no equal or comparable one.","Supplication can include praise before asking."],"related_hadiths":[{"id":"3475","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1493","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Asking by Allah the One","description":"$book_name$ $hadith_number$ - $chapter_name$. A man asked Allah by His oneness, and the Prophet said he asked by Allah’s Greatest Name."},"heading":{"title":"Asking Allah by His Oneness: A Dua Linked to Ism al-Azam","description":"This Hadith describes a man making dua by affirming Allah as the One, the Self-Sufficient Master, who does not beget, was not begotten, and has no equal. The Prophet heard him and said that he had asked Allah by His Greatest Name, which, if Allah is asked by it, He gives, and if called upon by it, He answers. The core topic is tawhid in dua. The wording shows that praise and belief in Allah’s oneness can be part of supplication. The explanation should stay close to the text: this specific wording was praised by the Prophet as asking by Allah’s Greatest Name. It is a strong reminder to begin dua with clear faith."},"teachings":["Affirm Allah’s oneness when making dua.","The man’s wording was praised by the Prophet.","Allah has no equal or comparable one.","Supplication can include praise before asking."],"related_hadiths":[{"id":"3475","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1493","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E381" s="4" t="n"/>
@@ -9272,7 +9276,7 @@
       </c>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua with Al-Mannan and Dhul-Jalal","description":"$book_name$ $hadith_number$ - $chapter_name$. A dua praising Allah as Al-Mannan and Creator was called a supplication by His Greatest Name."},"heading":{"title":"Dua with Al-Mannan, Creator of the Heavens and Earth","description":"This Hadith tells of a man who called upon Allah with praise. He said that all praise belongs to Allah, that none has the right to be worshiped but Him alone, with no partner. He called Allah Al-Mannan, the Bestower, the Originator of the heavens and the earth, and the Possessor of majesty and honor. The Prophet said the man had asked Allah by His Greatest Name. The core topic is praising Allah in dua. The Hadith shows that supplication is not only a request; it can begin with deep praise, tawhid, and Allah’s names. This makes the dua rich in meaning while staying fully centered on Allah."},"teachings":["Begin dua with praise of Allah.","Affirm that Allah alone has the right to be worshiped.","Use Allah’s names in supplication.","The Prophet praised this wording as linked to the Greatest Name."],"related_hadiths":[{"id":"1495","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3544","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua with Al-Mannan and Dhul-Jalal","description":"$book_name$ $hadith_number$ - $chapter_name$. A dua praising Allah as Al-Mannan and Creator was called a supplication by His Greatest Name."},"heading":{"title":"Dua with Al-Mannan, Creator of the Heavens and Earth","description":"This Hadith tells of a man who called upon Allah with praise. He said that all praise belongs to Allah, that none has the right to be worshiped but Him alone, with no partner. He called Allah Al-Mannan, the Bestower, the Originator of the heavens and the earth, and the Possessor of majesty and honor. The Prophet said the man had asked Allah by His Greatest Name. The core topic is praising Allah in dua. The Hadith shows that supplication is not only a request; it can begin with deep praise, tawhid, and Allah’s names. This makes the dua rich in meaning while staying fully centered on Allah."},"teachings":["Begin dua with praise of Allah.","Affirm that Allah alone has the right to be worshiped.","Use Allah’s names in supplication.","The Prophet praised this wording as linked to the Greatest Name."],"related_hadiths":[{"id":"1495","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"3544","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E382" s="4" t="n"/>
@@ -9295,7 +9299,7 @@
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Calling Allah by His Beautiful Names","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah called upon Allah by His beautiful Names, asking for forgiveness and mercy."},"heading":{"title":"Calling Allah by His Beautiful Names for Forgiveness and Mercy","description":"This Hadith is about calling upon Allah by His pure, good, blessed, and beloved Name. The narration says that when Allah is called by it, He answers; when asked by it, He gives; when asked for mercy by it, He grants mercy; and when asked for relief by it, He grants relief. Aishah asked to be taught it, but the Prophet said it was not fitting for her to ask worldly things by it. She then made wudu, prayed two rak'ah, and called upon Allah, Ar-Rahman, Al-Barr, Ar-Rahim, and by all His beautiful Names, asking for forgiveness and mercy. The Prophet smiled and said it was among the names she used."},"teachings":["Call upon Allah by His beautiful Names.","Ask Allah for forgiveness and mercy.","Aishah prayed before making this supplication.","The narration warns against using this Name for worldly requests."],"related_hadiths":[{"id":"7392","book_id":"1","label":"Sahih Bukhari"},{"id":"3508","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Calling Allah by His Beautiful Names","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah called upon Allah by His beautiful Names, asking for forgiveness and mercy."},"heading":{"title":"Calling Allah by His Beautiful Names for Forgiveness and Mercy","description":"This Hadith is about calling upon Allah by His pure, good, blessed, and beloved Name. The narration says that when Allah is called by it, He answers; when asked by it, He gives; when asked for mercy by it, He grants mercy; and when asked for relief by it, He grants relief. Aishah asked to be taught it, but the Prophet said it was not fitting for her to ask worldly things by it. She then made wudu, prayed two rak'ah, and called upon Allah, Ar-Rahman, Al-Barr, Ar-Rahim, and by all His beautiful Names, asking for forgiveness and mercy. The Prophet smiled and said it was among the names she used."},"teachings":["Call upon Allah by His beautiful Names.","Ask Allah for forgiveness and mercy.","Aishah prayed before making this supplication.","The narration warns against using this Name for worldly requests."],"related_hadiths":[{"id":"7392","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3508","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E383" s="4" t="n"/>
@@ -9318,7 +9322,7 @@
       </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seawater for Ablution","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet answered that seawater is purifying and its dead meat is permissible when asked by travelers with little water."},"heading":{"title":"Wudu with Seawater Hadith and Its Clear Lesson","description":"This wudu with seawater hadith answers a real travel concern. A man told the Messenger of Allah that they traveled by sea and carried only a small amount of water. If they used that water for ablution, they would become thirsty. So he asked whether they could perform ablution with seawater. The Prophet gave a clear answer: its water is a means of purification, and its dead meat is permissible. The hadith directly connects seawater with wudu and purification. It also mentions the sea’s dead meat in the same reply, with the translation explaining fish found dead in the sea. The main lesson is ease in purification when people are at sea and need to save drinking water."},"teachings":["Seawater is described as a means of purification in the hadith.","The question came from travelers who had little drinking water.","The Prophet’s answer addressed both ablution and sea dead meat."],"related_hadiths":[{"id":"83","book_id":"4","label":"Sunan Abu Dawud"},{"id":"59","book_id":"3","label":"Sunan an-Nasai"},{"id":"3246","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seawater for Ablution","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet answered that seawater is purifying and its dead meat is permissible when asked by travelers with little water."},"heading":{"title":"Wudu with Seawater Hadith and Its Clear Lesson","description":"This wudu with seawater hadith answers a real travel concern. A man told the Messenger of Allah that they traveled by sea and carried only a small amount of water. If they used that water for ablution, they would become thirsty. So he asked whether they could perform ablution with seawater. The Prophet gave a clear answer: its water is a means of purification, and its dead meat is permissible. The hadith directly connects seawater with wudu and purification. It also mentions the sea’s dead meat in the same reply, with the translation explaining fish found dead in the sea. The main lesson is ease in purification when people are at sea and need to save drinking water."},"teachings":["Seawater is described as a means of purification in the hadith.","The question came from travelers who had little drinking water.","The Prophet’s answer addressed both ablution and sea dead meat."],"related_hadiths":[{"id":"83","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"59","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"3246","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E384" s="4" t="n"/>
@@ -9341,7 +9345,7 @@
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seawater and Purification","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Firasi used seawater for ablution while fishing, and the Prophet said its water purifies and its dead meat is permissible."},"heading":{"title":"Hadith About Seawater for Wudu While Fishing","description":"This hadith about seawater for wudu while fishing gives another report on the same subject. Ibn Firasi said he was fishing and had a vessel in which he kept water. He used seawater for ablution and later mentioned it to the Messenger of Allah. The Prophet answered with the same clear wording: its water is a means of purification, and its dead meat is permissible. The hadith is useful for readers searching for sea water wudu because it shows the issue through a practical fishing situation. The text does not add extra conditions beyond the report. It simply confirms, through the Prophet’s words, that seawater can serve as purifying water in the case described."},"teachings":["The report connects fishing, seawater, and ablution.","The Prophet described seawater as purifying.","The same answer also mentions the permissibility of dead meat from the sea."],"related_hadiths":[{"id":"83","book_id":"4","label":"Sunan Abu Dawud"},{"id":"59","book_id":"3","label":"Sunan an-Nasai"},{"id":"3246","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seawater and Purification","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Firasi used seawater for ablution while fishing, and the Prophet said its water purifies and its dead meat is permissible."},"heading":{"title":"Hadith About Seawater for Wudu While Fishing","description":"This hadith about seawater for wudu while fishing gives another report on the same subject. Ibn Firasi said he was fishing and had a vessel in which he kept water. He used seawater for ablution and later mentioned it to the Messenger of Allah. The Prophet answered with the same clear wording: its water is a means of purification, and its dead meat is permissible. The hadith is useful for readers searching for sea water wudu because it shows the issue through a practical fishing situation. The text does not add extra conditions beyond the report. It simply confirms, through the Prophet’s words, that seawater can serve as purifying water in the case described."},"teachings":["The report connects fishing, seawater, and ablution.","The Prophet described seawater as purifying.","The same answer also mentions the permissibility of dead meat from the sea."],"related_hadiths":[{"id":"83","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"59","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"3246","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E385" s="4" t="n"/>
@@ -9364,7 +9368,7 @@
       </c>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Purifying Sea Water","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir narrated that the Prophet was asked about seawater and replied that its water purifies and its dead meat is permissible."},"heading":{"title":"Seawater Purification Hadith from Jabir","description":"This seawater purification hadith from Jabir is short and direct. The Prophet was asked about seawater, and he answered that its water is a means of purification and its dead meat is permissible. The narration also notes another chain with similar wording. This makes the central topic easy to identify: sea water, wudu, purification, and the ruling mentioned about dead meat from the sea. For a reader, the safest explanation is to avoid adding unrelated rulings and stay with the Prophet’s answer. The hadith gives a clear phrase that people often search for: its water is purifying and its dead meat is permissible. It teaches that seawater is not treated as unusable merely because it is salty."},"teachings":["The Prophet was asked directly about seawater.","The answer describes seawater as purifying.","The same wording includes the permissibility of dead meat from the sea."],"related_hadiths":[{"id":"83","book_id":"4","label":"Sunan Abu Dawud"},{"id":"59","book_id":"3","label":"Sunan an-Nasai"},{"id":"3246","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Purifying Sea Water","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir narrated that the Prophet was asked about seawater and replied that its water purifies and its dead meat is permissible."},"heading":{"title":"Seawater Purification Hadith from Jabir","description":"This seawater purification hadith from Jabir is short and direct. The Prophet was asked about seawater, and he answered that its water is a means of purification and its dead meat is permissible. The narration also notes another chain with similar wording. This makes the central topic easy to identify: sea water, wudu, purification, and the ruling mentioned about dead meat from the sea. For a reader, the safest explanation is to avoid adding unrelated rulings and stay with the Prophet’s answer. The hadith gives a clear phrase that people often search for: its water is purifying and its dead meat is permissible. It teaches that seawater is not treated as unusable merely because it is salty."},"teachings":["The Prophet was asked directly about seawater.","The answer describes seawater as purifying.","The same wording includes the permissibility of dead meat from the sea."],"related_hadiths":[{"id":"83","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"59","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"3246","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E386" s="4" t="n"/>
@@ -9387,7 +9391,7 @@
       </c>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Distress and Tawhid","description":"$book_name$ $hadith_number$ - $chapter_name$. A short dua for distress that renews faith in Allah as Lord without associating partners."},"heading":{"title":"Dua for Distress: Allah Is My Lord and I Associate Nothing With Him","description":"This hadith teaches a short dua for distress that is easy to remember and deep in meaning. Asma bint Umais said that the Messenger of Allah صلى الله عليه وسلم taught her words to say at times of hardship: Allah, Allah is my Lord, I do not associate anything with Him. The focus is not on long wording. It is on turning the heart back to Allah and affirming tawhid during pressure. People often search for Allahu Rabbi la ushriku bihi shayan, dua for anxiety, and hadith about distress. The hadith itself keeps the message simple: in a hard moment, repeat Allahs name, remember that He is your Lord, and stay firm upon worshiping Him alone."},"teachings":["In distress, the Prophet صلى الله عليه وسلم taught words that center the heart on Allah.","The dua clearly affirms that Allah is the Lord.","The wording rejects associating anything with Allah.","Short supplications can carry strong meanings when said with faith."],"related_hadiths":[{"id":"3883","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3884","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3888","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Distress and Tawhid","description":"$book_name$ $hadith_number$ - $chapter_name$. A short dua for distress that renews faith in Allah as Lord without associating partners."},"heading":{"title":"Dua for Distress: Allah Is My Lord and I Associate Nothing With Him","description":"This hadith teaches a short dua for distress that is easy to remember and deep in meaning. Asma bint Umais said that the Messenger of Allah صلى الله عليه وسلم taught her words to say at times of hardship: Allah, Allah is my Lord, I do not associate anything with Him. The focus is not on long wording. It is on turning the heart back to Allah and affirming tawhid during pressure. People often search for Allahu Rabbi la ushriku bihi shayan, dua for anxiety, and hadith about distress. The hadith itself keeps the message simple: in a hard moment, repeat Allahs name, remember that He is your Lord, and stay firm upon worshiping Him alone."},"teachings":["In distress, the Prophet صلى الله عليه وسلم taught words that center the heart on Allah.","The dua clearly affirms that Allah is the Lord.","The wording rejects associating anything with Allah.","Short supplications can carry strong meanings when said with faith."],"related_hadiths":[{"id":"3883","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3884","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3888","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E387" s="4" t="n"/>
@@ -9410,7 +9414,7 @@
       </c>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Powerful Dua in Distress","description":"$book_name$ $hadith_number$ - $chapter_name$. A Prophetic dua for distress praising Allah, His forbearance, generosity, and lordship."},"heading":{"title":"Prophetic Dua for Distress With La Ilaha Illallah","description":"This hadith gives a Prophetic dua for distress that begins with the words of tawhid. Ibn Abbas narrated that the Prophet صلى الله عليه وسلم used to say these words at times of distress. The dua praises Allah as the Forbearing and the Most Generous, and glorifies Him as Lord of the Mighty Throne, Lord of the seven heavens, and Lord of the Magnificent Throne. The main search phrase is dua for distress in Islam, with related terms like La ilaha illallahul Halimul Karim and supplication for hardship. The hadith shows that when a believer feels pressure, the tongue can return to Allahs oneness, His greatness, and His perfect lordship instead of being lost in fear."},"teachings":["The Prophet صلى الله عليه وسلم used this remembrance at times of distress.","The dua begins with affirming that none has the right to be worshipped but Allah.","It praises Allah with meanings of forbearance, generosity, and greatness.","Remembering Allahs lordship can guide the heart during hardship."],"related_hadiths":[{"id":"3882","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3884","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3888","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Powerful Dua in Distress","description":"$book_name$ $hadith_number$ - $chapter_name$. A Prophetic dua for distress praising Allah, His forbearance, generosity, and lordship."},"heading":{"title":"Prophetic Dua for Distress With La Ilaha Illallah","description":"This hadith gives a Prophetic dua for distress that begins with the words of tawhid. Ibn Abbas narrated that the Prophet صلى الله عليه وسلم used to say these words at times of distress. The dua praises Allah as the Forbearing and the Most Generous, and glorifies Him as Lord of the Mighty Throne, Lord of the seven heavens, and Lord of the Magnificent Throne. The main search phrase is dua for distress in Islam, with related terms like La ilaha illallahul Halimul Karim and supplication for hardship. The hadith shows that when a believer feels pressure, the tongue can return to Allahs oneness, His greatness, and His perfect lordship instead of being lost in fear."},"teachings":["The Prophet صلى الله عليه وسلم used this remembrance at times of distress.","The dua begins with affirming that none has the right to be worshipped but Allah.","It praises Allah with meanings of forbearance, generosity, and greatness.","Remembering Allahs lordship can guide the heart during hardship."],"related_hadiths":[{"id":"3882","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3884","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3888","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E388" s="4" t="n"/>
@@ -9433,7 +9437,7 @@
       </c>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu and Wiping Over Leather Socks","description":"$book_name$ $hadith_number$ - $chapter_name$. Mughirah poured water for the Prophet, who washed for wudu, wiped over his leather socks, and led the prayer."},"heading":{"title":"Wiping Over Leather Socks in Wudu Hadith","description":"This wiping over leather socks in wudu hadith gives a step-by-step moment from the Prophet’s ablution. Mughirah bin Shubah met the Prophet with a water skin after he returned from relieving himself. He poured water for him. The Prophet washed his hands and face, then washed his forearms after bringing them out from under a tight garment. He then wiped over his leather socks and led the people in prayer. The text teaches careful wudu even when clothing makes washing harder. It also records wiping over leather socks in that situation. For someone searching for khuffayn hadith, this narration should be read as a direct description of what Mughirah saw and helped with."},"teachings":["Mughirah helped by pouring water for the Prophet’s wudu.","The Prophet washed the required parts mentioned in the report with care.","The narration records wiping over leather socks before leading prayer."],"related_hadiths":[{"id":"203","book_id":"1","label":"Sahih Bukhari"},{"id":"205","book_id":"1","label":"Sahih Bukhari"},{"id":"547","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu and Wiping Over Leather Socks","description":"$book_name$ $hadith_number$ - $chapter_name$. Mughirah poured water for the Prophet, who washed for wudu, wiped over his leather socks, and led the prayer."},"heading":{"title":"Wiping Over Leather Socks in Wudu Hadith","description":"This wiping over leather socks in wudu hadith gives a step-by-step moment from the Prophet’s ablution. Mughirah bin Shubah met the Prophet with a water skin after he returned from relieving himself. He poured water for him. The Prophet washed his hands and face, then washed his forearms after bringing them out from under a tight garment. He then wiped over his leather socks and led the people in prayer. The text teaches careful wudu even when clothing makes washing harder. It also records wiping over leather socks in that situation. For someone searching for khuffayn hadith, this narration should be read as a direct description of what Mughirah saw and helped with."},"teachings":["Mughirah helped by pouring water for the Prophet’s wudu.","The Prophet washed the required parts mentioned in the report with care.","The narration records wiping over leather socks before leading prayer."],"related_hadiths":[{"id":"203","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"205","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"547","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E389" s="4" t="n"/>
@@ -9456,7 +9460,7 @@
       </c>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Wudu Method","description":"$book_name$ $hadith_number$ - $chapter_name$. Rubai brought water and poured it as the Prophet washed, wiped his head with fresh water, and washed each part three times."},"heading":{"title":"Prophet Wudu Method Hadith with Fresh Water","description":"This Prophet wudu method hadith describes how Rubai bint Muawwidh brought a basin of water to the Prophet. He told her to pour it, and she poured. The narration says he washed his face and forearms, then took fresh water and wiped his head, front and back. It also says he washed his feet and that he washed each part three times. The core topic is the method of ablution as shown in the report. The text is practical and easy to follow, but we should not add steps not mentioned here. For readers searching how the Prophet performed wudu, this hadith highlights washing, wiping the head with fresh water, and repeating the washed parts three times."},"teachings":["The Prophet accepted water being poured for his wudu.","The report mentions fresh water for wiping the head.","The narration describes washing each part three times."],"related_hadiths":[{"id":"417","book_id":"6","label":"Sunan Ibn Majah"},{"id":"164","book_id":"1","label":"Sahih Bukhari"},{"id":"434","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Wudu Method","description":"$book_name$ $hadith_number$ - $chapter_name$. Rubai brought water and poured it as the Prophet washed, wiped his head with fresh water, and washed each part three times."},"heading":{"title":"Prophet Wudu Method Hadith with Fresh Water","description":"This Prophet wudu method hadith describes how Rubai bint Muawwidh brought a basin of water to the Prophet. He told her to pour it, and she poured. The narration says he washed his face and forearms, then took fresh water and wiped his head, front and back. It also says he washed his feet and that he washed each part three times. The core topic is the method of ablution as shown in the report. The text is practical and easy to follow, but we should not add steps not mentioned here. For readers searching how the Prophet performed wudu, this hadith highlights washing, wiping the head with fresh water, and repeating the washed parts three times."},"teachings":["The Prophet accepted water being poured for his wudu.","The report mentions fresh water for wiping the head.","The narration describes washing each part three times."],"related_hadiths":[{"id":"417","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"164","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"434","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E390" s="4" t="n"/>
@@ -9479,7 +9483,7 @@
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Satan Cannot Appear as the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever sees the Prophet in a dream has truly seen him, because Satan cannot take his form."},"heading":{"title":"Seeing the Prophet in a Dream: Satan Cannot Take His Form","description":"This narration repeats the clear meaning that seeing the Prophet in a dream is a real sighting of him. People often search for “Satan cannot appear as Prophet Muhammad” or “whoever sees me in a dream hadith,” and this hadith gives the answer directly. The Messenger of Allah (صلى الله عليه وسلم) said that whoever sees him in a dream has seen him, because it is not proper or possible for Satan to appear in his image. The hadith does not give extra rules about interpreting dreams or judging other people’s claims. Its message is focused: the Prophet’s form is protected from Satan’s imitation. That is the core teaching to take from this text."},"teachings":["The Prophet (صلى الله عليه وسلم) described seeing him in a dream as truly seeing him.","Satan cannot appear in the image of the Prophet (صلى الله عليه وسلم).","The hadith keeps the matter focused on the Prophet’s protected form, not general dream claims."],"related_hadiths":[{"id":"3901","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3904","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3905","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Satan Cannot Appear as the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever sees the Prophet in a dream has truly seen him, because Satan cannot take his form."},"heading":{"title":"Seeing the Prophet in a Dream: Satan Cannot Take His Form","description":"This narration repeats the clear meaning that seeing the Prophet in a dream is a real sighting of him. People often search for “Satan cannot appear as Prophet Muhammad” or “whoever sees me in a dream hadith,” and this hadith gives the answer directly. The Messenger of Allah (صلى الله عليه وسلم) said that whoever sees him in a dream has seen him, because it is not proper or possible for Satan to appear in his image. The hadith does not give extra rules about interpreting dreams or judging other people’s claims. Its message is focused: the Prophet’s form is protected from Satan’s imitation. That is the core teaching to take from this text."},"teachings":["The Prophet (صلى الله عليه وسلم) described seeing him in a dream as truly seeing him.","Satan cannot appear in the image of the Prophet (صلى الله عليه وسلم).","The hadith keeps the matter focused on the Prophet’s protected form, not general dream claims."],"related_hadiths":[{"id":"3901","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3904","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3905","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E391" s="4" t="n"/>
@@ -9502,7 +9506,7 @@
       </c>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Satan Cannot Imitate the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that seeing him in a dream is true, since Satan cannot imitate him."},"heading":{"title":"Whoever Sees the Prophet in a Dream: A Hadith on True Prophetic Dreams","description":"This hadith is another narration on the topic of seeing Prophet Muhammad in a dream. The wording is short but meaningful. The Prophet (صلى الله عليه وسلم) said that whoever sees him in a dream has really seen him, because Satan cannot imitate him. This is why the key search phrase “hadith seeing Prophet in dream” is closely tied to this narration. The hadith does not talk about every type of dream, nor does it explain signs for dream interpretation. It only states the special point that Satan cannot take the Prophet’s form. A reader should take comfort from the wording while also avoiding extra details that are not found in this specific text."},"teachings":["The hadith affirms the reality of seeing the Prophet (صلى الله عليه وسلم) in a dream.","Satan is unable to imitate the Prophet (صلى الله عليه وسلم).","The narration teaches believers to stay with the exact wording when discussing this topic."],"related_hadiths":[{"id":"3901","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3902","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3905","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Satan Cannot Imitate the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that seeing him in a dream is true, since Satan cannot imitate him."},"heading":{"title":"Whoever Sees the Prophet in a Dream: A Hadith on True Prophetic Dreams","description":"This hadith is another narration on the topic of seeing Prophet Muhammad in a dream. The wording is short but meaningful. The Prophet (صلى الله عليه وسلم) said that whoever sees him in a dream has really seen him, because Satan cannot imitate him. This is why the key search phrase “hadith seeing Prophet in dream” is closely tied to this narration. The hadith does not talk about every type of dream, nor does it explain signs for dream interpretation. It only states the special point that Satan cannot take the Prophet’s form. A reader should take comfort from the wording while also avoiding extra details that are not found in this specific text."},"teachings":["The hadith affirms the reality of seeing the Prophet (صلى الله عليه وسلم) in a dream.","Satan is unable to imitate the Prophet (صلى الله عليه وسلم).","The narration teaches believers to stay with the exact wording when discussing this topic."],"related_hadiths":[{"id":"3901","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3902","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3905","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E392" s="4" t="n"/>
@@ -9525,7 +9529,7 @@
       </c>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | True Dream of the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever sees the Messenger in a dream has seen him, for Satan cannot imitate him."},"heading":{"title":"True Dream of the Prophet: Whoever Sees Him Has Seen Him","description":"This narration from Ibn Abbas gives the same clear lesson found in several reports: whoever sees the Messenger of Allah (صلى الله عليه وسلم) in a dream has truly seen him. The hadith explains the reason by saying that Satan cannot imitate him. Many people search for “true dream of Prophet Muhammad” and “can Satan imitate the Prophet,” and this hadith answers both in a short way. It does not describe how the dream looks, how a person should prove it, or how to interpret every detail. Its lesson is limited and clear: the Prophet’s form is not open to Satan’s imitation. That is the careful meaning to keep."},"teachings":["The hadith states that seeing the Prophet (صلى الله عليه وسلم) in a dream is a true sighting.","Satan cannot imitate the Messenger of Allah (صلى الله عليه وسلم).","The text teaches careful speech about dreams without adding details not mentioned."],"related_hadiths":[{"id":"3901","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3903","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3904","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | True Dream of the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever sees the Messenger in a dream has seen him, for Satan cannot imitate him."},"heading":{"title":"True Dream of the Prophet: Whoever Sees Him Has Seen Him","description":"This narration from Ibn Abbas gives the same clear lesson found in several reports: whoever sees the Messenger of Allah (صلى الله عليه وسلم) in a dream has truly seen him. The hadith explains the reason by saying that Satan cannot imitate him. Many people search for “true dream of Prophet Muhammad” and “can Satan imitate the Prophet,” and this hadith answers both in a short way. It does not describe how the dream looks, how a person should prove it, or how to interpret every detail. Its lesson is limited and clear: the Prophet’s form is not open to Satan’s imitation. That is the careful meaning to keep."},"teachings":["The hadith states that seeing the Prophet (صلى الله عليه وسلم) in a dream is a true sighting.","Satan cannot imitate the Messenger of Allah (صلى الله عليه وسلم).","The text teaches careful speech about dreams without adding details not mentioned."],"related_hadiths":[{"id":"3901","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3903","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3904","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E393" s="4" t="n"/>
@@ -9548,7 +9552,7 @@
       </c>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Types of Dreams in Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. Dreams may be glad tidings, personal thoughts, or frightening dreams from Satan, with guidance on how to respond."},"heading":{"title":"Three Types of Dreams in Islam: Glad Tidings, Thoughts, and Fear","description":"This hadith is a key text for the search term “three types of dreams in Islam.” The Prophet (صلى الله عليه وسلم) explains that dreams are of three types: glad tidings from Allah, what is on a person’s mind, and frightening dreams from Satan. The hadith also gives simple guidance. If someone sees a dream that he likes, he may tell it if he wishes. If he sees something he dislikes, he should not tell anyone about it and should get up to pray. This teaching keeps dream talk balanced. Not every dream has the same source, and not every dream should be shared. The response depends on what was seen."},"teachings":["Dreams are described as glad tidings from Allah, thoughts of the self, or frightening dreams from Satan.","A pleasing dream may be shared if the person wishes.","A disliked dream should not be shared, and the person should get up and pray."],"related_hadiths":[{"id":"3907","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3908","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3909","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Types of Dreams in Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. Dreams may be glad tidings, personal thoughts, or frightening dreams from Satan, with guidance on how to respond."},"heading":{"title":"Three Types of Dreams in Islam: Glad Tidings, Thoughts, and Fear","description":"This hadith is a key text for the search term “three types of dreams in Islam.” The Prophet (صلى الله عليه وسلم) explains that dreams are of three types: glad tidings from Allah, what is on a person’s mind, and frightening dreams from Satan. The hadith also gives simple guidance. If someone sees a dream that he likes, he may tell it if he wishes. If he sees something he dislikes, he should not tell anyone about it and should get up to pray. This teaching keeps dream talk balanced. Not every dream has the same source, and not every dream should be shared. The response depends on what was seen."},"teachings":["Dreams are described as glad tidings from Allah, thoughts of the self, or frightening dreams from Satan.","A pleasing dream may be shared if the person wishes.","A disliked dream should not be shared, and the person should get up and pray."],"related_hadiths":[{"id":"3907","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3908","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3909","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E394" s="4" t="n"/>
@@ -9571,7 +9575,7 @@
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | What to Do After a Bad Dream","description":"$book_name$ $hadith_number$ - $chapter_name$. After a disliked dream, spit dryly left three times, seek refuge with Allah, and turn to the other side."},"heading":{"title":"What to Do After a Bad Dream in Islam: Seek Refuge and Turn Over","description":"This hadith gives practical guidance for the search phrase “what to do after a bad dream in Islam.” The Messenger of Allah (صلى الله عليه وسلم) says that when a person sees a dream he dislikes, he should spit dryly to his left three times, seek refuge with Allah from Satan three times, and turn over onto the other side. The teaching is simple and action-based. It does not tell the person to chase the meaning of the bad dream or spread it to others. Instead, it directs him to seek Allah’s protection and change his sleeping position. This keeps the heart from staying stuck in fear."},"teachings":["After a disliked dream, a person should spit dryly to the left three times.","He should seek refuge with Allah from Satan three times.","He should turn over onto his other side."],"related_hadiths":[{"id":"3909","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3910","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3906","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | What to Do After a Bad Dream","description":"$book_name$ $hadith_number$ - $chapter_name$. After a disliked dream, spit dryly left three times, seek refuge with Allah, and turn to the other side."},"heading":{"title":"What to Do After a Bad Dream in Islam: Seek Refuge and Turn Over","description":"This hadith gives practical guidance for the search phrase “what to do after a bad dream in Islam.” The Messenger of Allah (صلى الله عليه وسلم) says that when a person sees a dream he dislikes, he should spit dryly to his left three times, seek refuge with Allah from Satan three times, and turn over onto the other side. The teaching is simple and action-based. It does not tell the person to chase the meaning of the bad dream or spread it to others. Instead, it directs him to seek Allah’s protection and change his sleeping position. This keeps the heart from staying stuck in fear."},"teachings":["After a disliked dream, a person should spit dryly to the left three times.","He should seek refuge with Allah from Satan three times.","He should turn over onto his other side."],"related_hadiths":[{"id":"3909","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3910","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3906","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E395" s="4" t="n"/>
@@ -9594,7 +9598,7 @@
       </c>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Good Dreams and Bad Dreams","description":"$book_name$ $hadith_number$ - $chapter_name$. Good dreams come from Allah and bad dreams from Satan, with steps for disliked dreams."},"heading":{"title":"Good Dreams and Bad Dreams in Islam: Guidance for Disliked Dreams","description":"This hadith explains the difference between good dreams and bad dreams in Islam. The Messenger of Allah (صلى الله عليه وسلم) says that good dreams come from Allah and bad dreams come from Satan. Then he gives steps for a dream a person dislikes: spit dryly to the left three times, seek refuge with Allah from the accursed Satan three times, and turn over onto the other side. This narration is helpful for people searching “bad dreams in Islam” or “good dreams from Allah hadith.” The hadith does not ask a person to share frightening dreams. It teaches a calm response that turns the person back to Allah and away from Satan’s fear."},"teachings":["Good dreams are described as coming from Allah.","Bad dreams are described as coming from Satan.","When seeing something disliked, the person should seek refuge with Allah and turn over."],"related_hadiths":[{"id":"3908","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3910","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3906","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Good Dreams and Bad Dreams","description":"$book_name$ $hadith_number$ - $chapter_name$. Good dreams come from Allah and bad dreams from Satan, with steps for disliked dreams."},"heading":{"title":"Good Dreams and Bad Dreams in Islam: Guidance for Disliked Dreams","description":"This hadith explains the difference between good dreams and bad dreams in Islam. The Messenger of Allah (صلى الله عليه وسلم) says that good dreams come from Allah and bad dreams come from Satan. Then he gives steps for a dream a person dislikes: spit dryly to the left three times, seek refuge with Allah from the accursed Satan three times, and turn over onto the other side. This narration is helpful for people searching “bad dreams in Islam” or “good dreams from Allah hadith.” The hadith does not ask a person to share frightening dreams. It teaches a calm response that turns the person back to Allah and away from Satan’s fear."},"teachings":["Good dreams are described as coming from Allah.","Bad dreams are described as coming from Satan.","When seeing something disliked, the person should seek refuge with Allah and turn over."],"related_hadiths":[{"id":"3908","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3910","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3906","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E396" s="4" t="n"/>
@@ -9617,7 +9621,7 @@
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Helping with Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Safwan said he poured water for the Prophet during ablution, both while traveling and while resident."},"heading":{"title":"Hadith About Helping Someone Perform Wudu","description":"This hadith about helping someone perform wudu is very simple. Safwan bin Assal said that he poured water for the Prophet during ablution in travel and while resident. The narration does not give the full steps of wudu, and it does not need to. Its main point is service during purification. It shows that another person may assist by pouring water while someone performs ablution. The wording also covers two settings: journeys and staying at home. For people searching for pouring water for wudu hadith, this report gives a clear example from the Prophet’s own practice. The teaching is practical: helping with worship can be a small, quiet act, such as providing water for purification."},"teachings":["Pouring water for another person’s wudu is recorded in the narration.","The report mentions both travel and residence.","Small acts of service can support worship and purification."],"related_hadiths":[{"id":"164","book_id":"1","label":"Sahih Bukhari"},{"id":"405","book_id":"6","label":"Sunan Ibn Majah"},{"id":"417","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Helping with Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Safwan said he poured water for the Prophet during ablution, both while traveling and while resident."},"heading":{"title":"Hadith About Helping Someone Perform Wudu","description":"This hadith about helping someone perform wudu is very simple. Safwan bin Assal said that he poured water for the Prophet during ablution in travel and while resident. The narration does not give the full steps of wudu, and it does not need to. Its main point is service during purification. It shows that another person may assist by pouring water while someone performs ablution. The wording also covers two settings: journeys and staying at home. For people searching for pouring water for wudu hadith, this report gives a clear example from the Prophet’s own practice. The teaching is practical: helping with worship can be a small, quiet act, such as providing water for purification."},"teachings":["Pouring water for another person’s wudu is recorded in the narration.","The report mentions both travel and residence.","Small acts of service can support worship and purification."],"related_hadiths":[{"id":"164","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"405","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"417","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E397" s="4" t="n"/>
@@ -9640,7 +9644,7 @@
       </c>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Satan Playing in Dreams","description":"$book_name$ $hadith_number$ - $chapter_name$. If Satan plays with someone in a dream, the Prophet taught not to tell people about it."},"heading":{"title":"Satan Playing in Dreams: Why Bad Dreams Should Not Be Shared","description":"This hadith gives a clear lesson about telling bad dreams to people. A man described a disturbing dream during the Prophet’s sermon: his neck was struck, his head fell, and he chased it and put it back. The Messenger of Allah (صلى الله عليه وسلم) said that if Satan plays with any one of you in his dream, he should not tell people about it. The search phrase “Satan playing in dreams hadith” matches this text closely. The Prophet (صلى الله عليه وسلم) did not explain the dream image or invite public discussion about it. He gave a simple rule for this kind of dream: do not spread it among people."},"teachings":["Some disturbing dreams are described as Satan playing with a person.","Such dreams should not be told to people.","The Prophet (صلى الله عليه وسلم) redirected attention away from the disturbing details."],"related_hadiths":[{"id":"3911","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3913","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3906","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Satan Playing in Dreams","description":"$book_name$ $hadith_number$ - $chapter_name$. If Satan plays with someone in a dream, the Prophet taught not to tell people about it."},"heading":{"title":"Satan Playing in Dreams: Why Bad Dreams Should Not Be Shared","description":"This hadith gives a clear lesson about telling bad dreams to people. A man described a disturbing dream during the Prophet’s sermon: his neck was struck, his head fell, and he chased it and put it back. The Messenger of Allah (صلى الله عليه وسلم) said that if Satan plays with any one of you in his dream, he should not tell people about it. The search phrase “Satan playing in dreams hadith” matches this text closely. The Prophet (صلى الله عليه وسلم) did not explain the dream image or invite public discussion about it. He gave a simple rule for this kind of dream: do not spread it among people."},"teachings":["Some disturbing dreams are described as Satan playing with a person.","Such dreams should not be told to people.","The Prophet (صلى الله عليه وسلم) redirected attention away from the disturbing details."],"related_hadiths":[{"id":"3911","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3913","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3906","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E398" s="4" t="n"/>
@@ -9663,7 +9667,7 @@
       </c>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dream Interpretation in Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. Dreams are treated with care, and a person should tell them only to someone loved or wise."},"heading":{"title":"Dream Interpretation in Islam: Tell Dreams to Someone Loved or Wise","description":"This hadith is a key narration for the search term “dream interpretation in Islam.” The Prophet (صلى الله عليه وسلم) says that dreams are attached to the foot of a bird until they are interpreted; when they are interpreted, they come to pass. He also says that dreams are one of the forty-six parts of prophecy. The narrator adds that he thinks the Prophet (صلى الله عليه وسلم) said a person should not tell a dream except to someone he loves or someone wise. The text teaches care before sharing dreams. It does not encourage careless interpretation or public guessing. The main lesson is to treat dreams seriously and speak about them with the right person."},"teachings":["Dreams should be treated carefully before they are interpreted.","Dreams are described as one of the forty-six parts of prophecy.","A person should tell dreams only to someone loved or wise, as mentioned by the narrator."],"related_hadiths":[{"id":"3915","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3907","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3917","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dream Interpretation in Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. Dreams are treated with care, and a person should tell them only to someone loved or wise."},"heading":{"title":"Dream Interpretation in Islam: Tell Dreams to Someone Loved or Wise","description":"This hadith is a key narration for the search term “dream interpretation in Islam.” The Prophet (صلى الله عليه وسلم) says that dreams are attached to the foot of a bird until they are interpreted; when they are interpreted, they come to pass. He also says that dreams are one of the forty-six parts of prophecy. The narrator adds that he thinks the Prophet (صلى الله عليه وسلم) said a person should not tell a dream except to someone he loves or someone wise. The text teaches care before sharing dreams. It does not encourage careless interpretation or public guessing. The main lesson is to treat dreams seriously and speak about them with the right person."},"teachings":["Dreams should be treated carefully before they are interpreted.","Dreams are described as one of the forty-six parts of prophecy.","A person should tell dreams only to someone loved or wise, as mentioned by the narrator."],"related_hadiths":[{"id":"3915","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3907","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3917","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E399" s="4" t="n"/>
@@ -9686,7 +9690,7 @@
       </c>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr Interprets a Dream","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr interpreted a dream of shade, honey, ghee, Qur’an, truth, and a rope reaching heaven."},"heading":{"title":"Abu Bakr’s Dream Interpretation: Shade, Qur’an, Truth, and the Rope to Heaven","description":"This hadith gives a detailed example of dream interpretation in Islam. A man told the Prophet (صلى الله عليه وسلم) about a cloud giving shade, drops of ghee and honey, people collecting them, and a rope reaching to heaven. Abu Bakr asked to interpret it. He said the shade was Islam, the honey and ghee were the Qur’an with its sweetness and softness, and people collecting from it meant people taking much or little from the Qur’an. He also interpreted the rope as the truth followed by the Prophet (صلى الله عليه وسلم). The Prophet (صلى الله عليه وسلم) said Abu Bakr got some right and some wrong, but did not tell him which parts. The hadith teaches care and humility in interpretation."},"teachings":["Dream interpretation may involve meanings connected to Islam, the Qur’an, and truth, as stated in the report.","Even Abu Bakr’s interpretation was described as partly right and partly wrong.","The Prophet (صلى الله عليه وسلم) told Abu Bakr not to swear when asking about the interpretation."],"related_hadiths":[{"id":"3914","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3915","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3920","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr Interprets a Dream","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr interpreted a dream of shade, honey, ghee, Qur’an, truth, and a rope reaching heaven."},"heading":{"title":"Abu Bakr’s Dream Interpretation: Shade, Qur’an, Truth, and the Rope to Heaven","description":"This hadith gives a detailed example of dream interpretation in Islam. A man told the Prophet (صلى الله عليه وسلم) about a cloud giving shade, drops of ghee and honey, people collecting them, and a rope reaching to heaven. Abu Bakr asked to interpret it. He said the shade was Islam, the honey and ghee were the Qur’an with its sweetness and softness, and people collecting from it meant people taking much or little from the Qur’an. He also interpreted the rope as the truth followed by the Prophet (صلى الله عليه وسلم). The Prophet (صلى الله عليه وسلم) said Abu Bakr got some right and some wrong, but did not tell him which parts. The hadith teaches care and humility in interpretation."},"teachings":["Dream interpretation may involve meanings connected to Islam, the Qur’an, and truth, as stated in the report.","Even Abu Bakr’s interpretation was described as partly right and partly wrong.","The Prophet (صلى الله عليه وسلم) told Abu Bakr not to swear when asking about the interpretation."],"related_hadiths":[{"id":"3914","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3915","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3920","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E400" s="4" t="n"/>
@@ -9709,7 +9713,7 @@
       </c>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Umar and Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar’s dream was interpreted with praise for his righteousness and encouragement to pray more at night."},"heading":{"title":"Ibn Umar’s Dream and Night Prayer: A Lesson in Growing Closer to Allah","description":"This hadith tells how Ibn Umar, as a young unmarried man, used to sleep in the mosque during the time of the Messenger of Allah (صلى الله عليه وسلم). He wished for a dream that the Prophet (صلى الله عليه وسلم) could interpret. In the dream, two angels took him, another angel told him not to be alarmed, and he was shown Hell with people he recognized. Then he was taken to the right. Hafsah told the Prophet (صلى الله عليه وسلم) about the dream, and he said Abdullah was a righteous man, if only he would pray more at night. The key phrase is “Ibn Umar night prayer hadith.” The direct lesson is that the dream led to encouragement for more night prayer."},"teachings":["Ibn Umar was praised as a righteous man in the Prophet’s interpretation.","The Prophet (صلى الله عليه وسلم) encouraged him to pray more at night.","The report shows that a dream may lead to a personal lesson when interpreted by the Prophet (صلى الله عليه وسلم)."],"related_hadiths":[{"id":"3920","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3918","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3914","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Umar and Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar’s dream was interpreted with praise for his righteousness and encouragement to pray more at night."},"heading":{"title":"Ibn Umar’s Dream and Night Prayer: A Lesson in Growing Closer to Allah","description":"This hadith tells how Ibn Umar, as a young unmarried man, used to sleep in the mosque during the time of the Messenger of Allah (صلى الله عليه وسلم). He wished for a dream that the Prophet (صلى الله عليه وسلم) could interpret. In the dream, two angels took him, another angel told him not to be alarmed, and he was shown Hell with people he recognized. Then he was taken to the right. Hafsah told the Prophet (صلى الله عليه وسلم) about the dream, and he said Abdullah was a righteous man, if only he would pray more at night. The key phrase is “Ibn Umar night prayer hadith.” The direct lesson is that the dream led to encouragement for more night prayer."},"teachings":["Ibn Umar was praised as a righteous man in the Prophet’s interpretation.","The Prophet (صلى الله عليه وسلم) encouraged him to pray more at night.","The report shows that a dream may lead to a personal lesson when interpreted by the Prophet (صلى الله عليه وسلم)."],"related_hadiths":[{"id":"3920","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3918","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3914","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E401" s="4" t="n"/>
@@ -9732,7 +9736,7 @@
       </c>
       <c r="D402" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Serving Water for Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Ayyash said she helped the Prophet perform ablution while she stood and he sat."},"heading":{"title":"Hadith About Serving Water for the Prophet's Wudu","description":"This hadith about serving water for the Prophet’s wudu records a humble act of assistance. Umm Ayyash, who was connected to the household of Ruqayyah, said that she used to help the Messenger of Allah perform ablution. She described the scene plainly: she was standing and he was sitting. The narration does not give a full wudu method or extra rulings. It only tells us that help was given during ablution and how their positions were at that time. For a reader searching for helping with wudu or serving water for ablution, the main lesson is simple service. The hadith shows that purification can involve cooperation, care, and respect in small daily actions."},"teachings":["Umm Ayyash helped the Prophet with ablution.","The report describes her standing while the Prophet sat.","The narration teaches simple service connected to purification."],"related_hadiths":[{"id":"164","book_id":"1","label":"Sahih Bukhari"},{"id":"405","book_id":"6","label":"Sunan Ibn Majah"},{"id":"417","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Serving Water for Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Ayyash said she helped the Prophet perform ablution while she stood and he sat."},"heading":{"title":"Hadith About Serving Water for the Prophet's Wudu","description":"This hadith about serving water for the Prophet’s wudu records a humble act of assistance. Umm Ayyash, who was connected to the household of Ruqayyah, said that she used to help the Messenger of Allah perform ablution. She described the scene plainly: she was standing and he was sitting. The narration does not give a full wudu method or extra rulings. It only tells us that help was given during ablution and how their positions were at that time. For a reader searching for helping with wudu or serving water for ablution, the main lesson is simple service. The hadith shows that purification can involve cooperation, care, and respect in small daily actions."},"teachings":["Umm Ayyash helped the Prophet with ablution.","The report describes her standing while the Prophet sat.","The narration teaches simple service connected to purification."],"related_hadiths":[{"id":"164","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"405","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"417","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E402" s="4" t="n"/>
@@ -9755,7 +9759,7 @@
       </c>
       <c r="D403" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hold Tight to Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. Abdullah bin Salam’s dream was interpreted as a call to hold tight to the handhold of Islam until death."},"heading":{"title":"Hold Tight to Islam: Abdullah bin Salam’s Dream and the Firm Handhold","description":"This hadith presents a dream of Abdullah bin Salam and the Prophet’s interpretation of it. In the dream, he was guided along a great road, shown a path on the left and told he was not of its people, then taken on a path to the right. He reached a slippery mountain and then held firmly to a golden ring on an iron pillar. The Prophet (صلى الله عليه وسلم) interpreted the great road as the plain of gathering, the left road as the way of the people of Hell, the right road as the way of the people of Paradise, the slippery mountain as the place of the martyrs, and the handhold as the handhold of Islam. The main lesson is to hold tight to Islam until death."},"teachings":["The Prophet (صلى الله عليه وسلم) interpreted the handhold as the handhold of Islam.","Abdullah bin Salam was told to hold tight to it until death.","The dream included a clear contrast between the road of Hell and the road of Paradise."],"related_hadiths":[{"id":"3919","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3918","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3914","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hold Tight to Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. Abdullah bin Salam’s dream was interpreted as a call to hold tight to the handhold of Islam until death."},"heading":{"title":"Hold Tight to Islam: Abdullah bin Salam’s Dream and the Firm Handhold","description":"This hadith presents a dream of Abdullah bin Salam and the Prophet’s interpretation of it. In the dream, he was guided along a great road, shown a path on the left and told he was not of its people, then taken on a path to the right. He reached a slippery mountain and then held firmly to a golden ring on an iron pillar. The Prophet (صلى الله عليه وسلم) interpreted the great road as the plain of gathering, the left road as the way of the people of Hell, the right road as the way of the people of Paradise, the slippery mountain as the place of the martyrs, and the handhold as the handhold of Islam. The main lesson is to hold tight to Islam until death."},"teachings":["The Prophet (صلى الله عليه وسلم) interpreted the handhold as the handhold of Islam.","Abdullah bin Salam was told to hold tight to it until death.","The dream included a clear contrast between the road of Hell and the road of Paradise."],"related_hadiths":[{"id":"3919","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3918","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3914","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E403" s="4" t="n"/>
@@ -9778,7 +9782,7 @@
       </c>
       <c r="D404" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Dream of Hijrah and Hope","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet’s dream pointed to Madinah, Uhud, later victory, unity, and the reward linked with truth at Badr."},"heading":{"title":"Hadith About Prophetic Dream Interpretation and Hope After Uhud","description":"This hadith about dream interpretation shows how the Prophet (صلى الله عليه وسلم) described a dream with clear signs. He saw himself moving from Makkah to a land of date-palm trees. At first he thought it may be Yamamah or Hajar, but it was Al-Madinah, Yathrib. He also saw a sword break in the middle, and he explained it as what happened to the believers on the Day of Uhud. Then the sword became better than before, pointing to the Conquest and the believers coming together again. The dream also included cows, which he linked to the believers who were martyred at Uhud. The message stays close to the text: loss came, but Allah also brought goodness after it, along with the reward of truth connected with Badr."},"teachings":["A true dream may carry meanings that Allah makes clear through His Messenger (صلى الله عليه وسلم).","The move to Madinah was shown as part of the Prophet’s dream.","The pain of Uhud is mentioned along with later goodness and unity.","The text links the reward of truth with what Allah gave on the Day of Badr."],"related_hadiths":[{"id":"3918","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3920","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3925","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Dream of Hijrah and Hope","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet’s dream pointed to Madinah, Uhud, later victory, unity, and the reward linked with truth at Badr."},"heading":{"title":"Hadith About Prophetic Dream Interpretation and Hope After Uhud","description":"This hadith about dream interpretation shows how the Prophet (صلى الله عليه وسلم) described a dream with clear signs. He saw himself moving from Makkah to a land of date-palm trees. At first he thought it may be Yamamah or Hajar, but it was Al-Madinah, Yathrib. He also saw a sword break in the middle, and he explained it as what happened to the believers on the Day of Uhud. Then the sword became better than before, pointing to the Conquest and the believers coming together again. The dream also included cows, which he linked to the believers who were martyred at Uhud. The message stays close to the text: loss came, but Allah also brought goodness after it, along with the reward of truth connected with Badr."},"teachings":["A true dream may carry meanings that Allah makes clear through His Messenger (صلى الله عليه وسلم).","The move to Madinah was shown as part of the Prophet’s dream.","The pain of Uhud is mentioned along with later goodness and unity.","The text links the reward of truth with what Allah gave on the Day of Badr."],"related_hadiths":[{"id":"3918","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3920","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3925","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E404" s="4" t="n"/>
@@ -9801,7 +9805,7 @@
       </c>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gold Wristbands and False Claimants","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains the Prophet’s dream of two gold wristbands and his interpretation of them as Musailimah and Ansi."},"heading":{"title":"Hadith About Dream Interpretation: Gold Wristbands and the Two Liars","description":"This hadith about dream interpretation is short, but its meaning is very direct. The Messenger of Allah (صلى الله عليه وسلم) said that he saw two wristbands of gold on his arms. He then blew into them, and he interpreted them as two liars: Musailimah and ‘Ansi. The core point is not a general rule about every dream with gold. It is the Prophet’s own dream and his own explanation of it. The hadith uses simple symbols: two gold wristbands, an action of blowing, and then the named meaning. For readers searching for the hadith of Musailimah and Ansi, this narration shows how the Prophet (صلى الله عليه وسلم) explained what he saw without leaving the meaning open to guesswork."},"teachings":["The Prophet (صلى الله عليه وسلم) interpreted this dream himself, so the meaning is taken from his words.","The two wristbands were linked in the text to Musailimah and ‘Ansi.","Not every dream symbol should be explained by guesswork.","The hadith warns by naming two liars in the Prophet’s interpretation."],"related_hadiths":[{"id":"3918","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3921","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3926","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gold Wristbands and False Claimants","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains the Prophet’s dream of two gold wristbands and his interpretation of them as Musailimah and Ansi."},"heading":{"title":"Hadith About Dream Interpretation: Gold Wristbands and the Two Liars","description":"This hadith about dream interpretation is short, but its meaning is very direct. The Messenger of Allah (صلى الله عليه وسلم) said that he saw two wristbands of gold on his arms. He then blew into them, and he interpreted them as two liars: Musailimah and ‘Ansi. The core point is not a general rule about every dream with gold. It is the Prophet’s own dream and his own explanation of it. The hadith uses simple symbols: two gold wristbands, an action of blowing, and then the named meaning. For readers searching for the hadith of Musailimah and Ansi, this narration shows how the Prophet (صلى الله عليه وسلم) explained what he saw without leaving the meaning open to guesswork."},"teachings":["The Prophet (صلى الله عليه وسلم) interpreted this dream himself, so the meaning is taken from his words.","The two wristbands were linked in the text to Musailimah and ‘Ansi.","Not every dream symbol should be explained by guesswork.","The hadith warns by naming two liars in the Prophet’s interpretation."],"related_hadiths":[{"id":"3918","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3921","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3926","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E405" s="4" t="n"/>
@@ -9824,7 +9828,7 @@
       </c>
       <c r="D406" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umm Fadl Dream and Mercy to a Child","description":"$book_name$ $hadith_number$ - $chapter_name$. See how Umm Fadl’s dream was explained as good news and how the Prophet showed care when a child was struck."},"heading":{"title":"Hadith About Umm Fadl’s Dream and Kindness to Children","description":"This hadith about Umm Fadl’s dream brings together dream interpretation and gentle treatment of a child. Umm Fadl told the Messenger of Allah (صلى الله عليه وسلم) that she saw, as if in a dream, one of his limbs in her house. He replied that she had seen good and said Fatimah would give birth to a boy and Umm Fadl would breastfeed him. The narration then mentions that Fatimah gave birth to Husain or Hasan, and Umm Fadl breastfed him. Later she brought the child to the Prophet (صلى الله عليه وسلم), placed him in his lap, and he urinated. When she struck his shoulder, the Prophet (صلى الله عليه وسلم) told her, “You have hurt my son, may Allah have mercy on you.” The clear lesson is care, mercy, and avoiding harshness with a small child."},"teachings":["Good news in the dream was explained by the Prophet (صلى الله عليه وسلم) himself.","The narration shows the Prophet’s close care for his family.","A small child should not be treated harshly for something like urinating.","The Prophet (صلى الله عليه وسلم) corrected Umm Fadl while also making a prayer of mercy for her."],"related_hadiths":[{"id":"3918","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3920","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3921","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umm Fadl Dream and Mercy to a Child","description":"$book_name$ $hadith_number$ - $chapter_name$. See how Umm Fadl’s dream was explained as good news and how the Prophet showed care when a child was struck."},"heading":{"title":"Hadith About Umm Fadl’s Dream and Kindness to Children","description":"This hadith about Umm Fadl’s dream brings together dream interpretation and gentle treatment of a child. Umm Fadl told the Messenger of Allah (صلى الله عليه وسلم) that she saw, as if in a dream, one of his limbs in her house. He replied that she had seen good and said Fatimah would give birth to a boy and Umm Fadl would breastfeed him. The narration then mentions that Fatimah gave birth to Husain or Hasan, and Umm Fadl breastfed him. Later she brought the child to the Prophet (صلى الله عليه وسلم), placed him in his lap, and he urinated. When she struck his shoulder, the Prophet (صلى الله عليه وسلم) told her, “You have hurt my son, may Allah have mercy on you.” The clear lesson is care, mercy, and avoiding harshness with a small child."},"teachings":["Good news in the dream was explained by the Prophet (صلى الله عليه وسلم) himself.","The narration shows the Prophet’s close care for his family.","A small child should not be treated harshly for something like urinating.","The Prophet (صلى الله عليه وسلم) corrected Umm Fadl while also making a prayer of mercy for her."],"related_hadiths":[{"id":"3918","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3920","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3921","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E406" s="4" t="n"/>
@@ -9847,7 +9851,7 @@
       </c>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Epidemic Leaving Madinah","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows the Prophet’s dream of a woman leaving Madinah and his interpretation of an epidemic moving to Juhfah."},"heading":{"title":"Hadith About Dream Interpretation and an Epidemic Leaving Madinah","description":"This hadith about dream interpretation mentions a dream of the Prophet (صلى الله عليه وسلم) concerning Madinah. He saw a black woman with disheveled hair leaving Al-Madinah and going to Al-Mahya’ah, which is Juhfah. He then interpreted that dream as an epidemic in Al-Madinah being moved to Juhfah. The narration does not give extra details about the illness, its time, or a legal ruling. It simply reports the dream and the Prophet’s explanation. For people searching for the hadith about epidemic in Madinah, the safe way to read it is to stay with the wording: a dream was seen, a place was named, and the meaning given was that the epidemic moved from Madinah to Juhfah."},"teachings":["The Prophet (صلى الله عليه وسلم) gave the interpretation of the dream, so the meaning is taken from his words.","The dream connects Madinah, Juhfah, and the moving of an epidemic.","The text does not invite guessing beyond the stated interpretation.","The narration shows that some dreams were explained with specific meanings."],"related_hadiths":[{"id":"3918","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3921","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3926","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Epidemic Leaving Madinah","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows the Prophet’s dream of a woman leaving Madinah and his interpretation of an epidemic moving to Juhfah."},"heading":{"title":"Hadith About Dream Interpretation and an Epidemic Leaving Madinah","description":"This hadith about dream interpretation mentions a dream of the Prophet (صلى الله عليه وسلم) concerning Madinah. He saw a black woman with disheveled hair leaving Al-Madinah and going to Al-Mahya’ah, which is Juhfah. He then interpreted that dream as an epidemic in Al-Madinah being moved to Juhfah. The narration does not give extra details about the illness, its time, or a legal ruling. It simply reports the dream and the Prophet’s explanation. For people searching for the hadith about epidemic in Madinah, the safe way to read it is to stay with the wording: a dream was seen, a place was named, and the meaning given was that the epidemic moved from Madinah to Juhfah."},"teachings":["The Prophet (صلى الله عليه وسلم) gave the interpretation of the dream, so the meaning is taken from his words.","The dream connects Madinah, Juhfah, and the moving of an epidemic.","The text does not invite guessing beyond the stated interpretation.","The narration shows that some dreams were explained with specific meanings."],"related_hadiths":[{"id":"3918","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3921","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3926","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E407" s="4" t="n"/>
@@ -9870,7 +9874,7 @@
       </c>
       <c r="D408" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Value of One More Ramadan","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows how another year of fasting Ramadan and prayer raised the rank of the man who died later."},"heading":{"title":"Hadith About Ramadan, Prayer, and the Value of Extra Life","description":"This hadith about Ramadan and prayer shows how a year of worship can matter greatly. Two men became Muslim together. One worked harder, went out to fight, and was martyred. The other lived one more year and then died. Talhah saw in a dream that the man who died later was admitted to Paradise before the martyr, and people were amazed. The Messenger of Allah (صلى الله عليه وسلم) asked why they were amazed. He pointed out that the second man lived another year, reached Ramadan and fasted it, and offered many prayers during that year. Then he said the difference between them was greater than the distance between heaven and earth. The hadith does not reduce the rank of martyrdom; it highlights the great value of extra time used in fasting and prayer."},"teachings":["A longer life can be a great gift when it includes worship.","Fasting Ramadan is named as a reason for the man’s raised standing in this report.","Regular prayer across a year is shown as weighty and meaningful.","People may be surprised by Allah’s reward, but the Prophet (صلى الله عليه وسلم) explained the reason in this case."],"related_hadiths":[{"id":"3919","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3920","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3921","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Value of One More Ramadan","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows how another year of fasting Ramadan and prayer raised the rank of the man who died later."},"heading":{"title":"Hadith About Ramadan, Prayer, and the Value of Extra Life","description":"This hadith about Ramadan and prayer shows how a year of worship can matter greatly. Two men became Muslim together. One worked harder, went out to fight, and was martyred. The other lived one more year and then died. Talhah saw in a dream that the man who died later was admitted to Paradise before the martyr, and people were amazed. The Messenger of Allah (صلى الله عليه وسلم) asked why they were amazed. He pointed out that the second man lived another year, reached Ramadan and fasted it, and offered many prayers during that year. Then he said the difference between them was greater than the distance between heaven and earth. The hadith does not reduce the rank of martyrdom; it highlights the great value of extra time used in fasting and prayer."},"teachings":["A longer life can be a great gift when it includes worship.","Fasting Ramadan is named as a reason for the man’s raised standing in this report.","Regular prayer across a year is shown as weighty and meaningful.","People may be surprised by Allah’s reward, but the Prophet (صلى الله عليه وسلم) explained the reason in this case."],"related_hadiths":[{"id":"3919","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3920","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3921","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E408" s="4" t="n"/>
@@ -9893,7 +9897,7 @@
       </c>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fetters as Firmness in Religion","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration contrasts a disliked chain around the neck with fetters on the feet as a sign of firmness in religion."},"heading":{"title":"Hadith About Dream Symbols and Steadfastness in Religion","description":"This hadith about dream symbols focuses on two images: a chain around the neck and fetters on the feet. The Messenger of Allah (صلى الله عليه وسلم) said that he disliked seeing a chain around the neck, but liked seeing fetters on the feet, because fetters represent steadfastness in religion. The narration is brief, so the explanation should also stay careful. It does not give a wide dream dictionary or say that every person may interpret dreams freely. It simply tells us how this symbol is described in this report. For someone looking for a hadith about steadfastness in religion, the phrase “fetters represent steadfastness” is the main teaching. The heart of it is firmness, staying put, and holding steady in faith."},"teachings":["The hadith directly links fetters in a dream with steadfastness in religion.","The Prophet (صلى الله عليه وسلم) disliked the image of a chain around the neck in a dream.","The narration teaches caution in how dream symbols are understood.","Firmness in religion is presented as something good and loved in this wording."],"related_hadiths":[{"id":"3917","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3918","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3920","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fetters as Firmness in Religion","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration contrasts a disliked chain around the neck with fetters on the feet as a sign of firmness in religion."},"heading":{"title":"Hadith About Dream Symbols and Steadfastness in Religion","description":"This hadith about dream symbols focuses on two images: a chain around the neck and fetters on the feet. The Messenger of Allah (صلى الله عليه وسلم) said that he disliked seeing a chain around the neck, but liked seeing fetters on the feet, because fetters represent steadfastness in religion. The narration is brief, so the explanation should also stay careful. It does not give a wide dream dictionary or say that every person may interpret dreams freely. It simply tells us how this symbol is described in this report. For someone looking for a hadith about steadfastness in religion, the phrase “fetters represent steadfastness” is the main teaching. The heart of it is firmness, staying put, and holding steady in faith."},"teachings":["The hadith directly links fetters in a dream with steadfastness in religion.","The Prophet (صلى الله عليه وسلم) disliked the image of a chain around the neck in a dream.","The narration teaches caution in how dream symbols are understood.","Firmness in religion is presented as something good and loved in this wording."],"related_hadiths":[{"id":"3917","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3918","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3920","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E409" s="4" t="n"/>
@@ -9916,7 +9920,7 @@
       </c>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Ilaha Illallah and Protection","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that saying La ilaha illallah protects blood and wealth, while final reckoning belongs to Allah."},"heading":{"title":"Hadith About La Ilaha Illallah and the Sanctity of Life","description":"This hadith about La ilaha illallah centers on the weight of the testimony of faith. The Messenger of Allah (صلى الله عليه وسلم) said he was commanded to fight the people until they say: La ilaha illallah. Then, when they say it, their blood and wealth are protected from him, except for a right that is due from it, and their reckoning is with Allah. The wording keeps two points together. First, the outward statement is given protection in this hadith. Second, what remains hidden inside a person is left to Allah’s reckoning. The explanation should not go beyond the text into wider legal detail. The clear teaching here is the sanctity connected to the declaration of Tawhid and the fact that Allah handles the final account."},"teachings":["The testimony La ilaha illallah is treated with great seriousness in this narration.","The hadith states that blood and wealth are protected after this statement, except by due right.","Hidden reckoning belongs to Allah, not to people.","The wording teaches respect for the outward declaration of faith."],"related_hadiths":[{"id":"3928","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3929","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3930","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Ilaha Illallah and Protection","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that saying La ilaha illallah protects blood and wealth, while final reckoning belongs to Allah."},"heading":{"title":"Hadith About La Ilaha Illallah and the Sanctity of Life","description":"This hadith about La ilaha illallah centers on the weight of the testimony of faith. The Messenger of Allah (صلى الله عليه وسلم) said he was commanded to fight the people until they say: La ilaha illallah. Then, when they say it, their blood and wealth are protected from him, except for a right that is due from it, and their reckoning is with Allah. The wording keeps two points together. First, the outward statement is given protection in this hadith. Second, what remains hidden inside a person is left to Allah’s reckoning. The explanation should not go beyond the text into wider legal detail. The clear teaching here is the sanctity connected to the declaration of Tawhid and the fact that Allah handles the final account."},"teachings":["The testimony La ilaha illallah is treated with great seriousness in this narration.","The hadith states that blood and wealth are protected after this statement, except by due right.","Hidden reckoning belongs to Allah, not to people.","The wording teaches respect for the outward declaration of faith."],"related_hadiths":[{"id":"3928","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3929","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3930","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E410" s="4" t="n"/>
@@ -9939,7 +9943,7 @@
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Ilaha Illallah and Reckoning with Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration states that saying La ilaha illallah protects blood and wealth, except by due right, with Allah as judge."},"heading":{"title":"Hadith About La Ilaha Illallah and Allah’s Reckoning","description":"This hadith about La ilaha illallah is narrated from Jabir and repeats the same main meaning: when people say La ilaha illallah, their blood and wealth are protected from the Messenger of Allah (صلى الله عليه وسلم), except for a right due from it, and their reckoning will be with Allah. The power of the hadith is in its balance. It names the statement of Tawhid and then says that final judgment belongs to Allah. It also includes the phrase “except for a right that is due from it,” so the wording does not erase responsibility. For readers searching for the hadith blood and wealth are protected, this narration should be understood through its own words: the outward declaration is protected, and the hidden account is with Allah."},"teachings":["The statement of La ilaha illallah is linked with protection in the text.","The hadith still mentions a due right, so responsibility is not removed.","Final reckoning is with Allah.","The narration helps show the serious place of Tawhid in Islam."],"related_hadiths":[{"id":"3927","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3929","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3930","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Ilaha Illallah and Reckoning with Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration states that saying La ilaha illallah protects blood and wealth, except by due right, with Allah as judge."},"heading":{"title":"Hadith About La Ilaha Illallah and Allah’s Reckoning","description":"This hadith about La ilaha illallah is narrated from Jabir and repeats the same main meaning: when people say La ilaha illallah, their blood and wealth are protected from the Messenger of Allah (صلى الله عليه وسلم), except for a right due from it, and their reckoning will be with Allah. The power of the hadith is in its balance. It names the statement of Tawhid and then says that final judgment belongs to Allah. It also includes the phrase “except for a right that is due from it,” so the wording does not erase responsibility. For readers searching for the hadith blood and wealth are protected, this narration should be understood through its own words: the outward declaration is protected, and the hidden account is with Allah."},"teachings":["The statement of La ilaha illallah is linked with protection in the text.","The hadith still mentions a due right, so responsibility is not removed.","Final reckoning is with Allah.","The narration helps show the serious place of Tawhid in Islam."],"related_hadiths":[{"id":"3927","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3929","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3930","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E411" s="4" t="n"/>
@@ -9962,7 +9966,7 @@
       </c>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bearing Witness and Letting Him Go","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet asking about the testimony of faith and ordering that the man be released after affirming it."},"heading":{"title":"Hadith About Bearing Witness to La Ilaha Illallah","description":"This hadith about bearing witness to La ilaha illallah gives a clear scene. A man came and spoke privately to the Prophet (صلى الله عليه وسلم). An order was first given concerning him. When the man turned away, the Messenger of Allah (صلى الله عليه وسلم) called him back and asked whether he bore witness that none has the right to be worshiped but Allah. When the man answered yes, the Prophet (صلى الله عليه وسلم) ordered that he be let go. He then explained that he was commanded to fight the people until they say La ilaha illallah, and when they do that, their blood and wealth are forbidden to him. The main teaching is direct: the spoken testimony was treated as a reason to stop and release the man in this report."},"teachings":["The Prophet (صلى الله عليه وسلم) asked the man about the testimony of faith before the matter continued.","When the man affirmed La ilaha illallah, he was released.","The hadith links the testimony with the protection of blood and wealth.","The narration shows the Prophet (صلى الله عليه وسلم) acting on the outward statement given by the man."],"related_hadiths":[{"id":"3927","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3928","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3930","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bearing Witness and Letting Him Go","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet asking about the testimony of faith and ordering that the man be released after affirming it."},"heading":{"title":"Hadith About Bearing Witness to La Ilaha Illallah","description":"This hadith about bearing witness to La ilaha illallah gives a clear scene. A man came and spoke privately to the Prophet (صلى الله عليه وسلم). An order was first given concerning him. When the man turned away, the Messenger of Allah (صلى الله عليه وسلم) called him back and asked whether he bore witness that none has the right to be worshiped but Allah. When the man answered yes, the Prophet (صلى الله عليه وسلم) ordered that he be let go. He then explained that he was commanded to fight the people until they say La ilaha illallah, and when they do that, their blood and wealth are forbidden to him. The main teaching is direct: the spoken testimony was treated as a reason to stop and release the man in this report."},"teachings":["The Prophet (صلى الله عليه وسلم) asked the man about the testimony of faith before the matter continued.","When the man affirmed La ilaha illallah, he was released.","The hadith links the testimony with the protection of blood and wealth.","The narration shows the Prophet (صلى الله عليه وسلم) acting on the outward statement given by the man."],"related_hadiths":[{"id":"3927","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3928","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3930","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E412" s="4" t="n"/>
@@ -9985,7 +9989,7 @@
       </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wash Hands After Sleep","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught not to put one’s hand into a vessel after sleep until pouring water on it two or three times."},"heading":{"title":"Hadith About Washing Hands After Sleep Before Wudu","description":"This hadith about washing hands after sleep before wudu teaches care before using a water vessel. Abu Hurairah reported that the Messenger of Allah said that when someone wakes up from sleep, he should not put his hand into the vessel until he has poured water on it two or three times. The reason is also stated: a person does not know where his hand spent the night. The hadith is practical and easy to apply. It connects cleanliness, sleep, and ablution water. For people searching where his hand spent the night hadith, the message is not fear, but caution and cleanliness before dipping the hand into shared or stored water."},"teachings":["Wash the hand before putting it into the vessel after sleep.","The hadith gives the reason: a person may not know where the hand was during sleep.","The instruction protects the cleanliness of ablution water."],"related_hadiths":[{"id":"162","book_id":"1","label":"Sahih Bukhari"},{"id":"1","book_id":"3","label":"Sunan an-Nasai"},{"id":"105","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wash Hands After Sleep","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught not to put one’s hand into a vessel after sleep until pouring water on it two or three times."},"heading":{"title":"Hadith About Washing Hands After Sleep Before Wudu","description":"This hadith about washing hands after sleep before wudu teaches care before using a water vessel. Abu Hurairah reported that the Messenger of Allah said that when someone wakes up from sleep, he should not put his hand into the vessel until he has poured water on it two or three times. The reason is also stated: a person does not know where his hand spent the night. The hadith is practical and easy to apply. It connects cleanliness, sleep, and ablution water. For people searching where his hand spent the night hadith, the message is not fear, but caution and cleanliness before dipping the hand into shared or stored water."},"teachings":["Wash the hand before putting it into the vessel after sleep.","The hadith gives the reason: a person may not know where the hand was during sleep.","The instruction protects the cleanliness of ablution water."],"related_hadiths":[{"id":"162","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"105","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E413" s="4" t="n"/>
@@ -10008,7 +10012,7 @@
       </c>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Judge the Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against killing one who says La ilaha illallah and shows the great sanctity of the testimony."},"heading":{"title":"Hadith About La Ilaha Illallah and Not Judging the Heart","description":"This hadith about not judging the heart is one of the strongest lessons in this batch. A man in battle said, “I bear witness that none has the right to be worshipped but Allah, I am a Muslim,” yet he was killed. When the matter reached the Messenger of Allah (صلى الله عليه وسلم), he asked why the killer did not open the man’s belly to know what was in his heart. The point was not that a person can truly see a heart; the Prophet (صلى الله عليه وسلم) made clear that the man did not accept what was spoken and could not know what was hidden. The later wording says Allah wanted to show the greatness of the sanctity of La ilaha illallah. The core teaching is to honor the outward declaration and leave hearts to Allah."},"teachings":["A person’s claim of Islam in this report was not to be dismissed by guessing his hidden intent.","The Prophet (صلى الله عليه وسلم) made clear that people cannot know what is in someone’s heart.","The sanctity of La ilaha illallah is shown as very great in the narration.","The hadith warns against acting on suspicion when a person states the testimony."],"related_hadiths":[{"id":"3927","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3928","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3929","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Judge the Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against killing one who says La ilaha illallah and shows the great sanctity of the testimony."},"heading":{"title":"Hadith About La Ilaha Illallah and Not Judging the Heart","description":"This hadith about not judging the heart is one of the strongest lessons in this batch. A man in battle said, “I bear witness that none has the right to be worshipped but Allah, I am a Muslim,” yet he was killed. When the matter reached the Messenger of Allah (صلى الله عليه وسلم), he asked why the killer did not open the man’s belly to know what was in his heart. The point was not that a person can truly see a heart; the Prophet (صلى الله عليه وسلم) made clear that the man did not accept what was spoken and could not know what was hidden. The later wording says Allah wanted to show the greatness of the sanctity of La ilaha illallah. The core teaching is to honor the outward declaration and leave hearts to Allah."},"teachings":["A person’s claim of Islam in this report was not to be dismissed by guessing his hidden intent.","The Prophet (صلى الله عليه وسلم) made clear that people cannot know what is in someone’s heart.","The sanctity of La ilaha illallah is shown as very great in the narration.","The hadith warns against acting on suspicion when a person states the testimony."],"related_hadiths":[{"id":"3927","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3928","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3929","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E414" s="4" t="n"/>
@@ -10031,7 +10035,7 @@
       </c>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sacred Blood and Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. This Farewell Pilgrimage sermon teaches that Muslim blood and wealth are sacred like the sacred day, month, and land."},"heading":{"title":"Hadith About Sacred Blood and Wealth in the Farewell Pilgrimage","description":"This hadith about sacred blood and wealth comes from the Prophet’s words during the Farewell Pilgrimage. He asked about the sacredness of that day, that month, and that land. He then said that the people’s blood and wealth were sacred to them like the sanctity of that day in that month in that land. After conveying this, he asked, “Have I not conveyed?” They said yes, and he called Allah to bear witness. The hadith is direct and powerful. It teaches that life and property are not small matters. For readers searching for a hadith about the sanctity of Muslim blood and wealth, this narration states the idea in plain words and ties it to a deeply sacred time and place."},"teachings":["Human life and wealth are described as sacred in this sermon.","The Prophet (صلى الله عليه وسلم) compared that sanctity to the sacred day, month, and land.","The message was openly conveyed to those present.","The Prophet (صلى الله عليه وسلم) called Allah to witness after the people confirmed the message."],"related_hadiths":[{"id":"3932","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3933","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3934","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sacred Blood and Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. This Farewell Pilgrimage sermon teaches that Muslim blood and wealth are sacred like the sacred day, month, and land."},"heading":{"title":"Hadith About Sacred Blood and Wealth in the Farewell Pilgrimage","description":"This hadith about sacred blood and wealth comes from the Prophet’s words during the Farewell Pilgrimage. He asked about the sacredness of that day, that month, and that land. He then said that the people’s blood and wealth were sacred to them like the sanctity of that day in that month in that land. After conveying this, he asked, “Have I not conveyed?” They said yes, and he called Allah to bear witness. The hadith is direct and powerful. It teaches that life and property are not small matters. For readers searching for a hadith about the sanctity of Muslim blood and wealth, this narration states the idea in plain words and ties it to a deeply sacred time and place."},"teachings":["Human life and wealth are described as sacred in this sermon.","The Prophet (صلى الله عليه وسلم) compared that sanctity to the sacred day, month, and land.","The message was openly conveyed to those present.","The Prophet (صلى الله عليه وسلم) called Allah to witness after the people confirmed the message."],"related_hadiths":[{"id":"3932","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3933","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3934","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E415" s="4" t="n"/>
@@ -10054,7 +10058,7 @@
       </c>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blood Wealth and Honor Are Sacred","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that the whole Muslim is sacred to another Muslim: blood, wealth, and honor."},"heading":{"title":"Hadith About Muslim Blood, Wealth, and Honor Being Sacred","description":"This hadith about Muslim blood, wealth, and honor is simple and easy to remember. The Messenger of Allah (صلى الله عليه وسلم) said that the whole of the Muslim is sacred to his fellow Muslim: his blood, his wealth, and his honor. The hadith does not list many examples, but its three words cover major parts of daily life. Blood points to safety of life. Wealth points to property and what belongs to a person. Honor points to dignity and reputation. The wording teaches Muslims to be careful not only with physical harm, but also with taking what is not theirs and harming someone’s good name. For readers looking up “the whole Muslim is sacred hadith,” this is the core message: a Muslim is not an easy target for harm."},"teachings":["A Muslim’s life is sacred to another Muslim.","A Muslim’s wealth is not to be treated carelessly or taken wrongly.","A Muslim’s honor and reputation are included in the sanctity mentioned.","The hadith gives a short rule that covers speech, actions, and dealings."],"related_hadiths":[{"id":"3931","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3932","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3934","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blood Wealth and Honor Are Sacred","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that the whole Muslim is sacred to another Muslim: blood, wealth, and honor."},"heading":{"title":"Hadith About Muslim Blood, Wealth, and Honor Being Sacred","description":"This hadith about Muslim blood, wealth, and honor is simple and easy to remember. The Messenger of Allah (صلى الله عليه وسلم) said that the whole of the Muslim is sacred to his fellow Muslim: his blood, his wealth, and his honor. The hadith does not list many examples, but its three words cover major parts of daily life. Blood points to safety of life. Wealth points to property and what belongs to a person. Honor points to dignity and reputation. The wording teaches Muslims to be careful not only with physical harm, but also with taking what is not theirs and harming someone’s good name. For readers looking up “the whole Muslim is sacred hadith,” this is the core message: a Muslim is not an easy target for harm."},"teachings":["A Muslim’s life is sacred to another Muslim.","A Muslim’s wealth is not to be treated carelessly or taken wrongly.","A Muslim’s honor and reputation are included in the sanctity mentioned.","The hadith gives a short rule that covers speech, actions, and dealings."],"related_hadiths":[{"id":"3931","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3932","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3934","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E416" s="4" t="n"/>
@@ -10077,7 +10081,7 @@
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Believer as a Source of Safety","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith defines the believer as one from whom people’s lives and wealth are safe, and the Muhajir as one who leaves sins."},"heading":{"title":"Hadith About the True Believer and Safety from Harm","description":"This hadith about the true believer gives a practical sign of faith. The Prophet (صلى الله عليه وسلم) said that the believer is the one from whom people’s wealth and lives are safe. He also said that the Muhajir is the one who forsakes mistakes and sins. The wording makes faith visible in how safe others feel around a person. It does not only speak about claims or labels. It points to trust: people are not afraid for their lives or property from a believer. The second part gives the word Muhajir a moral meaning in this narration: leaving mistakes and sins. For people searching for “the believer is one from whom people are safe,” this hadith explains faith through safety, self-control, and leaving wrong actions."},"teachings":["A believer should be a source of safety for people’s lives.","People’s wealth should also be safe from a believer’s harm.","The Muhajir is described here as one who leaves mistakes and sins.","Faith is shown through real conduct, not only words."],"related_hadiths":[{"id":"3931","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3932","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3933","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Believer as a Source of Safety","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith defines the believer as one from whom people’s lives and wealth are safe, and the Muhajir as one who leaves sins."},"heading":{"title":"Hadith About the True Believer and Safety from Harm","description":"This hadith about the true believer gives a practical sign of faith. The Prophet (صلى الله عليه وسلم) said that the believer is the one from whom people’s wealth and lives are safe. He also said that the Muhajir is the one who forsakes mistakes and sins. The wording makes faith visible in how safe others feel around a person. It does not only speak about claims or labels. It points to trust: people are not afraid for their lives or property from a believer. The second part gives the word Muhajir a moral meaning in this narration: leaving mistakes and sins. For people searching for “the believer is one from whom people are safe,” this hadith explains faith through safety, self-control, and leaving wrong actions."},"teachings":["A believer should be a source of safety for people’s lives.","People’s wealth should also be safe from a believer’s harm.","The Muhajir is described here as one who leaves mistakes and sins.","Faith is shown through real conduct, not only words."],"related_hadiths":[{"id":"3931","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3932","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3933","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E417" s="4" t="n"/>
@@ -10100,7 +10104,7 @@
       </c>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Open Plunder Is Not from Us","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns that whoever openly plunders is not one of the Prophet’s way."},"heading":{"title":"Hadith About Plunder: Whoever Plunders Openly Is Not One of Us","description":"This hadith about plunder is brief and serious. The Messenger of Allah (صلى الله عليه وسلم) said, “Whoever plunders openly is not one of us.” The wording points to taking property by open force or public grabbing. The hadith does not add a long story here, but the warning is clear. A Muslim cannot treat other people’s property as something to snatch while people watch. For readers searching for “whoever plunders is not one of us hadith,” the main teaching is that open plunder is not a small mistake in this wording. It is spoken of in a way that distances the act from the Prophet’s path. The lesson stays close to the text: do not take what is not yours by plunder."},"teachings":["Open plunder is strongly condemned in this hadith.","The phrase “not one of us” shows the act is far from the Prophet’s way.","The narration protects people’s property from public grabbing.","The hadith teaches restraint even when a person has the chance to take by force."],"related_hadiths":[{"id":"3936","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3937","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3938","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Open Plunder Is Not from Us","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns that whoever openly plunders is not one of the Prophet’s way."},"heading":{"title":"Hadith About Plunder: Whoever Plunders Openly Is Not One of Us","description":"This hadith about plunder is brief and serious. The Messenger of Allah (صلى الله عليه وسلم) said, “Whoever plunders openly is not one of us.” The wording points to taking property by open force or public grabbing. The hadith does not add a long story here, but the warning is clear. A Muslim cannot treat other people’s property as something to snatch while people watch. For readers searching for “whoever plunders is not one of us hadith,” the main teaching is that open plunder is not a small mistake in this wording. It is spoken of in a way that distances the act from the Prophet’s path. The lesson stays close to the text: do not take what is not yours by plunder."},"teachings":["Open plunder is strongly condemned in this hadith.","The phrase “not one of us” shows the act is far from the Prophet’s way.","The narration protects people’s property from public grabbing.","The hadith teaches restraint even when a person has the chance to take by force."],"related_hadiths":[{"id":"3936","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3937","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3938","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E418" s="4" t="n"/>
@@ -10123,7 +10127,7 @@
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sins That Clash with Faith","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns that adultery, drinking, stealing, and public plunder clash with the state of faith while being committed."},"heading":{"title":"Hadith About Major Sins and Faith at the Time of Sin","description":"This hadith about major sins names several actions and links them to the state of faith while they are being done. The Messenger of Allah (صلى الله عليه وسلم) said that the adulterer is not a believer at the time of adultery, the drinker is not a believer at the time of drinking, the thief is not a believer at the time of stealing, and the plunderer is not a believer at the time he plunders while people look on. The wording is about the time of committing those acts. The safe explanation is to stay with that phrasing and not make extra claims beyond it. The hadith makes these sins feel heavy, not casual. It warns the believer to step back before desire, theft, drink, or public plunder pulls him into a dangerous act."},"teachings":["The hadith names adultery, drinking, theft, and public plunder as serious sins.","It speaks about the person’s state at the time the sin is being committed.","The warning is meant to make these actions feel weighty, not normal.","Public plunder is included among actions that clash with faith in this report."],"related_hadiths":[{"id":"3935","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3937","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3938","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sins That Clash with Faith","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns that adultery, drinking, stealing, and public plunder clash with the state of faith while being committed."},"heading":{"title":"Hadith About Major Sins and Faith at the Time of Sin","description":"This hadith about major sins names several actions and links them to the state of faith while they are being done. The Messenger of Allah (صلى الله عليه وسلم) said that the adulterer is not a believer at the time of adultery, the drinker is not a believer at the time of drinking, the thief is not a believer at the time of stealing, and the plunderer is not a believer at the time he plunders while people look on. The wording is about the time of committing those acts. The safe explanation is to stay with that phrasing and not make extra claims beyond it. The hadith makes these sins feel heavy, not casual. It warns the believer to step back before desire, theft, drink, or public plunder pulls him into a dangerous act."},"teachings":["The hadith names adultery, drinking, theft, and public plunder as serious sins.","It speaks about the person’s state at the time the sin is being committed.","The warning is meant to make these actions feel weighty, not normal.","Public plunder is included among actions that clash with faith in this report."],"related_hadiths":[{"id":"3935","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3937","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3938","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E419" s="4" t="n"/>
@@ -10146,7 +10150,7 @@
       </c>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Whoever Plunders Is Not One of Us","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration gives a short warning against plunder and distances it from the Prophet’s way."},"heading":{"title":"Hadith About Plunder Not Being from the Prophet’s Way","description":"This hadith about plunder is a short narration from ‘Imran bin Husain. The Messenger of Allah (صلى الله عليه وسلم) said, “Whoever plunders is not one of us.” The wording is even shorter than the narration that mentions open plunder, but the meaning is direct. Plunder means taking by force or grabbing what is not rightfully taken. The hadith does not give exceptions or a story in this version, so the explanation should not add one. It teaches that plunder is not part of the conduct linked with the Prophet (صلى الله عليه وسلم). For readers searching for the hadith on plunder in Islam, this report gives a plain moral line: do not join in taking property through plunder."},"teachings":["Plunder is clearly warned against in this narration.","The phrase “not one of us” distances the act from the Prophet’s way.","The hadith protects property from forceful taking.","The short wording makes the message easy to remember and act on."],"related_hadiths":[{"id":"3935","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3936","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3938","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Whoever Plunders Is Not One of Us","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration gives a short warning against plunder and distances it from the Prophet’s way."},"heading":{"title":"Hadith About Plunder Not Being from the Prophet’s Way","description":"This hadith about plunder is a short narration from ‘Imran bin Husain. The Messenger of Allah (صلى الله عليه وسلم) said, “Whoever plunders is not one of us.” The wording is even shorter than the narration that mentions open plunder, but the meaning is direct. Plunder means taking by force or grabbing what is not rightfully taken. The hadith does not give exceptions or a story in this version, so the explanation should not add one. It teaches that plunder is not part of the conduct linked with the Prophet (صلى الله عليه وسلم). For readers searching for the hadith on plunder in Islam, this report gives a plain moral line: do not join in taking property through plunder."},"teachings":["Plunder is clearly warned against in this narration.","The phrase “not one of us” distances the act from the Prophet’s way.","The hadith protects property from forceful taking.","The short wording makes the message easy to remember and act on."],"related_hadiths":[{"id":"3935","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3936","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3938","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E420" s="4" t="n"/>
@@ -10169,7 +10173,7 @@
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Plunder Is Not Permissible","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet stopping plundered sheep from being cooked and saying that plunder is not permissible."},"heading":{"title":"Hadith About Plunder Not Being Permissible","description":"This hadith about plunder not being permissible gives a clear example. Tha’labah bin Hakam said they came across some of the enemy’s sheep, plundered them, and set up cooking pots. The Prophet (صلى الله عليه وسلم) passed by the pots and ordered that they be overturned. Then he said, “Plunder is not permissible.” The action and the words go together. He did not only give a warning after the food was eaten; he stopped the use of what had been taken by plunder. The narration is useful for readers searching for “plunder is not halal hadith” or “plunder is not permissible hadith.” The lesson is plain from the text: taking goods through plunder is not allowed, and benefit from such taking was stopped in that scene."},"teachings":["The Prophet (صلى الله عليه وسلم) stopped the cooking pots connected to the plundered sheep.","The hadith states plainly that plunder is not permissible.","The narration shows action was taken, not just words spoken.","Property taken by plunder was not treated as a normal benefit in this event."],"related_hadiths":[{"id":"3935","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3936","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3937","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Plunder Is Not Permissible","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet stopping plundered sheep from being cooked and saying that plunder is not permissible."},"heading":{"title":"Hadith About Plunder Not Being Permissible","description":"This hadith about plunder not being permissible gives a clear example. Tha’labah bin Hakam said they came across some of the enemy’s sheep, plundered them, and set up cooking pots. The Prophet (صلى الله عليه وسلم) passed by the pots and ordered that they be overturned. Then he said, “Plunder is not permissible.” The action and the words go together. He did not only give a warning after the food was eaten; he stopped the use of what had been taken by plunder. The narration is useful for readers searching for “plunder is not halal hadith” or “plunder is not permissible hadith.” The lesson is plain from the text: taking goods through plunder is not allowed, and benefit from such taking was stopped in that scene."},"teachings":["The Prophet (صلى الله عليه وسلم) stopped the cooking pots connected to the plundered sheep.","The hadith states plainly that plunder is not permissible.","The narration shows action was taken, not just words spoken.","Property taken by plunder was not treated as a normal benefit in this event."],"related_hadiths":[{"id":"3935","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3936","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3937","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E421" s="4" t="n"/>
@@ -10192,7 +10196,7 @@
       </c>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Verbal Abuse and Fighting a Muslim","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns that verbally abusing a Muslim is disobedience and fighting him is kufr in the wording of the report."},"heading":{"title":"Hadith About Verbally Abusing a Muslim and Fighting Him","description":"This hadith about verbally abusing a Muslim is short, but it carries a strong warning. The Messenger of Allah (صلى الله عليه وسلم) said that verbally abusing a Muslim is Fusuq, meaning disobedience, and fighting him is Kufr, described here as ungratefulness to Allah. The hadith does not give a long list of insults or conflicts. It places two harmful actions in clear terms: abuse with the tongue and fighting with the hand. For readers searching for “sabab al Muslim fusuq hadith,” the message is that a Muslim’s honor and safety are not to be treated lightly. Words can be sinful, and fighting a Muslim is spoken of with even heavier wording in this narration."},"teachings":["Verbal abuse of a Muslim is called Fusuq in this hadith.","Fighting a Muslim is described with the serious word Kufr in this wording.","The narration warns against harm by speech and by violence.","A Muslim’s honor and safety should be treated with care."],"related_hadiths":[{"id":"3940","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3933","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3931","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Verbal Abuse and Fighting a Muslim","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns that verbally abusing a Muslim is disobedience and fighting him is kufr in the wording of the report."},"heading":{"title":"Hadith About Verbally Abusing a Muslim and Fighting Him","description":"This hadith about verbally abusing a Muslim is short, but it carries a strong warning. The Messenger of Allah (صلى الله عليه وسلم) said that verbally abusing a Muslim is Fusuq, meaning disobedience, and fighting him is Kufr, described here as ungratefulness to Allah. The hadith does not give a long list of insults or conflicts. It places two harmful actions in clear terms: abuse with the tongue and fighting with the hand. For readers searching for “sabab al Muslim fusuq hadith,” the message is that a Muslim’s honor and safety are not to be treated lightly. Words can be sinful, and fighting a Muslim is spoken of with even heavier wording in this narration."},"teachings":["Verbal abuse of a Muslim is called Fusuq in this hadith.","Fighting a Muslim is described with the serious word Kufr in this wording.","The narration warns against harm by speech and by violence.","A Muslim’s honor and safety should be treated with care."],"related_hadiths":[{"id":"3940","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3933","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3931","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E422" s="4" t="n"/>
@@ -10215,7 +10219,7 @@
       </c>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Clean Hands Before Vessel","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that after waking from sleep, a person should not put his hand into the vessel until washing it."},"heading":{"title":"Hadith on Washing Hands Before Putting Them in Water","description":"This hadith on washing hands before putting them in water gives the same core teaching in a shorter form. The Messenger of Allah said that when anyone wakes from sleep, he should not put his hand into the vessel until he has washed it. The wording is direct and practical. It is about keeping the water vessel clean before using it for purification. The narration does not mention a long list of steps, so the explanation should stay with the text: wake from sleep, wash the hand, then use the vessel. For readers searching for hand washing before wudu hadith, this report shows the careful manner taught by the Prophet when dealing with water after sleep."},"teachings":["Do not place the hand into the vessel right after waking until it is washed.","The teaching is tied to sleep and the use of water containers.","Cleanliness begins before the main act of ablution."],"related_hadiths":[{"id":"162","book_id":"1","label":"Sahih Bukhari"},{"id":"1","book_id":"3","label":"Sunan an-Nasai"},{"id":"105","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Clean Hands Before Vessel","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that after waking from sleep, a person should not put his hand into the vessel until washing it."},"heading":{"title":"Hadith on Washing Hands Before Putting Them in Water","description":"This hadith on washing hands before putting them in water gives the same core teaching in a shorter form. The Messenger of Allah said that when anyone wakes from sleep, he should not put his hand into the vessel until he has washed it. The wording is direct and practical. It is about keeping the water vessel clean before using it for purification. The narration does not mention a long list of steps, so the explanation should stay with the text: wake from sleep, wash the hand, then use the vessel. For readers searching for hand washing before wudu hadith, this report shows the careful manner taught by the Prophet when dealing with water after sleep."},"teachings":["Do not place the hand into the vessel right after waking until it is washed.","The teaching is tied to sleep and the use of water containers.","Cleanliness begins before the main act of ablution."],"related_hadiths":[{"id":"162","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"105","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E423" s="4" t="n"/>
@@ -10238,7 +10242,7 @@
       </c>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Insulting and Fighting a Muslim","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration repeats the warning that abusing a Muslim is disobedience and fighting him is kufr."},"heading":{"title":"Hadith About Insulting a Muslim and the Danger of Fighting","description":"This hadith about insulting a Muslim repeats the same clear warning narrated from Abu Hurairah. The Prophet (صلى الله عليه وسلم) said that verbally abusing a Muslim is Fusuq, or disobedience, and fighting him is Kufr, described in the translation as ungratefulness to Allah. The hadith is not long, so its message should not be made complicated. It tells Muslims to take their words seriously and to avoid turning conflict into abuse or fighting. For search terms like “verbally abusing a Muslim is fusuq” and “fighting a Muslim is kufr,” this narration gives a direct phrase that is easy to memorize. The core teaching is respect for a Muslim’s dignity, safety, and rights in speech and action."},"teachings":["Abusing a Muslim with words is named as Fusuq in the narration.","Fighting a Muslim is described with very serious wording.","The hadith encourages restraint before speech becomes sinful.","The report protects both a Muslim’s dignity and physical safety."],"related_hadiths":[{"id":"3939","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3933","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3931","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Insulting and Fighting a Muslim","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration repeats the warning that abusing a Muslim is disobedience and fighting him is kufr."},"heading":{"title":"Hadith About Insulting a Muslim and the Danger of Fighting","description":"This hadith about insulting a Muslim repeats the same clear warning narrated from Abu Hurairah. The Prophet (صلى الله عليه وسلم) said that verbally abusing a Muslim is Fusuq, or disobedience, and fighting him is Kufr, described in the translation as ungratefulness to Allah. The hadith is not long, so its message should not be made complicated. It tells Muslims to take their words seriously and to avoid turning conflict into abuse or fighting. For search terms like “verbally abusing a Muslim is fusuq” and “fighting a Muslim is kufr,” this narration gives a direct phrase that is easy to memorize. The core teaching is respect for a Muslim’s dignity, safety, and rights in speech and action."},"teachings":["Abusing a Muslim with words is named as Fusuq in the narration.","Fighting a Muslim is described with very serious wording.","The hadith encourages restraint before speech becomes sinful.","The report protects both a Muslim’s dignity and physical safety."],"related_hadiths":[{"id":"3939","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3933","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3931","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E424" s="4" t="n"/>
@@ -10261,7 +10265,7 @@
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Fight One Another After the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. A strong Farewell Pilgrimage warning against Muslims returning to disbelief by striking one another’s necks."},"heading":{"title":"Do Not Turn Back as Disbelievers: Hadith on Muslim Unity","description":"This Hadith is often searched as do not turn back into disbelievers hadith. The Prophet (صلى الله عليه وسلم) said it during the Farewell Pilgrimage after asking that the people be made attentive. That setting in the text shows the weight of the warning. The teaching is simple and serious: Muslims must not fall into fighting one another after him. The phrase about striking one another’s necks points to violent conflict, not a small disagreement. The Hadith does not ask us to ignore truth or pretend there are no disputes. It warns against turning disagreement into bloodshed. Its core lesson is Muslim unity, restraint, and listening carefully when a serious warning is given."},"teachings":["Important religious warnings should be heard with attention.","Muslims are warned not to turn conflict into violence.","Fighting one another is described with very severe language.","Unity after the Prophet (صلى الله عليه وسلم) is treated as a serious trust."],"related_hadiths":[{"id":"3943","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3944","book_id":"6","label":"Sunan Ibn Majah"},{"id":"65","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Fight One Another After the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. A strong Farewell Pilgrimage warning against Muslims returning to disbelief by striking one another’s necks."},"heading":{"title":"Do Not Turn Back as Disbelievers: Hadith on Muslim Unity","description":"This Hadith is often searched as do not turn back into disbelievers hadith. The Prophet (صلى الله عليه وسلم) said it during the Farewell Pilgrimage after asking that the people be made attentive. That setting in the text shows the weight of the warning. The teaching is simple and serious: Muslims must not fall into fighting one another after him. The phrase about striking one another’s necks points to violent conflict, not a small disagreement. The Hadith does not ask us to ignore truth or pretend there are no disputes. It warns against turning disagreement into bloodshed. Its core lesson is Muslim unity, restraint, and listening carefully when a serious warning is given."},"teachings":["Important religious warnings should be heard with attention.","Muslims are warned not to turn conflict into violence.","Fighting one another is described with very severe language.","Unity after the Prophet (صلى الله عليه وسلم) is treated as a serious trust."],"related_hadiths":[{"id":"3943","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3944","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"65","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E425" s="4" t="n"/>
@@ -10284,7 +10288,7 @@
       </c>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Morning Prayer and Allah’s Protection","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever offers the morning prayer is under Allah’s protection, and harming him is warned against in severe terms."},"heading":{"title":"Fajr Prayer Protection Hadith: Under the Protection of Allah","description":"This Hadith is searched often as Fajr prayer protection hadith. It says that whoever offers the morning prayer is under the protection of Allah. The text then gives a strong warning: do not betray Allah by betraying someone under His protection. It also mentions the severe outcome for the one who kills such a person. The Hadith is not a general slogan about every comfort in life. It speaks specifically about the morning prayer and the protected status mentioned by the Prophet (صلى الله عليه وسلم). It teaches respect for those who pray and warns against harming them. For daily life, it also reminds a Muslim that Fajr is not only a routine act, but a prayer tied to a serious covenant of safety."},"teachings":["Offering the morning prayer is linked to being under Allah’s protection.","Harming someone under that protection is warned against severely.","The Hadith gives special weight to the Fajr prayer.","A Muslim should respect the safety of those who pray."],"related_hadiths":[{"id":"3946","book_id":"6","label":"Sunan Ibn Majah"},{"id":"657","book_id":"2","label":"Sahih Muslim"},{"id":"3947","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Morning Prayer and Allah’s Protection","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever offers the morning prayer is under Allah’s protection, and harming him is warned against in severe terms."},"heading":{"title":"Fajr Prayer Protection Hadith: Under the Protection of Allah","description":"This Hadith is searched often as Fajr prayer protection hadith. It says that whoever offers the morning prayer is under the protection of Allah. The text then gives a strong warning: do not betray Allah by betraying someone under His protection. It also mentions the severe outcome for the one who kills such a person. The Hadith is not a general slogan about every comfort in life. It speaks specifically about the morning prayer and the protected status mentioned by the Prophet (صلى الله عليه وسلم). It teaches respect for those who pray and warns against harming them. For daily life, it also reminds a Muslim that Fajr is not only a routine act, but a prayer tied to a serious covenant of safety."},"teachings":["Offering the morning prayer is linked to being under Allah’s protection.","Harming someone under that protection is warned against severely.","The Hadith gives special weight to the Fajr prayer.","A Muslim should respect the safety of those who pray."],"related_hadiths":[{"id":"3946","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"657","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"3947","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E426" s="4" t="n"/>
@@ -10307,7 +10311,7 @@
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fajr Prayer Under Allah’s Protection","description":"$book_name$ $hadith_number$ - $chapter_name$. A concise Hadith stating that whoever offers the morning prayer is under the protection of Allah."},"heading":{"title":"Whoever Offers Fajr Is Under Allah’s Protection","description":"This short Hadith gives a message that many people search for as whoever prays Fajr is under Allah protection. The Prophet (صلى الله عليه وسلم) said that whoever offers the morning prayer is under the protection of Allah, the Mighty and Sublime. The text is brief, so we should not add details beyond it. Its strength is in its simple wording. It presents Fajr as a prayer with a special meaning for the believer’s day. The Hadith also indirectly teaches respect for the person who has entered that protection, because the related narration in the same topic warns against betraying those under it. The core message remains clear: take the morning prayer seriously and honor what Allah has honored."},"teachings":["The morning prayer is connected to Allah’s protection.","The Hadith uses short wording with a strong meaning.","Fajr should be treated as a serious daily act of worship.","A believer should honor what Allah places under His care."],"related_hadiths":[{"id":"3945","book_id":"6","label":"Sunan Ibn Majah"},{"id":"657","book_id":"2","label":"Sahih Muslim"},{"id":"3947","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fajr Prayer Under Allah’s Protection","description":"$book_name$ $hadith_number$ - $chapter_name$. A concise Hadith stating that whoever offers the morning prayer is under the protection of Allah."},"heading":{"title":"Whoever Offers Fajr Is Under Allah’s Protection","description":"This short Hadith gives a message that many people search for as whoever prays Fajr is under Allah protection. The Prophet (صلى الله عليه وسلم) said that whoever offers the morning prayer is under the protection of Allah, the Mighty and Sublime. The text is brief, so we should not add details beyond it. Its strength is in its simple wording. It presents Fajr as a prayer with a special meaning for the believer’s day. The Hadith also indirectly teaches respect for the person who has entered that protection, because the related narration in the same topic warns against betraying those under it. The core message remains clear: take the morning prayer seriously and honor what Allah has honored."},"teachings":["The morning prayer is connected to Allah’s protection.","The Hadith uses short wording with a strong meaning.","Fajr should be treated as a serious daily act of worship.","A believer should honor what Allah places under His care."],"related_hadiths":[{"id":"3945","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"657","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"3947","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E427" s="4" t="n"/>
@@ -10330,7 +10334,7 @@
       </c>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Believer Is Precious to Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. A reminder that the believer holds a precious rank before Allah, even above some of His angels."},"heading":{"title":"Hadith About the Believer Being Precious to Allah","description":"This Hadith is centered on the honor of a believer. A strong search phrase is the believer is precious to Allah hadith. The Prophet (صلى الله عليه وسلم) said that the believer is more precious to Allah, the Mighty and Sublime, than some of His angels. The text does not explain why, and it does not list conditions beyond the word believer. So the safe explanation is to keep the message simple: faith gives a person a valued standing with Allah. This should not make someone proud or careless. Rather, it should make a believer guard faith, respect other believers, and avoid treating a person of faith as worthless. The Hadith lifts the heart while also reminding us to be careful with the honor of believers."},"teachings":["A believer has a precious rank with Allah.","The Hadith encourages respect for people of faith.","This honor should lead to humility, not arrogance.","A Muslim should not treat a believer as worthless."],"related_hadiths":[{"id":"3941","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6044","book_id":"1","label":"Sahih Bukhari"},{"id":"64a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Believer Is Precious to Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. A reminder that the believer holds a precious rank before Allah, even above some of His angels."},"heading":{"title":"Hadith About the Believer Being Precious to Allah","description":"This Hadith is centered on the honor of a believer. A strong search phrase is the believer is precious to Allah hadith. The Prophet (صلى الله عليه وسلم) said that the believer is more precious to Allah, the Mighty and Sublime, than some of His angels. The text does not explain why, and it does not list conditions beyond the word believer. So the safe explanation is to keep the message simple: faith gives a person a valued standing with Allah. This should not make someone proud or careless. Rather, it should make a believer guard faith, respect other believers, and avoid treating a person of faith as worthless. The Hadith lifts the heart while also reminding us to be careful with the honor of believers."},"teachings":["A believer has a precious rank with Allah.","The Hadith encourages respect for people of faith.","This honor should lead to humility, not arrogance.","A Muslim should not treat a believer as worthless."],"related_hadiths":[{"id":"3941","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"6044","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"64a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E428" s="4" t="n"/>
@@ -10353,7 +10357,7 @@
       </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Washing Hands Before Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Before wudu after sleep, the Prophet taught not to put the hand into the ablution vessel until it has been washed."},"heading":{"title":"Hadith About Washing Hands Before Wudu After Sleep","description":"This hadith about washing hands before wudu after sleep adds another detail to the same lesson. Jabir narrated that when someone gets up from sleep and wants to perform ablution, he should not put his hand into the vessel used for wudu until he has washed it. The reason is clear: he does not know where his hand spent the night or where he put it. The narration also includes a note about the correct route of narration, but the teaching remains focused on cleanliness before using the wudu vessel. For anyone searching for wash hands before wudu hadith, this text shows a careful first step before starting ablution with stored water."},"teachings":["Wash the hand before using the wudu vessel after sleep.","The hadith explains the reason as uncertainty about where the hand was.","The teaching protects the water used for ablution."],"related_hadiths":[{"id":"162","book_id":"1","label":"Sahih Bukhari"},{"id":"1","book_id":"3","label":"Sunan an-Nasai"},{"id":"105","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Washing Hands Before Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Before wudu after sleep, the Prophet taught not to put the hand into the ablution vessel until it has been washed."},"heading":{"title":"Hadith About Washing Hands Before Wudu After Sleep","description":"This hadith about washing hands before wudu after sleep adds another detail to the same lesson. Jabir narrated that when someone gets up from sleep and wants to perform ablution, he should not put his hand into the vessel used for wudu until he has washed it. The reason is clear: he does not know where his hand spent the night or where he put it. The narration also includes a note about the correct route of narration, but the teaching remains focused on cleanliness before using the wudu vessel. For anyone searching for wash hands before wudu hadith, this text shows a careful first step before starting ablution with stored water."},"teachings":["Wash the hand before using the wudu vessel after sleep.","The hadith explains the reason as uncertainty about where the hand was.","The teaching protects the water used for ablution."],"related_hadiths":[{"id":"162","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"105","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E429" s="4" t="n"/>
@@ -10376,7 +10380,7 @@
       </c>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Follow the Great Majority During Differences","description":"$book_name$ $hadith_number$ - $chapter_name$. When disagreement appears, this Hadith points people toward the great majority and away from misguidance."},"heading":{"title":"Hadith About Following the Great Majority of the Ummah","description":"This Hadith is commonly searched as follow the great majority hadith. The Prophet (صلى الله عليه وسلم) said that his nation will not unite on misguidance, and when disagreement is seen, people should follow the great majority. The text is about difference and how to respond to it. It does not give a full rulebook for every dispute, so the explanation should stay direct. The Hadith tells a believer not to rush behind every small group or loud claim when confusion spreads. It points to staying connected to the main body of the Ummah. Its core topic is unity, caution, and avoiding isolation during religious disagreement."},"teachings":["The Ummah is not described as uniting upon misguidance.","During disagreement, the Hadith directs people toward the great majority.","A believer should be careful before following isolated claims.","The text encourages staying connected to the main body of Muslims."],"related_hadiths":[{"id":"3951","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3952","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3956","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Follow the Great Majority During Differences","description":"$book_name$ $hadith_number$ - $chapter_name$. When disagreement appears, this Hadith points people toward the great majority and away from misguidance."},"heading":{"title":"Hadith About Following the Great Majority of the Ummah","description":"This Hadith is commonly searched as follow the great majority hadith. The Prophet (صلى الله عليه وسلم) said that his nation will not unite on misguidance, and when disagreement is seen, people should follow the great majority. The text is about difference and how to respond to it. It does not give a full rulebook for every dispute, so the explanation should stay direct. The Hadith tells a believer not to rush behind every small group or loud claim when confusion spreads. It points to staying connected to the main body of the Ummah. Its core topic is unity, caution, and avoiding isolation during religious disagreement."},"teachings":["The Ummah is not described as uniting upon misguidance.","During disagreement, the Hadith directs people toward the great majority.","A believer should be careful before following isolated claims.","The text encourages staying connected to the main body of Muslims."],"related_hadiths":[{"id":"3951","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3952","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3956","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E430" s="4" t="n"/>
@@ -10399,7 +10403,7 @@
       </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | When Sin and Evil Deeds Increase","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet warned of approaching evil and explained that destruction may come when sin and evil deeds increase."},"heading":{"title":"Hadith About Gog and Magog and the Increase of Sin","description":"This Hadith is often searched as Gog and Magog hole opened hadith. The Prophet (صلى الله عليه وسلم) woke with his face red and said that an evil had drawn near. He mentioned that a hole had been opened in the barrier of Gog and Magog and showed its size with his hand. Zainab bint Jahsh then asked an important question: can people be destroyed while righteous people are among them? The Prophet (صلى الله عليه وسلم) answered, “If sin and evil deeds increase.” The Hadith does not give a full timeline, and we should not invent one. Its core teaching is that public growth of sin and evil deeds is dangerous for a society, even when righteous people are present among them."},"teachings":["The Prophet (صلى الله عليه وسلم) warned about an approaching evil.","The Hadith mentions an opening in the barrier of Gog and Magog.","The presence of righteous people does not remove concern if evil spreads.","Increasing sin and evil deeds is presented as a cause for fear."],"related_hadiths":[{"id":"3952","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3954","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3955","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | When Sin and Evil Deeds Increase","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet warned of approaching evil and explained that destruction may come when sin and evil deeds increase."},"heading":{"title":"Hadith About Gog and Magog and the Increase of Sin","description":"This Hadith is often searched as Gog and Magog hole opened hadith. The Prophet (صلى الله عليه وسلم) woke with his face red and said that an evil had drawn near. He mentioned that a hole had been opened in the barrier of Gog and Magog and showed its size with his hand. Zainab bint Jahsh then asked an important question: can people be destroyed while righteous people are among them? The Prophet (صلى الله عليه وسلم) answered, “If sin and evil deeds increase.” The Hadith does not give a full timeline, and we should not invent one. Its core teaching is that public growth of sin and evil deeds is dangerous for a society, even when righteous people are present among them."},"teachings":["The Prophet (صلى الله عليه وسلم) warned about an approaching evil.","The Hadith mentions an opening in the barrier of Gog and Magog.","The presence of righteous people does not remove concern if evil spreads.","Increasing sin and evil deeds is presented as a cause for fear."],"related_hadiths":[{"id":"3952","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3954","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3955","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E431" s="4" t="n"/>
@@ -10422,7 +10426,7 @@
       </c>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fitnah of Family, Wealth, and Wider Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. Daily personal trials are expiated by worship and good deeds, while a greater fitnah is described like waves of the sea."},"heading":{"title":"Hadith About Fitnah Like Waves of the Sea","description":"This Hadith is often searched as fitnah like waves of the sea hadith. Hudhaifah mentioned the Prophet’s words that a man’s fitnah regarding his family, children, and neighbors is expiated by prayer, fasting, charity, enjoining good, and forbidding evil. Umar then asked about a different fitnah, one that moves like waves of the sea. Hudhaifah said there was a closed door between Umar and that fitnah, and later explained that the door was Umar. The text separates two kinds of trial: personal daily tests and a wider public fitnah. It also names acts of worship and moral duty as expiation for the first type. The narration should be explained without turning the broken door into extra details not stated here."},"teachings":["Family, children, and neighbors can be areas of personal trial.","Prayer, fasting, charity, enjoining good, and forbidding evil are named as expiation.","The Hadith also speaks about a larger fitnah like sea waves.","Hudhaifah identified Umar as the closed door mentioned in the narration."],"related_hadiths":[{"id":"3956","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3957","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3954","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fitnah of Family, Wealth, and Wider Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. Daily personal trials are expiated by worship and good deeds, while a greater fitnah is described like waves of the sea."},"heading":{"title":"Hadith About Fitnah Like Waves of the Sea","description":"This Hadith is often searched as fitnah like waves of the sea hadith. Hudhaifah mentioned the Prophet’s words that a man’s fitnah regarding his family, children, and neighbors is expiated by prayer, fasting, charity, enjoining good, and forbidding evil. Umar then asked about a different fitnah, one that moves like waves of the sea. Hudhaifah said there was a closed door between Umar and that fitnah, and later explained that the door was Umar. The text separates two kinds of trial: personal daily tests and a wider public fitnah. It also names acts of worship and moral duty as expiation for the first type. The narration should be explained without turning the broken door into extra details not stated here."},"teachings":["Family, children, and neighbors can be areas of personal trial.","Prayer, fasting, charity, enjoining good, and forbidding evil are named as expiation.","The Hadith also speaks about a larger fitnah like sea waves.","Hudhaifah identified Umar as the closed door mentioned in the narration."],"related_hadiths":[{"id":"3956","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3957","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3954","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E432" s="4" t="n"/>
@@ -10445,7 +10449,7 @@
       </c>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stay Away From Killing During Fitnah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet advised Abu Dharr to be patient, stay chaste during famine, and avoid joining killing during fitnah."},"heading":{"title":"Hadith About Avoiding Killing During Fitnah","description":"This Hadith is a detailed personal advice to Abu Dharr, and people may search it as hadith stay in your house during fitnah. The Prophet (صلى الله عليه وسلم) asked what he would do when death, famine, and killing overtake people. In response to death, he said, “Be patient.” In response to famine, he said, “You must refrain from forbidden things.” When killing spreads, Abu Dharr asked if he should take his sword and strike those involved. The Prophet (صلى الله عليه وسلم) said that would make him like the people, and told him to enter his house. The narration is about avoiding participation in widespread killing. It teaches patience, restraint, and staying away from actions that join a violent fitnah."},"teachings":["Patience is advised when death overwhelms people.","Refraining from forbidden things is advised during famine.","The Prophet (صلى الله عليه وسلم) told Abu Dharr not to join the killing.","Staying away from violent fitnah is a clear message of the Hadith."],"related_hadiths":[{"id":"3960","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3959","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3957","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stay Away From Killing During Fitnah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet advised Abu Dharr to be patient, stay chaste during famine, and avoid joining killing during fitnah."},"heading":{"title":"Hadith About Avoiding Killing During Fitnah","description":"This Hadith is a detailed personal advice to Abu Dharr, and people may search it as hadith stay in your house during fitnah. The Prophet (صلى الله عليه وسلم) asked what he would do when death, famine, and killing overtake people. In response to death, he said, “Be patient.” In response to famine, he said, “You must refrain from forbidden things.” When killing spreads, Abu Dharr asked if he should take his sword and strike those involved. The Prophet (صلى الله عليه وسلم) said that would make him like the people, and told him to enter his house. The narration is about avoiding participation in widespread killing. It teaches patience, restraint, and staying away from actions that join a violent fitnah."},"teachings":["Patience is advised when death overwhelms people.","Refraining from forbidden things is advised during famine.","The Prophet (صلى الله عليه وسلم) told Abu Dharr not to join the killing.","Staying away from violent fitnah is a clear message of the Hadith."],"related_hadiths":[{"id":"3960","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3959","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3957","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E433" s="4" t="n"/>
@@ -10468,7 +10472,7 @@
       </c>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Starting Wudu with Clean Hands","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali washed his hands before putting them into the vessel and said he saw the Messenger of Allah do the same."},"heading":{"title":"Ali Hadith About Washing Hands Before the Vessel","description":"This Ali hadith about washing hands before the vessel gives an example through action. Harith narrated that Ali called for water and washed his hands before putting them into the vessel. Then Ali said that this is what he saw the Messenger of Allah doing. The report is short, but it clearly connects the practice to the Prophet’s example. It also fits the wider theme of clean hands before using ablution water. The text does not mention sleep directly, unlike the previous narrations, so the explanation should not force that detail here. The simple point is that Ali began by washing his hands before placing them in the vessel, following what he had seen from the Prophet."},"teachings":["Ali washed his hands before putting them into the vessel.","He linked this action to what he saw from the Messenger of Allah.","The report teaches beginning purification with clean hands."],"related_hadiths":[{"id":"162","book_id":"1","label":"Sahih Bukhari"},{"id":"1","book_id":"3","label":"Sunan an-Nasai"},{"id":"401","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Starting Wudu with Clean Hands","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali washed his hands before putting them into the vessel and said he saw the Messenger of Allah do the same."},"heading":{"title":"Ali Hadith About Washing Hands Before the Vessel","description":"This Ali hadith about washing hands before the vessel gives an example through action. Harith narrated that Ali called for water and washed his hands before putting them into the vessel. Then Ali said that this is what he saw the Messenger of Allah doing. The report is short, but it clearly connects the practice to the Prophet’s example. It also fits the wider theme of clean hands before using ablution water. The text does not mention sleep directly, unlike the previous narrations, so the explanation should not force that detail here. The simple point is that Ali began by washing his hands before placing them in the vessel, following what he had seen from the Prophet."},"teachings":["Ali washed his hands before putting them into the vessel.","He linked this action to what he saw from the Messenger of Allah.","The report teaches beginning purification with clean hands."],"related_hadiths":[{"id":"162","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"401","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E434" s="4" t="n"/>
@@ -10491,7 +10495,7 @@
       </c>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Wooden Sword During Muslim Fitnah","description":"$book_name$ $hadith_number$ - $chapter_name$. When fitnah arose among Muslims, the Prophet’s advice mentioned a wooden sword as a way of not joining the fighting."},"heading":{"title":"Hadith About the Wooden Sword During Fitnah Among Muslims","description":"This Hadith is often searched as wooden sword during fitnah hadith. The narration says that Ali came to Basrah and asked Abu Muslim for help. Abu Muslim agreed, then called for his sword. When it was drawn, it was seen to be made of wood. He explained that the Prophet (صلى الله عليه وسلم) had advised him that if fitnah arose among the Muslims, he should take a sword of wood. The point in the text is clear: he was not prepared to join real fighting between Muslims. Ali then said he had no need of him or his sword. The Hadith teaches caution during Muslim fitnah and shows a practical symbol of refusing bloodshed: a sword that cannot be used as a killing weapon."},"teachings":["The wooden sword shows refusal to join real fighting in fitnah.","The advice is linked specifically to tribulation among Muslims.","Abu Muslim was willing to go out, but not to carry a killing weapon.","The Hadith warns against being drawn into Muslim bloodshed."],"related_hadiths":[{"id":"3958","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3959","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3948","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Wooden Sword During Muslim Fitnah","description":"$book_name$ $hadith_number$ - $chapter_name$. When fitnah arose among Muslims, the Prophet’s advice mentioned a wooden sword as a way of not joining the fighting."},"heading":{"title":"Hadith About the Wooden Sword During Fitnah Among Muslims","description":"This Hadith is often searched as wooden sword during fitnah hadith. The narration says that Ali came to Basrah and asked Abu Muslim for help. Abu Muslim agreed, then called for his sword. When it was drawn, it was seen to be made of wood. He explained that the Prophet (صلى الله عليه وسلم) had advised him that if fitnah arose among the Muslims, he should take a sword of wood. The point in the text is clear: he was not prepared to join real fighting between Muslims. Ali then said he had no need of him or his sword. The Hadith teaches caution during Muslim fitnah and shows a practical symbol of refusing bloodshed: a sword that cannot be used as a killing weapon."},"teachings":["The wooden sword shows refusal to join real fighting in fitnah.","The advice is linked specifically to tribulation among Muslims.","Abu Muslim was willing to go out, but not to carry a killing weapon.","The Hadith warns against being drawn into Muslim bloodshed."],"related_hadiths":[{"id":"3958","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3959","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3948","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E435" s="4" t="n"/>
@@ -10514,7 +10518,7 @@
       </c>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing Firm During Fitnah","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns about dark trials and teaches Muslims to avoid rushing into bloodshed."},"heading":{"title":"Hadith About Fitnah: Standing Firm During Dark Trials","description":"This hadith about fitnah gives a clear warning about severe tribulations before the Hour. The Prophet صلى الله عليه وسلم describes them as pieces of black night, showing how confusing and dangerous they can be for faith. A person may start the day as a believer and end it in disbelief, or the opposite may happen by morning. The main lesson is restraint. The hadith praises the one who sits over the one who stands, the one who stands over the one who walks, and the one who walks over the one who runs. In simple words, rushing into violent conflict during tribulation is not praised here. The instruction to break weapons and be like the better son of Adam points to avoiding unjust killing."},"teachings":["During confusing trials, a Muslim should slow down and avoid rushing into conflict.","Faith can be tested heavily during fitnah, so caution is needed.","The hadith teaches restraint from bloodshed when tribulation spreads.","Being wrongfully killed is presented here as better than becoming a killer."],"related_hadiths":[{"id":"3962","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3980","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3979","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing Firm During Fitnah","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns about dark trials and teaches Muslims to avoid rushing into bloodshed."},"heading":{"title":"Hadith About Fitnah: Standing Firm During Dark Trials","description":"This hadith about fitnah gives a clear warning about severe tribulations before the Hour. The Prophet صلى الله عليه وسلم describes them as pieces of black night, showing how confusing and dangerous they can be for faith. A person may start the day as a believer and end it in disbelief, or the opposite may happen by morning. The main lesson is restraint. The hadith praises the one who sits over the one who stands, the one who stands over the one who walks, and the one who walks over the one who runs. In simple words, rushing into violent conflict during tribulation is not praised here. The instruction to break weapons and be like the better son of Adam points to avoiding unjust killing."},"teachings":["During confusing trials, a Muslim should slow down and avoid rushing into conflict.","Faith can be tested heavily during fitnah, so caution is needed.","The hadith teaches restraint from bloodshed when tribulation spreads.","Being wrongfully killed is presented here as better than becoming a killer."],"related_hadiths":[{"id":"3962","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3980","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3979","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E436" s="4" t="n"/>
@@ -10537,7 +10541,7 @@
       </c>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Division and Violence","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches restraint during division and warns against taking part in violent turmoil."},"heading":{"title":"Hadith About Fitnah and Division: Put Down the Sword","description":"This hadith about fitnah speaks about a time of tribulation, division, and disagreement. The Prophet صلى الله عليه وسلم gives a very strong image: take the sword to Uhud and strike it until it breaks. The point in this narration is not to join the violence when the situation becomes confused and divided. Muhammad bin Maslamah says that the event came to pass and he did what the Messenger of Allah صلى الله عليه وسلم told him. The hadith teaches that when fighting and division spread, safety for religion may come through stepping back, staying home, and refusing to become part of wrongful bloodshed. The wording also reminds us that a person may face harm from an evildoer or meet a natural death, but should still avoid sinful violence."},"teachings":["When tribulation brings division, a Muslim should not rush into violent conflict.","Breaking the sword in this narration shows a serious choice to avoid bloodshed.","Staying away from fitnah can be a form of protecting one’s religion.","The hadith points to patience even when harm may come from others."],"related_hadiths":[{"id":"3961","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3980","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3979","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Division and Violence","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches restraint during division and warns against taking part in violent turmoil."},"heading":{"title":"Hadith About Fitnah and Division: Put Down the Sword","description":"This hadith about fitnah speaks about a time of tribulation, division, and disagreement. The Prophet صلى الله عليه وسلم gives a very strong image: take the sword to Uhud and strike it until it breaks. The point in this narration is not to join the violence when the situation becomes confused and divided. Muhammad bin Maslamah says that the event came to pass and he did what the Messenger of Allah صلى الله عليه وسلم told him. The hadith teaches that when fighting and division spread, safety for religion may come through stepping back, staying home, and refusing to become part of wrongful bloodshed. The wording also reminds us that a person may face harm from an evildoer or meet a natural death, but should still avoid sinful violence."},"teachings":["When tribulation brings division, a Muslim should not rush into violent conflict.","Breaking the sword in this narration shows a serious choice to avoid bloodshed.","Staying away from fitnah can be a form of protecting one’s religion.","The hadith points to patience even when harm may come from others."],"related_hadiths":[{"id":"3961","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3980","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3979","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E437" s="4" t="n"/>
@@ -10560,7 +10564,7 @@
       </c>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Intent Behind Violence","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains why the slain is warned: he also intended to kill his companion."},"heading":{"title":"Hadith About Intention in Fighting: Wanting to Kill Matters","description":"This hadith about intention in fighting explains the warning found in similar narrations. The Prophet صلى الله عليه وسلم said that when two Muslims confront each other with their swords, both the killer and the slain will be in Hell. The Companions asked about the slain person, because the guilt of the killer was clear to them. The Prophet صلى الله عليه وسلم answered that the slain person wanted to kill his companion. This makes the teaching very direct. The issue is not only the final action, but also the intent to kill. In the setting of Muslims facing each other with swords, wanting to take the life of one’s companion is itself a grave matter. The hadith teaches care before anger turns into action."},"teachings":["A harmful intention can make a person blameworthy even if he is not able to finish the act.","The hadith warns against wanting to kill a Muslim companion.","The Companions asked for clarity, and the Prophet صلى الله عليه وسلم explained the reason.","Internal fighting between Muslims is treated as a serious danger."],"related_hadiths":[{"id":"3963","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3965","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3973","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Intent Behind Violence","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains why the slain is warned: he also intended to kill his companion."},"heading":{"title":"Hadith About Intention in Fighting: Wanting to Kill Matters","description":"This hadith about intention in fighting explains the warning found in similar narrations. The Prophet صلى الله عليه وسلم said that when two Muslims confront each other with their swords, both the killer and the slain will be in Hell. The Companions asked about the slain person, because the guilt of the killer was clear to them. The Prophet صلى الله عليه وسلم answered that the slain person wanted to kill his companion. This makes the teaching very direct. The issue is not only the final action, but also the intent to kill. In the setting of Muslims facing each other with swords, wanting to take the life of one’s companion is itself a grave matter. The hadith teaches care before anger turns into action."},"teachings":["A harmful intention can make a person blameworthy even if he is not able to finish the act.","The hadith warns against wanting to kill a Muslim companion.","The Companions asked for clarity, and the Prophet صلى الله عليه وسلم explained the reason.","Internal fighting between Muslims is treated as a serious danger."],"related_hadiths":[{"id":"3963","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3965","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3973","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E438" s="4" t="n"/>
@@ -10583,7 +10587,7 @@
       </c>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning Against Raising Weapons","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns that raising a weapon against a Muslim brother brings one near danger."},"heading":{"title":"Hadith About Weapons Against a Muslim Brother","description":"This hadith about weapons against a Muslim brother uses a strong warning. The Prophet صلى الله عليه وسلم said that when one Muslim carries a weapon against his brother, both are at the edge of Hell. If one kills the other, they both enter it. The wording shows how serious it is for Muslims to turn weapons on each other. The phrase edge of Hell makes the danger feel very close, not distant. The hadith does not give details about every possible case. It focuses on the act of a Muslim attacking his brother with a weapon and the deadly result that may follow. The simple message is to step away before anger, conflict, or fitnah reaches bloodshed."},"teachings":["Raising a weapon against a Muslim brother is treated as a serious danger.","The hadith warns before the killing happens, not only after it happens.","Killing in this kind of conflict carries a severe warning.","A Muslim should avoid the path that leads to bloodshed."],"related_hadiths":[{"id":"3963","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3964","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3971","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning Against Raising Weapons","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns that raising a weapon against a Muslim brother brings one near danger."},"heading":{"title":"Hadith About Weapons Against a Muslim Brother","description":"This hadith about weapons against a Muslim brother uses a strong warning. The Prophet صلى الله عليه وسلم said that when one Muslim carries a weapon against his brother, both are at the edge of Hell. If one kills the other, they both enter it. The wording shows how serious it is for Muslims to turn weapons on each other. The phrase edge of Hell makes the danger feel very close, not distant. The hadith does not give details about every possible case. It focuses on the act of a Muslim attacking his brother with a weapon and the deadly result that may follow. The simple message is to step away before anger, conflict, or fitnah reaches bloodshed."},"teachings":["Raising a weapon against a Muslim brother is treated as a serious danger.","The hadith warns before the killing happens, not only after it happens.","Killing in this kind of conflict carries a severe warning.","A Muslim should avoid the path that leads to bloodshed."],"related_hadiths":[{"id":"3963","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3964","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"3971","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E439" s="4" t="n"/>
@@ -10606,7 +10610,7 @@
       </c>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Saying Bismillah Before Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said there is no ablution for one who does not mention Allah’s Name before it."},"heading":{"title":"Bismillah Before Wudu Hadith","description":"This Bismillah before wudu hadith focuses on remembering Allah at the start of ablution. Abu Saeed narrated that the Messenger of Allah said there is no ablution for one who does not mention the Name of Allah before doing it. The hadith links wudu with the remembrance of Allah, not just washing the limbs. The provided wording is strong, so the explanation should stay with the text and not add detailed juristic differences unless clearly labeled. In simple terms, the hadith teaches that beginning wudu with Allah’s Name is a serious part of the act as narrated here. For readers searching for saying Bismillah before wudu, this report is one of the main narrations."},"teachings":["Mention Allah’s Name before wudu as stated in the narration.","Wudu is presented as both physical purification and remembrance.","The hadith gives special weight to beginning ablution with Allah’s Name."],"related_hadiths":[{"id":"101","book_id":"4","label":"Sunan Abu Dawud"},{"id":"86","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"272","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Saying Bismillah Before Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said there is no ablution for one who does not mention Allah’s Name before it."},"heading":{"title":"Bismillah Before Wudu Hadith","description":"This Bismillah before wudu hadith focuses on remembering Allah at the start of ablution. Abu Saeed narrated that the Messenger of Allah said there is no ablution for one who does not mention the Name of Allah before doing it. The hadith links wudu with the remembrance of Allah, not just washing the limbs. The provided wording is strong, so the explanation should stay with the text and not add detailed juristic differences unless clearly labeled. In simple terms, the hadith teaches that beginning wudu with Allah’s Name is a serious part of the act as narrated here. For readers searching for saying Bismillah before wudu, this report is one of the main narrations."},"teachings":["Mention Allah’s Name before wudu as stated in the narration.","Wudu is presented as both physical purification and remembrance.","The hadith gives special weight to beginning ablution with Allah’s Name."],"related_hadiths":[{"id":"101","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"86","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"272","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E440" s="4" t="n"/>
@@ -10629,7 +10633,7 @@
       </c>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Needs Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said prayer requires ablution, and ablution is tied to mentioning Allah’s Name before it."},"heading":{"title":"No Prayer Without Wudu Hadith","description":"This no prayer without wudu hadith connects two important acts: prayer and ablution. Abu Saeed bin Zaid narrated that the Messenger of Allah said there is no prayer for one who does not have ablution, and there is no ablution for one who does not mention the Name of Allah before it. The text keeps the order clear: prayer is tied to wudu, and wudu is tied to remembrance of Allah. This is not just a technical line; it teaches that salah should be approached with purification and awareness of Allah. For people searching for no prayer without wudu, this hadith gives a direct statement and also reminds them to begin ablution with Allah’s Name."},"teachings":["Prayer is linked to having ablution in the text.","The hadith also links wudu to mentioning Allah’s Name.","Preparation for salah includes both purification and remembrance."],"related_hadiths":[{"id":"101","book_id":"4","label":"Sunan Abu Dawud"},{"id":"86","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"272","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Needs Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said prayer requires ablution, and ablution is tied to mentioning Allah’s Name before it."},"heading":{"title":"No Prayer Without Wudu Hadith","description":"This no prayer without wudu hadith connects two important acts: prayer and ablution. Abu Saeed bin Zaid narrated that the Messenger of Allah said there is no prayer for one who does not have ablution, and there is no ablution for one who does not mention the Name of Allah before it. The text keeps the order clear: prayer is tied to wudu, and wudu is tied to remembrance of Allah. This is not just a technical line; it teaches that salah should be approached with purification and awareness of Allah. For people searching for no prayer without wudu, this hadith gives a direct statement and also reminds them to begin ablution with Allah’s Name."},"teachings":["Prayer is linked to having ablution in the text.","The hadith also links wudu to mentioning Allah’s Name.","Preparation for salah includes both purification and remembrance."],"related_hadiths":[{"id":"101","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"86","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"272","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E441" s="4" t="n"/>
@@ -10652,7 +10656,7 @@
       </c>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hadith About Fitnah and False Callers","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear warning to avoid callers to Hell during trials and not follow them."},"heading":{"title":"Hadith About Fitnah: Avoiding Callers to Hell","description":"This Hadith about fitnah gives a serious warning about times of tribulation. The Prophet صلى الله عليه وسلم said there will be trials, and at the gates of those trials will be people calling others to Hell. The message is simple: when a path clearly leads to ruin, a believer should not follow it, even if the pressure is strong. The phrase about dying while biting onto the stump of a tree shows how dangerous those callers are. The Hadith teaches caution, patience, and distance from harmful leadership during religious trials. It does not describe every trial in detail, so the safest lesson from the text is to avoid anyone calling toward evil."},"teachings":["Trials can include people who invite others toward serious harm.","A believer should not follow callers who lead away from safety and faith.","Staying away from corrupt influence may be better than joining a dangerous path."],"related_hadiths":[{"id":"7084","book_id":"1","label":"Sahih Bukhari"},{"id":"1847a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hadith About Fitnah and False Callers","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear warning to avoid callers to Hell during trials and not follow them."},"heading":{"title":"Hadith About Fitnah: Avoiding Callers to Hell","description":"This Hadith about fitnah gives a serious warning about times of tribulation. The Prophet صلى الله عليه وسلم said there will be trials, and at the gates of those trials will be people calling others to Hell. The message is simple: when a path clearly leads to ruin, a believer should not follow it, even if the pressure is strong. The phrase about dying while biting onto the stump of a tree shows how dangerous those callers are. The Hadith teaches caution, patience, and distance from harmful leadership during religious trials. It does not describe every trial in detail, so the safest lesson from the text is to avoid anyone calling toward evil."},"teachings":["Trials can include people who invite others toward serious harm.","A believer should not follow callers who lead away from safety and faith.","Staying away from corrupt influence may be better than joining a dangerous path."],"related_hadiths":[{"id":"7084","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1847a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E442" s="4" t="n"/>
@@ -10675,7 +10679,7 @@
       </c>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learn From Mistakes in Faith","description":"$book_name$ $hadith_number$ - $chapter_name$. A concise reminder that a believer should be careful after being harmed once."},"heading":{"title":"Hadith About Learning From Mistakes: The Believer Is Careful","description":"This narration from Ibn Umar carries the same clear teaching: the believer should not be stung from the same hole twice. It is a Hadith about learning from mistakes and acting with caution. The wording is short, but the lesson is strong. A believer is not asked to live in fear, yet he or she should not walk back into the same known harm without thought. The Hadith points to practical wisdom. When a wrong choice, harmful company, or unsafe situation has already shown its danger, the believer should take that lesson seriously. Faith and good judgment should work together."},"teachings":["A believer should not ignore clear warning signs.","Past harm can teach better choices for the future.","Being careful is part of wise conduct."],"related_hadiths":[{"id":"6133","book_id":"1","label":"Sahih Bukhari"},{"id":"2998a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learn From Mistakes in Faith","description":"$book_name$ $hadith_number$ - $chapter_name$. A concise reminder that a believer should be careful after being harmed once."},"heading":{"title":"Hadith About Learning From Mistakes: The Believer Is Careful","description":"This narration from Ibn Umar carries the same clear teaching: the believer should not be stung from the same hole twice. It is a Hadith about learning from mistakes and acting with caution. The wording is short, but the lesson is strong. A believer is not asked to live in fear, yet he or she should not walk back into the same known harm without thought. The Hadith points to practical wisdom. When a wrong choice, harmful company, or unsafe situation has already shown its danger, the believer should take that lesson seriously. Faith and good judgment should work together."},"teachings":["A believer should not ignore clear warning signs.","Past harm can teach better choices for the future.","Being careful is part of wise conduct."],"related_hadiths":[{"id":"6133","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2998a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E443" s="4" t="n"/>
@@ -10698,7 +10702,7 @@
       </c>
       <c r="D444" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Halal, Haram, and the Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. A deep reminder to avoid doubtful matters and guard the soundness of the heart."},"heading":{"title":"Halal and Haram Hadith: Guarding the Heart From Doubtful Matters","description":"This halal and haram Hadith explains that lawful matters are clear and unlawful matters are clear. Between them are doubtful matters that many people do not know. The Prophet صلى الله عليه وسلم teaches that avoiding doubtful matters helps a person protect religion and honor. He gives the example of a shepherd grazing near a protected area; the closer he gets, the more likely he is to enter it. The Hadith then points to the heart. If the heart is sound, the whole body is sound, and if it is corrupt, the whole body is corrupt. The main lesson is careful faith, clean choices, and a sound heart."},"teachings":["Halal and haram are clear in many matters.","Avoiding doubtful matters protects religion and honor.","The state of the heart affects the whole person.","Getting close to prohibited matters can lead to falling into them."],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"2051","book_id":"1","label":"Sahih Bukhari"},{"id":"1599a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Halal, Haram, and the Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. A deep reminder to avoid doubtful matters and guard the soundness of the heart."},"heading":{"title":"Halal and Haram Hadith: Guarding the Heart From Doubtful Matters","description":"This halal and haram Hadith explains that lawful matters are clear and unlawful matters are clear. Between them are doubtful matters that many people do not know. The Prophet صلى الله عليه وسلم teaches that avoiding doubtful matters helps a person protect religion and honor. He gives the example of a shepherd grazing near a protected area; the closer he gets, the more likely he is to enter it. The Hadith then points to the heart. If the heart is sound, the whole body is sound, and if it is corrupt, the whole body is corrupt. The main lesson is careful faith, clean choices, and a sound heart."},"teachings":["Halal and haram are clear in many matters.","Avoiding doubtful matters protects religion and honor.","The state of the heart affects the whole person.","Getting close to prohibited matters can lead to falling into them."],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2051","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1599a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E444" s="4" t="n"/>
@@ -10721,7 +10725,7 @@
       </c>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Worship During Bloodshed","description":"$book_name$ $hadith_number$ - $chapter_name$. A strong encouragement to hold to worship during times of bloodshed and chaos."},"heading":{"title":"Worship During Fitnah: A Hadith About Devotion in Chaos","description":"This Hadith about worship during fitnah says that worship during a time of bloodshed is like emigrating to the Prophet صلى الله عليه وسلم. The text focuses on one clear point: when chaos spreads, worship becomes especially meaningful. Bloodshed can distract people, pull them into fear, anger, or confusion, and make hearts restless. The Hadith points the believer back to worship. It does not list which acts are meant, so the safe wording is general worship, such as acts done for Allah. The main message is to stay close to Allah when the world around you is disturbed. Faithful worship can steady the heart in hard times."},"teachings":["Worship remains important during times of bloodshed.","A believer should not let chaos pull the heart away from Allah.","Turning to worship in troubled times has special value in this Hadith."],"related_hadiths":[{"id":"2948a","book_id":"2","label":"Sahih Muslim"},{"id":"2201","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Worship During Bloodshed","description":"$book_name$ $hadith_number$ - $chapter_name$. A strong encouragement to hold to worship during times of bloodshed and chaos."},"heading":{"title":"Worship During Fitnah: A Hadith About Devotion in Chaos","description":"This Hadith about worship during fitnah says that worship during a time of bloodshed is like emigrating to the Prophet صلى الله عليه وسلم. The text focuses on one clear point: when chaos spreads, worship becomes especially meaningful. Bloodshed can distract people, pull them into fear, anger, or confusion, and make hearts restless. The Hadith points the believer back to worship. It does not list which acts are meant, so the safe wording is general worship, such as acts done for Allah. The main message is to stay close to Allah when the world around you is disturbed. Faithful worship can steady the heart in hard times."},"teachings":["Worship remains important during times of bloodshed.","A believer should not let chaos pull the heart away from Allah.","Turning to worship in troubled times has special value in this Hadith."],"related_hadiths":[{"id":"2948a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2201","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E445" s="4" t="n"/>
@@ -10744,7 +10748,7 @@
       </c>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Islam Began as Strange","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful reminder for those who hold to Islam when it feels unfamiliar to others."},"heading":{"title":"Islam Began as Strange Hadith: Glad Tidings to the Strangers","description":"This famous Islam began as strange Hadith gives comfort to believers who feel out of place because of their faith. The Prophet صلى الله عليه وسلم said Islam began as something strange and will return to being strange, so glad tidings are for the strangers. The text does not describe every quality of the strangers here, so the explanation should stay close to the words. It teaches that feeling strange for holding to Islam is not always a sign of failure. At times, truth may feel unfamiliar among people. The Hadith gives hope, not pride. It reminds Muslims to stay steady when practicing Islam seems unusual to others."},"teachings":["Islam began as something strange and will return to being strange.","Believers may sometimes feel unfamiliar among people because of faith.","The Hadith gives glad tidings to those described as strangers."],"related_hadiths":[{"id":"145","book_id":"2","label":"Sahih Muslim"},{"id":"2629","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Islam Began as Strange","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful reminder for those who hold to Islam when it feels unfamiliar to others."},"heading":{"title":"Islam Began as Strange Hadith: Glad Tidings to the Strangers","description":"This famous Islam began as strange Hadith gives comfort to believers who feel out of place because of their faith. The Prophet صلى الله عليه وسلم said Islam began as something strange and will return to being strange, so glad tidings are for the strangers. The text does not describe every quality of the strangers here, so the explanation should stay close to the words. It teaches that feeling strange for holding to Islam is not always a sign of failure. At times, truth may feel unfamiliar among people. The Hadith gives hope, not pride. It reminds Muslims to stay steady when practicing Islam seems unusual to others."},"teachings":["Islam began as something strange and will return to being strange.","Believers may sometimes feel unfamiliar among people because of faith.","The Hadith gives glad tidings to those described as strangers."],"related_hadiths":[{"id":"145","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2629","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E446" s="4" t="n"/>
@@ -10767,7 +10771,7 @@
       </c>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Showing Off and Hidden Piety","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning against showing off and a praise of hidden, pious servants loved by Allah."},"heading":{"title":"Showing Off Is Shirk Hadith: Sincerity and Hidden Piety","description":"This Hadith about showing off warns that even a little showing off is polytheism. It also warns against showing enmity to a friend of Allah. Then it describes people loved by Allah: righteous, pious, and hidden. If they are absent, they are not missed, and if present, they are not invited or known. Their hearts are described as lamps of guidance, and they get out of trials and difficulty. The main lesson is sincerity. A person does not need public attention to be close to Allah. The Hadith praises quiet goodness, clean intention, and hearts that carry guidance without seeking fame or status."},"teachings":["Showing off in worship is strongly warned against.","Hidden righteousness and piety are praised in this Hadith.","A person may be unknown to people yet loved by Allah.","The heart can be a source of guidance through sincere faith."],"related_hadiths":[{"id":"6502","book_id":"1","label":"Sahih Bukhari"},{"id":"1905a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Showing Off and Hidden Piety","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning against showing off and a praise of hidden, pious servants loved by Allah."},"heading":{"title":"Showing Off Is Shirk Hadith: Sincerity and Hidden Piety","description":"This Hadith about showing off warns that even a little showing off is polytheism. It also warns against showing enmity to a friend of Allah. Then it describes people loved by Allah: righteous, pious, and hidden. If they are absent, they are not missed, and if present, they are not invited or known. Their hearts are described as lamps of guidance, and they get out of trials and difficulty. The main lesson is sincerity. A person does not need public attention to be close to Allah. The Hadith praises quiet goodness, clean intention, and hearts that carry guidance without seeking fame or status."},"teachings":["Showing off in worship is strongly warned against.","Hidden righteousness and piety are praised in this Hadith.","A person may be unknown to people yet loved by Allah.","The heart can be a source of guidance through sincere faith."],"related_hadiths":[{"id":"6502","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1905a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E447" s="4" t="n"/>
@@ -10790,7 +10794,7 @@
       </c>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu and Allah's Name","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah narrated that prayer requires ablution and ablution is tied to mentioning Allah’s Name before it."},"heading":{"title":"Hadith on Wudu and Mentioning Allah's Name","description":"This hadith on wudu and mentioning Allah’s Name carries the same wording through Abu Hurairah. The Messenger of Allah said there is no prayer for one who does not have ablution, and there is no ablution for one who does not mention the Name of Allah before it. The hadith places spiritual awareness at the start of purification. It also reminds the reader that prayer is not approached casually; it is preceded by wudu. Since the text is concise, we should not add extra events or background. The core teaching is enough: prepare for prayer with ablution, and begin that ablution by remembering Allah. This is why searches like Bismillah before wudu hadith often lead to this narration."},"teachings":["Ablution is mentioned as a condition before prayer in the narration.","Mentioning Allah’s Name is connected to the validity or completeness of wudu in the wording.","The report encourages awareness of Allah before beginning purification."],"related_hadiths":[{"id":"101","book_id":"4","label":"Sunan Abu Dawud"},{"id":"86","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"272","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu and Allah's Name","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah narrated that prayer requires ablution and ablution is tied to mentioning Allah’s Name before it."},"heading":{"title":"Hadith on Wudu and Mentioning Allah's Name","description":"This hadith on wudu and mentioning Allah’s Name carries the same wording through Abu Hurairah. The Messenger of Allah said there is no prayer for one who does not have ablution, and there is no ablution for one who does not mention the Name of Allah before it. The hadith places spiritual awareness at the start of purification. It also reminds the reader that prayer is not approached casually; it is preceded by wudu. Since the text is concise, we should not add extra events or background. The core teaching is enough: prepare for prayer with ablution, and begin that ablution by remembering Allah. This is why searches like Bismillah before wudu hadith often lead to this narration."},"teachings":["Ablution is mentioned as a condition before prayer in the narration.","Mentioning Allah’s Name is connected to the validity or completeness of wudu in the wording.","The report encourages awareness of Allah before beginning purification."],"related_hadiths":[{"id":"101","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"86","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"272","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E448" s="4" t="n"/>
@@ -10813,7 +10817,7 @@
       </c>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seventy-Three Sects Hadith","description":"$book_name$ $hadith_number$ - $chapter_name$. A prophetic statement about the nation splitting into seventy-three sects."},"heading":{"title":"73 Sects Hadith: A Warning About Division","description":"This 73 sects Hadith states that the Jews split into seventy-one sects and that the Prophet’s صلى الله عليه وسلم nation will split into seventy-three sects. The wording here is brief, so the explanation should not add details not present in this narration. The main message is that division will occur within the nation. It is a warning, not a reason for careless labeling or harsh speech. A believer reading this Hadith should take division seriously and be careful about paths that break unity in faith. The Hadith helps Muslims search for truth with humility, avoid pride, and understand that religious splitting is a serious matter."},"teachings":["The Hadith foretells division within the nation.","Religious splitting is treated as a serious matter.","The wording here should be understood without adding details not stated in it."],"related_hadiths":[{"id":"4597","book_id":"4","label":"Sunan Abu Dawud"},{"id":"2641","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seventy-Three Sects Hadith","description":"$book_name$ $hadith_number$ - $chapter_name$. A prophetic statement about the nation splitting into seventy-three sects."},"heading":{"title":"73 Sects Hadith: A Warning About Division","description":"This 73 sects Hadith states that the Jews split into seventy-one sects and that the Prophet’s صلى الله عليه وسلم nation will split into seventy-three sects. The wording here is brief, so the explanation should not add details not present in this narration. The main message is that division will occur within the nation. It is a warning, not a reason for careless labeling or harsh speech. A believer reading this Hadith should take division seriously and be careful about paths that break unity in faith. The Hadith helps Muslims search for truth with humility, avoid pride, and understand that religious splitting is a serious matter."},"teachings":["The Hadith foretells division within the nation.","Religious splitting is treated as a serious matter.","The wording here should be understood without adding details not stated in it."],"related_hadiths":[{"id":"4597","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"2641","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E449" s="4" t="n"/>
@@ -10836,7 +10840,7 @@
       </c>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lawful Wealth and Blessing","description":"$book_name$ $hadith_number$ - $chapter_name$. A teaching on worldly attraction, lawful wealth, and greed that never feels satisfied."},"heading":{"title":"Lawful Wealth Hadith: Blessing, Greed, and the Attraction of Dunya","description":"This lawful wealth Hadith begins with the Prophet صلى الله عليه وسلم saying he feared the attractions of this world for the people. A man asked whether good can bring evil. The Prophet صلى الله عليه وسلم explained that good brings only good, but he questioned whether what people call good is truly good. He gave the image of animals overeating from fresh growth, which may harm them, except when the animal eats, rests, releases waste, chews the cud, and returns. Then he gave the direct money lesson: wealth taken lawfully is blessed, while wealth taken unlawfully is like eating without being satisfied. The Hadith teaches balance, lawful earning, and caution from greed."},"teachings":["Worldly attraction can be a test.","Lawful wealth is connected with blessing in this Hadith.","Unlawful taking of wealth is compared to eating without satisfaction.","Not everything people call good is truly good."],"related_hadiths":[{"id":"6427","book_id":"1","label":"Sahih Bukhari"},{"id":"1052","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lawful Wealth and Blessing","description":"$book_name$ $hadith_number$ - $chapter_name$. A teaching on worldly attraction, lawful wealth, and greed that never feels satisfied."},"heading":{"title":"Lawful Wealth Hadith: Blessing, Greed, and the Attraction of Dunya","description":"This lawful wealth Hadith begins with the Prophet صلى الله عليه وسلم saying he feared the attractions of this world for the people. A man asked whether good can bring evil. The Prophet صلى الله عليه وسلم explained that good brings only good, but he questioned whether what people call good is truly good. He gave the image of animals overeating from fresh growth, which may harm them, except when the animal eats, rests, releases waste, chews the cud, and returns. Then he gave the direct money lesson: wealth taken lawfully is blessed, while wealth taken unlawfully is like eating without being satisfied. The Hadith teaches balance, lawful earning, and caution from greed."},"teachings":["Worldly attraction can be a test.","Lawful wealth is connected with blessing in this Hadith.","Unlawful taking of wealth is compared to eating without satisfaction.","Not everything people call good is truly good."],"related_hadiths":[{"id":"6427","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1052","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E450" s="4" t="n"/>
@@ -10859,7 +10863,7 @@
       </c>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wealth, Envy, and Rivalry","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning that opened treasures may lead to rivalry, envy, distance, and hatred."},"heading":{"title":"Hadith About Wealth Competition: Rivalry, Envy, and Turning Away","description":"This Hadith about wealth competition speaks about a time when the treasures of Persia and Rome would be opened. The Prophet صلى الله عليه وسلم asked what kind of people they would be then. Abdur-Rahman bin Awf answered with hope that they would say what Allah commanded. The Prophet صلى الله عليه وسلم then warned of another outcome: competition, envy, turning backs on one another, and hatred. The text shows how wealth can test relationships. It does not say wealth itself is always evil. Rather, it warns that access to treasure can stir rivalry and social harm when hearts are not careful. The lesson is to watch the heart when worldly gain increases."},"teachings":["New wealth can become a test for people.","Competition over wealth may lead to envy and hatred.","The heart needs care when worldly doors open."],"related_hadiths":[{"id":"3158","book_id":"1","label":"Sahih Bukhari"},{"id":"2961","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wealth, Envy, and Rivalry","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning that opened treasures may lead to rivalry, envy, distance, and hatred."},"heading":{"title":"Hadith About Wealth Competition: Rivalry, Envy, and Turning Away","description":"This Hadith about wealth competition speaks about a time when the treasures of Persia and Rome would be opened. The Prophet صلى الله عليه وسلم asked what kind of people they would be then. Abdur-Rahman bin Awf answered with hope that they would say what Allah commanded. The Prophet صلى الله عليه وسلم then warned of another outcome: competition, envy, turning backs on one another, and hatred. The text shows how wealth can test relationships. It does not say wealth itself is always evil. Rather, it warns that access to treasure can stir rivalry and social harm when hearts are not careful. The lesson is to watch the heart when worldly gain increases."},"teachings":["New wealth can become a test for people.","Competition over wealth may lead to envy and hatred.","The heart needs care when worldly doors open."],"related_hadiths":[{"id":"3158","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2961","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E451" s="4" t="n"/>
@@ -10882,7 +10886,7 @@
       </c>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fear of Worldly Plenty","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning that ease and plenty may lead to rivalry and ruin like earlier people."},"heading":{"title":"Fear of Dunya Hadith: When Plenty Becomes a Test","description":"This fear of dunya Hadith tells of wealth coming from Bahrain and the Ansar coming after Fajr. The Prophet صلى الله عليه وسلم smiled and knew they had heard about the wealth. He gave them good news and allowed hope for what would please them. Then he made the key point: he did not fear poverty for them, but feared that worldly ease would be spread before them as it was for people before them. He warned that they might compete for it and be harmed as earlier people were harmed. The Hadith does not condemn receiving wealth. It warns against rivalry and being consumed by worldly plenty."},"teachings":["Worldly ease can become a serious test.","The Prophet صلى الله عليه وسلم did not fear poverty here as much as harmful competition over plenty.","Wealth should not lead people to rivalry and ruin."],"related_hadiths":[{"id":"3158","book_id":"1","label":"Sahih Bukhari"},{"id":"2961","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fear of Worldly Plenty","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning that ease and plenty may lead to rivalry and ruin like earlier people."},"heading":{"title":"Fear of Dunya Hadith: When Plenty Becomes a Test","description":"This fear of dunya Hadith tells of wealth coming from Bahrain and the Ansar coming after Fajr. The Prophet صلى الله عليه وسلم smiled and knew they had heard about the wealth. He gave them good news and allowed hope for what would please them. Then he made the key point: he did not fear poverty for them, but feared that worldly ease would be spread before them as it was for people before them. He warned that they might compete for it and be harmed as earlier people were harmed. The Hadith does not condemn receiving wealth. It warns against rivalry and being consumed by worldly plenty."},"teachings":["Worldly ease can become a serious test.","The Prophet صلى الله عليه وسلم did not fear poverty here as much as harmful competition over plenty.","Wealth should not lead people to rivalry and ruin."],"related_hadiths":[{"id":"3158","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2961","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E452" s="4" t="n"/>
@@ -10905,7 +10909,7 @@
       </c>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Trial for Men","description":"$book_name$ $hadith_number$ - $chapter_name$. A direct warning that women can be a serious trial for men."},"heading":{"title":"Women as a Trial Hadith: A Warning for Men","description":"This women as a trial Hadith states that the Prophet صلى الله عليه وسلم did not leave behind any tribulation more harmful to men than women. The text is short and direct. It is not a statement that women are evil, and it should not be used to blame women as a whole. The wording speaks about a trial that affects men. A fair reading keeps the focus on self-control, caution, and guarding one’s conduct. The Hadith teaches men to take temptation seriously and not act as if they are safe from it. It also reminds readers that attraction can become a real test when not handled with faith and restraint."},"teachings":["Men are warned about a serious trial connected to women.","The Hadith calls for self-control and caution.","The wording should not be used to unfairly blame women as a whole."],"related_hadiths":[{"id":"5096","book_id":"1","label":"Sahih Bukhari"},{"id":"2740","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Trial for Men","description":"$book_name$ $hadith_number$ - $chapter_name$. A direct warning that women can be a serious trial for men."},"heading":{"title":"Women as a Trial Hadith: A Warning for Men","description":"This women as a trial Hadith states that the Prophet صلى الله عليه وسلم did not leave behind any tribulation more harmful to men than women. The text is short and direct. It is not a statement that women are evil, and it should not be used to blame women as a whole. The wording speaks about a trial that affects men. A fair reading keeps the focus on self-control, caution, and guarding one’s conduct. The Hadith teaches men to take temptation seriously and not act as if they are safe from it. It also reminds readers that attraction can become a real test when not handled with faith and restraint."},"teachings":["Men are warned about a serious trial connected to women.","The Hadith calls for self-control and caution.","The wording should not be used to unfairly blame women as a whole."],"related_hadiths":[{"id":"5096","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2740","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E453" s="4" t="n"/>
@@ -10928,7 +10932,7 @@
       </c>
       <c r="D454" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Men and Women as Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning that men and women can be a source of trial for one another."},"heading":{"title":"Men and Women Trial Hadith: A Daily Warning","description":"This men and women trial Hadith says that no morning comes except that two angels call out: woe to men from women, and woe to women from men. The wording points both ways. It warns men about women and women about men. The text does not say marriage is bad, nor does it attack either gender. It speaks about the danger of temptation and harm that can arise between men and women when limits are not guarded. A balanced explanation is to take the warning seriously without adding blame beyond the words. The Hadith calls for careful conduct, respect, and fear of Allah in gender relations."},"teachings":["The warning in this Hadith is directed both ways.","Men and women can be a trial for one another.","Careful conduct is needed in relationships and interactions."],"related_hadiths":[{"id":"5096","book_id":"1","label":"Sahih Bukhari"},{"id":"2742","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Men and Women as Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning that men and women can be a source of trial for one another."},"heading":{"title":"Men and Women Trial Hadith: A Daily Warning","description":"This men and women trial Hadith says that no morning comes except that two angels call out: woe to men from women, and woe to women from men. The wording points both ways. It warns men about women and women about men. The text does not say marriage is bad, nor does it attack either gender. It speaks about the danger of temptation and harm that can arise between men and women when limits are not guarded. A balanced explanation is to take the warning seriously without adding blame beyond the words. The Hadith calls for careful conduct, respect, and fear of Allah in gender relations."},"teachings":["The warning in this Hadith is directed both ways.","Men and women can be a trial for one another.","Careful conduct is needed in relationships and interactions."],"related_hadiths":[{"id":"5096","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2742","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E454" s="4" t="n"/>
@@ -10951,7 +10955,7 @@
       </c>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu, Salat on Prophet, and Love for Ansar","description":"$book_name$ $hadith_number$ - $chapter_name$. This Daif report links prayer with wudu, Allah’s Name, sending blessings on the Prophet, and loving the Ansar."},"heading":{"title":"Hadith on Wudu, Salat on the Prophet, and Love for Ansar","description":"This hadith on wudu, Salat on the Prophet, and love for Ansar includes several connected statements in one report. The Prophet is narrated to have said that there is no prayer for one who does not have ablution, and no ablution for one who does not mention Allah’s Name before it. The narration also says there is no prayer for one who does not send blessings upon the Prophet, and no prayer for one who does not love the Ansar. The input marks this narration as Daif, so it should be presented with care. The explanation should not build broad rulings beyond the wording. Its core message, as stated, points to purification, remembrance, honor for the Prophet, and love for the Ansar."},"teachings":["The report connects prayer with having ablution.","It links wudu with mentioning Allah’s Name before it.","The narration also mentions sending blessings on the Prophet and loving the Ansar, while the input marks it Daif."],"related_hadiths":[{"id":"101","book_id":"4","label":"Sunan Abu Dawud"},{"id":"17","book_id":"1","label":"Sahih Bukhari"},{"id":"272","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu, Salat on Prophet, and Love for Ansar","description":"$book_name$ $hadith_number$ - $chapter_name$. This Daif report links prayer with wudu, Allah’s Name, sending blessings on the Prophet, and loving the Ansar."},"heading":{"title":"Hadith on Wudu, Salat on the Prophet, and Love for Ansar","description":"This hadith on wudu, Salat on the Prophet, and love for Ansar includes several connected statements in one report. The Prophet is narrated to have said that there is no prayer for one who does not have ablution, and no ablution for one who does not mention Allah’s Name before it. The narration also says there is no prayer for one who does not send blessings upon the Prophet, and no prayer for one who does not love the Ansar. The input marks this narration as Daif, so it should be presented with care. The explanation should not build broad rulings beyond the wording. Its core message, as stated, points to purification, remembrance, honor for the Prophet, and love for the Ansar."},"teachings":["The report connects prayer with having ablution.","It links wudu with mentioning Allah’s Name before it.","The narration also mentions sending blessings on the Prophet and loving the Ansar, while the input marks it Daif."],"related_hadiths":[{"id":"101","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"17","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"272","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E455" s="4" t="n"/>
@@ -10974,7 +10978,7 @@
       </c>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Modesty in the Mosque","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches mosque etiquette: worship spaces should not become places of adornment, pride, or show."},"heading":{"title":"Hadith About Women in the Mosque: Modesty and Humility","description":"This Hadith about women in the mosque teaches a clear lesson about mosque etiquette, modesty, and humility. A woman entered the mosque while showing adornment and trailing her garment, and the Prophet صلى الله عليه وسلم told the people to stop women from wearing adornments and walking proudly in the mosque. The focus of the narration is not on stopping women from worship, but on protecting the mosque from show, pride, and display. The Prophet صلى الله عليه وسلم also warned by mentioning the Children of Israel, whose women wore adornments and walked proudly in their places of worship. The core message is simple: a place of worship should be entered with respect, calm behavior, and a humble heart."},"teachings":["The mosque should be treated as a place of worship, not a place for showing beauty or status.","Prideful walking in a place of worship is warned against in the text.","Families are told to guide one another toward respectful mosque behavior.","Outward appearance should not distract from humility before Allah."],"related_hadiths":[{"id":"4002","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4003","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Modesty in the Mosque","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches mosque etiquette: worship spaces should not become places of adornment, pride, or show."},"heading":{"title":"Hadith About Women in the Mosque: Modesty and Humility","description":"This Hadith about women in the mosque teaches a clear lesson about mosque etiquette, modesty, and humility. A woman entered the mosque while showing adornment and trailing her garment, and the Prophet صلى الله عليه وسلم told the people to stop women from wearing adornments and walking proudly in the mosque. The focus of the narration is not on stopping women from worship, but on protecting the mosque from show, pride, and display. The Prophet صلى الله عليه وسلم also warned by mentioning the Children of Israel, whose women wore adornments and walked proudly in their places of worship. The core message is simple: a place of worship should be entered with respect, calm behavior, and a humble heart."},"teachings":["The mosque should be treated as a place of worship, not a place for showing beauty or status.","Prideful walking in a place of worship is warned against in the text.","Families are told to guide one another toward respectful mosque behavior.","Outward appearance should not distract from humility before Allah."],"related_hadiths":[{"id":"4002","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4003","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E456" s="4" t="n"/>
@@ -10997,7 +11001,7 @@
       </c>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Perfume and Mosque Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns against wearing perfume to the mosque and links public scent with acceptance of prayer."},"heading":{"title":"Hadith About Women Wearing Perfume to the Mosque","description":"This Hadith about women wearing perfume to the mosque gives a direct warning about perfume, prayer, and mosque etiquette. Abu Hurairah met a woman who had put on perfume and was going to the mosque. When she said that she had worn it for that purpose, he quoted the Prophet صلى الله عليه وسلم: any woman who puts on perfume and goes out to the mosque will not have her prayer accepted until she takes a bath. The wording is strong, so the explanation should stay close to the text. The Hadith teaches that worship is not only about reaching the mosque. It also includes how a person goes there, what attention they draw, and whether their outward state fits the humility of prayer."},"teachings":["Going to the mosque should be done with modesty and care.","The Hadith gives a clear warning about perfume worn when going out to the mosque.","Prayer is connected to outward conduct as well as the act itself.","A person should avoid what may draw improper attention in a worship setting."],"related_hadiths":[{"id":"4001","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4003","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Perfume and Mosque Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns against wearing perfume to the mosque and links public scent with acceptance of prayer."},"heading":{"title":"Hadith About Women Wearing Perfume to the Mosque","description":"This Hadith about women wearing perfume to the mosque gives a direct warning about perfume, prayer, and mosque etiquette. Abu Hurairah met a woman who had put on perfume and was going to the mosque. When she said that she had worn it for that purpose, he quoted the Prophet صلى الله عليه وسلم: any woman who puts on perfume and goes out to the mosque will not have her prayer accepted until she takes a bath. The wording is strong, so the explanation should stay close to the text. The Hadith teaches that worship is not only about reaching the mosque. It also includes how a person goes there, what attention they draw, and whether their outward state fits the humility of prayer."},"teachings":["Going to the mosque should be done with modesty and care.","The Hadith gives a clear warning about perfume worn when going out to the mosque.","Prayer is connected to outward conduct as well as the act itself.","A person should avoid what may draw improper attention in a worship setting."],"related_hadiths":[{"id":"4001","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4003","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E457" s="4" t="n"/>
@@ -11020,7 +11024,7 @@
       </c>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Charity and Seeking Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith urges women to give charity, seek forgiveness, avoid cursing, and be grateful in family life."},"heading":{"title":"Hadith About Charity and Istighfar for Women","description":"This Hadith about charity and istighfar speaks in a serious but practical way. The Prophet صلى الله عليه وسلم addressed women and told them to give in charity and ask Allah for forgiveness often. He then explained reasons mentioned in the narration: frequent cursing and ingratitude toward husbands. A wise woman asked for more explanation, and the Prophet صلى الله عليه وسلم explained what was meant by lacking in discernment and religion in this specific text. The Hadith should be read with care and without adding claims that are not stated here. Its clear teaching is that speech, gratitude, prayer, fasting, charity, and seeking forgiveness all matter. It turns attention toward self-correction instead of blame."},"teachings":["Charity and asking forgiveness are encouraged as practical acts of worship.","The text warns against frequent cursing and ingratitude within marriage.","Questions about religious teaching can be asked respectfully, as the woman did.","The narration connects worship habits with accountability before Allah."],"related_hadiths":[{"id":"79a","book_id":"2","label":"Sahih Muslim"},{"id":"304","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Charity and Seeking Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith urges women to give charity, seek forgiveness, avoid cursing, and be grateful in family life."},"heading":{"title":"Hadith About Charity and Istighfar for Women","description":"This Hadith about charity and istighfar speaks in a serious but practical way. The Prophet صلى الله عليه وسلم addressed women and told them to give in charity and ask Allah for forgiveness often. He then explained reasons mentioned in the narration: frequent cursing and ingratitude toward husbands. A wise woman asked for more explanation, and the Prophet صلى الله عليه وسلم explained what was meant by lacking in discernment and religion in this specific text. The Hadith should be read with care and without adding claims that are not stated here. Its clear teaching is that speech, gratitude, prayer, fasting, charity, and seeking forgiveness all matter. It turns attention toward self-correction instead of blame."},"teachings":["Charity and asking forgiveness are encouraged as practical acts of worship.","The text warns against frequent cursing and ingratitude within marriage.","Questions about religious teaching can be asked respectfully, as the woman did.","The narration connects worship habits with accountability before Allah."],"related_hadiths":[{"id":"79a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"304","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E458" s="4" t="n"/>
@@ -11043,7 +11047,7 @@
       </c>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Changing Evil Before Collective Punishment","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains that seeing evil without changing it can expose a community to wider punishment."},"heading":{"title":"Hadith About Changing Evil: Do Not Misread Self-Care","description":"This Hadith about changing evil explains that caring for oneself does not mean ignoring public wrong. Abu Bakr mentioned the verse about taking care of your own selves, then clarified what he heard from the Prophet صلى الله عليه وسلم: if people see evil and do not change it, Allah may send punishment upon them all. The Hadith speaks to people who are aware of wrong but remain inactive. It does not tell people to act without wisdom or ability, but it does show that silence in the face of evil is not a safe path. The main lesson is that personal guidance and social responsibility are connected in Islam."},"teachings":["Personal guidance does not cancel concern for public wrongdoing.","Seeing evil and leaving it unchanged is warned against in the text.","A community can be affected when people ignore wrong around them.","The Hadith teaches responsibility, not isolation from moral duty."],"related_hadiths":[{"id":"4004","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4009","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4013","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Changing Evil Before Collective Punishment","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains that seeing evil without changing it can expose a community to wider punishment."},"heading":{"title":"Hadith About Changing Evil: Do Not Misread Self-Care","description":"This Hadith about changing evil explains that caring for oneself does not mean ignoring public wrong. Abu Bakr mentioned the verse about taking care of your own selves, then clarified what he heard from the Prophet صلى الله عليه وسلم: if people see evil and do not change it, Allah may send punishment upon them all. The Hadith speaks to people who are aware of wrong but remain inactive. It does not tell people to act without wisdom or ability, but it does show that silence in the face of evil is not a safe path. The main lesson is that personal guidance and social responsibility are connected in Islam."},"teachings":["Personal guidance does not cancel concern for public wrongdoing.","Seeing evil and leaving it unchanged is warned against in the text.","A community can be affected when people ignore wrong around them.","The Hadith teaches responsibility, not isolation from moral duty."],"related_hadiths":[{"id":"4004","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4009","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4013","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E459" s="4" t="n"/>
@@ -11066,7 +11070,7 @@
       </c>
       <c r="D460" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Taking the Hand of the Wrongdoer","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns against empty advice and calls for firm help in turning wrongdoers back to truth."},"heading":{"title":"Hadith About Restraining the Wrongdoer and Standing for Truth","description":"This Hadith about restraining the wrongdoer gives a strong picture of moral responsibility. The Prophet صلى الله عليه وسلم described how, among the Children of Israel, a man would see his brother sin, tell him not to do it, but then continue eating, drinking, and mixing with him as if nothing had happened. The narration says Allah made their hearts alike and mentions Qur’anic verses about them. Then the Prophet صلى الله عليه وسلم sat up and said that people must take the hand of the wrongdoer and force him toward the right way. The lesson is not about harshness without wisdom. It is about not treating clear wrongdoing as normal after giving a few empty words."},"teachings":["Advice should not become only words while wrong continues unchanged.","The text warns against becoming comfortable with sin after seeing it.","Helping a wrongdoer may require firm action within one’s ability and role.","A community should not let repeated wrong become normal behavior."],"related_hadiths":[{"id":"4005","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4009","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4013","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Taking the Hand of the Wrongdoer","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns against empty advice and calls for firm help in turning wrongdoers back to truth."},"heading":{"title":"Hadith About Restraining the Wrongdoer and Standing for Truth","description":"This Hadith about restraining the wrongdoer gives a strong picture of moral responsibility. The Prophet صلى الله عليه وسلم described how, among the Children of Israel, a man would see his brother sin, tell him not to do it, but then continue eating, drinking, and mixing with him as if nothing had happened. The narration says Allah made their hearts alike and mentions Qur’anic verses about them. Then the Prophet صلى الله عليه وسلم sat up and said that people must take the hand of the wrongdoer and force him toward the right way. The lesson is not about harshness without wisdom. It is about not treating clear wrongdoing as normal after giving a few empty words."},"teachings":["Advice should not become only words while wrong continues unchanged.","The text warns against becoming comfortable with sin after seeing it.","Helping a wrongdoer may require firm action within one’s ability and role.","A community should not let repeated wrong become normal behavior."],"related_hadiths":[{"id":"4005","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4009","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4013","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E460" s="4" t="n"/>
@@ -11089,7 +11093,7 @@
       </c>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fear of People Should Not Stop Truth","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that fear of people should not stop a person from speaking known truth."},"heading":{"title":"Hadith About Speaking the Truth Without Fear of People","description":"This Hadith about speaking the truth is simple and powerful. During a sermon, the Prophet صلى الله عليه وسلم said that fear of people should not stop a man from saying the truth when he knows it. Abu Sa’eed then cried and admitted that they had seen things that made them afraid. The narration is honest about human weakness. It does not pretend that speaking truth is always easy. It teaches that fear of people can become a barrier between a person and the duty to say what is right. The related search phrase, speak the truth in Islam, fits this Hadith well because the message is about courage, knowledge, and moral duty."},"teachings":["Truth should be spoken when a person knows it and has a duty to speak.","Fear of people is named as a real barrier in the narration.","The Companion’s reaction shows the seriousness of staying silent out of fear.","The Hadith encourages moral courage without adding details beyond the text."],"related_hadiths":[{"id":"4008","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4011","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4012","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fear of People Should Not Stop Truth","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that fear of people should not stop a person from speaking known truth."},"heading":{"title":"Hadith About Speaking the Truth Without Fear of People","description":"This Hadith about speaking the truth is simple and powerful. During a sermon, the Prophet صلى الله عليه وسلم said that fear of people should not stop a man from saying the truth when he knows it. Abu Sa’eed then cried and admitted that they had seen things that made them afraid. The narration is honest about human weakness. It does not pretend that speaking truth is always easy. It teaches that fear of people can become a barrier between a person and the duty to say what is right. The related search phrase, speak the truth in Islam, fits this Hadith well because the message is about courage, knowledge, and moral duty."},"teachings":["Truth should be spoken when a person knows it and has a duty to speak.","Fear of people is named as a real barrier in the narration.","The Companion’s reaction shows the seriousness of staying silent out of fear.","The Hadith encourages moral courage without adding details beyond the text."],"related_hadiths":[{"id":"4008","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4011","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4012","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E461" s="4" t="n"/>
@@ -11112,7 +11116,7 @@
       </c>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Belittle Yourself by Silence","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that silence when one should speak for Allah is a way of belittling oneself."},"heading":{"title":"Hadith About Speaking Out: Do Not Belittle Yourself","description":"This Hadith about speaking out explains a deep form of self-belittling. The Prophet صلى الله عليه وسلم said that no one should belittle himself. When the Companions asked how this happens, he explained: a person sees a matter in which he should speak for the sake of Allah, but he stays silent. On the Day of Resurrection, he is asked what stopped him, and he says it was fear of people. Allah then says that He was more deserving of being feared. This Hadith keeps the focus on duty, fear, and accountability. It does not call for reckless speech. It warns against silence when a person knows there is a duty to speak."},"teachings":["Staying silent out of fear can be a form of belittling oneself.","The Hadith connects speaking for Allah with accountability on the Day of Resurrection.","Fear of people should not be placed above fear of Allah.","A person should think carefully when they see a matter that calls for speech."],"related_hadiths":[{"id":"4007","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4017","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4013","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Belittle Yourself by Silence","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that silence when one should speak for Allah is a way of belittling oneself."},"heading":{"title":"Hadith About Speaking Out: Do Not Belittle Yourself","description":"This Hadith about speaking out explains a deep form of self-belittling. The Prophet صلى الله عليه وسلم said that no one should belittle himself. When the Companions asked how this happens, he explained: a person sees a matter in which he should speak for the sake of Allah, but he stays silent. On the Day of Resurrection, he is asked what stopped him, and he says it was fear of people. Allah then says that He was more deserving of being feared. This Hadith keeps the focus on duty, fear, and accountability. It does not call for reckless speech. It warns against silence when a person knows there is a duty to speak."},"teachings":["Staying silent out of fear can be a form of belittling oneself.","The Hadith connects speaking for Allah with accountability on the Day of Resurrection.","Fear of people should not be placed above fear of Allah.","A person should think carefully when they see a matter that calls for speech."],"related_hadiths":[{"id":"4007","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4017","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4013","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E462" s="4" t="n"/>
@@ -11135,7 +11139,7 @@
       </c>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Supporting the Weak Against the Strong","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that a people are not purified when the weak are not supported against the strong."},"heading":{"title":"Hadith About Justice: Support the Weak Against the Strong","description":"This Hadith about justice and supporting the weak tells a clear story. The emigrants described an old nun in Abyssinia who was pushed by a young man, fell, and broke her water vessel. She warned him that Allah would gather people and that hands and feet would speak about what they used to do. The Prophet صلى الله عليه وسلم confirmed her words and said: how can Allah purify a people when they do not support their weak from their strong? The lesson is plain. A society should not allow the powerful to harm the weak without support or correction. The Hadith links justice, public responsibility, and accountability before Allah in a very direct way."},"teachings":["The weak should be supported when they are wronged by the strong.","The narration reminds people that deeds will be brought before Allah.","A society is blamed when it leaves the weak without help.","Justice is not only a private feeling; it includes standing with those harmed."],"related_hadiths":[{"id":"4009","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4018","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Supporting the Weak Against the Strong","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that a people are not purified when the weak are not supported against the strong."},"heading":{"title":"Hadith About Justice: Support the Weak Against the Strong","description":"This Hadith about justice and supporting the weak tells a clear story. The emigrants described an old nun in Abyssinia who was pushed by a young man, fell, and broke her water vessel. She warned him that Allah would gather people and that hands and feet would speak about what they used to do. The Prophet صلى الله عليه وسلم confirmed her words and said: how can Allah purify a people when they do not support their weak from their strong? The lesson is plain. A society should not allow the powerful to harm the weak without support or correction. The Hadith links justice, public responsibility, and accountability before Allah in a very direct way."},"teachings":["The weak should be supported when they are wronged by the strong.","The narration reminds people that deeds will be brought before Allah.","A society is blamed when it leaves the weak without help.","Justice is not only a private feeling; it includes standing with those harmed."],"related_hadiths":[{"id":"4009","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4018","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E463" s="4" t="n"/>
@@ -11158,7 +11162,7 @@
       </c>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Jihad Before an Unjust Ruler","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that a just word spoken to an unjust ruler is described as the best jihad."},"heading":{"title":"Best Jihad Hadith: A Just Word to an Unjust Ruler","description":"This best jihad Hadith gives a short but bold teaching. Abu Sa’eed Al-Khudri narrated that the Prophet صلى الله عليه وسلم said: the best of jihad is a just word spoken to an unjust ruler. The core topic is not general debate or anger. It is a just word, spoken where injustice has power. The Hadith shows that truth and justice can require courage, especially when the listener has authority. The phrase hadith about speaking truth to power is often searched, and this narration directly fits it. At the same time, the wording stays focused: a just word, not insults, not pride, and not speech for personal fame."},"teachings":["A just word has high value when spoken before an unjust ruler.","The Hadith connects courage with fairness, not reckless speech.","Authority does not remove the duty to say what is right.","The wording highlights justice as the quality of the speech."],"related_hadiths":[{"id":"4012","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4209","book_id":"3","label":"Sunan an-Nasai"},{"id":"4007","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Jihad Before an Unjust Ruler","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that a just word spoken to an unjust ruler is described as the best jihad."},"heading":{"title":"Best Jihad Hadith: A Just Word to an Unjust Ruler","description":"This best jihad Hadith gives a short but bold teaching. Abu Sa’eed Al-Khudri narrated that the Prophet صلى الله عليه وسلم said: the best of jihad is a just word spoken to an unjust ruler. The core topic is not general debate or anger. It is a just word, spoken where injustice has power. The Hadith shows that truth and justice can require courage, especially when the listener has authority. The phrase hadith about speaking truth to power is often searched, and this narration directly fits it. At the same time, the wording stays focused: a just word, not insults, not pride, and not speech for personal fame."},"teachings":["A just word has high value when spoken before an unjust ruler.","The Hadith connects courage with fairness, not reckless speech.","Authority does not remove the duty to say what is right.","The wording highlights justice as the quality of the speech."],"related_hadiths":[{"id":"4012","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4209","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"4007","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E464" s="4" t="n"/>
@@ -11181,7 +11185,7 @@
       </c>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Change Evil by Hand, Tongue, or Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches the three levels of responding to evil: action, speech, and rejection in the heart."},"heading":{"title":"Whoever Sees an Evil Hadith: Hand, Tongue, and Heart","description":"This famous Hadith about changing evil explains what a believer should do when seeing wrong. Abu Sa’eed mentioned a man who objected when Marwan changed the Eid order by starting with the sermon before the prayer. Abu Sa’eed said the man had done his duty, then narrated the Prophet’s صلى الله عليه وسلم words: whoever sees an evil and can change it with his hand should do so; if not, then with his tongue; if not, then with his heart, and that is the weakest of faith. The Hadith gives a clear order based on ability. It teaches action when possible, speech when action is not possible, and inward rejection when neither is possible."},"teachings":["Responding to evil is tied to ability: hand, tongue, then heart.","Speaking against wrong can fulfill a duty when action is not possible.","Rejecting evil in the heart still matters, though it is called the weakest faith.","The Hadith uses a real example of correcting a change in the Eid practice."],"related_hadiths":[{"id":"49a","book_id":"2","label":"Sahih Muslim"},{"id":"4004","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Change Evil by Hand, Tongue, or Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches the three levels of responding to evil: action, speech, and rejection in the heart."},"heading":{"title":"Whoever Sees an Evil Hadith: Hand, Tongue, and Heart","description":"This famous Hadith about changing evil explains what a believer should do when seeing wrong. Abu Sa’eed mentioned a man who objected when Marwan changed the Eid order by starting with the sermon before the prayer. Abu Sa’eed said the man had done his duty, then narrated the Prophet’s صلى الله عليه وسلم words: whoever sees an evil and can change it with his hand should do so; if not, then with his tongue; if not, then with his heart, and that is the weakest of faith. The Hadith gives a clear order based on ability. It teaches action when possible, speech when action is not possible, and inward rejection when neither is possible."},"teachings":["Responding to evil is tied to ability: hand, tongue, then heart.","Speaking against wrong can fulfill a duty when action is not possible.","Rejecting evil in the heart still matters, though it is called the weakest faith.","The Hadith uses a real example of correcting a change in the Eid practice."],"related_hadiths":[{"id":"49a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4004","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E465" s="4" t="n"/>
@@ -11204,7 +11208,7 @@
       </c>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Days of Patience and Holding to Good","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains when public correction may become beyond one’s power and praises patience in hard days."},"heading":{"title":"Hadith About Days of Patience Like Holding Burning Ember","description":"This Hadith about days of patience explains the verse about taking care of yourselves. The Prophet صلى الله عليه وسلم first said to enjoin good and forbid evil. Then he described conditions such as obeyed stinginess, followed desires, the world being preferred, every person being proud of their opinion, and a matter that a person has no power to deal with. In that situation, the person is told to mind their own particular duty and leave the common people. The Hadith then says days of patience will come, when patience is like holding a burning ember, and one who does good deeds will have a reward like fifty men doing the same deed. The text teaches duty, limits, and patience."},"teachings":["Enjoining good and forbidding evil remains the first instruction in the narration.","When a matter is beyond one’s power, a person is told to focus on their own duty.","The Hadith describes patience in hard times as like holding a burning ember.","Doing good in difficult days is praised in the wording of the text."],"related_hadiths":[{"id":"4004","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4013","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Days of Patience and Holding to Good","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains when public correction may become beyond one’s power and praises patience in hard days."},"heading":{"title":"Hadith About Days of Patience Like Holding Burning Ember","description":"This Hadith about days of patience explains the verse about taking care of yourselves. The Prophet صلى الله عليه وسلم first said to enjoin good and forbid evil. Then he described conditions such as obeyed stinginess, followed desires, the world being preferred, every person being proud of their opinion, and a matter that a person has no power to deal with. In that situation, the person is told to mind their own particular duty and leave the common people. The Hadith then says days of patience will come, when patience is like holding a burning ember, and one who does good deeds will have a reward like fifty men doing the same deed. The text teaches duty, limits, and patience."},"teachings":["Enjoining good and forbidding evil remains the first instruction in the narration.","When a matter is beyond one’s power, a person is told to focus on their own duty.","The Hadith describes patience in hard times as like holding a burning ember.","Doing good in difficult days is praised in the wording of the text."],"related_hadiths":[{"id":"4004","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4013","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E466" s="4" t="n"/>
@@ -11227,7 +11231,7 @@
       </c>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Signs Linked to Leaving Good Counsel","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions signs among people before stopping enjoining good and forbidding evil."},"heading":{"title":"Hadith About When to Stop Enjoining Good and Forbidding Evil","description":"This Hadith about enjoining good and forbidding evil records a direct question: when should people stop this duty? The Prophet صلى الله عليه وسلم answered that it would be when what appeared among earlier nations appears among you. When asked what that meant, he mentioned kingship among the youth, immorality among the old, and knowledge among the base and vile. The narration also includes an explanation from Zaid about knowledge among the base and vile: when knowledge is with the sinful. The Hadith is not a long rulebook, so we should not add extra details. Its clear point is that moral decline affects leadership, age groups, and even who carries knowledge."},"teachings":["The Hadith keeps enjoining good and forbidding evil as a serious public duty.","Moral decline is described through leadership, immorality, and misuse of knowledge.","The narration warns when knowledge is held by people described as sinful or vile.","The question shows concern for knowing the limits of public correction."],"related_hadiths":[{"id":"4004","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4014","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Signs Linked to Leaving Good Counsel","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions signs among people before stopping enjoining good and forbidding evil."},"heading":{"title":"Hadith About When to Stop Enjoining Good and Forbidding Evil","description":"This Hadith about enjoining good and forbidding evil records a direct question: when should people stop this duty? The Prophet صلى الله عليه وسلم answered that it would be when what appeared among earlier nations appears among you. When asked what that meant, he mentioned kingship among the youth, immorality among the old, and knowledge among the base and vile. The narration also includes an explanation from Zaid about knowledge among the base and vile: when knowledge is with the sinful. The Hadith is not a long rulebook, so we should not add extra details. Its clear point is that moral decline affects leadership, age groups, and even who carries knowledge."},"teachings":["The Hadith keeps enjoining good and forbidding evil as a serious public duty.","Moral decline is described through leadership, immorality, and misuse of knowledge.","The narration warns when knowledge is held by people described as sinful or vile.","The question shows concern for knowing the limits of public correction."],"related_hadiths":[{"id":"4004","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4014","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E467" s="4" t="n"/>
@@ -11250,7 +11254,7 @@
       </c>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Take on Trials Beyond Your Strength","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that a believer should not humiliate himself by taking on trials he cannot bear."},"heading":{"title":"Hadith About Not Humiliating Yourself With Trials Beyond Your Ability","description":"This Hadith about not humiliating yourself gives a balanced lesson on courage and limits. The Prophet صلى الله عليه وسلم said that a believer should not humiliate himself. When asked how that could happen, he explained that it is by taking on a trial that he cannot deal with. The narration does not praise fear or silence in every case, and it does not call for careless risk. It teaches that a believer should know his limits and should not expose himself to a burden he cannot handle. This is an important balance beside other Hadiths about speaking truth. One should act for Allah, but not put oneself into a trial beyond one’s ability."},"teachings":["A believer should avoid taking on a trial beyond what he can handle.","The Hadith teaches self-respect, not pride.","Religious courage should be balanced with real ability.","A person should not confuse reckless exposure to hardship with duty."],"related_hadiths":[{"id":"4008","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4017","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4007","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Take on Trials Beyond Your Strength","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that a believer should not humiliate himself by taking on trials he cannot bear."},"heading":{"title":"Hadith About Not Humiliating Yourself With Trials Beyond Your Ability","description":"This Hadith about not humiliating yourself gives a balanced lesson on courage and limits. The Prophet صلى الله عليه وسلم said that a believer should not humiliate himself. When asked how that could happen, he explained that it is by taking on a trial that he cannot deal with. The narration does not praise fear or silence in every case, and it does not call for careless risk. It teaches that a believer should know his limits and should not expose himself to a burden he cannot handle. This is an important balance beside other Hadiths about speaking truth. One should act for Allah, but not put oneself into a trial beyond one’s ability."},"teachings":["A believer should avoid taking on a trial beyond what he can handle.","The Hadith teaches self-respect, not pride.","Religious courage should be balanced with real ability.","A person should not confuse reckless exposure to hardship with duty."],"related_hadiths":[{"id":"4008","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4017","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4007","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E468" s="4" t="n"/>
@@ -11273,7 +11277,7 @@
       </c>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Questioned for Not Denouncing Evil","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that Allah will question a person about not denouncing evil when he saw it."},"heading":{"title":"Hadith About Denouncing Evil and Fear of People","description":"This Hadith about denouncing evil reminds the believer of the Day of Resurrection. Abu Sa’eed narrated that Allah will question His slave until He asks what kept him from denouncing evil when he saw it. When Allah grants the slave a response, he will say that he hoped for Allah’s mercy but feared people. The narration brings together hope, fear, and responsibility. It does not tell us to speak in every matter without wisdom. It does warn that fear of people can stop a person from doing what he knows is right. The main lesson is to remember Allah when deciding whether to speak against a wrong."},"teachings":["A person may be questioned for not denouncing evil that he saw.","Fear of people is shown as a reason that can hold someone back.","The slave mentions hope in Allah’s mercy in the response given in the text.","Seeing wrong brings a responsibility that should not be ignored lightly."],"related_hadiths":[{"id":"4008","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4007","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4013","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Questioned for Not Denouncing Evil","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that Allah will question a person about not denouncing evil when he saw it."},"heading":{"title":"Hadith About Denouncing Evil and Fear of People","description":"This Hadith about denouncing evil reminds the believer of the Day of Resurrection. Abu Sa’eed narrated that Allah will question His slave until He asks what kept him from denouncing evil when he saw it. When Allah grants the slave a response, he will say that he hoped for Allah’s mercy but feared people. The narration brings together hope, fear, and responsibility. It does not tell us to speak in every matter without wisdom. It does warn that fear of people can stop a person from doing what he knows is right. The main lesson is to remember Allah when deciding whether to speak against a wrong."},"teachings":["A person may be questioned for not denouncing evil that he saw.","Fear of people is shown as a reason that can hold someone back.","The slave mentions hope in Allah’s mercy in the response given in the text.","Seeing wrong brings a responsibility that should not be ignored lightly."],"related_hadiths":[{"id":"4008","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4007","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4013","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E469" s="4" t="n"/>
@@ -11296,7 +11300,7 @@
       </c>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah Gives Respite to the Wrongdoer","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that Allah may give respite to wrongdoers, but His seizure is not escaped."},"heading":{"title":"Hadith About Allah Giving Respite to the Wrongdoer","description":"This Hadith about Allah giving respite to the wrongdoer is a clear warning about injustice. The Prophet صلى الله عليه وسلم said that Allah gives time to the wrongdoer, but when He seizes him, He does not let him go. He then recited the verse about the seizure of the Lord when He seizes towns while they are doing wrong. The message is direct: delay should not be mistaken for safety. A person may continue in wrongdoing for a time, but the Hadith reminds us that accountability belongs to Allah. This narration also comforts those who see injustice and wonder why judgment has not come yet. The text teaches patience, fear of Allah, and trust in His justice."},"teachings":["A delay in punishment does not mean wrongdoing is safe.","The Hadith warns wrongdoers about Allah’s final seizure.","The recited verse connects the warning to unjust towns.","Believers are reminded to trust Allah’s justice even when judgment is delayed."],"related_hadiths":[{"id":"4019","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4010","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah Gives Respite to the Wrongdoer","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that Allah may give respite to wrongdoers, but His seizure is not escaped."},"heading":{"title":"Hadith About Allah Giving Respite to the Wrongdoer","description":"This Hadith about Allah giving respite to the wrongdoer is a clear warning about injustice. The Prophet صلى الله عليه وسلم said that Allah gives time to the wrongdoer, but when He seizes him, He does not let him go. He then recited the verse about the seizure of the Lord when He seizes towns while they are doing wrong. The message is direct: delay should not be mistaken for safety. A person may continue in wrongdoing for a time, but the Hadith reminds us that accountability belongs to Allah. This narration also comforts those who see injustice and wonder why judgment has not come yet. The text teaches patience, fear of Allah, and trust in His justice."},"teachings":["A delay in punishment does not mean wrongdoing is safe.","The Hadith warns wrongdoers about Allah’s final seizure.","The recited verse connects the warning to unjust towns.","Believers are reminded to trust Allah’s justice even when judgment is delayed."],"related_hadiths":[{"id":"4019","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4010","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E470" s="4" t="n"/>
@@ -11319,7 +11323,7 @@
       </c>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Five Tests and Their Consequences","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith lists five public wrongs and the hardships linked to them in the Prophet’s warning."},"heading":{"title":"Hadith About Five Tests: Public Sin, Zakah, Justice, and Rule","description":"This Hadith about five tests gives a serious warning to the Muhajirun. The Prophet صلى الله عليه وسلم mentioned five matters: open immorality, cheating in weights and measures, withholding Zakah, breaking the covenant with Allah and His Messenger, and leaders not ruling by the Book of Allah. The narration links each with hardship, such as disease, famine, oppression, loss to enemies, and fighting among people. The explanation should stay close to the text and not turn it into claims about every specific event today. The Hadith teaches that public sins have public effects. It also shows that worship, trade honesty, covenants, Zakah, and just rule are all part of a healthy community."},"teachings":["Open immorality is warned against in the narration.","Cheating in weights and measures is linked with hardship and oppression.","Withholding Zakah is mentioned as a cause of rain being withheld.","Leadership that leaves the Book of Allah is linked with conflict among people."],"related_hadiths":[{"id":"4018","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4009","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Five Tests and Their Consequences","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith lists five public wrongs and the hardships linked to them in the Prophet’s warning."},"heading":{"title":"Hadith About Five Tests: Public Sin, Zakah, Justice, and Rule","description":"This Hadith about five tests gives a serious warning to the Muhajirun. The Prophet صلى الله عليه وسلم mentioned five matters: open immorality, cheating in weights and measures, withholding Zakah, breaking the covenant with Allah and His Messenger, and leaders not ruling by the Book of Allah. The narration links each with hardship, such as disease, famine, oppression, loss to enemies, and fighting among people. The explanation should stay close to the text and not turn it into claims about every specific event today. The Hadith teaches that public sins have public effects. It also shows that worship, trade honesty, covenants, Zakah, and just rule are all part of a healthy community."},"teachings":["Open immorality is warned against in the narration.","Cheating in weights and measures is linked with hardship and oppression.","Withholding Zakah is mentioned as a cause of rain being withheld.","Leadership that leaves the Book of Allah is linked with conflict among people."],"related_hadiths":[{"id":"4018","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4005","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4009","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E471" s="4" t="n"/>
@@ -11342,7 +11346,7 @@
       </c>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Start Ablution on the Right","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration teaches starting on the right when performing ablution, with the grading noted as Da'if in the text."},"heading":{"title":"Start Ablution on the Right: A Wudu Reminder","description":"This Hadith focuses on one direct instruction: when you perform ablution, start on the right. The translation also notes that this report is Da'if, so the explanation should stay close to the wording and not build extra claims on it. Its message is easy to understand: the right side is given attention at the start of wudu. People searching for start ablution on the right or wudu right side first are usually looking for this simple practice. The narration does not list every step of ablution. It only highlights the beginning point. Read together with authentic narrations on the Prophet liking the right side, it fits the broader Sunnah of giving preference to the right in clean and honorable actions."},"teachings":["The stated instruction is to begin ablution from the right side.","The text itself notes the grading as Da'if, so extra claims should be avoided.","The narration is about the start of wudu, not every detail of wudu.","It supports learning wudu with attention and order."],"related_hadiths":[{"id":"168","book_id":"1","label":"Sahih Bukhari"},{"id":"5926","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Start Ablution on the Right","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration teaches starting on the right when performing ablution, with the grading noted as Da'if in the text."},"heading":{"title":"Start Ablution on the Right: A Wudu Reminder","description":"This Hadith focuses on one direct instruction: when you perform ablution, start on the right. The translation also notes that this report is Da'if, so the explanation should stay close to the wording and not build extra claims on it. Its message is easy to understand: the right side is given attention at the start of wudu. People searching for start ablution on the right or wudu right side first are usually looking for this simple practice. The narration does not list every step of ablution. It only highlights the beginning point. Read together with authentic narrations on the Prophet liking the right side, it fits the broader Sunnah of giving preference to the right in clean and honorable actions."},"teachings":["The stated instruction is to begin ablution from the right side.","The text itself notes the grading as Da'if, so extra claims should be avoided.","The narration is about the start of wudu, not every detail of wudu.","It supports learning wudu with attention and order."],"related_hadiths":[{"id":"168","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5926","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E472" s="4" t="n"/>
@@ -11365,7 +11369,7 @@
       </c>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Calling Wine by Another Name","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns about people drinking wine while renaming it and gathering around music and singers."},"heading":{"title":"Hadith About Wine Called by Another Name","description":"This Hadith about wine called by another name warns against changing the label of a forbidden act while still doing it. The Prophet صلى الله عليه وسلم said that people from his nation will drink wine and call it by another name. The narration also mentions musical instruments being played for them and singing girls singing for them. Then it states a severe punishment: Allah will cause the earth to swallow them and will turn some of them into monkeys and pigs. The safest explanation is to stay with the text. The Hadith warns that renaming something does not make it acceptable, and public gatherings built around disobedience are treated with serious warning in this narration."},"teachings":["Changing the name of wine does not change the act described in the Hadith.","The narration warns about gatherings connected with wine, music, and singers.","The punishment mentioned in the text is severe and should be taken seriously.","A believer should not use new labels to hide a forbidden act."],"related_hadiths":[{"id":"4019","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4018","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5590","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Calling Wine by Another Name","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns about people drinking wine while renaming it and gathering around music and singers."},"heading":{"title":"Hadith About Wine Called by Another Name","description":"This Hadith about wine called by another name warns against changing the label of a forbidden act while still doing it. The Prophet صلى الله عليه وسلم said that people from his nation will drink wine and call it by another name. The narration also mentions musical instruments being played for them and singing girls singing for them. Then it states a severe punishment: Allah will cause the earth to swallow them and will turn some of them into monkeys and pigs. The safest explanation is to stay with the text. The Hadith warns that renaming something does not make it acceptable, and public gatherings built around disobedience are treated with serious warning in this narration."},"teachings":["Changing the name of wine does not change the act described in the Hadith.","The narration warns about gatherings connected with wine, music, and singers.","The punishment mentioned in the text is severe and should be taken seriously.","A believer should not use new labels to hide a forbidden act."],"related_hadiths":[{"id":"4019","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4018","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"5590","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E473" s="4" t="n"/>
@@ -11388,7 +11392,7 @@
       </c>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Righteousness, Dua, and Provision","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how righteousness, supplication, and sin are linked to lifespan, divine decree, and provision in this powerful hadith."},"heading":{"title":"Hadith About Dua, Righteousness, and Provision","description":"This hadith brings together three clear lessons: righteousness, supplication, and the effect of sin. The Prophet صلى الله عليه وسلم said that nothing increases one’s lifespan except righteousness, nothing repels the Divine decree except supplication, and a person may be deprived of provision because of a sin he commits. For people searching for a hadith about dua and qadar, this narration gives a simple but strong reminder. A believer should not treat dua as a small act. It is directly mentioned as a means related to Divine decree. The hadith also connects good conduct with blessing and warns that sins can affect a person’s provision. The message is not to lose hope, but to turn back to Allah through righteousness and supplication."},"teachings":["Righteousness is mentioned as a means connected to increase in lifespan.","Supplication is directly linked to repelling Divine decree in the wording of the hadith.","Sin can be a reason for being deprived of provision.","A believer should combine good actions with sincere dua."],"related_hadiths":[{"id":"2139","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"90","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4031","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Righteousness, Dua, and Provision","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how righteousness, supplication, and sin are linked to lifespan, divine decree, and provision in this powerful hadith."},"heading":{"title":"Hadith About Dua, Righteousness, and Provision","description":"This hadith brings together three clear lessons: righteousness, supplication, and the effect of sin. The Prophet صلى الله عليه وسلم said that nothing increases one’s lifespan except righteousness, nothing repels the Divine decree except supplication, and a person may be deprived of provision because of a sin he commits. For people searching for a hadith about dua and qadar, this narration gives a simple but strong reminder. A believer should not treat dua as a small act. It is directly mentioned as a means related to Divine decree. The hadith also connects good conduct with blessing and warns that sins can affect a person’s provision. The message is not to lose hope, but to turn back to Allah through righteousness and supplication."},"teachings":["Righteousness is mentioned as a means connected to increase in lifespan.","Supplication is directly linked to repelling Divine decree in the wording of the hadith.","Sin can be a reason for being deprived of provision.","A believer should combine good actions with sincere dua."],"related_hadiths":[{"id":"2139","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"90","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4031","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E474" s="4" t="n"/>
@@ -11411,7 +11415,7 @@
       </c>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Why the Prophets Were Tested","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains that the Prophets faced the hardest trials, and that each person is tested according to religious commitment."},"heading":{"title":"Hadith About Trials: Why Believers Are Tested","description":"This is a well-known hadith about trials and tests in Islam. Sa’d bin Abu Waqqas asked which people are most severely tested. The Prophet صلى الله عليه وسلم answered: the Prophets, then the next best and the next best. He explained that a person is tested according to his religious commitment. If someone is firm in faith, the test may be stronger; if his commitment is weaker, the test comes according to that level. The hadith does not present trials as pointless pain. It says trials continue until a person is left walking on earth with no sin on him. This gives comfort to a believer facing hardship, while also teaching patience, humility, and trust in Allah during difficult times."},"teachings":["The Prophets were the most severely tested among people.","A person’s test is connected to his level of religious commitment.","Stronger faith may come with stronger trials.","Trials can be a means through which sins are removed."],"related_hadiths":[{"id":"4024","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4031","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2398","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Why the Prophets Were Tested","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains that the Prophets faced the hardest trials, and that each person is tested according to religious commitment."},"heading":{"title":"Hadith About Trials: Why Believers Are Tested","description":"This is a well-known hadith about trials and tests in Islam. Sa’d bin Abu Waqqas asked which people are most severely tested. The Prophet صلى الله عليه وسلم answered: the Prophets, then the next best and the next best. He explained that a person is tested according to his religious commitment. If someone is firm in faith, the test may be stronger; if his commitment is weaker, the test comes according to that level. The hadith does not present trials as pointless pain. It says trials continue until a person is left walking on earth with no sin on him. This gives comfort to a believer facing hardship, while also teaching patience, humility, and trust in Allah during difficult times."},"teachings":["The Prophets were the most severely tested among people.","A person’s test is connected to his level of religious commitment.","Stronger faith may come with stronger trials.","Trials can be a means through which sins are removed."],"related_hadiths":[{"id":"4024","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4031","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"2398","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E475" s="4" t="n"/>
@@ -11434,7 +11438,7 @@
       </c>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Trials and Reward","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet’s fever and words teach that the Prophets and righteous may face stronger trials, with reward also multiplied."},"heading":{"title":"Hadith About Prophetic Trials and Great Reward","description":"This hadith about trials shows a very personal moment. Abu Sa’eed Al-Khudri visited the Prophet صلى الله عليه وسلم while he was suffering from fever and felt the heat even above the blanket. When he said how hard it was for him, the Prophet صلى الله عليه وسلم explained that the trial is multiplied for the Prophets and so is the reward. He then said that the Prophets are most severely tested, then the righteous. The narration also mentions poverty as one form of trial, to the point that a person may only find a cloak to wrap around himself. The hadith teaches that hardship can come to people of high rank, and that patient acceptance can change how a believer sees calamity."},"teachings":["The Prophets faced severe trials, including physical sickness.","Greater trial is linked in the text with greater reward for the Prophets.","The righteous may also face hard tests, including poverty.","Some righteous people may meet calamity with deep acceptance rather than only fear."],"related_hadiths":[{"id":"4023","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4031","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5641","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Trials and Reward","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet’s fever and words teach that the Prophets and righteous may face stronger trials, with reward also multiplied."},"heading":{"title":"Hadith About Prophetic Trials and Great Reward","description":"This hadith about trials shows a very personal moment. Abu Sa’eed Al-Khudri visited the Prophet صلى الله عليه وسلم while he was suffering from fever and felt the heat even above the blanket. When he said how hard it was for him, the Prophet صلى الله عليه وسلم explained that the trial is multiplied for the Prophets and so is the reward. He then said that the Prophets are most severely tested, then the righteous. The narration also mentions poverty as one form of trial, to the point that a person may only find a cloak to wrap around himself. The hadith teaches that hardship can come to people of high rank, and that patient acceptance can change how a believer sees calamity."},"teachings":["The Prophets faced severe trials, including physical sickness.","Greater trial is linked in the text with greater reward for the Prophets.","The righteous may also face hard tests, including poverty.","Some righteous people may meet calamity with deep acceptance rather than only fear."],"related_hadiths":[{"id":"4023","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4031","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"5641","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E476" s="4" t="n"/>
@@ -11457,7 +11461,7 @@
       </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forgiving People Who Harm You","description":"$book_name$ $hadith_number$ - $chapter_name$. A Prophet was beaten by his people yet prayed for their forgiveness, showing patience and mercy during deep personal harm."},"heading":{"title":"Hadith About Forgiveness: O Lord Forgive My People","description":"This hadith about forgiveness gives a moving picture of prophetic patience. The Messenger of Allah صلى الله عليه وسلم described one of the Prophets who was beaten by his people. While wiping blood from his face, he said, “O Lord forgive my people, for they do not know.” The text is short, but its message is clear. The Prophet in the story was harmed, yet his response was not revenge in that moment. He turned to Allah and asked forgiveness for the very people who hurt him. For anyone searching for a hadith about forgiving others, this narration shows mercy under pressure. It also teaches that ignorance can be a reason to ask Allah to forgive people, without denying the pain of what they did."},"teachings":["Prophetic patience can appear even when a person is badly harmed.","The Prophet in the story asked Allah to forgive his people.","The words “for they do not know” show mercy toward people acting in ignorance.","Responding to harm with dua is a noble prophetic example mentioned in the text."],"related_hadiths":[{"id":"3477","book_id":"1","label":"Sahih Bukhari"},{"id":"1792a","book_id":"2","label":"Sahih Muslim"},{"id":"4027","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forgiving People Who Harm You","description":"$book_name$ $hadith_number$ - $chapter_name$. A Prophet was beaten by his people yet prayed for their forgiveness, showing patience and mercy during deep personal harm."},"heading":{"title":"Hadith About Forgiveness: O Lord Forgive My People","description":"This hadith about forgiveness gives a moving picture of prophetic patience. The Messenger of Allah صلى الله عليه وسلم described one of the Prophets who was beaten by his people. While wiping blood from his face, he said, “O Lord forgive my people, for they do not know.” The text is short, but its message is clear. The Prophet in the story was harmed, yet his response was not revenge in that moment. He turned to Allah and asked forgiveness for the very people who hurt him. For anyone searching for a hadith about forgiving others, this narration shows mercy under pressure. It also teaches that ignorance can be a reason to ask Allah to forgive people, without denying the pain of what they did."},"teachings":["Prophetic patience can appear even when a person is badly harmed.","The Prophet in the story asked Allah to forgive his people.","The words “for they do not know” show mercy toward people acting in ignorance.","Responding to harm with dua is a noble prophetic example mentioned in the text."],"related_hadiths":[{"id":"3477","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1792a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4027","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E477" s="4" t="n"/>
@@ -11480,7 +11484,7 @@
       </c>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibrahim, Lut, and Yusuf in One Hadith","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions Ibrahim’s request for stronger faith, Lut’s wish for support, and Yusuf’s patience in prison."},"heading":{"title":"Hadith About Ibrahim’s Faith and a Heart at Peace","description":"This hadith brings three prophetic moments together. The Prophet صلى الله عليه وسلم mentioned Ibrahim, who asked Allah to show him how He gives life to the dead. The verse quoted in the hadith states that Ibrahim already believed, but wanted his heart to be stronger in faith. The narration also says, “May Allah have mercy on Lut,” and mentions that Lut wished to have powerful support. Then the Prophet صلى الله عليه وسلم spoke about Yusuf and said that if he had stayed in prison as long as Yusuf stayed, he would have accepted the offer. For readers searching for a hadith about Ibrahim and stronger faith, this narration shows that seeking a heart at peace is not the same as rejecting belief."},"teachings":["Ibrahim’s request was tied in the text to making his heart stronger in faith.","The hadith speaks with mercy about Lut and his wish for strong support.","Yusuf’s long stay in prison is mentioned as a sign of great patience.","The narration teaches respect for the Prophets while reflecting on their tests."],"related_hadiths":[{"id":"3372","book_id":"1","label":"Sahih Bukhari"},{"id":"151","book_id":"2","label":"Sahih Muslim"},{"id":"4023","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibrahim, Lut, and Yusuf in One Hadith","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions Ibrahim’s request for stronger faith, Lut’s wish for support, and Yusuf’s patience in prison."},"heading":{"title":"Hadith About Ibrahim’s Faith and a Heart at Peace","description":"This hadith brings three prophetic moments together. The Prophet صلى الله عليه وسلم mentioned Ibrahim, who asked Allah to show him how He gives life to the dead. The verse quoted in the hadith states that Ibrahim already believed, but wanted his heart to be stronger in faith. The narration also says, “May Allah have mercy on Lut,” and mentions that Lut wished to have powerful support. Then the Prophet صلى الله عليه وسلم spoke about Yusuf and said that if he had stayed in prison as long as Yusuf stayed, he would have accepted the offer. For readers searching for a hadith about Ibrahim and stronger faith, this narration shows that seeking a heart at peace is not the same as rejecting belief."},"teachings":["Ibrahim’s request was tied in the text to making his heart stronger in faith.","The hadith speaks with mercy about Lut and his wish for strong support.","Yusuf’s long stay in prison is mentioned as a sign of great patience.","The narration teaches respect for the Prophets while reflecting on their tests."],"related_hadiths":[{"id":"3372","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"151","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4023","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E478" s="4" t="n"/>
@@ -11503,7 +11507,7 @@
       </c>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Uhud and Allah’s Decision","description":"$book_name$ $hadith_number$ - $chapter_name$. After the Prophet was wounded at Uhud, this hadith shows that final judgment and decision belong to Allah alone."},"heading":{"title":"Hadith About Uhud: Not for You Is the Decision","description":"This hadith about Uhud shows a painful scene from the life of the Messenger of Allah صلى الله عليه وسلم. On the Day of Uhud, his molar was broken, he was wounded, and blood flowed down his face. As he wiped the blood, he asked how a people could prosper when they had soaked the face of their Prophet in blood while he was calling them to Allah. Then Allah revealed, “Not for you is the decision.” The lesson must stay close to the text. The Prophet صلى الله عليه وسلم was calling them to Allah, yet he was harmed by them. The revealed words remind us that the final decision belongs to Allah. Even in pain, the matter returns to Him."},"teachings":["The Prophet صلى الله عليه وسلم was harmed while calling people to Allah.","The hadith shows the pain and hardship faced at Uhud.","The revealed verse teaches that the final decision belongs to Allah.","A believer should be careful when speaking about people’s final fate."],"related_hadiths":[{"id":"4067","book_id":"1","label":"Sahih Bukhari"},{"id":"1791","book_id":"2","label":"Sahih Muslim"},{"id":"4025","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Uhud and Allah’s Decision","description":"$book_name$ $hadith_number$ - $chapter_name$. After the Prophet was wounded at Uhud, this hadith shows that final judgment and decision belong to Allah alone."},"heading":{"title":"Hadith About Uhud: Not for You Is the Decision","description":"This hadith about Uhud shows a painful scene from the life of the Messenger of Allah صلى الله عليه وسلم. On the Day of Uhud, his molar was broken, he was wounded, and blood flowed down his face. As he wiped the blood, he asked how a people could prosper when they had soaked the face of their Prophet in blood while he was calling them to Allah. Then Allah revealed, “Not for you is the decision.” The lesson must stay close to the text. The Prophet صلى الله عليه وسلم was calling them to Allah, yet he was harmed by them. The revealed words remind us that the final decision belongs to Allah. Even in pain, the matter returns to Him."},"teachings":["The Prophet صلى الله عليه وسلم was harmed while calling people to Allah.","The hadith shows the pain and hardship faced at Uhud.","The revealed verse teaches that the final decision belongs to Allah.","A believer should be careful when speaking about people’s final fate."],"related_hadiths":[{"id":"4067","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1791","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4025","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E479" s="4" t="n"/>
@@ -11526,7 +11530,7 @@
       </c>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Tree That Came to the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration describes a sign shown to the Prophet when a tree came to him and returned by his command."},"heading":{"title":"Hadith About the Tree Miracle of the Prophet","description":"This hadith about a tree miracle describes a moment when the Messenger of Allah صلى الله عليه وسلم was sorrowful, with his face soaked in blood after some people of Makkah had struck him. Jibril came and asked what had happened. Then he offered to show him a sign. The Prophet صلى الله عليه وسلم agreed, and Jibril told him to call a tree from the far side of the valley. The Prophet صلى الله عليه وسلم called it, and it came walking until it stood before him. Then he told it to go back, and it returned to its place. The Prophet صلى الله عليه وسلم then said, “That is sufficient for me.” The narration shows a sign, comfort after harm, and the Prophet’s calm response when the sign was shown."},"teachings":["The Prophet صلى الله عليه وسلم experienced sorrow and physical harm from some people of Makkah.","Jibril offered to show him a sign at that moment.","The tree came when called and returned when told to go back.","The Prophet صلى الله عليه وسلم accepted the sign and said that it was sufficient for him."],"related_hadiths":[{"id":"4027","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4025","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4026","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Tree That Came to the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration describes a sign shown to the Prophet when a tree came to him and returned by his command."},"heading":{"title":"Hadith About the Tree Miracle of the Prophet","description":"This hadith about a tree miracle describes a moment when the Messenger of Allah صلى الله عليه وسلم was sorrowful, with his face soaked in blood after some people of Makkah had struck him. Jibril came and asked what had happened. Then he offered to show him a sign. The Prophet صلى الله عليه وسلم agreed, and Jibril told him to call a tree from the far side of the valley. The Prophet صلى الله عليه وسلم called it, and it came walking until it stood before him. Then he told it to go back, and it returned to its place. The Prophet صلى الله عليه وسلم then said, “That is sufficient for me.” The narration shows a sign, comfort after harm, and the Prophet’s calm response when the sign was shown."},"teachings":["The Prophet صلى الله عليه وسلم experienced sorrow and physical harm from some people of Makkah.","Jibril offered to show him a sign at that moment.","The tree came when called and returned when told to go back.","The Prophet صلى الله عليه وسلم accepted the sign and said that it was sufficient for him."],"related_hadiths":[{"id":"4027","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4025","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4026","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E480" s="4" t="n"/>
@@ -11549,7 +11553,7 @@
       </c>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Counting Muslims and Being Tested","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asked for Muslims to be counted and warned that even a large community may still be tested."},"heading":{"title":"Hadith About Community Testing and Hidden Prayer","description":"This hadith about community tests begins with the Prophet صلى الله عليه وسلم asking the Companions to count everyone who had uttered Islam. They felt safe because they numbered between six and seven hundred. But the Prophet صلى الله عليه وسلم answered, “You do not know, perhaps you will be tested.” The report then says they were tested until a man among them would not pray except secretly. The message is direct. Numbers alone do not remove the possibility of trial. A community may look strong, yet still face pressure, fear, or hardship. For readers searching for a hadith about Muslims being tested, this narration teaches humility. It also shows that faith may sometimes be protected quietly during times of danger."},"teachings":["Large numbers do not mean a community is free from tests.","The Prophet صلى الله عليه وسلم warned them that they might be tested despite their number.","The report mentions a time when some prayed secretly because of the test.","Believers should not rely only on outward strength."],"related_hadiths":[{"id":"4023","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4032","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4035","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Counting Muslims and Being Tested","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asked for Muslims to be counted and warned that even a large community may still be tested."},"heading":{"title":"Hadith About Community Testing and Hidden Prayer","description":"This hadith about community tests begins with the Prophet صلى الله عليه وسلم asking the Companions to count everyone who had uttered Islam. They felt safe because they numbered between six and seven hundred. But the Prophet صلى الله عليه وسلم answered, “You do not know, perhaps you will be tested.” The report then says they were tested until a man among them would not pray except secretly. The message is direct. Numbers alone do not remove the possibility of trial. A community may look strong, yet still face pressure, fear, or hardship. For readers searching for a hadith about Muslims being tested, this narration teaches humility. It also shows that faith may sometimes be protected quietly during times of danger."},"teachings":["Large numbers do not mean a community is free from tests.","The Prophet صلى الله عليه وسلم warned them that they might be tested despite their number.","The report mentions a time when some prayed secretly because of the test.","Believers should not rely only on outward strength."],"related_hadiths":[{"id":"4023","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4032","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4035","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E481" s="4" t="n"/>
@@ -11572,7 +11576,7 @@
       </c>
       <c r="D482" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Faith of the Hairdresser’s Family","description":"$book_name$ $hadith_number$ - $chapter_name$. This Isra narration tells of the hairdresser, her husband, and sons who refused to give up their religion under threat."},"heading":{"title":"Hadith About the Hairdresser of Pharaoh’s Daughter","description":"This hadith about the hairdresser of Pharaoh’s daughter is a long narration from the Night Journey. The Prophet صلى الله عليه وسلم noticed a good fragrance and asked Jibril about it. Jibril said it was the fragrance of the grave of the hairdresser, her two sons, and her husband. The narration tells how she dropped a comb while combing Pharaoh’s daughter’s hair and said words against Pharaoh. When Pharaoh tried to make her and her husband leave their religion, they refused. He threatened to kill them, and they asked that they be placed together in one grave. The hadith, as given, centers on steadfast faith under severe pressure. It also shows the honor connected to their grave through the good fragrance mentioned during Isra."},"teachings":["The Prophet صلى الله عليه وسلم noticed a good fragrance during the Night Journey.","Jibril identified it as the fragrance of the grave of the hairdresser and her family.","The woman and her husband refused to give up their religion when pressured.","They asked to be placed together in one grave if they were killed."],"related_hadiths":[{"id":"4033","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4034","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4023","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Faith of the Hairdresser’s Family","description":"$book_name$ $hadith_number$ - $chapter_name$. This Isra narration tells of the hairdresser, her husband, and sons who refused to give up their religion under threat."},"heading":{"title":"Hadith About the Hairdresser of Pharaoh’s Daughter","description":"This hadith about the hairdresser of Pharaoh’s daughter is a long narration from the Night Journey. The Prophet صلى الله عليه وسلم noticed a good fragrance and asked Jibril about it. Jibril said it was the fragrance of the grave of the hairdresser, her two sons, and her husband. The narration tells how she dropped a comb while combing Pharaoh’s daughter’s hair and said words against Pharaoh. When Pharaoh tried to make her and her husband leave their religion, they refused. He threatened to kill them, and they asked that they be placed together in one grave. The hadith, as given, centers on steadfast faith under severe pressure. It also shows the honor connected to their grave through the good fragrance mentioned during Isra."},"teachings":["The Prophet صلى الله عليه وسلم noticed a good fragrance during the Night Journey.","Jibril identified it as the fragrance of the grave of the hairdresser and her family.","The woman and her husband refused to give up their religion when pressured.","They asked to be placed together in one grave if they were killed."],"related_hadiths":[{"id":"4033","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4034","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4023","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E482" s="4" t="n"/>
@@ -11595,7 +11599,7 @@
       </c>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mixing With People and Bearing Harm","description":"$book_name$ $hadith_number$ - $chapter_name$. The believer who mixes with people and patiently bears their annoyance is promised a greater reward than one who avoids it."},"heading":{"title":"Hadith About Patience With People and Their Harm","description":"This hadith about patience with people speaks to daily life. The Prophet صلى الله عليه وسلم compared two believers. One mixes with people and bears their annoyance with patience. The other does not mix with people and does not put up with their annoyance. The first is described as having a greater reward. The narration does not praise every kind of social mixing without limits, nor does it discuss every situation. It simply highlights the value of patient conduct when dealing with people and their harm. For anyone searching for a hadith about patience with others, this text gives a balanced reminder: being around people may bring annoyance, but bearing it with patience is a path to greater reward mentioned by the Prophet صلى الله عليه وسلم."},"teachings":["Mixing with people can bring annoyance and harm.","Patience is the key quality praised in the narration.","The believer who bears people’s annoyance is promised a greater reward.","Avoiding people is not presented here as better than patient engagement."],"related_hadiths":[{"id":"4031","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5641","book_id":"1","label":"Sahih Bukhari"},{"id":"2507","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mixing With People and Bearing Harm","description":"$book_name$ $hadith_number$ - $chapter_name$. The believer who mixes with people and patiently bears their annoyance is promised a greater reward than one who avoids it."},"heading":{"title":"Hadith About Patience With People and Their Harm","description":"This hadith about patience with people speaks to daily life. The Prophet صلى الله عليه وسلم compared two believers. One mixes with people and bears their annoyance with patience. The other does not mix with people and does not put up with their annoyance. The first is described as having a greater reward. The narration does not praise every kind of social mixing without limits, nor does it discuss every situation. It simply highlights the value of patient conduct when dealing with people and their harm. For anyone searching for a hadith about patience with others, this text gives a balanced reminder: being around people may bring annoyance, but bearing it with patience is a path to greater reward mentioned by the Prophet صلى الله عليه وسلم."},"teachings":["Mixing with people can bring annoyance and harm.","Patience is the key quality praised in the narration.","The believer who bears people’s annoyance is promised a greater reward.","Avoiding people is not presented here as better than patient engagement."],"related_hadiths":[{"id":"4031","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"5641","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2507","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E483" s="4" t="n"/>
@@ -11618,7 +11622,7 @@
       </c>
       <c r="D484" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Sweetness of Faith","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith names three qualities by which a believer finds the taste or sweetness of faith."},"heading":{"title":"Hadith About the Sweetness of Faith and Love for Allah","description":"This is the famous hadith about the sweetness of faith. The Prophet صلى الله عليه وسلم mentioned three qualities: loving a person only for the sake of Allah, loving Allah and His Messenger more than anything else, and preferring being thrown into fire over returning to disbelief after Allah has saved a person from it. The narration uses the words “taste of faith,” and one narrator said “sweetness of faith.” The meaning is simple and powerful. Faith is not only a statement on the tongue. It shapes love, loyalty, and what a person refuses to return to. For readers searching for three qualities of faith hadith, this narration shows that true faith touches the heart, relationships, and a believer’s sense of safety with Islam."},"teachings":["Loving someone for Allah’s sake is one sign mentioned in the hadith.","Allah and His Messenger should be more beloved than anything else.","A believer should hate returning to disbelief after being saved from it.","Faith has a taste or sweetness connected to these qualities."],"related_hadiths":[{"id":"16","book_id":"1","label":"Sahih Bukhari"},{"id":"43a","book_id":"2","label":"Sahih Muslim"},{"id":"4987","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Sweetness of Faith","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith names three qualities by which a believer finds the taste or sweetness of faith."},"heading":{"title":"Hadith About the Sweetness of Faith and Love for Allah","description":"This is the famous hadith about the sweetness of faith. The Prophet صلى الله عليه وسلم mentioned three qualities: loving a person only for the sake of Allah, loving Allah and His Messenger more than anything else, and preferring being thrown into fire over returning to disbelief after Allah has saved a person from it. The narration uses the words “taste of faith,” and one narrator said “sweetness of faith.” The meaning is simple and powerful. Faith is not only a statement on the tongue. It shapes love, loyalty, and what a person refuses to return to. For readers searching for three qualities of faith hadith, this narration shows that true faith touches the heart, relationships, and a believer’s sense of safety with Islam."},"teachings":["Loving someone for Allah’s sake is one sign mentioned in the hadith.","Allah and His Messenger should be more beloved than anything else.","A believer should hate returning to disbelief after being saved from it.","Faith has a taste or sweetness connected to these qualities."],"related_hadiths":[{"id":"16","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"43a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4987","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E484" s="4" t="n"/>
@@ -11641,7 +11645,7 @@
       </c>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawhid, Prayer, and Avoiding Wine","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet advised Abu Darda not to commit shirk, not to deliberately abandon prayer, and not to drink wine."},"heading":{"title":"Hadith About Tawhid, Prayer, and Avoiding Alcohol","description":"This hadith about tawhid and prayer contains direct advice from the Prophet صلى الله عليه وسلم to Abu Darda. He told him not to associate anything with Allah, even if he was cut and burned. He also warned him not to deliberately leave any prescribed prayer. The hadith says that whoever deliberately neglects it no longer has the protection of Allah. The final advice is not to drink wine, because it is the key to all evil. The text brings together three serious matters: worshiping Allah alone, guarding the obligatory prayer, and staying away from wine. For readers searching for a hadith about abandoning prayer or a hadith about alcohol, this narration gives a clear warning in simple words."},"teachings":["A believer must not associate anything with Allah.","The prescribed prayer should not be deliberately neglected.","The hadith gives a serious warning about leaving prayer on purpose.","Wine is described in the narration as the key to all evil."],"related_hadiths":[{"id":"2621","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1079","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2003a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawhid, Prayer, and Avoiding Wine","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet advised Abu Darda not to commit shirk, not to deliberately abandon prayer, and not to drink wine."},"heading":{"title":"Hadith About Tawhid, Prayer, and Avoiding Alcohol","description":"This hadith about tawhid and prayer contains direct advice from the Prophet صلى الله عليه وسلم to Abu Darda. He told him not to associate anything with Allah, even if he was cut and burned. He also warned him not to deliberately leave any prescribed prayer. The hadith says that whoever deliberately neglects it no longer has the protection of Allah. The final advice is not to drink wine, because it is the key to all evil. The text brings together three serious matters: worshiping Allah alone, guarding the obligatory prayer, and staying away from wine. For readers searching for a hadith about abandoning prayer or a hadith about alcohol, this narration gives a clear warning in simple words."},"teachings":["A believer must not associate anything with Allah.","The prescribed prayer should not be deliberately neglected.","The hadith gives a serious warning about leaving prayer on purpose.","Wine is described in the narration as the key to all evil."],"related_hadiths":[{"id":"2621","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1079","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"2003a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E485" s="4" t="n"/>
@@ -11664,7 +11668,7 @@
       </c>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The World of Trials and Tribulations","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith gives a brief warning that what remains of worldly life is filled with trials and tribulations."},"heading":{"title":"Hadith About Trials and Tribulations in the World","description":"This hadith about trials and tribulations is very brief, but it carries a strong warning. Mu’awiyah narrated that he heard the Prophet صلى الله عليه وسلم say, “There is nothing left of this world except trials and tribulations.” The hadith does not list the types of trials, nor does it give dates or details. So the explanation should stay simple. The world is not a place free from tests. A believer should expect hardship, confusion, and pressure, and should not be shocked when life becomes difficult. The narration points the heart away from false comfort in the world and toward readiness. For people searching for end times trials hadith, this text reminds us to stay alert and steady."},"teachings":["The world is described as a place where trials and tribulations remain.","The hadith gives a warning without listing every type of trial.","A believer should not assume worldly life will be free of tests.","The narration encourages readiness and steadiness in faith."],"related_hadiths":[{"id":"4036","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4037","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4039","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The World of Trials and Tribulations","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith gives a brief warning that what remains of worldly life is filled with trials and tribulations."},"heading":{"title":"Hadith About Trials and Tribulations in the World","description":"This hadith about trials and tribulations is very brief, but it carries a strong warning. Mu’awiyah narrated that he heard the Prophet صلى الله عليه وسلم say, “There is nothing left of this world except trials and tribulations.” The hadith does not list the types of trials, nor does it give dates or details. So the explanation should stay simple. The world is not a place free from tests. A believer should expect hardship, confusion, and pressure, and should not be shocked when life becomes difficult. The narration points the heart away from false comfort in the world and toward readiness. For people searching for end times trials hadith, this text reminds us to stay alert and steady."},"teachings":["The world is described as a place where trials and tribulations remain.","The hadith gives a warning without listing every type of trial.","A believer should not assume worldly life will be free of tests.","The narration encourages readiness and steadiness in faith."],"related_hadiths":[{"id":"4036","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4037","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4039","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E486" s="4" t="n"/>
@@ -11687,7 +11691,7 @@
       </c>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Years of Deception and Ruwaibidah","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns of years when liars are trusted, honest people are rejected, and base people speak on public affairs."},"heading":{"title":"Hadith About Ruwaibidah and Years of Deception","description":"This hadith about Ruwaibidah gives a clear warning about moral confusion. The Prophet صلى الله عليه وسلم said that years of treachery would come, when the liar is regarded as honest and the honest person is regarded as a liar. The traitor is treated as faithful, while the faithful person is treated as a traitor. Then the Ruwaibidah will speak. When asked who the Ruwaibidah are, the Prophet صلى الله عليه وسلم described them as vile and base men who control the affairs of the people. The narration is not a license to insult people carelessly. It is a warning about a time when truth, trust, and public responsibility are turned upside down. The believer should value honesty and be careful who is trusted with public matters."},"teachings":["A time will come when honesty and lying are confused in people’s eyes.","The traitor may be treated as faithful, and the faithful person as a traitor.","The Ruwaibidah are described as vile and base men involved in public affairs.","The hadith teaches caution about truth, trust, and leadership."],"related_hadiths":[{"id":"4035","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4038","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4039","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Years of Deception and Ruwaibidah","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns of years when liars are trusted, honest people are rejected, and base people speak on public affairs."},"heading":{"title":"Hadith About Ruwaibidah and Years of Deception","description":"This hadith about Ruwaibidah gives a clear warning about moral confusion. The Prophet صلى الله عليه وسلم said that years of treachery would come, when the liar is regarded as honest and the honest person is regarded as a liar. The traitor is treated as faithful, while the faithful person is treated as a traitor. Then the Ruwaibidah will speak. When asked who the Ruwaibidah are, the Prophet صلى الله عليه وسلم described them as vile and base men who control the affairs of the people. The narration is not a license to insult people carelessly. It is a warning about a time when truth, trust, and public responsibility are turned upside down. The believer should value honesty and be careful who is trusted with public matters."},"teachings":["A time will come when honesty and lying are confused in people’s eyes.","The traitor may be treated as faithful, and the faithful person as a traitor.","The Ruwaibidah are described as vile and base men involved in public affairs.","The hadith teaches caution about truth, trust, and leadership."],"related_hadiths":[{"id":"4035","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4038","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4039","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E487" s="4" t="n"/>
@@ -11710,7 +11714,7 @@
       </c>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | When Calamity Makes Life Feel Heavy","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns that severe calamity may make a person wish to be in the place of someone in the grave."},"heading":{"title":"Hadith About Calamity and Wishing for Death","description":"This hadith about calamity describes a hard future scene. The Prophet صلى الله عليه وسلم swore by the One in Whose Hand is his soul that the world would not pass away until a man would pass by a grave, roll on it, and say that he wished he were in the place of its occupant. The narration then clarifies that the reason is not a religious motive, but calamity. The text is not telling people to seek death. It shows how heavy worldly hardship can become for some people. For readers searching for a hadith about wishing for death, this narration should be read with care: it describes the pressure of calamity and the weakness people may feel under it."},"teachings":["Some future calamities may become very heavy for people.","The person in the hadith wishes to be in the grave because of calamity, not religion.","The narration shows how worldly pressure can affect a person’s heart.","The hadith describes a situation; it does not encourage seeking death."],"related_hadiths":[{"id":"5671","book_id":"1","label":"Sahih Bukhari"},{"id":"5673","book_id":"1","label":"Sahih Bukhari"},{"id":"4035","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | When Calamity Makes Life Feel Heavy","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns that severe calamity may make a person wish to be in the place of someone in the grave."},"heading":{"title":"Hadith About Calamity and Wishing for Death","description":"This hadith about calamity describes a hard future scene. The Prophet صلى الله عليه وسلم swore by the One in Whose Hand is his soul that the world would not pass away until a man would pass by a grave, roll on it, and say that he wished he were in the place of its occupant. The narration then clarifies that the reason is not a religious motive, but calamity. The text is not telling people to seek death. It shows how heavy worldly hardship can become for some people. For readers searching for a hadith about wishing for death, this narration should be read with care: it describes the pressure of calamity and the weakness people may feel under it."},"teachings":["Some future calamities may become very heavy for people.","The person in the hadith wishes to be in the grave because of calamity, not religion.","The narration shows how worldly pressure can affect a person’s heart.","The hadith describes a situation; it does not encourage seeking death."],"related_hadiths":[{"id":"5671","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5673","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4035","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E488" s="4" t="n"/>
@@ -11733,7 +11737,7 @@
       </c>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | When the Best Are Taken","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes people being sorted like dates, with the best taken and the worst left behind."},"heading":{"title":"Hadith About End Times: The Best Taken and Worst Left","description":"This hadith about the end times uses a strong image. The Prophet صلى الله عليه وسلم said that people will be picked over just as good dates are selected and separated from bad ones. Then he said the best of people will be taken and the worst will remain. The final words, “so die if you can,” should be read carefully as part of this difficult warning, not as a simple instruction to harm oneself. The main point in the text is the decline that happens when the best people are removed and the worst are left behind. For readers searching for hadith about the best people being taken, this narration reminds us that the quality of people around a community matters deeply."},"teachings":["The hadith compares people being sorted to dates being selected.","It says the best of people will be taken away.","It warns that the worst of people will remain after that selection.","The narration points to a serious decline in people’s condition."],"related_hadiths":[{"id":"4037","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4039","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4035","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | When the Best Are Taken","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes people being sorted like dates, with the best taken and the worst left behind."},"heading":{"title":"Hadith About End Times: The Best Taken and Worst Left","description":"This hadith about the end times uses a strong image. The Prophet صلى الله عليه وسلم said that people will be picked over just as good dates are selected and separated from bad ones. Then he said the best of people will be taken and the worst will remain. The final words, “so die if you can,” should be read carefully as part of this difficult warning, not as a simple instruction to harm oneself. The main point in the text is the decline that happens when the best people are removed and the worst are left behind. For readers searching for hadith about the best people being taken, this narration reminds us that the quality of people around a community matters deeply."},"teachings":["The hadith compares people being sorted to dates being selected.","It says the best of people will be taken away.","It warns that the worst of people will remain after that selection.","The narration points to a serious decline in people’s condition."],"related_hadiths":[{"id":"4037","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4039","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4035","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E489" s="4" t="n"/>
@@ -11756,7 +11760,7 @@
       </c>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Harder Religion and the Hour","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions growing difficulty, stinginess, the Hour coming upon the worst people, and Eisa ibn Maryam."},"heading":{"title":"Hadith About Hardship, Stinginess, and the Hour","description":"This hadith about the end times lists several hard conditions. The Prophet صلى الله عليه وسلم said that adhering to religion will become harder, worldly affairs will become more difficult, and people will become more stingy. He also said that the Hour will come only upon the worst of people, and mentioned that the only Mahdi after Muhammad صلى الله عليه وسلم is Eisa ibn Maryam. The explanation must stay close to the wording. The narration is about growing hardship, decline in generosity, and the condition of people near the Hour. For readers searching for a hadith about religion becoming harder, this text is a reminder to stay steady when faith feels difficult and when people around us become less giving."},"teachings":["Adhering to religion is described as becoming harder.","Worldly affairs are described as becoming more difficult.","The hadith mentions that people will become more stingy.","The Hour is described as coming upon the worst of people."],"related_hadiths":[{"id":"2949a","book_id":"2","label":"Sahih Muslim"},{"id":"4035","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4038","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Harder Religion and the Hour","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions growing difficulty, stinginess, the Hour coming upon the worst people, and Eisa ibn Maryam."},"heading":{"title":"Hadith About Hardship, Stinginess, and the Hour","description":"This hadith about the end times lists several hard conditions. The Prophet صلى الله عليه وسلم said that adhering to religion will become harder, worldly affairs will become more difficult, and people will become more stingy. He also said that the Hour will come only upon the worst of people, and mentioned that the only Mahdi after Muhammad صلى الله عليه وسلم is Eisa ibn Maryam. The explanation must stay close to the wording. The narration is about growing hardship, decline in generosity, and the condition of people near the Hour. For readers searching for a hadith about religion becoming harder, this text is a reminder to stay steady when faith feels difficult and when people around us become less giving."},"teachings":["Adhering to religion is described as becoming harder.","Worldly affairs are described as becoming more difficult.","The hadith mentions that people will become more stingy.","The Hour is described as coming upon the worst of people."],"related_hadiths":[{"id":"2949a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4035","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4038","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E490" s="4" t="n"/>
@@ -11779,7 +11783,7 @@
       </c>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | I and the Hour Like Two Fingers","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said that he and the Hour were sent like two fingers held together, pointing to the nearness of the Hour."},"heading":{"title":"Hadith About the Hour Being Near","description":"This hadith about the Hour is short and easy to remember. Abu Hurairah narrated that the Messenger of Allah صلى الله عليه وسلم said, “I and the Hour have been sent like these two,” and he held up two fingers together. The image is simple: two fingers placed close together. The hadith does not give a date for the Hour. It only points to nearness in relation to the Prophet’s mission. For people searching for the hadith I and the Hour are like these two fingers, this narration reminds us not to live as if the Hereafter is far away. It calls the heart to awareness, preparation, and seriousness, while leaving the exact timing of the Hour to Allah."},"teachings":["The Prophet صلى الله عليه وسلم described his coming and the Hour as close like two fingers.","The hadith does not give the exact time of the Hour.","The image teaches awareness of the nearness of the Hereafter.","A believer should respond with preparation, not date-setting."],"related_hadiths":[{"id":"4936","book_id":"1","label":"Sahih Bukhari"},{"id":"6504","book_id":"1","label":"Sahih Bukhari"},{"id":"2951a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | I and the Hour Like Two Fingers","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said that he and the Hour were sent like two fingers held together, pointing to the nearness of the Hour."},"heading":{"title":"Hadith About the Hour Being Near","description":"This hadith about the Hour is short and easy to remember. Abu Hurairah narrated that the Messenger of Allah صلى الله عليه وسلم said, “I and the Hour have been sent like these two,” and he held up two fingers together. The image is simple: two fingers placed close together. The hadith does not give a date for the Hour. It only points to nearness in relation to the Prophet’s mission. For people searching for the hadith I and the Hour are like these two fingers, this narration reminds us not to live as if the Hereafter is far away. It calls the heart to awareness, preparation, and seriousness, while leaving the exact timing of the Hour to Allah."},"teachings":["The Prophet صلى الله عليه وسلم described his coming and the Hour as close like two fingers.","The hadith does not give the exact time of the Hour.","The image teaches awareness of the nearness of the Hereafter.","A believer should respond with preparation, not date-setting."],"related_hadiths":[{"id":"4936","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6504","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2951a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E491" s="4" t="n"/>
@@ -11802,7 +11806,7 @@
       </c>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Signs of the Hour and the Ten Major Signs","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how this Hadith names major signs of the Hour, including Dajjal, smoke, and the sun rising from the west."},"heading":{"title":"Signs of the Hour: Dajjal, Smoke, and the Sun Rising from the West","description":"This Hadith about the signs of the Hour shows a short but strong warning from the Prophet صلى الله عليه وسلم. The companions were talking about the Hour, and the Prophet صلى الله عليه وسلم told them that it would not begin until ten signs appear. In this narration, three signs are named: Dajjal, the smoke, and the rising of the sun from the west. The core topic is End Times. The Hadith does not give dates or ask people to guess when these signs will happen. It simply teaches awareness. For anyone searching for signs of Qiyamah or major signs of the Day of Judgment, this Hadith reminds us that the Hour is real and known by Allah."},"teachings":["The Hour has signs that will appear before it begins.","Dajjal, smoke, and the sun rising from the west are named among these signs.","The Hadith teaches awareness without giving a date for the Hour.","Talking about the Hour should lead to seriousness and reflection."],"related_hadiths":[{"id":"4055","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4056","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2901a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Signs of the Hour and the Ten Major Signs","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how this Hadith names major signs of the Hour, including Dajjal, smoke, and the sun rising from the west."},"heading":{"title":"Signs of the Hour: Dajjal, Smoke, and the Sun Rising from the West","description":"This Hadith about the signs of the Hour shows a short but strong warning from the Prophet صلى الله عليه وسلم. The companions were talking about the Hour, and the Prophet صلى الله عليه وسلم told them that it would not begin until ten signs appear. In this narration, three signs are named: Dajjal, the smoke, and the rising of the sun from the west. The core topic is End Times. The Hadith does not give dates or ask people to guess when these signs will happen. It simply teaches awareness. For anyone searching for signs of Qiyamah or major signs of the Day of Judgment, this Hadith reminds us that the Hour is real and known by Allah."},"teachings":["The Hour has signs that will appear before it begins.","Dajjal, smoke, and the sun rising from the west are named among these signs.","The Hadith teaches awareness without giving a date for the Hour.","Talking about the Hour should lead to seriousness and reflection."],"related_hadiths":[{"id":"4055","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4056","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"2901a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E492" s="4" t="n"/>
@@ -11825,7 +11829,7 @@
       </c>
       <c r="D493" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Six Signs Before the Hour","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith lists six events before the Hour, including the Prophet’s death, Jerusalem, trials, wealth, and betrayal."},"heading":{"title":"Six Signs Before the Hour: A Hadith on Trials, Wealth, and Betrayal","description":"This Hadith about six signs before the Hour records a serious message given to Awf bin Malik during Tabuk. The Prophet صلى الله عليه وسلم told him to remember six matters before the Hour: his own death, the conquest of Baitul-Maqdis, a disease, much wealth with continued dissatisfaction, a tribulation entering every Muslim house, and a treaty with the Romans followed by betrayal. The core topic is End Times. The Hadith joins personal grief, public events, wealth, and conflict in one warning. It does not ask believers to make wild claims. It teaches that the signs of the Hour include both large world events and deep social tests."},"teachings":["The Prophet صلى الله عليه وسلم named six events that would come before the Hour.","Abundant wealth does not always remove dissatisfaction.","Trials may spread widely and touch many homes.","A treaty can be broken, so people should not be careless about trust."],"related_hadiths":[{"id":"3176","book_id":"1","label":"Sahih Bukhari"},{"id":"4047","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4052","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Six Signs Before the Hour","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith lists six events before the Hour, including the Prophet’s death, Jerusalem, trials, wealth, and betrayal."},"heading":{"title":"Six Signs Before the Hour: A Hadith on Trials, Wealth, and Betrayal","description":"This Hadith about six signs before the Hour records a serious message given to Awf bin Malik during Tabuk. The Prophet صلى الله عليه وسلم told him to remember six matters before the Hour: his own death, the conquest of Baitul-Maqdis, a disease, much wealth with continued dissatisfaction, a tribulation entering every Muslim house, and a treaty with the Romans followed by betrayal. The core topic is End Times. The Hadith joins personal grief, public events, wealth, and conflict in one warning. It does not ask believers to make wild claims. It teaches that the signs of the Hour include both large world events and deep social tests."},"teachings":["The Prophet صلى الله عليه وسلم named six events that would come before the Hour.","Abundant wealth does not always remove dissatisfaction.","Trials may spread widely and touch many homes.","A treaty can be broken, so people should not be careless about trust."],"related_hadiths":[{"id":"3176","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4047","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4052","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E493" s="4" t="n"/>
@@ -11848,7 +11852,7 @@
       </c>
       <c r="D494" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Social Chaos Before the Hour","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns of killing rulers, sword fighting, and the worst people gaining worldly control before the Hour."},"heading":{"title":"Social Chaos Before the Hour: A Hadith on Fighting and Corruption","description":"This Hadith about signs of the Hour speaks about a time of deep disorder. The Prophet صلى الله عليه وسلم said the Hour will not begin until people kill their ruler, fight one another with swords, and the world is inherited by the worst among them. The core topic is Social Chaos. The wording is direct and heavy. It points to broken order, violence, and the rise of corrupt people. The Hadith does not give a timetable or name a specific ruler. It teaches that one sign of the end times is not only strange events in nature, but also severe moral and social breakdown among people."},"teachings":["Killing and internal fighting are named as signs before the Hour.","Leadership and public order can break down near the end times.","The Hadith warns against a society where the worst people gain control.","Violence among people is treated as a serious sign, not a small matter."],"related_hadiths":[{"id":"4047","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4050","book_id":"6","label":"Sunan Ibn Majah"},{"id":"7062","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Social Chaos Before the Hour","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns of killing rulers, sword fighting, and the worst people gaining worldly control before the Hour."},"heading":{"title":"Social Chaos Before the Hour: A Hadith on Fighting and Corruption","description":"This Hadith about signs of the Hour speaks about a time of deep disorder. The Prophet صلى الله عليه وسلم said the Hour will not begin until people kill their ruler, fight one another with swords, and the world is inherited by the worst among them. The core topic is Social Chaos. The wording is direct and heavy. It points to broken order, violence, and the rise of corrupt people. The Hadith does not give a timetable or name a specific ruler. It teaches that one sign of the end times is not only strange events in nature, but also severe moral and social breakdown among people."},"teachings":["Killing and internal fighting are named as signs before the Hour.","Leadership and public order can break down near the end times.","The Hadith warns against a society where the worst people gain control.","Violence among people is treated as a serious sign, not a small matter."],"related_hadiths":[{"id":"4047","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4050","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"7062","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E494" s="4" t="n"/>
@@ -11871,7 +11875,7 @@
       </c>
       <c r="D495" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Knowledge of the Hour Belongs to Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains that only Allah knows the Hour, while some of its portents are clearly mentioned."},"heading":{"title":"Knowledge of the Hour: Only Allah Knows When It Will Come","description":"This Hadith about the Hour answers a question many people ask: when will it happen? The Prophet صلى الله عليه وسلم said that the one being asked did not know more than the one asking. Then he mentioned signs: the slave woman giving birth to her mistress, barefoot and naked people becoming leaders, and shepherds competing in buildings. He also recited the verse that knowledge of the Hour is with Allah alone. The core topic is Divine Knowledge. This Hadith teaches balance. We can know some signs of the Hour, but we cannot know its exact time. So the believer should avoid guessing dates and focus on what Allah has revealed."},"teachings":["The exact time of the Hour is known only to Allah.","The Prophet صلى الله عليه وسلم mentioned signs without giving a date.","Building competition and social change are named among the portents.","A believer should not claim hidden knowledge that belongs to Allah."],"related_hadiths":[{"id":"50","book_id":"1","label":"Sahih Bukhari"},{"id":"64","book_id":"6","label":"Sunan Ibn Majah"},{"id":"8a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Knowledge of the Hour Belongs to Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains that only Allah knows the Hour, while some of its portents are clearly mentioned."},"heading":{"title":"Knowledge of the Hour: Only Allah Knows When It Will Come","description":"This Hadith about the Hour answers a question many people ask: when will it happen? The Prophet صلى الله عليه وسلم said that the one being asked did not know more than the one asking. Then he mentioned signs: the slave woman giving birth to her mistress, barefoot and naked people becoming leaders, and shepherds competing in buildings. He also recited the verse that knowledge of the Hour is with Allah alone. The core topic is Divine Knowledge. This Hadith teaches balance. We can know some signs of the Hour, but we cannot know its exact time. So the believer should avoid guessing dates and focus on what Allah has revealed."},"teachings":["The exact time of the Hour is known only to Allah.","The Prophet صلى الله عليه وسلم mentioned signs without giving a date.","Building competition and social change are named among the portents.","A believer should not claim hidden knowledge that belongs to Allah."],"related_hadiths":[{"id":"50","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"64","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"8a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E495" s="4" t="n"/>
@@ -11894,7 +11898,7 @@
       </c>
       <c r="D496" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Loss of Knowledge and Spread of Ignorance","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith names signs of the Hour: loss of knowledge, spread of ignorance, immoral acts, wine, and imbalance."},"heading":{"title":"Loss of Knowledge Before the Hour: A Hadith on Ignorance and Moral Decline","description":"This Hadith about the signs of the Hour focuses on knowledge and moral decline. Anas bin Malik said he heard this directly from the Messenger of Allah صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم said that among the portents of the Hour are that knowledge will be taken away, ignorance will spread, illegal sex will become widespread, wine will be drunk, and men will disappear while women remain, until one man is in charge of fifty women. The core topic is Knowledge. The Hadith shows that the end times are marked by changes in belief, behavior, and society. It warns against ignorance and careless living without adding details beyond the narration."},"teachings":["Loss of knowledge is named as a sign of the Hour.","Ignorance spreading among people is treated as a major warning.","Widespread illegal sex and drinking wine are signs of moral decline.","The Hadith points to a future social imbalance mentioned by the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"80","book_id":"1","label":"Sahih Bukhari"},{"id":"4050","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4051","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Loss of Knowledge and Spread of Ignorance","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith names signs of the Hour: loss of knowledge, spread of ignorance, immoral acts, wine, and imbalance."},"heading":{"title":"Loss of Knowledge Before the Hour: A Hadith on Ignorance and Moral Decline","description":"This Hadith about the signs of the Hour focuses on knowledge and moral decline. Anas bin Malik said he heard this directly from the Messenger of Allah صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم said that among the portents of the Hour are that knowledge will be taken away, ignorance will spread, illegal sex will become widespread, wine will be drunk, and men will disappear while women remain, until one man is in charge of fifty women. The core topic is Knowledge. The Hadith shows that the end times are marked by changes in belief, behavior, and society. It warns against ignorance and careless living without adding details beyond the narration."},"teachings":["Loss of knowledge is named as a sign of the Hour.","Ignorance spreading among people is treated as a major warning.","Widespread illegal sex and drinking wine are signs of moral decline.","The Hadith points to a future social imbalance mentioned by the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"80","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4050","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4051","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E496" s="4" t="n"/>
@@ -11917,7 +11921,7 @@
       </c>
       <c r="D497" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Euphrates Mountain of Gold","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that the Euphrates will uncover a mountain of gold and people will fight over it."},"heading":{"title":"Euphrates Mountain of Gold Hadith: A Warning About Greed and Fighting","description":"This Hadith about the Euphrates mountain of gold gives a clear sign before the Hour. The Prophet صلى الله عليه وسلم said the Hour will not begin until the Euphrates uncovers a mountain of gold. People will fight over it, and nine out of every ten will be killed. The core topic is Greed. The Hadith does not tell people to seek that gold. It shows how wealth can become a cause of deadly conflict when people rush toward it. For those searching for the Euphrates river hadith, the message here is serious: a worldly treasure can become a great trial when people fight over it."},"teachings":["The Euphrates uncovering a mountain of gold is named as a sign before the Hour.","People fighting over wealth is shown as a dangerous trial.","The Hadith links greed with severe loss of life.","A believer should see wealth as a test, not only as a gain."],"related_hadiths":[{"id":"7119","book_id":"1","label":"Sahih Bukhari"},{"id":"4047","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4052","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Euphrates Mountain of Gold","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that the Euphrates will uncover a mountain of gold and people will fight over it."},"heading":{"title":"Euphrates Mountain of Gold Hadith: A Warning About Greed and Fighting","description":"This Hadith about the Euphrates mountain of gold gives a clear sign before the Hour. The Prophet صلى الله عليه وسلم said the Hour will not begin until the Euphrates uncovers a mountain of gold. People will fight over it, and nine out of every ten will be killed. The core topic is Greed. The Hadith does not tell people to seek that gold. It shows how wealth can become a cause of deadly conflict when people rush toward it. For those searching for the Euphrates river hadith, the message here is serious: a worldly treasure can become a great trial when people fight over it."},"teachings":["The Euphrates uncovering a mountain of gold is named as a sign before the Hour.","People fighting over wealth is shown as a dangerous trial.","The Hadith links greed with severe loss of life.","A believer should see wealth as a test, not only as a gain."],"related_hadiths":[{"id":"7119","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4047","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4052","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E497" s="4" t="n"/>
@@ -11940,7 +11944,7 @@
       </c>
       <c r="D498" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wealth, Trials, and Harj","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that abundant wealth, tribulations, and much killing will appear before the Hour."},"heading":{"title":"Harj Before the Hour: Wealth, Tribulations, and Killing","description":"This Hadith about Harj explains one of the serious signs before the Hour. The Prophet صلى الله عليه وسلم said the Hour will not begin until wealth becomes abundant, tribulations appear, and Harj increases. When the companions asked what Harj means, he answered: killing, killing, killing. The core topic is Tribulation. The Hadith shows that more wealth does not always mean more peace. A society may have much money and still face trials and bloodshed. The repeated word killing makes the warning stronger. For anyone searching for Harj meaning in Hadith, this narration gives the meaning clearly and directly from the Prophet صلى الله عليه وسلم."},"teachings":["Abundant wealth is named among signs before the Hour.","Tribulations will appear before the Hour.","Harj is explained in the Hadith as killing.","Material wealth does not by itself protect people from social disorder."],"related_hadiths":[{"id":"4050","book_id":"6","label":"Sunan Ibn Majah"},{"id":"7062","book_id":"1","label":"Sahih Bukhari"},{"id":"4052","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wealth, Trials, and Harj","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that abundant wealth, tribulations, and much killing will appear before the Hour."},"heading":{"title":"Harj Before the Hour: Wealth, Tribulations, and Killing","description":"This Hadith about Harj explains one of the serious signs before the Hour. The Prophet صلى الله عليه وسلم said the Hour will not begin until wealth becomes abundant, tribulations appear, and Harj increases. When the companions asked what Harj means, he answered: killing, killing, killing. The core topic is Tribulation. The Hadith shows that more wealth does not always mean more peace. A society may have much money and still face trials and bloodshed. The repeated word killing makes the warning stronger. For anyone searching for Harj meaning in Hadith, this narration gives the meaning clearly and directly from the Prophet صلى الله عليه وسلم."},"teachings":["Abundant wealth is named among signs before the Hour.","Tribulations will appear before the Hour.","Harj is explained in the Hadith as killing.","Material wealth does not by itself protect people from social disorder."],"related_hadiths":[{"id":"4050","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"7062","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4052","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E498" s="4" t="n"/>
@@ -11963,7 +11967,7 @@
       </c>
       <c r="D499" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Acting on Knowledge","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that reading scripture is not enough if people do not act upon what it contains."},"heading":{"title":"Acting on Knowledge: Reading the Qur’an Must Lead to Practice","description":"This Hadith about knowledge explains that real knowledge is not only reading words. Ziyad bin Labid wondered how knowledge could disappear while Muslims read the Qur’an and teach it to their children. The Prophet صلى الله عليه وسلم answered by pointing to Jews and Christians who read the Tawrah and Injil but did not act upon what was in them. The core topic is Knowledge. The message is simple and direct: knowledge can lose its effect when people do not live by it. For those searching for a Hadith about acting on knowledge, this narration warns against treating recitation and teaching as enough without practice."},"teachings":["Reading scripture alone is not enough if people do not act on it.","Knowledge can disappear in effect when practice is lost.","Teaching children the Qur’an should be joined with living by its guidance.","The Hadith warns against a gap between learning and action."],"related_hadiths":[{"id":"100","book_id":"1","label":"Sahih Bukhari"},{"id":"2673","book_id":"2","label":"Sahih Muslim"},{"id":"4050","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Acting on Knowledge","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that reading scripture is not enough if people do not act upon what it contains."},"heading":{"title":"Acting on Knowledge: Reading the Qur’an Must Lead to Practice","description":"This Hadith about knowledge explains that real knowledge is not only reading words. Ziyad bin Labid wondered how knowledge could disappear while Muslims read the Qur’an and teach it to their children. The Prophet صلى الله عليه وسلم answered by pointing to Jews and Christians who read the Tawrah and Injil but did not act upon what was in them. The core topic is Knowledge. The message is simple and direct: knowledge can lose its effect when people do not live by it. For those searching for a Hadith about acting on knowledge, this narration warns against treating recitation and teaching as enough without practice."},"teachings":["Reading scripture alone is not enough if people do not act on it.","Knowledge can disappear in effect when practice is lost.","Teaching children the Qur’an should be joined with living by its guidance.","The Hadith warns against a gap between learning and action."],"related_hadiths":[{"id":"100","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2673","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4050","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E499" s="4" t="n"/>
@@ -11986,7 +11990,7 @@
       </c>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Ilaha Illallah and Fading Knowledge","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes Islam fading, the Qur’an being taken away, and people holding to La ilaha illallah."},"heading":{"title":"La Ilaha Illallah Hadith: Faith When Knowledge Fades","description":"This Hadith about La ilaha illallah describes a time when Islam will wear out like embroidery on a garment. People will no longer know fasting, prayer, rites, or charity. The Book of Allah will be taken away at night, and no verse will remain on earth. Some old men and women will still say that they heard their fathers saying La ilaha illallah, so they say it too. When Silah asked what good it would do them, Hudhaifah answered that it would save them from Hell. The core topic is Faith. The Hadith focuses on fading knowledge and the remaining value of the testimony of faith in that situation."},"teachings":["Islam is described as wearing out among people near the end times.","Knowledge of fasting, prayer, rites, and charity will be lost among some people.","The Qur’an being taken away is mentioned in this narration.","La ilaha illallah is shown as saving those people from Hell in the stated situation."],"related_hadiths":[{"id":"4048","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4053","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2673","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Ilaha Illallah and Fading Knowledge","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes Islam fading, the Qur’an being taken away, and people holding to La ilaha illallah."},"heading":{"title":"La Ilaha Illallah Hadith: Faith When Knowledge Fades","description":"This Hadith about La ilaha illallah describes a time when Islam will wear out like embroidery on a garment. People will no longer know fasting, prayer, rites, or charity. The Book of Allah will be taken away at night, and no verse will remain on earth. Some old men and women will still say that they heard their fathers saying La ilaha illallah, so they say it too. When Silah asked what good it would do them, Hudhaifah answered that it would save them from Hell. The core topic is Faith. The Hadith focuses on fading knowledge and the remaining value of the testimony of faith in that situation."},"teachings":["Islam is described as wearing out among people near the end times.","Knowledge of fasting, prayer, rites, and charity will be lost among some people.","The Qur’an being taken away is mentioned in this narration.","La ilaha illallah is shown as saving those people from Hell in the stated situation."],"related_hadiths":[{"id":"4048","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4053","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"2673","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E500" s="4" t="n"/>
@@ -12009,7 +12013,7 @@
       </c>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Knowledge Lost and Harj Increases","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that before the Hour, knowledge will disappear, ignorance will spread, and killing will increase."},"heading":{"title":"Knowledge Will Disappear Before the Hour: A Hadith on Ignorance and Harj","description":"This Hadith about knowledge disappearing before the Hour gives a short warning with three signs. The Prophet صلى الله عليه وسلم said that just before the Hour there will be days when knowledge will disappear, ignorance will become widespread, and Harj will increase. The narration also explains that Harj means killing. The core topic is Knowledge. The Hadith shows that loss of knowledge is not a small matter. When knowledge fades, ignorance spreads, and violence becomes common. The message is not to guess dates for Qiyamah, but to value true knowledge and understand the danger of ignorance and killing in society."},"teachings":["Knowledge disappearing is named as a sign before the Hour.","Ignorance becoming widespread is linked with the end times.","Harj is explained as killing.","The Hadith warns that loss of knowledge and violence can appear together."],"related_hadiths":[{"id":"4051","book_id":"6","label":"Sunan Ibn Majah"},{"id":"7062","book_id":"1","label":"Sahih Bukhari"},{"id":"7064","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Knowledge Lost and Harj Increases","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that before the Hour, knowledge will disappear, ignorance will spread, and killing will increase."},"heading":{"title":"Knowledge Will Disappear Before the Hour: A Hadith on Ignorance and Harj","description":"This Hadith about knowledge disappearing before the Hour gives a short warning with three signs. The Prophet صلى الله عليه وسلم said that just before the Hour there will be days when knowledge will disappear, ignorance will become widespread, and Harj will increase. The narration also explains that Harj means killing. The core topic is Knowledge. The Hadith shows that loss of knowledge is not a small matter. When knowledge fades, ignorance spreads, and violence becomes common. The message is not to guess dates for Qiyamah, but to value true knowledge and understand the danger of ignorance and killing in society."},"teachings":["Knowledge disappearing is named as a sign before the Hour.","Ignorance becoming widespread is linked with the end times.","Harj is explained as killing.","The Hadith warns that loss of knowledge and violence can appear together."],"related_hadiths":[{"id":"4051","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"7062","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7064","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E501" s="4" t="n"/>
@@ -12032,7 +12036,7 @@
       </c>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ignorance, Lost Knowledge, and Killing","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith says days will come when ignorance spreads, knowledge disappears, and Harj becomes common."},"heading":{"title":"Ignorance Will Spread: A Hadith on Knowledge Disappearing and Harj","description":"This Hadith about ignorance and Harj is very close in meaning to other narrations on the signs before the Hour. The Prophet صلى الله عليه وسلم said that days would come after the companions when ignorance would become widespread, knowledge would disappear, and Harj would become much. When they asked what Harj meant, he answered: killing. The core topic is Ignorance. The Hadith is simple but serious. It shows that losing knowledge changes society. Ignorance does not stay private; it can appear with public harm and killing. For searchers asking what Harj means in Islam, this Hadith gives a clear answer from the Prophet صلى الله عليه وسلم."},"teachings":["Ignorance spreading is named as a future sign.","Knowledge disappearing is treated as a serious loss.","Harj is clearly explained as killing.","The Hadith connects public violence with a decline in knowledge."],"related_hadiths":[{"id":"4050","book_id":"6","label":"Sunan Ibn Majah"},{"id":"7062","book_id":"1","label":"Sahih Bukhari"},{"id":"7064","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ignorance, Lost Knowledge, and Killing","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith says days will come when ignorance spreads, knowledge disappears, and Harj becomes common."},"heading":{"title":"Ignorance Will Spread: A Hadith on Knowledge Disappearing and Harj","description":"This Hadith about ignorance and Harj is very close in meaning to other narrations on the signs before the Hour. The Prophet صلى الله عليه وسلم said that days would come after the companions when ignorance would become widespread, knowledge would disappear, and Harj would become much. When they asked what Harj meant, he answered: killing. The core topic is Ignorance. The Hadith is simple but serious. It shows that losing knowledge changes society. Ignorance does not stay private; it can appear with public harm and killing. For searchers asking what Harj means in Islam, this Hadith gives a clear answer from the Prophet صلى الله عليه وسلم."},"teachings":["Ignorance spreading is named as a future sign.","Knowledge disappearing is treated as a serious loss.","Harj is clearly explained as killing.","The Hadith connects public violence with a decline in knowledge."],"related_hadiths":[{"id":"4050","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"7062","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7064","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E502" s="4" t="n"/>
@@ -12055,7 +12059,7 @@
       </c>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Time Passing Quickly and Tribulations","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith names fast-moving time, less knowledge, miserliness, tribulations, and much killing."},"heading":{"title":"Time Will Pass Quickly: A Hadith on Trials, Miserliness, and Harj","description":"This Hadith about signs of the Hour mentions several changes together. Time will pass quickly, knowledge will decrease, miserliness will be cast into people’s hearts, tribulations will appear, and Harj will increase. When asked what Harj means, the Prophet صلى الله عليه وسلم said it means killing. The core topic is Tribulation. The Hadith shows that the end times are not described by one sign only. It mentions time, knowledge, hearts, trials, and violence. For people searching for a Hadith about time passing quickly, this narration teaches that rapid time and social trouble are part of a wider warning before the Hour."},"teachings":["Time passing quickly is named in this Hadith.","Knowledge decreasing is linked with other end-time signs.","Miserliness being cast into hearts is mentioned as a serious moral change.","Harj is explained as killing."],"related_hadiths":[{"id":"4047","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4050","book_id":"6","label":"Sunan Ibn Majah"},{"id":"7064","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Time Passing Quickly and Tribulations","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith names fast-moving time, less knowledge, miserliness, tribulations, and much killing."},"heading":{"title":"Time Will Pass Quickly: A Hadith on Trials, Miserliness, and Harj","description":"This Hadith about signs of the Hour mentions several changes together. Time will pass quickly, knowledge will decrease, miserliness will be cast into people’s hearts, tribulations will appear, and Harj will increase. When asked what Harj means, the Prophet صلى الله عليه وسلم said it means killing. The core topic is Tribulation. The Hadith shows that the end times are not described by one sign only. It mentions time, knowledge, hearts, trials, and violence. For people searching for a Hadith about time passing quickly, this narration teaches that rapid time and social trouble are part of a wider warning before the Hour."},"teachings":["Time passing quickly is named in this Hadith.","Knowledge decreasing is linked with other end-time signs.","Miserliness being cast into hearts is mentioned as a serious moral change.","Harj is explained as killing."],"related_hadiths":[{"id":"4047","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4050","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"7064","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E503" s="4" t="n"/>
@@ -12078,7 +12082,7 @@
       </c>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Honesty Taken from Hearts","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes honesty being removed from hearts and trustworthy people becoming rare."},"heading":{"title":"Honesty Taken from Hearts: A Hadith on Trust and Faith","description":"This Hadith about honesty describes how trust can fade from people’s hearts. Hudhaifah reported that honesty was once preserved in the roots of men’s hearts, then the Qur’an was revealed and they learned from the Qur’an and Sunnah. The Prophet صلى الله عليه وسلم then described honesty being taken away until only traces remain, like a mark or an empty blister. People will trade with one another, yet hardly anyone will fulfill trust. A person may be praised for intelligence, manners, and strength while not having even a mustard seed of faith in his heart. The core topic is Trust. The Hadith warns that outward praise does not replace true faith and honesty."},"teachings":["Honesty is described as rooted in the heart.","The Qur’an and Sunnah are mentioned as sources people learned from.","Trustworthiness may become rare among people.","Outward skills and praise do not prove true faith in the heart."],"related_hadiths":[{"id":"6497","book_id":"1","label":"Sahih Bukhari"},{"id":"7086","book_id":"1","label":"Sahih Bukhari"},{"id":"4054","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Honesty Taken from Hearts","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes honesty being removed from hearts and trustworthy people becoming rare."},"heading":{"title":"Honesty Taken from Hearts: A Hadith on Trust and Faith","description":"This Hadith about honesty describes how trust can fade from people’s hearts. Hudhaifah reported that honesty was once preserved in the roots of men’s hearts, then the Qur’an was revealed and they learned from the Qur’an and Sunnah. The Prophet صلى الله عليه وسلم then described honesty being taken away until only traces remain, like a mark or an empty blister. People will trade with one another, yet hardly anyone will fulfill trust. A person may be praised for intelligence, manners, and strength while not having even a mustard seed of faith in his heart. The core topic is Trust. The Hadith warns that outward praise does not replace true faith and honesty."},"teachings":["Honesty is described as rooted in the heart.","The Qur’an and Sunnah are mentioned as sources people learned from.","Trustworthiness may become rare among people.","Outward skills and praise do not prove true faith in the heart."],"related_hadiths":[{"id":"6497","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7086","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4054","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E504" s="4" t="n"/>
@@ -12101,7 +12105,7 @@
       </c>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Loss of Modesty, Honesty, and Mercy","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith links the loss of modesty, honesty, mercy, and the bond of Islam in a person."},"heading":{"title":"Loss of Modesty Hadith: How Honesty and Mercy Fade","description":"This Hadith about modesty describes a chain of spiritual and moral loss. The Prophet صلى الله عليه وسلم said that when Allah wants to destroy a person, modesty is taken away from him. Then he becomes hated. After that, honesty is taken away, and he becomes known as a traitor. Then mercy is taken away, and he becomes rejected and accursed. Finally, the bond of Islam is taken away from him. The core topic is Modesty. The Hadith presents modesty, honesty, and mercy as connected qualities. It does not speak about small mistakes in isolation. It describes a serious downward path when these qualities are stripped away."},"teachings":["Modesty is shown as a key quality in a person.","The Hadith connects loss of modesty with loss of honesty.","Loss of mercy is mentioned as part of a serious decline.","The bond of Islam being taken away is described at the end of this path."],"related_hadiths":[{"id":"4053","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6497","book_id":"1","label":"Sahih Bukhari"},{"id":"7086","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Loss of Modesty, Honesty, and Mercy","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith links the loss of modesty, honesty, mercy, and the bond of Islam in a person."},"heading":{"title":"Loss of Modesty Hadith: How Honesty and Mercy Fade","description":"This Hadith about modesty describes a chain of spiritual and moral loss. The Prophet صلى الله عليه وسلم said that when Allah wants to destroy a person, modesty is taken away from him. Then he becomes hated. After that, honesty is taken away, and he becomes known as a traitor. Then mercy is taken away, and he becomes rejected and accursed. Finally, the bond of Islam is taken away from him. The core topic is Modesty. The Hadith presents modesty, honesty, and mercy as connected qualities. It does not speak about small mistakes in isolation. It describes a serious downward path when these qualities are stripped away."},"teachings":["Modesty is shown as a key quality in a person.","The Hadith connects loss of modesty with loss of honesty.","Loss of mercy is mentioned as part of a serious decline.","The bond of Islam being taken away is described at the end of this path."],"related_hadiths":[{"id":"4053","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"6497","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7086","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E505" s="4" t="n"/>
@@ -12124,7 +12128,7 @@
       </c>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ten Major Signs of the Hour","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith lists ten major signs before the Hour, including Dajjal, the Beast, Gog and Magog, and the fire."},"heading":{"title":"Ten Major Signs of the Hour: Dajjal, Gog and Magog, and the Final Fire","description":"This Hadith about the ten major signs of the Hour gives a fuller list than some shorter narrations. The Prophet صلى الله عليه وسلم mentioned the rising of the sun from the west, Dajjal, the smoke, the beast, Gog and Magog, the appearance of Eisa son of Mary, three earth collapses, and a fire from Aden Abyan that will drive people to the place of Gathering. The core topic is End Times. The Hadith is direct and descriptive. It does not invite date-setting or guesswork. It gives believers a named list of signs and reminds them that the Hour has real portents known through revelation."},"teachings":["The Hadith lists ten signs before the Hour.","Dajjal, the smoke, the beast, and Gog and Magog are named.","The appearance of Eisa son of Mary is included among the signs.","A fire from Aden Abyan is described as driving people to the Gathering place."],"related_hadiths":[{"id":"4041","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4056","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2901a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ten Major Signs of the Hour","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith lists ten major signs before the Hour, including Dajjal, the Beast, Gog and Magog, and the fire."},"heading":{"title":"Ten Major Signs of the Hour: Dajjal, Gog and Magog, and the Final Fire","description":"This Hadith about the ten major signs of the Hour gives a fuller list than some shorter narrations. The Prophet صلى الله عليه وسلم mentioned the rising of the sun from the west, Dajjal, the smoke, the beast, Gog and Magog, the appearance of Eisa son of Mary, three earth collapses, and a fire from Aden Abyan that will drive people to the place of Gathering. The core topic is End Times. The Hadith is direct and descriptive. It does not invite date-setting or guesswork. It gives believers a named list of signs and reminds them that the Hour has real portents known through revelation."},"teachings":["The Hadith lists ten signs before the Hour.","Dajjal, the smoke, the beast, and Gog and Magog are named.","The appearance of Eisa son of Mary is included among the signs.","A fire from Aden Abyan is described as driving people to the Gathering place."],"related_hadiths":[{"id":"4041","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4056","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"2901a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E506" s="4" t="n"/>
@@ -12147,7 +12151,7 @@
       </c>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hasten to Good Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith urges believers to do good deeds before six major events and personal death arrive."},"heading":{"title":"Hasten to Good Deeds Before Six Things Happen","description":"This Hadith about hastening to good deeds gives a practical warning. The Prophet صلى الله عليه وسلم told people to hurry to good deeds before six things: the sun rising from the west, the smoke, the beast of the earth, Dajjal, what happens to each person, meaning death, and what happens to all people, meaning the Day of Resurrection. The core topic is Good Deeds. Unlike narrations that mainly list signs, this Hadith tells people how to respond. The answer is not fear alone and not guessing dates. The answer is action while there is still time, especially before personal death or the general Resurrection comes."},"teachings":["Believers are told to hasten to good deeds.","The Hadith names major signs such as the sun rising from the west, smoke, the beast, and Dajjal.","Personal death is mentioned as something each person will face.","The Day of Resurrection is described as something that will happen to all people."],"related_hadiths":[{"id":"2947a","book_id":"2","label":"Sahih Muslim"},{"id":"4055","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4041","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hasten to Good Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith urges believers to do good deeds before six major events and personal death arrive."},"heading":{"title":"Hasten to Good Deeds Before Six Things Happen","description":"This Hadith about hastening to good deeds gives a practical warning. The Prophet صلى الله عليه وسلم told people to hurry to good deeds before six things: the sun rising from the west, the smoke, the beast of the earth, Dajjal, what happens to each person, meaning death, and what happens to all people, meaning the Day of Resurrection. The core topic is Good Deeds. Unlike narrations that mainly list signs, this Hadith tells people how to respond. The answer is not fear alone and not guessing dates. The answer is action while there is still time, especially before personal death or the general Resurrection comes."},"teachings":["Believers are told to hasten to good deeds.","The Hadith names major signs such as the sun rising from the west, smoke, the beast, and Dajjal.","Personal death is mentioned as something each person will face.","The Day of Resurrection is described as something that will happen to all people."],"related_hadiths":[{"id":"2947a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4055","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4041","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E507" s="4" t="n"/>
@@ -12170,7 +12174,7 @@
       </c>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lesser Signs After Two Hundred Years","description":"$book_name$ $hadith_number$ - $chapter_name$. This brief Hadith states that the lesser signs would come after two hundred years."},"heading":{"title":"Lesser Signs Hadith: The Signs After Two Hundred Years","description":"This Hadith about the lesser signs is very brief. Abu Qatadah narrated that the Messenger of Allah صلى الله عليه وسلم said that the signs would come after two hundred years. The translation explains these as lesser signs. The core topic is End Times. Because the wording is short, the explanation should stay short in meaning too. The Hadith does not list the signs in this report, and it does not explain the details of the two hundred years in the provided text. So the safe lesson is to note that the Prophet صلى الله عليه وسلم spoke about signs appearing in relation to time, while detailed claims should not be added from outside this narration."},"teachings":["The Hadith mentions signs connected to a time after two hundred years.","The provided text does not list the signs in detail.","The narration points to lesser signs according to the translation.","The wording teaches caution about adding details not stated in the report."],"related_hadiths":[{"id":"4055","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4056","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4059","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lesser Signs After Two Hundred Years","description":"$book_name$ $hadith_number$ - $chapter_name$. This brief Hadith states that the lesser signs would come after two hundred years."},"heading":{"title":"Lesser Signs Hadith: The Signs After Two Hundred Years","description":"This Hadith about the lesser signs is very brief. Abu Qatadah narrated that the Messenger of Allah صلى الله عليه وسلم said that the signs would come after two hundred years. The translation explains these as lesser signs. The core topic is End Times. Because the wording is short, the explanation should stay short in meaning too. The Hadith does not list the signs in this report, and it does not explain the details of the two hundred years in the provided text. So the safe lesson is to note that the Prophet صلى الله عليه وسلم spoke about signs appearing in relation to time, while detailed claims should not be added from outside this narration."},"teachings":["The Hadith mentions signs connected to a time after two hundred years.","The provided text does not list the signs in detail.","The narration points to lesser signs according to the translation.","The wording teaches caution about adding details not stated in the report."],"related_hadiths":[{"id":"4055","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4056","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4059","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E508" s="4" t="n"/>
@@ -12193,7 +12197,7 @@
       </c>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stages of the Ummah and Harj","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes stages of the Ummah, then warns of severed ties and repeated killing."},"heading":{"title":"Stages of the Ummah Hadith: Mercy, Broken Ties, and Harj","description":"This Hadith about the stages of the Ummah describes groups over time. It mentions a period of righteousness and piety, then people who show mercy and keep ties, then people who turn away from one another and cut ties. After that comes Harj after Harj, meaning killing after killing, and the words seek deliverance are repeated. The core topic is Community. The Hadith focuses on changes in people’s qualities: piety, mercy, family and social ties, then separation and violence. It teaches that the health of the community is tied to righteousness, mercy, and keeping bonds, while broken ties and killing are signs of danger."},"teachings":["The Hadith describes stages within the Ummah.","Righteousness, piety, mercy, and keeping ties are praised by mention.","Turning away from one another and severing ties are named as later problems.","Repeated Harj is treated as a serious danger."],"related_hadiths":[{"id":"4050","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4051","book_id":"6","label":"Sunan Ibn Majah"},{"id":"7062","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stages of the Ummah and Harj","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes stages of the Ummah, then warns of severed ties and repeated killing."},"heading":{"title":"Stages of the Ummah Hadith: Mercy, Broken Ties, and Harj","description":"This Hadith about the stages of the Ummah describes groups over time. It mentions a period of righteousness and piety, then people who show mercy and keep ties, then people who turn away from one another and cut ties. After that comes Harj after Harj, meaning killing after killing, and the words seek deliverance are repeated. The core topic is Community. The Hadith focuses on changes in people’s qualities: piety, mercy, family and social ties, then separation and violence. It teaches that the health of the community is tied to righteousness, mercy, and keeping bonds, while broken ties and killing are signs of danger."},"teachings":["The Hadith describes stages within the Ummah.","Righteousness, piety, mercy, and keeping ties are praised by mention.","Turning away from one another and severing ties are named as later problems.","Repeated Harj is treated as a serious danger."],"related_hadiths":[{"id":"4050","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4051","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"7062","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E509" s="4" t="n"/>
@@ -12216,7 +12220,7 @@
       </c>
       <c r="D510" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Transformations and Earth Collapsing","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith says that before the Hour there will be transformations, earth collapse, and Qadhf."},"heading":{"title":"Before the Hour: Transformations, Earth Collapsing, and Qadhf","description":"This Hadith about events before the Hour mentions three matters: transformations, the earth collapsing, and Qadhf. The translation explains Qadhf as the throwing of stones, perhaps as a means of punishment, and possibly referring to landslides. The core topic is End Times. The narration is brief, so it should be read with care. It does not explain where or when these events happen in this text. It simply states that such matters will occur just before the Hour. For people searching for Hadith about earth collapsing before Qiyamah, this report gives a short warning about frightening events near the end times."},"teachings":["Transformations are mentioned as events before the Hour.","The earth collapsing is named in the Hadith.","Qadhf is mentioned, with the translation giving possible meaning.","The Hadith gives a warning without giving dates or locations."],"related_hadiths":[{"id":"4060","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4055","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2901a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Transformations and Earth Collapsing","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith says that before the Hour there will be transformations, earth collapse, and Qadhf."},"heading":{"title":"Before the Hour: Transformations, Earth Collapsing, and Qadhf","description":"This Hadith about events before the Hour mentions three matters: transformations, the earth collapsing, and Qadhf. The translation explains Qadhf as the throwing of stones, perhaps as a means of punishment, and possibly referring to landslides. The core topic is End Times. The narration is brief, so it should be read with care. It does not explain where or when these events happen in this text. It simply states that such matters will occur just before the Hour. For people searching for Hadith about earth collapsing before Qiyamah, this report gives a short warning about frightening events near the end times."},"teachings":["Transformations are mentioned as events before the Hour.","The earth collapsing is named in the Hadith.","Qadhf is mentioned, with the translation giving possible meaning.","The Hadith gives a warning without giving dates or locations."],"related_hadiths":[{"id":"4060","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4055","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"2901a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E510" s="4" t="n"/>
@@ -12239,7 +12243,7 @@
       </c>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Earth Collapse at the End of the Ummah","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that near the end of the Ummah there will be earth collapse, transformations, and Qadhf."},"heading":{"title":"Earth Collapse at the End of the Ummah: A Hadith on Final Trials","description":"This Hadith about the end of the Ummah mentions three events: the earth collapsing, transformations, and Qadhf. It is similar in topic to other reports about frightening signs before the Hour. The core topic is End Times. The wording does not give a place, date, or detailed explanation of each event. It simply states that these matters will occur at the end of the Prophet’s صلى الله عليه وسلم nation. That makes the Hadith a warning, not a timeline to be guessed. For anyone searching for signs of Qiyamah involving earth collapse, this narration points to serious events while keeping the details limited to what is stated."},"teachings":["The Hadith mentions events at the end of the Ummah.","Earth collapse is named as one of those events.","Transformations and Qadhf are also mentioned.","The narration warns without giving exact dates or places."],"related_hadiths":[{"id":"4059","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4055","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2901a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Earth Collapse at the End of the Ummah","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns that near the end of the Ummah there will be earth collapse, transformations, and Qadhf."},"heading":{"title":"Earth Collapse at the End of the Ummah: A Hadith on Final Trials","description":"This Hadith about the end of the Ummah mentions three events: the earth collapsing, transformations, and Qadhf. It is similar in topic to other reports about frightening signs before the Hour. The core topic is End Times. The wording does not give a place, date, or detailed explanation of each event. It simply states that these matters will occur at the end of the Prophet’s صلى الله عليه وسلم nation. That makes the Hadith a warning, not a timeline to be guessed. For anyone searching for signs of Qiyamah involving earth collapse, this narration points to serious events while keeping the details limited to what is stated."},"teachings":["The Hadith mentions events at the end of the Ummah.","Earth collapse is named as one of those events.","Transformations and Qadhf are also mentioned.","The narration warns without giving exact dates or places."],"related_hadiths":[{"id":"4059","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4055","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"2901a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E511" s="4" t="n"/>
@@ -12262,7 +12266,7 @@
       </c>
       <c r="D512" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning Against Religious Innovation","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear warning about innovations and the serious signs mentioned for Ahlul-Qadar."},"heading":{"title":"Hadith About Religious Innovation and Ahlul-Qadar","description":"This hadith about religious innovation shows how serious Ibn Umar viewed changes introduced into Islam. A man came to him carrying Salam from another person. Ibn Umar replied that he had heard that the person had introduced innovations. He said that if this report was true, then his Salam should not be conveyed back. He then mentioned a saying of the Messenger of Allah صلى الله عليه وسلم about transformations, the earth collapsing, and Qadhf appearing among this nation. The narration connects that warning to Ahlul-Qadar. The core message is not about personal anger. It is about guarding faith and treating invented beliefs in religion as a serious matter. The hadith teaches caution, firmness, and respect for the limits of the religion."},"teachings":["Religious innovation is treated as a serious matter in this narration.","Ibn Umar did not act carelessly; he said if the report was true, then Salam should not be conveyed.","The hadith links certain end-time punishments with Ahlul-Qadar.","A believer should be careful about beliefs that are introduced into Islam."],"related_hadiths":[{"id":"4062","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4064","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning Against Religious Innovation","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear warning about innovations and the serious signs mentioned for Ahlul-Qadar."},"heading":{"title":"Hadith About Religious Innovation and Ahlul-Qadar","description":"This hadith about religious innovation shows how serious Ibn Umar viewed changes introduced into Islam. A man came to him carrying Salam from another person. Ibn Umar replied that he had heard that the person had introduced innovations. He said that if this report was true, then his Salam should not be conveyed back. He then mentioned a saying of the Messenger of Allah صلى الله عليه وسلم about transformations, the earth collapsing, and Qadhf appearing among this nation. The narration connects that warning to Ahlul-Qadar. The core message is not about personal anger. It is about guarding faith and treating invented beliefs in religion as a serious matter. The hadith teaches caution, firmness, and respect for the limits of the religion."},"teachings":["Religious innovation is treated as a serious matter in this narration.","Ibn Umar did not act carelessly; he said if the report was true, then Salam should not be conveyed.","The hadith links certain end-time punishments with Ahlul-Qadar.","A believer should be careful about beliefs that are introduced into Islam."],"related_hadiths":[{"id":"4062","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4064","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E512" s="4" t="n"/>
@@ -12285,7 +12289,7 @@
       </c>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Signs of Collapse and Transformation","description":"$book_name$ $hadith_number$ - $chapter_name$. A brief warning that collapse, transformation, and Qadhf will occur among the Prophet’s nation."},"heading":{"title":"Hadith About Earth Collapse and Transformation in the Ummah","description":"This short hadith about end times gives a strong warning in very few words. The Messenger of Allah صلى الله عليه وسلم said that among his nation there will be the collapsing of the earth, transformations, and Qadhf. The narration does not give extra details here, so the safest way to read it is to stay with the exact message. It is a reminder that the future contains serious trials and signs that Allah’s Messenger صلى الله عليه وسلم warned about. The hadith does not ask the reader to guess dates or name people. Instead, it pushes the heart toward humility, awareness, and caution. A Muslim reads this kind of hadith as a warning to stay firm, avoid false confidence, and remember that the Hour has signs known to Allah."},"teachings":["The Prophet صلى الله عليه وسلم warned that serious signs would appear among his nation.","The hadith mentions collapse, transformation, and Qadhf without giving a date.","A believer should not treat warnings about the Hour lightly.","The narration encourages caution rather than speculation."],"related_hadiths":[{"id":"4061","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4063","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Signs of Collapse and Transformation","description":"$book_name$ $hadith_number$ - $chapter_name$. A brief warning that collapse, transformation, and Qadhf will occur among the Prophet’s nation."},"heading":{"title":"Hadith About Earth Collapse and Transformation in the Ummah","description":"This short hadith about end times gives a strong warning in very few words. The Messenger of Allah صلى الله عليه وسلم said that among his nation there will be the collapsing of the earth, transformations, and Qadhf. The narration does not give extra details here, so the safest way to read it is to stay with the exact message. It is a reminder that the future contains serious trials and signs that Allah’s Messenger صلى الله عليه وسلم warned about. The hadith does not ask the reader to guess dates or name people. Instead, it pushes the heart toward humility, awareness, and caution. A Muslim reads this kind of hadith as a warning to stay firm, avoid false confidence, and remember that the Hour has signs known to Allah."},"teachings":["The Prophet صلى الله عليه وسلم warned that serious signs would appear among his nation.","The hadith mentions collapse, transformation, and Qadhf without giving a date.","A believer should not treat warnings about the Hour lightly.","The narration encourages caution rather than speculation."],"related_hadiths":[{"id":"4061","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4063","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E513" s="4" t="n"/>
@@ -12308,7 +12312,7 @@
       </c>
       <c r="D514" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Army Swallowed by the Earth","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning about an invading army heading to the House and being swallowed at Bayda."},"heading":{"title":"Hadith About the Army Swallowed by the Earth at Bayda","description":"This hadith about the army swallowed by the earth describes a future event involving an invading army that comes toward this House. When they reach Bayda, the middle of the army is swallowed up. The first of them call out to the last of them, and then they are swallowed too. Only a fugitive remains to tell others what happened. The narration also mentions that when the army of Hajjaj came, some people thought it might be the army spoken about in the hadith. The main lesson is clear: attacking what Allah has made sacred is not a small matter. The report also shows how the Companions and later narrators took the Prophet’s words seriously and watched events through that warning."},"teachings":["The hadith warns about an army that attacks the House.","The punishment described happens when the army reaches Bayda.","Only one fugitive remains to report what happened.","The narration shows that people took the Prophet’s warning seriously."],"related_hadiths":[{"id":"4064","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4065","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Army Swallowed by the Earth","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning about an invading army heading to the House and being swallowed at Bayda."},"heading":{"title":"Hadith About the Army Swallowed by the Earth at Bayda","description":"This hadith about the army swallowed by the earth describes a future event involving an invading army that comes toward this House. When they reach Bayda, the middle of the army is swallowed up. The first of them call out to the last of them, and then they are swallowed too. Only a fugitive remains to tell others what happened. The narration also mentions that when the army of Hajjaj came, some people thought it might be the army spoken about in the hadith. The main lesson is clear: attacking what Allah has made sacred is not a small matter. The report also shows how the Companions and later narrators took the Prophet’s words seriously and watched events through that warning."},"teachings":["The hadith warns about an army that attacks the House.","The punishment described happens when the army reaches Bayda.","Only one fugitive remains to report what happened.","The narration shows that people took the Prophet’s warning seriously."],"related_hadiths":[{"id":"4064","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4065","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E514" s="4" t="n"/>
@@ -12331,7 +12335,7 @@
       </c>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Resurrected According to Hearts","description":"$book_name$ $hadith_number$ - $chapter_name$. The army is swallowed, while the forced among them are judged by what is in their hearts."},"heading":{"title":"Hadith About Intentions and the Army Swallowed at Bayda","description":"This hadith about intentions explains an important point in the story of the army that attacks this House. The Prophet صلى الله عليه وسلم said that people would not stop attacking this House until an army comes and is swallowed in Bayda. The narrator asked about those who may have been forced to join that army. The answer was that Allah will resurrect them according to what is in their hearts. This keeps the warning strong, but it also shows that Allah knows the inner state of each person. The outward event is one thing, and the heart is another matter known to Allah. The hadith teaches that people may be gathered in one situation, but their inner intentions still matter before Allah."},"teachings":["The hadith warns against joining an attack on the House.","Those forced to be present are not ignored in Allah’s judgment.","Allah will resurrect people according to what is in their hearts.","Outward association and inner intention are both serious matters."],"related_hadiths":[{"id":"4065","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4063","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Resurrected According to Hearts","description":"$book_name$ $hadith_number$ - $chapter_name$. The army is swallowed, while the forced among them are judged by what is in their hearts."},"heading":{"title":"Hadith About Intentions and the Army Swallowed at Bayda","description":"This hadith about intentions explains an important point in the story of the army that attacks this House. The Prophet صلى الله عليه وسلم said that people would not stop attacking this House until an army comes and is swallowed in Bayda. The narrator asked about those who may have been forced to join that army. The answer was that Allah will resurrect them according to what is in their hearts. This keeps the warning strong, but it also shows that Allah knows the inner state of each person. The outward event is one thing, and the heart is another matter known to Allah. The hadith teaches that people may be gathered in one situation, but their inner intentions still matter before Allah."},"teachings":["The hadith warns against joining an attack on the House.","Those forced to be present are not ignored in Allah’s judgment.","Allah will resurrect people according to what is in their hearts.","Outward association and inner intention are both serious matters."],"related_hadiths":[{"id":"4065","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4063","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E515" s="4" t="n"/>
@@ -12354,7 +12358,7 @@
       </c>
       <c r="D516" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Beast and Clear Signs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Beast emerges with the seal and staff, marking believers and disbelievers."},"heading":{"title":"Hadith About the Beast Emerging Before the Hour","description":"This hadith about the Beast describes one of the major signs connected to the end times. The Prophet صلى الله عليه وسلم said that the Beast will emerge carrying the seal of Sulaiman and the staff of Musa, peace be upon them. It will brighten the faces of the believers with the staff and mark the noses of the disbelievers with the seal. The narration then describes people gathering in a cluster of houses and addressing one another openly as believer or disbeliever. The hadith is not asking us to guess the time of this event. It presents the Beast as a sign that makes faith and disbelief openly known. The main message is to take belief seriously before such clear signs appear."},"teachings":["The Beast is described as a sign that will emerge.","The narration mentions the staff of Musa and the seal of Sulaiman.","Believers and disbelievers are marked in different ways.","The hadith points to a time when inner belief becomes outwardly clear."],"related_hadiths":[{"id":"4067","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4069","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4068","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Beast and Clear Signs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Beast emerges with the seal and staff, marking believers and disbelievers."},"heading":{"title":"Hadith About the Beast Emerging Before the Hour","description":"This hadith about the Beast describes one of the major signs connected to the end times. The Prophet صلى الله عليه وسلم said that the Beast will emerge carrying the seal of Sulaiman and the staff of Musa, peace be upon them. It will brighten the faces of the believers with the staff and mark the noses of the disbelievers with the seal. The narration then describes people gathering in a cluster of houses and addressing one another openly as believer or disbeliever. The hadith is not asking us to guess the time of this event. It presents the Beast as a sign that makes faith and disbelief openly known. The main message is to take belief seriously before such clear signs appear."},"teachings":["The Beast is described as a sign that will emerge.","The narration mentions the staff of Musa and the seal of Sulaiman.","Believers and disbelievers are marked in different ways.","The hadith points to a time when inner belief becomes outwardly clear."],"related_hadiths":[{"id":"4067","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4069","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4068","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E516" s="4" t="n"/>
@@ -12377,7 +12381,7 @@
       </c>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Place Where the Beast Emerges","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet shows a dry place near Makkah where the Beast will emerge."},"heading":{"title":"Hadith About Where the Beast Will Emerge","description":"This hadith about the Beast focuses on the place of its emergence. Buraidah said that the Messenger of Allah صلى الله عليه وسلم took him to a place in the desert near Makkah. The land was dry and surrounded by sand. The Prophet صلى الله عليه وسلم said that the Beast would emerge from that spot, and the narration describes the small measure of that place. The report is simple and specific. It does not give a date, nor does it invite people to search for the spot today. It only records what the Prophet صلى الله عليه وسلم showed and said. The core lesson is that the signs of the Hour are real matters taught by revelation, and a believer should receive them with seriousness and humility."},"teachings":["The Prophet صلى الله عليه وسلم pointed to a specific place connected to the Beast.","The narration describes the place as dry land near Makkah.","The hadith does not give a date for the Beast’s emergence.","A believer should treat the signs of the Hour with seriousness."],"related_hadiths":[{"id":"4066","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4069","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Place Where the Beast Emerges","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet shows a dry place near Makkah where the Beast will emerge."},"heading":{"title":"Hadith About Where the Beast Will Emerge","description":"This hadith about the Beast focuses on the place of its emergence. Buraidah said that the Messenger of Allah صلى الله عليه وسلم took him to a place in the desert near Makkah. The land was dry and surrounded by sand. The Prophet صلى الله عليه وسلم said that the Beast would emerge from that spot, and the narration describes the small measure of that place. The report is simple and specific. It does not give a date, nor does it invite people to search for the spot today. It only records what the Prophet صلى الله عليه وسلم showed and said. The core lesson is that the signs of the Hour are real matters taught by revelation, and a believer should receive them with seriousness and humility."},"teachings":["The Prophet صلى الله عليه وسلم pointed to a specific place connected to the Beast.","The narration describes the place as dry land near Makkah.","The hadith does not give a date for the Beast’s emergence.","A believer should treat the signs of the Hour with seriousness."],"related_hadiths":[{"id":"4066","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4069","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E517" s="4" t="n"/>
@@ -12400,7 +12404,7 @@
       </c>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sun Rising from the West","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hour will not begin until the sun rises from the west and late faith no longer benefits."},"heading":{"title":"Hadith About the Sun Rising from the West and Faith","description":"This hadith about the sun rising from the west gives a serious warning about delaying faith. The Prophet صلى الله عليه وسلم said that the Hour will not begin until the sun rises from the west, the place where it normally sets. When people see it, everyone on earth will believe. But at that time, faith will not benefit a person who had not believed before. The point is not to wait for a final visible sign before turning to Allah. The hadith teaches that belief should come before the door reaches that stage. It is a reminder to respond to guidance while there is still time, instead of waiting for a sign that leaves no room for meaningful choice."},"teachings":["The sun rising from the west is mentioned as a sign before the Hour.","People will believe when they see it, but late faith will not benefit those who did not believe before.","The hadith warns against delaying faith until signs become undeniable.","A believer should value the chance to believe and do good before that time."],"related_hadiths":[{"id":"4069","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4070","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sun Rising from the West","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hour will not begin until the sun rises from the west and late faith no longer benefits."},"heading":{"title":"Hadith About the Sun Rising from the West and Faith","description":"This hadith about the sun rising from the west gives a serious warning about delaying faith. The Prophet صلى الله عليه وسلم said that the Hour will not begin until the sun rises from the west, the place where it normally sets. When people see it, everyone on earth will believe. But at that time, faith will not benefit a person who had not believed before. The point is not to wait for a final visible sign before turning to Allah. The hadith teaches that belief should come before the door reaches that stage. It is a reminder to respond to guidance while there is still time, instead of waiting for a sign that leaves no room for meaningful choice."},"teachings":["The sun rising from the west is mentioned as a sign before the Hour.","People will believe when they see it, but late faith will not benefit those who did not believe before.","The hadith warns against delaying faith until signs become undeniable.","A believer should value the chance to believe and do good before that time."],"related_hadiths":[{"id":"4069","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4070","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E518" s="4" t="n"/>
@@ -12423,7 +12427,7 @@
       </c>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | First Major Signs of the Hour","description":"$book_name$ $hadith_number$ - $chapter_name$. The sun rising from the west and the Beast are described as closely linked signs."},"heading":{"title":"Hadith About the First Signs: Sun from the West and the Beast","description":"This hadith about the first signs of the Hour joins two major events together: the sun rising from the west and the Beast emerging to the people at forenoon. Abdullah bin Amr added that whichever one appears first, the other will come soon after. He also said that he thought it would be the sun rising from the west. The hadith gives a strong sense of closeness between these two signs. It does not give a calendar or ask people to predict the exact order with certainty beyond what is reported. The simple lesson is to stay awake to the reality of the Hour. The signs are not stories for curiosity only; they are reminders that faith and good deeds should not be delayed."},"teachings":["The sun rising from the west and the Beast are mentioned together.","Whichever of the two signs appears first, the other will come soon after.","The narration does not give a date for these signs.","The hadith encourages readiness through faith and good action."],"related_hadiths":[{"id":"4068","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4066","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4070","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | First Major Signs of the Hour","description":"$book_name$ $hadith_number$ - $chapter_name$. The sun rising from the west and the Beast are described as closely linked signs."},"heading":{"title":"Hadith About the First Signs: Sun from the West and the Beast","description":"This hadith about the first signs of the Hour joins two major events together: the sun rising from the west and the Beast emerging to the people at forenoon. Abdullah bin Amr added that whichever one appears first, the other will come soon after. He also said that he thought it would be the sun rising from the west. The hadith gives a strong sense of closeness between these two signs. It does not give a calendar or ask people to predict the exact order with certainty beyond what is reported. The simple lesson is to stay awake to the reality of the Hour. The signs are not stories for curiosity only; they are reminders that faith and good deeds should not be delayed."},"teachings":["The sun rising from the west and the Beast are mentioned together.","Whichever of the two signs appears first, the other will come soon after.","The narration does not give a date for these signs.","The hadith encourages readiness through faith and good action."],"related_hadiths":[{"id":"4068","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4066","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4070","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E519" s="4" t="n"/>
@@ -12446,7 +12450,7 @@
       </c>
       <c r="D520" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Door of Repentance","description":"$book_name$ $hadith_number$ - $chapter_name$. A door for repentance remains open until the sun rises from the west."},"heading":{"title":"Hadith About the Door of Repentance Before the Sun Rises from the West","description":"This hadith about repentance gives hope and warning together. The Prophet صلى الله عليه وسلم said that toward the west there is an open door, seventy years wide. That door remains open for repentance until the sun rises from that direction. When it rises from the west, faith will not benefit a soul that did not believe before or earn good through its faith. The message is very direct: repentance should not be delayed. The hadith does not ask the believer to guess when this sign will happen. It calls the heart to use the open door now. Faith is not only a word said at the end; the narration also mentions earning good through faith before that time arrives."},"teachings":["A door for repentance is described as open until the sun rises from the west.","The hadith encourages repentance before the final sign appears.","Faith and good deeds are both mentioned in the warning.","The narration teaches urgency without giving a date."],"related_hadiths":[{"id":"4068","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4069","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Door of Repentance","description":"$book_name$ $hadith_number$ - $chapter_name$. A door for repentance remains open until the sun rises from the west."},"heading":{"title":"Hadith About the Door of Repentance Before the Sun Rises from the West","description":"This hadith about repentance gives hope and warning together. The Prophet صلى الله عليه وسلم said that toward the west there is an open door, seventy years wide. That door remains open for repentance until the sun rises from that direction. When it rises from the west, faith will not benefit a soul that did not believe before or earn good through its faith. The message is very direct: repentance should not be delayed. The hadith does not ask the believer to guess when this sign will happen. It calls the heart to use the open door now. Faith is not only a word said at the end; the narration also mentions earning good through faith before that time arrives."},"teachings":["A door for repentance is described as open until the sun rises from the west.","The hadith encourages repentance before the final sign appears.","Faith and good deeds are both mentioned in the warning.","The narration teaches urgency without giving a date."],"related_hadiths":[{"id":"4068","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4069","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E520" s="4" t="n"/>
@@ -12469,7 +12473,7 @@
       </c>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dajjal Emerging from Khorasan","description":"$book_name$ $hadith_number$ - $chapter_name$. Dajjal is said to emerge from Khorasan and be followed by people with shield-like faces."},"heading":{"title":"Hadith About Dajjal Emerging from Khorasan","description":"This hadith about Dajjal mentions where he will emerge from and who will follow him. Abu Bakr Siddiq narrated that the Messenger of Allah صلى الله عليه وسلم said Dajjal will emerge in a land in the east called Khorasan. The hadith also describes groups following him with faces like hammered shields. The narration is brief, so the explanation should remain brief and careful. It gives a location and a description, but it does not give a date or name a current people. The main lesson is to take the Prophet’s warning seriously without turning the hadith into guesswork. For readers searching Dajjal Khorasan hadith, this report is about awareness of a future fitnah and the need to remain firm upon truth."},"teachings":["The hadith says Dajjal will emerge from a land in the east called Khorasan.","It describes some followers with faces like hammered shields.","The narration does not give a date for Dajjal’s appearance.","A believer should avoid careless speculation about future signs."],"related_hadiths":[{"id":"4075","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4077","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4071","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dajjal Emerging from Khorasan","description":"$book_name$ $hadith_number$ - $chapter_name$. Dajjal is said to emerge from Khorasan and be followed by people with shield-like faces."},"heading":{"title":"Hadith About Dajjal Emerging from Khorasan","description":"This hadith about Dajjal mentions where he will emerge from and who will follow him. Abu Bakr Siddiq narrated that the Messenger of Allah صلى الله عليه وسلم said Dajjal will emerge in a land in the east called Khorasan. The hadith also describes groups following him with faces like hammered shields. The narration is brief, so the explanation should remain brief and careful. It gives a location and a description, but it does not give a date or name a current people. The main lesson is to take the Prophet’s warning seriously without turning the hadith into guesswork. For readers searching Dajjal Khorasan hadith, this report is about awareness of a future fitnah and the need to remain firm upon truth."},"teachings":["The hadith says Dajjal will emerge from a land in the east called Khorasan.","It describes some followers with faces like hammered shields.","The narration does not give a date for Dajjal’s appearance.","A believer should avoid careless speculation about future signs."],"related_hadiths":[{"id":"4075","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4077","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4071","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E521" s="4" t="n"/>
@@ -12492,7 +12496,7 @@
       </c>
       <c r="D522" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dajjal Is Insignificant Before Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. A reminder that Dajjal, despite frightening reports, is too insignificant before Allah."},"heading":{"title":"Hadith About Dajjal Being Too Insignificant Before Allah","description":"This hadith about Dajjal gives balance to fear. Mughirah bin Shubah said that no one asked the Prophet صلى الله عليه وسلم about Dajjal more than he did. He asked about what people were saying, that Dajjal would have food and drink with him. The Prophet صلى الله عليه وسلم answered that he is too insignificant before Allah for that. The hadith does not deny that Dajjal is a serious trial in other narrations, but in this text the focus is on Allah’s greatness over him. It teaches that fear should not become bigger than faith in Allah. A Muslim may learn about Dajjal’s fitnah, but the heart should remember that Dajjal is not powerful before Allah. That is the calming point of this narration."},"teachings":["The Companions asked serious questions about Dajjal.","The Prophet صلى الله عليه وسلم directed attention back to Allah’s greatness.","Dajjal is described as too insignificant before Allah.","A believer should learn warnings without letting fear overpower trust in Allah."],"related_hadiths":[{"id":"4071","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4077","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dajjal Is Insignificant Before Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. A reminder that Dajjal, despite frightening reports, is too insignificant before Allah."},"heading":{"title":"Hadith About Dajjal Being Too Insignificant Before Allah","description":"This hadith about Dajjal gives balance to fear. Mughirah bin Shubah said that no one asked the Prophet صلى الله عليه وسلم about Dajjal more than he did. He asked about what people were saying, that Dajjal would have food and drink with him. The Prophet صلى الله عليه وسلم answered that he is too insignificant before Allah for that. The hadith does not deny that Dajjal is a serious trial in other narrations, but in this text the focus is on Allah’s greatness over him. It teaches that fear should not become bigger than faith in Allah. A Muslim may learn about Dajjal’s fitnah, but the heart should remember that Dajjal is not powerful before Allah. That is the calming point of this narration."},"teachings":["The Companions asked serious questions about Dajjal.","The Prophet صلى الله عليه وسلم directed attention back to Allah’s greatness.","Dajjal is described as too insignificant before Allah.","A believer should learn warnings without letting fear overpower trust in Allah."],"related_hadiths":[{"id":"4071","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4077","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E522" s="4" t="n"/>
@@ -12515,7 +12519,7 @@
       </c>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Jassasah and Protected Taibah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Jassasah report ends with the Prophet’s joy over Taibah being guarded by angels."},"heading":{"title":"Hadith About Jassasah and the Protection of Taibah","description":"This hadith about Jassasah is a long report shared by the Prophet صلى الله عليه وسلم after Tamim Dari brought news that pleased him. The story mentions people driven by wind to an unknown island, where they met Jassasah and were directed to a shackled man in a monastery. The man asked about the Arabs, the Prophet صلى الله عليه وسلم, the spring of Zughar, the date-palms between Amman and Baisan, and the Lake of Tiberias. He said that if freed, he would enter every land except Taibah, because he had no way to enter it. The Prophet صلى الله عليه وسلم then explained his joy: Taibah is Madinah, and every road, plain, and mountain is guarded by an angel with an unsheathed sword until the Day of Resurrection."},"teachings":["The hadith records the report of Jassasah and the shackled man.","The shackled man said he had no way to enter Taibah.","The Prophet صلى الله عليه وسلم identified Taibah as Madinah.","Madinah is described as guarded by angels until the Day of Resurrection."],"related_hadiths":[{"id":"4071","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4077","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Jassasah and Protected Taibah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Jassasah report ends with the Prophet’s joy over Taibah being guarded by angels."},"heading":{"title":"Hadith About Jassasah and the Protection of Taibah","description":"This hadith about Jassasah is a long report shared by the Prophet صلى الله عليه وسلم after Tamim Dari brought news that pleased him. The story mentions people driven by wind to an unknown island, where they met Jassasah and were directed to a shackled man in a monastery. The man asked about the Arabs, the Prophet صلى الله عليه وسلم, the spring of Zughar, the date-palms between Amman and Baisan, and the Lake of Tiberias. He said that if freed, he would enter every land except Taibah, because he had no way to enter it. The Prophet صلى الله عليه وسلم then explained his joy: Taibah is Madinah, and every road, plain, and mountain is guarded by an angel with an unsheathed sword until the Day of Resurrection."},"teachings":["The hadith records the report of Jassasah and the shackled man.","The shackled man said he had no way to enter Taibah.","The Prophet صلى الله عليه وسلم identified Taibah as Madinah.","Madinah is described as guarded by angels until the Day of Resurrection."],"related_hadiths":[{"id":"4071","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4077","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E523" s="4" t="n"/>
@@ -12538,7 +12542,7 @@
       </c>
       <c r="D524" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dajjal, Eisa, and Gog and Magog","description":"$book_name$ $hadith_number$ - $chapter_name$. A detailed warning about Dajjal, steadfastness, Eisa’s descent, and Gog and Magog."},"heading":{"title":"Hadith About Dajjal, Surat Al-Kahf, Eisa, and Gog and Magog","description":"This long hadith about Dajjal gives many connected signs and instructions. The Prophet صلى الله عليه وسلم described Dajjal, warned the believers to remain steadfast, and told whoever sees him to recite the opening verses of Surat Al-Kahf. The hadith says Dajjal will stay forty days, with some days unlike normal days, so prayer times should be estimated. It also describes his movement, his trials with rain, crops, wealth, and a young man. Then Allah sends Eisa son of Maryam, who kills Dajjal at the gate of Ludd. After that, Gog and Magog emerge, and Allah destroys them after Eisa and his companions supplicate. The narration ends with blessing on the earth, then a pleasant wind taking the souls of every Muslim before the Hour comes upon the remaining people."},"teachings":["The Prophet صلى الله عليه وسلم instructed believers to remain steadfast during Dajjal’s trial.","The opening verses of Surat Al-Kahf are mentioned as protection for those who see him.","Prayer is still observed by estimating time when days are unusual.","The hadith connects Dajjal’s end with the descent of Eisa son of Maryam."],"related_hadiths":[{"id":"4077","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4078","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4079","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dajjal, Eisa, and Gog and Magog","description":"$book_name$ $hadith_number$ - $chapter_name$. A detailed warning about Dajjal, steadfastness, Eisa’s descent, and Gog and Magog."},"heading":{"title":"Hadith About Dajjal, Surat Al-Kahf, Eisa, and Gog and Magog","description":"This long hadith about Dajjal gives many connected signs and instructions. The Prophet صلى الله عليه وسلم described Dajjal, warned the believers to remain steadfast, and told whoever sees him to recite the opening verses of Surat Al-Kahf. The hadith says Dajjal will stay forty days, with some days unlike normal days, so prayer times should be estimated. It also describes his movement, his trials with rain, crops, wealth, and a young man. Then Allah sends Eisa son of Maryam, who kills Dajjal at the gate of Ludd. After that, Gog and Magog emerge, and Allah destroys them after Eisa and his companions supplicate. The narration ends with blessing on the earth, then a pleasant wind taking the souls of every Muslim before the Hour comes upon the remaining people."},"teachings":["The Prophet صلى الله عليه وسلم instructed believers to remain steadfast during Dajjal’s trial.","The opening verses of Surat Al-Kahf are mentioned as protection for those who see him.","Prayer is still observed by estimating time when days are unusual.","The hadith connects Dajjal’s end with the descent of Eisa son of Maryam."],"related_hadiths":[{"id":"4077","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4078","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4079","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E524" s="4" t="n"/>
@@ -12561,7 +12565,7 @@
       </c>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Remains of Gog and Magog","description":"$book_name$ $hadith_number$ - $chapter_name$. Muslims will use the weapons of Gog and Magog as firewood for seven years."},"heading":{"title":"Hadith About Gog and Magog Weapons Used as Firewood","description":"This hadith about Gog and Magog is short, but it gives a vivid picture of what remains after their episode. The Prophet صلى الله عليه وسلم said that Muslims will use the bows, arrows, and shields of Gog and Magog as firewood for seven years. The narration does not explain every part of the Gog and Magog story here, and it does not describe their full emergence in this specific text. It simply points to the large amount of weapons left behind and how Muslims will use them after that event. The lesson is that even what looks huge and threatening can be brought to an end by Allah’s decree. The believer reads it as part of the wider signs of the Hour and keeps faith in Allah’s control."},"teachings":["The hadith mentions the weapons of Gog and Magog after their event.","Muslims will use their bows, arrows, and shields as firewood.","The period mentioned is seven years.","The narration points to Allah’s control over even massive trials."],"related_hadiths":[{"id":"4079","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4080","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Remains of Gog and Magog","description":"$book_name$ $hadith_number$ - $chapter_name$. Muslims will use the weapons of Gog and Magog as firewood for seven years."},"heading":{"title":"Hadith About Gog and Magog Weapons Used as Firewood","description":"This hadith about Gog and Magog is short, but it gives a vivid picture of what remains after their episode. The Prophet صلى الله عليه وسلم said that Muslims will use the bows, arrows, and shields of Gog and Magog as firewood for seven years. The narration does not explain every part of the Gog and Magog story here, and it does not describe their full emergence in this specific text. It simply points to the large amount of weapons left behind and how Muslims will use them after that event. The lesson is that even what looks huge and threatening can be brought to an end by Allah’s decree. The believer reads it as part of the wider signs of the Hour and keeps faith in Allah’s control."},"teachings":["The hadith mentions the weapons of Gog and Magog after their event.","Muslims will use their bows, arrows, and shields as firewood.","The period mentioned is seven years.","The narration points to Allah’s control over even massive trials."],"related_hadiths":[{"id":"4079","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4080","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E525" s="4" t="n"/>
@@ -12584,7 +12588,7 @@
       </c>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Great Warning About Dajjal","description":"$book_name$ $hadith_number$ - $chapter_name$. A detailed sermon warning about Dajjal’s claims, trials, and the descent of Eisa."},"heading":{"title":"Hadith About Dajjal’s Fitnah and How Believers Stay Firm","description":"This hadith about Dajjal is a detailed warning from the Prophet صلى الله عليه وسلم. He described Dajjal as a great tribulation, said every Prophet warned his people about him, and told the believers to remain steadfast. The hadith gives signs: Dajjal will claim prophethood and then lordship, but there is no Prophet after Muhammad صلى الله عليه وسلم, and the believers will not see their Lord until they die. He is one-eyed, while Allah is not one-eyed. The word Kafir will be written between his eyes, and every believer will read it. The narration also mentions his false Paradise and Hell, the instruction to seek Allah’s help and recite the first verses of Al-Kahf, the protection of Makkah and Madinah, and the descent of Eisa son of Maryam."},"teachings":["The Prophet صلى الله عليه وسلم warned strongly about Dajjal’s fitnah.","Dajjal’s claims are rejected by clear truths mentioned in the hadith.","Believers are told to seek Allah’s help and recite the first verses of Al-Kahf.","Makkah and Madinah are described as protected from Dajjal’s entry."],"related_hadiths":[{"id":"4071","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4078","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Great Warning About Dajjal","description":"$book_name$ $hadith_number$ - $chapter_name$. A detailed sermon warning about Dajjal’s claims, trials, and the descent of Eisa."},"heading":{"title":"Hadith About Dajjal’s Fitnah and How Believers Stay Firm","description":"This hadith about Dajjal is a detailed warning from the Prophet صلى الله عليه وسلم. He described Dajjal as a great tribulation, said every Prophet warned his people about him, and told the believers to remain steadfast. The hadith gives signs: Dajjal will claim prophethood and then lordship, but there is no Prophet after Muhammad صلى الله عليه وسلم, and the believers will not see their Lord until they die. He is one-eyed, while Allah is not one-eyed. The word Kafir will be written between his eyes, and every believer will read it. The narration also mentions his false Paradise and Hell, the instruction to seek Allah’s help and recite the first verses of Al-Kahf, the protection of Makkah and Madinah, and the descent of Eisa son of Maryam."},"teachings":["The Prophet صلى الله عليه وسلم warned strongly about Dajjal’s fitnah.","Dajjal’s claims are rejected by clear truths mentioned in the hadith.","Believers are told to seek Allah’s help and recite the first verses of Al-Kahf.","Makkah and Madinah are described as protected from Dajjal’s entry."],"related_hadiths":[{"id":"4071","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4078","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E526" s="4" t="n"/>
@@ -12607,7 +12611,7 @@
       </c>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eisa Returns as a Just Ruler","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hour will not begin until Eisa returns as a just judge and ruler."},"heading":{"title":"Hadith About Eisa Son of Maryam Returning as a Just Judge","description":"This hadith about Eisa son of Maryam gives a clear sign before the Hour. The Prophet صلى الله عليه وسلم said that the Hour will not begin until Eisa descends as a just judge and a just ruler. The narration then mentions that he will break the cross, kill the pigs, abolish the Jizyah, and wealth will become so abundant that no one will accept it. The hadith is direct and should be explained without adding extra details not found in the text. Its main message is that the return of Eisa is linked to justice, correction of false religious claims, and a time of great wealth. For readers searching for hadith about the return of Jesus in Islam, this narration gives the core points in a short form."},"teachings":["Eisa son of Maryam will descend before the Hour.","He is described as a just judge and a just ruler.","The hadith mentions breaking the cross, killing pigs, and abolishing Jizyah.","Wealth will become abundant until no one accepts it."],"related_hadiths":[{"id":"4075","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4077","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eisa Returns as a Just Ruler","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hour will not begin until Eisa returns as a just judge and ruler."},"heading":{"title":"Hadith About Eisa Son of Maryam Returning as a Just Judge","description":"This hadith about Eisa son of Maryam gives a clear sign before the Hour. The Prophet صلى الله عليه وسلم said that the Hour will not begin until Eisa descends as a just judge and a just ruler. The narration then mentions that he will break the cross, kill the pigs, abolish the Jizyah, and wealth will become so abundant that no one will accept it. The hadith is direct and should be explained without adding extra details not found in the text. Its main message is that the return of Eisa is linked to justice, correction of false religious claims, and a time of great wealth. For readers searching for hadith about the return of Jesus in Islam, this narration gives the core points in a short form."},"teachings":["Eisa son of Maryam will descend before the Hour.","He is described as a just judge and a just ruler.","The hadith mentions breaking the cross, killing pigs, and abolishing Jizyah.","Wealth will become abundant until no one accepts it."],"related_hadiths":[{"id":"4075","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4077","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E527" s="4" t="n"/>
@@ -12630,7 +12634,7 @@
       </c>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gog and Magog Spread Across the Earth","description":"$book_name$ $hadith_number$ - $chapter_name$. Gog and Magog emerge, spread across the earth, and are destroyed by Allah."},"heading":{"title":"Hadith About Gog and Magog Emerging and Being Destroyed","description":"This hadith about Gog and Magog describes their release and spread across the earth. The Prophet صلى الله عليه وسلم said they will emerge as Allah says, coming down from every mound. Muslims will withdraw from them into cities and fortresses with their flocks. Gog and Magog will pass by a river and drink it until nothing remains. The narration describes their arrogance, even claiming they have dealt with the people of earth and then trying to face the people of heaven. While they are in that state, Allah sends worms that take them by their necks, and they die. The Muslims then discover that the enemy has perished. The hadith shows a frightening trial, but also that its end comes by Allah’s command."},"teachings":["Gog and Magog will spread across the earth after being released.","Muslims will seek safety in cities and fortresses.","Their arrogance is described in strong terms.","Allah destroys them through a means mentioned in the hadith."],"related_hadiths":[{"id":"4080","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4076","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gog and Magog Spread Across the Earth","description":"$book_name$ $hadith_number$ - $chapter_name$. Gog and Magog emerge, spread across the earth, and are destroyed by Allah."},"heading":{"title":"Hadith About Gog and Magog Emerging and Being Destroyed","description":"This hadith about Gog and Magog describes their release and spread across the earth. The Prophet صلى الله عليه وسلم said they will emerge as Allah says, coming down from every mound. Muslims will withdraw from them into cities and fortresses with their flocks. Gog and Magog will pass by a river and drink it until nothing remains. The narration describes their arrogance, even claiming they have dealt with the people of earth and then trying to face the people of heaven. While they are in that state, Allah sends worms that take them by their necks, and they die. The Muslims then discover that the enemy has perished. The hadith shows a frightening trial, but also that its end comes by Allah’s command."},"teachings":["Gog and Magog will spread across the earth after being released.","Muslims will seek safety in cities and fortresses.","Their arrogance is described in strong terms.","Allah destroys them through a means mentioned in the hadith."],"related_hadiths":[{"id":"4080","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4076","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E528" s="4" t="n"/>
@@ -12653,7 +12657,7 @@
       </c>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gog and Magog Digging the Barrier","description":"$book_name$ $hadith_number$ - $chapter_name$. Gog and Magog dig daily until Allah permits their emergence and later destroys them."},"heading":{"title":"Hadith About Gog and Magog Digging and Saying If Allah Wills","description":"This hadith about Gog and Magog focuses on their daily digging. The Prophet صلى الله عليه وسلم said they dig every day until they almost see the rays of the sun. Their leader tells them to return and dig tomorrow, but Allah restores it stronger than before. This continues until their appointed time comes. Then their leader says they will return tomorrow if Allah wills. When they come back, it remains as they left it, so they dig through and come out to the people. They drink the water, people fortify themselves, and they shoot arrows toward the sky. Then Allah sends worms in the napes of their necks and kills them. The hadith teaches that even their emergence happens only when Allah wills."},"teachings":["Gog and Magog are described as digging every day.","Their barrier is restored until their appointed time comes.","The phrase if Allah wills is connected to the moment they succeed in digging through.","Allah destroys them through worms in their necks."],"related_hadiths":[{"id":"4079","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4076","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gog and Magog Digging the Barrier","description":"$book_name$ $hadith_number$ - $chapter_name$. Gog and Magog dig daily until Allah permits their emergence and later destroys them."},"heading":{"title":"Hadith About Gog and Magog Digging and Saying If Allah Wills","description":"This hadith about Gog and Magog focuses on their daily digging. The Prophet صلى الله عليه وسلم said they dig every day until they almost see the rays of the sun. Their leader tells them to return and dig tomorrow, but Allah restores it stronger than before. This continues until their appointed time comes. Then their leader says they will return tomorrow if Allah wills. When they come back, it remains as they left it, so they dig through and come out to the people. They drink the water, people fortify themselves, and they shoot arrows toward the sky. Then Allah sends worms in the napes of their necks and kills them. The hadith teaches that even their emergence happens only when Allah wills."},"teachings":["Gog and Magog are described as digging every day.","Their barrier is restored until their appointed time comes.","The phrase if Allah wills is connected to the moment they succeed in digging through.","Allah destroys them through worms in their necks."],"related_hadiths":[{"id":"4079","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4076","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4075","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E529" s="4" t="n"/>
@@ -12676,7 +12680,7 @@
       </c>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Signs of the Hour and Gog and Magog","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how this Hadith describes Dajjal, Gog and Magog, and that the Hour is known only to Allah."},"heading":{"title":"Hadith About Dajjal, Gog and Magog, and the Signs of the Hour","description":"This Hadith focuses on the signs of the Hour and teaches that the exact time of the Hour is known only to Allah. The Prophet (صلى الله عليه وسلم) is narrated to have met Ibrahim, Musa, and Eisa during the Night Journey, and they discussed the Hour. Ibrahim and Musa did not have knowledge of its exact time, while Eisa said that he was assigned tasks before it happens. The Hadith then mentions Dajjal, the descent of Eisa, Gog and Magog, their spread across the land, the people calling upon Allah, and Allah sending relief. The main message is clear: major signs may be known, but the timing of the Hour belongs to Allah alone."},"teachings":["The exact time of the Hour is known only to Allah.","The Hadith mentions major signs such as Dajjal and Gog and Magog.","People are shown turning to Allah during great hardship.","The coming of the Hour is described as sudden and unexpected."],"related_hadiths":[{"id":"4091","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4092","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4093","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Signs of the Hour and Gog and Magog","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how this Hadith describes Dajjal, Gog and Magog, and that the Hour is known only to Allah."},"heading":{"title":"Hadith About Dajjal, Gog and Magog, and the Signs of the Hour","description":"This Hadith focuses on the signs of the Hour and teaches that the exact time of the Hour is known only to Allah. The Prophet (صلى الله عليه وسلم) is narrated to have met Ibrahim, Musa, and Eisa during the Night Journey, and they discussed the Hour. Ibrahim and Musa did not have knowledge of its exact time, while Eisa said that he was assigned tasks before it happens. The Hadith then mentions Dajjal, the descent of Eisa, Gog and Magog, their spread across the land, the people calling upon Allah, and Allah sending relief. The main message is clear: major signs may be known, but the timing of the Hour belongs to Allah alone."},"teachings":["The exact time of the Hour is known only to Allah.","The Hadith mentions major signs such as Dajjal and Gog and Magog.","People are shown turning to Allah during great hardship.","The coming of the Hour is described as sudden and unexpected."],"related_hadiths":[{"id":"4091","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4092","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4093","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E530" s="4" t="n"/>
@@ -12699,7 +12703,7 @@
       </c>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mahdi and Abundance","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes the Mahdi, a time of ease, abundant yield, and wealth being given freely."},"heading":{"title":"Hadith About Mahdi and a Time of Ease and Abundance","description":"This Hadith is about the Mahdi and the ease described during his time. The Prophet (صلى الله عليه وسلم) is narrated to have said that the Mahdi will be among his nation. The Hadith mentions a period of seven or nine, and during that time the nation will enjoy great ease. The land will bring out its produce and will not hold back. Wealth will be piled up, and when a man asks the Mahdi to give him, he will be told to take. The Hadith gives a picture of relief, open provision, and generous giving. It does not ask the reader to guess dates or details beyond what is stated."},"teachings":["The Mahdi is described as being from the Prophet’s nation.","The Hadith mentions a time of ease and open provision.","The land is described as giving its yield without holding back.","The Mahdi is shown responding generously to a request."],"related_hadiths":[{"id":"4082","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4085","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4086","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mahdi and Abundance","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes the Mahdi, a time of ease, abundant yield, and wealth being given freely."},"heading":{"title":"Hadith About Mahdi and a Time of Ease and Abundance","description":"This Hadith is about the Mahdi and the ease described during his time. The Prophet (صلى الله عليه وسلم) is narrated to have said that the Mahdi will be among his nation. The Hadith mentions a period of seven or nine, and during that time the nation will enjoy great ease. The land will bring out its produce and will not hold back. Wealth will be piled up, and when a man asks the Mahdi to give him, he will be told to take. The Hadith gives a picture of relief, open provision, and generous giving. It does not ask the reader to guess dates or details beyond what is stated."},"teachings":["The Mahdi is described as being from the Prophet’s nation.","The Hadith mentions a time of ease and open provision.","The land is described as giving its yield without holding back.","The Mahdi is shown responding generously to a request."],"related_hadiths":[{"id":"4082","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4085","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4086","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E531" s="4" t="n"/>
@@ -12722,7 +12726,7 @@
       </c>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allegiance to Mahdi","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions conflict, black banners from the east, and pledging allegiance to the Mahdi."},"heading":{"title":"Hadith About Black Banners and Pledging Allegiance to Mahdi","description":"This Hadith speaks about the Mahdi, conflict, and allegiance. The narration says that three people, each a son of a caliph, will fight over a treasure, but none will gain it. Then black banners will come from the east, and the report mentions severe fighting. After that, the narrator says the Prophet (صلى الله عليه وسلم) mentioned something he did not remember, then said that when people see them, they should pledge allegiance, even if they have to crawl over snow. The Hadith identifies the figure as the Mahdi. The core message in the text is not about guessing modern groups, but about the described signs and the call to recognize the Mahdi when that time comes."},"teachings":["The Hadith mentions conflict over a treasure before the appearance of the Mahdi.","Black banners from the east are connected with events before allegiance.","The narration stresses responding when the Mahdi is seen.","The text should be read carefully without forcing it onto unclear events."],"related_hadiths":[{"id":"4082","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4085","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4088","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allegiance to Mahdi","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions conflict, black banners from the east, and pledging allegiance to the Mahdi."},"heading":{"title":"Hadith About Black Banners and Pledging Allegiance to Mahdi","description":"This Hadith speaks about the Mahdi, conflict, and allegiance. The narration says that three people, each a son of a caliph, will fight over a treasure, but none will gain it. Then black banners will come from the east, and the report mentions severe fighting. After that, the narrator says the Prophet (صلى الله عليه وسلم) mentioned something he did not remember, then said that when people see them, they should pledge allegiance, even if they have to crawl over snow. The Hadith identifies the figure as the Mahdi. The core message in the text is not about guessing modern groups, but about the described signs and the call to recognize the Mahdi when that time comes."},"teachings":["The Hadith mentions conflict over a treasure before the appearance of the Mahdi.","Black banners from the east are connected with events before allegiance.","The narration stresses responding when the Mahdi is seen.","The text should be read carefully without forcing it onto unclear events."],"related_hadiths":[{"id":"4082","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4085","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4088","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E532" s="4" t="n"/>
@@ -12745,7 +12749,7 @@
       </c>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Treaty with Romans and Fierce Battle","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes a treaty with the Romans, its breach, and a fierce battle."},"heading":{"title":"Hadith About the Treaty with the Romans and the Fierce Battle","description":"This Hadith focuses on a peace treaty with the Romans and events that lead to a fierce battle. Dhu Mikhmar narrated that the Prophet (صلى الله عليه وسلم) said the Romans would make a safe treaty with the Muslims. Then both sides would fight an enemy, and the Muslims would be victorious, gain spoils, and return safely. After they stop in a meadow with many hillocks, a man from the people of the Cross raises the Cross and claims victory for it. A Muslim man becomes angry and breaks it. At that point, the Romans break the treaty and gather for the fierce battle. Another report adds that they come with eighty banners, each with twelve thousand troops."},"teachings":["The Hadith mentions a peace treaty before later betrayal.","The narration shows victory and safety before the conflict changes.","A public claim about the Cross becomes the trigger in the text.","The fierce battle is linked with the Romans gathering in large numbers."],"related_hadiths":[{"id":"4095","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4092","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4093","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Treaty with Romans and Fierce Battle","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes a treaty with the Romans, its breach, and a fierce battle."},"heading":{"title":"Hadith About the Treaty with the Romans and the Fierce Battle","description":"This Hadith focuses on a peace treaty with the Romans and events that lead to a fierce battle. Dhu Mikhmar narrated that the Prophet (صلى الله عليه وسلم) said the Romans would make a safe treaty with the Muslims. Then both sides would fight an enemy, and the Muslims would be victorious, gain spoils, and return safely. After they stop in a meadow with many hillocks, a man from the people of the Cross raises the Cross and claims victory for it. A Muslim man becomes angry and breaks it. At that point, the Romans break the treaty and gather for the fierce battle. Another report adds that they come with eighty banners, each with twelve thousand troops."},"teachings":["The Hadith mentions a peace treaty before later betrayal.","The narration shows victory and safety before the conflict changes.","A public claim about the Cross becomes the trigger in the text.","The fierce battle is linked with the Romans gathering in large numbers."],"related_hadiths":[{"id":"4095","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4092","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4093","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E533" s="4" t="n"/>
@@ -12768,7 +12772,7 @@
       </c>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Constantinople and Tasbih","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions fighting the Romans and conquering Constantinople with Tasbih and Takbir."},"heading":{"title":"Hadith About Conquering Constantinople with Tasbih and Takbir","description":"This Hadith mentions signs before the Hour, fighting Banu Asfar, and the conquest of Constantinople. The Prophet (صلى الله عليه وسلم) is narrated to have said that the Hour will not begin until the closest Muslim outpost is at Baula. He then addressed Ali and spoke about fighting Banu Asfar, and that those after them would also fight. The Hadith says the best of the Muslims from the people of Hijaz would go out, not fearing blame for the sake of Allah. It then says they would conquer Constantinople with Tasbih and Takbir and gain large spoils. A caller would later claim that Masih had appeared in their lands, but the Hadith says that claim would be a lie."},"teachings":["The Hadith mentions fighting Banu Asfar before later events.","The people of Hijaz are described as not fearing blame for Allah’s sake.","Constantinople is described as conquered with Tasbih and Takbir.","The narration warns of a false claim about Masih appearing."],"related_hadiths":[{"id":"4092","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4095","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4091","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Constantinople and Tasbih","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions fighting the Romans and conquering Constantinople with Tasbih and Takbir."},"heading":{"title":"Hadith About Conquering Constantinople with Tasbih and Takbir","description":"This Hadith mentions signs before the Hour, fighting Banu Asfar, and the conquest of Constantinople. The Prophet (صلى الله عليه وسلم) is narrated to have said that the Hour will not begin until the closest Muslim outpost is at Baula. He then addressed Ali and spoke about fighting Banu Asfar, and that those after them would also fight. The Hadith says the best of the Muslims from the people of Hijaz would go out, not fearing blame for the sake of Allah. It then says they would conquer Constantinople with Tasbih and Takbir and gain large spoils. A caller would later claim that Masih had appeared in their lands, but the Hadith says that claim would be a lie."},"teachings":["The Hadith mentions fighting Banu Asfar before later events.","The people of Hijaz are described as not fearing blame for Allah’s sake.","Constantinople is described as conquered with Tasbih and Takbir.","The narration warns of a false claim about Masih appearing."],"related_hadiths":[{"id":"4092","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4095","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4091","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E534" s="4" t="n"/>
@@ -12791,7 +12795,7 @@
       </c>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | True Zuhd in Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains true zuhd as trust in Allah and hope in reward during hardship."},"heading":{"title":"True Zuhd in Islam: Trusting Allah More Than What You Own","description":"This Hadith explains true zuhd, or indifference toward this world, in a balanced way. The Prophet (صلى الله عليه وسلم) is narrated to have said that zuhd does not mean making lawful things forbidden, and it does not mean wasting wealth. Instead, zuhd means not trusting what is in your hand more than what is in Allah’s Hand. It also means that when a calamity reaches you, you desire the reward for patience more than the worldly thing you lost. The Hadith teaches that zuhd is not carelessness or self-made hardship. It is a heart matter: relying on Allah, using blessings properly, and seeing hardship with faith."},"teachings":["Zuhd does not mean forbidding what Allah has made lawful.","Zuhd does not mean wasting wealth.","True zuhd means trusting what is with Allah more than what is in your hand.","The Hadith teaches hope in reward when a calamity causes loss."],"related_hadiths":[{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"2956","book_id":"2","label":"Sahih Muslim"},{"id":"2324","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | True Zuhd in Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains true zuhd as trust in Allah and hope in reward during hardship."},"heading":{"title":"True Zuhd in Islam: Trusting Allah More Than What You Own","description":"This Hadith explains true zuhd, or indifference toward this world, in a balanced way. The Prophet (صلى الله عليه وسلم) is narrated to have said that zuhd does not mean making lawful things forbidden, and it does not mean wasting wealth. Instead, zuhd means not trusting what is in your hand more than what is in Allah’s Hand. It also means that when a calamity reaches you, you desire the reward for patience more than the worldly thing you lost. The Hadith teaches that zuhd is not carelessness or self-made hardship. It is a heart matter: relying on Allah, using blessings properly, and seeing hardship with faith."},"teachings":["Zuhd does not mean forbidding what Allah has made lawful.","Zuhd does not mean wasting wealth.","True zuhd means trusting what is with Allah more than what is in your hand.","The Hadith teaches hope in reward when a calamity causes loss."],"related_hadiths":[{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2956","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2324","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E535" s="4" t="n"/>
@@ -12814,7 +12818,7 @@
       </c>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Be Indifferent to Dunya","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that zuhd in dunya and not desiring what people have are paths to love and respect."},"heading":{"title":"Hadith About Zuhd: Be Indifferent to Dunya","description":"This famous Hadith about zuhd gives a clear answer to a man who wanted a deed that would bring Allah’s love and people’s love. The Prophet صلى الله عليه وسلم told him to be indifferent toward this world, and Allah would love him. He also told him to be indifferent to what is in people’s hands, and people would love him. The message is not about hating life or refusing every good thing. The wording focuses on the heart: do not make dunya your main desire, and do not keep looking at what others own. This creates a clean heart, less jealousy, and fewer demands from people. The Hadith teaches simple living, contentment, and freedom from craving what belongs to others."},"teachings":["Zuhd in this world is linked in the Hadith with Allah’s love.","Not craving what people own can help protect relationships.","A believer should avoid building life around envy or greed.","Contentment can make the heart lighter and speech calmer."],"related_hadiths":[{"id":"4101","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4105","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4107","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Be Indifferent to Dunya","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that zuhd in dunya and not desiring what people have are paths to love and respect."},"heading":{"title":"Hadith About Zuhd: Be Indifferent to Dunya","description":"This famous Hadith about zuhd gives a clear answer to a man who wanted a deed that would bring Allah’s love and people’s love. The Prophet صلى الله عليه وسلم told him to be indifferent toward this world, and Allah would love him. He also told him to be indifferent to what is in people’s hands, and people would love him. The message is not about hating life or refusing every good thing. The wording focuses on the heart: do not make dunya your main desire, and do not keep looking at what others own. This creates a clean heart, less jealousy, and fewer demands from people. The Hadith teaches simple living, contentment, and freedom from craving what belongs to others."},"teachings":["Zuhd in this world is linked in the Hadith with Allah’s love.","Not craving what people own can help protect relationships.","A believer should avoid building life around envy or greed.","Contentment can make the heart lighter and speech calmer."],"related_hadiths":[{"id":"4101","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4105","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4107","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E536" s="4" t="n"/>
@@ -12837,7 +12841,7 @@
       </c>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wealth and Enoughness","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hashim recalls advice about taking only what is enough, then regrets accumulating wealth."},"heading":{"title":"Hadith About Wealth, Contentment, and Taking What Is Enough","description":"This Hadith shows a personal moment of regret. Abu Hashim was ill and wept, not because of pain and not because he was attached to the world. He remembered advice from the Messenger of Allah صلى الله عليه وسلم. The advice was that when wealth would be divided among people, what would be enough for him was a servant and a mount to ride in the cause of Allah. Abu Hashim then said that the time came, but he accumulated wealth. The Hadith focuses on contentment and the danger of collecting more than one needs. It does not say every possession is forbidden. It shows how a Companion feared that he had gone beyond the level of simple sufficiency advised to him."},"teachings":["A person may regret taking more of the world than he needed.","Sufficiency is a key theme in the Prophet’s advice here.","Wealth can test whether a person follows sincere advice.","Remembering prophetic guidance can awaken the heart even near death."],"related_hadiths":[{"id":"4104","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4105","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4109","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wealth and Enoughness","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hashim recalls advice about taking only what is enough, then regrets accumulating wealth."},"heading":{"title":"Hadith About Wealth, Contentment, and Taking What Is Enough","description":"This Hadith shows a personal moment of regret. Abu Hashim was ill and wept, not because of pain and not because he was attached to the world. He remembered advice from the Messenger of Allah صلى الله عليه وسلم. The advice was that when wealth would be divided among people, what would be enough for him was a servant and a mount to ride in the cause of Allah. Abu Hashim then said that the time came, but he accumulated wealth. The Hadith focuses on contentment and the danger of collecting more than one needs. It does not say every possession is forbidden. It shows how a Companion feared that he had gone beyond the level of simple sufficiency advised to him."},"teachings":["A person may regret taking more of the world than he needed.","Sufficiency is a key theme in the Prophet’s advice here.","Wealth can test whether a person follows sincere advice.","Remembering prophetic guidance can awaken the heart even near death."],"related_hadiths":[{"id":"4104","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4105","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4109","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E537" s="4" t="n"/>
@@ -12860,7 +12864,7 @@
       </c>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Provision of a Rider","description":"$book_name$ $hadith_number$ - $chapter_name$. Salman remembers the advice that a rider’s provision is enough and warns Sa’d to fear Allah."},"heading":{"title":"Hadith About Simple Provision and Fear of Allah","description":"This Hadith gives a moving picture of Salman during illness. When Sa’d saw him crying, Salman explained that he was not crying out of love for the world or dislike of the Hereafter. He cried because the Messenger of Allah صلى الله عليه وسلم had advised him that something like the provision of a rider is enough for one of you, and he feared he had gone beyond that. The Hadith also includes Salman’s advice to Sa’d: fear Allah when judging, when distributing, and when deciding to do anything. The main message is about simple provision and careful responsibility. It teaches that zuhd is not only about owning less, but also about fearing Allah in decisions that affect others."},"teachings":["A believer can fear falling short of prophetic advice even in small matters.","Simple provision is praised in this narration as enough for the journey of life.","Fear of Allah should guide judgment, distribution, and personal decisions.","Crying here came from self-accounting, not from love of dunya."],"related_hadiths":[{"id":"4103","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4105","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4118","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Provision of a Rider","description":"$book_name$ $hadith_number$ - $chapter_name$. Salman remembers the advice that a rider’s provision is enough and warns Sa’d to fear Allah."},"heading":{"title":"Hadith About Simple Provision and Fear of Allah","description":"This Hadith gives a moving picture of Salman during illness. When Sa’d saw him crying, Salman explained that he was not crying out of love for the world or dislike of the Hereafter. He cried because the Messenger of Allah صلى الله عليه وسلم had advised him that something like the provision of a rider is enough for one of you, and he feared he had gone beyond that. The Hadith also includes Salman’s advice to Sa’d: fear Allah when judging, when distributing, and when deciding to do anything. The main message is about simple provision and careful responsibility. It teaches that zuhd is not only about owning less, but also about fearing Allah in decisions that affect others."},"teachings":["A believer can fear falling short of prophetic advice even in small matters.","Simple provision is praised in this narration as enough for the journey of life.","Fear of Allah should guide judgment, distribution, and personal decisions.","Crying here came from self-accounting, not from love of dunya."],"related_hadiths":[{"id":"4103","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4105","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4118","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E538" s="4" t="n"/>
@@ -12883,7 +12887,7 @@
       </c>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Focus on the Hereafter","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith contrasts making dunya the main concern with making the Hereafter one’s intention."},"heading":{"title":"Hadith About Focusing on the Hereafter, Not Only Dunya","description":"This Hadith compares two life directions. One person makes this world his main concern. The Hadith says Allah will scatter his affairs, place fear of poverty before his eyes, and he will only receive what was written for him. Another person makes the Hereafter his intention. The Hadith says Allah will gather his affairs, place richness in his heart, and worldly provision will come to him. The message is not to stop working or to ignore needs. The wording is about what rules the heart. If dunya becomes the whole aim, it brings worry and fear. If the Hereafter becomes the aim, the heart is given contentment and life is kept in better order by Allah’s will."},"teachings":["Making dunya the main concern can bring scattered worries.","Making the Hereafter one’s intention is linked with inner richness.","A person receives from the world only what has been written for him.","The heart’s main focus shapes how a person experiences life."],"related_hadiths":[{"id":"4106","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4107","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4108","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Focus on the Hereafter","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith contrasts making dunya the main concern with making the Hereafter one’s intention."},"heading":{"title":"Hadith About Focusing on the Hereafter, Not Only Dunya","description":"This Hadith compares two life directions. One person makes this world his main concern. The Hadith says Allah will scatter his affairs, place fear of poverty before his eyes, and he will only receive what was written for him. Another person makes the Hereafter his intention. The Hadith says Allah will gather his affairs, place richness in his heart, and worldly provision will come to him. The message is not to stop working or to ignore needs. The wording is about what rules the heart. If dunya becomes the whole aim, it brings worry and fear. If the Hereafter becomes the aim, the heart is given contentment and life is kept in better order by Allah’s will."},"teachings":["Making dunya the main concern can bring scattered worries.","Making the Hereafter one’s intention is linked with inner richness.","A person receives from the world only what has been written for him.","The heart’s main focus shapes how a person experiences life."],"related_hadiths":[{"id":"4106","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4107","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4108","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E539" s="4" t="n"/>
@@ -12906,7 +12910,7 @@
       </c>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Concern for the Hereafter","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith urges the believer to gather the heart around the Hereafter instead of scattered worldly worries."},"heading":{"title":"Hadith About One Main Concern: The Hereafter","description":"This Hadith speaks about the direction of a person’s worries. The Prophet صلى الله عليه وسلم said that whoever makes all his concerns one concern, the concern of the Hereafter, Allah will relieve him of worldly concerns. But whoever lets his concerns scatter across worldly issues is warned with severe words. The Hadith does not deny that people have daily duties, family needs, or work. Its focus is on what captures the heart and becomes the main weight inside a person. When the Hereafter is the main concern, other worries are placed in their proper size. When worldly concerns spread in every direction, a person can become lost in them. This is a strong reminder to keep the Hereafter at the center."},"teachings":["The Hereafter should be the believer’s main concern.","Scattered worldly worries can pull the heart in many directions.","Allah’s help is mentioned for the one who gathers his concern around the Hereafter.","Daily matters should not replace the greater aim of returning to Allah."],"related_hadiths":[{"id":"4105","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4107","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4109","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Concern for the Hereafter","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith urges the believer to gather the heart around the Hereafter instead of scattered worldly worries."},"heading":{"title":"Hadith About One Main Concern: The Hereafter","description":"This Hadith speaks about the direction of a person’s worries. The Prophet صلى الله عليه وسلم said that whoever makes all his concerns one concern, the concern of the Hereafter, Allah will relieve him of worldly concerns. But whoever lets his concerns scatter across worldly issues is warned with severe words. The Hadith does not deny that people have daily duties, family needs, or work. Its focus is on what captures the heart and becomes the main weight inside a person. When the Hereafter is the main concern, other worries are placed in their proper size. When worldly concerns spread in every direction, a person can become lost in them. This is a strong reminder to keep the Hereafter at the center."},"teachings":["The Hereafter should be the believer’s main concern.","Scattered worldly worries can pull the heart in many directions.","Allah’s help is mentioned for the one who gathers his concern around the Hereafter.","Daily matters should not replace the greater aim of returning to Allah."],"related_hadiths":[{"id":"4105","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4107","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4109","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E540" s="4" t="n"/>
@@ -12929,7 +12933,7 @@
       </c>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dunya Compared to the Hereafter","description":"$book_name$ $hadith_number$ - $chapter_name$. The world is compared to what a finger brings from the sea beside the lasting Hereafter."},"heading":{"title":"Hadith About Dunya Compared to the Hereafter","description":"This Hadith gives a picture that is easy to understand. The Prophet صلى الله عليه وسلم compared this world in relation to the Hereafter to a person putting his finger into the sea, then looking at what comes back on it. The image shows how small the world is when compared to the Hereafter. It does not ask the believer to deny that worldly life exists. It asks the heart to see its size correctly. A wet finger beside the sea is tiny. In the same way, dunya should not be treated as if it is equal to the Hereafter. This Hadith about dunya and akhirah helps a person reduce worry over short-term gain and remember the lasting life ahead."},"teachings":["The world is very small when compared with the Hereafter.","A clear example can help the heart understand the value of life.","The believer should not treat dunya as equal to the Hereafter.","Remembering the Hereafter can reduce attachment to temporary gain."],"related_hadiths":[{"id":"4109","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4110","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4113","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dunya Compared to the Hereafter","description":"$book_name$ $hadith_number$ - $chapter_name$. The world is compared to what a finger brings from the sea beside the lasting Hereafter."},"heading":{"title":"Hadith About Dunya Compared to the Hereafter","description":"This Hadith gives a picture that is easy to understand. The Prophet صلى الله عليه وسلم compared this world in relation to the Hereafter to a person putting his finger into the sea, then looking at what comes back on it. The image shows how small the world is when compared to the Hereafter. It does not ask the believer to deny that worldly life exists. It asks the heart to see its size correctly. A wet finger beside the sea is tiny. In the same way, dunya should not be treated as if it is equal to the Hereafter. This Hadith about dunya and akhirah helps a person reduce worry over short-term gain and remember the lasting life ahead."},"teachings":["The world is very small when compared with the Hereafter.","A clear example can help the heart understand the value of life.","The believer should not treat dunya as equal to the Hereafter.","Remembering the Hereafter can reduce attachment to temporary gain."],"related_hadiths":[{"id":"4109","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4110","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4113","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E541" s="4" t="n"/>
@@ -12952,7 +12956,7 @@
       </c>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Worth of the World","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith uses a dead sheep to show how little worldly life weighs before Allah."},"heading":{"title":"Hadith About the Worth of Dunya Before Allah","description":"This Hadith uses a strong example. The Prophet صلى الله عليه وسلم and his Companions saw a dead sheep, and he asked whether they thought it was worthless to its owner. Then he said that this world is more worthless to Allah than that dead sheep is to its owner. He also said that if the world were worth the wing of a mosquito to Allah, a disbeliever would not be given even a drop to drink from it. The message is about the low value of dunya when measured against Allah’s sight. It does not say food, drink, or life needs have no use. It says worldly life should not be treated as the highest measure of success."},"teachings":["The world has little weight before Allah compared with what truly matters.","Worldly gifts do not by themselves prove a person’s rank with Allah.","A vivid example can help people see dunya in its real size.","A believer should not use worldly comfort as the only sign of success."],"related_hadiths":[{"id":"4111","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4108","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4113","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Worth of the World","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith uses a dead sheep to show how little worldly life weighs before Allah."},"heading":{"title":"Hadith About the Worth of Dunya Before Allah","description":"This Hadith uses a strong example. The Prophet صلى الله عليه وسلم and his Companions saw a dead sheep, and he asked whether they thought it was worthless to its owner. Then he said that this world is more worthless to Allah than that dead sheep is to its owner. He also said that if the world were worth the wing of a mosquito to Allah, a disbeliever would not be given even a drop to drink from it. The message is about the low value of dunya when measured against Allah’s sight. It does not say food, drink, or life needs have no use. It says worldly life should not be treated as the highest measure of success."},"teachings":["The world has little weight before Allah compared with what truly matters.","Worldly gifts do not by themselves prove a person’s rank with Allah.","A vivid example can help people see dunya in its real size.","A believer should not use worldly comfort as the only sign of success."],"related_hadiths":[{"id":"4111","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4108","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4113","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E542" s="4" t="n"/>
@@ -12975,7 +12979,7 @@
       </c>
       <c r="D543" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Worldly Life Has Little Worth","description":"$book_name$ $hadith_number$ - $chapter_name$. A discarded dead lamb becomes a lesson on how little dunya is worth before Allah."},"heading":{"title":"Hadith About Dunya Being Worthless Before Allah","description":"This Hadith is close in meaning to the narration about the dead sheep. Mustawrid bin Shaddad says he was riding with the Messenger of Allah صلى الله عليه وسلم when they passed a dead lamb that had been thrown out. The Prophet صلى الله عليه وسلم asked whether it was worthless to its owners. The people said it was thrown out because of its low value. He then swore by Allah that this world is more worthless to Allah than that lamb was to its owners. The Hadith teaches the believer not to be fooled by the shine of dunya. A thing can look large to people but still be small in value before Allah. The lesson is to measure life by faith and the Hereafter."},"teachings":["Dunya can seem important to people while having little value before Allah.","The Prophet صلى الله عليه وسلم used a visible scene to teach a lasting lesson.","Being thrown away showed the lamb’s low value to its owners.","A believer should not be deceived by worldly shine."],"related_hadiths":[{"id":"4110","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4108","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4113","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Worldly Life Has Little Worth","description":"$book_name$ $hadith_number$ - $chapter_name$. A discarded dead lamb becomes a lesson on how little dunya is worth before Allah."},"heading":{"title":"Hadith About Dunya Being Worthless Before Allah","description":"This Hadith is close in meaning to the narration about the dead sheep. Mustawrid bin Shaddad says he was riding with the Messenger of Allah صلى الله عليه وسلم when they passed a dead lamb that had been thrown out. The Prophet صلى الله عليه وسلم asked whether it was worthless to its owners. The people said it was thrown out because of its low value. He then swore by Allah that this world is more worthless to Allah than that lamb was to its owners. The Hadith teaches the believer not to be fooled by the shine of dunya. A thing can look large to people but still be small in value before Allah. The lesson is to measure life by faith and the Hereafter."},"teachings":["Dunya can seem important to people while having little value before Allah.","The Prophet صلى الله عليه وسلم used a visible scene to teach a lasting lesson.","Being thrown away showed the lamb’s low value to its owners.","A believer should not be deceived by worldly shine."],"related_hadiths":[{"id":"4110","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4108","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4113","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E543" s="4" t="n"/>
@@ -12998,7 +13002,7 @@
       </c>
       <c r="D544" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prison of the Believer","description":"$book_name$ $hadith_number$ - $chapter_name$. The world is described as a prison for the believer and a paradise for the disbeliever."},"heading":{"title":"Hadith: The World Is a Prison for the Believer","description":"This short Hadith gives a sharp contrast. The Messenger of Allah صلى الله عليه وسلم said that this world is a prison for the believer and a paradise for the disbeliever. The wording points to how the believer sees worldly life. A prison limits a person. In this life, the believer is not free to follow every desire without care. He lives with commands, limits, worship, patience, and hope in the Hereafter. The disbeliever, in this wording, is described as having paradise in this world compared with what is beyond it. The Hadith does not list details of reward or punishment here. It simply reminds the believer not to expect dunya to feel like the final place of ease."},"teachings":["The believer’s life in dunya includes limits and restraint.","This world is not presented as the believer’s final comfort.","The Hadith helps explain why faith may involve patience.","Worldly ease should not be confused with lasting success."],"related_hadiths":[{"id":"4108","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4110","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4114","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prison of the Believer","description":"$book_name$ $hadith_number$ - $chapter_name$. The world is described as a prison for the believer and a paradise for the disbeliever."},"heading":{"title":"Hadith: The World Is a Prison for the Believer","description":"This short Hadith gives a sharp contrast. The Messenger of Allah صلى الله عليه وسلم said that this world is a prison for the believer and a paradise for the disbeliever. The wording points to how the believer sees worldly life. A prison limits a person. In this life, the believer is not free to follow every desire without care. He lives with commands, limits, worship, patience, and hope in the Hereafter. The disbeliever, in this wording, is described as having paradise in this world compared with what is beyond it. The Hadith does not list details of reward or punishment here. It simply reminds the believer not to expect dunya to feel like the final place of ease."},"teachings":["The believer’s life in dunya includes limits and restraint.","This world is not presented as the believer’s final comfort.","The Hadith helps explain why faith may involve patience.","Worldly ease should not be confused with lasting success."],"related_hadiths":[{"id":"4108","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4110","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4114","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E544" s="4" t="n"/>
@@ -13021,7 +13025,7 @@
       </c>
       <c r="D545" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Poverty with Dignity","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear reminder that Allah loves the poor believer who stays modest, avoids begging, and carries family duties."},"heading":{"title":"Hadith About the Poor Believer and Poverty with Dignity","description":"This hadith teaches a simple but deep message about poverty with dignity. The Messenger of Allah صلى الله عليه وسلم said that Allah loves His believing slave who is poor, does not beg, and has many children. The focus is not on poverty by itself, but on faith, self-restraint, and patient family care. A poor believer may face need, yet the hadith praises the one who does not turn need into begging. It also mentions many children, showing a person who carries real family duties while still keeping faith and honor. For anyone searching for a hadith about the poor believer, this narration points to quiet strength, modest conduct, and trust in Allah during hardship."},"teachings":["Faith gives honor to a person even when wealth is limited.","Avoiding begging is praised in this hadith when a person can remain patient.","Caring for family while poor is a respected form of steadfastness.","Allah loves the believing servant who combines poverty with modest self-restraint."],"related_hadiths":[{"id":"4122","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4126","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Poverty with Dignity","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear reminder that Allah loves the poor believer who stays modest, avoids begging, and carries family duties."},"heading":{"title":"Hadith About the Poor Believer and Poverty with Dignity","description":"This hadith teaches a simple but deep message about poverty with dignity. The Messenger of Allah صلى الله عليه وسلم said that Allah loves His believing slave who is poor, does not beg, and has many children. The focus is not on poverty by itself, but on faith, self-restraint, and patient family care. A poor believer may face need, yet the hadith praises the one who does not turn need into begging. It also mentions many children, showing a person who carries real family duties while still keeping faith and honor. For anyone searching for a hadith about the poor believer, this narration points to quiet strength, modest conduct, and trust in Allah during hardship."},"teachings":["Faith gives honor to a person even when wealth is limited.","Avoiding begging is praised in this hadith when a person can remain patient.","Caring for family while poor is a respected form of steadfastness.","Allah loves the believing servant who combines poverty with modest self-restraint."],"related_hadiths":[{"id":"4122","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4126","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E545" s="4" t="n"/>
@@ -13044,7 +13048,7 @@
       </c>
       <c r="D546" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Poor Believers Enter Paradise First","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith gives glad news that poor believers will enter Paradise before the rich by five hundred years."},"heading":{"title":"Hadith About Poor Believers Entering Paradise Before the Rich","description":"This hadith speaks about the rank of poor believers in the Hereafter. The Messenger of Allah صلى الله عليه وسلم said that the poor believers will enter Paradise before the rich by half a day, explained in the hadith as five hundred years. The main message is not that wealth itself is evil, but that the poor believers mentioned here receive a special glad tiding. The wording points to honor, patience, and a lighter worldly burden. For people searching for a hadith about poor believers entering Jannah, this narration gives comfort to believers who lived with little in this world. It reminds us that worldly lack does not mean low standing with Allah."},"teachings":["Poor believers are given a special glad tiding in this narration.","Worldly wealth is not the only measure of success.","The Hereafter may raise people whose worldly life looked hard.","A believer should not look down on poverty when faith is present."],"related_hadiths":[{"id":"4123","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4124","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4121","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Poor Believers Enter Paradise First","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith gives glad news that poor believers will enter Paradise before the rich by five hundred years."},"heading":{"title":"Hadith About Poor Believers Entering Paradise Before the Rich","description":"This hadith speaks about the rank of poor believers in the Hereafter. The Messenger of Allah صلى الله عليه وسلم said that the poor believers will enter Paradise before the rich by half a day, explained in the hadith as five hundred years. The main message is not that wealth itself is evil, but that the poor believers mentioned here receive a special glad tiding. The wording points to honor, patience, and a lighter worldly burden. For people searching for a hadith about poor believers entering Jannah, this narration gives comfort to believers who lived with little in this world. It reminds us that worldly lack does not mean low standing with Allah."},"teachings":["Poor believers are given a special glad tiding in this narration.","Worldly wealth is not the only measure of success.","The Hereafter may raise people whose worldly life looked hard.","A believer should not look down on poverty when faith is present."],"related_hadiths":[{"id":"4123","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4124","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4121","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E546" s="4" t="n"/>
@@ -13067,7 +13071,7 @@
       </c>
       <c r="D547" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Poor Muhajirun and Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. The poor Muhajirun are promised entry into Paradise before their wealthy counterparts by five hundred years."},"heading":{"title":"Hadith About the Poor Muhajirun Entering Paradise First","description":"This hadith focuses on the poor Muhajirun and their place in the Hereafter. The Messenger of Allah صلى الله عليه وسلم said that the poor among the Muhajirun will enter Paradise before their rich ones by the equivalent of five hundred years. The wording is specific, so the explanation should stay close to that point. It does not say every poor person is better than every rich person in every way. Rather, it gives a clear honor to the poor Muhajirun mentioned in the narration. For readers searching for a hadith about the poor Muhajirun, the key lesson is that limited wealth did not reduce their value with Allah. Their poverty is remembered with glad news connected to Paradise."},"teachings":["The poor Muhajirun are mentioned with a special honor in this narration.","Being poor did not lower their rank in the sight of Allah.","The Hereafter can show a value that people may not see in this world.","A believer should avoid judging people by wealth alone."],"related_hadiths":[{"id":"4122","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4124","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4128","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Poor Muhajirun and Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. The poor Muhajirun are promised entry into Paradise before their wealthy counterparts by five hundred years."},"heading":{"title":"Hadith About the Poor Muhajirun Entering Paradise First","description":"This hadith focuses on the poor Muhajirun and their place in the Hereafter. The Messenger of Allah صلى الله عليه وسلم said that the poor among the Muhajirun will enter Paradise before their rich ones by the equivalent of five hundred years. The wording is specific, so the explanation should stay close to that point. It does not say every poor person is better than every rich person in every way. Rather, it gives a clear honor to the poor Muhajirun mentioned in the narration. For readers searching for a hadith about the poor Muhajirun, the key lesson is that limited wealth did not reduce their value with Allah. Their poverty is remembered with glad news connected to Paradise."},"teachings":["The poor Muhajirun are mentioned with a special honor in this narration.","Being poor did not lower their rank in the sight of Allah.","The Hereafter can show a value that people may not see in this world.","A believer should avoid judging people by wealth alone."],"related_hadiths":[{"id":"4122","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4124","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4128","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E547" s="4" t="n"/>
@@ -13090,7 +13094,7 @@
       </c>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Glad Tidings for the Poor","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم comforted poor believers with news of Paradise before the rich by half a day."},"heading":{"title":"Glad Tidings for Poor Believers in the Hadith","description":"This narration shows poor Muhajirun coming to the Messenger of Allah صلى الله عليه وسلم with a concern. They felt the rich had been favored over them in worldly means. The Prophet صلى الله عليه وسلم answered with glad tidings: the poor believers will enter Paradise before the rich by half a day, explained as five hundred years. This hadith about poor believers and Paradise is comforting because it addresses a real feeling of being left behind in worldly life. The answer moves the heart from comparison to hope in the Hereafter. The hadith does not deny that the rich had certain worldly advantages. It instead reminds the poor believers that Allah has prepared honor beyond what people see now."},"teachings":["The Prophet صلى الله عليه وسلم responded to the concern of poor believers with comfort.","Worldly advantage does not erase reward in the Hereafter.","Poor believers are given glad tidings of early entry into Paradise.","A believer can bring honest concerns to religious guidance."],"related_hadiths":[{"id":"4122","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4123","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4127","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Glad Tidings for the Poor","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم comforted poor believers with news of Paradise before the rich by half a day."},"heading":{"title":"Glad Tidings for Poor Believers in the Hadith","description":"This narration shows poor Muhajirun coming to the Messenger of Allah صلى الله عليه وسلم with a concern. They felt the rich had been favored over them in worldly means. The Prophet صلى الله عليه وسلم answered with glad tidings: the poor believers will enter Paradise before the rich by half a day, explained as five hundred years. This hadith about poor believers and Paradise is comforting because it addresses a real feeling of being left behind in worldly life. The answer moves the heart from comparison to hope in the Hereafter. The hadith does not deny that the rich had certain worldly advantages. It instead reminds the poor believers that Allah has prepared honor beyond what people see now."},"teachings":["The Prophet صلى الله عليه وسلم responded to the concern of poor believers with comfort.","Worldly advantage does not erase reward in the Hereafter.","Poor believers are given glad tidings of early entry into Paradise.","A believer can bring honest concerns to religious guidance."],"related_hadiths":[{"id":"4122","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4123","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4127","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E548" s="4" t="n"/>
@@ -13113,7 +13117,7 @@
       </c>
       <c r="D549" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ja‘far and the Poor","description":"$book_name$ $hadith_number$ - $chapter_name$. Ja‘far bin Abu Talib loved the poor, sat with them, and was known as Abul-Masakin."},"heading":{"title":"Hadith About Ja‘far bin Abu Talib and Love for the Poor","description":"This hadith gives a warm picture of Ja‘far bin Abu Talib and his care for poor people. Abu Hurairah said that Ja‘far used to like the poor. He would sit with them, speak with them, and listen when they spoke to him. The Messenger of Allah صلى الله عليه وسلم gave him the kunyah Abul-Masakin, meaning Father of the Poor. The teaching is very practical. Love for the poor is not shown only by words. In this narration, it appears through sitting, talking, and giving them attention. For someone searching for a hadith about loving the poor, this report shows respect, closeness, and human care. It reminds us that poor people should not be treated as invisible."},"teachings":["Ja‘far bin Abu Talib showed love for the poor by spending time with them.","Speaking with poor people and listening to them is a form of respect.","The Prophet صلى الله عليه وسلم honored Ja‘far with the title Abul-Masakin.","Care for the poor can be shown through closeness and kind company."],"related_hadiths":[{"id":"4126","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4127","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4128","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ja‘far and the Poor","description":"$book_name$ $hadith_number$ - $chapter_name$. Ja‘far bin Abu Talib loved the poor, sat with them, and was known as Abul-Masakin."},"heading":{"title":"Hadith About Ja‘far bin Abu Talib and Love for the Poor","description":"This hadith gives a warm picture of Ja‘far bin Abu Talib and his care for poor people. Abu Hurairah said that Ja‘far used to like the poor. He would sit with them, speak with them, and listen when they spoke to him. The Messenger of Allah صلى الله عليه وسلم gave him the kunyah Abul-Masakin, meaning Father of the Poor. The teaching is very practical. Love for the poor is not shown only by words. In this narration, it appears through sitting, talking, and giving them attention. For someone searching for a hadith about loving the poor, this report shows respect, closeness, and human care. It reminds us that poor people should not be treated as invisible."},"teachings":["Ja‘far bin Abu Talib showed love for the poor by spending time with them.","Speaking with poor people and listening to them is a form of respect.","The Prophet صلى الله عليه وسلم honored Ja‘far with the title Abul-Masakin.","Care for the poor can be shown through closeness and kind company."],"related_hadiths":[{"id":"4126","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4127","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4128","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E549" s="4" t="n"/>
@@ -13136,7 +13140,7 @@
       </c>
       <c r="D550" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Love the Poor","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught love for the poor and prayed to live, die, and be gathered among them."},"heading":{"title":"Hadith About Loving the Poor and Being Gathered With Them","description":"This hadith directly teaches love for the poor. Abu Sa‘eed Al-Khudri said to love the poor because he heard the Messenger of Allah صلى الله عليه وسلم make a supplication: O Allah, cause me to live poor, cause me to die poor, and gather me among the poor on the Day of Resurrection. The hadith about loving the poor is clear in its wording. It links love for poor people with the Prophet’s صلى الله عليه وسلم own prayer. The focus is not on praising hunger or hardship in a careless way. The text points to nearness to the poor, humility, and being counted with them. It helps readers see that poor believers should be loved, honored, and remembered, not pushed away."},"teachings":["The hadith directly calls for love toward the poor.","The Prophet صلى الله عليه وسلم made a supplication connected to living, dying, and being gathered among the poor.","Poor people should be treated with honor, not distance.","Love for the poor is tied in this narration to humility and the Hereafter."],"related_hadiths":[{"id":"4125","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4121","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4127","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Love the Poor","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught love for the poor and prayed to live, die, and be gathered among them."},"heading":{"title":"Hadith About Loving the Poor and Being Gathered With Them","description":"This hadith directly teaches love for the poor. Abu Sa‘eed Al-Khudri said to love the poor because he heard the Messenger of Allah صلى الله عليه وسلم make a supplication: O Allah, cause me to live poor, cause me to die poor, and gather me among the poor on the Day of Resurrection. The hadith about loving the poor is clear in its wording. It links love for poor people with the Prophet’s صلى الله عليه وسلم own prayer. The focus is not on praising hunger or hardship in a careless way. The text points to nearness to the poor, humility, and being counted with them. It helps readers see that poor believers should be loved, honored, and remembered, not pushed away."},"teachings":["The hadith directly calls for love toward the poor.","The Prophet صلى الله عليه وسلم made a supplication connected to living, dying, and being gathered among the poor.","Poor people should be treated with honor, not distance.","Love for the poor is tied in this narration to humility and the Hereafter."],"related_hadiths":[{"id":"4125","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4121","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4127","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E550" s="4" t="n"/>
@@ -13159,7 +13163,7 @@
       </c>
       <c r="D551" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Turn Away Believers","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration teaches respect for weak believers who call on Allah and warns against favoring status over faith."},"heading":{"title":"Hadith About Not Turning Away Poor Believers","description":"This narration explains an event connected to believers who were socially weak but devoted to Allah. Some leaders saw the Prophet صلى الله عليه وسلم sitting with Suhaib, Bilal, Ammar, Khabbab, and other weak believers, then asked for a separate sitting so their status would be seen. They wanted those believers moved away. Then revelation came: do not turn away those who call upon their Lord morning and afternoon, seeking His Face. The hadith about not turning away poor believers teaches that faith and sincere worship matter more than social rank. It also shows that people who are looked down upon by others may be honored by Allah. The message is simple: do not push away believers because they are poor, weak, or low in people’s eyes."},"teachings":["Believers who call upon Allah should not be pushed away for social reasons.","Status and public image should not be placed above sincere faith.","The weak believers in this narration were brought close, not excluded.","Looking down on poor or weak believers is warned against in the text."],"related_hadiths":[{"id":"4128","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4125","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4126","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Turn Away Believers","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration teaches respect for weak believers who call on Allah and warns against favoring status over faith."},"heading":{"title":"Hadith About Not Turning Away Poor Believers","description":"This narration explains an event connected to believers who were socially weak but devoted to Allah. Some leaders saw the Prophet صلى الله عليه وسلم sitting with Suhaib, Bilal, Ammar, Khabbab, and other weak believers, then asked for a separate sitting so their status would be seen. They wanted those believers moved away. Then revelation came: do not turn away those who call upon their Lord morning and afternoon, seeking His Face. The hadith about not turning away poor believers teaches that faith and sincere worship matter more than social rank. It also shows that people who are looked down upon by others may be honored by Allah. The message is simple: do not push away believers because they are poor, weak, or low in people’s eyes."},"teachings":["Believers who call upon Allah should not be pushed away for social reasons.","Status and public image should not be placed above sincere faith.","The weak believers in this narration were brought close, not excluded.","Looking down on poor or weak believers is warned against in the text."],"related_hadiths":[{"id":"4128","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4125","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4126","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E551" s="4" t="n"/>
@@ -13182,7 +13186,7 @@
       </c>
       <c r="D552" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Honor Sincere Believers","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows that sincere believers should not be sent away to satisfy social pride."},"heading":{"title":"Hadith About Honoring Sincere Believers Over Social Status","description":"This hadith tells of a verse revealed about six believers, including Sa‘d, Ibn Mas‘ud, Suhaib, Ammar, Miqdad, and Bilal. The Quraish did not want to join them and asked the Messenger of Allah صلى الله عليه وسلم to send them away. Then Allah revealed the command not to turn away those who call upon their Lord morning and afternoon, seeking His Face. The message is direct and powerful. A believer’s worth is not set by tribe, wealth, or public standing. The hadith about not sending away poor believers teaches that sincere worship is honored. It also warns against making faith gatherings serve pride. Those who seek Allah should be welcomed, not removed to please others."},"teachings":["Sincere believers should not be removed to please people of status.","Calling upon Allah morning and afternoon is praised in the revealed verse.","Social pride should not control religious gatherings.","The value of believers is tied to faith and seeking Allah, not rank."],"related_hadiths":[{"id":"4127","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4125","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4126","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Honor Sincere Believers","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows that sincere believers should not be sent away to satisfy social pride."},"heading":{"title":"Hadith About Honoring Sincere Believers Over Social Status","description":"This hadith tells of a verse revealed about six believers, including Sa‘d, Ibn Mas‘ud, Suhaib, Ammar, Miqdad, and Bilal. The Quraish did not want to join them and asked the Messenger of Allah صلى الله عليه وسلم to send them away. Then Allah revealed the command not to turn away those who call upon their Lord morning and afternoon, seeking His Face. The message is direct and powerful. A believer’s worth is not set by tribe, wealth, or public standing. The hadith about not sending away poor believers teaches that sincere worship is honored. It also warns against making faith gatherings serve pride. Those who seek Allah should be welcomed, not removed to please others."},"teachings":["Sincere believers should not be removed to please people of status.","Calling upon Allah morning and afternoon is praised in the revealed verse.","Social pride should not control religious gatherings.","The value of believers is tied to faith and seeking Allah, not rank."],"related_hadiths":[{"id":"4127","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4125","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4126","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E552" s="4" t="n"/>
@@ -13205,7 +13209,7 @@
       </c>
       <c r="D553" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wealth and Giving","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning for the very wealthy, except those who spend their wealth widely in good ways."},"heading":{"title":"Hadith About Wealth and Spending in Good Ways","description":"This hadith gives a warning about great wealth when it is not used properly. The Messenger of Allah صلى الله عليه وسلم said woe to the most wealthy, except those who do such and such with their money. The narration describes four directions: right, left, front, and behind. The meaning within the text is that wealth should not remain locked to the owner alone. It should be used and given out widely. This hadith about wealth and charity does not say that having money is always blameworthy. It makes an exception for the wealthy person who uses money in giving. The key message is that wealth brings responsibility, and spending it well changes how it is viewed."},"teachings":["Great wealth carries a serious warning when it is not used well.","The exception is for those who spend their money widely.","Money should not make a person closed-handed.","The hadith links wealth with responsibility and giving."],"related_hadiths":[{"id":"4130","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4131","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4132","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wealth and Giving","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning for the very wealthy, except those who spend their wealth widely in good ways."},"heading":{"title":"Hadith About Wealth and Spending in Good Ways","description":"This hadith gives a warning about great wealth when it is not used properly. The Messenger of Allah صلى الله عليه وسلم said woe to the most wealthy, except those who do such and such with their money. The narration describes four directions: right, left, front, and behind. The meaning within the text is that wealth should not remain locked to the owner alone. It should be used and given out widely. This hadith about wealth and charity does not say that having money is always blameworthy. It makes an exception for the wealthy person who uses money in giving. The key message is that wealth brings responsibility, and spending it well changes how it is viewed."},"teachings":["Great wealth carries a serious warning when it is not used well.","The exception is for those who spend their money widely.","Money should not make a person closed-handed.","The hadith links wealth with responsibility and giving."],"related_hadiths":[{"id":"4130","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4131","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4132","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E553" s="4" t="n"/>
@@ -13228,7 +13232,7 @@
       </c>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wealth from Good Sources","description":"$book_name$ $hadith_number$ - $chapter_name$. The wealthy are warned, except those who spend well and earn their money from good sources."},"heading":{"title":"Hadith About Wealth, Charity, and Good Earnings","description":"This hadith gives two clear points about wealth. The Messenger of Allah صلى الله عليه وسلم said that the wealthiest will be the lowest on the Day of Resurrection, except those who do such and such with their money and earn it from good sources. The hadith about halal earnings and charity connects both sides: how wealth is gained and how it is used. It is not enough in this wording for a person simply to possess much. The exception is tied to spending and good sources of income. The message is balanced. Wealth can become a burden, but it can also be handled in a better way when earned cleanly and used for giving."},"teachings":["The hadith warns the very wealthy about their standing on the Day of Resurrection.","Spending wealth in good ways is mentioned as an exception.","Earning from good sources is part of the exception in this text.","A believer should care about both income and spending."],"related_hadiths":[{"id":"4129","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4131","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4135","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wealth from Good Sources","description":"$book_name$ $hadith_number$ - $chapter_name$. The wealthy are warned, except those who spend well and earn their money from good sources."},"heading":{"title":"Hadith About Wealth, Charity, and Good Earnings","description":"This hadith gives two clear points about wealth. The Messenger of Allah صلى الله عليه وسلم said that the wealthiest will be the lowest on the Day of Resurrection, except those who do such and such with their money and earn it from good sources. The hadith about halal earnings and charity connects both sides: how wealth is gained and how it is used. It is not enough in this wording for a person simply to possess much. The exception is tied to spending and good sources of income. The message is balanced. Wealth can become a burden, but it can also be handled in a better way when earned cleanly and used for giving."},"teachings":["The hadith warns the very wealthy about their standing on the Day of Resurrection.","Spending wealth in good ways is mentioned as an exception.","Earning from good sources is part of the exception in this text.","A believer should care about both income and spending."],"related_hadiths":[{"id":"4129","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4131","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4135","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E554" s="4" t="n"/>
@@ -13251,7 +13255,7 @@
       </c>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Wealthiest and Accountability","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم warned that the wealthiest are lowest, except those who use wealth in giving."},"heading":{"title":"Hadith About the Wealthiest Being Lowest Except Those Who Give","description":"This narration repeats a strong warning about wealth. The Messenger of Allah صلى الله عليه وسلم said that the wealthiest will be the lowest, except one who does such and such, mentioned three times. The wording does not give all the details in the translation, but the repeated phrase shows an exception for using wealth in a giving way. This hadith about rich people and charity reminds us that wealth is not only a blessing to enjoy. It also brings a test. A person with much wealth should think about how it is used. The text points away from proud ownership and toward active giving. In simple terms, money should not control the heart or stay only with the owner."},"teachings":["The hadith gives a serious warning to the wealthiest.","There is an exception for those who use wealth in a giving way.","Having more money can bring more responsibility.","A believer should not let wealth become a reason for low standing."],"related_hadiths":[{"id":"4129","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4130","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Wealthiest and Accountability","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم warned that the wealthiest are lowest, except those who use wealth in giving."},"heading":{"title":"Hadith About the Wealthiest Being Lowest Except Those Who Give","description":"This narration repeats a strong warning about wealth. The Messenger of Allah صلى الله عليه وسلم said that the wealthiest will be the lowest, except one who does such and such, mentioned three times. The wording does not give all the details in the translation, but the repeated phrase shows an exception for using wealth in a giving way. This hadith about rich people and charity reminds us that wealth is not only a blessing to enjoy. It also brings a test. A person with much wealth should think about how it is used. The text points away from proud ownership and toward active giving. In simple terms, money should not control the heart or stay only with the owner."},"teachings":["The hadith gives a serious warning to the wealthiest.","There is an exception for those who use wealth in a giving way.","Having more money can bring more responsibility.","A believer should not let wealth become a reason for low standing."],"related_hadiths":[{"id":"4129","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4130","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E555" s="4" t="n"/>
@@ -13274,7 +13278,7 @@
       </c>
       <c r="D556" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Uhud in Gold","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said he would not keep Uhud in gold beyond three nights except for debt."},"heading":{"title":"Hadith About Uhud in Gold and Not Hoarding Wealth","description":"This hadith gives a strong image about wealth. The Prophet صلى الله عليه وسلم said he would not like to have the equivalent of Mount Uhud in gold and then let a third night come while any of it remained with him, except something set aside to pay a debt. The hadith about Uhud in gold teaches that wealth should not be hoarded for its own sake. It also makes a clear exception for paying debt, showing that financial duties matter. The wording points to quick use of wealth in the right way rather than keeping huge amounts unused. It is a lesson in detachment, giving, and taking debt seriously."},"teachings":["The Prophet صلى الله عليه وسلم did not wish to keep a huge amount of gold unused.","The hadith makes an exception for money set aside to pay debt.","Wealth should be handled with purpose, not hoarded for pride.","Paying debt is treated as a serious financial duty in this narration."],"related_hadiths":[{"id":"4129","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4130","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Uhud in Gold","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said he would not keep Uhud in gold beyond three nights except for debt."},"heading":{"title":"Hadith About Uhud in Gold and Not Hoarding Wealth","description":"This hadith gives a strong image about wealth. The Prophet صلى الله عليه وسلم said he would not like to have the equivalent of Mount Uhud in gold and then let a third night come while any of it remained with him, except something set aside to pay a debt. The hadith about Uhud in gold teaches that wealth should not be hoarded for its own sake. It also makes a clear exception for paying debt, showing that financial duties matter. The wording points to quick use of wealth in the right way rather than keeping huge amounts unused. It is a lesson in detachment, giving, and taking debt seriously."},"teachings":["The Prophet صلى الله عليه وسلم did not wish to keep a huge amount of gold unused.","The hadith makes an exception for money set aside to pay debt.","Wealth should be handled with purpose, not hoarded for pride.","Paying debt is treated as a serious financial duty in this narration."],"related_hadiths":[{"id":"4129","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4130","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E556" s="4" t="n"/>
@@ -13297,7 +13301,7 @@
       </c>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Faith and Meeting Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. This supplication places faith, love of meeting Allah, and distance from worldly attachment in focus."},"heading":{"title":"Hadith About Faith, Less Worldly Attachment, and Meeting Allah","description":"This hadith is a supplication of the Messenger of Allah صلى الله عليه وسلم. In it, he asks Allah concerning the one who believes in him, affirms him, and knows that what he brought is the truth from Allah. The prayer asks for that person’s wealth and children to be decreased, for the meeting with Allah to be made dear to him, and for his death to be hastened. Then the narration mentions the one who does not believe or know the truth, asking that his wealth and children be increased and his life made long. This hadith about faith and worldly attachment is serious in tone. The main point from the wording is that faith and loving the meeting with Allah are placed above increase in worldly things."},"teachings":["The hadith links true belief with love of meeting Allah.","Increase in wealth and children is not presented here as the main sign of honor.","The supplication turns the believer’s focus toward Allah rather than worldly increase.","The text contrasts faith with disbelief through different worldly outcomes."],"related_hadiths":[{"id":"4138","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4140","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Faith and Meeting Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. This supplication places faith, love of meeting Allah, and distance from worldly attachment in focus."},"heading":{"title":"Hadith About Faith, Less Worldly Attachment, and Meeting Allah","description":"This hadith is a supplication of the Messenger of Allah صلى الله عليه وسلم. In it, he asks Allah concerning the one who believes in him, affirms him, and knows that what he brought is the truth from Allah. The prayer asks for that person’s wealth and children to be decreased, for the meeting with Allah to be made dear to him, and for his death to be hastened. Then the narration mentions the one who does not believe or know the truth, asking that his wealth and children be increased and his life made long. This hadith about faith and worldly attachment is serious in tone. The main point from the wording is that faith and loving the meeting with Allah are placed above increase in worldly things."},"teachings":["The hadith links true belief with love of meeting Allah.","Increase in wealth and children is not presented here as the main sign of honor.","The supplication turns the believer’s focus toward Allah rather than worldly increase.","The text contrasts faith with disbelief through different worldly outcomes."],"related_hadiths":[{"id":"4138","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4140","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E557" s="4" t="n"/>
@@ -13320,7 +13324,7 @@
       </c>
       <c r="D558" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blessed Giving","description":"$book_name$ $hadith_number$ - $chapter_name$. A man sent a she-camel, the Prophet صلى الله عليه وسلم prayed for blessing, and it gave plenty of milk."},"heading":{"title":"Hadith About Blessed Giving and Daily Provision","description":"This hadith shows a clear contrast between withholding and giving. The Messenger of Allah صلى الله عليه وسلم sent Nuqadah to a man to ask for a she-camel to be used for milk and returned, but the man refused. Then he sent him to another man, who sent a she-camel. When the Prophet صلى الله عليه وسلم saw it, he prayed for blessing upon it and upon the one who sent it. Nuqadah asked that the one who brought it also be included, and the Prophet صلى الله عليه وسلم included him. The camel was milked and gave plenty. Then the Prophet صلى الله عليه وسلم prayed for increased wealth for the one who refused and daily provision for the one who gave. This hadith about giving and provision shows blessing tied to helpful generosity."},"teachings":["Helping with a needed item is praised through the Prophet’s صلى الله عليه وسلم prayer for blessing.","The one who delivered the help was also included in the prayer when asked.","The she-camel gave plenty of milk after the supplication for blessing.","The narration contrasts increase in wealth with provision given day by day."],"related_hadiths":[{"id":"4129","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4138","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blessed Giving","description":"$book_name$ $hadith_number$ - $chapter_name$. A man sent a she-camel, the Prophet صلى الله عليه وسلم prayed for blessing, and it gave plenty of milk."},"heading":{"title":"Hadith About Blessed Giving and Daily Provision","description":"This hadith shows a clear contrast between withholding and giving. The Messenger of Allah صلى الله عليه وسلم sent Nuqadah to a man to ask for a she-camel to be used for milk and returned, but the man refused. Then he sent him to another man, who sent a she-camel. When the Prophet صلى الله عليه وسلم saw it, he prayed for blessing upon it and upon the one who sent it. Nuqadah asked that the one who brought it also be included, and the Prophet صلى الله عليه وسلم included him. The camel was milked and gave plenty. Then the Prophet صلى الله عليه وسلم prayed for increased wealth for the one who refused and daily provision for the one who gave. This hadith about giving and provision shows blessing tied to helpful generosity."},"teachings":["Helping with a needed item is praised through the Prophet’s صلى الله عليه وسلم prayer for blessing.","The one who delivered the help was also included in the prayer when asked.","The she-camel gave plenty of milk after the supplication for blessing.","The narration contrasts increase in wealth with provision given day by day."],"related_hadiths":[{"id":"4129","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4138","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E558" s="4" t="n"/>
@@ -13343,7 +13347,7 @@
       </c>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Slave of Dinar and Dirham","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم warned against serving money and clothes, pleased only when given."},"heading":{"title":"Hadith About the Slave of Dinar and Dirham","description":"This hadith warns against becoming controlled by money and material things. The Messenger of Allah صلى الله عليه وسلم said wretched is the slave of the Dinar, the slave of the Dirham, the slave of velvet, and the slave of the Khamisah. The text then describes a person whose loyalty depends on being given: if he is given, he is pleased, and if he is not given, he does not fulfill his pledge. This hadith about the slave of Dinar and Dirham is really about the heart’s attachment. Money and clothing become dangerous when they decide a person’s satisfaction and commitment. The narration teaches that a believer should not let gifts, wealth, or fine items control faithfulness."},"teachings":["The hadith warns against being controlled by money and material items.","A person should not make loyalty depend only on being given.","Worldly goods can affect the heart if they become the main concern.","Faithfulness should not rise and fall only with material benefit."],"related_hadiths":[{"id":"4136","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4130","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Slave of Dinar and Dirham","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم warned against serving money and clothes, pleased only when given."},"heading":{"title":"Hadith About the Slave of Dinar and Dirham","description":"This hadith warns against becoming controlled by money and material things. The Messenger of Allah صلى الله عليه وسلم said wretched is the slave of the Dinar, the slave of the Dirham, the slave of velvet, and the slave of the Khamisah. The text then describes a person whose loyalty depends on being given: if he is given, he is pleased, and if he is not given, he does not fulfill his pledge. This hadith about the slave of Dinar and Dirham is really about the heart’s attachment. Money and clothing become dangerous when they decide a person’s satisfaction and commitment. The narration teaches that a believer should not let gifts, wealth, or fine items control faithfulness."},"teachings":["The hadith warns against being controlled by money and material items.","A person should not make loyalty depend only on being given.","Worldly goods can affect the heart if they become the main concern.","Faithfulness should not rise and fall only with material benefit."],"related_hadiths":[{"id":"4136","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4130","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E559" s="4" t="n"/>
@@ -13366,7 +13370,7 @@
       </c>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning Against Greed","description":"$book_name$ $hadith_number$ - $chapter_name$. A sharp warning is given against becoming a slave to the Dinar, Dirham, and fine clothing."},"heading":{"title":"Hadith Warning Against Being a Slave to Wealth","description":"This hadith is another warning about being enslaved by wealth and fine clothing. The Prophet صلى الله عليه وسلم said wretched is the slave of the Dinar, the slave of the Dirham, and the slave of the Khamisah. He added that such a person is wretched, thrown down, and if pricked by a thorn may find no relief. The hadith about being a slave to wealth uses strong words to show the harm of deep attachment to money. The focus is not on using money for needs. The warning is about a person whose heart becomes tied to worldly items like a servant tied to a master. It calls the reader to freedom from greed and blind love of possessions."},"teachings":["The hadith strongly warns against being enslaved by money.","Fine clothing is also mentioned as something that can control the heart.","Worldly attachment is described with harsh outcomes in the narration.","A believer should not let possessions become like a master over him."],"related_hadiths":[{"id":"4135","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4130","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning Against Greed","description":"$book_name$ $hadith_number$ - $chapter_name$. A sharp warning is given against becoming a slave to the Dinar, Dirham, and fine clothing."},"heading":{"title":"Hadith Warning Against Being a Slave to Wealth","description":"This hadith is another warning about being enslaved by wealth and fine clothing. The Prophet صلى الله عليه وسلم said wretched is the slave of the Dinar, the slave of the Dirham, and the slave of the Khamisah. He added that such a person is wretched, thrown down, and if pricked by a thorn may find no relief. The hadith about being a slave to wealth uses strong words to show the harm of deep attachment to money. The focus is not on using money for needs. The warning is about a person whose heart becomes tied to worldly items like a servant tied to a master. It calls the reader to freedom from greed and blind love of possessions."},"teachings":["The hadith strongly warns against being enslaved by money.","Fine clothing is also mentioned as something that can control the heart.","Worldly attachment is described with harsh outcomes in the narration.","A believer should not let possessions become like a master over him."],"related_hadiths":[{"id":"4135","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4130","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E560" s="4" t="n"/>
@@ -13389,7 +13393,7 @@
       </c>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | True Richness Is Contentment","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught that real richness is not many goods, but contentment of the soul."},"heading":{"title":"Hadith About True Richness and Contentment of the Soul","description":"This famous hadith defines true richness in a simple way. The Messenger of Allah صلى الله عليه وسلم said that richness is not an abundance of worldly goods. Rather, richness is contentment with one’s lot. The hadith about true richness moves the meaning of wealth from the hand to the heart. A person may own many things and still feel empty or restless. Another person may have less but carry contentment. The wording does not praise laziness or deny the use of lawful goods. It teaches that the deepest form of richness is not measured by the amount of property. For anyone searching for a hadith about contentment, this narration gives a short and clear rule: the rich heart is the content heart."},"teachings":["True richness is not defined by having many worldly goods.","Contentment of the soul is called richness in this hadith.","A person can own much and still lack inner contentment.","The heart’s state matters more than the size of possessions."],"related_hadiths":[{"id":"4138","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4140","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | True Richness Is Contentment","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught that real richness is not many goods, but contentment of the soul."},"heading":{"title":"Hadith About True Richness and Contentment of the Soul","description":"This famous hadith defines true richness in a simple way. The Messenger of Allah صلى الله عليه وسلم said that richness is not an abundance of worldly goods. Rather, richness is contentment with one’s lot. The hadith about true richness moves the meaning of wealth from the hand to the heart. A person may own many things and still feel empty or restless. Another person may have less but carry contentment. The wording does not praise laziness or deny the use of lawful goods. It teaches that the deepest form of richness is not measured by the amount of property. For anyone searching for a hadith about contentment, this narration gives a short and clear rule: the rich heart is the content heart."},"teachings":["True richness is not defined by having many worldly goods.","Contentment of the soul is called richness in this hadith.","A person can own much and still lack inner contentment.","The heart’s state matters more than the size of possessions."],"related_hadiths":[{"id":"4138","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4140","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E561" s="4" t="n"/>
@@ -13412,7 +13416,7 @@
       </c>
       <c r="D562" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Success with Sufficiency","description":"$book_name$ $hadith_number$ - $chapter_name$. Success is described as guidance to Islam, sufficient provision, and contentment with it."},"heading":{"title":"Hadith About Success, Sufficient Provision, and Contentment","description":"This hadith gives a clear picture of success. The Messenger of Allah صلى الله عليه وسلم said that the one has succeeded who is guided to Islam, granted sufficient provision, and is content with it. The hadith about sufficient provision does not define success as having the largest amount of wealth. It joins three things together: Islam, enough provision, and contentment. This is a balanced message. A person needs provision, but the hadith praises provision that is enough, along with a heart that accepts it. For readers searching for a hadith about contentment in Islam, this narration is direct and easy to remember. It teaches that success includes guidance, basic sufficiency, and a satisfied heart."},"teachings":["Guidance to Islam is mentioned first in this description of success.","Sufficient provision is praised in the hadith.","Contentment with what is enough is part of the stated success.","Success is not presented as endless increase in worldly goods."],"related_hadiths":[{"id":"4137","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4140","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Success with Sufficiency","description":"$book_name$ $hadith_number$ - $chapter_name$. Success is described as guidance to Islam, sufficient provision, and contentment with it."},"heading":{"title":"Hadith About Success, Sufficient Provision, and Contentment","description":"This hadith gives a clear picture of success. The Messenger of Allah صلى الله عليه وسلم said that the one has succeeded who is guided to Islam, granted sufficient provision, and is content with it. The hadith about sufficient provision does not define success as having the largest amount of wealth. It joins three things together: Islam, enough provision, and contentment. This is a balanced message. A person needs provision, but the hadith praises provision that is enough, along with a heart that accepts it. For readers searching for a hadith about contentment in Islam, this narration is direct and easy to remember. It teaches that success includes guidance, basic sufficiency, and a satisfied heart."},"teachings":["Guidance to Islam is mentioned first in this description of success.","Sufficient provision is praised in the hadith.","Contentment with what is enough is part of the stated success.","Success is not presented as endless increase in worldly goods."],"related_hadiths":[{"id":"4137","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4140","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E562" s="4" t="n"/>
@@ -13435,7 +13439,7 @@
       </c>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sufficient Provision","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed that the family of Muhammad be given provision sufficient for them."},"heading":{"title":"Hadith About Sufficient Provision for the Family of Muhammad صلى الله عليه وسلم","description":"This hadith is a short supplication with a clear meaning. The Messenger of Allah صلى الله عليه وسلم prayed: O Allah, make the provision of the family of Muhammad sufficient for them. The hadith about sufficient provision points to enough, not excess. It teaches that provision which meets need is a blessing worth asking for. The wording is simple and does not focus on luxury, large amounts, or display. It asks for what can sustain and cover the family. For someone looking for a hadith about rizq and contentment, this narration shows a Prophetic prayer centered on sufficiency. It reminds us that having enough for one’s needs is a great matter, even when it is not a life of plenty."},"teachings":["The Prophet صلى الله عليه وسلم asked Allah for sufficient provision for his family.","The supplication focuses on enough, not excess.","Provision that meets real needs is valued in this narration.","A believer can ask Allah for sustenance that is sufficient."],"related_hadiths":[{"id":"4138","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4140","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sufficient Provision","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed that the family of Muhammad be given provision sufficient for them."},"heading":{"title":"Hadith About Sufficient Provision for the Family of Muhammad صلى الله عليه وسلم","description":"This hadith is a short supplication with a clear meaning. The Messenger of Allah صلى الله عليه وسلم prayed: O Allah, make the provision of the family of Muhammad sufficient for them. The hadith about sufficient provision points to enough, not excess. It teaches that provision which meets need is a blessing worth asking for. The wording is simple and does not focus on luxury, large amounts, or display. It asks for what can sustain and cover the family. For someone looking for a hadith about rizq and contentment, this narration shows a Prophetic prayer centered on sufficiency. It reminds us that having enough for one’s needs is a great matter, even when it is not a life of plenty."},"teachings":["The Prophet صلى الله عليه وسلم asked Allah for sufficient provision for his family.","The supplication focuses on enough, not excess.","Provision that meets real needs is valued in this narration.","A believer can ask Allah for sustenance that is sufficient."],"related_hadiths":[{"id":"4138","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4140","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E563" s="4" t="n"/>
@@ -13458,7 +13462,7 @@
       </c>
       <c r="D564" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bare Minimum Provision","description":"$book_name$ $hadith_number$ - $chapter_name$. On the Day of Resurrection, rich and poor will wish they had only bare provision from the world."},"heading":{"title":"Hadith About Bare Minimum Provision on the Day of Resurrection","description":"This hadith looks at worldly provision from the view of the Hereafter. The Messenger of Allah صلى الله عليه وسلم said that there is no rich man and no poor man except that he will wish on the Day of Resurrection that he had been given the bare minimum of provision in the world. The hadith about bare minimum provision is a reminder that both wealth and poverty will be seen differently when people face the Day of Resurrection. The wording includes both rich and poor, so the lesson is not only for one group. It points to the weight of worldly life and the value of having just enough without being heavily tied to more. It encourages a calm view of rizq and a heart that thinks ahead."},"teachings":["Both rich and poor are mentioned in this hadith.","On the Day of Resurrection, people will view worldly provision differently.","The narration points to the value of bare minimum provision.","A believer should not become overly attached to worldly increase."],"related_hadiths":[{"id":"4138","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bare Minimum Provision","description":"$book_name$ $hadith_number$ - $chapter_name$. On the Day of Resurrection, rich and poor will wish they had only bare provision from the world."},"heading":{"title":"Hadith About Bare Minimum Provision on the Day of Resurrection","description":"This hadith looks at worldly provision from the view of the Hereafter. The Messenger of Allah صلى الله عليه وسلم said that there is no rich man and no poor man except that he will wish on the Day of Resurrection that he had been given the bare minimum of provision in the world. The hadith about bare minimum provision is a reminder that both wealth and poverty will be seen differently when people face the Day of Resurrection. The wording includes both rich and poor, so the lesson is not only for one group. It points to the weight of worldly life and the value of having just enough without being heavily tied to more. It encourages a calm view of rizq and a heart that thinks ahead."},"teachings":["Both rich and poor are mentioned in this hadith.","On the Day of Resurrection, people will view worldly provision differently.","The narration points to the value of bare minimum provision.","A believer should not become overly attached to worldly increase."],"related_hadiths":[{"id":"4138","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4139","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4137","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E564" s="4" t="n"/>
@@ -13481,7 +13485,7 @@
       </c>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gratitude for Daily Blessings","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith reminds us that health, safety, and daily food are enough to see life as a great gift."},"heading":{"title":"Hadith About Gratitude: Health, Safety, and Daily Food","description":"This hadith about gratitude gives a simple way to look at life. The Prophet (صلى الله عليه وسلم) mentions three blessings: physical health, safety, and food for the day. These are not small things. Many people search for more comfort, more wealth, and more status, but this hadith teaches us to notice what we already have. The message is not that a person should stop working or caring for their needs. Rather, it shows that basic blessings are a huge gift from Allah. When a person wakes up healthy, safe, and with enough food for the day, they have been given something very valuable. This is a strong reminder to thank Allah and not look down on daily blessings."},"teachings":["Health is a blessing that should not be taken lightly.","Safety and peace are part of Allah’s gifts.","Having enough food for the day is a reason to be thankful.","A grateful heart can see value in simple daily blessings."],"related_hadiths":[{"id":"2346","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"6416","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gratitude for Daily Blessings","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith reminds us that health, safety, and daily food are enough to see life as a great gift."},"heading":{"title":"Hadith About Gratitude: Health, Safety, and Daily Food","description":"This hadith about gratitude gives a simple way to look at life. The Prophet (صلى الله عليه وسلم) mentions three blessings: physical health, safety, and food for the day. These are not small things. Many people search for more comfort, more wealth, and more status, but this hadith teaches us to notice what we already have. The message is not that a person should stop working or caring for their needs. Rather, it shows that basic blessings are a huge gift from Allah. When a person wakes up healthy, safe, and with enough food for the day, they have been given something very valuable. This is a strong reminder to thank Allah and not look down on daily blessings."},"teachings":["Health is a blessing that should not be taken lightly.","Safety and peace are part of Allah’s gifts.","Having enough food for the day is a reason to be thankful.","A grateful heart can see value in simple daily blessings."],"related_hadiths":[{"id":"2346","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E565" s="4" t="n"/>
@@ -13531,7 +13535,7 @@
       </c>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah Looks at Hearts and Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that Allah values hearts and deeds, not outer looks or wealth."},"heading":{"title":"Allah Looks at Hearts and Deeds: A Hadith About Sincerity","description":"This famous hadith about sincerity gives a clear lesson about what matters before Allah. People often judge by appearance, status, money, or social image. But the Prophet (صلى الله عليه وسلم) says that Allah does not look at forms or wealth. Rather, He looks at deeds and hearts. This means a person should not depend on looks, money, or outward display. The hadith points the heart toward sincere faith and good actions. It also warns us not to measure people only by what we can see. The message is simple: a clean heart and good deeds matter more than outer beauty or wealth. This hadith is a strong reminder to work on what is inside and what we actually do."},"teachings":["Allah’s regard is linked to hearts and deeds, not outer appearance.","Wealth and looks are not the measure of true worth before Allah.","A person should care about sincerity and good actions.","The hadith warns against judging people only by what is visible."],"related_hadiths":[{"id":"6437","book_id":"2","label":"Sahih Muslim"},{"id":"1","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah Looks at Hearts and Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that Allah values hearts and deeds, not outer looks or wealth."},"heading":{"title":"Allah Looks at Hearts and Deeds: A Hadith About Sincerity","description":"This famous hadith about sincerity gives a clear lesson about what matters before Allah. People often judge by appearance, status, money, or social image. But the Prophet (صلى الله عليه وسلم) says that Allah does not look at forms or wealth. Rather, He looks at deeds and hearts. This means a person should not depend on looks, money, or outward display. The hadith points the heart toward sincere faith and good actions. It also warns us not to measure people only by what we can see. The message is simple: a clean heart and good deeds matter more than outer beauty or wealth. This hadith is a strong reminder to work on what is inside and what we actually do."},"teachings":["Allah’s regard is linked to hearts and deeds, not outer appearance.","Wealth and looks are not the measure of true worth before Allah.","A person should care about sincerity and good actions.","The hadith warns against judging people only by what is visible."],"related_hadiths":[{"id":"6437","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E567" s="4" t="n"/>
@@ -13554,7 +13558,7 @@
       </c>
       <c r="D568" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Simple Household","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the simple life of the Prophet’s family, living at times on dates and water."},"heading":{"title":"The Prophet’s Simple Life: Dates and Water in His Home","description":"This hadith about the Prophet’s simple life shows the humble living condition of the family of Muhammad (صلى الله عليه وسلم). Aishah (may Allah be pleased with her) says that a month could pass without fire being lit for cooking in their home. Their food was only dates and water. The hadith does not give a long speech, but the picture is powerful. It shows a home with very little cooked food, yet it belonged to the family of the Messenger of Allah (صلى الله عليه وسلم). This helps us understand that honor is not always shown through comfort or wealth. It also reminds us to value food, avoid waste, and be patient when life is not full of ease."},"teachings":["The family of the Prophet (صلى الله عليه وسلم) lived with great simplicity.","Dates and water were enough for them at times.","Lack of comfort does not reduce a person’s honor.","The hadith encourages gratitude for everyday food."],"related_hadiths":[{"id":"5383","book_id":"1","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Simple Household","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the simple life of the Prophet’s family, living at times on dates and water."},"heading":{"title":"The Prophet’s Simple Life: Dates and Water in His Home","description":"This hadith about the Prophet’s simple life shows the humble living condition of the family of Muhammad (صلى الله عليه وسلم). Aishah (may Allah be pleased with her) says that a month could pass without fire being lit for cooking in their home. Their food was only dates and water. The hadith does not give a long speech, but the picture is powerful. It shows a home with very little cooked food, yet it belonged to the family of the Messenger of Allah (صلى الله عليه وسلم). This helps us understand that honor is not always shown through comfort or wealth. It also reminds us to value food, avoid waste, and be patient when life is not full of ease."},"teachings":["The family of the Prophet (صلى الله عليه وسلم) lived with great simplicity.","Dates and water were enough for them at times.","Lack of comfort does not reduce a person’s honor.","The hadith encourages gratitude for everyday food."],"related_hadiths":[{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E568" s="4" t="n"/>
@@ -13577,7 +13581,7 @@
       </c>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dates, Water, and Good Neighbors","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows simple living, dates and water, and the kindness of sincere Ansar neighbors."},"heading":{"title":"Hadith About Simple Living and Good Neighbors","description":"This hadith about simple living adds another warm detail to the life of the Prophet’s household. Aishah (may Allah be pleased with her) says that a month would pass with no smoke seen in any of the homes of the family of Muhammad (صلى الله عليه وسلم). Their food was dates and water. The hadith also mentions sincere neighbors from the Ansar who had sheep and would send milk to them. So the lesson is not only about little food. It also shows neighborly kindness. The family of the Prophet (صلى الله عليه وسلم) lived simply, and good neighbors helped with what they had. This hadith reminds us to be thankful for food, to value simple meals, and to be caring neighbors."},"teachings":["The Prophet’s family sometimes lived on dates and water.","Good neighbors can be a real blessing in hard times.","Sharing food, even milk, can bring comfort to others.","Simple living can still include kindness and care."],"related_hadiths":[{"id":"6459","book_id":"1","label":"Sahih Bukhari"},{"id":"5383","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dates, Water, and Good Neighbors","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows simple living, dates and water, and the kindness of sincere Ansar neighbors."},"heading":{"title":"Hadith About Simple Living and Good Neighbors","description":"This hadith about simple living adds another warm detail to the life of the Prophet’s household. Aishah (may Allah be pleased with her) says that a month would pass with no smoke seen in any of the homes of the family of Muhammad (صلى الله عليه وسلم). Their food was dates and water. The hadith also mentions sincere neighbors from the Ansar who had sheep and would send milk to them. So the lesson is not only about little food. It also shows neighborly kindness. The family of the Prophet (صلى الله عليه وسلم) lived simply, and good neighbors helped with what they had. This hadith reminds us to be thankful for food, to value simple meals, and to be caring neighbors."},"teachings":["The Prophet’s family sometimes lived on dates and water.","Good neighbors can be a real blessing in hard times.","Sharing food, even milk, can bring comfort to others.","Simple living can still include kindness and care."],"related_hadiths":[{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E569" s="4" t="n"/>
@@ -13600,7 +13604,7 @@
       </c>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Hunger and Patience","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the Prophet’s hunger and his patient life with very little food."},"heading":{"title":"Hadith About the Prophet’s Hunger and Patience","description":"This hadith about the Prophet’s hunger is a strong reminder of how difficult life could be for the Messenger of Allah (صلى الله عليه وسلم). Umar (may Allah be pleased with him) said that he saw the Prophet (صلى الله عليه وسلم) writhing from hunger during the day. He could not even find the worst kind of dates to fill his stomach. The hadith is direct and serious. It shows that the Prophet (صلى الله عليه وسلم) faced real hunger, not just a small lack of comfort. This helps us value food and avoid waste. It also reminds us that hardship can touch even the best of people. The lesson is to stay patient, thankful, and aware of those who have little."},"teachings":["The Prophet (صلى الله عليه وسلم) experienced real hunger.","Even simple food like poor-quality dates was not always available.","Hardship can touch people of great honor.","The hadith encourages care for the hungry and gratitude for food."],"related_hadiths":[{"id":"5383","book_id":"1","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Hunger and Patience","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the Prophet’s hunger and his patient life with very little food."},"heading":{"title":"Hadith About the Prophet’s Hunger and Patience","description":"This hadith about the Prophet’s hunger is a strong reminder of how difficult life could be for the Messenger of Allah (صلى الله عليه وسلم). Umar (may Allah be pleased with him) said that he saw the Prophet (صلى الله عليه وسلم) writhing from hunger during the day. He could not even find the worst kind of dates to fill his stomach. The hadith is direct and serious. It shows that the Prophet (صلى الله عليه وسلم) faced real hunger, not just a small lack of comfort. This helps us value food and avoid waste. It also reminds us that hardship can touch even the best of people. The lesson is to stay patient, thankful, and aware of those who have little."},"teachings":["The Prophet (صلى الله عليه وسلم) experienced real hunger.","Even simple food like poor-quality dates was not always available.","Hardship can touch people of great honor.","The hadith encourages care for the hungry and gratitude for food."],"related_hadiths":[{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E570" s="4" t="n"/>
@@ -13623,7 +13627,7 @@
       </c>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Family Had Little Food","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows that the Prophet’s family sometimes had no Sa’ of grain or dates."},"heading":{"title":"The Prophet’s Family Had Little Food: A Hadith About Simplicity","description":"This hadith about the Prophet’s family and food shows the simple and hard living condition in his home. Anas bin Malik (may Allah be pleased with him) heard the Messenger of Allah (صلى الله عليه وسلم) say several times that the family of Muhammad did not have a Sa’ of food grains or a Sa’ of dates. The narration also says he had nine wives at that time. This makes the picture even clearer: the household was not small, yet the food was very limited. The hadith teaches us not to link honor with plenty of food or wealth. It also reminds us to be thankful for what we have and to notice families who may be quietly struggling."},"teachings":["The Prophet’s household sometimes had very little stored food.","A large family can face real food limits.","Honor is not measured by wealth or full storage.","The hadith encourages gratitude and concern for families in need."],"related_hadiths":[{"id":"6459","book_id":"1","label":"Sahih Bukhari"},{"id":"5383","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Family Had Little Food","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows that the Prophet’s family sometimes had no Sa’ of grain or dates."},"heading":{"title":"The Prophet’s Family Had Little Food: A Hadith About Simplicity","description":"This hadith about the Prophet’s family and food shows the simple and hard living condition in his home. Anas bin Malik (may Allah be pleased with him) heard the Messenger of Allah (صلى الله عليه وسلم) say several times that the family of Muhammad did not have a Sa’ of food grains or a Sa’ of dates. The narration also says he had nine wives at that time. This makes the picture even clearer: the household was not small, yet the food was very limited. The hadith teaches us not to link honor with plenty of food or wealth. It also reminds us to be thankful for what we have and to notice families who may be quietly struggling."},"teachings":["The Prophet’s household sometimes had very little stored food.","A large family can face real food limits.","Honor is not measured by wealth or full storage.","The hadith encourages gratitude and concern for families in need."],"related_hadiths":[{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E571" s="4" t="n"/>
@@ -13646,7 +13650,7 @@
       </c>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Mudd of Food in the Prophet’s Home","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the small amount of food found in the Prophet’s family."},"heading":{"title":"Hadith About the Prophet’s Simple Home and Little Food","description":"This hadith about little food in the Prophet’s home gives another short but strong picture of simple living. The Messenger of Allah (صلى الله عليه وسلم) said that the family of Muhammad had only a Mudd of food, or did not even have a Mudd of food. The wording in the narration shows the smallness of what was available. The lesson is not to praise hunger by itself, but to understand that the Prophet’s family lived with very limited means at times. This hadith can help a person become more thankful for meals, storage, and comfort. It also softens the heart toward people who do not have enough food in their homes."},"teachings":["The Prophet’s family sometimes had only a very small amount of food.","Simple living was part of the Prophet’s household experience.","Food in the home should be valued and not wasted.","The hadith reminds us to notice people with little food."],"related_hadiths":[{"id":"6459","book_id":"1","label":"Sahih Bukhari"},{"id":"5383","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Mudd of Food in the Prophet’s Home","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the small amount of food found in the Prophet’s family."},"heading":{"title":"Hadith About the Prophet’s Simple Home and Little Food","description":"This hadith about little food in the Prophet’s home gives another short but strong picture of simple living. The Messenger of Allah (صلى الله عليه وسلم) said that the family of Muhammad had only a Mudd of food, or did not even have a Mudd of food. The wording in the narration shows the smallness of what was available. The lesson is not to praise hunger by itself, but to understand that the Prophet’s family lived with very limited means at times. This hadith can help a person become more thankful for meals, storage, and comfort. It also softens the heart toward people who do not have enough food in their homes."},"teachings":["The Prophet’s family sometimes had only a very small amount of food.","Simple living was part of the Prophet’s household experience.","Food in the home should be valued and not wasted.","The hadith reminds us to notice people with little food."],"related_hadiths":[{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E572" s="4" t="n"/>
@@ -13669,7 +13673,7 @@
       </c>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Nights Without Food","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows a time when the Prophet and his companions went three nights without food."},"heading":{"title":"Three Nights Without Food: A Hadith About Hunger and Patience","description":"This hadith about hunger describes a difficult time with the Messenger of Allah (صلى الله عليه وسلم). Sulaiman bin Surad said that the Prophet (صلى الله عليه وسلم) came to them, and they stayed for three nights without being able to find food. The wording is plain, but the meaning is heavy. It shows that hunger was not just a quick feeling; it lasted for days. This hadith teaches us to value food and to remember that early Muslims faced real hardship. It also reminds us to be patient during tight times and to care for people who may be going through hunger. The hadith keeps the focus on the lived reality mentioned in the narration."},"teachings":["The Prophet (صلى الله عليه وسلم) and others faced days without food.","Hunger can be a serious test.","Food should be valued when it is available.","The hadith encourages patience and awareness of the hungry."],"related_hadiths":[{"id":"5383","book_id":"1","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Nights Without Food","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows a time when the Prophet and his companions went three nights without food."},"heading":{"title":"Three Nights Without Food: A Hadith About Hunger and Patience","description":"This hadith about hunger describes a difficult time with the Messenger of Allah (صلى الله عليه وسلم). Sulaiman bin Surad said that the Prophet (صلى الله عليه وسلم) came to them, and they stayed for three nights without being able to find food. The wording is plain, but the meaning is heavy. It shows that hunger was not just a quick feeling; it lasted for days. This hadith teaches us to value food and to remember that early Muslims faced real hardship. It also reminds us to be patient during tight times and to care for people who may be going through hunger. The hadith keeps the focus on the lived reality mentioned in the narration."},"teachings":["The Prophet (صلى الله عليه وسلم) and others faced days without food.","Hunger can be a serious test.","Food should be valued when it is available.","The hadith encourages patience and awareness of the hungry."],"related_hadiths":[{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E573" s="4" t="n"/>
@@ -13692,7 +13696,7 @@
       </c>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praising Allah for Hot Food","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet praising Allah after eating hot food after a long time."},"heading":{"title":"Hadith About Gratitude for Food: Praising Allah After a Meal","description":"This hadith about gratitude for food shows how the Prophet (صلى الله عليه وسلم) responded when hot food was brought to him. He ate, and when he finished, he praised Allah. Then he said that no hot food had entered his stomach for such and such a time. The message is simple and touching. Hot food, which many people may see as normal, was something he had not had for a period of time. The hadith teaches us to notice food as a blessing, especially warm meals that bring comfort. It also shows the Prophet’s habit of praising Allah after receiving food. This is a clear reminder to be thankful for what reaches our plate."},"teachings":["The Prophet (صلى الله عليه وسلم) praised Allah after eating.","Hot food was not always available to him.","Common meals can be a meaningful blessing.","The hadith encourages gratitude after food."],"related_hadiths":[{"id":"5383","book_id":"1","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praising Allah for Hot Food","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet praising Allah after eating hot food after a long time."},"heading":{"title":"Hadith About Gratitude for Food: Praising Allah After a Meal","description":"This hadith about gratitude for food shows how the Prophet (صلى الله عليه وسلم) responded when hot food was brought to him. He ate, and when he finished, he praised Allah. Then he said that no hot food had entered his stomach for such and such a time. The message is simple and touching. Hot food, which many people may see as normal, was something he had not had for a period of time. The hadith teaches us to notice food as a blessing, especially warm meals that bring comfort. It also shows the Prophet’s habit of praising Allah after receiving food. This is a clear reminder to be thankful for what reaches our plate."},"teachings":["The Prophet (صلى الله عليه وسلم) praised Allah after eating.","Hot food was not always available to him.","Common meals can be a meaningful blessing.","The hadith encourages gratitude after food."],"related_hadiths":[{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E574" s="4" t="n"/>
@@ -13715,7 +13719,7 @@
       </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Simple Bed","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the Prophet’s bed as leather stuffed with date-palm fibers."},"heading":{"title":"The Prophet’s Simple Bed: A Hadith About Humble Living","description":"This hadith about the Prophet’s simple bed gives a small but clear picture of his home life. Aishah (may Allah be pleased with her) said that the bed of the Messenger of Allah (صلى الله عليه وسلم) was made of leather and stuffed with fibers from date-palm trees. The hadith does not speak about luxury or decoration. It shows a plain bed made from simple materials. This teaches us that comfort does not have to be excessive, and a person’s value is not tied to expensive things. The hadith also helps us understand the Prophet’s humble lifestyle through everyday items. It is a reminder to be thankful for what we sleep on and to avoid making comfort the main goal of life."},"teachings":["The Prophet’s bed was simple and plain.","A simple home item can teach humility.","A person’s worth is not based on luxury.","The hadith encourages gratitude for basic comfort."],"related_hadiths":[{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Simple Bed","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the Prophet’s bed as leather stuffed with date-palm fibers."},"heading":{"title":"The Prophet’s Simple Bed: A Hadith About Humble Living","description":"This hadith about the Prophet’s simple bed gives a small but clear picture of his home life. Aishah (may Allah be pleased with her) said that the bed of the Messenger of Allah (صلى الله عليه وسلم) was made of leather and stuffed with fibers from date-palm trees. The hadith does not speak about luxury or decoration. It shows a plain bed made from simple materials. This teaches us that comfort does not have to be excessive, and a person’s value is not tied to expensive things. The hadith also helps us understand the Prophet’s humble lifestyle through everyday items. It is a reminder to be thankful for what we sleep on and to avoid making comfort the main goal of life."},"teachings":["The Prophet’s bed was simple and plain.","A simple home item can teach humility.","A person’s worth is not based on luxury.","The hadith encourages gratitude for basic comfort."],"related_hadiths":[{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E575" s="4" t="n"/>
@@ -13738,7 +13742,7 @@
       </c>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Simple Wedding Gifts","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions simple wedding gifts given to Ali and Fatimah."},"heading":{"title":"Simple Wedding Gifts in Islam: A Hadith About Ali and Fatimah","description":"This hadith about simple wedding gifts describes what the Messenger of Allah (صلى الله عليه وسلم) gave to Ali and Fatimah. He came to them while they were covered with a Khamil, a white woolen cloth. The narration says he had given them that cloth as a wedding gift, along with a pillow stuffed with Idhkhir and a water skin. The items are simple and useful. The hadith does not present marriage through heavy spending or display. It shows a practical start to married life with basic household things. This can help readers understand that blessing in a marriage is not measured by how expensive the gifts are. The hadith points to useful, modest gifts and a simple home setup."},"teachings":["Wedding gifts can be simple and useful.","Ali and Fatimah received basic household items.","Marriage does not have to begin with display or excess.","The hadith values practical support for a new home."],"related_hadiths":[{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Simple Wedding Gifts","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions simple wedding gifts given to Ali and Fatimah."},"heading":{"title":"Simple Wedding Gifts in Islam: A Hadith About Ali and Fatimah","description":"This hadith about simple wedding gifts describes what the Messenger of Allah (صلى الله عليه وسلم) gave to Ali and Fatimah. He came to them while they were covered with a Khamil, a white woolen cloth. The narration says he had given them that cloth as a wedding gift, along with a pillow stuffed with Idhkhir and a water skin. The items are simple and useful. The hadith does not present marriage through heavy spending or display. It shows a practical start to married life with basic household things. This can help readers understand that blessing in a marriage is not measured by how expensive the gifts are. The hadith points to useful, modest gifts and a simple home setup."},"teachings":["Wedding gifts can be simple and useful.","Ali and Fatimah received basic household items.","Marriage does not have to begin with display or excess.","The hadith values practical support for a new home."],"related_hadiths":[{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E576" s="4" t="n"/>
@@ -13761,7 +13765,7 @@
       </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Choosing the Hereafter Over the World","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet’s simple room and his reminder that the Hereafter is better."},"heading":{"title":"Choosing the Hereafter: The Prophet’s Reed Mat and Simple Room","description":"This hadith about the Hereafter gives a deep picture of the Prophet’s simple life. Umar (may Allah be pleased with him) entered and saw the Messenger of Allah (صلى الله عليه وسلم) on a reed mat. The mat had left marks on his side. Umar also saw only a small amount of barley, acacia leaves, and a hanging skin. He cried because leaders like Chosroes and Caesar had fruits and rivers, while the Prophet (صلى الله عليه وسلم) had so little. The Prophet (صلى الله عليه وسلم) answered by pointing to the Hereafter. The hadith teaches that the world is not the final measure of success. It also shows that the Prophet’s simple life was tied to a greater hope beyond this world."},"teachings":["The Prophet (صلى الله عليه وسلم) lived with very simple belongings.","Umar was moved by the marks of the mat and the small storage.","Worldly comfort is not the final measure of honor.","The hadith directs the heart toward the Hereafter."],"related_hadiths":[{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"6438","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Choosing the Hereafter Over the World","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet’s simple room and his reminder that the Hereafter is better."},"heading":{"title":"Choosing the Hereafter: The Prophet’s Reed Mat and Simple Room","description":"This hadith about the Hereafter gives a deep picture of the Prophet’s simple life. Umar (may Allah be pleased with him) entered and saw the Messenger of Allah (صلى الله عليه وسلم) on a reed mat. The mat had left marks on his side. Umar also saw only a small amount of barley, acacia leaves, and a hanging skin. He cried because leaders like Chosroes and Caesar had fruits and rivers, while the Prophet (صلى الله عليه وسلم) had so little. The Prophet (صلى الله عليه وسلم) answered by pointing to the Hereafter. The hadith teaches that the world is not the final measure of success. It also shows that the Prophet’s simple life was tied to a greater hope beyond this world."},"teachings":["The Prophet (صلى الله عليه وسلم) lived with very simple belongings.","Umar was moved by the marks of the mat and the small storage.","Worldly comfort is not the final measure of honor.","The hadith directs the heart toward the Hereafter."],"related_hadiths":[{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6438","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E577" s="4" t="n"/>
@@ -13784,7 +13788,7 @@
       </c>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Simple Wedding Bed","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions Ali and Fatimah’s simple bed on their wedding night."},"heading":{"title":"Simple Marriage in Islam: Ali and Fatimah’s Wedding Bed","description":"This hadith about simple marriage gives a brief but clear detail from the home of Ali and Fatimah. Ali (may Allah be pleased with him) said that when the daughter of the Messenger of Allah (صلى الله عليه وسلم) was presented to him as a bride, their bed that night was no more than the hide of a ram. The wording shows a very simple beginning. The hadith does not speak about luxury, show, or expensive arrangements. It reminds us that marriage can begin with little, and that honor is not built on costly household items. The teaching stays close to the text: their bed was simple, and the start of their married life was modest."},"teachings":["Ali and Fatimah began married life with a very simple bed.","A wedding does not need expensive display to be meaningful.","Simple household items can be enough at the start.","The hadith shows modest living in a family close to the Prophet (صلى الله عليه وسلم)."],"related_hadiths":[{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Simple Wedding Bed","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions Ali and Fatimah’s simple bed on their wedding night."},"heading":{"title":"Simple Marriage in Islam: Ali and Fatimah’s Wedding Bed","description":"This hadith about simple marriage gives a brief but clear detail from the home of Ali and Fatimah. Ali (may Allah be pleased with him) said that when the daughter of the Messenger of Allah (صلى الله عليه وسلم) was presented to him as a bride, their bed that night was no more than the hide of a ram. The wording shows a very simple beginning. The hadith does not speak about luxury, show, or expensive arrangements. It reminds us that marriage can begin with little, and that honor is not built on costly household items. The teaching stays close to the text: their bed was simple, and the start of their married life was modest."},"teachings":["Ali and Fatimah began married life with a very simple bed.","A wedding does not need expensive display to be meaningful.","Simple household items can be enough at the start.","The hadith shows modest living in a family close to the Prophet (صلى الله عليه وسلم)."],"related_hadiths":[{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E578" s="4" t="n"/>
@@ -13807,7 +13811,7 @@
       </c>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Earning to Give Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows companions working hard to earn even a small amount for charity."},"heading":{"title":"Hadith About Charity: Working Hard to Give Even a Little","description":"This hadith about charity shows how seriously the companions responded when the Messenger of Allah (صلى الله عليه وسلم) encouraged giving. Abu Mas’ud said that one of them would go out and carry goods for others until he earned a Mudd, then he would bring it. This was not a story of giving from extra wealth. It was about working hard just to have something to donate. The narration then mentions that some people later had one hundred thousand. The lesson from the text is clear: charity was valued even when the amount was small and the effort was great. This hadith helps us see that giving is not only for the rich. A small gift earned with effort can still carry real meaning."},"teachings":["The Prophet (صلى الله عليه وسلم) encouraged charity.","Some companions worked hard to earn even a small amount to give.","Charity is not only linked to large wealth.","Effort behind giving matters in how we understand this narration."],"related_hadiths":[{"id":"1417","book_id":"1","label":"Sahih Bukhari"},{"id":"6438","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Earning to Give Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows companions working hard to earn even a small amount for charity."},"heading":{"title":"Hadith About Charity: Working Hard to Give Even a Little","description":"This hadith about charity shows how seriously the companions responded when the Messenger of Allah (صلى الله عليه وسلم) encouraged giving. Abu Mas’ud said that one of them would go out and carry goods for others until he earned a Mudd, then he would bring it. This was not a story of giving from extra wealth. It was about working hard just to have something to donate. The narration then mentions that some people later had one hundred thousand. The lesson from the text is clear: charity was valued even when the amount was small and the effort was great. This hadith helps us see that giving is not only for the rich. A small gift earned with effort can still carry real meaning."},"teachings":["The Prophet (صلى الله عليه وسلم) encouraged charity.","Some companions worked hard to earn even a small amount to give.","Charity is not only linked to large wealth.","Effort behind giving matters in how we understand this narration."],"related_hadiths":[{"id":"1417","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6438","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E579" s="4" t="n"/>
@@ -13830,7 +13834,7 @@
       </c>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Leaves as Food in Hardship","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes severe hunger when leaves were eaten until gums hurt."},"heading":{"title":"Hadith About Hardship: Eating Leaves Until Gums Hurt","description":"This hadith about hardship describes a very difficult time with the Messenger of Allah (صلى الله عليه وسلم). Utbah bin Ghazwan said that he was the seventh of seven with the Prophet (صلى الله عليه وسلم), and they had no food except leaves from trees. The hunger was so severe that their gums hurt. The hadith is simple, but it gives a strong picture of real pain and limited food. It teaches us to value the ease we have and to remember that the early Muslims faced hard days. The hadith also helps soften the heart toward people who live with hunger. It is not just a story from the past; it is a reminder to be thankful and not waste what Allah provides."},"teachings":["Some companions faced severe hunger with the Prophet (صلى الله عليه وسلم).","They ate leaves when no other food was available.","Hardship can include real physical pain.","The hadith encourages gratitude and care for those in hunger."],"related_hadiths":[{"id":"5383","book_id":"1","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Leaves as Food in Hardship","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes severe hunger when leaves were eaten until gums hurt."},"heading":{"title":"Hadith About Hardship: Eating Leaves Until Gums Hurt","description":"This hadith about hardship describes a very difficult time with the Messenger of Allah (صلى الله عليه وسلم). Utbah bin Ghazwan said that he was the seventh of seven with the Prophet (صلى الله عليه وسلم), and they had no food except leaves from trees. The hunger was so severe that their gums hurt. The hadith is simple, but it gives a strong picture of real pain and limited food. It teaches us to value the ease we have and to remember that the early Muslims faced hard days. The hadith also helps soften the heart toward people who live with hunger. It is not just a story from the past; it is a reminder to be thankful and not waste what Allah provides."},"teachings":["Some companions faced severe hunger with the Prophet (صلى الله عليه وسلم).","They ate leaves when no other food was available.","Hardship can include real physical pain.","The hadith encourages gratitude and care for those in hunger."],"related_hadiths":[{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E580" s="4" t="n"/>
@@ -13853,7 +13857,7 @@
       </c>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Date for Each Man","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows hunger and sharing, as seven dates were given to seven men."},"heading":{"title":"Hadith About Sharing Food: One Date for Each Person","description":"This hadith about sharing food shows a moment of hunger among seven people. Abu Hurairah said that they suffered from hunger, and the Prophet (صلى الله عليه وسلم) gave seven dates: one date for each man. The amount was very small, but it was shared fairly. The hadith teaches us to notice the value of food, even when it is only one date. It also shows that in hard times, whatever is available can be divided with care. The narration does not add extra promises or rulings; it simply shows hunger and sharing. This can remind us to be thankful for meals, to avoid waste, and to help others even when what we have is small."},"teachings":["The companions faced hunger together.","A small amount of food was shared among them.","One date had value in a time of need.","The hadith encourages fair sharing and gratitude."],"related_hadiths":[{"id":"5383","book_id":"1","label":"Sahih Bukhari"},{"id":"1417","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Date for Each Man","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows hunger and sharing, as seven dates were given to seven men."},"heading":{"title":"Hadith About Sharing Food: One Date for Each Person","description":"This hadith about sharing food shows a moment of hunger among seven people. Abu Hurairah said that they suffered from hunger, and the Prophet (صلى الله عليه وسلم) gave seven dates: one date for each man. The amount was very small, but it was shared fairly. The hadith teaches us to notice the value of food, even when it is only one date. It also shows that in hard times, whatever is available can be divided with care. The narration does not add extra promises or rulings; it simply shows hunger and sharing. This can remind us to be thankful for meals, to avoid waste, and to help others even when what we have is small."},"teachings":["The companions faced hunger together.","A small amount of food was shared among them.","One date had value in a time of need.","The hadith encourages fair sharing and gratitude."],"related_hadiths":[{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1417","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E581" s="4" t="n"/>
@@ -13876,7 +13880,7 @@
       </c>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Asked About Worldly Delights","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith reminds us that people will be asked about worldly delights, even basic blessings."},"heading":{"title":"Hadith About Blessings: You Will Be Asked About Delights","description":"This hadith about blessings is linked to the verse, “Then on that Day you shall be asked about the delights.” Zubair asked what delights they would be asked about when they only had the two black ones: dates and water. The Prophet (صلى الله عليه وسلم) answered, “It is going to happen.” The hadith teaches that even basic food and drink are blessings worth noticing. It does not describe luxury. It speaks about dates and water, yet the question of blessings still remains. This makes the lesson very personal. A person should not wait for wealth before feeling responsible for gratitude. Even simple daily items can be part of the blessings a person should recognize."},"teachings":["People will be asked about blessings.","Dates and water are also blessings.","Basic food and drink should not be treated as nothing.","The hadith encourages gratitude for simple delights."],"related_hadiths":[{"id":"5383","book_id":"1","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Asked About Worldly Delights","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith reminds us that people will be asked about worldly delights, even basic blessings."},"heading":{"title":"Hadith About Blessings: You Will Be Asked About Delights","description":"This hadith about blessings is linked to the verse, “Then on that Day you shall be asked about the delights.” Zubair asked what delights they would be asked about when they only had the two black ones: dates and water. The Prophet (صلى الله عليه وسلم) answered, “It is going to happen.” The hadith teaches that even basic food and drink are blessings worth noticing. It does not describe luxury. It speaks about dates and water, yet the question of blessings still remains. This makes the lesson very personal. A person should not wait for wealth before feeling responsible for gratitude. Even simple daily items can be part of the blessings a person should recognize."},"teachings":["People will be asked about blessings.","Dates and water are also blessings.","Basic food and drink should not be treated as nothing.","The hadith encourages gratitude for simple delights."],"related_hadiths":[{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E582" s="4" t="n"/>
@@ -13899,7 +13903,7 @@
       </c>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Date and a Whale","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows scarce provisions, one date a day, and food found at the sea."},"heading":{"title":"Hadith About Provision: One Date a Day and Food from the Sea","description":"This hadith about provision tells of a group of three hundred men sent by the Messenger of Allah (صلى الله عليه وسلم). They carried their supplies, but those supplies ran out until each man had only one date a day. When someone asked how one date could satisfy a man, Jabir said they only realized its worth when they no longer had it. Then they reached the sea and found a whale thrown up by the sea, and they ate from it for eighteen days. The hadith shows the value of small food during hardship. It also shows how relief came after scarcity. The lesson should stay close to the narration: food can feel small until it is gone, and provision may come after difficulty."},"teachings":["One date became valuable when food was scarce.","The companions faced a serious shortage of provisions.","Relief came after hardship through food found at the sea.","The hadith encourages gratitude for even small daily food."],"related_hadiths":[{"id":"5383","book_id":"1","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Date and a Whale","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows scarce provisions, one date a day, and food found at the sea."},"heading":{"title":"Hadith About Provision: One Date a Day and Food from the Sea","description":"This hadith about provision tells of a group of three hundred men sent by the Messenger of Allah (صلى الله عليه وسلم). They carried their supplies, but those supplies ran out until each man had only one date a day. When someone asked how one date could satisfy a man, Jabir said they only realized its worth when they no longer had it. Then they reached the sea and found a whale thrown up by the sea, and they ate from it for eighteen days. The hadith shows the value of small food during hardship. It also shows how relief came after scarcity. The lesson should stay close to the narration: food can feel small until it is gone, and provision may come after difficulty."},"teachings":["One date became valuable when food was scarce.","The companions faced a serious shortage of provisions.","Relief came after hardship through food found at the sea.","The hadith encourages gratitude for even small daily food."],"related_hadiths":[{"id":"5383","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6459","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E583" s="4" t="n"/>
@@ -13922,7 +13926,7 @@
       </c>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Death May Come Sooner","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith reminds us that death may come sooner than worldly repairs and plans."},"heading":{"title":"Hadith About Death: The Matter May Come Sooner","description":"This hadith about death gives a short reminder through a normal daily task. Abdullah bin Amr said that the Messenger of Allah (صلى الله عليه وسلم) passed by while they were fixing a hut that had fallen into disrepair. The Prophet (صلى الله عليه وسلم) asked what they were doing, and after hearing the answer, he said that the matter, meaning death, may come sooner than that. The hadith does not say people can never fix their homes. It simply turns the heart toward the shortness of life. Even while working on needed repairs, a person should remember that death can come before long plans are finished. This hadith is a gentle but serious reminder to not be trapped by the world."},"teachings":["Death may come before worldly plans are completed.","Daily tasks can become reminders of the Hereafter.","The hadith warns against becoming too attached to worldly repairs.","Remembering death can help a person keep life in balance."],"related_hadiths":[{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"6438","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Death May Come Sooner","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith reminds us that death may come sooner than worldly repairs and plans."},"heading":{"title":"Hadith About Death: The Matter May Come Sooner","description":"This hadith about death gives a short reminder through a normal daily task. Abdullah bin Amr said that the Messenger of Allah (صلى الله عليه وسلم) passed by while they were fixing a hut that had fallen into disrepair. The Prophet (صلى الله عليه وسلم) asked what they were doing, and after hearing the answer, he said that the matter, meaning death, may come sooner than that. The hadith does not say people can never fix their homes. It simply turns the heart toward the shortness of life. Even while working on needed repairs, a person should remember that death can come before long plans are finished. This hadith is a gentle but serious reminder to not be trapped by the world."},"teachings":["Death may come before worldly plans are completed.","Daily tasks can become reminders of the Hereafter.","The hadith warns against becoming too attached to worldly repairs.","Remembering death can help a person keep life in balance."],"related_hadiths":[{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6438","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E584" s="4" t="n"/>
@@ -13945,7 +13949,7 @@
       </c>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Extravagant Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear warning against showy wealth and a lesson in quick correction after sincere advice."},"heading":{"title":"Hadith About Extravagance: When Wealth Becomes a Burden","description":"This hadith about extravagance shows a simple but serious lesson. The Prophet صلى الله عليه وسلم saw a dome-shaped structure at the door of a man from the Ansar and asked about it. When he was told it was built by someone, he warned that wealth used in this showy way can become a burden for its owner on the Day of Resurrection. The man did not argue or delay. When he heard the Prophet’s words, he demolished it. The Prophet صلى الله عليه وسلم then made dua for mercy for him twice. The main message is not about rejecting every building. It is about avoiding wasteful display and responding humbly when truth reaches us."},"teachings":["Extravagant display of wealth can become a harmful burden.","A believer should accept sincere advice without pride or delay.","Correcting a wrong choice can be a means of Allah’s mercy.","Wealth should not be used in a way that harms a person in the Hereafter."],"related_hadiths":[{"id":"4161","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"4141","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Extravagant Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear warning against showy wealth and a lesson in quick correction after sincere advice."},"heading":{"title":"Hadith About Extravagance: When Wealth Becomes a Burden","description":"This hadith about extravagance shows a simple but serious lesson. The Prophet صلى الله عليه وسلم saw a dome-shaped structure at the door of a man from the Ansar and asked about it. When he was told it was built by someone, he warned that wealth used in this showy way can become a burden for its owner on the Day of Resurrection. The man did not argue or delay. When he heard the Prophet’s words, he demolished it. The Prophet صلى الله عليه وسلم then made dua for mercy for him twice. The main message is not about rejecting every building. It is about avoiding wasteful display and responding humbly when truth reaches us."},"teachings":["Extravagant display of wealth can become a harmful burden.","A believer should accept sincere advice without pride or delay.","Correcting a wrong choice can be a means of Allah’s mercy.","Wealth should not be used in a way that harms a person in the Hereafter."],"related_hadiths":[{"id":"4161","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4141","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E585" s="4" t="n"/>
@@ -13968,7 +13972,7 @@
       </c>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Simple Shelter and Self-Reliance","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar’s simple home reminds us that shelter is for need, protection, and honest effort."},"heading":{"title":"Hadith About Simple Shelter: A Home for Rain and Sun","description":"This narration gives a quiet picture of simple shelter in Islam. Ibn Umar said that during the time of Allah’s Messenger صلى الله عليه وسلم, he built a house that would protect him from rain and shade him from the sun. He also said that no creature of Allah helped him in building it. The wording is plain, and the lesson should stay plain too. A house can serve a real need: safety from weather, shade, and basic comfort. The narration does not praise showing off, luxury, or dependence on others. It points to a simple home built for use, not display. For people searching for a hadith about building a house, this report highlights need, effort, and modest living."},"teachings":["A home may be built for real protection from rain and sun.","Simple shelter is different from showy display.","Personal effort and self-reliance are shown in Ibn Umar’s action.","Basic needs should be kept clear from unnecessary pride."],"related_hadiths":[{"id":"4141","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"4161","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Simple Shelter and Self-Reliance","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar’s simple home reminds us that shelter is for need, protection, and honest effort."},"heading":{"title":"Hadith About Simple Shelter: A Home for Rain and Sun","description":"This narration gives a quiet picture of simple shelter in Islam. Ibn Umar said that during the time of Allah’s Messenger صلى الله عليه وسلم, he built a house that would protect him from rain and shade him from the sun. He also said that no creature of Allah helped him in building it. The wording is plain, and the lesson should stay plain too. A house can serve a real need: safety from weather, shade, and basic comfort. The narration does not praise showing off, luxury, or dependence on others. It points to a simple home built for use, not display. For people searching for a hadith about building a house, this report highlights need, effort, and modest living."},"teachings":["A home may be built for real protection from rain and sun.","Simple shelter is different from showy display.","Personal effort and self-reliance are shown in Ibn Umar’s action.","Basic needs should be kept clear from unnecessary pride."],"related_hadiths":[{"id":"4141","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4161","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E586" s="4" t="n"/>
@@ -13991,7 +13995,7 @@
       </c>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Patience in Sickness and Spending","description":"$book_name$ $hadith_number$ - $chapter_name$. A sick Companion recalls not wishing for death and warns about unrewarded spending on building."},"heading":{"title":"Hadith About Not Wishing for Death During Hardship","description":"This hadith about not wishing for death comes through Khabbab during a long sickness. He said that if he had not heard the Messenger of Allah صلى الله عليه وسلم say, “Do not wish for death,” he would have wished for it. That shows how heavy his illness felt, but it also shows how firmly he held to the Prophet’s instruction. The report also mentions that a person is rewarded for all spending except what is spent on dust, or building. The wording keeps the focus on patience during suffering and care with spending. It does not say that every building is forbidden. It warns against spending that becomes mere dust or unnecessary building, while reminding the sick heart not to ask for death."},"teachings":["Severe sickness can be hard, but the Prophet صلى الله عليه وسلم taught not to wish for death.","A believer may feel pain while still holding to prophetic guidance.","Spending should be checked so it does not become empty building or dust.","Not all spending carries the same value in reward."],"related_hadiths":[{"id":"5671","book_id":"1","label":"Sahih Bukhari"},{"id":"2680a","book_id":"2","label":"Sahih Muslim"},{"id":"4161","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Patience in Sickness and Spending","description":"$book_name$ $hadith_number$ - $chapter_name$. A sick Companion recalls not wishing for death and warns about unrewarded spending on building."},"heading":{"title":"Hadith About Not Wishing for Death During Hardship","description":"This hadith about not wishing for death comes through Khabbab during a long sickness. He said that if he had not heard the Messenger of Allah صلى الله عليه وسلم say, “Do not wish for death,” he would have wished for it. That shows how heavy his illness felt, but it also shows how firmly he held to the Prophet’s instruction. The report also mentions that a person is rewarded for all spending except what is spent on dust, or building. The wording keeps the focus on patience during suffering and care with spending. It does not say that every building is forbidden. It warns against spending that becomes mere dust or unnecessary building, while reminding the sick heart not to ask for death."},"teachings":["Severe sickness can be hard, but the Prophet صلى الله عليه وسلم taught not to wish for death.","A believer may feel pain while still holding to prophetic guidance.","Spending should be checked so it does not become empty building or dust.","Not all spending carries the same value in reward."],"related_hadiths":[{"id":"5671","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2680a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4161","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E587" s="4" t="n"/>
@@ -14014,7 +14018,7 @@
       </c>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawakkul Like the Birds","description":"$book_name$ $hadith_number$ - $chapter_name$. Trust Allah sincerely, as birds leave hungry and return with provision by His care."},"heading":{"title":"Hadith About Tawakkul: Trust Allah Like the Birds","description":"This famous hadith about tawakkul teaches trust in Allah through the example of birds. The Prophet صلى الله عليه وسلم said that if people relied upon Allah with the reliance He is due, they would be given provision like the birds. The birds go out hungry in the morning and return in the evening with full bellies. The image is easy to understand. They do not own storehouses, yet they are provided for. At the same time, the text says they go out in the morning, so the hadith shows reliance along with movement. For anyone searching for a hadith about rizq, this report gives hope without teaching laziness. Real reliance means the heart depends on Allah while life continues under His provision."},"teachings":["True reliance on Allah is linked to trust in His provision.","The birds’ morning and evening show provision comes by Allah’s care.","The hadith gives hope to people who fear for their rizq.","Going out hungry and returning full shows need and provision together."],"related_hadiths":[{"id":"2344","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"2577a","book_id":"2","label":"Sahih Muslim"},{"id":"4141","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawakkul Like the Birds","description":"$book_name$ $hadith_number$ - $chapter_name$. Trust Allah sincerely, as birds leave hungry and return with provision by His care."},"heading":{"title":"Hadith About Tawakkul: Trust Allah Like the Birds","description":"This famous hadith about tawakkul teaches trust in Allah through the example of birds. The Prophet صلى الله عليه وسلم said that if people relied upon Allah with the reliance He is due, they would be given provision like the birds. The birds go out hungry in the morning and return in the evening with full bellies. The image is easy to understand. They do not own storehouses, yet they are provided for. At the same time, the text says they go out in the morning, so the hadith shows reliance along with movement. For anyone searching for a hadith about rizq, this report gives hope without teaching laziness. Real reliance means the heart depends on Allah while life continues under His provision."},"teachings":["True reliance on Allah is linked to trust in His provision.","The birds’ morning and evening show provision comes by Allah’s care.","The hadith gives hope to people who fear for their rizq.","Going out hungry and returning full shows need and provision together."],"related_hadiths":[{"id":"2344","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"2577a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4141","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E588" s="4" t="n"/>
@@ -14037,7 +14041,7 @@
       </c>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Despair of Rizq","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful reminder that Allah provides for people from birth and throughout life."},"heading":{"title":"Hadith About Rizq: Do Not Despair of Provision","description":"This hadith about rizq speaks to people who feel fear about provision. Habbah and Sawa’ entered upon the Prophet صلى الله عليه وسلم while he was doing something, and they helped him. He then told them not to despair of provision as long as their heads were still moving. He gave a clear example: a person is born from his mother red, with raw skin, and then Allah provides for him. The hadith does not deny hardship, work, or need. It simply closes the door to despair while life remains. For someone searching for a hadith about provision, the message is warm and direct: the One who provided for a helpless newborn can provide through the stages of life."},"teachings":["A believer should not fall into despair over provision while life remains.","Allah’s care is shown from the helpless state of birth.","Helping others is shown in the setting of this narration.","Fear about rizq should be met with hope in Allah’s provision."],"related_hadiths":[{"id":"2344","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"2577a","book_id":"2","label":"Sahih Muslim"},{"id":"4141","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Despair of Rizq","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful reminder that Allah provides for people from birth and throughout life."},"heading":{"title":"Hadith About Rizq: Do Not Despair of Provision","description":"This hadith about rizq speaks to people who feel fear about provision. Habbah and Sawa’ entered upon the Prophet صلى الله عليه وسلم while he was doing something, and they helped him. He then told them not to despair of provision as long as their heads were still moving. He gave a clear example: a person is born from his mother red, with raw skin, and then Allah provides for him. The hadith does not deny hardship, work, or need. It simply closes the door to despair while life remains. For someone searching for a hadith about provision, the message is warm and direct: the One who provided for a helpless newborn can provide through the stages of life."},"teachings":["A believer should not fall into despair over provision while life remains.","Allah’s care is shown from the helpless state of birth.","Helping others is shown in the setting of this narration.","Fear about rizq should be met with hope in Allah’s provision."],"related_hadiths":[{"id":"2344","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"2577a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4141","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E589" s="4" t="n"/>
@@ -14060,7 +14064,7 @@
       </c>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Relying on Allah Amid Desires","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning against chasing every desire and a call to rely on Allah for inner steadiness."},"heading":{"title":"Hadith About Tawakkul and Scattered Desires","description":"This hadith about tawakkul looks inside the human heart. The Prophet صلى الله عليه وسلم said that the heart of the son of Adam has an inclination toward every desirable thing. When a person follows all those inclinations, he may be led toward harm, and the hadith says Allah will not care which valley causes his doom. But whoever relies upon Allah, Allah will protect him from the pain of scattered inclinations. The wording is strong because the danger is real. A heart that runs after every desire becomes divided and tired. Reliance on Allah gives the heart a path, a center, and protection from being pulled in every direction by whatever looks attractive."},"teachings":["The heart can be pulled toward many desirable things.","Following every desire can lead a person toward harm.","Reliance on Allah protects from the pain of a scattered heart.","A believer should not let every inner pull decide his direction."],"related_hadiths":[{"id":"2664","book_id":"2","label":"Sahih Muslim"},{"id":"2344","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"6416","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Relying on Allah Amid Desires","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning against chasing every desire and a call to rely on Allah for inner steadiness."},"heading":{"title":"Hadith About Tawakkul and Scattered Desires","description":"This hadith about tawakkul looks inside the human heart. The Prophet صلى الله عليه وسلم said that the heart of the son of Adam has an inclination toward every desirable thing. When a person follows all those inclinations, he may be led toward harm, and the hadith says Allah will not care which valley causes his doom. But whoever relies upon Allah, Allah will protect him from the pain of scattered inclinations. The wording is strong because the danger is real. A heart that runs after every desire becomes divided and tired. Reliance on Allah gives the heart a path, a center, and protection from being pulled in every direction by whatever looks attractive."},"teachings":["The heart can be pulled toward many desirable things.","Following every desire can lead a person toward harm.","Reliance on Allah protects from the pain of a scattered heart.","A believer should not let every inner pull decide his direction."],"related_hadiths":[{"id":"2664","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2344","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E590" s="4" t="n"/>
@@ -14083,7 +14087,7 @@
       </c>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Thinking Positively of Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. A brief but deep reminder to meet death with good thoughts about Allah."},"heading":{"title":"Hadith About Thinking Positively of Allah at Death","description":"This hadith about thinking positively of Allah is short, but it carries deep comfort. Jabir said that he heard the Messenger of Allah صلى الله عليه وسلم say that no one should die except while thinking positively of Allah. The wording points to the final state of a believer’s heart. It does not invite carelessness or empty claims. It teaches that when death comes, the heart should not be filled with despair about Allah. A person should hold good thoughts of the Lord who knows him and has power over him. For people searching for husn al-dhann billah hadith, this narration is a clear reminder to keep hope in Allah, especially at the end of life."},"teachings":["A believer should avoid despair when death approaches.","Good thoughts about Allah are part of a sound final state.","The hadith gives hope without removing personal responsibility.","The heart should meet Allah with trust in His goodness."],"related_hadiths":[{"id":"2877c","book_id":"2","label":"Sahih Muslim"},{"id":"2577a","book_id":"2","label":"Sahih Muslim"},{"id":"6416","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Thinking Positively of Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. A brief but deep reminder to meet death with good thoughts about Allah."},"heading":{"title":"Hadith About Thinking Positively of Allah at Death","description":"This hadith about thinking positively of Allah is short, but it carries deep comfort. Jabir said that he heard the Messenger of Allah صلى الله عليه وسلم say that no one should die except while thinking positively of Allah. The wording points to the final state of a believer’s heart. It does not invite carelessness or empty claims. It teaches that when death comes, the heart should not be filled with despair about Allah. A person should hold good thoughts of the Lord who knows him and has power over him. For people searching for husn al-dhann billah hadith, this narration is a clear reminder to keep hope in Allah, especially at the end of life."},"teachings":["A believer should avoid despair when death approaches.","Good thoughts about Allah are part of a sound final state.","The hadith gives hope without removing personal responsibility.","The heart should meet Allah with trust in His goodness."],"related_hadiths":[{"id":"2877c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2577a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E591" s="4" t="n"/>
@@ -14106,7 +14110,7 @@
       </c>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Strong Believer and Qadar","description":"$book_name$ $hadith_number$ - $chapter_name$. Strive for what benefits you, avoid helplessness, and accept Allah’s decree."},"heading":{"title":"Strong Believer Hadith: Strive, Trust, and Avoid If Only","description":"This strong believer hadith gives a balanced way to face life. The Prophet صلى الله عليه وسلم said that the stronger believer is better and more beloved to Allah than the weak believer, while making clear that there is good in both. Then he taught action: seek what benefits you and do not feel helpless. If something overwhelms you, say, “Qaddarallah, wa ma sha’a fa’al,” meaning it is Allah’s decree and what He wills He does. The hadith also warns against saying “if only,” because it opens the door to Satan. The message is not passive. It joins effort, strength, useful goals, and acceptance of qadar after events unfold."},"teachings":["A believer should seek what is beneficial and not give in to helplessness.","Both strong and weak believers have good, as stated in the hadith.","After being overwhelmed, a believer should accept Allah’s decree.","Regretful “if only” thinking can open a harmful door."],"related_hadiths":[{"id":"2664","book_id":"2","label":"Sahih Muslim"},{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"2344","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Strong Believer and Qadar","description":"$book_name$ $hadith_number$ - $chapter_name$. Strive for what benefits you, avoid helplessness, and accept Allah’s decree."},"heading":{"title":"Strong Believer Hadith: Strive, Trust, and Avoid If Only","description":"This strong believer hadith gives a balanced way to face life. The Prophet صلى الله عليه وسلم said that the stronger believer is better and more beloved to Allah than the weak believer, while making clear that there is good in both. Then he taught action: seek what benefits you and do not feel helpless. If something overwhelms you, say, “Qaddarallah, wa ma sha’a fa’al,” meaning it is Allah’s decree and what He wills He does. The hadith also warns against saying “if only,” because it opens the door to Satan. The message is not passive. It joins effort, strength, useful goals, and acceptance of qadar after events unfold."},"teachings":["A believer should seek what is beneficial and not give in to helplessness.","Both strong and weak believers have good, as stated in the hadith.","After being overwhelmed, a believer should accept Allah’s decree.","Regretful “if only” thinking can open a harmful door."],"related_hadiths":[{"id":"2664","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2344","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E592" s="4" t="n"/>
@@ -14129,7 +14133,7 @@
       </c>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wisdom Is the Believer’s Lost Property","description":"$book_name$ $hadith_number$ - $chapter_name$. A believer should value wise words wherever he finds them."},"heading":{"title":"Hadith About Wisdom: The Believer’s Lost Property","description":"This hadith about wisdom uses a memorable image. The Prophet صلى الله عليه وسلم said that a wise word is the lost property of the believer, so wherever he finds it, he has more right to it. Lost property is something a person looks for and feels happy to recover. In the same way, a believer should not ignore a wise word when it comes to him. The hadith does not say to accept falsehood or careless talk. It speaks about a word of wisdom, something sound and beneficial. For people searching for “wisdom is the lost property of the believer,” this narration teaches a humble attitude toward learning: recognize good speech and take benefit from it."},"teachings":["A believer should value true wisdom when he finds it.","Wise words are worth seeking and holding onto.","Learning should not be blocked by pride or ego.","The hadith encourages benefit from sound speech."],"related_hadiths":[{"id":"2687","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"6412","book_id":"1","label":"Sahih Bukhari"},{"id":"6416","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wisdom Is the Believer’s Lost Property","description":"$book_name$ $hadith_number$ - $chapter_name$. A believer should value wise words wherever he finds them."},"heading":{"title":"Hadith About Wisdom: The Believer’s Lost Property","description":"This hadith about wisdom uses a memorable image. The Prophet صلى الله عليه وسلم said that a wise word is the lost property of the believer, so wherever he finds it, he has more right to it. Lost property is something a person looks for and feels happy to recover. In the same way, a believer should not ignore a wise word when it comes to him. The hadith does not say to accept falsehood or careless talk. It speaks about a word of wisdom, something sound and beneficial. For people searching for “wisdom is the lost property of the believer,” this narration teaches a humble attitude toward learning: recognize good speech and take benefit from it."},"teachings":["A believer should value true wisdom when he finds it.","Wise words are worth seeking and holding onto.","Learning should not be blocked by pride or ego.","The hadith encourages benefit from sound speech."],"related_hadiths":[{"id":"2687","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"6412","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E593" s="4" t="n"/>
@@ -14152,7 +14156,7 @@
       </c>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Health and Free Time","description":"$book_name$ $hadith_number$ - $chapter_name$. Many people waste two blessings: good health and free time."},"heading":{"title":"Hadith About Health and Free Time: Two Often-Wasted Blessings","description":"This hadith about health and free time is direct and easy to feel in daily life. The Prophet صلى الله عليه وسلم said that two blessings are squandered by many people: good health and free time. The hadith does not list many details. It makes us stop and look at two gifts that are often noticed only after they fade. Good health gives a person ability. Free time gives a person space to choose. When both are present, a person has a chance to use them well. For anyone searching for the two blessings hadith, the message is clear: do not treat health and spare time as empty things. They are blessings, and many people lose their value."},"teachings":["Good health is a blessing that can be wasted.","Free time is also a blessing and should not be treated carelessly.","Many people fail to see the value of these two gifts.","The hadith invites a person to notice blessings before they are gone."],"related_hadiths":[{"id":"6412","book_id":"1","label":"Sahih Bukhari"},{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"4141","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Health and Free Time","description":"$book_name$ $hadith_number$ - $chapter_name$. Many people waste two blessings: good health and free time."},"heading":{"title":"Hadith About Health and Free Time: Two Often-Wasted Blessings","description":"This hadith about health and free time is direct and easy to feel in daily life. The Prophet صلى الله عليه وسلم said that two blessings are squandered by many people: good health and free time. The hadith does not list many details. It makes us stop and look at two gifts that are often noticed only after they fade. Good health gives a person ability. Free time gives a person space to choose. When both are present, a person has a chance to use them well. For anyone searching for the two blessings hadith, the message is clear: do not treat health and spare time as empty things. They are blessings, and many people lose their value."},"teachings":["Good health is a blessing that can be wasted.","Free time is also a blessing and should not be treated carelessly.","Many people fail to see the value of these two gifts.","The hadith invites a person to notice blessings before they are gone."],"related_hadiths":[{"id":"6412","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4141","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E594" s="4" t="n"/>
@@ -14175,7 +14179,7 @@
       </c>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray Like a Farewell Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Concise advice: pray with focus, guard your words, and stop longing for people’s possessions."},"heading":{"title":"Hadith About Farewell Prayer and Guarding Speech","description":"This hadith about praying like a farewell prayer gives three short pieces of advice. A man asked the Prophet صلى الله عليه وسلم to teach him and keep it brief. The Prophet صلى الله عليه وسلم told him that when he stands to pray, he should pray like a man bidding farewell. That makes the prayer feel serious, focused, and present. Then he said not to speak words for which one would have to apologize. This points to careful speech before it leaves the tongue. Finally, he said to give up hope for what other people have. The hadith joins prayer, speech, and inner freedom from people’s possessions. It is concise, but it touches daily worship, daily words, and daily desire."},"teachings":["Prayer should be performed with deep focus, as if it were a farewell prayer.","A believer should avoid speech that later needs apology.","The heart should not be attached to what is in people’s hands.","Brief advice can cover worship, words, and inner attitude."],"related_hadiths":[{"id":"6416","book_id":"1","label":"Sahih Bukhari"},{"id":"6475","book_id":"1","label":"Sahih Bukhari"},{"id":"4141","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray Like a Farewell Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Concise advice: pray with focus, guard your words, and stop longing for people’s possessions."},"heading":{"title":"Hadith About Farewell Prayer and Guarding Speech","description":"This hadith about praying like a farewell prayer gives three short pieces of advice. A man asked the Prophet صلى الله عليه وسلم to teach him and keep it brief. The Prophet صلى الله عليه وسلم told him that when he stands to pray, he should pray like a man bidding farewell. That makes the prayer feel serious, focused, and present. Then he said not to speak words for which one would have to apologize. This points to careful speech before it leaves the tongue. Finally, he said to give up hope for what other people have. The hadith joins prayer, speech, and inner freedom from people’s possessions. It is concise, but it touches daily worship, daily words, and daily desire."},"teachings":["Prayer should be performed with deep focus, as if it were a farewell prayer.","A believer should avoid speech that later needs apology.","The heart should not be attached to what is in people’s hands.","Brief advice can cover worship, words, and inner attitude."],"related_hadiths":[{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6475","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4141","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E595" s="4" t="n"/>
@@ -14198,7 +14202,7 @@
       </c>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Report Only the Bad","description":"$book_name$ $hadith_number$ - $chapter_name$. A sharp example warns against hearing wisdom but spreading only the worst part."},"heading":{"title":"Hadith About Wisdom and Fair Speech","description":"This hadith about wisdom and fair speech warns against a bad habit. The Prophet صلى الله عليه وسلم described a person who sits and listens to wisdom, but when he speaks about the one he heard from, he mentions only the bad things. The example is striking: a man asks a shepherd for a sheep to slaughter. The shepherd tells him to take the best one, but he grabs the sheepdog instead. The point is clear from the image. Some people hear good and bad, but choose to carry only what is worst. For anyone searching for a hadith about speaking fairly, this narration teaches us not to ignore wisdom while spreading only faults."},"teachings":["A person should not listen to wisdom and then report only bad things.","Fairness in speech means recognizing the good that was heard.","Choosing the worst while leaving the best is blameworthy in this example.","The hadith warns against spreading faults while ignoring benefit."],"related_hadiths":[{"id":"2687","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"6475","book_id":"1","label":"Sahih Bukhari"},{"id":"91a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Report Only the Bad","description":"$book_name$ $hadith_number$ - $chapter_name$. A sharp example warns against hearing wisdom but spreading only the worst part."},"heading":{"title":"Hadith About Wisdom and Fair Speech","description":"This hadith about wisdom and fair speech warns against a bad habit. The Prophet صلى الله عليه وسلم described a person who sits and listens to wisdom, but when he speaks about the one he heard from, he mentions only the bad things. The example is striking: a man asks a shepherd for a sheep to slaughter. The shepherd tells him to take the best one, but he grabs the sheepdog instead. The point is clear from the image. Some people hear good and bad, but choose to carry only what is worst. For anyone searching for a hadith about speaking fairly, this narration teaches us not to ignore wisdom while spreading only faults."},"teachings":["A person should not listen to wisdom and then report only bad things.","Fairness in speech means recognizing the good that was heard.","Choosing the worst while leaving the best is blameworthy in this example.","The hadith warns against spreading faults while ignoring benefit."],"related_hadiths":[{"id":"2687","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"6475","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"91a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E596" s="4" t="n"/>
@@ -14221,7 +14225,7 @@
       </c>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pride and Faith in the Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. A grave warning about pride and a hopeful mention of faith, even the weight of a mustard seed."},"heading":{"title":"Hadith About Pride and Faith the Weight of a Mustard Seed","description":"This hadith about pride and faith puts the heart in front of us. The Prophet صلى الله عليه وسلم said that no one will enter Paradise who has pride in his heart equal to the weight of a mustard seed. He also said that no one will enter Hell who has faith in his heart equal to the weight of a mustard seed. The wording is strong on both sides. Pride is not treated as a small matter, even when it is tiny. Faith is also not ignored, even when it is small. For someone searching for a hadith about pride in Islam, this narration teaches fear of arrogance and hope connected to true faith in the heart."},"teachings":["Even a small amount of pride in the heart is treated as dangerous.","Faith in the heart has great value, even when described as tiny.","A believer should check the inner state, not only outward actions.","The hadith joins warning against pride with hope through faith."],"related_hadiths":[{"id":"91a","book_id":"2","label":"Sahih Muslim"},{"id":"4090","book_id":"4","label":"Sunan Abu Dawud"},{"id":"2865a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pride and Faith in the Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. A grave warning about pride and a hopeful mention of faith, even the weight of a mustard seed."},"heading":{"title":"Hadith About Pride and Faith the Weight of a Mustard Seed","description":"This hadith about pride and faith puts the heart in front of us. The Prophet صلى الله عليه وسلم said that no one will enter Paradise who has pride in his heart equal to the weight of a mustard seed. He also said that no one will enter Hell who has faith in his heart equal to the weight of a mustard seed. The wording is strong on both sides. Pride is not treated as a small matter, even when it is tiny. Faith is also not ignored, even when it is small. For someone searching for a hadith about pride in Islam, this narration teaches fear of arrogance and hope connected to true faith in the heart."},"teachings":["Even a small amount of pride in the heart is treated as dangerous.","Faith in the heart has great value, even when described as tiny.","A believer should check the inner state, not only outward actions.","The hadith joins warning against pride with hope through faith."],"related_hadiths":[{"id":"91a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4090","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"2865a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E597" s="4" t="n"/>
@@ -14244,7 +14248,7 @@
       </c>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pride Belongs to Allah Alone","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah says pride and greatness belong to Him, warning against competing with Him in them."},"heading":{"title":"Hadith Qudsi About Pride: Pride Is Allah’s Cloak","description":"This hadith qudsi about pride is narrated from Abu Hurairah. The Prophet صلى الله عليه وسلم reported that Allah, the Glorified, says: “Pride is My cloak and greatness My robe.” The hadith then warns that whoever competes with Allah regarding either of them will be thrown into Hell. The meaning in the wording is severe and clear. Pride and greatness are not qualities for a servant to claim against Allah. A human being is needy, limited, and owned by Allah. So when a person behaves with arrogance, he is stepping into something that does not belong to him. For searches about arrogance in Islam, this hadith gives one of the strongest warnings in the provided text."},"teachings":["Pride and greatness belong to Allah, as stated in this hadith qudsi.","A servant should not compete with Allah in what belongs to Him.","Arrogance is shown as a path to severe punishment.","The wording teaches humility before Allah’s greatness."],"related_hadiths":[{"id":"4090","book_id":"4","label":"Sunan Abu Dawud"},{"id":"91a","book_id":"2","label":"Sahih Muslim"},{"id":"2865a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pride Belongs to Allah Alone","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah says pride and greatness belong to Him, warning against competing with Him in them."},"heading":{"title":"Hadith Qudsi About Pride: Pride Is Allah’s Cloak","description":"This hadith qudsi about pride is narrated from Abu Hurairah. The Prophet صلى الله عليه وسلم reported that Allah, the Glorified, says: “Pride is My cloak and greatness My robe.” The hadith then warns that whoever competes with Allah regarding either of them will be thrown into Hell. The meaning in the wording is severe and clear. Pride and greatness are not qualities for a servant to claim against Allah. A human being is needy, limited, and owned by Allah. So when a person behaves with arrogance, he is stepping into something that does not belong to him. For searches about arrogance in Islam, this hadith gives one of the strongest warnings in the provided text."},"teachings":["Pride and greatness belong to Allah, as stated in this hadith qudsi.","A servant should not compete with Allah in what belongs to Him.","Arrogance is shown as a path to severe punishment.","The wording teaches humility before Allah’s greatness."],"related_hadiths":[{"id":"4090","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"91a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2865a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E598" s="4" t="n"/>
@@ -14267,7 +14271,7 @@
       </c>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Danger of Competing in Pride","description":"$book_name$ $hadith_number$ - $chapter_name$. A firm reminder that pride and greatness are Allah’s, not traits for humans to claim."},"heading":{"title":"Hadith About Arrogance: Pride and Greatness Are Allah’s","description":"This narration from Ibn Abbas carries the same grave message about pride. The Messenger of Allah صلى الله عليه وسلم said that Allah, the Glorified, says: “Pride is My cloak and greatness My robe.” Whoever competes with Him in either of them will be thrown into the Fire. The hadith is not soft in tone because pride is not a light matter here. It teaches that greatness belongs to Allah, while the servant’s place is humility. A person may own things, hold status, or receive respect, but none of that gives him the right to act arrogantly before Allah. For anyone looking for a hadith about arrogance, this text is a direct warning."},"teachings":["Allah alone has true pride and greatness.","Competing with Allah in pride is warned against with severe wording.","Human status does not justify arrogance.","The hadith calls the servant back to humility before Allah."],"related_hadiths":[{"id":"4090","book_id":"4","label":"Sunan Abu Dawud"},{"id":"91a","book_id":"2","label":"Sahih Muslim"},{"id":"2865a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Danger of Competing in Pride","description":"$book_name$ $hadith_number$ - $chapter_name$. A firm reminder that pride and greatness are Allah’s, not traits for humans to claim."},"heading":{"title":"Hadith About Arrogance: Pride and Greatness Are Allah’s","description":"This narration from Ibn Abbas carries the same grave message about pride. The Messenger of Allah صلى الله عليه وسلم said that Allah, the Glorified, says: “Pride is My cloak and greatness My robe.” Whoever competes with Him in either of them will be thrown into the Fire. The hadith is not soft in tone because pride is not a light matter here. It teaches that greatness belongs to Allah, while the servant’s place is humility. A person may own things, hold status, or receive respect, but none of that gives him the right to act arrogantly before Allah. For anyone looking for a hadith about arrogance, this text is a direct warning."},"teachings":["Allah alone has true pride and greatness.","Competing with Allah in pride is warned against with severe wording.","Human status does not justify arrogance.","The hadith calls the servant back to humility before Allah."],"related_hadiths":[{"id":"4090","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"91a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2865a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E599" s="4" t="n"/>
@@ -14290,7 +14294,7 @@
       </c>
       <c r="D600" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Humility Raises a Person","description":"$book_name$ $hadith_number$ - $chapter_name$. Humility for Allah raises a person, while arrogance lowers him step by step."},"heading":{"title":"Hadith About Humility: Allah Raises the Humble","description":"This hadith about humility explains two opposite paths. The Prophet صلى الله عليه وسلم said that whoever humbles himself one degree for the sake of Allah, Allah will raise him one degree. Whoever behaves arrogantly toward Allah one degree, Allah will lower him one degree, until He makes him among the lowest of the low. The hadith connects humility directly to Allah, not to public praise. A person may look lower in people’s eyes, but if the humility is for Allah, the hadith promises raising in status. Arrogance moves in the other direction. It lowers a person. For people searching for a humility hadith, this narration gives a clear scale: humility raises, arrogance lowers."},"teachings":["Humility for the sake of Allah is linked to being raised in status.","Arrogance toward Allah is linked to being lowered.","The hadith teaches that inner attitude has real consequences.","A believer should choose humility over self-importance."],"related_hadiths":[{"id":"2865a","book_id":"2","label":"Sahih Muslim"},{"id":"91a","book_id":"2","label":"Sahih Muslim"},{"id":"4090","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Humility Raises a Person","description":"$book_name$ $hadith_number$ - $chapter_name$. Humility for Allah raises a person, while arrogance lowers him step by step."},"heading":{"title":"Hadith About Humility: Allah Raises the Humble","description":"This hadith about humility explains two opposite paths. The Prophet صلى الله عليه وسلم said that whoever humbles himself one degree for the sake of Allah, Allah will raise him one degree. Whoever behaves arrogantly toward Allah one degree, Allah will lower him one degree, until He makes him among the lowest of the low. The hadith connects humility directly to Allah, not to public praise. A person may look lower in people’s eyes, but if the humility is for Allah, the hadith promises raising in status. Arrogance moves in the other direction. It lowers a person. For people searching for a humility hadith, this narration gives a clear scale: humility raises, arrogance lowers."},"teachings":["Humility for the sake of Allah is linked to being raised in status.","Arrogance toward Allah is linked to being lowered.","The hadith teaches that inner attitude has real consequences.","A believer should choose humility over self-importance."],"related_hadiths":[{"id":"2865a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"91a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4090","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E600" s="4" t="n"/>
@@ -14313,7 +14317,7 @@
       </c>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Humility in Helping Others","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet’s patience in helping a needy person shows humble service and care."},"heading":{"title":"Hadith About Prophetic Humility and Helping the Needy","description":"This hadith about prophetic humility shows the Messenger of Allah صلى الله عليه وسلم serving someone with very low social status. Anas said that if a female slave from the people of Madinah took the Prophet’s hand, he would not pull his hand away from hers until she had taken him wherever she wanted in Madinah so her need could be met. The narration does not need extra decoration. It shows patience, care, and readiness to help. The Prophet صلى الله عليه وسلم did not act too important to respond to her need. For anyone searching for a hadith about helping others, this report gives a living example of humility: giving time, attention, and help to someone who needs it."},"teachings":["The Prophet صلى الله عليه وسلم showed patience with a person seeking help.","Humble service includes giving time to meet someone’s need.","Social status did not stop the Prophet صلى الله عليه وسلم from helping.","A believer should not be too proud to assist the needy."],"related_hadiths":[{"id":"2865a","book_id":"2","label":"Sahih Muslim"},{"id":"3562","book_id":"1","label":"Sahih Bukhari"},{"id":"91a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophetic Humility in Helping Others","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet’s patience in helping a needy person shows humble service and care."},"heading":{"title":"Hadith About Prophetic Humility and Helping the Needy","description":"This hadith about prophetic humility shows the Messenger of Allah صلى الله عليه وسلم serving someone with very low social status. Anas said that if a female slave from the people of Madinah took the Prophet’s hand, he would not pull his hand away from hers until she had taken him wherever she wanted in Madinah so her need could be met. The narration does not need extra decoration. It shows patience, care, and readiness to help. The Prophet صلى الله عليه وسلم did not act too important to respond to her need. For anyone searching for a hadith about helping others, this report gives a living example of humility: giving time, attention, and help to someone who needs it."},"teachings":["The Prophet صلى الله عليه وسلم showed patience with a person seeking help.","Humble service includes giving time to meet someone’s need.","Social status did not stop the Prophet صلى الله عليه وسلم from helping.","A believer should not be too proud to assist the needy."],"related_hadiths":[{"id":"2865a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"3562","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"91a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E601" s="4" t="n"/>
@@ -14336,7 +14340,7 @@
       </c>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Simple Prophetic Character","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet visited the sick, attended funerals, accepted slave invitations, and rode donkeys."},"heading":{"title":"Hadith About the Prophet’s Humility in Daily Life","description":"This hadith about the Prophet’s humility lists simple actions from his life. Anas said that the Messenger of Allah صلى الله عليه وسلم used to visit the sick, attend funerals, accept the invitations of slaves, and ride donkeys. The narration also mentions that he rode a donkey on the days of Quraizah and Nadir, and on the day of Khaibar he rode a donkey with a bridle and packsaddle made from palm fibers. The point is clear from the details. His honor did not stop him from simple transport, social care, or responding to people of low status. For searches about the humble lifestyle of Prophet Muhammad, this hadith gives practical examples without needing added stories."},"teachings":["The Prophet صلى الله عليه وسلم visited the sick and attended funerals.","He accepted invitations from slaves, showing humility.","He used simple transport without pride.","Care for people was part of his daily character."],"related_hadiths":[{"id":"3562","book_id":"1","label":"Sahih Bukhari"},{"id":"2865a","book_id":"2","label":"Sahih Muslim"},{"id":"91a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Simple Prophetic Character","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet visited the sick, attended funerals, accepted slave invitations, and rode donkeys."},"heading":{"title":"Hadith About the Prophet’s Humility in Daily Life","description":"This hadith about the Prophet’s humility lists simple actions from his life. Anas said that the Messenger of Allah صلى الله عليه وسلم used to visit the sick, attend funerals, accept the invitations of slaves, and ride donkeys. The narration also mentions that he rode a donkey on the days of Quraizah and Nadir, and on the day of Khaibar he rode a donkey with a bridle and packsaddle made from palm fibers. The point is clear from the details. His honor did not stop him from simple transport, social care, or responding to people of low status. For searches about the humble lifestyle of Prophet Muhammad, this hadith gives practical examples without needing added stories."},"teachings":["The Prophet صلى الله عليه وسلم visited the sick and attended funerals.","He accepted invitations from slaves, showing humility.","He used simple transport without pride.","Care for people was part of his daily character."],"related_hadiths":[{"id":"3562","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2865a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"91a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E602" s="4" t="n"/>
@@ -14359,7 +14363,7 @@
       </c>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Be Humble to One Another","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah revealed that people should be humble so no one boasts over another."},"heading":{"title":"Hadith About Humility: Do Not Boast Over Others","description":"This hadith about humility gives a clear social lesson. The Prophet صلى الله عليه وسلم addressed the people and said that Allah revealed to him that they should be humble toward one another so that no one boasts to another. The wording is simple and direct. Humility is not only an inner feeling; it shapes how people treat each other. Boasting creates distance, pride, and a sense of being above others. The hadith tells believers to lower that attitude and deal with one another in a humble way. For anyone searching for an Islamic hadith about humility, this narration is easy to apply: do not use rank, wealth, family, knowledge, or success as a reason to boast over people."},"teachings":["Allah revealed the command to be humble toward one another.","Boasting over others is directly discouraged in the hadith.","Humility should shape social behavior, not only private feelings.","A believer should not act superior to another person."],"related_hadiths":[{"id":"2865a","book_id":"2","label":"Sahih Muslim"},{"id":"91a","book_id":"2","label":"Sahih Muslim"},{"id":"4090","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Be Humble to One Another","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah revealed that people should be humble so no one boasts over another."},"heading":{"title":"Hadith About Humility: Do Not Boast Over Others","description":"This hadith about humility gives a clear social lesson. The Prophet صلى الله عليه وسلم addressed the people and said that Allah revealed to him that they should be humble toward one another so that no one boasts to another. The wording is simple and direct. Humility is not only an inner feeling; it shapes how people treat each other. Boasting creates distance, pride, and a sense of being above others. The hadith tells believers to lower that attitude and deal with one another in a humble way. For anyone searching for an Islamic hadith about humility, this narration is easy to apply: do not use rank, wealth, family, knowledge, or success as a reason to boast over people."},"teachings":["Allah revealed the command to be humble toward one another.","Boasting over others is directly discouraged in the hadith.","Humility should shape social behavior, not only private feelings.","A believer should not act superior to another person."],"related_hadiths":[{"id":"2865a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"91a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4090","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E603" s="4" t="n"/>
@@ -14382,7 +14386,7 @@
       </c>
       <c r="D604" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Modesty","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet’s deep modesty was so clear that dislike could be seen on his face."},"heading":{"title":"Hadith About Modesty: The Prophet’s Shyness and Character","description":"This hadith about modesty describes the character of the Messenger of Allah صلى الله عليه وسلم. Abu Sa’eed Al-Khudri said that the Prophet صلى الله عليه وسلم was more modest than a virgin in her chamber. He also said that when the Prophet صلى الله عليه وسلم disliked something, it could be seen in his face. The report gives two simple signs. First, his modesty was deep and visible. Second, even when he disliked something, the narration points to his face rather than harsh words in this wording. For people searching for a hadith about haya or modesty of Prophet Muhammad, this narration shows that modesty is not weakness. It is a noble manner seen in the Prophet’s presence, reactions, and self-control."},"teachings":["The Prophet صلى الله عليه وسلم had deep and visible modesty.","His dislike of something could be seen in his face.","Modesty is shown as part of noble character.","A believer can dislike something without rushing into harsh speech."],"related_hadiths":[{"id":"3562","book_id":"1","label":"Sahih Bukhari"},{"id":"24","book_id":"1","label":"Sahih Bukhari"},{"id":"36","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Modesty","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet’s deep modesty was so clear that dislike could be seen on his face."},"heading":{"title":"Hadith About Modesty: The Prophet’s Shyness and Character","description":"This hadith about modesty describes the character of the Messenger of Allah صلى الله عليه وسلم. Abu Sa’eed Al-Khudri said that the Prophet صلى الله عليه وسلم was more modest than a virgin in her chamber. He also said that when the Prophet صلى الله عليه وسلم disliked something, it could be seen in his face. The report gives two simple signs. First, his modesty was deep and visible. Second, even when he disliked something, the narration points to his face rather than harsh words in this wording. For people searching for a hadith about haya or modesty of Prophet Muhammad, this narration shows that modesty is not weakness. It is a noble manner seen in the Prophet’s presence, reactions, and self-control."},"teachings":["The Prophet صلى الله عليه وسلم had deep and visible modesty.","His dislike of something could be seen in his face.","Modesty is shown as part of noble character.","A believer can dislike something without rushing into harsh speech."],"related_hadiths":[{"id":"3562","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"24","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"36","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E604" s="4" t="n"/>
@@ -14405,7 +14409,7 @@
       </c>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Haya as Islam’s Distinct Trait","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith highlights modesty as the special character of Islam and a guide for Muslim behavior."},"heading":{"title":"Haya in Islam: Modesty as a Defining Muslim Character","description":"This narration carries the same central message: the distinct characteristic of Islam is modesty. For anyone searching for haya in Islam hadith, this text is direct and easy to understand. The Prophet (صلى الله عليه وسلم) links Islam with modesty in a way that makes it more than a small personal habit. It becomes a mark of faith-based character. The Hadith does not add extra examples, so the explanation should not add details beyond the words given. It teaches that a Muslim’s conduct should have a sense of decency, shame from wrong, and respect. Modesty is not shown as weakness here. It is shown as a special quality connected to the religion itself."},"teachings":["Islam has a distinct character, and that character is modesty.","Haya should shape how a Muslim behaves with others.","Modesty is a valued Islamic quality, not a minor habit.","A believer should avoid behavior that conflicts with decency."],"related_hadiths":[{"id":"35a","book_id":"2","label":"Sahih Muslim"},{"id":"24","book_id":"1","label":"Sahih Bukhari"},{"id":"5006","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Haya as Islam’s Distinct Trait","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith highlights modesty as the special character of Islam and a guide for Muslim behavior."},"heading":{"title":"Haya in Islam: Modesty as a Defining Muslim Character","description":"This narration carries the same central message: the distinct characteristic of Islam is modesty. For anyone searching for haya in Islam hadith, this text is direct and easy to understand. The Prophet (صلى الله عليه وسلم) links Islam with modesty in a way that makes it more than a small personal habit. It becomes a mark of faith-based character. The Hadith does not add extra examples, so the explanation should not add details beyond the words given. It teaches that a Muslim’s conduct should have a sense of decency, shame from wrong, and respect. Modesty is not shown as weakness here. It is shown as a special quality connected to the religion itself."},"teachings":["Islam has a distinct character, and that character is modesty.","Haya should shape how a Muslim behaves with others.","Modesty is a valued Islamic quality, not a minor habit.","A believer should avoid behavior that conflicts with decency."],"related_hadiths":[{"id":"35a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"24","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5006","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E605" s="4" t="n"/>
@@ -14428,7 +14432,7 @@
       </c>
       <c r="D606" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Modesty Is Part of Faith","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith links modesty with faith and warns against obscene speech and harsh behavior."},"heading":{"title":"Modesty Is Part of Faith Hadith: Haya and Clean Speech","description":"This hadith about modesty is part of faith connects inner belief with outward manners. The Prophet (صلى الله عليه وسلم) says modesty is part of faith, and faith will be in Paradise. He also says obscenity in speech is part of harshness, and harshness will be in Hell. The Hadith places two paths side by side. One path is haya, faith, and Paradise. The other is obscene speech, harshness, and Hell. The main lesson is not only about what a person feels inside, but also about how a person speaks. Clean speech and modest conduct are not small matters. They show the direction of a person’s character and the state of his faith."},"teachings":["Modesty is described as part of faith.","Obscene speech is linked with harshness.","A believer should take speech seriously.","Good character is connected to the path of faith."],"related_hadiths":[{"id":"24","book_id":"1","label":"Sahih Bukhari"},{"id":"35a","book_id":"2","label":"Sahih Muslim"},{"id":"5006","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Modesty Is Part of Faith","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith links modesty with faith and warns against obscene speech and harsh behavior."},"heading":{"title":"Modesty Is Part of Faith Hadith: Haya and Clean Speech","description":"This hadith about modesty is part of faith connects inner belief with outward manners. The Prophet (صلى الله عليه وسلم) says modesty is part of faith, and faith will be in Paradise. He also says obscenity in speech is part of harshness, and harshness will be in Hell. The Hadith places two paths side by side. One path is haya, faith, and Paradise. The other is obscene speech, harshness, and Hell. The main lesson is not only about what a person feels inside, but also about how a person speaks. Clean speech and modest conduct are not small matters. They show the direction of a person’s character and the state of his faith."},"teachings":["Modesty is described as part of faith.","Obscene speech is linked with harshness.","A believer should take speech seriously.","Good character is connected to the path of faith."],"related_hadiths":[{"id":"24","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"35a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"5006","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E606" s="4" t="n"/>
@@ -14451,7 +14455,7 @@
       </c>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Modesty Adorns Every Matter","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that obscenity harms a matter, while modesty beautifies it."},"heading":{"title":"Hadith About Modesty and Obscenity: Haya Beautifies What It Touches","description":"This hadith about modesty and obscenity uses simple words that are easy to remember. The Prophet (صلى الله عليه وسلم) says that whenever obscenity is found in something, it mars it, and whenever modesty is found in something, it adorns it. The key search phrase is modesty adorns hadith. The Hadith does not limit the lesson to speech only, although obscenity often appears in words. It gives a wider rule: foulness damages, while haya brings beauty. This can apply to conduct, tone, and the way a person deals with others, as long as we stay within the Hadith’s wording. It teaches that modesty makes a matter better, calmer, and more pleasing."},"teachings":["Obscenity mars whatever it enters.","Modesty adorns whatever it enters.","A believer should avoid foul behavior and indecent words.","Haya brings beauty to conduct and interaction."],"related_hadiths":[{"id":"6117","book_id":"1","label":"Sahih Bukhari"},{"id":"24","book_id":"1","label":"Sahih Bukhari"},{"id":"35a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Modesty Adorns Every Matter","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that obscenity harms a matter, while modesty beautifies it."},"heading":{"title":"Hadith About Modesty and Obscenity: Haya Beautifies What It Touches","description":"This hadith about modesty and obscenity uses simple words that are easy to remember. The Prophet (صلى الله عليه وسلم) says that whenever obscenity is found in something, it mars it, and whenever modesty is found in something, it adorns it. The key search phrase is modesty adorns hadith. The Hadith does not limit the lesson to speech only, although obscenity often appears in words. It gives a wider rule: foulness damages, while haya brings beauty. This can apply to conduct, tone, and the way a person deals with others, as long as we stay within the Hadith’s wording. It teaches that modesty makes a matter better, calmer, and more pleasing."},"teachings":["Obscenity mars whatever it enters.","Modesty adorns whatever it enters.","A believer should avoid foul behavior and indecent words.","Haya brings beauty to conduct and interaction."],"related_hadiths":[{"id":"6117","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"24","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"35a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E607" s="4" t="n"/>
@@ -14474,7 +14478,7 @@
       </c>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward for Restraining Anger","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows the great reward for restraining anger when one has the power to act on it."},"heading":{"title":"Hadith About Controlling Anger: Restraining Anger When You Can Act","description":"This hadith about controlling anger focuses on a hard moment: a person is angry and has the ability to act on that anger. The Prophet (صلى الله عليه وسلم) says that whoever restrains his anger in that state will be called by Allah before all creation on the Day of Resurrection and given his choice of any houri he wants. The Hadith is very specific. It is not only about being calm when one is weak. It praises the person who has the power to respond but holds back. This makes anger control a matter of self-restraint and trust in Allah’s reward. The lesson is clear: holding anger for Allah is not wasted."},"teachings":["Restraining anger is praised when a person is able to act on it.","Self-control in anger is tied to reward from Allah.","Power should not be used to follow every angry feeling.","A believer should pause before turning anger into action."],"related_hadiths":[{"id":"6114","book_id":"1","label":"Sahih Bukhari"},{"id":"2609","book_id":"2","label":"Sahih Muslim"},{"id":"4189","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward for Restraining Anger","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows the great reward for restraining anger when one has the power to act on it."},"heading":{"title":"Hadith About Controlling Anger: Restraining Anger When You Can Act","description":"This hadith about controlling anger focuses on a hard moment: a person is angry and has the ability to act on that anger. The Prophet (صلى الله عليه وسلم) says that whoever restrains his anger in that state will be called by Allah before all creation on the Day of Resurrection and given his choice of any houri he wants. The Hadith is very specific. It is not only about being calm when one is weak. It praises the person who has the power to respond but holds back. This makes anger control a matter of self-restraint and trust in Allah’s reward. The lesson is clear: holding anger for Allah is not wasted."},"teachings":["Restraining anger is praised when a person is able to act on it.","Self-control in anger is tied to reward from Allah.","Power should not be used to follow every angry feeling.","A believer should pause before turning anger into action."],"related_hadiths":[{"id":"6114","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2609","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4189","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E608" s="4" t="n"/>
@@ -14497,7 +14501,7 @@
       </c>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hold Firm to the Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. A powerful advice to fear Allah, obey rightful leadership, follow the Sunnah, and avoid innovation."},"heading":{"title":"Hadith About Following the Sunnah in Times of Conflict","description":"This Hadith is a well-known hadith about following the Sunnah, especially when people face conflict and disagreement. The Prophet gave a moving reminder that made the hearts soft and the eyes tearful. When the companions asked for final advice, he urged them to fear Allah, listen and obey, and hold tightly to his Sunnah and the path of the Rightly-Guided Caliphs. The Hadith also warns against newly-invented matters in religion, calling every innovation a going astray. The message is practical and direct: when confusion appears, the safe path is to stay close to the Prophetic way and avoid religious changes that are not from it."},"teachings":["Taqwa is the first foundation of religious guidance.","The Sunnah is a path to hold firmly during conflict.","The path of the Rightly-Guided Caliphs is linked to Prophetic guidance.","Newly-invented matters in religion are warned against in this narration."],"related_hadiths":[{"id":"5","book_id":"6","label":"Sunan Ibn Majah"},{"id":"7","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hold Firm to the Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. A powerful advice to fear Allah, obey rightful leadership, follow the Sunnah, and avoid innovation."},"heading":{"title":"Hadith About Following the Sunnah in Times of Conflict","description":"This Hadith is a well-known hadith about following the Sunnah, especially when people face conflict and disagreement. The Prophet gave a moving reminder that made the hearts soft and the eyes tearful. When the companions asked for final advice, he urged them to fear Allah, listen and obey, and hold tightly to his Sunnah and the path of the Rightly-Guided Caliphs. The Hadith also warns against newly-invented matters in religion, calling every innovation a going astray. The message is practical and direct: when confusion appears, the safe path is to stay close to the Prophetic way and avoid religious changes that are not from it."},"teachings":["Taqwa is the first foundation of religious guidance.","The Sunnah is a path to hold firmly during conflict.","The path of the Rightly-Guided Caliphs is linked to Prophetic guidance.","Newly-invented matters in religion are warned against in this narration."],"related_hadiths":[{"id":"5","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"7","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E609" s="4" t="n"/>
@@ -14520,7 +14524,7 @@
       </c>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sincerity in Deeds for Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah accepts deeds done for Him alone and rejects actions mixed with seeking another’s share."},"heading":{"title":"Hadith About Sincerity in Deeds and Avoiding Shirk","description":"This Hadith Qudsi focuses on sincerity in Islam. Allah says that He is free of any need for a partner. If someone does an action for Allah but also includes someone else as a partner in that action, Allah leaves that action to the one who was associated with Him. The lesson is simple: worship and good deeds should be for Allah alone. The Hadith does not speak about the size of the deed; it speaks about the direction of the heart. A small act done only for Allah is cleaner than an act mixed with showing off or pleasing others in worship. Searchers often look for “hadith about sincerity,” “riya hadith,” and “actions for Allah alone.” This Hadith answers that need with a direct warning."},"teachings":["Actions done for Allah should not be mixed with seeking others.","Allah has no need for any partner in worship.","Sincerity is tied to the acceptance of deeds.","Check the intention behind every act of worship."],"related_hadiths":[{"id":"2985","book_id":"2","label":"Sahih Muslim"},{"id":"1","book_id":"1","label":"Sahih Bukhari"},{"id":"1907","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sincerity in Deeds for Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah accepts deeds done for Him alone and rejects actions mixed with seeking another’s share."},"heading":{"title":"Hadith About Sincerity in Deeds and Avoiding Shirk","description":"This Hadith Qudsi focuses on sincerity in Islam. Allah says that He is free of any need for a partner. If someone does an action for Allah but also includes someone else as a partner in that action, Allah leaves that action to the one who was associated with Him. The lesson is simple: worship and good deeds should be for Allah alone. The Hadith does not speak about the size of the deed; it speaks about the direction of the heart. A small act done only for Allah is cleaner than an act mixed with showing off or pleasing others in worship. Searchers often look for “hadith about sincerity,” “riya hadith,” and “actions for Allah alone.” This Hadith answers that need with a direct warning."},"teachings":["Actions done for Allah should not be mixed with seeking others.","Allah has no need for any partner in worship.","Sincerity is tied to the acceptance of deeds.","Check the intention behind every act of worship."],"related_hadiths":[{"id":"2985","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1907","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E610" s="4" t="n"/>
@@ -14543,7 +14547,7 @@
       </c>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Reward Only from Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. On the Day of Resurrection, mixed intentions are exposed and reward is sought from other than Allah."},"heading":{"title":"Hadith About Seeking Reward from Allah Alone","description":"This Hadith gives a serious scene from the Day of Resurrection. When Allah gathers the first and the last, a caller will announce that whoever associated anyone else in an action done for Allah should seek his reward from someone other than Allah. The reason is stated clearly: Allah has no need of any associate. The core topic is sincerity, especially doing deeds for Allah alone. This is closely linked to search terms like “hadith about riya,” “reward from Allah hadith,” and “Day of Judgment sincerity hadith.” The Hadith warns that actions are not only judged by their outer form. The purpose behind them matters. A believer should therefore protect his intention before, during, and after every good deed."},"teachings":["Good deeds should be done for Allah, not for shared motives.","The Day of Resurrection will make hidden intentions known.","Reward should be sought from Allah alone.","Associating others in deeds done for Allah is a serious danger."],"related_hadiths":[{"id":"2985","book_id":"2","label":"Sahih Muslim"},{"id":"6499","book_id":"1","label":"Sahih Bukhari"},{"id":"2987","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Reward Only from Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. On the Day of Resurrection, mixed intentions are exposed and reward is sought from other than Allah."},"heading":{"title":"Hadith About Seeking Reward from Allah Alone","description":"This Hadith gives a serious scene from the Day of Resurrection. When Allah gathers the first and the last, a caller will announce that whoever associated anyone else in an action done for Allah should seek his reward from someone other than Allah. The reason is stated clearly: Allah has no need of any associate. The core topic is sincerity, especially doing deeds for Allah alone. This is closely linked to search terms like “hadith about riya,” “reward from Allah hadith,” and “Day of Judgment sincerity hadith.” The Hadith warns that actions are not only judged by their outer form. The purpose behind them matters. A believer should therefore protect his intention before, during, and after every good deed."},"teachings":["Good deeds should be done for Allah, not for shared motives.","The Day of Resurrection will make hidden intentions known.","Reward should be sought from Allah alone.","Associating others in deeds done for Allah is a serious danger."],"related_hadiths":[{"id":"2985","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"6499","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2987","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E611" s="4" t="n"/>
@@ -14566,7 +14570,7 @@
       </c>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Showing Off and Seeking Fame","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever seeks to be heard or seen for display risks having true motives made known by Allah."},"heading":{"title":"Hadith About Showing Off and Wanting to Be Seen","description":"This Hadith warns against doing acts for reputation. The Prophet صلى الله عليه وسلم said that whoever wants to be heard of, Allah will make him heard of, and whoever wants to be seen, Allah will show him. The translation explains this as Allah making known the person’s true motives and intentions. The core topic is showing off, also known as riya. People often search for “showing off hadith,” “riya hadith,” and “seeking fame in Islam.” This Hadith speaks to anyone who wants religious actions to become a personal image. It teaches that the heart behind an action is not hidden from Allah. Instead of chasing praise, a believer should seek Allah’s acceptance and keep good deeds clean from display."},"teachings":["Seeking reputation through deeds is spiritually dangerous.","Allah can make hidden motives known.","Good actions should not become tools for self-display.","Protecting intention is part of protecting worship."],"related_hadiths":[{"id":"6499","book_id":"1","label":"Sahih Bukhari"},{"id":"2987","book_id":"2","label":"Sahih Muslim"},{"id":"1","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Showing Off and Seeking Fame","description":"$book_name$ $hadith_number$ - $chapter_name$. Whoever seeks to be heard or seen for display risks having true motives made known by Allah."},"heading":{"title":"Hadith About Showing Off and Wanting to Be Seen","description":"This Hadith warns against doing acts for reputation. The Prophet صلى الله عليه وسلم said that whoever wants to be heard of, Allah will make him heard of, and whoever wants to be seen, Allah will show him. The translation explains this as Allah making known the person’s true motives and intentions. The core topic is showing off, also known as riya. People often search for “showing off hadith,” “riya hadith,” and “seeking fame in Islam.” This Hadith speaks to anyone who wants religious actions to become a personal image. It teaches that the heart behind an action is not hidden from Allah. Instead of chasing praise, a believer should seek Allah’s acceptance and keep good deeds clean from display."},"teachings":["Seeking reputation through deeds is spiritually dangerous.","Allah can make hidden motives known.","Good actions should not become tools for self-display.","Protecting intention is part of protecting worship."],"related_hadiths":[{"id":"6499","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2987","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E612" s="4" t="n"/>
@@ -14589,7 +14593,7 @@
       </c>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Guarding Against Waswas in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns against waswas in wudu and teaches calm, careful use of water without doubt."},"heading":{"title":"Hadith About Waswas in Wudu and Water Doubts","description":"This Hadith focuses on waswas in wudu, especially doubts linked to water. The Prophet said that there is a devil for ablution called Walahan, and he told believers to be on guard against insinuating thoughts about water. The message is simple: wudu should not become a place of stress, repeated doubt, or overthinking. A person should perform ablution carefully, but not allow whispers to push them into confusion. The Hadith does not give a long ruling list; it gives a warning and a practical mindset. Be alert, stay calm, and do not let water-related doubts disturb your worship."},"teachings":["Waswas can affect a person during ablution, especially through doubts about water.","A believer should be alert and careful without becoming trapped in repeated doubt.","Wudu should be done with calm attention, not with anxiety or endless repetition.","The Hadith warns against letting whispers disturb a simple act of worship."],"related_hadiths":[{"id":"162","book_id":"1","label":"Sahih Bukhari"},{"id":"3295","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Guarding Against Waswas in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns against waswas in wudu and teaches calm, careful use of water without doubt."},"heading":{"title":"Hadith About Waswas in Wudu and Water Doubts","description":"This Hadith focuses on waswas in wudu, especially doubts linked to water. The Prophet said that there is a devil for ablution called Walahan, and he told believers to be on guard against insinuating thoughts about water. The message is simple: wudu should not become a place of stress, repeated doubt, or overthinking. A person should perform ablution carefully, but not allow whispers to push them into confusion. The Hadith does not give a long ruling list; it gives a warning and a practical mindset. Be alert, stay calm, and do not let water-related doubts disturb your worship."},"teachings":["Waswas can affect a person during ablution, especially through doubts about water.","A believer should be alert and careful without becoming trapped in repeated doubt.","Wudu should be done with calm attention, not with anxiety or endless repetition.","The Hadith warns against letting whispers disturb a simple act of worship."],"related_hadiths":[{"id":"162","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3295","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E613" s="4" t="n"/>
@@ -14612,7 +14616,7 @@
       </c>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Brief Ablution of the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows the Prophet performing a brief wudu and Ibn Abbas following his example."},"heading":{"title":"Brief Wudu Hadith and Following the Sunnah","description":"This Hadith shows a simple scene from the life of the Prophet. Ibn Abbas stayed overnight at the home of his maternal aunt Maimunah. The Prophet got up and performed ablution from an old water skin, and the narration says he did a brief ablution. Then Ibn Abbas got up and did the same as the Prophet had done. The core teaching is brief wudu and following the Sunnah. The Hadith does not describe every step in detail, so the explanation should stay close to the text: the Prophet used available water, performed a light form of ablution, and Ibn Abbas copied what he saw."},"teachings":["The Prophet performed ablution using the available water vessel.","The narration shows that wudu may be done briefly when performed properly.","Ibn Abbas learned by watching and following the Prophet’s action.","Good learning can happen through direct observation of the Sunnah."],"related_hadiths":[{"id":"157","book_id":"1","label":"Sahih Bukhari"},{"id":"158","book_id":"1","label":"Sahih Bukhari"},{"id":"418","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Brief Ablution of the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows the Prophet performing a brief wudu and Ibn Abbas following his example."},"heading":{"title":"Brief Wudu Hadith and Following the Sunnah","description":"This Hadith shows a simple scene from the life of the Prophet. Ibn Abbas stayed overnight at the home of his maternal aunt Maimunah. The Prophet got up and performed ablution from an old water skin, and the narration says he did a brief ablution. Then Ibn Abbas got up and did the same as the Prophet had done. The core teaching is brief wudu and following the Sunnah. The Hadith does not describe every step in detail, so the explanation should stay close to the text: the Prophet used available water, performed a light form of ablution, and Ibn Abbas copied what he saw."},"teachings":["The Prophet performed ablution using the available water vessel.","The narration shows that wudu may be done briefly when performed properly.","Ibn Abbas learned by watching and following the Prophet’s action.","Good learning can happen through direct observation of the Sunnah."],"related_hadiths":[{"id":"157","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"158","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"418","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E614" s="4" t="n"/>
@@ -14635,7 +14639,7 @@
       </c>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoid Extravagance in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns against extravagance in wudu and reminds believers to avoid wasting water."},"heading":{"title":"Hadith About Avoiding Extravagance in Wudu","description":"This Hadith is short, but its message is direct. Ibn Umar narrated that the Messenger of Allah saw a man performing ablution and said, Do not be extravagant, do not be extravagant. The focus is avoiding extravagance in wudu. The narration does not list the exact amount of water used or the man’s full action, so the explanation should not add extra details. What it clearly teaches is that even during a good act like ablution, a person should not go beyond proper limits in water use. The note in the input says Maudu, so this should be treated carefully when using it for content."},"teachings":["The narration warns against extravagance while performing ablution.","Water use in worship should be careful and measured.","Repeating the warning shows that wastefulness is not a light matter in the text.","The input labels this narration Maudu, so it should be presented with care."],"related_hadiths":[{"id":"201","book_id":"1","label":"Sahih Bukhari"},{"id":"92","book_id":"4","label":"Sunan Abu Dawud"},{"id":"140","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoid Extravagance in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith warns against extravagance in wudu and reminds believers to avoid wasting water."},"heading":{"title":"Hadith About Avoiding Extravagance in Wudu","description":"This Hadith is short, but its message is direct. Ibn Umar narrated that the Messenger of Allah saw a man performing ablution and said, Do not be extravagant, do not be extravagant. The focus is avoiding extravagance in wudu. The narration does not list the exact amount of water used or the man’s full action, so the explanation should not add extra details. What it clearly teaches is that even during a good act like ablution, a person should not go beyond proper limits in water use. The note in the input says Maudu, so this should be treated carefully when using it for content."},"teachings":["The narration warns against extravagance while performing ablution.","Water use in worship should be careful and measured.","Repeating the warning shows that wastefulness is not a light matter in the text.","The input labels this narration Maudu, so it should be presented with care."],"related_hadiths":[{"id":"201","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"92","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"140","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E615" s="4" t="n"/>
@@ -14658,7 +14662,7 @@
       </c>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hope and Fear at Death","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how hope in Allah and fear of sins can meet in a dying believer’s heart, bringing comfort at life’s final moment."},"heading":{"title":"Hadith About Hope and Fear in Allah at the Time of Death","description":"This hadith about hope and fear in Allah shows a dying young man speaking with honest faith. When the Prophet asked how he felt, the young man did not claim to be perfect. He said he hoped in Allah, yet feared his sins. The teaching is clear: at a moment like death, a servant’s heart may hold both trust in Allah’s mercy and worry over personal sins. The Prophet then gave glad news about that state. Allah gives what the person hopes for and grants safety from what he fears. The core message is balanced faith. A believer should not fall into despair, and should not treat sins lightly either."},"teachings":["A believer may hold hope in Allah and fear of sins at the same time.","Being honest about one’s sins is part of a serious heart.","At the time of death, balanced hope and fear are praised in this narration."],"related_hadiths":[{"id":"6508","book_id":"1","label":"Sahih Bukhari"},{"id":"7405","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hope and Fear at Death","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how hope in Allah and fear of sins can meet in a dying believer’s heart, bringing comfort at life’s final moment."},"heading":{"title":"Hadith About Hope and Fear in Allah at the Time of Death","description":"This hadith about hope and fear in Allah shows a dying young man speaking with honest faith. When the Prophet asked how he felt, the young man did not claim to be perfect. He said he hoped in Allah, yet feared his sins. The teaching is clear: at a moment like death, a servant’s heart may hold both trust in Allah’s mercy and worry over personal sins. The Prophet then gave glad news about that state. Allah gives what the person hopes for and grants safety from what he fears. The core message is balanced faith. A believer should not fall into despair, and should not treat sins lightly either."},"teachings":["A believer may hold hope in Allah and fear of sins at the same time.","Being honest about one’s sins is part of a serious heart.","At the time of death, balanced hope and fear are praised in this narration."],"related_hadiths":[{"id":"6508","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"7405","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E616" s="4" t="n"/>
@@ -14681,7 +14685,7 @@
       </c>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Good Soul and Evil Soul","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear reminder that the dying soul is met with glad tidings or warning, showing the weight of righteousness and evil."},"heading":{"title":"Hadith About the Good Soul and Evil Soul at Death","description":"This hadith about the soul after death gives a strong picture of what happens to the dying person. The righteous man is addressed as a good soul that was in a good body. He is called out with praise and is given glad tidings of mercy, fragrance, and a Lord Who is not angry. The evil man is addressed in a very different way, as an evil soul in an evil body, and is warned of punishment. The hadith keeps the focus on two states: righteousness and evil. It teaches that death is not only the end of worldly life. It is also the start of meeting results linked to one’s inner and outer state."},"teachings":["Righteousness is linked with the good soul and good body in this narration.","The evil soul is warned and returned in a blameworthy state.","The moment of death is shown as a serious change, not a small event."],"related_hadiths":[{"id":"1379","book_id":"1","label":"Sahih Bukhari"},{"id":"1369","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Good Soul and Evil Soul","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear reminder that the dying soul is met with glad tidings or warning, showing the weight of righteousness and evil."},"heading":{"title":"Hadith About the Good Soul and Evil Soul at Death","description":"This hadith about the soul after death gives a strong picture of what happens to the dying person. The righteous man is addressed as a good soul that was in a good body. He is called out with praise and is given glad tidings of mercy, fragrance, and a Lord Who is not angry. The evil man is addressed in a very different way, as an evil soul in an evil body, and is warned of punishment. The hadith keeps the focus on two states: righteousness and evil. It teaches that death is not only the end of worldly life. It is also the start of meeting results linked to one’s inner and outer state."},"teachings":["Righteousness is linked with the good soul and good body in this narration.","The evil soul is warned and returned in a blameworthy state.","The moment of death is shown as a serious change, not a small event."],"related_hadiths":[{"id":"1379","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1369","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E617" s="4" t="n"/>
@@ -14704,7 +14708,7 @@
       </c>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Death in a Decreed Land","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that death comes by Allah’s decree, even when a need takes a person to the place appointed for him."},"heading":{"title":"Hadith About Death in a Decreed Land and Allah’s Plan","description":"This hadith about death in a decreed land teaches that a person’s final place is not random. The Prophet said that when someone’s appointed time of death is in a certain land, a need will cause him to go there. When he reaches the furthest point decreed for him, Allah takes his soul. The hadith also says that on the Day of Resurrection, the earth will speak and say that this person was entrusted to it. The meaning is simple and serious: life moves under Allah’s decree. People make journeys for needs, but the final point belongs to Allah’s knowledge and command. This should bring humility, not carelessness."},"teachings":["The time and place of death are under Allah’s decree.","A normal need may lead a person to the place appointed for his death.","The earth is described as holding what Allah entrusted to it until Resurrection."],"related_hadiths":[{"id":"2146","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"2147","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Death in a Decreed Land","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that death comes by Allah’s decree, even when a need takes a person to the place appointed for him."},"heading":{"title":"Hadith About Death in a Decreed Land and Allah’s Plan","description":"This hadith about death in a decreed land teaches that a person’s final place is not random. The Prophet said that when someone’s appointed time of death is in a certain land, a need will cause him to go there. When he reaches the furthest point decreed for him, Allah takes his soul. The hadith also says that on the Day of Resurrection, the earth will speak and say that this person was entrusted to it. The meaning is simple and serious: life moves under Allah’s decree. People make journeys for needs, but the final point belongs to Allah’s knowledge and command. This should bring humility, not carelessness."},"teachings":["The time and place of death are under Allah’s decree.","A normal need may lead a person to the place appointed for his death.","The earth is described as holding what Allah entrusted to it until Resurrection."],"related_hadiths":[{"id":"2146","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"2147","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E618" s="4" t="n"/>
@@ -14727,7 +14731,7 @@
       </c>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Loving to Meet Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. Understand the hadith on loving to meet Allah, where glad tidings at death shape a believer’s longing and response."},"heading":{"title":"Whoever Loves to Meet Allah: Hadith Meaning and Core Lesson","description":"This hadith about loving to meet Allah explains an important point with care. The Prophet said that whoever loves to meet Allah, Allah loves to meet him, and whoever hates to meet Allah, Allah hates to meet him. When it was asked whether this means simply hating death, the Prophet said no. He explained that it is about the moment of death. If a person is given glad tidings of Allah’s mercy and forgiveness, he loves to meet Allah. If he is given tidings of Allah’s punishment, he hates that meeting. So the hadith is not saying that natural fear of death itself is blameworthy. It is speaking about the final news given at death."},"teachings":["Hating death is not the same as hating to meet Allah in this hadith.","Glad tidings of mercy and forgiveness make the meeting beloved.","Tidings of punishment bring fear and dislike at the moment of death."],"related_hadiths":[{"id":"6508","book_id":"1","label":"Sahih Bukhari"},{"id":"2683a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Loving to Meet Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. Understand the hadith on loving to meet Allah, where glad tidings at death shape a believer’s longing and response."},"heading":{"title":"Whoever Loves to Meet Allah: Hadith Meaning and Core Lesson","description":"This hadith about loving to meet Allah explains an important point with care. The Prophet said that whoever loves to meet Allah, Allah loves to meet him, and whoever hates to meet Allah, Allah hates to meet him. When it was asked whether this means simply hating death, the Prophet said no. He explained that it is about the moment of death. If a person is given glad tidings of Allah’s mercy and forgiveness, he loves to meet Allah. If he is given tidings of Allah’s punishment, he hates that meeting. So the hadith is not saying that natural fear of death itself is blameworthy. It is speaking about the final news given at death."},"teachings":["Hating death is not the same as hating to meet Allah in this hadith.","Glad tidings of mercy and forgiveness make the meeting beloved.","Tidings of punishment bring fear and dislike at the moment of death."],"related_hadiths":[{"id":"6508","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2683a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E619" s="4" t="n"/>
@@ -14750,7 +14754,7 @@
       </c>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Coccyx and Resurrection","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith points to bodily decay and recreation on the Day of Resurrection from the bone at the base of the coccyx."},"heading":{"title":"Hadith About the Coccyx Bone and Resurrection","description":"This hadith about the coccyx bone and resurrection teaches that the human body will decay after death, except one bone at the base of the coccyx. The Prophet said that from it the creation will be put together again on the Day of Resurrection. The hadith is short, but it gives a clear link between death, bodily disintegration, and being recreated. Its focus is not on medical detail or debate. It teaches belief in resurrection through a concrete sign mentioned in the text. A believer reading this hadith is reminded that the body may return to dust, but Allah’s power is not limited by decay. The final return remains real."},"teachings":["The body decays after death except the bone mentioned in the hadith.","The hadith links that bone to recreation on the Day of Resurrection.","Death and bodily decay do not cancel the reality of being raised again."],"related_hadiths":[{"id":"4935","book_id":"1","label":"Sahih Bukhari"},{"id":"2955a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Coccyx and Resurrection","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith points to bodily decay and recreation on the Day of Resurrection from the bone at the base of the coccyx."},"heading":{"title":"Hadith About the Coccyx Bone and Resurrection","description":"This hadith about the coccyx bone and resurrection teaches that the human body will decay after death, except one bone at the base of the coccyx. The Prophet said that from it the creation will be put together again on the Day of Resurrection. The hadith is short, but it gives a clear link between death, bodily disintegration, and being recreated. Its focus is not on medical detail or debate. It teaches belief in resurrection through a concrete sign mentioned in the text. A believer reading this hadith is reminded that the body may return to dust, but Allah’s power is not limited by decay. The final return remains real."},"teachings":["The body decays after death except the bone mentioned in the hadith.","The hadith links that bone to recreation on the Day of Resurrection.","Death and bodily decay do not cancel the reality of being raised again."],"related_hadiths":[{"id":"4935","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2955a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E620" s="4" t="n"/>
@@ -14773,7 +14777,7 @@
       </c>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Grave as First Stage","description":"$book_name$ $hadith_number$ - $chapter_name$. A sober reminder that the grave is the first stage of the Hereafter, making preparation for death deeply personal."},"heading":{"title":"The Grave Is the First Stage of the Hereafter Hadith","description":"This hadith about the grave as the first stage of the Hereafter shows why Uthman wept when standing by a grave. He explained that the Prophet said the grave is the first stage of the Hereafter. If a person is delivered from it, what comes after it is easier. If he is not delivered from it, what comes after is harder. The narration also states that the Prophet had not seen any horrible scene except that the grave was more horrible. The lesson stays focused on the grave and its seriousness. It is not meant to create empty fear. It pushes the heart to remember death, prepare for the Hereafter, and take the first stage seriously."},"teachings":["The grave is described as the first stage of the Hereafter.","Being delivered from the grave is linked with what comes after being easier.","Remembering the grave can move the heart toward serious preparation."],"related_hadiths":[{"id":"2308","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1379","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Grave as First Stage","description":"$book_name$ $hadith_number$ - $chapter_name$. A sober reminder that the grave is the first stage of the Hereafter, making preparation for death deeply personal."},"heading":{"title":"The Grave Is the First Stage of the Hereafter Hadith","description":"This hadith about the grave as the first stage of the Hereafter shows why Uthman wept when standing by a grave. He explained that the Prophet said the grave is the first stage of the Hereafter. If a person is delivered from it, what comes after it is easier. If he is not delivered from it, what comes after is harder. The narration also states that the Prophet had not seen any horrible scene except that the grave was more horrible. The lesson stays focused on the grave and its seriousness. It is not meant to create empty fear. It pushes the heart to remember death, prepare for the Hereafter, and take the first stage seriously."},"teachings":["The grave is described as the first stage of the Hereafter.","Being delivered from the grave is linked with what comes after being easier.","Remembering the grave can move the heart toward serious preparation."],"related_hadiths":[{"id":"2308","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1379","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E621" s="4" t="n"/>
@@ -14796,7 +14800,7 @@
       </c>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Questions in the Grave","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration explains the grave questioning, certain faith, doubt, and the shown places of Paradise and Hell."},"heading":{"title":"Questions in the Grave Hadith: Faith, Certainty, and Doubt","description":"This hadith about questions in the grave shows two very different responses. The righteous man sits without fear or panic. He says he was in Islam and identifies Muhammad as the Messenger of Allah who brought clear signs from Allah. He is shown what Allah saved him from and then shown his place in Paradise. The evil man sits with fear and panic. He says he does not know and only repeated what people said. He is shown what was diverted away from him and then shown his place in Hell. The main lesson is about certainty and doubt. Faith is not shown as a slogan only; it is tied to belief in the Messenger and the clear signs from Allah."},"teachings":["The righteous person answers with Islam and belief in Muhammad, the Messenger of Allah.","The evil person is shown as uncertain and only repeating what people said.","The grave is a place where certainty and doubt become deeply serious."],"related_hadiths":[{"id":"1369","book_id":"1","label":"Sahih Bukhari"},{"id":"4699","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Questions in the Grave","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration explains the grave questioning, certain faith, doubt, and the shown places of Paradise and Hell."},"heading":{"title":"Questions in the Grave Hadith: Faith, Certainty, and Doubt","description":"This hadith about questions in the grave shows two very different responses. The righteous man sits without fear or panic. He says he was in Islam and identifies Muhammad as the Messenger of Allah who brought clear signs from Allah. He is shown what Allah saved him from and then shown his place in Paradise. The evil man sits with fear and panic. He says he does not know and only repeated what people said. He is shown what was diverted away from him and then shown his place in Hell. The main lesson is about certainty and doubt. Faith is not shown as a slogan only; it is tied to belief in the Messenger and the clear signs from Allah."},"teachings":["The righteous person answers with Islam and belief in Muhammad, the Messenger of Allah.","The evil person is shown as uncertain and only repeating what people said.","The grave is a place where certainty and doubt become deeply serious."],"related_hadiths":[{"id":"1369","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4699","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E622" s="4" t="n"/>
@@ -14819,7 +14823,7 @@
       </c>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shown the Final Place","description":"$book_name$ $hadith_number$ - $chapter_name$. After death, a person is shown his place morning and evening until being raised on the Day of Resurrection."},"heading":{"title":"Hadith About Being Shown Your Place After Death","description":"This hadith about being shown one’s place after death teaches that the deceased is shown his seat morning and evening. If he is among the people of Paradise, he is shown a place in Paradise. If he is among the people of Hell, he is shown a place in Hell. The statement ends with the words that this is his place until he is raised on the Day of Resurrection. The focus of the narration is the period after death and before the final resurrection. It reminds the reader that the Hereafter is not a distant idea only. After death, the person begins to face a reality connected to his final end."},"teachings":["After death, the person is shown his place morning and evening.","The place shown depends on whether he is among the people of Paradise or Hell.","This continues until the person is raised on the Day of Resurrection."],"related_hadiths":[{"id":"1379","book_id":"1","label":"Sahih Bukhari"},{"id":"3240","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shown the Final Place","description":"$book_name$ $hadith_number$ - $chapter_name$. After death, a person is shown his place morning and evening until being raised on the Day of Resurrection."},"heading":{"title":"Hadith About Being Shown Your Place After Death","description":"This hadith about being shown one’s place after death teaches that the deceased is shown his seat morning and evening. If he is among the people of Paradise, he is shown a place in Paradise. If he is among the people of Hell, he is shown a place in Hell. The statement ends with the words that this is his place until he is raised on the Day of Resurrection. The focus of the narration is the period after death and before the final resurrection. It reminds the reader that the Hereafter is not a distant idea only. After death, the person begins to face a reality connected to his final end."},"teachings":["After death, the person is shown his place morning and evening.","The place shown depends on whether he is among the people of Paradise or Hell.","This continues until the person is raised on the Day of Resurrection."],"related_hadiths":[{"id":"1379","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3240","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E623" s="4" t="n"/>
@@ -14842,7 +14846,7 @@
       </c>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Believer’s Soul in Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. The believer’s soul is described as a bird eating from Paradise until it returns to the body on Resurrection Day."},"heading":{"title":"Hadith About the Believer’s Soul as a Bird in Paradise","description":"This hadith about the believer’s soul gives a beautiful and simple image. The Prophet said that the believer’s soul is a bird that eats from the trees of Paradise until it is returned to his body on the Day when he is resurrected. The hadith does not describe every detail of the soul after death. It gives one clear teaching: the believer’s soul has a blessed state connected to Paradise before the resurrection. It also links that state to the final return of the soul to the body on the Day of Resurrection. The message is hopeful, but it stays within the words of the narration: the believer’s soul eats from the trees of Paradise until the day it is returned."},"teachings":["The believer’s soul is described as a bird in Paradise.","The soul eats from the trees of Paradise until Resurrection.","The hadith connects the soul’s state after death with return to the body."],"related_hadiths":[{"id":"1379","book_id":"1","label":"Sahih Bukhari"},{"id":"1887","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Believer’s Soul in Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. The believer’s soul is described as a bird eating from Paradise until it returns to the body on Resurrection Day."},"heading":{"title":"Hadith About the Believer’s Soul as a Bird in Paradise","description":"This hadith about the believer’s soul gives a beautiful and simple image. The Prophet said that the believer’s soul is a bird that eats from the trees of Paradise until it is returned to his body on the Day when he is resurrected. The hadith does not describe every detail of the soul after death. It gives one clear teaching: the believer’s soul has a blessed state connected to Paradise before the resurrection. It also links that state to the final return of the soul to the body on the Day of Resurrection. The message is hopeful, but it stays within the words of the narration: the believer’s soul eats from the trees of Paradise until the day it is returned."},"teachings":["The believer’s soul is described as a bird in Paradise.","The soul eats from the trees of Paradise until Resurrection.","The hadith connects the soul’s state after death with return to the body."],"related_hadiths":[{"id":"1379","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1887","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E624" s="4" t="n"/>
@@ -14865,7 +14869,7 @@
       </c>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Let Me Pray in the Grave","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the deceased sitting in the grave as the sun appears to set and saying, Let me pray."},"heading":{"title":"Let Me Pray: Hadith About the Deceased in the Grave","description":"This hadith about prayer in the grave describes a striking scene. When the deceased is placed in the grave, the sun is made to appear as if it is setting. The person sits up, wipes his eyes, and says: Let me pray. The hadith does not give a long explanation. Its message is carried by the scene itself. Prayer is shown as something the person still speaks of after being placed in the grave. The words also remind the reader that the time for normal action belongs to worldly life. Once a person has entered the grave, the scene is no longer the same as life before death. The hadith points the heart back to prayer before that moment arrives."},"teachings":["The deceased is described as asking to pray after entering the grave.","The scene reminds the living to value prayer while time remains.","The grave marks a change from the normal time of worldly action."],"related_hadiths":[{"id":"1369","book_id":"1","label":"Sahih Bukhari"},{"id":"1379","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Let Me Pray in the Grave","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the deceased sitting in the grave as the sun appears to set and saying, Let me pray."},"heading":{"title":"Let Me Pray: Hadith About the Deceased in the Grave","description":"This hadith about prayer in the grave describes a striking scene. When the deceased is placed in the grave, the sun is made to appear as if it is setting. The person sits up, wipes his eyes, and says: Let me pray. The hadith does not give a long explanation. Its message is carried by the scene itself. Prayer is shown as something the person still speaks of after being placed in the grave. The words also remind the reader that the time for normal action belongs to worldly life. Once a person has entered the grave, the scene is no longer the same as life before death. The hadith points the heart back to prayer before that moment arrives."},"teachings":["The deceased is described as asking to pray after entering the grave.","The scene reminds the living to value prayer while time remains.","The grave marks a change from the normal time of worldly action."],"related_hadiths":[{"id":"1369","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1379","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E625" s="4" t="n"/>
@@ -14888,7 +14892,7 @@
       </c>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Angels of the Trumpet","description":"$book_name$ $hadith_number$ - $chapter_name$. The two entrusted with the Trumpet are waiting with their horns until Allah’s command comes."},"heading":{"title":"Hadith About the Two Entrusted With the Trumpet","description":"This hadith about the Trumpet on the Day of Resurrection is brief but powerful. The Prophet said that the two who are entrusted with the Trumpet have two horns in their hands, watching and waiting until they are commanded. The hadith does not name them in this text, and it does not add a timeline. It simply shows readiness. The command has not yet come, but the ones entrusted with it are waiting for it. The main lesson is that the final events are not vague or uncontrolled. They are tied to Allah’s command. For readers searching for hadith about the trumpet, this narration highlights waiting, command, and the seriousness of the Day of Resurrection."},"teachings":["The Trumpet is connected to a command that has not yet been given.","The two entrusted with it are described as waiting and watching.","The final events occur by Allah’s command, not by chance."],"related_hadiths":[{"id":"4935","book_id":"1","label":"Sahih Bukhari"},{"id":"4814","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Angels of the Trumpet","description":"$book_name$ $hadith_number$ - $chapter_name$. The two entrusted with the Trumpet are waiting with their horns until Allah’s command comes."},"heading":{"title":"Hadith About the Two Entrusted With the Trumpet","description":"This hadith about the Trumpet on the Day of Resurrection is brief but powerful. The Prophet said that the two who are entrusted with the Trumpet have two horns in their hands, watching and waiting until they are commanded. The hadith does not name them in this text, and it does not add a timeline. It simply shows readiness. The command has not yet come, but the ones entrusted with it are waiting for it. The main lesson is that the final events are not vague or uncontrolled. They are tied to Allah’s command. For readers searching for hadith about the trumpet, this narration highlights waiting, command, and the seriousness of the Day of Resurrection."},"teachings":["The Trumpet is connected to a command that has not yet been given.","The two entrusted with it are described as waiting and watching.","The final events occur by Allah’s command, not by chance."],"related_hadiths":[{"id":"4935","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4814","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E626" s="4" t="n"/>
@@ -14911,7 +14915,7 @@
       </c>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Respect for the Prophets","description":"$book_name$ $hadith_number$ - $chapter_name$. A lesson in humility: the Prophet mentioned Musa after the Trumpet and warned against claiming superiority over Yunus."},"heading":{"title":"Hadith About Musa, Yunus, and Respect for the Prophets","description":"This hadith about Musa and Yunus teaches respect and careful speech about the Prophets. The event began when a Jewish man said that Allah chose Musa above mankind, and an Ansari man slapped him because the Messenger of Allah was among them. When this was mentioned to the Prophet, he did not respond with pride. He recited the verse about the Trumpet being blown and said he would be the first to raise his head, then he would see Musa holding one of the pillars of the Throne. He said he did not know whether Musa raised his head before him or was among those Allah exempted. He also said that whoever says he is better than Yunus bin Matta has lied. The lesson is humility and restraint in speaking about Allah’s Messengers."},"teachings":["The Prophet answered with humility when the issue of prophetic rank was raised.","He mentioned Musa with honor after the blowing of the Trumpet.","The narration warns against careless claims of superiority over Yunus bin Matta."],"related_hadiths":[{"id":"3414","book_id":"1","label":"Sahih Bukhari"},{"id":"3415","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Respect for the Prophets","description":"$book_name$ $hadith_number$ - $chapter_name$. A lesson in humility: the Prophet mentioned Musa after the Trumpet and warned against claiming superiority over Yunus."},"heading":{"title":"Hadith About Musa, Yunus, and Respect for the Prophets","description":"This hadith about Musa and Yunus teaches respect and careful speech about the Prophets. The event began when a Jewish man said that Allah chose Musa above mankind, and an Ansari man slapped him because the Messenger of Allah was among them. When this was mentioned to the Prophet, he did not respond with pride. He recited the verse about the Trumpet being blown and said he would be the first to raise his head, then he would see Musa holding one of the pillars of the Throne. He said he did not know whether Musa raised his head before him or was among those Allah exempted. He also said that whoever says he is better than Yunus bin Matta has lied. The lesson is humility and restraint in speaking about Allah’s Messengers."},"teachings":["The Prophet answered with humility when the issue of prophetic rank was raised.","He mentioned Musa with honor after the blowing of the Trumpet.","The narration warns against careless claims of superiority over Yunus bin Matta."],"related_hadiths":[{"id":"3414","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3415","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E627" s="4" t="n"/>
@@ -14934,7 +14938,7 @@
       </c>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The King and the Arrogant","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah seizes the heavens and earth and calls out, I am the King; where are the tyrants and arrogant?"},"heading":{"title":"Hadith About Allah as the King and the Fall of Arrogance","description":"This hadith about Allah as the King shows the greatness of Allah and the smallness of arrogance. Ibn Umar heard the Prophet say on the pulpit that the Compeller will seize His heavens and earths in His Hand. The Prophet then described Allah saying: I am the Compeller, I am the King. Where are the tyrants? Where are the arrogant? The narration also describes the Prophet moving to his right and left until the pulpit shook. The lesson is direct: worldly power, tyranny, and pride do not stand before Allah’s kingship. The hadith speaks about Allah’s authority and the end of false greatness. It should make a person lower his pride and remember who the true King is."},"teachings":["Allah is described as the Compeller and the King.","Tyrants and arrogant people are called out in this narration.","Human pride is shown as weak before Allah’s complete authority."],"related_hadiths":[{"id":"4812","book_id":"1","label":"Sahih Bukhari"},{"id":"2788a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The King and the Arrogant","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah seizes the heavens and earth and calls out, I am the King; where are the tyrants and arrogant?"},"heading":{"title":"Hadith About Allah as the King and the Fall of Arrogance","description":"This hadith about Allah as the King shows the greatness of Allah and the smallness of arrogance. Ibn Umar heard the Prophet say on the pulpit that the Compeller will seize His heavens and earths in His Hand. The Prophet then described Allah saying: I am the Compeller, I am the King. Where are the tyrants? Where are the arrogant? The narration also describes the Prophet moving to his right and left until the pulpit shook. The lesson is direct: worldly power, tyranny, and pride do not stand before Allah’s kingship. The hadith speaks about Allah’s authority and the end of false greatness. It should make a person lower his pride and remember who the true King is."},"teachings":["Allah is described as the Compeller and the King.","Tyrants and arrogant people are called out in this narration.","Human pride is shown as weak before Allah’s complete authority."],"related_hadiths":[{"id":"4812","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2788a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E628" s="4" t="n"/>
@@ -14957,7 +14961,7 @@
       </c>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gathered Barefoot and Naked","description":"$book_name$ $hadith_number$ - $chapter_name$. People will be gathered barefoot and naked, but the Day will be too serious for them to look at one another."},"heading":{"title":"Hadith About Being Gathered Barefoot and Naked on Judgment Day","description":"This hadith about being gathered barefoot and naked on the Day of Resurrection answers a question from Aishah. She asked how people would be gathered, and the Prophet said: barefoot and naked. She asked about women too, and he said that women would also be gathered that way. When she asked about shame, the Prophet explained that the matter would be too serious for people to look at one another. The hadith does not make the scene casual or light. It shows the weight of the Day of Resurrection. People will not be focused on each other in the usual way. The concern and seriousness of that Day will be greater than worldly embarrassment."},"teachings":["People will be gathered barefoot and naked on the Day of Resurrection.","The same gathering is mentioned for men and women in this narration.","The seriousness of that Day will distract people from looking at one another."],"related_hadiths":[{"id":"6527","book_id":"1","label":"Sahih Bukhari"},{"id":"2859a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gathered Barefoot and Naked","description":"$book_name$ $hadith_number$ - $chapter_name$. People will be gathered barefoot and naked, but the Day will be too serious for them to look at one another."},"heading":{"title":"Hadith About Being Gathered Barefoot and Naked on Judgment Day","description":"This hadith about being gathered barefoot and naked on the Day of Resurrection answers a question from Aishah. She asked how people would be gathered, and the Prophet said: barefoot and naked. She asked about women too, and he said that women would also be gathered that way. When she asked about shame, the Prophet explained that the matter would be too serious for people to look at one another. The hadith does not make the scene casual or light. It shows the weight of the Day of Resurrection. People will not be focused on each other in the usual way. The concern and seriousness of that Day will be greater than worldly embarrassment."},"teachings":["People will be gathered barefoot and naked on the Day of Resurrection.","The same gathering is mentioned for men and women in this narration.","The seriousness of that Day will distract people from looking at one another."],"related_hadiths":[{"id":"6527","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2859a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E629" s="4" t="n"/>
@@ -14980,7 +14984,7 @@
       </c>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Scrolls of Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. People will be presented three times, then the scrolls of deeds will fly into hands, right or left."},"heading":{"title":"Hadith About the Scrolls of Deeds on the Day of Resurrection","description":"This hadith about the scrolls of deeds describes people being presented before Allah three times on the Day of Resurrection. The first two presentations are for disputes and excuses. The third is when the scrolls fly into the hands. Some people receive the scroll in the right hand, and some receive it in the left. The hadith gives a short but serious picture of accountability. It does not list the deeds. It focuses on being presented, giving excuses, and then receiving the record. The right hand and left hand in the narration point to two different outcomes. For anyone searching for hadith about book of deeds, this narration is a reminder that deeds are recorded and will be faced."},"teachings":["People will be presented before Allah three times on the Day of Resurrection.","The first two presentations are linked with disputes and excuses.","The scrolls of deeds will be received in the right hand or the left."],"related_hadiths":[{"id":"6536","book_id":"1","label":"Sahih Bukhari"},{"id":"2425","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Scrolls of Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. People will be presented three times, then the scrolls of deeds will fly into hands, right or left."},"heading":{"title":"Hadith About the Scrolls of Deeds on the Day of Resurrection","description":"This hadith about the scrolls of deeds describes people being presented before Allah three times on the Day of Resurrection. The first two presentations are for disputes and excuses. The third is when the scrolls fly into the hands. Some people receive the scroll in the right hand, and some receive it in the left. The hadith gives a short but serious picture of accountability. It does not list the deeds. It focuses on being presented, giving excuses, and then receiving the record. The right hand and left hand in the narration point to two different outcomes. For anyone searching for hadith about book of deeds, this narration is a reminder that deeds are recorded and will be faced."},"teachings":["People will be presented before Allah three times on the Day of Resurrection.","The first two presentations are linked with disputes and excuses.","The scrolls of deeds will be received in the right hand or the left."],"related_hadiths":[{"id":"6536","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2425","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E630" s="4" t="n"/>
@@ -15003,7 +15007,7 @@
       </c>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing in Sweat","description":"$book_name$ $hadith_number$ - $chapter_name$. On the Day mankind stands before the Lord, a person may stand in sweat reaching halfway up his ears."},"heading":{"title":"Hadith About Standing in Sweat Before the Lord of the Worlds","description":"This hadith about standing in sweat explains the verse, the Day when mankind will stand before the Lord of all that exists. The Prophet said that one of them will stand in his sweat up to halfway up his ears. The narration gives a strong image of the pressure and seriousness of the Day of Resurrection. It does not turn the verse into a general idea only. It describes a physical state: standing and being surrounded by sweat. The main lesson is accountability before the Lord of the worlds. This hadith reminds the reader that the Day of Judgment is not a light matter. It calls the heart to prepare before that standing comes."},"teachings":["Mankind will stand before the Lord of all that exists.","The hadith describes a person standing in sweat up to halfway up his ears.","The scene points to the seriousness of accountability on that Day."],"related_hadiths":[{"id":"4938","book_id":"1","label":"Sahih Bukhari"},{"id":"2862a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing in Sweat","description":"$book_name$ $hadith_number$ - $chapter_name$. On the Day mankind stands before the Lord, a person may stand in sweat reaching halfway up his ears."},"heading":{"title":"Hadith About Standing in Sweat Before the Lord of the Worlds","description":"This hadith about standing in sweat explains the verse, the Day when mankind will stand before the Lord of all that exists. The Prophet said that one of them will stand in his sweat up to halfway up his ears. The narration gives a strong image of the pressure and seriousness of the Day of Resurrection. It does not turn the verse into a general idea only. It describes a physical state: standing and being surrounded by sweat. The main lesson is accountability before the Lord of the worlds. This hadith reminds the reader that the Day of Judgment is not a light matter. It calls the heart to prepare before that standing comes."},"teachings":["Mankind will stand before the Lord of all that exists.","The hadith describes a person standing in sweat up to halfway up his ears.","The scene points to the seriousness of accountability on that Day."],"related_hadiths":[{"id":"4938","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2862a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E631" s="4" t="n"/>
@@ -15026,7 +15030,7 @@
       </c>
       <c r="D632" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Crossing the Sirat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Sirat will be placed over Hell, and people will cross it with different outcomes: safe, detained, or fallen."},"heading":{"title":"Crossing the Sirat Over Hell: Hadith Meaning and Lessons","description":"This hadith about crossing the Sirat describes the bridge being placed across Hell. The Prophet said it will be on thorns like the thorns of the Sa’dan plant. Then people will cross it. Some will pass over safe and sound. Some will be detained. Some will fall in headfirst. The narration does not give a long sermon, but the image is enough to shake the heart. The Sirat is shown as a real stage with different outcomes. The hadith teaches that the Hereafter includes passing over a place of great danger, and that people will not all experience it in the same way. This should make a person think seriously about faith, actions, and meeting Allah."},"teachings":["The Sirat will be placed across Hell.","People will cross it with different outcomes.","Some will pass safely, while others will be detained or fall."],"related_hadiths":[{"id":"183a","book_id":"2","label":"Sahih Muslim"},{"id":"7439","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Crossing the Sirat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Sirat will be placed over Hell, and people will cross it with different outcomes: safe, detained, or fallen."},"heading":{"title":"Crossing the Sirat Over Hell: Hadith Meaning and Lessons","description":"This hadith about crossing the Sirat describes the bridge being placed across Hell. The Prophet said it will be on thorns like the thorns of the Sa’dan plant. Then people will cross it. Some will pass over safe and sound. Some will be detained. Some will fall in headfirst. The narration does not give a long sermon, but the image is enough to shake the heart. The Sirat is shown as a real stage with different outcomes. The hadith teaches that the Hereafter includes passing over a place of great danger, and that people will not all experience it in the same way. This should make a person think seriously about faith, actions, and meeting Allah."},"teachings":["The Sirat will be placed across Hell.","People will cross it with different outcomes.","Some will pass safely, while others will be detained or fall."],"related_hadiths":[{"id":"183a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"7439","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E632" s="4" t="n"/>
@@ -15049,7 +15053,7 @@
       </c>
       <c r="D633" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hope for the People of Badr and Hudaybiyah","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful Hadith on Badr, Hudaybiyah, Hell, and how Allah saves those who fear Him."},"heading":{"title":"Hadith About Badr and Hudaybiyah: Hope of Salvation from Hell","description":"This Hadith speaks about hope, fear of Allah, and the Hereafter. The Prophet صلى الله عليه وسلم said that he hoped no one who witnessed Badr and Hudaybiyah would enter Hell, if Allah wills. Hafsah asked about the verse saying that every person will pass over Hell. The Prophet صلى الله عليه وسلم answered by reminding her of the next verse: Allah will save those who used to fear Him and were dutiful to Him, while wrongdoers will be left there. The main lesson is balanced. A believer should have hope in Allah’s mercy, but also stay mindful of taqwa. This Hadith about Badr and Hudaybiyah also shows that Qur’anic verses are understood together, not by taking one verse alone."},"teachings":["The Prophet صلى الله عليه وسلم gave hopeful news for those who witnessed Badr and Hudaybiyah, while saying if Allah wills.","Questions about Qur’anic verses can be answered by referring to other verses.","Taqwa is linked in the text with being saved by Allah.","A believer should keep hope in Allah while taking the Hereafter seriously."],"related_hadiths":[{"id":"2496","book_id":"2","label":"Sahih Muslim"},{"id":"3007","book_id":"1","label":"Sahih Bukhari"},{"id":"4299","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hope for the People of Badr and Hudaybiyah","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful Hadith on Badr, Hudaybiyah, Hell, and how Allah saves those who fear Him."},"heading":{"title":"Hadith About Badr and Hudaybiyah: Hope of Salvation from Hell","description":"This Hadith speaks about hope, fear of Allah, and the Hereafter. The Prophet صلى الله عليه وسلم said that he hoped no one who witnessed Badr and Hudaybiyah would enter Hell, if Allah wills. Hafsah asked about the verse saying that every person will pass over Hell. The Prophet صلى الله عليه وسلم answered by reminding her of the next verse: Allah will save those who used to fear Him and were dutiful to Him, while wrongdoers will be left there. The main lesson is balanced. A believer should have hope in Allah’s mercy, but also stay mindful of taqwa. This Hadith about Badr and Hudaybiyah also shows that Qur’anic verses are understood together, not by taking one verse alone."},"teachings":["The Prophet صلى الله عليه وسلم gave hopeful news for those who witnessed Badr and Hudaybiyah, while saying if Allah wills.","Questions about Qur’anic verses can be answered by referring to other verses.","Taqwa is linked in the text with being saved by Allah.","A believer should keep hope in Allah while taking the Hereafter seriously."],"related_hadiths":[{"id":"2496","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"3007","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4299","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E633" s="4" t="n"/>
@@ -15072,7 +15076,7 @@
       </c>
       <c r="D634" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Radiant Signs of Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear Hadith on wudu and the special radiant sign of the Prophet’s nation on the Day of Resurrection."},"heading":{"title":"Hadith About Wudu: Radiant Faces, Hands, and Feet","description":"This Hadith highlights the special sign of the Prophet’s nation through wudu. The Messenger of Allah صلى الله عليه وسلم said that his followers will come to him with radiant faces, hands, and feet from the traces of ablution. This sign belongs to his nation and does not belong to anyone else. The meaning is simple and moving: wudu is not only a washing before prayer. In this Hadith about wudu, it becomes a mark of honor and recognition in the Hereafter. The text does not add extra details about how to perform wudu; it focuses on the result mentioned by the Prophet صلى الله عليه وسلم. It encourages a Muslim to value ablution and see it as part of their identity as a follower of Muhammad صلى الله عليه وسلم."},"teachings":["Wudu leaves a special sign for the Prophet’s nation.","Purification is connected with honor in the Hereafter.","The Prophet صلى الله عليه وسلم will recognize his nation by this radiant mark.","Ablution should be valued as more than a routine act."],"related_hadiths":[{"id":"136","book_id":"1","label":"Sahih Bukhari"},{"id":"246","book_id":"2","label":"Sahih Muslim"},{"id":"4284","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Radiant Signs of Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear Hadith on wudu and the special radiant sign of the Prophet’s nation on the Day of Resurrection."},"heading":{"title":"Hadith About Wudu: Radiant Faces, Hands, and Feet","description":"This Hadith highlights the special sign of the Prophet’s nation through wudu. The Messenger of Allah صلى الله عليه وسلم said that his followers will come to him with radiant faces, hands, and feet from the traces of ablution. This sign belongs to his nation and does not belong to anyone else. The meaning is simple and moving: wudu is not only a washing before prayer. In this Hadith about wudu, it becomes a mark of honor and recognition in the Hereafter. The text does not add extra details about how to perform wudu; it focuses on the result mentioned by the Prophet صلى الله عليه وسلم. It encourages a Muslim to value ablution and see it as part of their identity as a follower of Muhammad صلى الله عليه وسلم."},"teachings":["Wudu leaves a special sign for the Prophet’s nation.","Purification is connected with honor in the Hereafter.","The Prophet صلى الله عليه وسلم will recognize his nation by this radiant mark.","Ablution should be valued as more than a routine act."],"related_hadiths":[{"id":"136","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"246","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4284","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E634" s="4" t="n"/>
@@ -15095,7 +15099,7 @@
       </c>
       <c r="D635" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Half of the People of Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful Hadith about the Muslim nation and the Prophet’s hope that they will be half of Paradise."},"heading":{"title":"Hadith About the Ummah Being Half of Paradise","description":"This Hadith gives a strong message of hope for the Muslim ummah. The Prophet صلى الله عليه وسلم asked his companions if they would be pleased to be one quarter of the people of Paradise, then one third. Then he said, by the One in Whose Hand is his soul, that he hoped they would be half of the people of Paradise. He also stated that only a Muslim soul will enter Paradise. The Hadith uses a clear image to show that the Muslims would be few compared with the people of polytheism, like a single hair on the hide of a bull. This Hadith about Paradise should build gratitude and hope, while reminding us that entry into Paradise is tied to being a Muslim soul."},"teachings":["The Prophet صلى الله عليه وسلم gave his companions hope about the large share of his nation in Paradise.","The Hadith connects entry into Paradise with being a Muslim soul.","The small number image reminds believers not to judge truth by numbers alone.","Hope in Paradise should lead to gratitude, not carelessness."],"related_hadiths":[{"id":"4289","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4290","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6528","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Half of the People of Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful Hadith about the Muslim nation and the Prophet’s hope that they will be half of Paradise."},"heading":{"title":"Hadith About the Ummah Being Half of Paradise","description":"This Hadith gives a strong message of hope for the Muslim ummah. The Prophet صلى الله عليه وسلم asked his companions if they would be pleased to be one quarter of the people of Paradise, then one third. Then he said, by the One in Whose Hand is his soul, that he hoped they would be half of the people of Paradise. He also stated that only a Muslim soul will enter Paradise. The Hadith uses a clear image to show that the Muslims would be few compared with the people of polytheism, like a single hair on the hide of a bull. This Hadith about Paradise should build gratitude and hope, while reminding us that entry into Paradise is tied to being a Muslim soul."},"teachings":["The Prophet صلى الله عليه وسلم gave his companions hope about the large share of his nation in Paradise.","The Hadith connects entry into Paradise with being a Muslim soul.","The small number image reminds believers not to judge truth by numbers alone.","Hope in Paradise should lead to gratitude, not carelessness."],"related_hadiths":[{"id":"4289","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4290","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"6528","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E635" s="4" t="n"/>
@@ -15118,7 +15122,7 @@
       </c>
       <c r="D636" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Just Nation as Witnesses","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith explaining how Muhammad’s nation will bear witness that the messengers conveyed their message."},"heading":{"title":"Hadith About the Ummah as Witnesses Over Mankind","description":"This Hadith explains the honor and duty of the nation of Muhammad صلى الله عليه وسلم on the Day of Resurrection. A Prophet will come with a small number of followers, and he will be asked whether he conveyed the message to his people. When his people deny it, he will say that Muhammad صلى الله عليه وسلم and his nation will bear witness for him. The nation of Muhammad صلى الله عليه وسلم will say that the Prophet صلى الله عليه وسلم told them the messengers had conveyed the message, and they believed him. The Hadith then connects this to the verse about being a just nation and witnesses over mankind. This Hadith about the ummah as witnesses teaches trust in the Prophet’s صلى الله عليه وسلم message and shows the weight of belief in what he taught."},"teachings":["The nation of Muhammad صلى الله عليه وسلم will bear witness based on what their Prophet told them.","Belief in the Prophet صلى الله عليه وسلم includes accepting his truthful news.","The Hadith explains the meaning of being a just nation in the cited verse.","Prophets conveyed their message, even if some people denied it."],"related_hadiths":[{"id":"3339","book_id":"1","label":"Sahih Bukhari"},{"id":"4287","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4288","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Just Nation as Witnesses","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith explaining how Muhammad’s nation will bear witness that the messengers conveyed their message."},"heading":{"title":"Hadith About the Ummah as Witnesses Over Mankind","description":"This Hadith explains the honor and duty of the nation of Muhammad صلى الله عليه وسلم on the Day of Resurrection. A Prophet will come with a small number of followers, and he will be asked whether he conveyed the message to his people. When his people deny it, he will say that Muhammad صلى الله عليه وسلم and his nation will bear witness for him. The nation of Muhammad صلى الله عليه وسلم will say that the Prophet صلى الله عليه وسلم told them the messengers had conveyed the message, and they believed him. The Hadith then connects this to the verse about being a just nation and witnesses over mankind. This Hadith about the ummah as witnesses teaches trust in the Prophet’s صلى الله عليه وسلم message and shows the weight of belief in what he taught."},"teachings":["The nation of Muhammad صلى الله عليه وسلم will bear witness based on what their Prophet told them.","Belief in the Prophet صلى الله عليه وسلم includes accepting his truthful news.","The Hadith explains the meaning of being a just nation in the cited verse.","Prophets conveyed their message, even if some people denied it."],"related_hadiths":[{"id":"3339","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4287","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4288","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E636" s="4" t="n"/>
@@ -15141,7 +15145,7 @@
       </c>
       <c r="D637" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Faith, Steadfastness, and Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful Hadith about belief, standing firm, dwelling in Paradise, and seventy thousand entering without account."},"heading":{"title":"Hadith About Seventy Thousand Entering Paradise Without Account","description":"This Hadith joins faith, firmness, and hope in Paradise. The Prophet صلى الله عليه وسلم said that no person believes and then stands firm except that he will be caused to enter Paradise. He also expressed hope that the companions and the righteous among their offspring would take their places in Paradise before others enter. Then he mentioned a great promise from Allah: seventy thousand of his nation would enter Paradise without being brought to account. This Hadith about seventy thousand entering Paradise gives hope, but it also begins with belief and standing firm. The text does not invite a person to feel safe without effort. It points to faith, uprightness, and Allah’s promise as causes of hope."},"teachings":["Belief should be followed by standing firm.","The Prophet صلى الله عليه وسلم gave hopeful news about Paradise to his companions and righteous offspring.","Seventy thousand from this nation are promised entry into Paradise without account.","Hope in Paradise is tied in the text to faith and firmness."],"related_hadiths":[{"id":"4286","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4300","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5705","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Faith, Steadfastness, and Paradise","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful Hadith about belief, standing firm, dwelling in Paradise, and seventy thousand entering without account."},"heading":{"title":"Hadith About Seventy Thousand Entering Paradise Without Account","description":"This Hadith joins faith, firmness, and hope in Paradise. The Prophet صلى الله عليه وسلم said that no person believes and then stands firm except that he will be caused to enter Paradise. He also expressed hope that the companions and the righteous among their offspring would take their places in Paradise before others enter. Then he mentioned a great promise from Allah: seventy thousand of his nation would enter Paradise without being brought to account. This Hadith about seventy thousand entering Paradise gives hope, but it also begins with belief and standing firm. The text does not invite a person to feel safe without effort. It points to faith, uprightness, and Allah’s promise as causes of hope."},"teachings":["Belief should be followed by standing firm.","The Prophet صلى الله عليه وسلم gave hopeful news about Paradise to his companions and righteous offspring.","Seventy thousand from this nation are promised entry into Paradise without account.","Hope in Paradise is tied in the text to faith and firmness."],"related_hadiths":[{"id":"4286","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4300","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"5705","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E637" s="4" t="n"/>
@@ -15164,7 +15168,7 @@
       </c>
       <c r="D638" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seventy Thousand and Allah’s Mercy","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith about seventy thousand from the ummah entering Paradise without account or punishment."},"heading":{"title":"Hadith About 70,000 Entering Jannah Without Account or Punishment","description":"This Hadith gives a wide message of Allah’s mercy toward the Prophet’s nation. Abu Umamah narrated that the Messenger of Allah صلى الله عليه وسلم said his Lord promised that seventy thousand of his nation would enter Paradise without being brought to account or punished. The Hadith also says that with every thousand there will be another seventy thousand, along with three handfuls from the Lord, the Glorified. The core topic is Paradise and mercy. A reader should notice that the Prophet صلى الله عليه وسلم is reporting a promise from Allah. The Hadith about 70,000 entering Jannah is full of hope, but it does not name who they are in this text. So the safe lesson is to hope in Allah, love this promise, and keep seeking His mercy."},"teachings":["Allah promised a group from the Prophet’s nation entry into Paradise without account or punishment.","The Hadith gives hope in Allah’s wide mercy.","The exact people included are not named in this text.","A Muslim should seek Allah’s mercy while staying sincere in faith."],"related_hadiths":[{"id":"4285","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4293","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5705","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seventy Thousand and Allah’s Mercy","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith about seventy thousand from the ummah entering Paradise without account or punishment."},"heading":{"title":"Hadith About 70,000 Entering Jannah Without Account or Punishment","description":"This Hadith gives a wide message of Allah’s mercy toward the Prophet’s nation. Abu Umamah narrated that the Messenger of Allah صلى الله عليه وسلم said his Lord promised that seventy thousand of his nation would enter Paradise without being brought to account or punished. The Hadith also says that with every thousand there will be another seventy thousand, along with three handfuls from the Lord, the Glorified. The core topic is Paradise and mercy. A reader should notice that the Prophet صلى الله عليه وسلم is reporting a promise from Allah. The Hadith about 70,000 entering Jannah is full of hope, but it does not name who they are in this text. So the safe lesson is to hope in Allah, love this promise, and keep seeking His mercy."},"teachings":["Allah promised a group from the Prophet’s nation entry into Paradise without account or punishment.","The Hadith gives hope in Allah’s wide mercy.","The exact people included are not named in this text.","A Muslim should seek Allah’s mercy while staying sincere in faith."],"related_hadiths":[{"id":"4285","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4293","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"5705","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E638" s="4" t="n"/>
@@ -15187,7 +15191,7 @@
       </c>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Last and Best Nation","description":"$book_name$ $hadith_number$ - $chapter_name$. A short Hadith describing the nation of Muhammad as the last and the best among seventy nations."},"heading":{"title":"Hadith About the Last and Best Ummah","description":"This Hadith is brief, but it carries a powerful meaning about the place of the Prophet’s nation. The Messenger of Allah صلى الله عليه وسلم said that on the Day of Resurrection, his nation will complete seventy nations, and that they are the last and the best. The text focuses on honor given by Allah, not on pride over others. Since the Hadith mentions the Day of Resurrection, the honor is connected with the final gathering before Allah. This Hadith about the last and best ummah should make a Muslim thankful for being from the nation of Muhammad صلى الله عليه وسلم. It should also remind them that honor is a responsibility. The Hadith itself does not list deeds here, so the explanation should stay with what it says: last in order, best in rank."},"teachings":["The nation of Muhammad صلى الله عليه وسلم is described as the last among seventy nations.","The Hadith also describes this nation as the best.","This honor is mentioned in connection with the Day of Resurrection.","The wording calls for gratitude, not empty pride."],"related_hadiths":[{"id":"4288","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4290","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4284","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Last and Best Nation","description":"$book_name$ $hadith_number$ - $chapter_name$. A short Hadith describing the nation of Muhammad as the last and the best among seventy nations."},"heading":{"title":"Hadith About the Last and Best Ummah","description":"This Hadith is brief, but it carries a powerful meaning about the place of the Prophet’s nation. The Messenger of Allah صلى الله عليه وسلم said that on the Day of Resurrection, his nation will complete seventy nations, and that they are the last and the best. The text focuses on honor given by Allah, not on pride over others. Since the Hadith mentions the Day of Resurrection, the honor is connected with the final gathering before Allah. This Hadith about the last and best ummah should make a Muslim thankful for being from the nation of Muhammad صلى الله عليه وسلم. It should also remind them that honor is a responsibility. The Hadith itself does not list deeds here, so the explanation should stay with what it says: last in order, best in rank."},"teachings":["The nation of Muhammad صلى الله عليه وسلم is described as the last among seventy nations.","The Hadith also describes this nation as the best.","This honor is mentioned in connection with the Day of Resurrection.","The wording calls for gratitude, not empty pride."],"related_hadiths":[{"id":"4288","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4290","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4284","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E639" s="4" t="n"/>
@@ -15210,7 +15214,7 @@
       </c>
       <c r="D640" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Best and Dearest Ummah","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith describing the Prophet’s nation as the best and dearest to Allah among seventy nations."},"heading":{"title":"Hadith About the Ummah Being the Best and Dearest to Allah","description":"This Hadith describes the special honor of the nation of Muhammad صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم said that this nation completes seventy nations and is the best and dearest to Allah. The message is direct and uplifting. It tells Muslims that belonging to this ummah is a great blessing. At the same time, the wording should not be used for arrogance. Being described as best and dearest to Allah is a gift that should make a believer grateful and careful. This Hadith about the best ummah is close in meaning to other narrations in this same group that speak about the nation being last, first, and given a large share in Paradise. The Hadith itself is short, so the safest explanation stays with its clear words: honor, nearness to Allah, and gratitude."},"teachings":["The Prophet’s nation is described as completing seventy nations.","This nation is described as the best and dearest to Allah.","The Hadith points to a blessing that should lead to gratitude.","Honor from Allah should not be turned into arrogance."],"related_hadiths":[{"id":"4287","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4289","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4290","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Best and Dearest Ummah","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith describing the Prophet’s nation as the best and dearest to Allah among seventy nations."},"heading":{"title":"Hadith About the Ummah Being the Best and Dearest to Allah","description":"This Hadith describes the special honor of the nation of Muhammad صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم said that this nation completes seventy nations and is the best and dearest to Allah. The message is direct and uplifting. It tells Muslims that belonging to this ummah is a great blessing. At the same time, the wording should not be used for arrogance. Being described as best and dearest to Allah is a gift that should make a believer grateful and careful. This Hadith about the best ummah is close in meaning to other narrations in this same group that speak about the nation being last, first, and given a large share in Paradise. The Hadith itself is short, so the safest explanation stays with its clear words: honor, nearness to Allah, and gratitude."},"teachings":["The Prophet’s nation is described as completing seventy nations.","This nation is described as the best and dearest to Allah.","The Hadith points to a blessing that should lead to gratitude.","Honor from Allah should not be turned into arrogance."],"related_hadiths":[{"id":"4287","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4289","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4290","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E640" s="4" t="n"/>
@@ -15233,7 +15237,7 @@
       </c>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eighty Ranks from This Ummah","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful Hadith on the ranks of Paradise, with eighty ranks from this nation and forty from others."},"heading":{"title":"Hadith About the People of Paradise and the Ranks of the Ummah","description":"This Hadith gives a clear picture of the large share of the Prophet’s nation among the people of Paradise. The Prophet صلى الله عليه وسلم said that the people of Paradise are one hundred and twenty ranks: eighty from this nation and forty from all other nations. The Hadith does not describe the ranks in detail, but it does show a great honor for this ummah. This Hadith about the people of Paradise should fill a Muslim with hope and gratitude. It also matches the wider theme in these narrations: the nation of Muhammad صلى الله عليه وسلم has a special place on the Day of Resurrection. The text is about Allah’s favor, not a reason to feel safe from accountability. A believer reads it with hope, love for the Prophet صلى الله عليه وسلم, and care for faith."},"teachings":["The Hadith says the people of Paradise are one hundred and twenty ranks.","Eighty of those ranks are from the nation of Muhammad صلى الله عليه وسلم.","The Hadith shows a special honor for this ummah.","Hope in Paradise should be joined with gratitude and faith."],"related_hadiths":[{"id":"4283","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4288","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4290","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eighty Ranks from This Ummah","description":"$book_name$ $hadith_number$ - $chapter_name$. A hopeful Hadith on the ranks of Paradise, with eighty ranks from this nation and forty from others."},"heading":{"title":"Hadith About the People of Paradise and the Ranks of the Ummah","description":"This Hadith gives a clear picture of the large share of the Prophet’s nation among the people of Paradise. The Prophet صلى الله عليه وسلم said that the people of Paradise are one hundred and twenty ranks: eighty from this nation and forty from all other nations. The Hadith does not describe the ranks in detail, but it does show a great honor for this ummah. This Hadith about the people of Paradise should fill a Muslim with hope and gratitude. It also matches the wider theme in these narrations: the nation of Muhammad صلى الله عليه وسلم has a special place on the Day of Resurrection. The text is about Allah’s favor, not a reason to feel safe from accountability. A believer reads it with hope, love for the Prophet صلى الله عليه وسلم, and care for faith."},"teachings":["The Hadith says the people of Paradise are one hundred and twenty ranks.","Eighty of those ranks are from the nation of Muhammad صلى الله عليه وسلم.","The Hadith shows a special honor for this ummah.","Hope in Paradise should be joined with gratitude and faith."],"related_hadiths":[{"id":"4283","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4288","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4290","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E641" s="4" t="n"/>
@@ -15256,7 +15260,7 @@
       </c>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Running Fingers Through the Beard","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith reports that the Prophet ran his fingers through his beard during wudu."},"heading":{"title":"Hadith About Running Fingers Through the Beard in Wudu","description":"This Hadith is about running fingers through the beard in wudu. Ammar bin Yasir said that he saw the Messenger of Allah running his fingers through his beard. The narration is simple and observational. It does not give extra detail about how many times this was done in this specific report, and it does not include a separate command in the translation. So the safest explanation is to say that Ammar witnessed this action from the Prophet during ablution. The Hadith helps readers notice that wudu includes careful attention to the face and beard area, based on what the narrator saw."},"teachings":["Ammar bin Yasir personally saw the Prophet run his fingers through his beard.","The Hadith highlights attention to the beard area during ablution.","The narration teaches by reporting a witnessed Prophetic action.","The explanation should stay limited to what the narrator directly reported."],"related_hadiths":[{"id":"31","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"145","book_id":"4","label":"Sunan Abu Dawud"},{"id":"164","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Running Fingers Through the Beard","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith reports that the Prophet ran his fingers through his beard during wudu."},"heading":{"title":"Hadith About Running Fingers Through the Beard in Wudu","description":"This Hadith is about running fingers through the beard in wudu. Ammar bin Yasir said that he saw the Messenger of Allah running his fingers through his beard. The narration is simple and observational. It does not give extra detail about how many times this was done in this specific report, and it does not include a separate command in the translation. So the safest explanation is to say that Ammar witnessed this action from the Prophet during ablution. The Hadith helps readers notice that wudu includes careful attention to the face and beard area, based on what the narrator saw."},"teachings":["Ammar bin Yasir personally saw the Prophet run his fingers through his beard.","The Hadith highlights attention to the beard area during ablution.","The narration teaches by reporting a witnessed Prophetic action.","The explanation should stay limited to what the narrator directly reported."],"related_hadiths":[{"id":"31","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"145","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"164","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E642" s="4" t="n"/>
@@ -15279,7 +15283,7 @@
       </c>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Last Nations and First to Account","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith about the Prophet’s nation being last among nations and first to be brought to account."},"heading":{"title":"Hadith About the Last Ummah Being First to Be Accounted","description":"This Hadith describes a special order for the nation of Muhammad صلى الله عليه وسلم on the Day of Resurrection. The Prophet صلى الله عليه وسلم said: We are the last of the nations and the first to be brought to account. It will be said: Where is the unlettered nation and its Prophet? Then he said: We are the last and the first. The meaning is simple: this ummah came last in time, but it will be given first place in the accounting mentioned here. This Hadith about the last and first ummah is a reminder of Allah’s favor. It also keeps the mind focused on the Day of Resurrection. Being first to account is not just an honor to mention; it reminds every believer that standing before Allah is real."},"teachings":["The nation of Muhammad صلى الله عليه وسلم is described as the last of the nations.","This nation will be the first to be brought to account.","The Prophet صلى الله عليه وسلم connected this honor with himself and his nation.","The Hadith reminds believers to think about standing before Allah."],"related_hadiths":[{"id":"4287","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4288","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4289","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Last Nations and First to Account","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith about the Prophet’s nation being last among nations and first to be brought to account."},"heading":{"title":"Hadith About the Last Ummah Being First to Be Accounted","description":"This Hadith describes a special order for the nation of Muhammad صلى الله عليه وسلم on the Day of Resurrection. The Prophet صلى الله عليه وسلم said: We are the last of the nations and the first to be brought to account. It will be said: Where is the unlettered nation and its Prophet? Then he said: We are the last and the first. The meaning is simple: this ummah came last in time, but it will be given first place in the accounting mentioned here. This Hadith about the last and first ummah is a reminder of Allah’s favor. It also keeps the mind focused on the Day of Resurrection. Being first to account is not just an honor to mention; it reminds every believer that standing before Allah is real."},"teachings":["The nation of Muhammad صلى الله عليه وسلم is described as the last of the nations.","This nation will be the first to be brought to account.","The Prophet صلى الله عليه وسلم connected this honor with himself and his nation.","The Hadith reminds believers to think about standing before Allah."],"related_hadiths":[{"id":"4287","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4288","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4289","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E643" s="4" t="n"/>
@@ -15302,7 +15306,7 @@
       </c>
       <c r="D644" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostration on the Day of Resurrection","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith about the nation of Muhammad being permitted to prostrate when Allah gathers all creatures."},"heading":{"title":"Hadith About Prostration on the Day of Resurrection","description":"This Hadith speaks about a scene on the Day of Resurrection. When Allah gathers all creatures, permission will be given to the nation of Muhammad صلى الله عليه وسلم to prostrate, and they will prostrate to Him for a long time. Then they will be told to raise their heads, and a certain number is mentioned as a ransom from Hell. The wording points to awe, worship, and Allah’s dealing with people in the Hereafter. This Hadith about prostration on the Day of Resurrection should make the reader think about standing before Allah. The text does not give extra details about who is included in the number, so it is better not to add details. The clear lesson is that worship belongs to Allah and the Hereafter is real."},"teachings":["The nation of Muhammad صلى الله عليه وسلم is described as being allowed to prostrate on the Day of Resurrection.","Prostration in the Hadith is directed to Allah alone.","The long prostration shows awe and worship before Allah.","The Hadith reminds believers of the gathering of all creatures."],"related_hadiths":[{"id":"4292","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4293","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostration on the Day of Resurrection","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith about the nation of Muhammad being permitted to prostrate when Allah gathers all creatures."},"heading":{"title":"Hadith About Prostration on the Day of Resurrection","description":"This Hadith speaks about a scene on the Day of Resurrection. When Allah gathers all creatures, permission will be given to the nation of Muhammad صلى الله عليه وسلم to prostrate, and they will prostrate to Him for a long time. Then they will be told to raise their heads, and a certain number is mentioned as a ransom from Hell. The wording points to awe, worship, and Allah’s dealing with people in the Hereafter. This Hadith about prostration on the Day of Resurrection should make the reader think about standing before Allah. The text does not give extra details about who is included in the number, so it is better not to add details. The clear lesson is that worship belongs to Allah and the Hereafter is real."},"teachings":["The nation of Muhammad صلى الله عليه وسلم is described as being allowed to prostrate on the Day of Resurrection.","Prostration in the Hadith is directed to Allah alone.","The long prostration shows awe and worship before Allah.","The Hadith reminds believers of the gathering of all creatures."],"related_hadiths":[{"id":"4292","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4293","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E644" s="4" t="n"/>
@@ -15325,7 +15329,7 @@
       </c>
       <c r="D645" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Nation Granted Mercy","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith describing the Prophet’s nation as granted mercy and mentioning ransom from the Fire."},"heading":{"title":"Hadith About This Ummah Being Granted Mercy","description":"This Hadith describes the nation of Muhammad صلى الله عليه وسلم as an ummah that has been granted mercy in the Hereafter. It also says that its torment in this world is at the hands of one another. Then the Hadith mentions a scene on the Day of Resurrection: each Muslim man will be given a man from among the idolaters, and it will be said that this is his ransom from the Fire. The core topic is mercy and salvation from the Fire. This Hadith about the ummah being granted mercy should be read with care, using only the wording given. It does not tell a person to be careless about sin. It points to Allah’s mercy toward this nation and reminds readers that the final decision belongs to Allah."},"teachings":["The Prophet صلى الله عليه وسلم described this nation as granted mercy in the Hereafter.","The Hadith mentions worldly torment occurring at the hands of one another.","The text speaks of ransom from the Fire on the Day of Resurrection.","The Hadith encourages hope in Allah’s mercy without adding claims beyond the text."],"related_hadiths":[{"id":"4291","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4293","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Nation Granted Mercy","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith describing the Prophet’s nation as granted mercy and mentioning ransom from the Fire."},"heading":{"title":"Hadith About This Ummah Being Granted Mercy","description":"This Hadith describes the nation of Muhammad صلى الله عليه وسلم as an ummah that has been granted mercy in the Hereafter. It also says that its torment in this world is at the hands of one another. Then the Hadith mentions a scene on the Day of Resurrection: each Muslim man will be given a man from among the idolaters, and it will be said that this is his ransom from the Fire. The core topic is mercy and salvation from the Fire. This Hadith about the ummah being granted mercy should be read with care, using only the wording given. It does not tell a person to be careless about sin. It points to Allah’s mercy toward this nation and reminds readers that the final decision belongs to Allah."},"teachings":["The Prophet صلى الله عليه وسلم described this nation as granted mercy in the Hereafter.","The Hadith mentions worldly torment occurring at the hands of one another.","The text speaks of ransom from the Fire on the Day of Resurrection.","The Hadith encourages hope in Allah’s mercy without adding claims beyond the text."],"related_hadiths":[{"id":"4291","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4293","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E645" s="4" t="n"/>
@@ -15348,7 +15352,7 @@
       </c>
       <c r="D646" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s One Hundred Mercies","description":"$book_name$ $hadith_number$ - $chapter_name$. A beautiful Hadith about Allah’s hundred mercies and the mercy seen among creation."},"heading":{"title":"Hadith About Allah’s 100 Mercies","description":"This Hadith gives a simple and deep picture of Allah’s mercy. The Prophet صلى الله عليه وسلم said that Allah has one hundred degrees of mercy. One mercy has been shared among all creation, and because of it people show mercy and compassion to one another. Even wild animals show compassion to their young because of that mercy. Allah has kept back ninety-nine degrees of mercy, by which He will show mercy to His slaves on the Day of Resurrection. This Hadith about Allah’s 100 mercies teaches hope without denying accountability. The mercy we see in this world is only one part mentioned in the text. The remaining mercy is saved for the Hereafter. A believer should feel hope, gratitude, and love for Allah’s mercy."},"teachings":["Allah has one hundred degrees of mercy.","The mercy seen among people and animals comes from one mercy shared in creation.","Ninety-nine degrees of mercy are kept for the Day of Resurrection.","The Hadith encourages hope in Allah’s mercy."],"related_hadiths":[{"id":"4294","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6000","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s One Hundred Mercies","description":"$book_name$ $hadith_number$ - $chapter_name$. A beautiful Hadith about Allah’s hundred mercies and the mercy seen among creation."},"heading":{"title":"Hadith About Allah’s 100 Mercies","description":"This Hadith gives a simple and deep picture of Allah’s mercy. The Prophet صلى الله عليه وسلم said that Allah has one hundred degrees of mercy. One mercy has been shared among all creation, and because of it people show mercy and compassion to one another. Even wild animals show compassion to their young because of that mercy. Allah has kept back ninety-nine degrees of mercy, by which He will show mercy to His slaves on the Day of Resurrection. This Hadith about Allah’s 100 mercies teaches hope without denying accountability. The mercy we see in this world is only one part mentioned in the text. The remaining mercy is saved for the Hereafter. A believer should feel hope, gratitude, and love for Allah’s mercy."},"teachings":["Allah has one hundred degrees of mercy.","The mercy seen among people and animals comes from one mercy shared in creation.","Ninety-nine degrees of mercy are kept for the Day of Resurrection.","The Hadith encourages hope in Allah’s mercy."],"related_hadiths":[{"id":"4294","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"6000","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E646" s="4" t="n"/>
@@ -15371,7 +15375,7 @@
       </c>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mercy Placed on Earth","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith about Allah creating one hundred mercies and placing one mercy on earth."},"heading":{"title":"Hadith About Mercy Placed on Earth","description":"This Hadith explains that Allah created one hundred mercies when He created the heavens and the earth. He placed one mercy on earth. Through it, a mother shows compassion to her child, animals show compassion to one another, and birds show compassion too. Allah kept back ninety-nine mercies until the Day of Resurrection. When that Day comes, Allah will complete this mercy. This Hadith about mercy placed on earth helps a reader see everyday compassion as a sign of Allah’s mercy. A mother caring for her child and animals caring for one another are not small things. They are examples given in the Hadith. The text leads the heart to hope in Allah’s mercy while remembering the Day of Resurrection."},"teachings":["Allah created one hundred mercies when He created the heavens and the earth.","One mercy was placed on earth and appears in compassion among creation.","Mothers, animals, and birds are examples mentioned in the Hadith.","Ninety-nine mercies are kept until the Day of Resurrection."],"related_hadiths":[{"id":"4293","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2753","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mercy Placed on Earth","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith about Allah creating one hundred mercies and placing one mercy on earth."},"heading":{"title":"Hadith About Mercy Placed on Earth","description":"This Hadith explains that Allah created one hundred mercies when He created the heavens and the earth. He placed one mercy on earth. Through it, a mother shows compassion to her child, animals show compassion to one another, and birds show compassion too. Allah kept back ninety-nine mercies until the Day of Resurrection. When that Day comes, Allah will complete this mercy. This Hadith about mercy placed on earth helps a reader see everyday compassion as a sign of Allah’s mercy. A mother caring for her child and animals caring for one another are not small things. They are examples given in the Hadith. The text leads the heart to hope in Allah’s mercy while remembering the Day of Resurrection."},"teachings":["Allah created one hundred mercies when He created the heavens and the earth.","One mercy was placed on earth and appears in compassion among creation.","Mothers, animals, and birds are examples mentioned in the Hadith.","Ninety-nine mercies are kept until the Day of Resurrection."],"related_hadiths":[{"id":"4293","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"2753","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E647" s="4" t="n"/>
@@ -15394,7 +15398,7 @@
       </c>
       <c r="D648" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | My Mercy Prevails Over My Wrath","description":"$book_name$ $hadith_number$ - $chapter_name$. A short and powerful Hadith about Allah decreeing that His mercy prevails over His wrath."},"heading":{"title":"Hadith About Allah’s Mercy Prevailing Over His Wrath","description":"This Hadith is short, clear, and full of hope. The Messenger of Allah صلى الله عليه وسلم said that when Allah created the universe, He decreed for Himself: My mercy prevails over My wrath. The core topic is Allah’s mercy. The Hadith does not remove fear of Allah or accountability, but it gives the believer a strong reason to hope in Allah. It teaches that mercy is not a small matter in the way Allah deals with His creation. This Hadith about Allah’s mercy is often searched because its words are easy to remember and deeply comforting. The safe way to understand it is to keep both meanings together: Allah is just, and His mercy prevails over His wrath as stated in the Hadith."},"teachings":["Allah decreed for Himself that His mercy prevails over His wrath.","The Hadith gives believers a strong reason for hope.","Allah’s mercy is central in how He deals with creation.","Hope in mercy should stay connected with respect and fear of Allah."],"related_hadiths":[{"id":"4293","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4294","book_id":"6","label":"Sunan Ibn Majah"},{"id":"7404","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | My Mercy Prevails Over My Wrath","description":"$book_name$ $hadith_number$ - $chapter_name$. A short and powerful Hadith about Allah decreeing that His mercy prevails over His wrath."},"heading":{"title":"Hadith About Allah’s Mercy Prevailing Over His Wrath","description":"This Hadith is short, clear, and full of hope. The Messenger of Allah صلى الله عليه وسلم said that when Allah created the universe, He decreed for Himself: My mercy prevails over My wrath. The core topic is Allah’s mercy. The Hadith does not remove fear of Allah or accountability, but it gives the believer a strong reason to hope in Allah. It teaches that mercy is not a small matter in the way Allah deals with His creation. This Hadith about Allah’s mercy is often searched because its words are easy to remember and deeply comforting. The safe way to understand it is to keep both meanings together: Allah is just, and His mercy prevails over His wrath as stated in the Hadith."},"teachings":["Allah decreed for Himself that His mercy prevails over His wrath.","The Hadith gives believers a strong reason for hope.","Allah’s mercy is central in how He deals with creation.","Hope in mercy should stay connected with respect and fear of Allah."],"related_hadiths":[{"id":"4293","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4294","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"7404","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E648" s="4" t="n"/>
@@ -15417,7 +15421,7 @@
       </c>
       <c r="D649" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Right Over His Slaves","description":"$book_name$ $hadith_number$ - $chapter_name$. A key Hadith about worshipping Allah alone and not associating anything with Him."},"heading":{"title":"Hadith About Tawhid: Allah’s Right Over His Slaves","description":"This Hadith explains the foundation of faith in a very simple way. The Prophet صلى الله عليه وسلم asked Mu’adh if he knew Allah’s right over His slaves and the slaves’ right over Allah. Mu’adh answered with respect: Allah and His Messenger know best. The Prophet صلى الله عليه وسلم then said that Allah’s right over His slaves is that they worship Him and do not associate anything with Him. He also said that the right of the slaves over Allah, if they do that, is that He should not punish them. This Hadith about Tawhid is direct and easy to understand. Worship belongs to Allah alone. The text links safety from punishment with worshipping Allah without shirk. It is a central teaching for every Muslim."},"teachings":["Allah’s right is that His slaves worship Him alone.","The Hadith clearly forbids associating anything with Allah.","Mu’adh showed humility by saying Allah and His Messenger know best.","The text links not being punished with fulfilling Tawhid."],"related_hadiths":[{"id":"4299","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4300","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2856","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Right Over His Slaves","description":"$book_name$ $hadith_number$ - $chapter_name$. A key Hadith about worshipping Allah alone and not associating anything with Him."},"heading":{"title":"Hadith About Tawhid: Allah’s Right Over His Slaves","description":"This Hadith explains the foundation of faith in a very simple way. The Prophet صلى الله عليه وسلم asked Mu’adh if he knew Allah’s right over His slaves and the slaves’ right over Allah. Mu’adh answered with respect: Allah and His Messenger know best. The Prophet صلى الله عليه وسلم then said that Allah’s right over His slaves is that they worship Him and do not associate anything with Him. He also said that the right of the slaves over Allah, if they do that, is that He should not punish them. This Hadith about Tawhid is direct and easy to understand. Worship belongs to Allah alone. The text links safety from punishment with worshipping Allah without shirk. It is a central teaching for every Muslim."},"teachings":["Allah’s right is that His slaves worship Him alone.","The Hadith clearly forbids associating anything with Allah.","Mu’adh showed humility by saying Allah and His Messenger know best.","The text links not being punished with fulfilling Tawhid."],"related_hadiths":[{"id":"4299","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4300","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"2856","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E649" s="4" t="n"/>
@@ -15440,7 +15444,7 @@
       </c>
       <c r="D650" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Mercy and La Ilaha Illallah","description":"$book_name$ $hadith_number$ - $chapter_name$. A moving Hadith showing Allah’s mercy and warning against rebellion and refusing Tawhid."},"heading":{"title":"Hadith About Allah Being More Merciful Than a Mother","description":"This Hadith shows Allah’s mercy through a scene people can understand. A woman was near an oven with her son. When the flames rose, she moved him away. She asked the Prophet صلى الله عليه وسلم whether Allah is the Most Merciful and whether He is more merciful to His slaves than a mother to her child. The Prophet صلى الله عليه وسلم said yes. She then said that a mother would not throw her child into the fire. The Messenger of Allah صلى الله عليه وسلم wept, then said that Allah does not punish any of His slaves except the defiant and rebellious one who rebels against Allah and refuses to say La ilaha illallah. This Hadith about Allah’s mercy and La ilaha illallah brings hope, but it also warns against rejecting Tawhid."},"teachings":["Allah is more merciful to His slaves than a mother to her child.","The Prophet صلى الله عليه وسلم was moved by the woman’s question and wept.","The Hadith warns against defiance, rebellion, and refusing La ilaha illallah.","Mercy and Tawhid are both central in the text."],"related_hadiths":[{"id":"4293","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4296","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Mercy and La Ilaha Illallah","description":"$book_name$ $hadith_number$ - $chapter_name$. A moving Hadith showing Allah’s mercy and warning against rebellion and refusing Tawhid."},"heading":{"title":"Hadith About Allah Being More Merciful Than a Mother","description":"This Hadith shows Allah’s mercy through a scene people can understand. A woman was near an oven with her son. When the flames rose, she moved him away. She asked the Prophet صلى الله عليه وسلم whether Allah is the Most Merciful and whether He is more merciful to His slaves than a mother to her child. The Prophet صلى الله عليه وسلم said yes. She then said that a mother would not throw her child into the fire. The Messenger of Allah صلى الله عليه وسلم wept, then said that Allah does not punish any of His slaves except the defiant and rebellious one who rebels against Allah and refuses to say La ilaha illallah. This Hadith about Allah’s mercy and La ilaha illallah brings hope, but it also warns against rejecting Tawhid."},"teachings":["Allah is more merciful to His slaves than a mother to her child.","The Prophet صلى الله عليه وسلم was moved by the woman’s question and wept.","The Hadith warns against defiance, rebellion, and refusing La ilaha illallah.","Mercy and Tawhid are both central in the text."],"related_hadiths":[{"id":"4293","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4296","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E650" s="4" t="n"/>
@@ -15463,7 +15467,7 @@
       </c>
       <c r="D651" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Doomed One and Disobedience","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning Hadith defining the doomed person as one who avoids obedience and does not leave sin."},"heading":{"title":"Hadith About the Doomed One Who Enters Hell","description":"This Hadith is a warning about a life empty of obedience to Allah and full of sin. The Messenger of Allah صلى الله عليه وسلم said that no one will enter Hell except one who is doomed. When he was asked who the doomed one is, he said it is the one who never does any act of obedience toward Allah and never omits any act of sin. The core topic is obedience and warning from Hell. This Hadith about the doomed one does not speak about a believer who slips and repents, nor does it discuss every case of sin. It gives a clear description from the text: leaving obedience and not leaving sin. The lesson is to take obedience seriously and not become comfortable with disobedience."},"teachings":["The Hadith warns against a life without obedience to Allah.","The doomed person is described as never leaving sin.","The text encourages taking obedience seriously.","The Hadith should make a person avoid becoming careless with sin."],"related_hadiths":[{"id":"4296","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4299","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4300","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Doomed One and Disobedience","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning Hadith defining the doomed person as one who avoids obedience and does not leave sin."},"heading":{"title":"Hadith About the Doomed One Who Enters Hell","description":"This Hadith is a warning about a life empty of obedience to Allah and full of sin. The Messenger of Allah صلى الله عليه وسلم said that no one will enter Hell except one who is doomed. When he was asked who the doomed one is, he said it is the one who never does any act of obedience toward Allah and never omits any act of sin. The core topic is obedience and warning from Hell. This Hadith about the doomed one does not speak about a believer who slips and repents, nor does it discuss every case of sin. It gives a clear description from the text: leaving obedience and not leaving sin. The lesson is to take obedience seriously and not become comfortable with disobedience."},"teachings":["The Hadith warns against a life without obedience to Allah.","The doomed person is described as never leaving sin.","The text encourages taking obedience seriously.","The Hadith should make a person avoid becoming careless with sin."],"related_hadiths":[{"id":"4296","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4299","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4300","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E651" s="4" t="n"/>
@@ -15486,7 +15490,7 @@
       </c>
       <c r="D652" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Taqwa, Tawhid, and Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith Qudsi about fearing Allah, avoiding shirk, and Allah being the One Who forgives."},"heading":{"title":"Hadith About Taqwa and Forgiveness Through Tawhid","description":"This Hadith explains the verse that Allah is the One deserving to be feared and the One Who forgives. The Prophet صلى الله عليه وسلم said that Allah says He is the One Who deserves to be feared, so no other god should be taken alongside Him. Whoever avoids appointing another god alongside Allah, then Allah is the One Who should forgive him. Another chain reports a similar wording: Allah is worthy that no partner be associated with Him, and He is worthy to forgive the one who avoids shirk. This Hadith about taqwa and forgiveness keeps the message focused on Tawhid. Fear of Allah is not empty fear; it means not placing another god with Him. Forgiveness is linked in the text to avoiding shirk."},"teachings":["Allah alone deserves to be feared and obeyed.","The Hadith clearly warns against shirk.","Forgiveness is linked with avoiding associating partners with Allah.","Taqwa in this text includes keeping worship for Allah alone."],"related_hadiths":[{"id":"4296","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4300","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Taqwa, Tawhid, and Forgiveness","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith Qudsi about fearing Allah, avoiding shirk, and Allah being the One Who forgives."},"heading":{"title":"Hadith About Taqwa and Forgiveness Through Tawhid","description":"This Hadith explains the verse that Allah is the One deserving to be feared and the One Who forgives. The Prophet صلى الله عليه وسلم said that Allah says He is the One Who deserves to be feared, so no other god should be taken alongside Him. Whoever avoids appointing another god alongside Allah, then Allah is the One Who should forgive him. Another chain reports a similar wording: Allah is worthy that no partner be associated with Him, and He is worthy to forgive the one who avoids shirk. This Hadith about taqwa and forgiveness keeps the message focused on Tawhid. Fear of Allah is not empty fear; it means not placing another god with Him. Forgiveness is linked in the text to avoiding shirk."},"teachings":["Allah alone deserves to be feared and obeyed.","The Hadith clearly warns against shirk.","Forgiveness is linked with avoiding associating partners with Allah.","Taqwa in this text includes keeping worship for Allah alone."],"related_hadiths":[{"id":"4296","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4300","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E652" s="4" t="n"/>
@@ -15509,7 +15513,7 @@
       </c>
       <c r="D653" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Card of Shahadah on the Scale","description":"$book_name$ $hadith_number$ - $chapter_name$. A powerful Hadith about the Shahadah card outweighing ninety-nine scrolls on the Balance."},"heading":{"title":"Hadith About the Shahadah Card Outweighing the Scrolls","description":"This Hadith describes a man from the Prophet’s nation being called before all creation on the Day of Resurrection. Ninety-nine scrolls of deeds are spread out for him, each stretching as far as the eye can see. He does not deny them, and he is told that he will not be treated unjustly. Then a card is brought out with the testimony: none has the right to be worshipped but Allah, and Muhammad is His slave and Messenger. The man wonders what this card can do beside the scrolls. Then the scrolls are placed on one side of the Balance and the card on the other. The card weighs heavy. This Hadith about the Shahadah card shows the weight of sincere Tawhid and the justice of Allah."},"teachings":["Every deed is brought forward with justice on the Day of Resurrection.","The man is told that he will not be treated unjustly.","The Shahadah is shown as very weighty on the Balance.","The Hadith points to the great value of Tawhid and belief in the Messenger صلى الله عليه وسلم."],"related_hadiths":[{"id":"4296","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4299","book_id":"6","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Card of Shahadah on the Scale","description":"$book_name$ $hadith_number$ - $chapter_name$. A powerful Hadith about the Shahadah card outweighing ninety-nine scrolls on the Balance."},"heading":{"title":"Hadith About the Shahadah Card Outweighing the Scrolls","description":"This Hadith describes a man from the Prophet’s nation being called before all creation on the Day of Resurrection. Ninety-nine scrolls of deeds are spread out for him, each stretching as far as the eye can see. He does not deny them, and he is told that he will not be treated unjustly. Then a card is brought out with the testimony: none has the right to be worshipped but Allah, and Muhammad is His slave and Messenger. The man wonders what this card can do beside the scrolls. Then the scrolls are placed on one side of the Balance and the card on the other. The card weighs heavy. This Hadith about the Shahadah card shows the weight of sincere Tawhid and the justice of Allah."},"teachings":["Every deed is brought forward with justice on the Day of Resurrection.","The man is told that he will not be treated unjustly.","The Shahadah is shown as very weighty on the Balance.","The Hadith points to the great value of Tawhid and belief in the Messenger صلى الله عليه وسلم."],"related_hadiths":[{"id":"4296","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4299","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"4295","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E653" s="4" t="n"/>
@@ -15532,7 +15536,7 @@
       </c>
       <c r="D654" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Cistern","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn about the Prophet’s Cistern, its bright water, countless vessels, and followers on Resurrection Day."},"heading":{"title":"Prophet Muhammad Cistern Hadith: A Hopeful Scene on the Day of Resurrection","description":"This Hadith about the Prophet’s Cistern gives a clear and powerful picture of honor on the Day of Resurrection. The Prophet صلى الله عليه وسلم describes a Cistern as wide as the distance between the Ka’bah and Baitul-Maqdis. Its color is whiter than milk, and its vessels are as many as the stars. The main message is simple: the Prophet صلى الله عليه وسلم will have a great following on that Day, and his Cistern is shown as a special gift connected to him and his nation. The Hadith does not ask us to guess details beyond the text. It points our hearts to the Hereafter, the Prophet’s honor, and the beauty of what Allah has prepared."},"teachings":["The Prophet صلى الله عليه وسلم described his Cistern as vast and bright.","The vessels of the Cistern are described as being as numerous as the stars.","The Hadith highlights the large number of followers of the Prophet صلى الله عليه وسلم on the Day of Resurrection."],"related_hadiths":[{"id":"6579","book_id":"1","label":"Sahih Bukhari"},{"id":"6580","book_id":"1","label":"Sahih Bukhari"},{"id":"2300","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Cistern","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn about the Prophet’s Cistern, its bright water, countless vessels, and followers on Resurrection Day."},"heading":{"title":"Prophet Muhammad Cistern Hadith: A Hopeful Scene on the Day of Resurrection","description":"This Hadith about the Prophet’s Cistern gives a clear and powerful picture of honor on the Day of Resurrection. The Prophet صلى الله عليه وسلم describes a Cistern as wide as the distance between the Ka’bah and Baitul-Maqdis. Its color is whiter than milk, and its vessels are as many as the stars. The main message is simple: the Prophet صلى الله عليه وسلم will have a great following on that Day, and his Cistern is shown as a special gift connected to him and his nation. The Hadith does not ask us to guess details beyond the text. It points our hearts to the Hereafter, the Prophet’s honor, and the beauty of what Allah has prepared."},"teachings":["The Prophet صلى الله عليه وسلم described his Cistern as vast and bright.","The vessels of the Cistern are described as being as numerous as the stars.","The Hadith highlights the large number of followers of the Prophet صلى الله عليه وسلم on the Day of Resurrection."],"related_hadiths":[{"id":"6579","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6580","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2300","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E654" s="4" t="n"/>
@@ -15555,7 +15559,7 @@
       </c>
       <c r="D655" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recognized by Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith links the Cistern with radiant traces of wudu and the Prophet’s recognition of his people."},"heading":{"title":"Hadith About Wudu Marks and the Prophet’s Cistern","description":"This Hadith connects the Prophet’s Cistern with the signs of ablution. The Prophet صلى الله عليه وسلم describes his Cistern as wider than the distance between Ailah and Aden. Its vessels are more than the stars, and its drink is whiter than milk and sweeter than honey. He also says that some men will be driven away from it, like strange camels are driven away from a person’s water. When asked if he will recognize his people, he says yes. They will come with radiant faces, hands, and feet because of the traces of wudu. The core lesson is that ablution has a visible honor on the Day of Resurrection, as stated in the Hadith."},"teachings":["The Cistern is descr